--- a/Result/checksun_type/PET膜.xlsx
+++ b/Result/checksun_type/PET膜.xlsx
@@ -878,12 +878,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>-0.95</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>192.0</t>
+          <t>213.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>47.05</t>
+          <t>46.6</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -903,17 +903,17 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>29.99</t>
+          <t>26.53</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -923,7 +923,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-5.43</t>
+          <t>-6.33</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -988,17 +988,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>3.88</t>
+          <t>4.31</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,72 +1014,72 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>311</t>
+          <t>213</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>57.45</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>71.82</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>-1.17</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-3.21</t>
+          <t>-2.88</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>47.23</t>
+          <t>47.15</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>46.15</t>
+          <t>46.22</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>47.68</t>
+          <t>47.59</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>47.48</t>
+          <t>47.5</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>100.64</t>
+          <t>98.12</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.00</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-106.58</t>
+          <t>-105.28</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1099,41 +1099,41 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>77474.67438494935</t>
+          <t>77384.26950867052</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>9018.0</t>
+          <t>9943.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>18831.4</t>
+          <t>18959.2</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>14486.8</t>
+          <t>14983.4</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>18676.0</t>
+          <t>17743.28</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>4344</t>
+          <t>3975</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-128.211286383547</t>
+          <t>-74.62310011749315</t>
         </is>
       </c>
       <c r="BC2" t="n">
-        <v>690.3200000000001</v>
+        <v>220.11</v>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>-3.49</t>
+          <t>-4.41</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1182,17 +1182,17 @@
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>8.591010580024943</t>
+          <t>-1.004452687200723</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>-14.93484897076815</t>
+          <t>11.92388165594906</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
         <is>
-          <t>1.909594416710131</t>
+          <t>2.060463205899802</t>
         </is>
       </c>
       <c r="BP2" t="inlineStr">
@@ -1202,17 +1202,17 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>1.89</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>5.88</t>
+          <t>5.94</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
@@ -1222,7 +1222,7 @@
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>10.63</t>
+          <t>10.52</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="BX2" t="inlineStr">
         <is>
-          <t>44.82</t>
+          <t>43.93</t>
         </is>
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>4432</t>
+          <t>4385</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
@@ -1257,27 +1257,27 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>其他電子業右上上櫃</t>
+          <t>其他電子業平上櫃</t>
         </is>
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>46.5</t>
+          <t>47.15</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>47.5</t>
+          <t>47.2</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>46.35</t>
+          <t>46.4</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>47.05</t>
+          <t>46.6</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1309,12 +1309,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-1.05</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>311.0</t>
+          <t>192.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>47.1</t>
+          <t>47.05</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1334,17 +1334,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>33.05</t>
+          <t>29.99</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1354,7 +1354,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -1409,7 +1409,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-5.33</t>
+          <t>-5.43</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1419,17 +1419,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>6.29</t>
+          <t>3.88</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-0.95</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1445,72 +1445,72 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>311</t>
+          <t>213</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>93.33</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>2.36</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-3.53</t>
+          <t>-3.21</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>0.60</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>47.15</t>
+          <t>47.23</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>46.06</t>
+          <t>46.15</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>47.75</t>
+          <t>47.68</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>47.47</t>
+          <t>47.48</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>89.68</t>
+          <t>100.64</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-108.23</t>
+          <t>-106.58</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,41 +1530,41 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>77474.67438494935</t>
+          <t>77384.26950867052</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>14718.0</t>
+          <t>9018.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>18629.2</t>
+          <t>18831.4</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>14001.9</t>
+          <t>14486.8</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>20406.5</t>
+          <t>18676.0</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>4627</t>
+          <t>4344</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-277.0356783742832</t>
+          <t>-128.211286383547</t>
         </is>
       </c>
       <c r="BC3" t="n">
-        <v>1436.51</v>
+        <v>690.3200000000001</v>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>-3.38</t>
+          <t>-3.49</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1613,17 +1613,17 @@
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>8.591010580024943</t>
+          <t>-1.004452687200723</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>-14.93484897076815</t>
+          <t>11.92388165594906</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
         <is>
-          <t>1.909594416710131</t>
+          <t>2.060463205899802</t>
         </is>
       </c>
       <c r="BP3" t="inlineStr">
@@ -1633,7 +1633,7 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1643,7 +1643,7 @@
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>5.88</t>
+          <t>5.94</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1653,7 +1653,7 @@
       </c>
       <c r="BU3" t="inlineStr">
         <is>
-          <t>10.63</t>
+          <t>10.52</t>
         </is>
       </c>
       <c r="BV3" t="inlineStr">
@@ -1668,12 +1668,12 @@
       </c>
       <c r="BX3" t="inlineStr">
         <is>
-          <t>44.82</t>
+          <t>43.93</t>
         </is>
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>4432</t>
+          <t>4385</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1688,27 +1688,27 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>其他電子業右上上櫃</t>
+          <t>其他電子業平上櫃</t>
         </is>
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>47.6</t>
+          <t>46.5</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>47.8</t>
+          <t>47.5</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>46.85</t>
+          <t>46.35</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>47.1</t>
+          <t>47.05</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1740,12 +1740,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>-1.05</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>474.0</t>
+          <t>311.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>47.6</t>
+          <t>47.1</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1765,17 +1765,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-1.06</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>50.85</t>
+          <t>33.05</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1785,7 +1785,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-4.32</t>
+          <t>-5.33</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1850,17 +1850,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>9.59</t>
+          <t>6.29</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-0.95</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1876,72 +1876,72 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>311</t>
+          <t>213</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>93.33</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>2.67</t>
+          <t>2.36</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-3.93</t>
+          <t>-3.53</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.60</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>47.13</t>
+          <t>47.15</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>45.9</t>
+          <t>46.06</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>47.78</t>
+          <t>47.75</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>47.45</t>
+          <t>47.47</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>79.21</t>
+          <t>89.68</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1951,7 +1951,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-110.08</t>
+          <t>-108.23</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1961,41 +1961,41 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>77474.67438494935</t>
+          <t>77384.26950867052</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>22600.0</t>
+          <t>14718.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>20034.4</t>
+          <t>18629.2</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>13280.9</t>
+          <t>14001.9</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>20741.92</t>
+          <t>20406.5</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>6753</t>
+          <t>4627</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-588.5886282543895</t>
+          <t>-277.0356783742832</t>
         </is>
       </c>
       <c r="BC4" t="n">
-        <v>1840.46</v>
+        <v>1436.51</v>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>-2.36</t>
+          <t>-3.38</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2044,37 +2044,37 @@
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>8.591010580024943</t>
+          <t>-1.004452687200723</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>-14.93484897076815</t>
+          <t>11.92388165594906</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>1.909594416710131</t>
+          <t>2.060463205899802</t>
         </is>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>5.88</t>
+          <t>5.94</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>10.63</t>
+          <t>10.52</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
@@ -2099,12 +2099,12 @@
       </c>
       <c r="BX4" t="inlineStr">
         <is>
-          <t>44.82</t>
+          <t>43.93</t>
         </is>
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>4432</t>
+          <t>4385</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -2119,27 +2119,27 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>其他電子業右上上櫃</t>
+          <t>其他電子業平上櫃</t>
         </is>
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>47.85</t>
+          <t>47.6</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>48.1</t>
+          <t>47.8</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>47.25</t>
+          <t>46.85</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>47.6</t>
+          <t>47.1</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>812.0</t>
+          <t>474.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>47.4</t>
+          <t>47.6</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2196,17 +2196,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-0.64</t>
+          <t>-2.15</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>43.35</t>
+          <t>50.85</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2216,7 +2216,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-4.72</t>
+          <t>-4.32</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2281,17 +2281,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16.43</t>
+          <t>9.59</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2307,7 +2307,7 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>311</t>
+          <t>213</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
@@ -2317,62 +2317,62 @@
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>93.86</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>2.67</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-4.23</t>
+          <t>-3.93</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>46.66</t>
+          <t>47.13</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>45.74</t>
+          <t>45.9</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>47.76</t>
+          <t>47.78</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>47.42</t>
+          <t>47.45</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>59.88</t>
+          <t>79.21</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-112.07</t>
+          <t>-110.08</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2392,41 +2392,41 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>77474.67438494935</t>
+          <t>77384.26950867052</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>38517.0</t>
+          <t>22600.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>16959.2</t>
+          <t>20034.4</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>11830.5</t>
+          <t>13280.9</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>20783.02</t>
+          <t>20741.92</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>5128</t>
+          <t>6753</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-1030.234332074163</t>
+          <t>-588.5886282543895</t>
         </is>
       </c>
       <c r="BC5" t="n">
-        <v>1507.31</v>
+        <v>1840.46</v>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
@@ -2445,7 +2445,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>-2.77</t>
+          <t>-2.36</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2475,22 +2475,22 @@
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>8.591010580024943</t>
+          <t>-1.004452687200723</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>-14.93484897076815</t>
+          <t>11.92388165594906</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>1.909594416710131</t>
+          <t>2.060463205899802</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
@@ -2500,12 +2500,12 @@
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>5.88</t>
+          <t>5.94</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2515,7 +2515,7 @@
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>10.63</t>
+          <t>10.52</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="BX5" t="inlineStr">
         <is>
-          <t>44.82</t>
+          <t>43.93</t>
         </is>
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>4432</t>
+          <t>4385</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
@@ -2550,27 +2550,27 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>其他電子業右上上櫃</t>
+          <t>其他電子業平上櫃</t>
         </is>
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>47.5</t>
+          <t>47.85</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>47.85</t>
+          <t>48.1</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>46.5</t>
+          <t>47.25</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>47.4</t>
+          <t>47.6</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2602,12 +2602,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>199.0</t>
+          <t>812.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2617,7 +2617,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>47.0</t>
+          <t>47.4</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2627,17 +2627,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>-1.72</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>32.28</t>
+          <t>43.35</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2647,7 +2647,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -2702,7 +2702,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-5.53</t>
+          <t>-4.72</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2712,17 +2712,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>4.03</t>
+          <t>16.43</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2738,7 +2738,7 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>311</t>
+          <t>213</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
@@ -2753,57 +2753,57 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-4.34</t>
+          <t>-4.23</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>46.2</t>
+          <t>46.66</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>45.67</t>
+          <t>45.74</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>47.75</t>
+          <t>47.76</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>47.39</t>
+          <t>47.42</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>43.77</t>
+          <t>59.88</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2813,7 +2813,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-113.88</t>
+          <t>-112.07</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2823,41 +2823,41 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>77474.67438494935</t>
+          <t>77384.26950867052</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>9304.0</t>
+          <t>38517.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>11007.6</t>
+          <t>16959.2</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>8321.2</t>
+          <t>11830.5</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>21296.56</t>
+          <t>20783.02</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>2686</t>
+          <t>5128</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-1491.606690671351</t>
+          <t>-1030.234332074163</t>
         </is>
       </c>
       <c r="BC6" t="n">
-        <v>-727.84</v>
+        <v>1507.31</v>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>-3.59</t>
+          <t>-2.77</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -2906,37 +2906,37 @@
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>8.591010580024943</t>
+          <t>-1.004452687200723</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
         <is>
-          <t>-14.93484897076815</t>
+          <t>11.92388165594906</t>
         </is>
       </c>
       <c r="BO6" t="inlineStr">
         <is>
-          <t>1.909594416710131</t>
+          <t>2.060463205899802</t>
         </is>
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>5.88</t>
+          <t>5.94</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BU6" t="inlineStr">
         <is>
-          <t>10.63</t>
+          <t>10.52</t>
         </is>
       </c>
       <c r="BV6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BX6" t="inlineStr">
         <is>
-          <t>44.82</t>
+          <t>43.93</t>
         </is>
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>4432</t>
+          <t>4385</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
@@ -2981,27 +2981,27 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>其他電子業右上上櫃</t>
+          <t>其他電子業平上櫃</t>
         </is>
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>46.85</t>
+          <t>47.5</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>47.1</t>
+          <t>47.85</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>46.25</t>
+          <t>46.5</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>47.0</t>
+          <t>47.4</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>170.0</t>
+          <t>199.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>46.65</t>
+          <t>47.0</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
+          <t>-0.86</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
           <t>0.96</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>0.72</t>
-        </is>
-      </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>23.31</t>
+          <t>32.28</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-6.23</t>
+          <t>-5.53</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>3.44</t>
+          <t>4.03</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-2.14</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3169,72 +3169,72 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>311</t>
+          <t>213</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>81.58</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>65.79</t>
+          <t>93.86</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-4.26</t>
+          <t>-4.34</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>45.88</t>
+          <t>46.2</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>45.73</t>
+          <t>45.67</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>47.76</t>
+          <t>47.75</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>47.37</t>
+          <t>47.39</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>31.68</t>
+          <t>43.77</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3244,7 +3244,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-115.40</t>
+          <t>-113.88</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3254,41 +3254,41 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>77474.67438494935</t>
+          <t>77384.26950867052</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>8007.0</t>
+          <t>9304.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>10142.2</t>
+          <t>11007.6</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>8225.2</t>
+          <t>8321.2</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>21859.62</t>
+          <t>21296.56</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>1917</t>
+          <t>2686</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-1630.473518740948</t>
+          <t>-1491.606690671351</t>
         </is>
       </c>
       <c r="BC7" t="n">
-        <v>-764.96</v>
+        <v>-727.84</v>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>-4.31</t>
+          <t>-3.59</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3337,22 +3337,22 @@
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>8.591010580024943</t>
+          <t>-1.004452687200723</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
         <is>
-          <t>-14.93484897076815</t>
+          <t>11.92388165594906</t>
         </is>
       </c>
       <c r="BO7" t="inlineStr">
         <is>
-          <t>1.909594416710131</t>
+          <t>2.060463205899802</t>
         </is>
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
@@ -3362,12 +3362,12 @@
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>1.89</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>5.88</t>
+          <t>5.94</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3377,7 +3377,7 @@
       </c>
       <c r="BU7" t="inlineStr">
         <is>
-          <t>10.63</t>
+          <t>10.52</t>
         </is>
       </c>
       <c r="BV7" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="BX7" t="inlineStr">
         <is>
-          <t>44.82</t>
+          <t>43.93</t>
         </is>
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>4432</t>
+          <t>4385</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3412,27 +3412,27 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>其他電子業右上上櫃</t>
+          <t>其他電子業平上櫃</t>
         </is>
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>47.8</t>
+          <t>46.85</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>47.8</t>
+          <t>47.1</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>46.5</t>
+          <t>46.25</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>46.65</t>
+          <t>47.0</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3464,12 +3464,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>3.8</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>464.0</t>
+          <t>170.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>47.0</t>
+          <t>46.65</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3489,17 +3489,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>15.69</t>
+          <t>23.31</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3509,7 +3509,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -3564,7 +3564,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-5.53</t>
+          <t>-6.23</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3574,17 +3574,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>9.39</t>
+          <t>3.44</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>-2.14</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3600,270 +3600,270 @@
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>311</t>
+          <t>213</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>81.58</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>38.6</t>
+          <t>65.79</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-0.37</t>
+          <t>0.33</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-4.22</t>
+          <t>-4.26</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>45.62</t>
+          <t>45.88</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>45.79</t>
+          <t>45.73</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
+          <t>47.76</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>47.37</t>
+        </is>
+      </c>
+      <c r="AP8" t="inlineStr">
+        <is>
+          <t>31.68</t>
+        </is>
+      </c>
+      <c r="AQ8" t="inlineStr">
+        <is>
+          <t>-0.45</t>
+        </is>
+      </c>
+      <c r="AR8" t="inlineStr">
+        <is>
+          <t>-0.66</t>
+        </is>
+      </c>
+      <c r="AS8" t="inlineStr">
+        <is>
+          <t>4.28</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr">
+        <is>
+          <t>-115.40</t>
+        </is>
+      </c>
+      <c r="AU8" t="inlineStr">
+        <is>
+          <t>2025/10/28</t>
+        </is>
+      </c>
+      <c r="AV8" t="inlineStr">
+        <is>
+          <t>77384.26950867052</t>
+        </is>
+      </c>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>8007.0</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>10142.2</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>8225.2</t>
+        </is>
+      </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>21859.62</t>
+        </is>
+      </c>
+      <c r="BA8" t="inlineStr">
+        <is>
+          <t>1917</t>
+        </is>
+      </c>
+      <c r="BB8" t="inlineStr">
+        <is>
+          <t>-1630.473518740948</t>
+        </is>
+      </c>
+      <c r="BC8" t="n">
+        <v>-764.96</v>
+      </c>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BE8" t="inlineStr">
+        <is>
+          <t>48.75</t>
+        </is>
+      </c>
+      <c r="BF8" t="inlineStr">
+        <is>
+          <t>2025/08/25</t>
+        </is>
+      </c>
+      <c r="BG8" t="inlineStr">
+        <is>
+          <t>-4.31</t>
+        </is>
+      </c>
+      <c r="BH8" t="inlineStr">
+        <is>
+          <t>岱稜</t>
+        </is>
+      </c>
+      <c r="BI8" t="inlineStr">
+        <is>
+          <t>岱稜</t>
+        </is>
+      </c>
+      <c r="BJ8" t="inlineStr">
+        <is>
+          <t>其他電子業</t>
+        </is>
+      </c>
+      <c r="BK8" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BL8" t="inlineStr">
+        <is>
+          <t>1.08</t>
+        </is>
+      </c>
+      <c r="BM8" t="inlineStr">
+        <is>
+          <t>-1.004452687200723</t>
+        </is>
+      </c>
+      <c r="BN8" t="inlineStr">
+        <is>
+          <t>11.92388165594906</t>
+        </is>
+      </c>
+      <c r="BO8" t="inlineStr">
+        <is>
+          <t>2.060463205899802</t>
+        </is>
+      </c>
+      <c r="BP8" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BQ8" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BR8" t="inlineStr">
+        <is>
+          <t>1.89</t>
+        </is>
+      </c>
+      <c r="BS8" t="inlineStr">
+        <is>
+          <t>5.94</t>
+        </is>
+      </c>
+      <c r="BT8" t="inlineStr">
+        <is>
+          <t>8.56</t>
+        </is>
+      </c>
+      <c r="BU8" t="inlineStr">
+        <is>
+          <t>10.52</t>
+        </is>
+      </c>
+      <c r="BV8" t="inlineStr">
+        <is>
+          <t>33.67%</t>
+        </is>
+      </c>
+      <c r="BW8" t="inlineStr">
+        <is>
+          <t>12.48%</t>
+        </is>
+      </c>
+      <c r="BX8" t="inlineStr">
+        <is>
+          <t>43.93</t>
+        </is>
+      </c>
+      <c r="BY8" t="inlineStr">
+        <is>
+          <t>4385</t>
+        </is>
+      </c>
+      <c r="BZ8" t="inlineStr">
+        <is>
+          <t>真空蒸鍍薄膜95.00%、光電材料5.00% (2024年)</t>
+        </is>
+      </c>
+      <c r="CA8" t="inlineStr">
+        <is>
+          <t>岱稜-其他電子業-上櫃</t>
+        </is>
+      </c>
+      <c r="CB8" t="inlineStr">
+        <is>
+          <t>其他電子業平上櫃</t>
+        </is>
+      </c>
+      <c r="CC8" t="inlineStr">
+        <is>
           <t>47.8</t>
         </is>
       </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>47.35</t>
-        </is>
-      </c>
-      <c r="AP8" t="inlineStr">
-        <is>
-          <t>21.78</t>
-        </is>
-      </c>
-      <c r="AQ8" t="inlineStr">
-        <is>
-          <t>-0.56</t>
-        </is>
-      </c>
-      <c r="AR8" t="inlineStr">
-        <is>
-          <t>-0.71</t>
-        </is>
-      </c>
-      <c r="AS8" t="inlineStr">
-        <is>
-          <t>4.28</t>
-        </is>
-      </c>
-      <c r="AT8" t="inlineStr">
-        <is>
-          <t>-116.62</t>
-        </is>
-      </c>
-      <c r="AU8" t="inlineStr">
-        <is>
-          <t>2025/10/28</t>
-        </is>
-      </c>
-      <c r="AV8" t="inlineStr">
-        <is>
-          <t>77474.67438494935</t>
-        </is>
-      </c>
-      <c r="AW8" t="inlineStr">
-        <is>
-          <t>21744.0</t>
-        </is>
-      </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>9374.6</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr">
-        <is>
-          <t>8103.2</t>
-        </is>
-      </c>
-      <c r="AZ8" t="inlineStr">
-        <is>
-          <t>22013.86</t>
-        </is>
-      </c>
-      <c r="BA8" t="inlineStr">
-        <is>
-          <t>1271</t>
-        </is>
-      </c>
-      <c r="BB8" t="inlineStr">
-        <is>
-          <t>-1787.840342020155</t>
-        </is>
-      </c>
-      <c r="BC8" t="n">
-        <v>-651.7</v>
-      </c>
-      <c r="BD8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BE8" t="inlineStr">
-        <is>
-          <t>48.75</t>
-        </is>
-      </c>
-      <c r="BF8" t="inlineStr">
-        <is>
-          <t>2025/08/25</t>
-        </is>
-      </c>
-      <c r="BG8" t="inlineStr">
-        <is>
-          <t>-3.59</t>
-        </is>
-      </c>
-      <c r="BH8" t="inlineStr">
-        <is>
-          <t>岱稜</t>
-        </is>
-      </c>
-      <c r="BI8" t="inlineStr">
-        <is>
-          <t>岱稜</t>
-        </is>
-      </c>
-      <c r="BJ8" t="inlineStr">
-        <is>
-          <t>其他電子業</t>
-        </is>
-      </c>
-      <c r="BK8" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BL8" t="inlineStr">
-        <is>
-          <t>1.08</t>
-        </is>
-      </c>
-      <c r="BM8" t="inlineStr">
-        <is>
-          <t>8.591010580024943</t>
-        </is>
-      </c>
-      <c r="BN8" t="inlineStr">
-        <is>
-          <t>-14.93484897076815</t>
-        </is>
-      </c>
-      <c r="BO8" t="inlineStr">
-        <is>
-          <t>1.909594416710131</t>
-        </is>
-      </c>
-      <c r="BP8" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BQ8" t="inlineStr">
-        <is>
-          <t>價漲量增</t>
-        </is>
-      </c>
-      <c r="BR8" t="inlineStr">
-        <is>
-          <t>1.91</t>
-        </is>
-      </c>
-      <c r="BS8" t="inlineStr">
-        <is>
-          <t>5.88</t>
-        </is>
-      </c>
-      <c r="BT8" t="inlineStr">
-        <is>
-          <t>8.56</t>
-        </is>
-      </c>
-      <c r="BU8" t="inlineStr">
-        <is>
-          <t>10.63</t>
-        </is>
-      </c>
-      <c r="BV8" t="inlineStr">
-        <is>
-          <t>33.67%</t>
-        </is>
-      </c>
-      <c r="BW8" t="inlineStr">
-        <is>
-          <t>12.48%</t>
-        </is>
-      </c>
-      <c r="BX8" t="inlineStr">
-        <is>
-          <t>44.82</t>
-        </is>
-      </c>
-      <c r="BY8" t="inlineStr">
-        <is>
-          <t>4432</t>
-        </is>
-      </c>
-      <c r="BZ8" t="inlineStr">
-        <is>
-          <t>真空蒸鍍薄膜95.00%、光電材料5.00% (2024年)</t>
-        </is>
-      </c>
-      <c r="CA8" t="inlineStr">
-        <is>
-          <t>岱稜-其他電子業-上櫃</t>
-        </is>
-      </c>
-      <c r="CB8" t="inlineStr">
-        <is>
-          <t>其他電子業右上上櫃</t>
-        </is>
-      </c>
-      <c r="CC8" t="inlineStr">
-        <is>
-          <t>46.0</t>
-        </is>
-      </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>47.7</t>
+          <t>47.8</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>45.9</t>
+          <t>46.5</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>47.0</t>
+          <t>46.65</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>3.8</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>161.0</t>
+          <t>464.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3910,7 +3910,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>45.25</t>
+          <t>47.0</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3920,17 +3920,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>3.93</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2.94</t>
+          <t>15.69</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3940,7 +3940,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-9.05</t>
+          <t>-5.53</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4005,17 +4005,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>3.26</t>
+          <t>9.39</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4031,205 +4031,205 @@
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>311</t>
+          <t>213</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>15.79</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>9.71</t>
+          <t>38.6</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>3.02</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-1.19</t>
+          <t>-0.37</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-4.21</t>
+          <t>-4.22</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
+          <t>0.97</t>
+        </is>
+      </c>
+      <c r="AL9" t="inlineStr">
+        <is>
+          <t>45.62</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>45.79</t>
+        </is>
+      </c>
+      <c r="AN9" t="inlineStr">
+        <is>
+          <t>47.8</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>47.35</t>
+        </is>
+      </c>
+      <c r="AP9" t="inlineStr">
+        <is>
+          <t>21.78</t>
+        </is>
+      </c>
+      <c r="AQ9" t="inlineStr">
+        <is>
+          <t>-0.56</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>-0.71</t>
+        </is>
+      </c>
+      <c r="AS9" t="inlineStr">
+        <is>
+          <t>4.28</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr">
+        <is>
+          <t>-116.62</t>
+        </is>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
+          <t>2025/10/28</t>
+        </is>
+      </c>
+      <c r="AV9" t="inlineStr">
+        <is>
+          <t>77384.26950867052</t>
+        </is>
+      </c>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>21744.0</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>9374.6</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>8103.2</t>
+        </is>
+      </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>22013.86</t>
+        </is>
+      </c>
+      <c r="BA9" t="inlineStr">
+        <is>
+          <t>1271</t>
+        </is>
+      </c>
+      <c r="BB9" t="inlineStr">
+        <is>
+          <t>-1787.840342020155</t>
+        </is>
+      </c>
+      <c r="BC9" t="n">
+        <v>-651.7</v>
+      </c>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BE9" t="inlineStr">
+        <is>
+          <t>48.75</t>
+        </is>
+      </c>
+      <c r="BF9" t="inlineStr">
+        <is>
+          <t>2025/08/25</t>
+        </is>
+      </c>
+      <c r="BG9" t="inlineStr">
+        <is>
+          <t>-3.59</t>
+        </is>
+      </c>
+      <c r="BH9" t="inlineStr">
+        <is>
+          <t>岱稜</t>
+        </is>
+      </c>
+      <c r="BI9" t="inlineStr">
+        <is>
+          <t>岱稜</t>
+        </is>
+      </c>
+      <c r="BJ9" t="inlineStr">
+        <is>
+          <t>其他電子業</t>
+        </is>
+      </c>
+      <c r="BK9" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BL9" t="inlineStr">
+        <is>
           <t>1.08</t>
         </is>
       </c>
-      <c r="AL9" t="inlineStr">
-        <is>
-          <t>45.27999999999999</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>45.82</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>47.84</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>47.32</t>
-        </is>
-      </c>
-      <c r="AP9" t="inlineStr">
-        <is>
-          <t>4.09</t>
-        </is>
-      </c>
-      <c r="AQ9" t="inlineStr">
-        <is>
-          <t>-0.72</t>
-        </is>
-      </c>
-      <c r="AR9" t="inlineStr">
-        <is>
-          <t>-0.75</t>
-        </is>
-      </c>
-      <c r="AS9" t="inlineStr">
-        <is>
-          <t>4.28</t>
-        </is>
-      </c>
-      <c r="AT9" t="inlineStr">
-        <is>
-          <t>-117.52</t>
-        </is>
-      </c>
-      <c r="AU9" t="inlineStr">
-        <is>
-          <t>2025/10/28</t>
-        </is>
-      </c>
-      <c r="AV9" t="inlineStr">
-        <is>
-          <t>77474.67438494935</t>
-        </is>
-      </c>
-      <c r="AW9" t="inlineStr">
-        <is>
-          <t>7224.0</t>
-        </is>
-      </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>6527.4</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr">
-        <is>
-          <t>6340.9</t>
-        </is>
-      </c>
-      <c r="AZ9" t="inlineStr">
-        <is>
-          <t>21843.6</t>
-        </is>
-      </c>
-      <c r="BA9" t="inlineStr">
-        <is>
-          <t>186</t>
-        </is>
-      </c>
-      <c r="BB9" t="inlineStr">
-        <is>
-          <t>-1994.41205403867</t>
-        </is>
-      </c>
-      <c r="BC9" t="n">
-        <v>-1938.44</v>
-      </c>
-      <c r="BD9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BE9" t="inlineStr">
-        <is>
-          <t>48.75</t>
-        </is>
-      </c>
-      <c r="BF9" t="inlineStr">
-        <is>
-          <t>2025/08/25</t>
-        </is>
-      </c>
-      <c r="BG9" t="inlineStr">
-        <is>
-          <t>-7.18</t>
-        </is>
-      </c>
-      <c r="BH9" t="inlineStr">
-        <is>
-          <t>岱稜</t>
-        </is>
-      </c>
-      <c r="BI9" t="inlineStr">
-        <is>
-          <t>岱稜</t>
-        </is>
-      </c>
-      <c r="BJ9" t="inlineStr">
-        <is>
-          <t>其他電子業</t>
-        </is>
-      </c>
-      <c r="BK9" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BL9" t="inlineStr">
-        <is>
-          <t>1.08</t>
-        </is>
-      </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>8.591010580024943</t>
+          <t>-1.004452687200723</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
         <is>
-          <t>-14.93484897076815</t>
+          <t>11.92388165594906</t>
         </is>
       </c>
       <c r="BO9" t="inlineStr">
         <is>
-          <t>1.909594416710131</t>
+          <t>2.060463205899802</t>
         </is>
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>5.88</t>
+          <t>5.94</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="BU9" t="inlineStr">
         <is>
-          <t>10.63</t>
+          <t>10.52</t>
         </is>
       </c>
       <c r="BV9" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="BX9" t="inlineStr">
         <is>
-          <t>44.82</t>
+          <t>43.93</t>
         </is>
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>4432</t>
+          <t>4385</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
@@ -4274,27 +4274,27 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>其他電子業右上上櫃</t>
+          <t>其他電子業平上櫃</t>
         </is>
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>44.75</t>
+          <t>46.0</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>45.25</t>
+          <t>47.7</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>44.35</t>
+          <t>45.9</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>45.25</t>
+          <t>47.0</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4326,12 +4326,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>194.0</t>
+          <t>161.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4341,7 +4341,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>45.1</t>
+          <t>45.25</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4351,17 +4351,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>4.25</t>
+          <t>2.9</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>2.94</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4371,7 +4371,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -4426,7 +4426,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-9.35</t>
+          <t>-9.05</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4436,17 +4436,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>3.92</t>
+          <t>3.26</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4462,52 +4462,52 @@
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>311</t>
+          <t>213</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>15.79</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>6.41</t>
+          <t>9.71</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-0.62</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-1.27</t>
+          <t>-1.19</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-4.08</t>
+          <t>-4.21</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>45.38</t>
+          <t>45.27999999999999</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>45.96</t>
+          <t>45.82</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>47.92</t>
+          <t>47.84</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
@@ -4517,17 +4517,17 @@
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>2.53</t>
+          <t>4.09</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-0.74</t>
+          <t>-0.72</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4537,7 +4537,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-117.70</t>
+          <t>-117.52</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4547,41 +4547,41 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>77474.67438494935</t>
+          <t>77384.26950867052</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>8759.0</t>
+          <t>7224.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>6701.8</t>
+          <t>6527.4</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>6573.5</t>
+          <t>6340.9</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>22067.68</t>
+          <t>21843.6</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>186</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-2004.588353420276</t>
+          <t>-1994.41205403867</t>
         </is>
       </c>
       <c r="BC10" t="n">
-        <v>-2151.71</v>
+        <v>-1938.44</v>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
@@ -4600,7 +4600,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>-7.49</t>
+          <t>-7.18</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -4630,22 +4630,22 @@
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>8.591010580024943</t>
+          <t>-1.004452687200723</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
         <is>
-          <t>-14.93484897076815</t>
+          <t>11.92388165594906</t>
         </is>
       </c>
       <c r="BO10" t="inlineStr">
         <is>
-          <t>1.909594416710131</t>
+          <t>2.060463205899802</t>
         </is>
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
@@ -4660,7 +4660,7 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>5.88</t>
+          <t>5.94</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4670,7 +4670,7 @@
       </c>
       <c r="BU10" t="inlineStr">
         <is>
-          <t>10.63</t>
+          <t>10.52</t>
         </is>
       </c>
       <c r="BV10" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="BX10" t="inlineStr">
         <is>
-          <t>44.82</t>
+          <t>43.93</t>
         </is>
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>4432</t>
+          <t>4385</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -4705,27 +4705,27 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>其他電子業右上上櫃</t>
+          <t>其他電子業平上櫃</t>
         </is>
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>45.4</t>
+          <t>44.75</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>45.8</t>
+          <t>45.25</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>44.85</t>
+          <t>44.35</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>45.1</t>
+          <t>45.25</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>110.0</t>
+          <t>194.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4772,7 +4772,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>45.4</t>
+          <t>45.1</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4782,17 +4782,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>3.61</t>
+          <t>3.22</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-19.80</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4802,7 +4802,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -4857,7 +4857,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-8.74</t>
+          <t>-9.35</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4867,17 +4867,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>3.92</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4893,62 +4893,62 @@
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>311</t>
+          <t>213</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>13.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>9.91</t>
+          <t>6.41</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>-0.62</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-1.39</t>
+          <t>-1.27</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-3.77</t>
+          <t>-4.08</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>45.52999999999999</t>
+          <t>45.38</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>46.17</t>
+          <t>45.96</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>47.98</t>
+          <t>47.92</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>47.33</t>
+          <t>47.32</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>3.33</t>
+          <t>2.53</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
@@ -4968,7 +4968,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-117.81</t>
+          <t>-117.70</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4978,41 +4978,41 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>77474.67438494935</t>
+          <t>77384.26950867052</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>4977.0</t>
+          <t>8759.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>5634.8</t>
+          <t>6701.8</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>7025.5</t>
+          <t>6573.5</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>22119.5</t>
+          <t>22067.68</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-1390</t>
+          <t>128</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-1977.839454939963</t>
+          <t>-2004.588353420276</t>
         </is>
       </c>
       <c r="BC11" t="n">
-        <v>-2543.99</v>
+        <v>-2151.71</v>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
@@ -5031,7 +5031,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>-6.87</t>
+          <t>-7.49</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5061,22 +5061,22 @@
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>8.591010580024943</t>
+          <t>-1.004452687200723</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
         <is>
-          <t>-14.93484897076815</t>
+          <t>11.92388165594906</t>
         </is>
       </c>
       <c r="BO11" t="inlineStr">
         <is>
-          <t>1.909594416710131</t>
+          <t>2.060463205899802</t>
         </is>
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
@@ -5086,12 +5086,12 @@
       </c>
       <c r="BR11" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>5.88</t>
+          <t>5.94</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5101,7 +5101,7 @@
       </c>
       <c r="BU11" t="inlineStr">
         <is>
-          <t>10.63</t>
+          <t>10.52</t>
         </is>
       </c>
       <c r="BV11" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="BX11" t="inlineStr">
         <is>
-          <t>44.82</t>
+          <t>43.93</t>
         </is>
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>4432</t>
+          <t>4385</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5136,27 +5136,27 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>其他電子業右上上櫃</t>
+          <t>其他電子業平上櫃</t>
         </is>
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>45.5</t>
+          <t>45.4</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>45.75</t>
+          <t>45.8</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>45.25</t>
+          <t>44.85</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>45.4</t>
+          <t>45.1</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
@@ -5193,7 +5193,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>110.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>45.35</t>
+          <t>45.4</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5213,17 +5213,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>3.72</t>
+          <t>2.58</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-11.17</t>
+          <t>-19.80</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5233,7 +5233,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -5288,7 +5288,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-8.84</t>
+          <t>-8.74</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5298,17 +5298,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>-0.44</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5324,72 +5324,72 @@
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>311</t>
+          <t>213</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>5.88</t>
+          <t>13.33</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>24.77</t>
+          <t>9.91</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-1.61</t>
+          <t>-1.39</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-3.44</t>
+          <t>-3.77</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>45.65</t>
+          <t>45.52999999999999</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>46.4</t>
+          <t>46.17</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>48.05</t>
+          <t>47.98</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>47.37</t>
+          <t>47.33</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>3.33</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-0.74</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-0.77</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5399,7 +5399,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-117.96</t>
+          <t>-117.81</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5409,41 +5409,41 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>77474.67438494935</t>
+          <t>77384.26950867052</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>4169.0</t>
+          <t>4977.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>6308.2</t>
+          <t>5634.8</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>7101.4</t>
+          <t>7025.5</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>22225.84</t>
+          <t>22119.5</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-793</t>
+          <t>-1390</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-1874.903170957873</t>
+          <t>-1977.839454939963</t>
         </is>
       </c>
       <c r="BC12" t="n">
-        <v>-2608.32</v>
+        <v>-2543.99</v>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
@@ -5462,7 +5462,7 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>-6.97</t>
+          <t>-6.87</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -5492,22 +5492,22 @@
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>8.591010580024943</t>
+          <t>-1.004452687200723</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
         <is>
-          <t>-14.93484897076815</t>
+          <t>11.92388165594906</t>
         </is>
       </c>
       <c r="BO12" t="inlineStr">
         <is>
-          <t>1.909594416710131</t>
+          <t>2.060463205899802</t>
         </is>
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
@@ -5522,7 +5522,7 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>5.88</t>
+          <t>5.94</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5532,7 +5532,7 @@
       </c>
       <c r="BU12" t="inlineStr">
         <is>
-          <t>10.63</t>
+          <t>10.52</t>
         </is>
       </c>
       <c r="BV12" t="inlineStr">
@@ -5547,12 +5547,12 @@
       </c>
       <c r="BX12" t="inlineStr">
         <is>
-          <t>44.82</t>
+          <t>43.93</t>
         </is>
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>4432</t>
+          <t>4385</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -5567,7 +5567,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>其他電子業右上上櫃</t>
+          <t>其他電子業平上櫃</t>
         </is>
       </c>
       <c r="CC12" t="inlineStr">
@@ -5577,17 +5577,17 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>45.95</t>
+          <t>45.75</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>45.3</t>
+          <t>45.25</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>45.35</t>
+          <t>45.4</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">

--- a/Result/checksun_type/PET膜.xlsx
+++ b/Result/checksun_type/PET膜.xlsx
@@ -878,12 +878,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-0.95</t>
+          <t>-3.84</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>213.0</t>
+          <t>315.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>46.6</t>
+          <t>44.8</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -908,12 +908,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>26.53</t>
+          <t>-9.12</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-6.33</t>
+          <t>-9.95</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -988,17 +988,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>4.31</t>
+          <t>6.37</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>-4.69</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1009,77 +1009,77 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>213</t>
+          <t>315</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>57.45</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>71.82</t>
+          <t>45.15</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-1.17</t>
+          <t>-3.92</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-2.88</t>
+          <t>-2.8</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>47.15</t>
+          <t>46.63</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>46.22</t>
+          <t>46.15</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>47.59</t>
+          <t>47.48</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>47.5</t>
+          <t>47.49</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>98.12</t>
+          <t>27.78</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-0.00</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-105.28</t>
+          <t>-104.94</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1099,41 +1099,41 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>77384.26950867052</t>
+          <t>77303.6341991342</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>9943.0</t>
+          <t>14336.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>18959.2</t>
+          <t>14123.0</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>14983.4</t>
+          <t>15541.1</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>17743.28</t>
+          <t>17446.4</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>3975</t>
+          <t>-1418</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-74.62310011749315</t>
+          <t>-30.07547477889878</t>
         </is>
       </c>
       <c r="BC2" t="n">
-        <v>220.11</v>
+        <v>214.94</v>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>-4.41</t>
+          <t>-8.10</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1177,7 +1177,7 @@
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="BM2" t="inlineStr">
@@ -1197,7 +1197,7 @@
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
@@ -1207,12 +1207,12 @@
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>1.89</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>5.94</t>
+          <t>6.17</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
@@ -1222,7 +1222,7 @@
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>10.52</t>
+          <t>10.11</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="BX2" t="inlineStr">
         <is>
-          <t>43.93</t>
+          <t>42.34</t>
         </is>
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>4385</t>
+          <t>4215</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
@@ -1262,22 +1262,22 @@
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>47.15</t>
+          <t>46.9</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>47.2</t>
+          <t>46.9</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>46.4</t>
+          <t>44.8</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>46.6</t>
+          <t>44.8</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1309,12 +1309,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>-0.95</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>192.0</t>
+          <t>213.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>47.05</t>
+          <t>46.6</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1334,17 +1334,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-0.97</t>
+          <t>-4.02</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>29.99</t>
+          <t>26.53</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1409,7 +1409,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-5.43</t>
+          <t>-6.33</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1419,17 +1419,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>3.88</t>
+          <t>4.31</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1440,77 +1440,77 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>213</t>
+          <t>315</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>57.45</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>71.82</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>-1.17</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-3.21</t>
+          <t>-2.88</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>47.23</t>
+          <t>47.15</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>46.15</t>
+          <t>46.22</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>47.68</t>
+          <t>47.59</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>47.48</t>
+          <t>47.5</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>100.64</t>
+          <t>98.12</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.00</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-106.58</t>
+          <t>-105.28</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,41 +1530,41 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>77384.26950867052</t>
+          <t>77303.6341991342</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>9018.0</t>
+          <t>9943.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>18831.4</t>
+          <t>18959.2</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>14486.8</t>
+          <t>14983.4</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>18676.0</t>
+          <t>17743.28</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>4344</t>
+          <t>3975</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-128.211286383547</t>
+          <t>-74.62310011749315</t>
         </is>
       </c>
       <c r="BC3" t="n">
-        <v>690.3200000000001</v>
+        <v>220.11</v>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>-3.49</t>
+          <t>-4.41</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1608,7 +1608,7 @@
       </c>
       <c r="BL3" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="BM3" t="inlineStr">
@@ -1633,17 +1633,17 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>1.89</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>5.94</t>
+          <t>6.17</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1653,7 +1653,7 @@
       </c>
       <c r="BU3" t="inlineStr">
         <is>
-          <t>10.52</t>
+          <t>10.11</t>
         </is>
       </c>
       <c r="BV3" t="inlineStr">
@@ -1668,12 +1668,12 @@
       </c>
       <c r="BX3" t="inlineStr">
         <is>
-          <t>43.93</t>
+          <t>42.34</t>
         </is>
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>4385</t>
+          <t>4215</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1693,22 +1693,22 @@
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>46.5</t>
+          <t>47.15</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>47.5</t>
+          <t>47.2</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>46.35</t>
+          <t>46.4</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>47.05</t>
+          <t>46.6</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1740,12 +1740,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-1.05</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>311.0</t>
+          <t>192.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>47.1</t>
+          <t>47.05</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1765,17 +1765,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-1.07</t>
+          <t>-5.02</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>33.05</t>
+          <t>29.99</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-5.33</t>
+          <t>-5.43</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1850,17 +1850,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>6.29</t>
+          <t>3.88</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-0.95</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1871,77 +1871,77 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>213</t>
+          <t>315</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>93.33</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>2.36</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-3.53</t>
+          <t>-3.21</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>0.60</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>47.15</t>
+          <t>47.23</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>46.06</t>
+          <t>46.15</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>47.75</t>
+          <t>47.68</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>47.47</t>
+          <t>47.48</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>89.68</t>
+          <t>100.64</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1951,7 +1951,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-108.23</t>
+          <t>-106.58</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1961,41 +1961,41 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>77384.26950867052</t>
+          <t>77303.6341991342</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>14718.0</t>
+          <t>9018.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>18629.2</t>
+          <t>18831.4</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>14001.9</t>
+          <t>14486.8</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>20406.5</t>
+          <t>18676.0</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>4627</t>
+          <t>4344</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-277.0356783742832</t>
+          <t>-128.211286383547</t>
         </is>
       </c>
       <c r="BC4" t="n">
-        <v>1436.51</v>
+        <v>690.3200000000001</v>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>-3.38</t>
+          <t>-3.49</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2039,7 +2039,7 @@
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="BM4" t="inlineStr">
@@ -2064,7 +2064,7 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2074,7 +2074,7 @@
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>5.94</t>
+          <t>6.17</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>10.52</t>
+          <t>10.11</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
@@ -2099,12 +2099,12 @@
       </c>
       <c r="BX4" t="inlineStr">
         <is>
-          <t>43.93</t>
+          <t>42.34</t>
         </is>
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>4385</t>
+          <t>4215</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -2124,22 +2124,22 @@
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>47.6</t>
+          <t>46.5</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>47.8</t>
+          <t>47.5</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>46.85</t>
+          <t>46.35</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>47.1</t>
+          <t>47.05</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>-1.05</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>474.0</t>
+          <t>311.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>47.6</t>
+          <t>47.1</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2196,17 +2196,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-2.15</t>
+          <t>-5.13</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>50.85</t>
+          <t>33.05</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-4.32</t>
+          <t>-5.33</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2281,17 +2281,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>9.59</t>
+          <t>6.29</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-0.95</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2302,77 +2302,77 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>213</t>
+          <t>315</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>93.33</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>2.67</t>
+          <t>2.36</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-3.93</t>
+          <t>-3.53</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.60</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>47.13</t>
+          <t>47.15</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>45.9</t>
+          <t>46.06</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>47.78</t>
+          <t>47.75</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>47.45</t>
+          <t>47.47</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>79.21</t>
+          <t>89.68</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-110.08</t>
+          <t>-108.23</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2392,41 +2392,41 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>77384.26950867052</t>
+          <t>77303.6341991342</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>22600.0</t>
+          <t>14718.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>20034.4</t>
+          <t>18629.2</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>13280.9</t>
+          <t>14001.9</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>20741.92</t>
+          <t>20406.5</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>6753</t>
+          <t>4627</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-588.5886282543895</t>
+          <t>-277.0356783742832</t>
         </is>
       </c>
       <c r="BC5" t="n">
-        <v>1840.46</v>
+        <v>1436.51</v>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
@@ -2445,7 +2445,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>-2.36</t>
+          <t>-3.38</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2470,7 +2470,7 @@
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="BM5" t="inlineStr">
@@ -2490,22 +2490,22 @@
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>5.94</t>
+          <t>6.17</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2515,7 +2515,7 @@
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>10.52</t>
+          <t>10.11</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="BX5" t="inlineStr">
         <is>
-          <t>43.93</t>
+          <t>42.34</t>
         </is>
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>4385</t>
+          <t>4215</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
@@ -2555,22 +2555,22 @@
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>47.85</t>
+          <t>47.6</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>48.1</t>
+          <t>47.8</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>47.25</t>
+          <t>46.85</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>47.6</t>
+          <t>47.1</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2602,12 +2602,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>812.0</t>
+          <t>474.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2617,7 +2617,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>47.4</t>
+          <t>47.6</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2627,17 +2627,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-1.72</t>
+          <t>-6.25</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>43.35</t>
+          <t>50.85</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2702,7 +2702,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-4.72</t>
+          <t>-4.32</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2712,17 +2712,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16.43</t>
+          <t>9.59</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2733,12 +2733,12 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>213</t>
+          <t>315</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
@@ -2748,62 +2748,62 @@
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>93.86</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>2.67</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-4.23</t>
+          <t>-3.93</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>46.66</t>
+          <t>47.13</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>45.74</t>
+          <t>45.9</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>47.76</t>
+          <t>47.78</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>47.42</t>
+          <t>47.45</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>59.88</t>
+          <t>79.21</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2813,7 +2813,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-112.07</t>
+          <t>-110.08</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2823,41 +2823,41 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>77384.26950867052</t>
+          <t>77303.6341991342</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>38517.0</t>
+          <t>22600.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>16959.2</t>
+          <t>20034.4</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>11830.5</t>
+          <t>13280.9</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>20783.02</t>
+          <t>20741.92</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>5128</t>
+          <t>6753</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-1030.234332074163</t>
+          <t>-588.5886282543895</t>
         </is>
       </c>
       <c r="BC6" t="n">
-        <v>1507.31</v>
+        <v>1840.46</v>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>-2.77</t>
+          <t>-2.36</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="BL6" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="BM6" t="inlineStr">
@@ -2921,7 +2921,7 @@
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
@@ -2931,12 +2931,12 @@
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>5.94</t>
+          <t>6.17</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BU6" t="inlineStr">
         <is>
-          <t>10.52</t>
+          <t>10.11</t>
         </is>
       </c>
       <c r="BV6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BX6" t="inlineStr">
         <is>
-          <t>43.93</t>
+          <t>42.34</t>
         </is>
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>4385</t>
+          <t>4215</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>47.5</t>
+          <t>47.85</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>47.85</t>
+          <t>48.1</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>46.5</t>
+          <t>47.25</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>47.4</t>
+          <t>47.6</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>199.0</t>
+          <t>812.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>47.0</t>
+          <t>47.4</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>-5.8</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>32.28</t>
+          <t>43.35</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-5.53</t>
+          <t>-4.72</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>4.03</t>
+          <t>16.43</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,12 +3164,12 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>213</t>
+          <t>315</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
@@ -3184,57 +3184,57 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-4.34</t>
+          <t>-4.23</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>46.2</t>
+          <t>46.66</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>45.67</t>
+          <t>45.74</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>47.75</t>
+          <t>47.76</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>47.39</t>
+          <t>47.42</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>43.77</t>
+          <t>59.88</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3244,7 +3244,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-113.88</t>
+          <t>-112.07</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3254,41 +3254,41 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>77384.26950867052</t>
+          <t>77303.6341991342</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>9304.0</t>
+          <t>38517.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>11007.6</t>
+          <t>16959.2</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>8321.2</t>
+          <t>11830.5</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>21296.56</t>
+          <t>20783.02</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>2686</t>
+          <t>5128</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-1491.606690671351</t>
+          <t>-1030.234332074163</t>
         </is>
       </c>
       <c r="BC7" t="n">
-        <v>-727.84</v>
+        <v>1507.31</v>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>-3.59</t>
+          <t>-2.77</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3332,7 +3332,7 @@
       </c>
       <c r="BL7" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="BM7" t="inlineStr">
@@ -3352,22 +3352,22 @@
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>5.94</t>
+          <t>6.17</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3377,7 +3377,7 @@
       </c>
       <c r="BU7" t="inlineStr">
         <is>
-          <t>10.52</t>
+          <t>10.11</t>
         </is>
       </c>
       <c r="BV7" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="BX7" t="inlineStr">
         <is>
-          <t>43.93</t>
+          <t>42.34</t>
         </is>
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>4385</t>
+          <t>4215</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3417,22 +3417,22 @@
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>46.85</t>
+          <t>47.5</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>47.1</t>
+          <t>47.85</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>46.25</t>
+          <t>46.5</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>47.0</t>
+          <t>47.4</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3464,12 +3464,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>170.0</t>
+          <t>199.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>46.65</t>
+          <t>47.0</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3489,17 +3489,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>-4.91</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>23.31</t>
+          <t>32.28</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3564,7 +3564,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-6.23</t>
+          <t>-5.53</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3574,17 +3574,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>3.44</t>
+          <t>4.03</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-2.14</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3595,77 +3595,77 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>213</t>
+          <t>315</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>81.58</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>65.79</t>
+          <t>93.86</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-4.26</t>
+          <t>-4.34</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>45.88</t>
+          <t>46.2</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>45.73</t>
+          <t>45.67</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>47.76</t>
+          <t>47.75</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>47.37</t>
+          <t>47.39</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>31.68</t>
+          <t>43.77</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3675,7 +3675,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-115.40</t>
+          <t>-113.88</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3685,41 +3685,41 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>77384.26950867052</t>
+          <t>77303.6341991342</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>8007.0</t>
+          <t>9304.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>10142.2</t>
+          <t>11007.6</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>8225.2</t>
+          <t>8321.2</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>21859.62</t>
+          <t>21296.56</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>1917</t>
+          <t>2686</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-1630.473518740948</t>
+          <t>-1491.606690671351</t>
         </is>
       </c>
       <c r="BC8" t="n">
-        <v>-764.96</v>
+        <v>-727.84</v>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>-4.31</t>
+          <t>-3.59</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -3763,7 +3763,7 @@
       </c>
       <c r="BL8" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="BM8" t="inlineStr">
@@ -3783,7 +3783,7 @@
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
@@ -3793,12 +3793,12 @@
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>1.89</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>5.94</t>
+          <t>6.17</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3808,7 +3808,7 @@
       </c>
       <c r="BU8" t="inlineStr">
         <is>
-          <t>10.52</t>
+          <t>10.11</t>
         </is>
       </c>
       <c r="BV8" t="inlineStr">
@@ -3823,12 +3823,12 @@
       </c>
       <c r="BX8" t="inlineStr">
         <is>
-          <t>43.93</t>
+          <t>42.34</t>
         </is>
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>4385</t>
+          <t>4215</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
@@ -3848,22 +3848,22 @@
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>47.8</t>
+          <t>46.85</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>47.8</t>
+          <t>47.1</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>46.5</t>
+          <t>46.25</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>46.65</t>
+          <t>47.0</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>3.8</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>464.0</t>
+          <t>170.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3910,7 +3910,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>47.0</t>
+          <t>46.65</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3920,17 +3920,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>-4.13</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>15.69</t>
+          <t>23.31</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-5.53</t>
+          <t>-6.23</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4005,17 +4005,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>9.39</t>
+          <t>3.44</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>-2.14</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4026,275 +4026,275 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>213</t>
+          <t>315</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>81.58</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>38.6</t>
+          <t>65.79</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-0.37</t>
+          <t>0.33</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-4.22</t>
+          <t>-4.26</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>45.62</t>
+          <t>45.88</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>45.79</t>
+          <t>45.73</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
+          <t>47.76</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>47.37</t>
+        </is>
+      </c>
+      <c r="AP9" t="inlineStr">
+        <is>
+          <t>31.68</t>
+        </is>
+      </c>
+      <c r="AQ9" t="inlineStr">
+        <is>
+          <t>-0.45</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>-0.66</t>
+        </is>
+      </c>
+      <c r="AS9" t="inlineStr">
+        <is>
+          <t>4.28</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr">
+        <is>
+          <t>-115.40</t>
+        </is>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
+          <t>2025/10/28</t>
+        </is>
+      </c>
+      <c r="AV9" t="inlineStr">
+        <is>
+          <t>77303.6341991342</t>
+        </is>
+      </c>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>8007.0</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>10142.2</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>8225.2</t>
+        </is>
+      </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>21859.62</t>
+        </is>
+      </c>
+      <c r="BA9" t="inlineStr">
+        <is>
+          <t>1917</t>
+        </is>
+      </c>
+      <c r="BB9" t="inlineStr">
+        <is>
+          <t>-1630.473518740948</t>
+        </is>
+      </c>
+      <c r="BC9" t="n">
+        <v>-764.96</v>
+      </c>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BE9" t="inlineStr">
+        <is>
+          <t>48.75</t>
+        </is>
+      </c>
+      <c r="BF9" t="inlineStr">
+        <is>
+          <t>2025/08/25</t>
+        </is>
+      </c>
+      <c r="BG9" t="inlineStr">
+        <is>
+          <t>-4.31</t>
+        </is>
+      </c>
+      <c r="BH9" t="inlineStr">
+        <is>
+          <t>岱稜</t>
+        </is>
+      </c>
+      <c r="BI9" t="inlineStr">
+        <is>
+          <t>岱稜</t>
+        </is>
+      </c>
+      <c r="BJ9" t="inlineStr">
+        <is>
+          <t>其他電子業</t>
+        </is>
+      </c>
+      <c r="BK9" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BL9" t="inlineStr">
+        <is>
+          <t>1.09</t>
+        </is>
+      </c>
+      <c r="BM9" t="inlineStr">
+        <is>
+          <t>-1.004452687200723</t>
+        </is>
+      </c>
+      <c r="BN9" t="inlineStr">
+        <is>
+          <t>11.92388165594906</t>
+        </is>
+      </c>
+      <c r="BO9" t="inlineStr">
+        <is>
+          <t>2.060463205899802</t>
+        </is>
+      </c>
+      <c r="BP9" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BQ9" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BR9" t="inlineStr">
+        <is>
+          <t>1.89</t>
+        </is>
+      </c>
+      <c r="BS9" t="inlineStr">
+        <is>
+          <t>6.17</t>
+        </is>
+      </c>
+      <c r="BT9" t="inlineStr">
+        <is>
+          <t>8.56</t>
+        </is>
+      </c>
+      <c r="BU9" t="inlineStr">
+        <is>
+          <t>10.11</t>
+        </is>
+      </c>
+      <c r="BV9" t="inlineStr">
+        <is>
+          <t>33.67%</t>
+        </is>
+      </c>
+      <c r="BW9" t="inlineStr">
+        <is>
+          <t>12.48%</t>
+        </is>
+      </c>
+      <c r="BX9" t="inlineStr">
+        <is>
+          <t>42.34</t>
+        </is>
+      </c>
+      <c r="BY9" t="inlineStr">
+        <is>
+          <t>4215</t>
+        </is>
+      </c>
+      <c r="BZ9" t="inlineStr">
+        <is>
+          <t>真空蒸鍍薄膜95.00%、光電材料5.00% (2024年)</t>
+        </is>
+      </c>
+      <c r="CA9" t="inlineStr">
+        <is>
+          <t>岱稜-其他電子業-上櫃</t>
+        </is>
+      </c>
+      <c r="CB9" t="inlineStr">
+        <is>
+          <t>其他電子業平上櫃</t>
+        </is>
+      </c>
+      <c r="CC9" t="inlineStr">
+        <is>
           <t>47.8</t>
         </is>
       </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>47.35</t>
-        </is>
-      </c>
-      <c r="AP9" t="inlineStr">
-        <is>
-          <t>21.78</t>
-        </is>
-      </c>
-      <c r="AQ9" t="inlineStr">
-        <is>
-          <t>-0.56</t>
-        </is>
-      </c>
-      <c r="AR9" t="inlineStr">
-        <is>
-          <t>-0.71</t>
-        </is>
-      </c>
-      <c r="AS9" t="inlineStr">
-        <is>
-          <t>4.28</t>
-        </is>
-      </c>
-      <c r="AT9" t="inlineStr">
-        <is>
-          <t>-116.62</t>
-        </is>
-      </c>
-      <c r="AU9" t="inlineStr">
-        <is>
-          <t>2025/10/28</t>
-        </is>
-      </c>
-      <c r="AV9" t="inlineStr">
-        <is>
-          <t>77384.26950867052</t>
-        </is>
-      </c>
-      <c r="AW9" t="inlineStr">
-        <is>
-          <t>21744.0</t>
-        </is>
-      </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>9374.6</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr">
-        <is>
-          <t>8103.2</t>
-        </is>
-      </c>
-      <c r="AZ9" t="inlineStr">
-        <is>
-          <t>22013.86</t>
-        </is>
-      </c>
-      <c r="BA9" t="inlineStr">
-        <is>
-          <t>1271</t>
-        </is>
-      </c>
-      <c r="BB9" t="inlineStr">
-        <is>
-          <t>-1787.840342020155</t>
-        </is>
-      </c>
-      <c r="BC9" t="n">
-        <v>-651.7</v>
-      </c>
-      <c r="BD9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BE9" t="inlineStr">
-        <is>
-          <t>48.75</t>
-        </is>
-      </c>
-      <c r="BF9" t="inlineStr">
-        <is>
-          <t>2025/08/25</t>
-        </is>
-      </c>
-      <c r="BG9" t="inlineStr">
-        <is>
-          <t>-3.59</t>
-        </is>
-      </c>
-      <c r="BH9" t="inlineStr">
-        <is>
-          <t>岱稜</t>
-        </is>
-      </c>
-      <c r="BI9" t="inlineStr">
-        <is>
-          <t>岱稜</t>
-        </is>
-      </c>
-      <c r="BJ9" t="inlineStr">
-        <is>
-          <t>其他電子業</t>
-        </is>
-      </c>
-      <c r="BK9" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BL9" t="inlineStr">
-        <is>
-          <t>1.08</t>
-        </is>
-      </c>
-      <c r="BM9" t="inlineStr">
-        <is>
-          <t>-1.004452687200723</t>
-        </is>
-      </c>
-      <c r="BN9" t="inlineStr">
-        <is>
-          <t>11.92388165594906</t>
-        </is>
-      </c>
-      <c r="BO9" t="inlineStr">
-        <is>
-          <t>2.060463205899802</t>
-        </is>
-      </c>
-      <c r="BP9" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BQ9" t="inlineStr">
-        <is>
-          <t>價漲量增</t>
-        </is>
-      </c>
-      <c r="BR9" t="inlineStr">
-        <is>
-          <t>1.91</t>
-        </is>
-      </c>
-      <c r="BS9" t="inlineStr">
-        <is>
-          <t>5.94</t>
-        </is>
-      </c>
-      <c r="BT9" t="inlineStr">
-        <is>
-          <t>8.56</t>
-        </is>
-      </c>
-      <c r="BU9" t="inlineStr">
-        <is>
-          <t>10.52</t>
-        </is>
-      </c>
-      <c r="BV9" t="inlineStr">
-        <is>
-          <t>33.67%</t>
-        </is>
-      </c>
-      <c r="BW9" t="inlineStr">
-        <is>
-          <t>12.48%</t>
-        </is>
-      </c>
-      <c r="BX9" t="inlineStr">
-        <is>
-          <t>43.93</t>
-        </is>
-      </c>
-      <c r="BY9" t="inlineStr">
-        <is>
-          <t>4385</t>
-        </is>
-      </c>
-      <c r="BZ9" t="inlineStr">
-        <is>
-          <t>真空蒸鍍薄膜95.00%、光電材料5.00% (2024年)</t>
-        </is>
-      </c>
-      <c r="CA9" t="inlineStr">
-        <is>
-          <t>岱稜-其他電子業-上櫃</t>
-        </is>
-      </c>
-      <c r="CB9" t="inlineStr">
-        <is>
-          <t>其他電子業平上櫃</t>
-        </is>
-      </c>
-      <c r="CC9" t="inlineStr">
-        <is>
-          <t>46.0</t>
-        </is>
-      </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>47.7</t>
+          <t>47.8</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>45.9</t>
+          <t>46.5</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>47.0</t>
+          <t>46.65</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4326,12 +4326,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>3.8</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>161.0</t>
+          <t>464.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4341,7 +4341,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>45.25</t>
+          <t>47.0</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4351,17 +4351,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2.9</t>
+          <t>-4.91</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2.94</t>
+          <t>15.69</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4426,7 +4426,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-9.05</t>
+          <t>-5.53</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4436,17 +4436,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>3.26</t>
+          <t>9.39</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4457,77 +4457,77 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>213</t>
+          <t>315</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>15.79</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>9.71</t>
+          <t>38.6</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>3.02</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-1.19</t>
+          <t>-0.37</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-4.21</t>
+          <t>-4.22</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>45.27999999999999</t>
+          <t>45.62</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>45.82</t>
+          <t>45.79</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>47.84</t>
+          <t>47.8</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>47.32</t>
+          <t>47.35</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>4.09</t>
+          <t>21.78</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>-0.56</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4537,7 +4537,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-117.52</t>
+          <t>-116.62</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4547,41 +4547,41 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>77384.26950867052</t>
+          <t>77303.6341991342</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>7224.0</t>
+          <t>21744.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>6527.4</t>
+          <t>9374.6</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>6340.9</t>
+          <t>8103.2</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>21843.6</t>
+          <t>22013.86</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>186</t>
+          <t>1271</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-1994.41205403867</t>
+          <t>-1787.840342020155</t>
         </is>
       </c>
       <c r="BC10" t="n">
-        <v>-1938.44</v>
+        <v>-651.7</v>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
@@ -4600,7 +4600,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>-7.18</t>
+          <t>-3.59</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -4625,7 +4625,7 @@
       </c>
       <c r="BL10" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="BM10" t="inlineStr">
@@ -4645,22 +4645,22 @@
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>5.94</t>
+          <t>6.17</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4670,7 +4670,7 @@
       </c>
       <c r="BU10" t="inlineStr">
         <is>
-          <t>10.52</t>
+          <t>10.11</t>
         </is>
       </c>
       <c r="BV10" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="BX10" t="inlineStr">
         <is>
-          <t>43.93</t>
+          <t>42.34</t>
         </is>
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>4385</t>
+          <t>4215</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -4710,22 +4710,22 @@
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>44.75</t>
+          <t>46.0</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>45.25</t>
+          <t>47.7</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>44.35</t>
+          <t>45.9</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>45.25</t>
+          <t>47.0</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>194.0</t>
+          <t>161.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4772,7 +4772,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>45.1</t>
+          <t>45.25</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4782,17 +4782,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>3.22</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>2.94</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4857,7 +4857,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-9.35</t>
+          <t>-9.05</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4867,17 +4867,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>3.92</t>
+          <t>3.26</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4888,57 +4888,57 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>213</t>
+          <t>315</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>15.79</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>6.41</t>
+          <t>9.71</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-0.62</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-1.27</t>
+          <t>-1.19</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-4.08</t>
+          <t>-4.21</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>45.38</t>
+          <t>45.27999999999999</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>45.96</t>
+          <t>45.82</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>47.92</t>
+          <t>47.84</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
@@ -4948,17 +4948,17 @@
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>2.53</t>
+          <t>4.09</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-0.74</t>
+          <t>-0.72</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4968,7 +4968,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-117.70</t>
+          <t>-117.52</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4978,41 +4978,41 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>77384.26950867052</t>
+          <t>77303.6341991342</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>8759.0</t>
+          <t>7224.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>6701.8</t>
+          <t>6527.4</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>6573.5</t>
+          <t>6340.9</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>22067.68</t>
+          <t>21843.6</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>186</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-2004.588353420276</t>
+          <t>-1994.41205403867</t>
         </is>
       </c>
       <c r="BC11" t="n">
-        <v>-2151.71</v>
+        <v>-1938.44</v>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
@@ -5031,7 +5031,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>-7.49</t>
+          <t>-7.18</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5056,7 +5056,7 @@
       </c>
       <c r="BL11" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="BM11" t="inlineStr">
@@ -5076,7 +5076,7 @@
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
@@ -5091,7 +5091,7 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>5.94</t>
+          <t>6.17</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5101,7 +5101,7 @@
       </c>
       <c r="BU11" t="inlineStr">
         <is>
-          <t>10.52</t>
+          <t>10.11</t>
         </is>
       </c>
       <c r="BV11" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="BX11" t="inlineStr">
         <is>
-          <t>43.93</t>
+          <t>42.34</t>
         </is>
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>4385</t>
+          <t>4215</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5141,22 +5141,22 @@
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>45.4</t>
+          <t>44.75</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>45.8</t>
+          <t>45.25</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>44.85</t>
+          <t>44.35</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>45.1</t>
+          <t>45.25</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>110.0</t>
+          <t>194.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>45.4</t>
+          <t>45.1</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5213,17 +5213,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2.58</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-19.80</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5288,7 +5288,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-8.74</t>
+          <t>-9.35</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5298,17 +5298,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>3.92</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5319,67 +5319,67 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>213</t>
+          <t>315</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>13.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>9.91</t>
+          <t>6.41</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>-0.62</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-1.39</t>
+          <t>-1.27</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-3.77</t>
+          <t>-4.08</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>45.52999999999999</t>
+          <t>45.38</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>46.17</t>
+          <t>45.96</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>47.98</t>
+          <t>47.92</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>47.33</t>
+          <t>47.32</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>3.33</t>
+          <t>2.53</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
@@ -5399,7 +5399,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-117.81</t>
+          <t>-117.70</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5409,41 +5409,41 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>77384.26950867052</t>
+          <t>77303.6341991342</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>4977.0</t>
+          <t>8759.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>5634.8</t>
+          <t>6701.8</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>7025.5</t>
+          <t>6573.5</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>22119.5</t>
+          <t>22067.68</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-1390</t>
+          <t>128</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-1977.839454939963</t>
+          <t>-2004.588353420276</t>
         </is>
       </c>
       <c r="BC12" t="n">
-        <v>-2543.99</v>
+        <v>-2151.71</v>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
@@ -5462,7 +5462,7 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>-6.87</t>
+          <t>-7.49</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -5487,7 +5487,7 @@
       </c>
       <c r="BL12" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="BM12" t="inlineStr">
@@ -5507,7 +5507,7 @@
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
@@ -5517,12 +5517,12 @@
       </c>
       <c r="BR12" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>5.94</t>
+          <t>6.17</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5532,7 +5532,7 @@
       </c>
       <c r="BU12" t="inlineStr">
         <is>
-          <t>10.52</t>
+          <t>10.11</t>
         </is>
       </c>
       <c r="BV12" t="inlineStr">
@@ -5547,12 +5547,12 @@
       </c>
       <c r="BX12" t="inlineStr">
         <is>
-          <t>43.93</t>
+          <t>42.34</t>
         </is>
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>4385</t>
+          <t>4215</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -5572,22 +5572,22 @@
       </c>
       <c r="CC12" t="inlineStr">
         <is>
-          <t>45.5</t>
+          <t>45.4</t>
         </is>
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>45.75</t>
+          <t>45.8</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>45.25</t>
+          <t>44.85</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>45.4</t>
+          <t>45.1</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">

--- a/Result/checksun_type/PET膜.xlsx
+++ b/Result/checksun_type/PET膜.xlsx
@@ -878,12 +878,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-3.84</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>315.0</t>
+          <t>112.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>44.8</t>
+          <t>45.05</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -908,12 +908,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-9.12</t>
+          <t>-30.74</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-9.95</t>
+          <t>-9.45</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -988,17 +988,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>6.37</t>
+          <t>2.27</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-4.69</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1009,57 +1009,57 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>315</t>
+          <t>112</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>8.93</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>45.15</t>
+          <t>22.13</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-3.92</t>
+          <t>-2.32</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-2.8</t>
+          <t>-2.65</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>46.63</t>
+          <t>46.12</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>46.15</t>
+          <t>46.12</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>47.48</t>
+          <t>47.37</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
@@ -1069,17 +1069,17 @@
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>27.78</t>
+          <t>-13.12</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-104.94</t>
+          <t>-105.11</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1099,41 +1099,41 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>77303.6341991342</t>
+          <t>77203.15201729107</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>14336.0</t>
+          <t>5046.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>14123.0</t>
+          <t>10612.2</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>15541.1</t>
+          <t>15323.3</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>17446.4</t>
+          <t>16780.18</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-1418</t>
+          <t>-4711</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-30.07547477889878</t>
+          <t>-100.9576738690555</t>
         </is>
       </c>
       <c r="BC2" t="n">
-        <v>214.94</v>
+        <v>-490.81</v>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>-8.10</t>
+          <t>-7.59</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1177,7 +1177,7 @@
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="BM2" t="inlineStr">
@@ -1197,7 +1197,7 @@
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
@@ -1207,12 +1207,12 @@
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>6.17</t>
+          <t>6.14</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
@@ -1222,7 +1222,7 @@
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>10.11</t>
+          <t>10.17</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="BX2" t="inlineStr">
         <is>
-          <t>42.34</t>
+          <t>41.96</t>
         </is>
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>4215</t>
+          <t>4239</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
@@ -1262,22 +1262,22 @@
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>46.9</t>
+          <t>44.55</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>46.9</t>
+          <t>45.4</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>44.8</t>
+          <t>44.55</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>44.8</t>
+          <t>45.05</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1309,12 +1309,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-0.95</t>
+          <t>-3.84</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>213.0</t>
+          <t>315.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>46.6</t>
+          <t>44.8</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1334,17 +1334,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-4.02</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>26.53</t>
+          <t>-9.12</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1409,7 +1409,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-6.33</t>
+          <t>-9.95</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1419,17 +1419,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>4.31</t>
+          <t>6.37</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>-4.69</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1440,77 +1440,77 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>315</t>
+          <t>112</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>57.45</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>71.82</t>
+          <t>45.15</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-1.17</t>
+          <t>-3.92</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-2.88</t>
+          <t>-2.8</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>47.15</t>
+          <t>46.63</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>46.22</t>
+          <t>46.15</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>47.59</t>
+          <t>47.48</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>47.5</t>
+          <t>47.49</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>98.12</t>
+          <t>27.78</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-0.00</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-105.28</t>
+          <t>-104.94</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,41 +1530,41 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>77303.6341991342</t>
+          <t>77203.15201729107</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>9943.0</t>
+          <t>14336.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>18959.2</t>
+          <t>14123.0</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>14983.4</t>
+          <t>15541.1</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>17743.28</t>
+          <t>17446.4</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>3975</t>
+          <t>-1418</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-74.62310011749315</t>
+          <t>-30.07547477889878</t>
         </is>
       </c>
       <c r="BC3" t="n">
-        <v>220.11</v>
+        <v>214.94</v>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>-4.41</t>
+          <t>-8.10</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1608,7 +1608,7 @@
       </c>
       <c r="BL3" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="BM3" t="inlineStr">
@@ -1628,7 +1628,7 @@
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
@@ -1638,12 +1638,12 @@
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>1.89</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>6.17</t>
+          <t>6.14</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1653,7 +1653,7 @@
       </c>
       <c r="BU3" t="inlineStr">
         <is>
-          <t>10.11</t>
+          <t>10.17</t>
         </is>
       </c>
       <c r="BV3" t="inlineStr">
@@ -1668,12 +1668,12 @@
       </c>
       <c r="BX3" t="inlineStr">
         <is>
-          <t>42.34</t>
+          <t>41.96</t>
         </is>
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>4215</t>
+          <t>4239</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1693,22 +1693,22 @@
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>47.15</t>
+          <t>46.9</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>47.2</t>
+          <t>46.9</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>46.4</t>
+          <t>44.8</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>46.6</t>
+          <t>44.8</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1740,12 +1740,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>-0.95</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>192.0</t>
+          <t>213.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>47.05</t>
+          <t>46.6</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1765,17 +1765,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-5.02</t>
+          <t>-3.44</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>29.99</t>
+          <t>26.53</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-5.43</t>
+          <t>-6.33</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1850,17 +1850,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>3.88</t>
+          <t>4.31</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1871,77 +1871,77 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>315</t>
+          <t>112</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>57.45</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>71.82</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>-1.17</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-3.21</t>
+          <t>-2.88</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>47.23</t>
+          <t>47.15</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>46.15</t>
+          <t>46.22</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>47.68</t>
+          <t>47.59</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>47.48</t>
+          <t>47.5</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>100.64</t>
+          <t>98.12</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.00</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1951,7 +1951,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-106.58</t>
+          <t>-105.28</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1961,41 +1961,41 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>77303.6341991342</t>
+          <t>77203.15201729107</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>9018.0</t>
+          <t>9943.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>18831.4</t>
+          <t>18959.2</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>14486.8</t>
+          <t>14983.4</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>18676.0</t>
+          <t>17743.28</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>4344</t>
+          <t>3975</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-128.211286383547</t>
+          <t>-74.62310011749315</t>
         </is>
       </c>
       <c r="BC4" t="n">
-        <v>690.3200000000001</v>
+        <v>220.11</v>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>-3.49</t>
+          <t>-4.41</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2039,7 +2039,7 @@
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="BM4" t="inlineStr">
@@ -2064,17 +2064,17 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>1.89</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>6.17</t>
+          <t>6.14</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>10.11</t>
+          <t>10.17</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
@@ -2099,12 +2099,12 @@
       </c>
       <c r="BX4" t="inlineStr">
         <is>
-          <t>42.34</t>
+          <t>41.96</t>
         </is>
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>4215</t>
+          <t>4239</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -2124,22 +2124,22 @@
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>46.5</t>
+          <t>47.15</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>47.5</t>
+          <t>47.2</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>46.35</t>
+          <t>46.4</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>47.05</t>
+          <t>46.6</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-1.05</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>311.0</t>
+          <t>192.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>47.1</t>
+          <t>47.05</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2196,17 +2196,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-5.13</t>
+          <t>-4.44</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>33.05</t>
+          <t>29.99</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-5.33</t>
+          <t>-5.43</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2281,17 +2281,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>6.29</t>
+          <t>3.88</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-0.95</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2302,77 +2302,77 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>315</t>
+          <t>112</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>93.33</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>2.36</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-3.53</t>
+          <t>-3.21</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>0.60</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>47.15</t>
+          <t>47.23</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>46.06</t>
+          <t>46.15</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>47.75</t>
+          <t>47.68</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>47.47</t>
+          <t>47.48</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>89.68</t>
+          <t>100.64</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-108.23</t>
+          <t>-106.58</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2392,41 +2392,41 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>77303.6341991342</t>
+          <t>77203.15201729107</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>14718.0</t>
+          <t>9018.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>18629.2</t>
+          <t>18831.4</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>14001.9</t>
+          <t>14486.8</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>20406.5</t>
+          <t>18676.0</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>4627</t>
+          <t>4344</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-277.0356783742832</t>
+          <t>-128.211286383547</t>
         </is>
       </c>
       <c r="BC5" t="n">
-        <v>1436.51</v>
+        <v>690.3200000000001</v>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
@@ -2445,7 +2445,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>-3.38</t>
+          <t>-3.49</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2470,7 +2470,7 @@
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="BM5" t="inlineStr">
@@ -2495,7 +2495,7 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2505,7 +2505,7 @@
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>6.17</t>
+          <t>6.14</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2515,7 +2515,7 @@
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>10.11</t>
+          <t>10.17</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="BX5" t="inlineStr">
         <is>
-          <t>42.34</t>
+          <t>41.96</t>
         </is>
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>4215</t>
+          <t>4239</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
@@ -2555,22 +2555,22 @@
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>47.6</t>
+          <t>46.5</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>47.8</t>
+          <t>47.5</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>46.85</t>
+          <t>46.35</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>47.1</t>
+          <t>47.05</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2602,12 +2602,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>-1.05</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>474.0</t>
+          <t>311.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2617,7 +2617,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>47.6</t>
+          <t>47.1</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2627,17 +2627,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-6.25</t>
+          <t>-4.55</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>50.85</t>
+          <t>33.05</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2702,7 +2702,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-4.32</t>
+          <t>-5.33</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2712,17 +2712,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>9.59</t>
+          <t>6.29</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-0.95</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2733,77 +2733,77 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>315</t>
+          <t>112</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>93.33</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>2.67</t>
+          <t>2.36</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-3.93</t>
+          <t>-3.53</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.60</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>47.13</t>
+          <t>47.15</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>45.9</t>
+          <t>46.06</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>47.78</t>
+          <t>47.75</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>47.45</t>
+          <t>47.47</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>79.21</t>
+          <t>89.68</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2813,7 +2813,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-110.08</t>
+          <t>-108.23</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2823,41 +2823,41 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>77303.6341991342</t>
+          <t>77203.15201729107</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>22600.0</t>
+          <t>14718.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>20034.4</t>
+          <t>18629.2</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>13280.9</t>
+          <t>14001.9</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>20741.92</t>
+          <t>20406.5</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>6753</t>
+          <t>4627</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-588.5886282543895</t>
+          <t>-277.0356783742832</t>
         </is>
       </c>
       <c r="BC6" t="n">
-        <v>1840.46</v>
+        <v>1436.51</v>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>-2.36</t>
+          <t>-3.38</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="BL6" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="BM6" t="inlineStr">
@@ -2921,22 +2921,22 @@
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>6.17</t>
+          <t>6.14</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BU6" t="inlineStr">
         <is>
-          <t>10.11</t>
+          <t>10.17</t>
         </is>
       </c>
       <c r="BV6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BX6" t="inlineStr">
         <is>
-          <t>42.34</t>
+          <t>41.96</t>
         </is>
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>4215</t>
+          <t>4239</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>47.85</t>
+          <t>47.6</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>48.1</t>
+          <t>47.8</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>47.25</t>
+          <t>46.85</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>47.6</t>
+          <t>47.1</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>812.0</t>
+          <t>474.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>47.4</t>
+          <t>47.6</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-5.8</t>
+          <t>-5.66</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>43.35</t>
+          <t>50.85</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-4.72</t>
+          <t>-4.32</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>16.43</t>
+          <t>9.59</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,12 +3164,12 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>315</t>
+          <t>112</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
@@ -3179,62 +3179,62 @@
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>93.86</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>2.67</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-4.23</t>
+          <t>-3.93</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>46.66</t>
+          <t>47.13</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>45.74</t>
+          <t>45.9</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>47.76</t>
+          <t>47.78</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>47.42</t>
+          <t>47.45</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>59.88</t>
+          <t>79.21</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3244,7 +3244,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-112.07</t>
+          <t>-110.08</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3254,41 +3254,41 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>77303.6341991342</t>
+          <t>77203.15201729107</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>38517.0</t>
+          <t>22600.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>16959.2</t>
+          <t>20034.4</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>11830.5</t>
+          <t>13280.9</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>20783.02</t>
+          <t>20741.92</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>5128</t>
+          <t>6753</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-1030.234332074163</t>
+          <t>-588.5886282543895</t>
         </is>
       </c>
       <c r="BC7" t="n">
-        <v>1507.31</v>
+        <v>1840.46</v>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>-2.77</t>
+          <t>-2.36</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3332,7 +3332,7 @@
       </c>
       <c r="BL7" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="BM7" t="inlineStr">
@@ -3352,7 +3352,7 @@
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
@@ -3362,12 +3362,12 @@
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>6.17</t>
+          <t>6.14</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3377,7 +3377,7 @@
       </c>
       <c r="BU7" t="inlineStr">
         <is>
-          <t>10.11</t>
+          <t>10.17</t>
         </is>
       </c>
       <c r="BV7" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="BX7" t="inlineStr">
         <is>
-          <t>42.34</t>
+          <t>41.96</t>
         </is>
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>4215</t>
+          <t>4239</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3417,22 +3417,22 @@
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>47.5</t>
+          <t>47.85</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>47.85</t>
+          <t>48.1</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>46.5</t>
+          <t>47.25</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>47.4</t>
+          <t>47.6</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3464,12 +3464,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>199.0</t>
+          <t>812.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>47.0</t>
+          <t>47.4</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3489,17 +3489,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-4.91</t>
+          <t>-5.22</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>32.28</t>
+          <t>43.35</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3564,7 +3564,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-5.53</t>
+          <t>-4.72</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3574,17 +3574,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>4.03</t>
+          <t>16.43</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3595,12 +3595,12 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>315</t>
+          <t>112</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
@@ -3615,57 +3615,57 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-4.34</t>
+          <t>-4.23</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>46.2</t>
+          <t>46.66</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>45.67</t>
+          <t>45.74</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>47.75</t>
+          <t>47.76</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>47.39</t>
+          <t>47.42</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>43.77</t>
+          <t>59.88</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3675,7 +3675,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-113.88</t>
+          <t>-112.07</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3685,41 +3685,41 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>77303.6341991342</t>
+          <t>77203.15201729107</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>9304.0</t>
+          <t>38517.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>11007.6</t>
+          <t>16959.2</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>8321.2</t>
+          <t>11830.5</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>21296.56</t>
+          <t>20783.02</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>2686</t>
+          <t>5128</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-1491.606690671351</t>
+          <t>-1030.234332074163</t>
         </is>
       </c>
       <c r="BC8" t="n">
-        <v>-727.84</v>
+        <v>1507.31</v>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>-3.59</t>
+          <t>-2.77</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -3763,7 +3763,7 @@
       </c>
       <c r="BL8" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="BM8" t="inlineStr">
@@ -3783,22 +3783,22 @@
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>6.17</t>
+          <t>6.14</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3808,7 +3808,7 @@
       </c>
       <c r="BU8" t="inlineStr">
         <is>
-          <t>10.11</t>
+          <t>10.17</t>
         </is>
       </c>
       <c r="BV8" t="inlineStr">
@@ -3823,12 +3823,12 @@
       </c>
       <c r="BX8" t="inlineStr">
         <is>
-          <t>42.34</t>
+          <t>41.96</t>
         </is>
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>4215</t>
+          <t>4239</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
@@ -3848,22 +3848,22 @@
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>46.85</t>
+          <t>47.5</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>47.1</t>
+          <t>47.85</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>46.25</t>
+          <t>46.5</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>47.0</t>
+          <t>47.4</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>170.0</t>
+          <t>199.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3910,7 +3910,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>46.65</t>
+          <t>47.0</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3920,17 +3920,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-4.13</t>
+          <t>-4.33</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>23.31</t>
+          <t>32.28</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-6.23</t>
+          <t>-5.53</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4005,17 +4005,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>3.44</t>
+          <t>4.03</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-2.14</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4026,77 +4026,77 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>315</t>
+          <t>112</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>81.58</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>65.79</t>
+          <t>93.86</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-4.26</t>
+          <t>-4.34</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>45.88</t>
+          <t>46.2</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>45.73</t>
+          <t>45.67</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>47.76</t>
+          <t>47.75</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>47.37</t>
+          <t>47.39</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>31.68</t>
+          <t>43.77</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-115.40</t>
+          <t>-113.88</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4116,41 +4116,41 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>77303.6341991342</t>
+          <t>77203.15201729107</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>8007.0</t>
+          <t>9304.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>10142.2</t>
+          <t>11007.6</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>8225.2</t>
+          <t>8321.2</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>21859.62</t>
+          <t>21296.56</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>1917</t>
+          <t>2686</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-1630.473518740948</t>
+          <t>-1491.606690671351</t>
         </is>
       </c>
       <c r="BC9" t="n">
-        <v>-764.96</v>
+        <v>-727.84</v>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>-4.31</t>
+          <t>-3.59</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4194,7 +4194,7 @@
       </c>
       <c r="BL9" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="BM9" t="inlineStr">
@@ -4214,7 +4214,7 @@
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
@@ -4224,12 +4224,12 @@
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>1.89</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>6.17</t>
+          <t>6.14</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="BU9" t="inlineStr">
         <is>
-          <t>10.11</t>
+          <t>10.17</t>
         </is>
       </c>
       <c r="BV9" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="BX9" t="inlineStr">
         <is>
-          <t>42.34</t>
+          <t>41.96</t>
         </is>
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>4215</t>
+          <t>4239</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
@@ -4279,22 +4279,22 @@
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>47.8</t>
+          <t>46.85</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>47.8</t>
+          <t>47.1</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>46.5</t>
+          <t>46.25</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>46.65</t>
+          <t>47.0</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4326,12 +4326,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>3.8</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>464.0</t>
+          <t>170.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4341,7 +4341,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>47.0</t>
+          <t>46.65</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4351,17 +4351,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-4.91</t>
+          <t>-3.55</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>15.69</t>
+          <t>23.31</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4426,7 +4426,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-5.53</t>
+          <t>-6.23</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4436,17 +4436,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>9.39</t>
+          <t>3.44</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>-2.14</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4457,275 +4457,275 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>315</t>
+          <t>112</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>81.58</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>38.6</t>
+          <t>65.79</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-0.37</t>
+          <t>0.33</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-4.22</t>
+          <t>-4.26</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>45.62</t>
+          <t>45.88</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>45.79</t>
+          <t>45.73</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
+          <t>47.76</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>47.37</t>
+        </is>
+      </c>
+      <c r="AP10" t="inlineStr">
+        <is>
+          <t>31.68</t>
+        </is>
+      </c>
+      <c r="AQ10" t="inlineStr">
+        <is>
+          <t>-0.45</t>
+        </is>
+      </c>
+      <c r="AR10" t="inlineStr">
+        <is>
+          <t>-0.66</t>
+        </is>
+      </c>
+      <c r="AS10" t="inlineStr">
+        <is>
+          <t>4.28</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr">
+        <is>
+          <t>-115.40</t>
+        </is>
+      </c>
+      <c r="AU10" t="inlineStr">
+        <is>
+          <t>2025/10/28</t>
+        </is>
+      </c>
+      <c r="AV10" t="inlineStr">
+        <is>
+          <t>77203.15201729107</t>
+        </is>
+      </c>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>8007.0</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>10142.2</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>8225.2</t>
+        </is>
+      </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>21859.62</t>
+        </is>
+      </c>
+      <c r="BA10" t="inlineStr">
+        <is>
+          <t>1917</t>
+        </is>
+      </c>
+      <c r="BB10" t="inlineStr">
+        <is>
+          <t>-1630.473518740948</t>
+        </is>
+      </c>
+      <c r="BC10" t="n">
+        <v>-764.96</v>
+      </c>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BE10" t="inlineStr">
+        <is>
+          <t>48.75</t>
+        </is>
+      </c>
+      <c r="BF10" t="inlineStr">
+        <is>
+          <t>2025/08/25</t>
+        </is>
+      </c>
+      <c r="BG10" t="inlineStr">
+        <is>
+          <t>-4.31</t>
+        </is>
+      </c>
+      <c r="BH10" t="inlineStr">
+        <is>
+          <t>岱稜</t>
+        </is>
+      </c>
+      <c r="BI10" t="inlineStr">
+        <is>
+          <t>岱稜</t>
+        </is>
+      </c>
+      <c r="BJ10" t="inlineStr">
+        <is>
+          <t>其他電子業</t>
+        </is>
+      </c>
+      <c r="BK10" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BL10" t="inlineStr">
+        <is>
+          <t>1.08</t>
+        </is>
+      </c>
+      <c r="BM10" t="inlineStr">
+        <is>
+          <t>-1.004452687200723</t>
+        </is>
+      </c>
+      <c r="BN10" t="inlineStr">
+        <is>
+          <t>11.92388165594906</t>
+        </is>
+      </c>
+      <c r="BO10" t="inlineStr">
+        <is>
+          <t>2.060463205899802</t>
+        </is>
+      </c>
+      <c r="BP10" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BQ10" t="inlineStr">
+        <is>
+          <t>價漲量增</t>
+        </is>
+      </c>
+      <c r="BR10" t="inlineStr">
+        <is>
+          <t>1.89</t>
+        </is>
+      </c>
+      <c r="BS10" t="inlineStr">
+        <is>
+          <t>6.14</t>
+        </is>
+      </c>
+      <c r="BT10" t="inlineStr">
+        <is>
+          <t>8.56</t>
+        </is>
+      </c>
+      <c r="BU10" t="inlineStr">
+        <is>
+          <t>10.17</t>
+        </is>
+      </c>
+      <c r="BV10" t="inlineStr">
+        <is>
+          <t>33.67%</t>
+        </is>
+      </c>
+      <c r="BW10" t="inlineStr">
+        <is>
+          <t>12.48%</t>
+        </is>
+      </c>
+      <c r="BX10" t="inlineStr">
+        <is>
+          <t>41.96</t>
+        </is>
+      </c>
+      <c r="BY10" t="inlineStr">
+        <is>
+          <t>4239</t>
+        </is>
+      </c>
+      <c r="BZ10" t="inlineStr">
+        <is>
+          <t>真空蒸鍍薄膜95.00%、光電材料5.00% (2024年)</t>
+        </is>
+      </c>
+      <c r="CA10" t="inlineStr">
+        <is>
+          <t>岱稜-其他電子業-上櫃</t>
+        </is>
+      </c>
+      <c r="CB10" t="inlineStr">
+        <is>
+          <t>其他電子業平上櫃</t>
+        </is>
+      </c>
+      <c r="CC10" t="inlineStr">
+        <is>
           <t>47.8</t>
         </is>
       </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>47.35</t>
-        </is>
-      </c>
-      <c r="AP10" t="inlineStr">
-        <is>
-          <t>21.78</t>
-        </is>
-      </c>
-      <c r="AQ10" t="inlineStr">
-        <is>
-          <t>-0.56</t>
-        </is>
-      </c>
-      <c r="AR10" t="inlineStr">
-        <is>
-          <t>-0.71</t>
-        </is>
-      </c>
-      <c r="AS10" t="inlineStr">
-        <is>
-          <t>4.28</t>
-        </is>
-      </c>
-      <c r="AT10" t="inlineStr">
-        <is>
-          <t>-116.62</t>
-        </is>
-      </c>
-      <c r="AU10" t="inlineStr">
-        <is>
-          <t>2025/10/28</t>
-        </is>
-      </c>
-      <c r="AV10" t="inlineStr">
-        <is>
-          <t>77303.6341991342</t>
-        </is>
-      </c>
-      <c r="AW10" t="inlineStr">
-        <is>
-          <t>21744.0</t>
-        </is>
-      </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>9374.6</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr">
-        <is>
-          <t>8103.2</t>
-        </is>
-      </c>
-      <c r="AZ10" t="inlineStr">
-        <is>
-          <t>22013.86</t>
-        </is>
-      </c>
-      <c r="BA10" t="inlineStr">
-        <is>
-          <t>1271</t>
-        </is>
-      </c>
-      <c r="BB10" t="inlineStr">
-        <is>
-          <t>-1787.840342020155</t>
-        </is>
-      </c>
-      <c r="BC10" t="n">
-        <v>-651.7</v>
-      </c>
-      <c r="BD10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BE10" t="inlineStr">
-        <is>
-          <t>48.75</t>
-        </is>
-      </c>
-      <c r="BF10" t="inlineStr">
-        <is>
-          <t>2025/08/25</t>
-        </is>
-      </c>
-      <c r="BG10" t="inlineStr">
-        <is>
-          <t>-3.59</t>
-        </is>
-      </c>
-      <c r="BH10" t="inlineStr">
-        <is>
-          <t>岱稜</t>
-        </is>
-      </c>
-      <c r="BI10" t="inlineStr">
-        <is>
-          <t>岱稜</t>
-        </is>
-      </c>
-      <c r="BJ10" t="inlineStr">
-        <is>
-          <t>其他電子業</t>
-        </is>
-      </c>
-      <c r="BK10" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BL10" t="inlineStr">
-        <is>
-          <t>1.09</t>
-        </is>
-      </c>
-      <c r="BM10" t="inlineStr">
-        <is>
-          <t>-1.004452687200723</t>
-        </is>
-      </c>
-      <c r="BN10" t="inlineStr">
-        <is>
-          <t>11.92388165594906</t>
-        </is>
-      </c>
-      <c r="BO10" t="inlineStr">
-        <is>
-          <t>2.060463205899802</t>
-        </is>
-      </c>
-      <c r="BP10" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BQ10" t="inlineStr">
-        <is>
-          <t>價漲量增</t>
-        </is>
-      </c>
-      <c r="BR10" t="inlineStr">
-        <is>
-          <t>1.91</t>
-        </is>
-      </c>
-      <c r="BS10" t="inlineStr">
-        <is>
-          <t>6.17</t>
-        </is>
-      </c>
-      <c r="BT10" t="inlineStr">
-        <is>
-          <t>8.56</t>
-        </is>
-      </c>
-      <c r="BU10" t="inlineStr">
-        <is>
-          <t>10.11</t>
-        </is>
-      </c>
-      <c r="BV10" t="inlineStr">
-        <is>
-          <t>33.67%</t>
-        </is>
-      </c>
-      <c r="BW10" t="inlineStr">
-        <is>
-          <t>12.48%</t>
-        </is>
-      </c>
-      <c r="BX10" t="inlineStr">
-        <is>
-          <t>42.34</t>
-        </is>
-      </c>
-      <c r="BY10" t="inlineStr">
-        <is>
-          <t>4215</t>
-        </is>
-      </c>
-      <c r="BZ10" t="inlineStr">
-        <is>
-          <t>真空蒸鍍薄膜95.00%、光電材料5.00% (2024年)</t>
-        </is>
-      </c>
-      <c r="CA10" t="inlineStr">
-        <is>
-          <t>岱稜-其他電子業-上櫃</t>
-        </is>
-      </c>
-      <c r="CB10" t="inlineStr">
-        <is>
-          <t>其他電子業平上櫃</t>
-        </is>
-      </c>
-      <c r="CC10" t="inlineStr">
-        <is>
-          <t>46.0</t>
-        </is>
-      </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>47.7</t>
+          <t>47.8</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>45.9</t>
+          <t>46.5</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>47.0</t>
+          <t>46.65</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>3.8</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>161.0</t>
+          <t>464.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4772,7 +4772,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>45.25</t>
+          <t>47.0</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4782,17 +4782,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-4.33</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2.94</t>
+          <t>15.69</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4857,7 +4857,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-9.05</t>
+          <t>-5.53</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4867,17 +4867,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>3.26</t>
+          <t>9.39</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4888,177 +4888,177 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>315</t>
+          <t>112</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>15.79</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>9.71</t>
+          <t>38.6</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>3.02</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-1.19</t>
+          <t>-0.37</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-4.21</t>
+          <t>-4.22</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
+          <t>0.97</t>
+        </is>
+      </c>
+      <c r="AL11" t="inlineStr">
+        <is>
+          <t>45.62</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>45.79</t>
+        </is>
+      </c>
+      <c r="AN11" t="inlineStr">
+        <is>
+          <t>47.8</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>47.35</t>
+        </is>
+      </c>
+      <c r="AP11" t="inlineStr">
+        <is>
+          <t>21.78</t>
+        </is>
+      </c>
+      <c r="AQ11" t="inlineStr">
+        <is>
+          <t>-0.56</t>
+        </is>
+      </c>
+      <c r="AR11" t="inlineStr">
+        <is>
+          <t>-0.71</t>
+        </is>
+      </c>
+      <c r="AS11" t="inlineStr">
+        <is>
+          <t>4.28</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr">
+        <is>
+          <t>-116.62</t>
+        </is>
+      </c>
+      <c r="AU11" t="inlineStr">
+        <is>
+          <t>2025/10/28</t>
+        </is>
+      </c>
+      <c r="AV11" t="inlineStr">
+        <is>
+          <t>77203.15201729107</t>
+        </is>
+      </c>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>21744.0</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>9374.6</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>8103.2</t>
+        </is>
+      </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>22013.86</t>
+        </is>
+      </c>
+      <c r="BA11" t="inlineStr">
+        <is>
+          <t>1271</t>
+        </is>
+      </c>
+      <c r="BB11" t="inlineStr">
+        <is>
+          <t>-1787.840342020155</t>
+        </is>
+      </c>
+      <c r="BC11" t="n">
+        <v>-651.7</v>
+      </c>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BE11" t="inlineStr">
+        <is>
+          <t>48.75</t>
+        </is>
+      </c>
+      <c r="BF11" t="inlineStr">
+        <is>
+          <t>2025/08/25</t>
+        </is>
+      </c>
+      <c r="BG11" t="inlineStr">
+        <is>
+          <t>-3.59</t>
+        </is>
+      </c>
+      <c r="BH11" t="inlineStr">
+        <is>
+          <t>岱稜</t>
+        </is>
+      </c>
+      <c r="BI11" t="inlineStr">
+        <is>
+          <t>岱稜</t>
+        </is>
+      </c>
+      <c r="BJ11" t="inlineStr">
+        <is>
+          <t>其他電子業</t>
+        </is>
+      </c>
+      <c r="BK11" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BL11" t="inlineStr">
+        <is>
           <t>1.08</t>
         </is>
       </c>
-      <c r="AL11" t="inlineStr">
-        <is>
-          <t>45.27999999999999</t>
-        </is>
-      </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>45.82</t>
-        </is>
-      </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>47.84</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>47.32</t>
-        </is>
-      </c>
-      <c r="AP11" t="inlineStr">
-        <is>
-          <t>4.09</t>
-        </is>
-      </c>
-      <c r="AQ11" t="inlineStr">
-        <is>
-          <t>-0.72</t>
-        </is>
-      </c>
-      <c r="AR11" t="inlineStr">
-        <is>
-          <t>-0.75</t>
-        </is>
-      </c>
-      <c r="AS11" t="inlineStr">
-        <is>
-          <t>4.28</t>
-        </is>
-      </c>
-      <c r="AT11" t="inlineStr">
-        <is>
-          <t>-117.52</t>
-        </is>
-      </c>
-      <c r="AU11" t="inlineStr">
-        <is>
-          <t>2025/10/28</t>
-        </is>
-      </c>
-      <c r="AV11" t="inlineStr">
-        <is>
-          <t>77303.6341991342</t>
-        </is>
-      </c>
-      <c r="AW11" t="inlineStr">
-        <is>
-          <t>7224.0</t>
-        </is>
-      </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>6527.4</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr">
-        <is>
-          <t>6340.9</t>
-        </is>
-      </c>
-      <c r="AZ11" t="inlineStr">
-        <is>
-          <t>21843.6</t>
-        </is>
-      </c>
-      <c r="BA11" t="inlineStr">
-        <is>
-          <t>186</t>
-        </is>
-      </c>
-      <c r="BB11" t="inlineStr">
-        <is>
-          <t>-1994.41205403867</t>
-        </is>
-      </c>
-      <c r="BC11" t="n">
-        <v>-1938.44</v>
-      </c>
-      <c r="BD11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BE11" t="inlineStr">
-        <is>
-          <t>48.75</t>
-        </is>
-      </c>
-      <c r="BF11" t="inlineStr">
-        <is>
-          <t>2025/08/25</t>
-        </is>
-      </c>
-      <c r="BG11" t="inlineStr">
-        <is>
-          <t>-7.18</t>
-        </is>
-      </c>
-      <c r="BH11" t="inlineStr">
-        <is>
-          <t>岱稜</t>
-        </is>
-      </c>
-      <c r="BI11" t="inlineStr">
-        <is>
-          <t>岱稜</t>
-        </is>
-      </c>
-      <c r="BJ11" t="inlineStr">
-        <is>
-          <t>其他電子業</t>
-        </is>
-      </c>
-      <c r="BK11" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BL11" t="inlineStr">
-        <is>
-          <t>1.09</t>
-        </is>
-      </c>
       <c r="BM11" t="inlineStr">
         <is>
           <t>-1.004452687200723</t>
@@ -5076,7 +5076,7 @@
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
@@ -5086,12 +5086,12 @@
       </c>
       <c r="BR11" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>6.17</t>
+          <t>6.14</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5101,7 +5101,7 @@
       </c>
       <c r="BU11" t="inlineStr">
         <is>
-          <t>10.11</t>
+          <t>10.17</t>
         </is>
       </c>
       <c r="BV11" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="BX11" t="inlineStr">
         <is>
-          <t>42.34</t>
+          <t>41.96</t>
         </is>
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>4215</t>
+          <t>4239</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5141,22 +5141,22 @@
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>44.75</t>
+          <t>46.0</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>45.25</t>
+          <t>47.7</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>44.35</t>
+          <t>45.9</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>45.25</t>
+          <t>47.0</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>194.0</t>
+          <t>161.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>45.1</t>
+          <t>45.25</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5213,17 +5213,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>-0.44</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>2.94</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5288,7 +5288,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-9.35</t>
+          <t>-9.05</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5298,17 +5298,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>3.92</t>
+          <t>3.26</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5319,57 +5319,57 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>315</t>
+          <t>112</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>15.79</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>6.41</t>
+          <t>9.71</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-0.62</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-1.27</t>
+          <t>-1.19</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-4.08</t>
+          <t>-4.21</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>45.38</t>
+          <t>45.27999999999999</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>45.96</t>
+          <t>45.82</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>47.92</t>
+          <t>47.84</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
@@ -5379,17 +5379,17 @@
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>2.53</t>
+          <t>4.09</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.74</t>
+          <t>-0.72</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5399,7 +5399,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-117.70</t>
+          <t>-117.52</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5409,41 +5409,41 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>77303.6341991342</t>
+          <t>77203.15201729107</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>8759.0</t>
+          <t>7224.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>6701.8</t>
+          <t>6527.4</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>6573.5</t>
+          <t>6340.9</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>22067.68</t>
+          <t>21843.6</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>186</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-2004.588353420276</t>
+          <t>-1994.41205403867</t>
         </is>
       </c>
       <c r="BC12" t="n">
-        <v>-2151.71</v>
+        <v>-1938.44</v>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
@@ -5462,7 +5462,7 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>-7.49</t>
+          <t>-7.18</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -5487,7 +5487,7 @@
       </c>
       <c r="BL12" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="BM12" t="inlineStr">
@@ -5507,7 +5507,7 @@
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
@@ -5522,7 +5522,7 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>6.17</t>
+          <t>6.14</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5532,7 +5532,7 @@
       </c>
       <c r="BU12" t="inlineStr">
         <is>
-          <t>10.11</t>
+          <t>10.17</t>
         </is>
       </c>
       <c r="BV12" t="inlineStr">
@@ -5547,12 +5547,12 @@
       </c>
       <c r="BX12" t="inlineStr">
         <is>
-          <t>42.34</t>
+          <t>41.96</t>
         </is>
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>4215</t>
+          <t>4239</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -5572,22 +5572,22 @@
       </c>
       <c r="CC12" t="inlineStr">
         <is>
-          <t>45.4</t>
+          <t>44.75</t>
         </is>
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>45.8</t>
+          <t>45.25</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>44.85</t>
+          <t>44.35</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>45.1</t>
+          <t>45.25</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">

--- a/Result/checksun_type/PET膜.xlsx
+++ b/Result/checksun_type/PET膜.xlsx
@@ -878,12 +878,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>112.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>45.05</t>
+          <t>45.55</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -908,12 +908,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>-0.3</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-30.74</t>
+          <t>-38.31</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-9.45</t>
+          <t>-8.44</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -988,17 +988,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>2.27</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1009,77 +1009,77 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>112</t>
+          <t>70</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>8.93</t>
+          <t>26.79</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>22.13</t>
+          <t>11.9</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-2.32</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-2.65</t>
+          <t>-2.47</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.50</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>46.12</t>
+          <t>45.81</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>46.12</t>
+          <t>46.09</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>47.37</t>
+          <t>47.26</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>47.49</t>
+          <t>47.5</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-13.12</t>
+          <t>-20.83</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-105.11</t>
+          <t>-105.39</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1099,41 +1099,41 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>77203.15201729107</t>
+          <t>77098.98345323741</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>5046.0</t>
+          <t>3204.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>10612.2</t>
+          <t>8309.4</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>15323.3</t>
+          <t>13469.3</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>16780.18</t>
+          <t>16218.6</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-4711</t>
+          <t>-5159</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-100.9576738690555</t>
+          <t>-256.304476051831</t>
         </is>
       </c>
       <c r="BC2" t="n">
-        <v>-490.81</v>
+        <v>-1110.71</v>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>-7.59</t>
+          <t>-6.56</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1177,7 +1177,7 @@
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="BM2" t="inlineStr">
@@ -1197,7 +1197,7 @@
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
@@ -1207,12 +1207,12 @@
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>6.14</t>
+          <t>6.07</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
@@ -1222,7 +1222,7 @@
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>10.17</t>
+          <t>10.28</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="BX2" t="inlineStr">
         <is>
-          <t>41.96</t>
+          <t>42.77</t>
         </is>
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>4239</t>
+          <t>4286</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
@@ -1262,22 +1262,22 @@
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>44.55</t>
+          <t>45.4</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>45.4</t>
+          <t>46.25</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>44.55</t>
+          <t>45.3</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>45.05</t>
+          <t>45.55</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1309,12 +1309,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-3.84</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>315.0</t>
+          <t>112.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>44.8</t>
+          <t>45.05</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1334,17 +1334,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>-0.3</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-9.12</t>
+          <t>-30.74</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1409,7 +1409,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-9.95</t>
+          <t>-9.45</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1419,17 +1419,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>6.37</t>
+          <t>2.27</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-4.69</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1440,57 +1440,57 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>112</t>
+          <t>70</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>8.93</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>45.15</t>
+          <t>22.13</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-3.92</t>
+          <t>-2.32</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-2.8</t>
+          <t>-2.65</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>46.63</t>
+          <t>46.12</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>46.15</t>
+          <t>46.12</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>47.48</t>
+          <t>47.37</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
@@ -1500,17 +1500,17 @@
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>27.78</t>
+          <t>-13.12</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-104.94</t>
+          <t>-105.11</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,41 +1530,41 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>77203.15201729107</t>
+          <t>77098.98345323741</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>14336.0</t>
+          <t>5046.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>14123.0</t>
+          <t>10612.2</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>15541.1</t>
+          <t>15323.3</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>17446.4</t>
+          <t>16780.18</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-1418</t>
+          <t>-4711</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-30.07547477889878</t>
+          <t>-100.9576738690555</t>
         </is>
       </c>
       <c r="BC3" t="n">
-        <v>214.94</v>
+        <v>-490.81</v>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>-8.10</t>
+          <t>-7.59</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1608,7 +1608,7 @@
       </c>
       <c r="BL3" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="BM3" t="inlineStr">
@@ -1628,7 +1628,7 @@
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
@@ -1638,12 +1638,12 @@
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>6.14</t>
+          <t>6.07</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1653,7 +1653,7 @@
       </c>
       <c r="BU3" t="inlineStr">
         <is>
-          <t>10.17</t>
+          <t>10.28</t>
         </is>
       </c>
       <c r="BV3" t="inlineStr">
@@ -1668,12 +1668,12 @@
       </c>
       <c r="BX3" t="inlineStr">
         <is>
-          <t>41.96</t>
+          <t>42.77</t>
         </is>
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>4239</t>
+          <t>4286</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1693,22 +1693,22 @@
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>46.9</t>
+          <t>44.55</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>46.9</t>
+          <t>45.4</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>44.8</t>
+          <t>44.55</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>44.8</t>
+          <t>45.05</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1740,12 +1740,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-0.95</t>
+          <t>-3.84</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>213.0</t>
+          <t>315.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>46.6</t>
+          <t>44.8</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1765,17 +1765,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-3.44</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>-0.3</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>26.53</t>
+          <t>-9.12</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-6.33</t>
+          <t>-9.95</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1850,17 +1850,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>4.31</t>
+          <t>6.37</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>-4.69</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1871,77 +1871,77 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>112</t>
+          <t>70</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>57.45</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>71.82</t>
+          <t>45.15</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-1.17</t>
+          <t>-3.92</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-2.88</t>
+          <t>-2.8</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>47.15</t>
+          <t>46.63</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>46.22</t>
+          <t>46.15</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>47.59</t>
+          <t>47.48</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>47.5</t>
+          <t>47.49</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>98.12</t>
+          <t>27.78</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-0.00</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1951,7 +1951,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-105.28</t>
+          <t>-104.94</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1961,41 +1961,41 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>77203.15201729107</t>
+          <t>77098.98345323741</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>9943.0</t>
+          <t>14336.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>18959.2</t>
+          <t>14123.0</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>14983.4</t>
+          <t>15541.1</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>17743.28</t>
+          <t>17446.4</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>3975</t>
+          <t>-1418</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-74.62310011749315</t>
+          <t>-30.07547477889878</t>
         </is>
       </c>
       <c r="BC4" t="n">
-        <v>220.11</v>
+        <v>214.94</v>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>-4.41</t>
+          <t>-8.10</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2039,7 +2039,7 @@
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="BM4" t="inlineStr">
@@ -2059,7 +2059,7 @@
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
@@ -2069,12 +2069,12 @@
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>1.89</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>6.14</t>
+          <t>6.07</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>10.17</t>
+          <t>10.28</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
@@ -2099,12 +2099,12 @@
       </c>
       <c r="BX4" t="inlineStr">
         <is>
-          <t>41.96</t>
+          <t>42.77</t>
         </is>
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>4239</t>
+          <t>4286</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -2124,22 +2124,22 @@
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>47.15</t>
+          <t>46.9</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>47.2</t>
+          <t>46.9</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>46.4</t>
+          <t>44.8</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>46.6</t>
+          <t>44.8</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>-0.95</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>192.0</t>
+          <t>213.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>47.05</t>
+          <t>46.6</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2196,17 +2196,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-4.44</t>
+          <t>-2.31</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>-0.3</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>29.99</t>
+          <t>26.53</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-5.43</t>
+          <t>-6.33</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2281,17 +2281,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>3.88</t>
+          <t>4.31</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2302,77 +2302,77 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>112</t>
+          <t>70</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>57.45</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>71.82</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>-1.17</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-3.21</t>
+          <t>-2.88</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>47.23</t>
+          <t>47.15</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>46.15</t>
+          <t>46.22</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>47.68</t>
+          <t>47.59</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>47.48</t>
+          <t>47.5</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>100.64</t>
+          <t>98.12</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.00</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-106.58</t>
+          <t>-105.28</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2392,41 +2392,41 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>77203.15201729107</t>
+          <t>77098.98345323741</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>9018.0</t>
+          <t>9943.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>18831.4</t>
+          <t>18959.2</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>14486.8</t>
+          <t>14983.4</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>18676.0</t>
+          <t>17743.28</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>4344</t>
+          <t>3975</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-128.211286383547</t>
+          <t>-74.62310011749315</t>
         </is>
       </c>
       <c r="BC5" t="n">
-        <v>690.3200000000001</v>
+        <v>220.11</v>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
@@ -2445,7 +2445,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>-3.49</t>
+          <t>-4.41</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2470,7 +2470,7 @@
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="BM5" t="inlineStr">
@@ -2495,17 +2495,17 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>1.89</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>6.14</t>
+          <t>6.07</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2515,7 +2515,7 @@
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>10.17</t>
+          <t>10.28</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="BX5" t="inlineStr">
         <is>
-          <t>41.96</t>
+          <t>42.77</t>
         </is>
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>4239</t>
+          <t>4286</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
@@ -2555,22 +2555,22 @@
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>46.5</t>
+          <t>47.15</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>47.5</t>
+          <t>47.2</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>46.35</t>
+          <t>46.4</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>47.05</t>
+          <t>46.6</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2602,12 +2602,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-1.05</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>311.0</t>
+          <t>192.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2617,7 +2617,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>47.1</t>
+          <t>47.05</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2627,17 +2627,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-4.55</t>
+          <t>-3.29</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>-0.3</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>33.05</t>
+          <t>29.99</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2702,7 +2702,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-5.33</t>
+          <t>-5.43</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2712,17 +2712,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>6.29</t>
+          <t>3.88</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-0.95</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2733,77 +2733,77 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>112</t>
+          <t>70</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>93.33</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>2.36</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-3.53</t>
+          <t>-3.21</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>0.60</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>47.15</t>
+          <t>47.23</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>46.06</t>
+          <t>46.15</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>47.75</t>
+          <t>47.68</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>47.47</t>
+          <t>47.48</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>89.68</t>
+          <t>100.64</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2813,7 +2813,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-108.23</t>
+          <t>-106.58</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2823,41 +2823,41 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>77203.15201729107</t>
+          <t>77098.98345323741</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>14718.0</t>
+          <t>9018.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>18629.2</t>
+          <t>18831.4</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>14001.9</t>
+          <t>14486.8</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>20406.5</t>
+          <t>18676.0</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>4627</t>
+          <t>4344</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-277.0356783742832</t>
+          <t>-128.211286383547</t>
         </is>
       </c>
       <c r="BC6" t="n">
-        <v>1436.51</v>
+        <v>690.3200000000001</v>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>-3.38</t>
+          <t>-3.49</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="BL6" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="BM6" t="inlineStr">
@@ -2926,7 +2926,7 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>6.14</t>
+          <t>6.07</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BU6" t="inlineStr">
         <is>
-          <t>10.17</t>
+          <t>10.28</t>
         </is>
       </c>
       <c r="BV6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BX6" t="inlineStr">
         <is>
-          <t>41.96</t>
+          <t>42.77</t>
         </is>
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>4239</t>
+          <t>4286</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>47.6</t>
+          <t>46.5</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>47.8</t>
+          <t>47.5</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>46.85</t>
+          <t>46.35</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>47.1</t>
+          <t>47.05</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>-1.05</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>474.0</t>
+          <t>311.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>47.6</t>
+          <t>47.1</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-5.66</t>
+          <t>-3.4</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>-0.3</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>50.85</t>
+          <t>33.05</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-4.32</t>
+          <t>-5.33</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>9.59</t>
+          <t>6.29</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-0.95</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,77 +3164,77 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>112</t>
+          <t>70</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>93.33</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>2.67</t>
+          <t>2.36</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-3.93</t>
+          <t>-3.53</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.60</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>47.13</t>
+          <t>47.15</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>45.9</t>
+          <t>46.06</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>47.78</t>
+          <t>47.75</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>47.45</t>
+          <t>47.47</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>79.21</t>
+          <t>89.68</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3244,7 +3244,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-110.08</t>
+          <t>-108.23</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3254,41 +3254,41 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>77203.15201729107</t>
+          <t>77098.98345323741</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>22600.0</t>
+          <t>14718.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>20034.4</t>
+          <t>18629.2</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>13280.9</t>
+          <t>14001.9</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>20741.92</t>
+          <t>20406.5</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>6753</t>
+          <t>4627</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-588.5886282543895</t>
+          <t>-277.0356783742832</t>
         </is>
       </c>
       <c r="BC7" t="n">
-        <v>1840.46</v>
+        <v>1436.51</v>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>-2.36</t>
+          <t>-3.38</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3332,7 +3332,7 @@
       </c>
       <c r="BL7" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="BM7" t="inlineStr">
@@ -3352,22 +3352,22 @@
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>6.14</t>
+          <t>6.07</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3377,7 +3377,7 @@
       </c>
       <c r="BU7" t="inlineStr">
         <is>
-          <t>10.17</t>
+          <t>10.28</t>
         </is>
       </c>
       <c r="BV7" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="BX7" t="inlineStr">
         <is>
-          <t>41.96</t>
+          <t>42.77</t>
         </is>
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>4239</t>
+          <t>4286</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3417,22 +3417,22 @@
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>47.85</t>
+          <t>47.6</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>48.1</t>
+          <t>47.8</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>47.25</t>
+          <t>46.85</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>47.6</t>
+          <t>47.1</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3464,12 +3464,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>812.0</t>
+          <t>474.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>47.4</t>
+          <t>47.6</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3489,17 +3489,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-5.22</t>
+          <t>-4.5</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>-0.3</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>43.35</t>
+          <t>50.85</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3564,7 +3564,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-4.72</t>
+          <t>-4.32</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3574,17 +3574,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16.43</t>
+          <t>9.59</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3595,12 +3595,12 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>112</t>
+          <t>70</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
@@ -3610,62 +3610,62 @@
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>93.86</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>2.67</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-4.23</t>
+          <t>-3.93</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>46.66</t>
+          <t>47.13</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>45.74</t>
+          <t>45.9</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>47.76</t>
+          <t>47.78</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>47.42</t>
+          <t>47.45</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>59.88</t>
+          <t>79.21</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3675,7 +3675,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-112.07</t>
+          <t>-110.08</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3685,41 +3685,41 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>77203.15201729107</t>
+          <t>77098.98345323741</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>38517.0</t>
+          <t>22600.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>16959.2</t>
+          <t>20034.4</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>11830.5</t>
+          <t>13280.9</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>20783.02</t>
+          <t>20741.92</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>5128</t>
+          <t>6753</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-1030.234332074163</t>
+          <t>-588.5886282543895</t>
         </is>
       </c>
       <c r="BC8" t="n">
-        <v>1507.31</v>
+        <v>1840.46</v>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>-2.77</t>
+          <t>-2.36</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -3763,7 +3763,7 @@
       </c>
       <c r="BL8" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="BM8" t="inlineStr">
@@ -3783,7 +3783,7 @@
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
@@ -3793,12 +3793,12 @@
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>6.14</t>
+          <t>6.07</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3808,7 +3808,7 @@
       </c>
       <c r="BU8" t="inlineStr">
         <is>
-          <t>10.17</t>
+          <t>10.28</t>
         </is>
       </c>
       <c r="BV8" t="inlineStr">
@@ -3823,12 +3823,12 @@
       </c>
       <c r="BX8" t="inlineStr">
         <is>
-          <t>41.96</t>
+          <t>42.77</t>
         </is>
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>4239</t>
+          <t>4286</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
@@ -3848,22 +3848,22 @@
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>47.5</t>
+          <t>47.85</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>47.85</t>
+          <t>48.1</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>46.5</t>
+          <t>47.25</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>47.4</t>
+          <t>47.6</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>199.0</t>
+          <t>812.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3910,7 +3910,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>47.0</t>
+          <t>47.4</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3920,17 +3920,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-4.33</t>
+          <t>-4.06</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>-0.3</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>32.28</t>
+          <t>43.35</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-5.53</t>
+          <t>-4.72</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4005,17 +4005,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>4.03</t>
+          <t>16.43</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4026,12 +4026,12 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>112</t>
+          <t>70</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
@@ -4046,57 +4046,57 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-4.34</t>
+          <t>-4.23</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>46.2</t>
+          <t>46.66</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>45.67</t>
+          <t>45.74</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>47.75</t>
+          <t>47.76</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>47.39</t>
+          <t>47.42</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>43.77</t>
+          <t>59.88</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-113.88</t>
+          <t>-112.07</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4116,41 +4116,41 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>77203.15201729107</t>
+          <t>77098.98345323741</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>9304.0</t>
+          <t>38517.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>11007.6</t>
+          <t>16959.2</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>8321.2</t>
+          <t>11830.5</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>21296.56</t>
+          <t>20783.02</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>2686</t>
+          <t>5128</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-1491.606690671351</t>
+          <t>-1030.234332074163</t>
         </is>
       </c>
       <c r="BC9" t="n">
-        <v>-727.84</v>
+        <v>1507.31</v>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>-3.59</t>
+          <t>-2.77</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4194,7 +4194,7 @@
       </c>
       <c r="BL9" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="BM9" t="inlineStr">
@@ -4214,22 +4214,22 @@
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>6.14</t>
+          <t>6.07</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="BU9" t="inlineStr">
         <is>
-          <t>10.17</t>
+          <t>10.28</t>
         </is>
       </c>
       <c r="BV9" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="BX9" t="inlineStr">
         <is>
-          <t>41.96</t>
+          <t>42.77</t>
         </is>
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>4239</t>
+          <t>4286</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
@@ -4279,22 +4279,22 @@
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>46.85</t>
+          <t>47.5</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>47.1</t>
+          <t>47.85</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>46.25</t>
+          <t>46.5</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>47.0</t>
+          <t>47.4</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4326,12 +4326,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>170.0</t>
+          <t>199.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4341,7 +4341,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>46.65</t>
+          <t>47.0</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4351,17 +4351,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-3.55</t>
+          <t>-3.18</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>-0.3</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>23.31</t>
+          <t>32.28</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4426,7 +4426,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-6.23</t>
+          <t>-5.53</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4436,17 +4436,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>3.44</t>
+          <t>4.03</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-2.14</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4457,77 +4457,77 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>112</t>
+          <t>70</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>81.58</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>65.79</t>
+          <t>93.86</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-4.26</t>
+          <t>-4.34</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>45.88</t>
+          <t>46.2</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>45.73</t>
+          <t>45.67</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>47.76</t>
+          <t>47.75</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>47.37</t>
+          <t>47.39</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>31.68</t>
+          <t>43.77</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4537,7 +4537,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-115.40</t>
+          <t>-113.88</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4547,41 +4547,41 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>77203.15201729107</t>
+          <t>77098.98345323741</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>8007.0</t>
+          <t>9304.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>10142.2</t>
+          <t>11007.6</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>8225.2</t>
+          <t>8321.2</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>21859.62</t>
+          <t>21296.56</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>1917</t>
+          <t>2686</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-1630.473518740948</t>
+          <t>-1491.606690671351</t>
         </is>
       </c>
       <c r="BC10" t="n">
-        <v>-764.96</v>
+        <v>-727.84</v>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
@@ -4600,7 +4600,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>-4.31</t>
+          <t>-3.59</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -4625,7 +4625,7 @@
       </c>
       <c r="BL10" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="BM10" t="inlineStr">
@@ -4645,7 +4645,7 @@
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
@@ -4655,12 +4655,12 @@
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>1.89</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>6.14</t>
+          <t>6.07</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4670,7 +4670,7 @@
       </c>
       <c r="BU10" t="inlineStr">
         <is>
-          <t>10.17</t>
+          <t>10.28</t>
         </is>
       </c>
       <c r="BV10" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="BX10" t="inlineStr">
         <is>
-          <t>41.96</t>
+          <t>42.77</t>
         </is>
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>4239</t>
+          <t>4286</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -4710,22 +4710,22 @@
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>47.8</t>
+          <t>46.85</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>47.8</t>
+          <t>47.1</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>46.5</t>
+          <t>46.25</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>46.65</t>
+          <t>47.0</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>3.8</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>464.0</t>
+          <t>170.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4772,7 +4772,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>47.0</t>
+          <t>46.65</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4782,17 +4782,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-4.33</t>
+          <t>-2.41</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>-0.3</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>15.69</t>
+          <t>23.31</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4857,7 +4857,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-5.53</t>
+          <t>-6.23</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4867,17 +4867,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>9.39</t>
+          <t>3.44</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>-2.14</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4888,275 +4888,275 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>112</t>
+          <t>70</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>81.58</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>38.6</t>
+          <t>65.79</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-0.37</t>
+          <t>0.33</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-4.22</t>
+          <t>-4.26</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>45.62</t>
+          <t>45.88</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>45.79</t>
+          <t>45.73</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
+          <t>47.76</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>47.37</t>
+        </is>
+      </c>
+      <c r="AP11" t="inlineStr">
+        <is>
+          <t>31.68</t>
+        </is>
+      </c>
+      <c r="AQ11" t="inlineStr">
+        <is>
+          <t>-0.45</t>
+        </is>
+      </c>
+      <c r="AR11" t="inlineStr">
+        <is>
+          <t>-0.66</t>
+        </is>
+      </c>
+      <c r="AS11" t="inlineStr">
+        <is>
+          <t>4.28</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr">
+        <is>
+          <t>-115.40</t>
+        </is>
+      </c>
+      <c r="AU11" t="inlineStr">
+        <is>
+          <t>2025/10/28</t>
+        </is>
+      </c>
+      <c r="AV11" t="inlineStr">
+        <is>
+          <t>77098.98345323741</t>
+        </is>
+      </c>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>8007.0</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>10142.2</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>8225.2</t>
+        </is>
+      </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>21859.62</t>
+        </is>
+      </c>
+      <c r="BA11" t="inlineStr">
+        <is>
+          <t>1917</t>
+        </is>
+      </c>
+      <c r="BB11" t="inlineStr">
+        <is>
+          <t>-1630.473518740948</t>
+        </is>
+      </c>
+      <c r="BC11" t="n">
+        <v>-764.96</v>
+      </c>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BE11" t="inlineStr">
+        <is>
+          <t>48.75</t>
+        </is>
+      </c>
+      <c r="BF11" t="inlineStr">
+        <is>
+          <t>2025/08/25</t>
+        </is>
+      </c>
+      <c r="BG11" t="inlineStr">
+        <is>
+          <t>-4.31</t>
+        </is>
+      </c>
+      <c r="BH11" t="inlineStr">
+        <is>
+          <t>岱稜</t>
+        </is>
+      </c>
+      <c r="BI11" t="inlineStr">
+        <is>
+          <t>岱稜</t>
+        </is>
+      </c>
+      <c r="BJ11" t="inlineStr">
+        <is>
+          <t>其他電子業</t>
+        </is>
+      </c>
+      <c r="BK11" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BL11" t="inlineStr">
+        <is>
+          <t>1.07</t>
+        </is>
+      </c>
+      <c r="BM11" t="inlineStr">
+        <is>
+          <t>-1.004452687200723</t>
+        </is>
+      </c>
+      <c r="BN11" t="inlineStr">
+        <is>
+          <t>11.92388165594906</t>
+        </is>
+      </c>
+      <c r="BO11" t="inlineStr">
+        <is>
+          <t>2.060463205899802</t>
+        </is>
+      </c>
+      <c r="BP11" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BQ11" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BR11" t="inlineStr">
+        <is>
+          <t>1.89</t>
+        </is>
+      </c>
+      <c r="BS11" t="inlineStr">
+        <is>
+          <t>6.07</t>
+        </is>
+      </c>
+      <c r="BT11" t="inlineStr">
+        <is>
+          <t>8.56</t>
+        </is>
+      </c>
+      <c r="BU11" t="inlineStr">
+        <is>
+          <t>10.28</t>
+        </is>
+      </c>
+      <c r="BV11" t="inlineStr">
+        <is>
+          <t>33.67%</t>
+        </is>
+      </c>
+      <c r="BW11" t="inlineStr">
+        <is>
+          <t>12.48%</t>
+        </is>
+      </c>
+      <c r="BX11" t="inlineStr">
+        <is>
+          <t>42.77</t>
+        </is>
+      </c>
+      <c r="BY11" t="inlineStr">
+        <is>
+          <t>4286</t>
+        </is>
+      </c>
+      <c r="BZ11" t="inlineStr">
+        <is>
+          <t>真空蒸鍍薄膜95.00%、光電材料5.00% (2024年)</t>
+        </is>
+      </c>
+      <c r="CA11" t="inlineStr">
+        <is>
+          <t>岱稜-其他電子業-上櫃</t>
+        </is>
+      </c>
+      <c r="CB11" t="inlineStr">
+        <is>
+          <t>其他電子業平上櫃</t>
+        </is>
+      </c>
+      <c r="CC11" t="inlineStr">
+        <is>
           <t>47.8</t>
         </is>
       </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>47.35</t>
-        </is>
-      </c>
-      <c r="AP11" t="inlineStr">
-        <is>
-          <t>21.78</t>
-        </is>
-      </c>
-      <c r="AQ11" t="inlineStr">
-        <is>
-          <t>-0.56</t>
-        </is>
-      </c>
-      <c r="AR11" t="inlineStr">
-        <is>
-          <t>-0.71</t>
-        </is>
-      </c>
-      <c r="AS11" t="inlineStr">
-        <is>
-          <t>4.28</t>
-        </is>
-      </c>
-      <c r="AT11" t="inlineStr">
-        <is>
-          <t>-116.62</t>
-        </is>
-      </c>
-      <c r="AU11" t="inlineStr">
-        <is>
-          <t>2025/10/28</t>
-        </is>
-      </c>
-      <c r="AV11" t="inlineStr">
-        <is>
-          <t>77203.15201729107</t>
-        </is>
-      </c>
-      <c r="AW11" t="inlineStr">
-        <is>
-          <t>21744.0</t>
-        </is>
-      </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>9374.6</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr">
-        <is>
-          <t>8103.2</t>
-        </is>
-      </c>
-      <c r="AZ11" t="inlineStr">
-        <is>
-          <t>22013.86</t>
-        </is>
-      </c>
-      <c r="BA11" t="inlineStr">
-        <is>
-          <t>1271</t>
-        </is>
-      </c>
-      <c r="BB11" t="inlineStr">
-        <is>
-          <t>-1787.840342020155</t>
-        </is>
-      </c>
-      <c r="BC11" t="n">
-        <v>-651.7</v>
-      </c>
-      <c r="BD11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BE11" t="inlineStr">
-        <is>
-          <t>48.75</t>
-        </is>
-      </c>
-      <c r="BF11" t="inlineStr">
-        <is>
-          <t>2025/08/25</t>
-        </is>
-      </c>
-      <c r="BG11" t="inlineStr">
-        <is>
-          <t>-3.59</t>
-        </is>
-      </c>
-      <c r="BH11" t="inlineStr">
-        <is>
-          <t>岱稜</t>
-        </is>
-      </c>
-      <c r="BI11" t="inlineStr">
-        <is>
-          <t>岱稜</t>
-        </is>
-      </c>
-      <c r="BJ11" t="inlineStr">
-        <is>
-          <t>其他電子業</t>
-        </is>
-      </c>
-      <c r="BK11" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BL11" t="inlineStr">
-        <is>
-          <t>1.08</t>
-        </is>
-      </c>
-      <c r="BM11" t="inlineStr">
-        <is>
-          <t>-1.004452687200723</t>
-        </is>
-      </c>
-      <c r="BN11" t="inlineStr">
-        <is>
-          <t>11.92388165594906</t>
-        </is>
-      </c>
-      <c r="BO11" t="inlineStr">
-        <is>
-          <t>2.060463205899802</t>
-        </is>
-      </c>
-      <c r="BP11" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BQ11" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="BR11" t="inlineStr">
-        <is>
-          <t>1.91</t>
-        </is>
-      </c>
-      <c r="BS11" t="inlineStr">
-        <is>
-          <t>6.14</t>
-        </is>
-      </c>
-      <c r="BT11" t="inlineStr">
-        <is>
-          <t>8.56</t>
-        </is>
-      </c>
-      <c r="BU11" t="inlineStr">
-        <is>
-          <t>10.17</t>
-        </is>
-      </c>
-      <c r="BV11" t="inlineStr">
-        <is>
-          <t>33.67%</t>
-        </is>
-      </c>
-      <c r="BW11" t="inlineStr">
-        <is>
-          <t>12.48%</t>
-        </is>
-      </c>
-      <c r="BX11" t="inlineStr">
-        <is>
-          <t>41.96</t>
-        </is>
-      </c>
-      <c r="BY11" t="inlineStr">
-        <is>
-          <t>4239</t>
-        </is>
-      </c>
-      <c r="BZ11" t="inlineStr">
-        <is>
-          <t>真空蒸鍍薄膜95.00%、光電材料5.00% (2024年)</t>
-        </is>
-      </c>
-      <c r="CA11" t="inlineStr">
-        <is>
-          <t>岱稜-其他電子業-上櫃</t>
-        </is>
-      </c>
-      <c r="CB11" t="inlineStr">
-        <is>
-          <t>其他電子業平上櫃</t>
-        </is>
-      </c>
-      <c r="CC11" t="inlineStr">
-        <is>
-          <t>46.0</t>
-        </is>
-      </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>47.7</t>
+          <t>47.8</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>45.9</t>
+          <t>46.5</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>47.0</t>
+          <t>46.65</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>3.8</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>161.0</t>
+          <t>464.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>45.25</t>
+          <t>47.0</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5213,17 +5213,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>-3.18</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>-0.3</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2.94</t>
+          <t>15.69</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5288,7 +5288,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-9.05</t>
+          <t>-5.53</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5298,17 +5298,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>3.26</t>
+          <t>9.39</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5319,77 +5319,77 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>112</t>
+          <t>70</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>15.79</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>9.71</t>
+          <t>38.6</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>3.02</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-1.19</t>
+          <t>-0.37</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-4.21</t>
+          <t>-4.22</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>45.27999999999999</t>
+          <t>45.62</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>45.82</t>
+          <t>45.79</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>47.84</t>
+          <t>47.8</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>47.32</t>
+          <t>47.35</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>4.09</t>
+          <t>21.78</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>-0.56</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5399,7 +5399,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-117.52</t>
+          <t>-116.62</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5409,41 +5409,41 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>77203.15201729107</t>
+          <t>77098.98345323741</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>7224.0</t>
+          <t>21744.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>6527.4</t>
+          <t>9374.6</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>6340.9</t>
+          <t>8103.2</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>21843.6</t>
+          <t>22013.86</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>186</t>
+          <t>1271</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-1994.41205403867</t>
+          <t>-1787.840342020155</t>
         </is>
       </c>
       <c r="BC12" t="n">
-        <v>-1938.44</v>
+        <v>-651.7</v>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
@@ -5462,7 +5462,7 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>-7.18</t>
+          <t>-3.59</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -5487,7 +5487,7 @@
       </c>
       <c r="BL12" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="BM12" t="inlineStr">
@@ -5507,7 +5507,7 @@
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
@@ -5517,12 +5517,12 @@
       </c>
       <c r="BR12" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>6.14</t>
+          <t>6.07</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5532,7 +5532,7 @@
       </c>
       <c r="BU12" t="inlineStr">
         <is>
-          <t>10.17</t>
+          <t>10.28</t>
         </is>
       </c>
       <c r="BV12" t="inlineStr">
@@ -5547,12 +5547,12 @@
       </c>
       <c r="BX12" t="inlineStr">
         <is>
-          <t>41.96</t>
+          <t>42.77</t>
         </is>
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>4239</t>
+          <t>4286</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -5572,22 +5572,22 @@
       </c>
       <c r="CC12" t="inlineStr">
         <is>
-          <t>44.75</t>
+          <t>46.0</t>
         </is>
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>45.25</t>
+          <t>47.7</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>44.35</t>
+          <t>45.9</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>45.25</t>
+          <t>47.0</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">

--- a/Result/checksun_type/PET膜.xlsx
+++ b/Result/checksun_type/PET膜.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CI12"/>
+  <dimension ref="A1:CJ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -701,165 +701,170 @@
       </c>
       <c r="BC1" s="1" t="inlineStr">
         <is>
-          <t>Volume_Price_Change_sum</t>
+          <t>VPC_MACD</t>
         </is>
       </c>
       <c r="BD1" s="1" t="inlineStr">
         <is>
+          <t>Volume_Price_Change</t>
+        </is>
+      </c>
+      <c r="BE1" s="1" t="inlineStr">
+        <is>
           <t>highlight_enddate</t>
         </is>
       </c>
-      <c r="BE1" s="1" t="inlineStr">
+      <c r="BF1" s="1" t="inlineStr">
         <is>
           <t>MA_last_cross_date收盤價</t>
         </is>
       </c>
-      <c r="BF1" s="1" t="inlineStr">
+      <c r="BG1" s="1" t="inlineStr">
         <is>
           <t>MA_last_cross_date</t>
         </is>
       </c>
-      <c r="BG1" s="1" t="inlineStr">
+      <c r="BH1" s="1" t="inlineStr">
         <is>
           <t>MA_last_cross_%</t>
         </is>
       </c>
-      <c r="BH1" s="1" t="inlineStr">
+      <c r="BI1" s="1" t="inlineStr">
         <is>
           <t>stock_name</t>
         </is>
       </c>
-      <c r="BI1" s="1" t="inlineStr">
+      <c r="BJ1" s="1" t="inlineStr">
         <is>
           <t>Type0</t>
         </is>
       </c>
-      <c r="BJ1" s="1" t="inlineStr">
+      <c r="BK1" s="1" t="inlineStr">
         <is>
           <t>Type1</t>
         </is>
       </c>
-      <c r="BK1" s="1" t="inlineStr">
+      <c r="BL1" s="1" t="inlineStr">
         <is>
           <t>Type2</t>
         </is>
       </c>
-      <c r="BL1" s="1" t="inlineStr">
+      <c r="BM1" s="1" t="inlineStr">
         <is>
           <t>貝他值</t>
         </is>
       </c>
-      <c r="BM1" s="1" t="inlineStr">
+      <c r="BN1" s="1" t="inlineStr">
         <is>
           <t>營業收入-上月比較增減(%)</t>
         </is>
       </c>
-      <c r="BN1" s="1" t="inlineStr">
+      <c r="BO1" s="1" t="inlineStr">
         <is>
           <t>營業收入-去年同月增減(%)</t>
         </is>
       </c>
-      <c r="BO1" s="1" t="inlineStr">
+      <c r="BP1" s="1" t="inlineStr">
         <is>
           <t>累計營業收入-前期比較增減(%)</t>
         </is>
       </c>
-      <c r="BP1" s="1" t="inlineStr">
+      <c r="BQ1" s="1" t="inlineStr">
         <is>
           <t>Full_Summary</t>
         </is>
       </c>
-      <c r="BQ1" s="1" t="inlineStr">
+      <c r="BR1" s="1" t="inlineStr">
         <is>
           <t>textdesc</t>
         </is>
       </c>
-      <c r="BR1" s="1" t="inlineStr">
+      <c r="BS1" s="1" t="inlineStr">
         <is>
           <t>淨值倍率</t>
         </is>
       </c>
-      <c r="BS1" s="1" t="inlineStr">
+      <c r="BT1" s="1" t="inlineStr">
         <is>
           <t>殖利率</t>
         </is>
       </c>
-      <c r="BT1" s="1" t="inlineStr">
+      <c r="BU1" s="1" t="inlineStr">
         <is>
           <t>每股營收(元)</t>
         </is>
       </c>
-      <c r="BU1" s="1" t="inlineStr">
+      <c r="BV1" s="1" t="inlineStr">
         <is>
           <t>本益比</t>
         </is>
       </c>
-      <c r="BV1" s="1" t="inlineStr">
+      <c r="BW1" s="1" t="inlineStr">
         <is>
           <t>營業毛利率</t>
         </is>
       </c>
-      <c r="BW1" s="1" t="inlineStr">
+      <c r="BX1" s="1" t="inlineStr">
         <is>
           <t>營業利益率</t>
         </is>
       </c>
-      <c r="BX1" s="1" t="inlineStr">
+      <c r="BY1" s="1" t="inlineStr">
         <is>
           <t>同業平均本益比</t>
         </is>
       </c>
-      <c r="BY1" s="1" t="inlineStr">
+      <c r="BZ1" s="1" t="inlineStr">
         <is>
           <t>總市值</t>
         </is>
       </c>
-      <c r="BZ1" s="1" t="inlineStr">
+      <c r="CA1" s="1" t="inlineStr">
         <is>
           <t>營收比重</t>
         </is>
       </c>
-      <c r="CA1" s="1" t="inlineStr">
+      <c r="CB1" s="1" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="CB1" s="1" t="inlineStr">
+      <c r="CC1" s="1" t="inlineStr">
         <is>
           <t>Typelevel</t>
         </is>
       </c>
-      <c r="CC1" s="1" t="inlineStr">
+      <c r="CD1" s="1" t="inlineStr">
         <is>
           <t>開盤價</t>
         </is>
       </c>
-      <c r="CD1" s="1" t="inlineStr">
+      <c r="CE1" s="1" t="inlineStr">
         <is>
           <t>最高價</t>
         </is>
       </c>
-      <c r="CE1" s="1" t="inlineStr">
+      <c r="CF1" s="1" t="inlineStr">
         <is>
           <t>最低價</t>
         </is>
       </c>
-      <c r="CF1" s="1" t="inlineStr">
+      <c r="CG1" s="1" t="inlineStr">
         <is>
           <t>收盤價</t>
         </is>
       </c>
-      <c r="CG1" s="1" t="inlineStr">
+      <c r="CH1" s="1" t="inlineStr">
         <is>
           <t>每股淨值(元)</t>
         </is>
       </c>
-      <c r="CH1" s="1" t="inlineStr">
+      <c r="CI1" s="1" t="inlineStr">
         <is>
           <t>desc</t>
         </is>
       </c>
-      <c r="CI1" s="1" t="inlineStr">
+      <c r="CJ1" s="1" t="inlineStr">
         <is>
           <t>flag_stat</t>
         </is>
@@ -878,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>-1.77</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>177.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -893,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>45.55</t>
+          <t>44.75</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -908,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-0.3</t>
+          <t>-0.96</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-38.31</t>
+          <t>-39.89</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -978,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-8.44</t>
+          <t>-10.05</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -988,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>3.91</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-0.98</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1009,17 +1014,17 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>177</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>26.79</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
@@ -1029,37 +1034,37 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>-1.32</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>-1.47</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-2.47</t>
+          <t>-2.34</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-0.50</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>45.81</t>
+          <t>45.35</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>46.09</t>
+          <t>46.03</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>47.26</t>
+          <t>47.13</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
@@ -1069,17 +1074,17 @@
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-20.83</t>
+          <t>-41.45</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>-0.36</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1089,7 +1094,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-105.39</t>
+          <t>-106.01</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1099,198 +1104,203 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>77098.98345323741</t>
+          <t>77005.29094827587</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>3204.0</t>
+          <t>7926.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>8309.4</t>
+          <t>8091.0</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>13469.3</t>
+          <t>13461.2</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>16218.6</t>
+          <t>15558.56</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-5159</t>
+          <t>-5370</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-256.304476051831</t>
-        </is>
-      </c>
-      <c r="BC2" t="n">
-        <v>-1110.71</v>
-      </c>
-      <c r="BD2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>-395.7538757808097</t>
+        </is>
+      </c>
+      <c r="BC2" t="inlineStr">
+        <is>
+          <t>-1162.725574290193</t>
+        </is>
+      </c>
+      <c r="BD2" t="n">
+        <v>7926</v>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF2" t="inlineStr">
+        <is>
           <t>48.75</t>
         </is>
       </c>
-      <c r="BF2" t="inlineStr">
+      <c r="BG2" t="inlineStr">
         <is>
           <t>2025/08/25</t>
         </is>
       </c>
-      <c r="BG2" t="inlineStr">
-        <is>
-          <t>-6.56</t>
-        </is>
-      </c>
       <c r="BH2" t="inlineStr">
         <is>
+          <t>-8.21</t>
+        </is>
+      </c>
+      <c r="BI2" t="inlineStr">
+        <is>
           <t>岱稜</t>
         </is>
       </c>
-      <c r="BI2" t="inlineStr">
+      <c r="BJ2" t="inlineStr">
         <is>
           <t>岱稜</t>
         </is>
       </c>
-      <c r="BJ2" t="inlineStr">
+      <c r="BK2" t="inlineStr">
         <is>
           <t>其他電子業</t>
         </is>
       </c>
-      <c r="BK2" t="inlineStr">
+      <c r="BL2" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BL2" t="inlineStr">
-        <is>
-          <t>1.07</t>
-        </is>
-      </c>
       <c r="BM2" t="inlineStr">
         <is>
+          <t>1.05</t>
+        </is>
+      </c>
+      <c r="BN2" t="inlineStr">
+        <is>
           <t>-1.004452687200723</t>
         </is>
       </c>
-      <c r="BN2" t="inlineStr">
+      <c r="BO2" t="inlineStr">
         <is>
           <t>11.92388165594906</t>
         </is>
       </c>
-      <c r="BO2" t="inlineStr">
+      <c r="BP2" t="inlineStr">
         <is>
           <t>2.060463205899802</t>
         </is>
       </c>
-      <c r="BP2" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="BQ2" t="inlineStr">
         <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR2" t="inlineStr">
+        <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="BR2" t="inlineStr">
-        <is>
-          <t>1.85</t>
-        </is>
-      </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>6.07</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
+          <t>6.18</t>
+        </is>
+      </c>
+      <c r="BU2" t="inlineStr">
+        <is>
           <t>8.56</t>
         </is>
       </c>
-      <c r="BU2" t="inlineStr">
-        <is>
-          <t>10.28</t>
-        </is>
-      </c>
       <c r="BV2" t="inlineStr">
         <is>
+          <t>10.1</t>
+        </is>
+      </c>
+      <c r="BW2" t="inlineStr">
+        <is>
           <t>33.67%</t>
         </is>
       </c>
-      <c r="BW2" t="inlineStr">
+      <c r="BX2" t="inlineStr">
         <is>
           <t>12.48%</t>
         </is>
       </c>
-      <c r="BX2" t="inlineStr">
-        <is>
-          <t>42.77</t>
-        </is>
-      </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>4286</t>
+          <t>41.57</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
+          <t>4211</t>
+        </is>
+      </c>
+      <c r="CA2" t="inlineStr">
+        <is>
           <t>真空蒸鍍薄膜95.00%、光電材料5.00% (2024年)</t>
         </is>
       </c>
-      <c r="CA2" t="inlineStr">
+      <c r="CB2" t="inlineStr">
         <is>
           <t>岱稜-其他電子業-上櫃</t>
         </is>
       </c>
-      <c r="CB2" t="inlineStr">
+      <c r="CC2" t="inlineStr">
         <is>
           <t>其他電子業平上櫃</t>
         </is>
       </c>
-      <c r="CC2" t="inlineStr">
-        <is>
-          <t>45.4</t>
-        </is>
-      </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>46.25</t>
+          <t>45.2</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>45.3</t>
+          <t>45.2</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>45.55</t>
+          <t>44.6</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
+          <t>44.75</t>
+        </is>
+      </c>
+      <c r="CH2" t="inlineStr">
+        <is>
           <t>24.66</t>
         </is>
       </c>
-      <c r="CH2" t="inlineStr">
+      <c r="CI2" t="inlineStr">
         <is>
           <t>** 觸控面板 - PET膜** 其他 - 其他電子產品及電子服務產業、其他** 醫療器材 - 塑化材料</t>
         </is>
       </c>
-      <c r="CI2" t="inlineStr">
+      <c r="CJ2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -1309,12 +1319,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>112.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1324,7 +1334,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>45.05</t>
+          <t>45.55</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1334,17 +1344,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>-1.79</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-0.3</t>
+          <t>-0.96</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-30.74</t>
+          <t>-38.31</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1409,7 +1419,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-9.45</t>
+          <t>-8.44</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1419,17 +1429,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>2.27</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1440,77 +1450,77 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>177</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>8.93</t>
+          <t>26.79</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>22.13</t>
+          <t>11.9</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-2.32</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-2.65</t>
+          <t>-2.47</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.50</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>46.12</t>
+          <t>45.81</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>46.12</t>
+          <t>46.09</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>47.37</t>
+          <t>47.26</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>47.49</t>
+          <t>47.5</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-13.12</t>
+          <t>-20.83</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1530,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-105.11</t>
+          <t>-105.39</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,172 +1540,172 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>77098.98345323741</t>
+          <t>77005.29094827587</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>5046.0</t>
+          <t>3204.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>10612.2</t>
+          <t>8309.4</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>15323.3</t>
+          <t>13469.3</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>16780.18</t>
+          <t>16218.6</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-4711</t>
+          <t>-5159</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-100.9576738690555</t>
-        </is>
-      </c>
-      <c r="BC3" t="n">
-        <v>-490.81</v>
-      </c>
-      <c r="BD3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>-256.304476051831</t>
+        </is>
+      </c>
+      <c r="BC3" t="inlineStr">
+        <is>
+          <t>-1110.711888057096</t>
+        </is>
+      </c>
+      <c r="BD3" t="n">
+        <v>3204</v>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF3" t="inlineStr">
+        <is>
           <t>48.75</t>
         </is>
       </c>
-      <c r="BF3" t="inlineStr">
+      <c r="BG3" t="inlineStr">
         <is>
           <t>2025/08/25</t>
         </is>
       </c>
-      <c r="BG3" t="inlineStr">
-        <is>
-          <t>-7.59</t>
-        </is>
-      </c>
       <c r="BH3" t="inlineStr">
         <is>
+          <t>-6.56</t>
+        </is>
+      </c>
+      <c r="BI3" t="inlineStr">
+        <is>
           <t>岱稜</t>
         </is>
       </c>
-      <c r="BI3" t="inlineStr">
+      <c r="BJ3" t="inlineStr">
         <is>
           <t>岱稜</t>
         </is>
       </c>
-      <c r="BJ3" t="inlineStr">
+      <c r="BK3" t="inlineStr">
         <is>
           <t>其他電子業</t>
         </is>
       </c>
-      <c r="BK3" t="inlineStr">
+      <c r="BL3" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BL3" t="inlineStr">
-        <is>
-          <t>1.07</t>
-        </is>
-      </c>
       <c r="BM3" t="inlineStr">
         <is>
+          <t>1.05</t>
+        </is>
+      </c>
+      <c r="BN3" t="inlineStr">
+        <is>
           <t>-1.004452687200723</t>
         </is>
       </c>
-      <c r="BN3" t="inlineStr">
+      <c r="BO3" t="inlineStr">
         <is>
           <t>11.92388165594906</t>
         </is>
       </c>
-      <c r="BO3" t="inlineStr">
+      <c r="BP3" t="inlineStr">
         <is>
           <t>2.060463205899802</t>
         </is>
       </c>
-      <c r="BP3" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="BQ3" t="inlineStr">
         <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR3" t="inlineStr">
+        <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="BR3" t="inlineStr">
-        <is>
-          <t>1.83</t>
-        </is>
-      </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>6.07</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
+          <t>6.18</t>
+        </is>
+      </c>
+      <c r="BU3" t="inlineStr">
+        <is>
           <t>8.56</t>
         </is>
       </c>
-      <c r="BU3" t="inlineStr">
-        <is>
-          <t>10.28</t>
-        </is>
-      </c>
       <c r="BV3" t="inlineStr">
         <is>
+          <t>10.1</t>
+        </is>
+      </c>
+      <c r="BW3" t="inlineStr">
+        <is>
           <t>33.67%</t>
         </is>
       </c>
-      <c r="BW3" t="inlineStr">
+      <c r="BX3" t="inlineStr">
         <is>
           <t>12.48%</t>
         </is>
       </c>
-      <c r="BX3" t="inlineStr">
-        <is>
-          <t>42.77</t>
-        </is>
-      </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>4286</t>
+          <t>41.57</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
+          <t>4211</t>
+        </is>
+      </c>
+      <c r="CA3" t="inlineStr">
+        <is>
           <t>真空蒸鍍薄膜95.00%、光電材料5.00% (2024年)</t>
         </is>
       </c>
-      <c r="CA3" t="inlineStr">
+      <c r="CB3" t="inlineStr">
         <is>
           <t>岱稜-其他電子業-上櫃</t>
         </is>
       </c>
-      <c r="CB3" t="inlineStr">
+      <c r="CC3" t="inlineStr">
         <is>
           <t>其他電子業平上櫃</t>
         </is>
       </c>
-      <c r="CC3" t="inlineStr">
-        <is>
-          <t>44.55</t>
-        </is>
-      </c>
       <c r="CD3" t="inlineStr">
         <is>
           <t>45.4</t>
@@ -1703,25 +1713,30 @@
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>44.55</t>
+          <t>46.25</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>45.05</t>
+          <t>45.3</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
+          <t>45.55</t>
+        </is>
+      </c>
+      <c r="CH3" t="inlineStr">
+        <is>
           <t>24.66</t>
         </is>
       </c>
-      <c r="CH3" t="inlineStr">
+      <c r="CI3" t="inlineStr">
         <is>
           <t>** 觸控面板 - PET膜** 其他 - 其他電子產品及電子服務產業、其他** 醫療器材 - 塑化材料</t>
         </is>
       </c>
-      <c r="CI3" t="inlineStr">
+      <c r="CJ3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -1740,12 +1755,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-3.84</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>315.0</t>
+          <t>112.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1755,7 +1770,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>44.8</t>
+          <t>45.05</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1765,17 +1780,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-0.3</t>
+          <t>-0.96</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-9.12</t>
+          <t>-30.74</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1840,7 +1855,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-9.95</t>
+          <t>-9.45</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1850,17 +1865,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>6.37</t>
+          <t>2.48</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-4.69</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1871,57 +1886,57 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>177</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>8.93</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>45.15</t>
+          <t>22.13</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-3.92</t>
+          <t>-2.32</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-2.8</t>
+          <t>-2.65</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>46.63</t>
+          <t>46.12</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>46.15</t>
+          <t>46.12</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>47.48</t>
+          <t>47.37</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
@@ -1931,17 +1946,17 @@
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>27.78</t>
+          <t>-13.12</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1951,7 +1966,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-104.94</t>
+          <t>-105.11</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1961,198 +1976,203 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>77098.98345323741</t>
+          <t>77005.29094827587</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>14336.0</t>
+          <t>5046.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>14123.0</t>
+          <t>10612.2</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>15541.1</t>
+          <t>15323.3</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>17446.4</t>
+          <t>16780.18</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-1418</t>
+          <t>-4711</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-30.07547477889878</t>
-        </is>
-      </c>
-      <c r="BC4" t="n">
-        <v>214.94</v>
-      </c>
-      <c r="BD4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>-100.9576738690555</t>
+        </is>
+      </c>
+      <c r="BC4" t="inlineStr">
+        <is>
+          <t>-490.8097688649177</t>
+        </is>
+      </c>
+      <c r="BD4" t="n">
+        <v>5046</v>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF4" t="inlineStr">
+        <is>
           <t>48.75</t>
         </is>
       </c>
-      <c r="BF4" t="inlineStr">
+      <c r="BG4" t="inlineStr">
         <is>
           <t>2025/08/25</t>
         </is>
       </c>
-      <c r="BG4" t="inlineStr">
-        <is>
-          <t>-8.10</t>
-        </is>
-      </c>
       <c r="BH4" t="inlineStr">
         <is>
+          <t>-7.59</t>
+        </is>
+      </c>
+      <c r="BI4" t="inlineStr">
+        <is>
           <t>岱稜</t>
         </is>
       </c>
-      <c r="BI4" t="inlineStr">
+      <c r="BJ4" t="inlineStr">
         <is>
           <t>岱稜</t>
         </is>
       </c>
-      <c r="BJ4" t="inlineStr">
+      <c r="BK4" t="inlineStr">
         <is>
           <t>其他電子業</t>
         </is>
       </c>
-      <c r="BK4" t="inlineStr">
+      <c r="BL4" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BL4" t="inlineStr">
-        <is>
-          <t>1.07</t>
-        </is>
-      </c>
       <c r="BM4" t="inlineStr">
         <is>
+          <t>1.05</t>
+        </is>
+      </c>
+      <c r="BN4" t="inlineStr">
+        <is>
           <t>-1.004452687200723</t>
         </is>
       </c>
-      <c r="BN4" t="inlineStr">
+      <c r="BO4" t="inlineStr">
         <is>
           <t>11.92388165594906</t>
         </is>
       </c>
-      <c r="BO4" t="inlineStr">
+      <c r="BP4" t="inlineStr">
         <is>
           <t>2.060463205899802</t>
         </is>
       </c>
-      <c r="BP4" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="BQ4" t="inlineStr">
         <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR4" t="inlineStr">
+        <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="BR4" t="inlineStr">
-        <is>
-          <t>1.82</t>
-        </is>
-      </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>6.07</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
+          <t>6.18</t>
+        </is>
+      </c>
+      <c r="BU4" t="inlineStr">
+        <is>
           <t>8.56</t>
         </is>
       </c>
-      <c r="BU4" t="inlineStr">
-        <is>
-          <t>10.28</t>
-        </is>
-      </c>
       <c r="BV4" t="inlineStr">
         <is>
+          <t>10.1</t>
+        </is>
+      </c>
+      <c r="BW4" t="inlineStr">
+        <is>
           <t>33.67%</t>
         </is>
       </c>
-      <c r="BW4" t="inlineStr">
+      <c r="BX4" t="inlineStr">
         <is>
           <t>12.48%</t>
         </is>
       </c>
-      <c r="BX4" t="inlineStr">
-        <is>
-          <t>42.77</t>
-        </is>
-      </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>4286</t>
+          <t>41.57</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
+          <t>4211</t>
+        </is>
+      </c>
+      <c r="CA4" t="inlineStr">
+        <is>
           <t>真空蒸鍍薄膜95.00%、光電材料5.00% (2024年)</t>
         </is>
       </c>
-      <c r="CA4" t="inlineStr">
+      <c r="CB4" t="inlineStr">
         <is>
           <t>岱稜-其他電子業-上櫃</t>
         </is>
       </c>
-      <c r="CB4" t="inlineStr">
+      <c r="CC4" t="inlineStr">
         <is>
           <t>其他電子業平上櫃</t>
         </is>
       </c>
-      <c r="CC4" t="inlineStr">
-        <is>
-          <t>46.9</t>
-        </is>
-      </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>46.9</t>
+          <t>44.55</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>44.8</t>
+          <t>45.4</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>44.8</t>
+          <t>44.55</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
+          <t>45.05</t>
+        </is>
+      </c>
+      <c r="CH4" t="inlineStr">
+        <is>
           <t>24.66</t>
         </is>
       </c>
-      <c r="CH4" t="inlineStr">
+      <c r="CI4" t="inlineStr">
         <is>
           <t>** 觸控面板 - PET膜** 其他 - 其他電子產品及電子服務產業、其他** 醫療器材 - 塑化材料</t>
         </is>
       </c>
-      <c r="CI4" t="inlineStr">
+      <c r="CJ4" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -2171,12 +2191,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-0.95</t>
+          <t>-3.84</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>213.0</t>
+          <t>315.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2186,7 +2206,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>46.6</t>
+          <t>44.8</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2196,17 +2216,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-2.31</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-0.3</t>
+          <t>-0.96</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>26.53</t>
+          <t>-9.12</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2271,7 +2291,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-6.33</t>
+          <t>-9.95</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2281,17 +2301,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>4.31</t>
+          <t>6.97</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>-4.69</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2302,77 +2322,77 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>177</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>57.45</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>71.82</t>
+          <t>45.15</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-1.17</t>
+          <t>-3.92</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-2.88</t>
+          <t>-2.8</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>47.15</t>
+          <t>46.63</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>46.22</t>
+          <t>46.15</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>47.59</t>
+          <t>47.48</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>47.5</t>
+          <t>47.49</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>98.12</t>
+          <t>27.78</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-0.00</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2382,7 +2402,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-105.28</t>
+          <t>-104.94</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2392,198 +2412,203 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>77098.98345323741</t>
+          <t>77005.29094827587</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>9943.0</t>
+          <t>14336.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>18959.2</t>
+          <t>14123.0</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>14983.4</t>
+          <t>15541.1</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>17743.28</t>
+          <t>17446.4</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>3975</t>
+          <t>-1418</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-74.62310011749315</t>
-        </is>
-      </c>
-      <c r="BC5" t="n">
-        <v>220.11</v>
-      </c>
-      <c r="BD5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>-30.07547477889878</t>
+        </is>
+      </c>
+      <c r="BC5" t="inlineStr">
+        <is>
+          <t>214.9364645833703</t>
+        </is>
+      </c>
+      <c r="BD5" t="n">
+        <v>14336</v>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF5" t="inlineStr">
+        <is>
           <t>48.75</t>
         </is>
       </c>
-      <c r="BF5" t="inlineStr">
+      <c r="BG5" t="inlineStr">
         <is>
           <t>2025/08/25</t>
         </is>
       </c>
-      <c r="BG5" t="inlineStr">
-        <is>
-          <t>-4.41</t>
-        </is>
-      </c>
       <c r="BH5" t="inlineStr">
         <is>
+          <t>-8.10</t>
+        </is>
+      </c>
+      <c r="BI5" t="inlineStr">
+        <is>
           <t>岱稜</t>
         </is>
       </c>
-      <c r="BI5" t="inlineStr">
+      <c r="BJ5" t="inlineStr">
         <is>
           <t>岱稜</t>
         </is>
       </c>
-      <c r="BJ5" t="inlineStr">
+      <c r="BK5" t="inlineStr">
         <is>
           <t>其他電子業</t>
         </is>
       </c>
-      <c r="BK5" t="inlineStr">
+      <c r="BL5" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BL5" t="inlineStr">
-        <is>
-          <t>1.07</t>
-        </is>
-      </c>
       <c r="BM5" t="inlineStr">
         <is>
+          <t>1.05</t>
+        </is>
+      </c>
+      <c r="BN5" t="inlineStr">
+        <is>
           <t>-1.004452687200723</t>
         </is>
       </c>
-      <c r="BN5" t="inlineStr">
+      <c r="BO5" t="inlineStr">
         <is>
           <t>11.92388165594906</t>
         </is>
       </c>
-      <c r="BO5" t="inlineStr">
+      <c r="BP5" t="inlineStr">
         <is>
           <t>2.060463205899802</t>
         </is>
       </c>
-      <c r="BP5" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="BQ5" t="inlineStr">
         <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR5" t="inlineStr">
+        <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="BR5" t="inlineStr">
-        <is>
-          <t>1.89</t>
-        </is>
-      </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>6.07</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
+          <t>6.18</t>
+        </is>
+      </c>
+      <c r="BU5" t="inlineStr">
+        <is>
           <t>8.56</t>
         </is>
       </c>
-      <c r="BU5" t="inlineStr">
-        <is>
-          <t>10.28</t>
-        </is>
-      </c>
       <c r="BV5" t="inlineStr">
         <is>
+          <t>10.1</t>
+        </is>
+      </c>
+      <c r="BW5" t="inlineStr">
+        <is>
           <t>33.67%</t>
         </is>
       </c>
-      <c r="BW5" t="inlineStr">
+      <c r="BX5" t="inlineStr">
         <is>
           <t>12.48%</t>
         </is>
       </c>
-      <c r="BX5" t="inlineStr">
-        <is>
-          <t>42.77</t>
-        </is>
-      </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>4286</t>
+          <t>41.57</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
+          <t>4211</t>
+        </is>
+      </c>
+      <c r="CA5" t="inlineStr">
+        <is>
           <t>真空蒸鍍薄膜95.00%、光電材料5.00% (2024年)</t>
         </is>
       </c>
-      <c r="CA5" t="inlineStr">
+      <c r="CB5" t="inlineStr">
         <is>
           <t>岱稜-其他電子業-上櫃</t>
         </is>
       </c>
-      <c r="CB5" t="inlineStr">
+      <c r="CC5" t="inlineStr">
         <is>
           <t>其他電子業平上櫃</t>
         </is>
       </c>
-      <c r="CC5" t="inlineStr">
-        <is>
-          <t>47.15</t>
-        </is>
-      </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>47.2</t>
+          <t>46.9</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>46.4</t>
+          <t>46.9</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>46.6</t>
+          <t>44.8</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
+          <t>44.8</t>
+        </is>
+      </c>
+      <c r="CH5" t="inlineStr">
+        <is>
           <t>24.66</t>
         </is>
       </c>
-      <c r="CH5" t="inlineStr">
+      <c r="CI5" t="inlineStr">
         <is>
           <t>** 觸控面板 - PET膜** 其他 - 其他電子產品及電子服務產業、其他** 醫療器材 - 塑化材料</t>
         </is>
       </c>
-      <c r="CI5" t="inlineStr">
+      <c r="CJ5" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -2602,12 +2627,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>-0.95</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>192.0</t>
+          <t>213.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2617,7 +2642,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>47.05</t>
+          <t>46.6</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2627,17 +2652,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-3.29</t>
+          <t>-4.13</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-0.3</t>
+          <t>-0.96</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>29.99</t>
+          <t>26.53</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2702,7 +2727,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-5.43</t>
+          <t>-6.33</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2712,17 +2737,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>3.88</t>
+          <t>4.71</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2733,77 +2758,77 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>177</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>57.45</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>71.82</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>-1.17</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-3.21</t>
+          <t>-2.88</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>47.23</t>
+          <t>47.15</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>46.15</t>
+          <t>46.22</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>47.68</t>
+          <t>47.59</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>47.48</t>
+          <t>47.5</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>100.64</t>
+          <t>98.12</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.00</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2813,7 +2838,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-106.58</t>
+          <t>-105.28</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2823,198 +2848,203 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>77098.98345323741</t>
+          <t>77005.29094827587</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>9018.0</t>
+          <t>9943.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>18831.4</t>
+          <t>18959.2</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>14486.8</t>
+          <t>14983.4</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>18676.0</t>
+          <t>17743.28</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>4344</t>
+          <t>3975</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-128.211286383547</t>
-        </is>
-      </c>
-      <c r="BC6" t="n">
-        <v>690.3200000000001</v>
-      </c>
-      <c r="BD6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>-74.62310011749315</t>
+        </is>
+      </c>
+      <c r="BC6" t="inlineStr">
+        <is>
+          <t>220.1119243458033</t>
+        </is>
+      </c>
+      <c r="BD6" t="n">
+        <v>9943</v>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF6" t="inlineStr">
+        <is>
           <t>48.75</t>
         </is>
       </c>
-      <c r="BF6" t="inlineStr">
+      <c r="BG6" t="inlineStr">
         <is>
           <t>2025/08/25</t>
         </is>
       </c>
-      <c r="BG6" t="inlineStr">
-        <is>
-          <t>-3.49</t>
-        </is>
-      </c>
       <c r="BH6" t="inlineStr">
         <is>
+          <t>-4.41</t>
+        </is>
+      </c>
+      <c r="BI6" t="inlineStr">
+        <is>
           <t>岱稜</t>
         </is>
       </c>
-      <c r="BI6" t="inlineStr">
+      <c r="BJ6" t="inlineStr">
         <is>
           <t>岱稜</t>
         </is>
       </c>
-      <c r="BJ6" t="inlineStr">
+      <c r="BK6" t="inlineStr">
         <is>
           <t>其他電子業</t>
         </is>
       </c>
-      <c r="BK6" t="inlineStr">
+      <c r="BL6" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BL6" t="inlineStr">
-        <is>
-          <t>1.07</t>
-        </is>
-      </c>
       <c r="BM6" t="inlineStr">
         <is>
+          <t>1.05</t>
+        </is>
+      </c>
+      <c r="BN6" t="inlineStr">
+        <is>
           <t>-1.004452687200723</t>
         </is>
       </c>
-      <c r="BN6" t="inlineStr">
+      <c r="BO6" t="inlineStr">
         <is>
           <t>11.92388165594906</t>
         </is>
       </c>
-      <c r="BO6" t="inlineStr">
+      <c r="BP6" t="inlineStr">
         <is>
           <t>2.060463205899802</t>
         </is>
       </c>
-      <c r="BP6" t="inlineStr">
+      <c r="BQ6" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BQ6" t="inlineStr">
-        <is>
-          <t>價-量縮</t>
-        </is>
-      </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>6.07</t>
+          <t>1.89</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
+          <t>6.18</t>
+        </is>
+      </c>
+      <c r="BU6" t="inlineStr">
+        <is>
           <t>8.56</t>
         </is>
       </c>
-      <c r="BU6" t="inlineStr">
-        <is>
-          <t>10.28</t>
-        </is>
-      </c>
       <c r="BV6" t="inlineStr">
         <is>
+          <t>10.1</t>
+        </is>
+      </c>
+      <c r="BW6" t="inlineStr">
+        <is>
           <t>33.67%</t>
         </is>
       </c>
-      <c r="BW6" t="inlineStr">
+      <c r="BX6" t="inlineStr">
         <is>
           <t>12.48%</t>
         </is>
       </c>
-      <c r="BX6" t="inlineStr">
-        <is>
-          <t>42.77</t>
-        </is>
-      </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>4286</t>
+          <t>41.57</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
+          <t>4211</t>
+        </is>
+      </c>
+      <c r="CA6" t="inlineStr">
+        <is>
           <t>真空蒸鍍薄膜95.00%、光電材料5.00% (2024年)</t>
         </is>
       </c>
-      <c r="CA6" t="inlineStr">
+      <c r="CB6" t="inlineStr">
         <is>
           <t>岱稜-其他電子業-上櫃</t>
         </is>
       </c>
-      <c r="CB6" t="inlineStr">
+      <c r="CC6" t="inlineStr">
         <is>
           <t>其他電子業平上櫃</t>
         </is>
       </c>
-      <c r="CC6" t="inlineStr">
-        <is>
-          <t>46.5</t>
-        </is>
-      </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>47.5</t>
+          <t>47.15</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>46.35</t>
+          <t>47.2</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>47.05</t>
+          <t>46.4</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
+          <t>46.6</t>
+        </is>
+      </c>
+      <c r="CH6" t="inlineStr">
+        <is>
           <t>24.66</t>
         </is>
       </c>
-      <c r="CH6" t="inlineStr">
+      <c r="CI6" t="inlineStr">
         <is>
           <t>** 觸控面板 - PET膜** 其他 - 其他電子產品及電子服務產業、其他** 醫療器材 - 塑化材料</t>
         </is>
       </c>
-      <c r="CI6" t="inlineStr">
+      <c r="CJ6" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -3033,12 +3063,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-1.05</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>311.0</t>
+          <t>192.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3078,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>47.1</t>
+          <t>47.05</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3088,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-3.4</t>
+          <t>-5.14</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-0.3</t>
+          <t>-0.96</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>33.05</t>
+          <t>29.99</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3163,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-5.33</t>
+          <t>-5.43</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3173,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>6.29</t>
+          <t>4.25</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-0.95</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,77 +3194,77 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>177</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>93.33</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>2.36</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-3.53</t>
+          <t>-3.21</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>0.60</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>47.15</t>
+          <t>47.23</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>46.06</t>
+          <t>46.15</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>47.75</t>
+          <t>47.68</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>47.47</t>
+          <t>47.48</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>89.68</t>
+          <t>100.64</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3244,7 +3274,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-108.23</t>
+          <t>-106.58</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3254,198 +3284,203 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>77098.98345323741</t>
+          <t>77005.29094827587</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>14718.0</t>
+          <t>9018.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>18629.2</t>
+          <t>18831.4</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>14001.9</t>
+          <t>14486.8</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>20406.5</t>
+          <t>18676.0</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>4627</t>
+          <t>4344</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-277.0356783742832</t>
-        </is>
-      </c>
-      <c r="BC7" t="n">
-        <v>1436.51</v>
-      </c>
-      <c r="BD7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>-128.211286383547</t>
+        </is>
+      </c>
+      <c r="BC7" t="inlineStr">
+        <is>
+          <t>690.3228695655016</t>
+        </is>
+      </c>
+      <c r="BD7" t="n">
+        <v>9018</v>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF7" t="inlineStr">
+        <is>
           <t>48.75</t>
         </is>
       </c>
-      <c r="BF7" t="inlineStr">
+      <c r="BG7" t="inlineStr">
         <is>
           <t>2025/08/25</t>
         </is>
       </c>
-      <c r="BG7" t="inlineStr">
-        <is>
-          <t>-3.38</t>
-        </is>
-      </c>
       <c r="BH7" t="inlineStr">
         <is>
+          <t>-3.49</t>
+        </is>
+      </c>
+      <c r="BI7" t="inlineStr">
+        <is>
           <t>岱稜</t>
         </is>
       </c>
-      <c r="BI7" t="inlineStr">
+      <c r="BJ7" t="inlineStr">
         <is>
           <t>岱稜</t>
         </is>
       </c>
-      <c r="BJ7" t="inlineStr">
+      <c r="BK7" t="inlineStr">
         <is>
           <t>其他電子業</t>
         </is>
       </c>
-      <c r="BK7" t="inlineStr">
+      <c r="BL7" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BL7" t="inlineStr">
-        <is>
-          <t>1.07</t>
-        </is>
-      </c>
       <c r="BM7" t="inlineStr">
         <is>
+          <t>1.05</t>
+        </is>
+      </c>
+      <c r="BN7" t="inlineStr">
+        <is>
           <t>-1.004452687200723</t>
         </is>
       </c>
-      <c r="BN7" t="inlineStr">
+      <c r="BO7" t="inlineStr">
         <is>
           <t>11.92388165594906</t>
         </is>
       </c>
-      <c r="BO7" t="inlineStr">
+      <c r="BP7" t="inlineStr">
         <is>
           <t>2.060463205899802</t>
         </is>
       </c>
-      <c r="BP7" t="inlineStr">
+      <c r="BQ7" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BQ7" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
       <c r="BR7" t="inlineStr">
         <is>
+          <t>價-量縮</t>
+        </is>
+      </c>
+      <c r="BS7" t="inlineStr">
+        <is>
           <t>1.91</t>
         </is>
       </c>
-      <c r="BS7" t="inlineStr">
-        <is>
-          <t>6.07</t>
-        </is>
-      </c>
       <c r="BT7" t="inlineStr">
         <is>
+          <t>6.18</t>
+        </is>
+      </c>
+      <c r="BU7" t="inlineStr">
+        <is>
           <t>8.56</t>
         </is>
       </c>
-      <c r="BU7" t="inlineStr">
-        <is>
-          <t>10.28</t>
-        </is>
-      </c>
       <c r="BV7" t="inlineStr">
         <is>
+          <t>10.1</t>
+        </is>
+      </c>
+      <c r="BW7" t="inlineStr">
+        <is>
           <t>33.67%</t>
         </is>
       </c>
-      <c r="BW7" t="inlineStr">
+      <c r="BX7" t="inlineStr">
         <is>
           <t>12.48%</t>
         </is>
       </c>
-      <c r="BX7" t="inlineStr">
-        <is>
-          <t>42.77</t>
-        </is>
-      </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>4286</t>
+          <t>41.57</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
+          <t>4211</t>
+        </is>
+      </c>
+      <c r="CA7" t="inlineStr">
+        <is>
           <t>真空蒸鍍薄膜95.00%、光電材料5.00% (2024年)</t>
         </is>
       </c>
-      <c r="CA7" t="inlineStr">
+      <c r="CB7" t="inlineStr">
         <is>
           <t>岱稜-其他電子業-上櫃</t>
         </is>
       </c>
-      <c r="CB7" t="inlineStr">
+      <c r="CC7" t="inlineStr">
         <is>
           <t>其他電子業平上櫃</t>
         </is>
       </c>
-      <c r="CC7" t="inlineStr">
-        <is>
-          <t>47.6</t>
-        </is>
-      </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>47.8</t>
+          <t>46.5</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>46.85</t>
+          <t>47.5</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>47.1</t>
+          <t>46.35</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
+          <t>47.05</t>
+        </is>
+      </c>
+      <c r="CH7" t="inlineStr">
+        <is>
           <t>24.66</t>
         </is>
       </c>
-      <c r="CH7" t="inlineStr">
+      <c r="CI7" t="inlineStr">
         <is>
           <t>** 觸控面板 - PET膜** 其他 - 其他電子產品及電子服務產業、其他** 醫療器材 - 塑化材料</t>
         </is>
       </c>
-      <c r="CI7" t="inlineStr">
+      <c r="CJ7" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -3464,12 +3499,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>-1.05</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>474.0</t>
+          <t>311.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3479,7 +3514,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>47.6</t>
+          <t>47.1</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3489,17 +3524,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-4.5</t>
+          <t>-5.25</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-0.3</t>
+          <t>-0.96</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>50.85</t>
+          <t>33.05</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3564,7 +3599,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-4.32</t>
+          <t>-5.33</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3574,17 +3609,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>9.59</t>
+          <t>6.88</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-0.95</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3595,77 +3630,77 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>177</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>93.33</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>2.67</t>
+          <t>2.36</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-3.93</t>
+          <t>-3.53</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.60</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>47.13</t>
+          <t>47.15</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>45.9</t>
+          <t>46.06</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>47.78</t>
+          <t>47.75</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>47.45</t>
+          <t>47.47</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>79.21</t>
+          <t>89.68</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3675,7 +3710,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-110.08</t>
+          <t>-108.23</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3685,198 +3720,203 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>77098.98345323741</t>
+          <t>77005.29094827587</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>22600.0</t>
+          <t>14718.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>20034.4</t>
+          <t>18629.2</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>13280.9</t>
+          <t>14001.9</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>20741.92</t>
+          <t>20406.5</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>6753</t>
+          <t>4627</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-588.5886282543895</t>
-        </is>
-      </c>
-      <c r="BC8" t="n">
-        <v>1840.46</v>
-      </c>
-      <c r="BD8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>-277.0356783742832</t>
+        </is>
+      </c>
+      <c r="BC8" t="inlineStr">
+        <is>
+          <t>1436.505545966302</t>
+        </is>
+      </c>
+      <c r="BD8" t="n">
+        <v>14718</v>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF8" t="inlineStr">
+        <is>
           <t>48.75</t>
         </is>
       </c>
-      <c r="BF8" t="inlineStr">
+      <c r="BG8" t="inlineStr">
         <is>
           <t>2025/08/25</t>
         </is>
       </c>
-      <c r="BG8" t="inlineStr">
-        <is>
-          <t>-2.36</t>
-        </is>
-      </c>
       <c r="BH8" t="inlineStr">
         <is>
+          <t>-3.38</t>
+        </is>
+      </c>
+      <c r="BI8" t="inlineStr">
+        <is>
           <t>岱稜</t>
         </is>
       </c>
-      <c r="BI8" t="inlineStr">
+      <c r="BJ8" t="inlineStr">
         <is>
           <t>岱稜</t>
         </is>
       </c>
-      <c r="BJ8" t="inlineStr">
+      <c r="BK8" t="inlineStr">
         <is>
           <t>其他電子業</t>
         </is>
       </c>
-      <c r="BK8" t="inlineStr">
+      <c r="BL8" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BL8" t="inlineStr">
-        <is>
-          <t>1.07</t>
-        </is>
-      </c>
       <c r="BM8" t="inlineStr">
         <is>
+          <t>1.05</t>
+        </is>
+      </c>
+      <c r="BN8" t="inlineStr">
+        <is>
           <t>-1.004452687200723</t>
         </is>
       </c>
-      <c r="BN8" t="inlineStr">
+      <c r="BO8" t="inlineStr">
         <is>
           <t>11.92388165594906</t>
         </is>
       </c>
-      <c r="BO8" t="inlineStr">
+      <c r="BP8" t="inlineStr">
         <is>
           <t>2.060463205899802</t>
         </is>
       </c>
-      <c r="BP8" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="BQ8" t="inlineStr">
         <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR8" t="inlineStr">
+        <is>
           <t>價-量增</t>
         </is>
       </c>
-      <c r="BR8" t="inlineStr">
-        <is>
-          <t>1.93</t>
-        </is>
-      </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>6.07</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
+          <t>6.18</t>
+        </is>
+      </c>
+      <c r="BU8" t="inlineStr">
+        <is>
           <t>8.56</t>
         </is>
       </c>
-      <c r="BU8" t="inlineStr">
-        <is>
-          <t>10.28</t>
-        </is>
-      </c>
       <c r="BV8" t="inlineStr">
         <is>
+          <t>10.1</t>
+        </is>
+      </c>
+      <c r="BW8" t="inlineStr">
+        <is>
           <t>33.67%</t>
         </is>
       </c>
-      <c r="BW8" t="inlineStr">
+      <c r="BX8" t="inlineStr">
         <is>
           <t>12.48%</t>
         </is>
       </c>
-      <c r="BX8" t="inlineStr">
-        <is>
-          <t>42.77</t>
-        </is>
-      </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>4286</t>
+          <t>41.57</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
+          <t>4211</t>
+        </is>
+      </c>
+      <c r="CA8" t="inlineStr">
+        <is>
           <t>真空蒸鍍薄膜95.00%、光電材料5.00% (2024年)</t>
         </is>
       </c>
-      <c r="CA8" t="inlineStr">
+      <c r="CB8" t="inlineStr">
         <is>
           <t>岱稜-其他電子業-上櫃</t>
         </is>
       </c>
-      <c r="CB8" t="inlineStr">
+      <c r="CC8" t="inlineStr">
         <is>
           <t>其他電子業平上櫃</t>
         </is>
       </c>
-      <c r="CC8" t="inlineStr">
-        <is>
-          <t>47.85</t>
-        </is>
-      </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>48.1</t>
+          <t>47.6</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>47.25</t>
+          <t>47.8</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>47.6</t>
+          <t>46.85</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
+          <t>47.1</t>
+        </is>
+      </c>
+      <c r="CH8" t="inlineStr">
+        <is>
           <t>24.66</t>
         </is>
       </c>
-      <c r="CH8" t="inlineStr">
+      <c r="CI8" t="inlineStr">
         <is>
           <t>** 觸控面板 - PET膜** 其他 - 其他電子產品及電子服務產業、其他** 醫療器材 - 塑化材料</t>
         </is>
       </c>
-      <c r="CI8" t="inlineStr">
+      <c r="CJ8" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -3895,12 +3935,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>812.0</t>
+          <t>474.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3910,7 +3950,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>47.4</t>
+          <t>47.6</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3920,17 +3960,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-4.06</t>
+          <t>-6.37</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-0.3</t>
+          <t>-0.96</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>43.35</t>
+          <t>50.85</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3995,7 +4035,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-4.72</t>
+          <t>-4.32</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4005,17 +4045,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16.43</t>
+          <t>10.48</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4026,12 +4066,12 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>177</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
@@ -4041,62 +4081,62 @@
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>93.86</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>2.67</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-4.23</t>
+          <t>-3.93</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>46.66</t>
+          <t>47.13</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>45.74</t>
+          <t>45.9</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>47.76</t>
+          <t>47.78</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>47.42</t>
+          <t>47.45</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>59.88</t>
+          <t>79.21</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4106,7 +4146,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-112.07</t>
+          <t>-110.08</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4116,172 +4156,172 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>77098.98345323741</t>
+          <t>77005.29094827587</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>38517.0</t>
+          <t>22600.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>16959.2</t>
+          <t>20034.4</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>11830.5</t>
+          <t>13280.9</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>20783.02</t>
+          <t>20741.92</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>5128</t>
+          <t>6753</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-1030.234332074163</t>
-        </is>
-      </c>
-      <c r="BC9" t="n">
-        <v>1507.31</v>
-      </c>
-      <c r="BD9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>-588.5886282543895</t>
+        </is>
+      </c>
+      <c r="BC9" t="inlineStr">
+        <is>
+          <t>1840.462742754364</t>
+        </is>
+      </c>
+      <c r="BD9" t="n">
+        <v>22600</v>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF9" t="inlineStr">
+        <is>
           <t>48.75</t>
         </is>
       </c>
-      <c r="BF9" t="inlineStr">
+      <c r="BG9" t="inlineStr">
         <is>
           <t>2025/08/25</t>
         </is>
       </c>
-      <c r="BG9" t="inlineStr">
-        <is>
-          <t>-2.77</t>
-        </is>
-      </c>
       <c r="BH9" t="inlineStr">
         <is>
+          <t>-2.36</t>
+        </is>
+      </c>
+      <c r="BI9" t="inlineStr">
+        <is>
           <t>岱稜</t>
         </is>
       </c>
-      <c r="BI9" t="inlineStr">
+      <c r="BJ9" t="inlineStr">
         <is>
           <t>岱稜</t>
         </is>
       </c>
-      <c r="BJ9" t="inlineStr">
+      <c r="BK9" t="inlineStr">
         <is>
           <t>其他電子業</t>
         </is>
       </c>
-      <c r="BK9" t="inlineStr">
+      <c r="BL9" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BL9" t="inlineStr">
-        <is>
-          <t>1.07</t>
-        </is>
-      </c>
       <c r="BM9" t="inlineStr">
         <is>
+          <t>1.05</t>
+        </is>
+      </c>
+      <c r="BN9" t="inlineStr">
+        <is>
           <t>-1.004452687200723</t>
         </is>
       </c>
-      <c r="BN9" t="inlineStr">
+      <c r="BO9" t="inlineStr">
         <is>
           <t>11.92388165594906</t>
         </is>
       </c>
-      <c r="BO9" t="inlineStr">
+      <c r="BP9" t="inlineStr">
         <is>
           <t>2.060463205899802</t>
         </is>
       </c>
-      <c r="BP9" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="BQ9" t="inlineStr">
         <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR9" t="inlineStr">
+        <is>
           <t>價-量增</t>
         </is>
       </c>
-      <c r="BR9" t="inlineStr">
-        <is>
-          <t>1.92</t>
-        </is>
-      </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>6.07</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
+          <t>6.18</t>
+        </is>
+      </c>
+      <c r="BU9" t="inlineStr">
+        <is>
           <t>8.56</t>
         </is>
       </c>
-      <c r="BU9" t="inlineStr">
-        <is>
-          <t>10.28</t>
-        </is>
-      </c>
       <c r="BV9" t="inlineStr">
         <is>
+          <t>10.1</t>
+        </is>
+      </c>
+      <c r="BW9" t="inlineStr">
+        <is>
           <t>33.67%</t>
         </is>
       </c>
-      <c r="BW9" t="inlineStr">
+      <c r="BX9" t="inlineStr">
         <is>
           <t>12.48%</t>
         </is>
       </c>
-      <c r="BX9" t="inlineStr">
-        <is>
-          <t>42.77</t>
-        </is>
-      </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>4286</t>
+          <t>41.57</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
+          <t>4211</t>
+        </is>
+      </c>
+      <c r="CA9" t="inlineStr">
+        <is>
           <t>真空蒸鍍薄膜95.00%、光電材料5.00% (2024年)</t>
         </is>
       </c>
-      <c r="CA9" t="inlineStr">
+      <c r="CB9" t="inlineStr">
         <is>
           <t>岱稜-其他電子業-上櫃</t>
         </is>
       </c>
-      <c r="CB9" t="inlineStr">
+      <c r="CC9" t="inlineStr">
         <is>
           <t>其他電子業平上櫃</t>
         </is>
       </c>
-      <c r="CC9" t="inlineStr">
-        <is>
-          <t>47.5</t>
-        </is>
-      </c>
       <c r="CD9" t="inlineStr">
         <is>
           <t>47.85</t>
@@ -4289,25 +4329,30 @@
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>46.5</t>
+          <t>48.1</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>47.4</t>
+          <t>47.25</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
+          <t>47.6</t>
+        </is>
+      </c>
+      <c r="CH9" t="inlineStr">
+        <is>
           <t>24.66</t>
         </is>
       </c>
-      <c r="CH9" t="inlineStr">
+      <c r="CI9" t="inlineStr">
         <is>
           <t>** 觸控面板 - PET膜** 其他 - 其他電子產品及電子服務產業、其他** 醫療器材 - 塑化材料</t>
         </is>
       </c>
-      <c r="CI9" t="inlineStr">
+      <c r="CJ9" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -4326,12 +4371,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>199.0</t>
+          <t>812.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4341,7 +4386,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>47.0</t>
+          <t>47.4</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4351,17 +4396,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-3.18</t>
+          <t>-5.92</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-0.3</t>
+          <t>-0.96</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>32.28</t>
+          <t>43.35</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4426,7 +4471,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-5.53</t>
+          <t>-4.72</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4436,17 +4481,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>4.03</t>
+          <t>17.96</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4457,12 +4502,12 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>177</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
@@ -4477,57 +4522,57 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-4.34</t>
+          <t>-4.23</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>46.2</t>
+          <t>46.66</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>45.67</t>
+          <t>45.74</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>47.75</t>
+          <t>47.76</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>47.39</t>
+          <t>47.42</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>43.77</t>
+          <t>59.88</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4537,7 +4582,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-113.88</t>
+          <t>-112.07</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4547,198 +4592,203 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>77098.98345323741</t>
+          <t>77005.29094827587</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>9304.0</t>
+          <t>38517.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>11007.6</t>
+          <t>16959.2</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>8321.2</t>
+          <t>11830.5</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>21296.56</t>
+          <t>20783.02</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>2686</t>
+          <t>5128</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-1491.606690671351</t>
-        </is>
-      </c>
-      <c r="BC10" t="n">
-        <v>-727.84</v>
-      </c>
-      <c r="BD10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>-1030.234332074163</t>
+        </is>
+      </c>
+      <c r="BC10" t="inlineStr">
+        <is>
+          <t>1507.31364021037</t>
+        </is>
+      </c>
+      <c r="BD10" t="n">
+        <v>38517</v>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF10" t="inlineStr">
+        <is>
           <t>48.75</t>
         </is>
       </c>
-      <c r="BF10" t="inlineStr">
+      <c r="BG10" t="inlineStr">
         <is>
           <t>2025/08/25</t>
         </is>
       </c>
-      <c r="BG10" t="inlineStr">
-        <is>
-          <t>-3.59</t>
-        </is>
-      </c>
       <c r="BH10" t="inlineStr">
         <is>
+          <t>-2.77</t>
+        </is>
+      </c>
+      <c r="BI10" t="inlineStr">
+        <is>
           <t>岱稜</t>
         </is>
       </c>
-      <c r="BI10" t="inlineStr">
+      <c r="BJ10" t="inlineStr">
         <is>
           <t>岱稜</t>
         </is>
       </c>
-      <c r="BJ10" t="inlineStr">
+      <c r="BK10" t="inlineStr">
         <is>
           <t>其他電子業</t>
         </is>
       </c>
-      <c r="BK10" t="inlineStr">
+      <c r="BL10" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BL10" t="inlineStr">
-        <is>
-          <t>1.07</t>
-        </is>
-      </c>
       <c r="BM10" t="inlineStr">
         <is>
+          <t>1.05</t>
+        </is>
+      </c>
+      <c r="BN10" t="inlineStr">
+        <is>
           <t>-1.004452687200723</t>
         </is>
       </c>
-      <c r="BN10" t="inlineStr">
+      <c r="BO10" t="inlineStr">
         <is>
           <t>11.92388165594906</t>
         </is>
       </c>
-      <c r="BO10" t="inlineStr">
+      <c r="BP10" t="inlineStr">
         <is>
           <t>2.060463205899802</t>
         </is>
       </c>
-      <c r="BP10" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>6.07</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
+          <t>6.18</t>
+        </is>
+      </c>
+      <c r="BU10" t="inlineStr">
+        <is>
           <t>8.56</t>
         </is>
       </c>
-      <c r="BU10" t="inlineStr">
-        <is>
-          <t>10.28</t>
-        </is>
-      </c>
       <c r="BV10" t="inlineStr">
         <is>
+          <t>10.1</t>
+        </is>
+      </c>
+      <c r="BW10" t="inlineStr">
+        <is>
           <t>33.67%</t>
         </is>
       </c>
-      <c r="BW10" t="inlineStr">
+      <c r="BX10" t="inlineStr">
         <is>
           <t>12.48%</t>
         </is>
       </c>
-      <c r="BX10" t="inlineStr">
-        <is>
-          <t>42.77</t>
-        </is>
-      </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>4286</t>
+          <t>41.57</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
+          <t>4211</t>
+        </is>
+      </c>
+      <c r="CA10" t="inlineStr">
+        <is>
           <t>真空蒸鍍薄膜95.00%、光電材料5.00% (2024年)</t>
         </is>
       </c>
-      <c r="CA10" t="inlineStr">
+      <c r="CB10" t="inlineStr">
         <is>
           <t>岱稜-其他電子業-上櫃</t>
         </is>
       </c>
-      <c r="CB10" t="inlineStr">
+      <c r="CC10" t="inlineStr">
         <is>
           <t>其他電子業平上櫃</t>
         </is>
       </c>
-      <c r="CC10" t="inlineStr">
-        <is>
-          <t>46.85</t>
-        </is>
-      </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>47.1</t>
+          <t>47.5</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>46.25</t>
+          <t>47.85</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>47.0</t>
+          <t>46.5</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
+          <t>47.4</t>
+        </is>
+      </c>
+      <c r="CH10" t="inlineStr">
+        <is>
           <t>24.66</t>
         </is>
       </c>
-      <c r="CH10" t="inlineStr">
+      <c r="CI10" t="inlineStr">
         <is>
           <t>** 觸控面板 - PET膜** 其他 - 其他電子產品及電子服務產業、其他** 醫療器材 - 塑化材料</t>
         </is>
       </c>
-      <c r="CI10" t="inlineStr">
+      <c r="CJ10" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -4757,12 +4807,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>170.0</t>
+          <t>199.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4772,7 +4822,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>46.65</t>
+          <t>47.0</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4782,17 +4832,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-2.41</t>
+          <t>-5.03</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-0.3</t>
+          <t>-0.96</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>23.31</t>
+          <t>32.28</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4857,7 +4907,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-6.23</t>
+          <t>-5.53</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4867,17 +4917,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>3.44</t>
+          <t>4.40</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-2.14</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4888,77 +4938,77 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>177</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>81.58</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>65.79</t>
+          <t>93.86</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-4.26</t>
+          <t>-4.34</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>45.88</t>
+          <t>46.2</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>45.73</t>
+          <t>45.67</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>47.76</t>
+          <t>47.75</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>47.37</t>
+          <t>47.39</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>31.68</t>
+          <t>43.77</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4968,7 +5018,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-115.40</t>
+          <t>-113.88</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4978,198 +5028,203 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>77098.98345323741</t>
+          <t>77005.29094827587</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>8007.0</t>
+          <t>9304.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>10142.2</t>
+          <t>11007.6</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>8225.2</t>
+          <t>8321.2</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>21859.62</t>
+          <t>21296.56</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>1917</t>
+          <t>2686</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-1630.473518740948</t>
-        </is>
-      </c>
-      <c r="BC11" t="n">
-        <v>-764.96</v>
-      </c>
-      <c r="BD11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>-1491.606690671351</t>
+        </is>
+      </c>
+      <c r="BC11" t="inlineStr">
+        <is>
+          <t>-727.839136288565</t>
+        </is>
+      </c>
+      <c r="BD11" t="n">
+        <v>9304</v>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF11" t="inlineStr">
+        <is>
           <t>48.75</t>
         </is>
       </c>
-      <c r="BF11" t="inlineStr">
+      <c r="BG11" t="inlineStr">
         <is>
           <t>2025/08/25</t>
         </is>
       </c>
-      <c r="BG11" t="inlineStr">
-        <is>
-          <t>-4.31</t>
-        </is>
-      </c>
       <c r="BH11" t="inlineStr">
         <is>
+          <t>-3.59</t>
+        </is>
+      </c>
+      <c r="BI11" t="inlineStr">
+        <is>
           <t>岱稜</t>
         </is>
       </c>
-      <c r="BI11" t="inlineStr">
+      <c r="BJ11" t="inlineStr">
         <is>
           <t>岱稜</t>
         </is>
       </c>
-      <c r="BJ11" t="inlineStr">
+      <c r="BK11" t="inlineStr">
         <is>
           <t>其他電子業</t>
         </is>
       </c>
-      <c r="BK11" t="inlineStr">
+      <c r="BL11" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BL11" t="inlineStr">
-        <is>
-          <t>1.07</t>
-        </is>
-      </c>
       <c r="BM11" t="inlineStr">
         <is>
+          <t>1.05</t>
+        </is>
+      </c>
+      <c r="BN11" t="inlineStr">
+        <is>
           <t>-1.004452687200723</t>
         </is>
       </c>
-      <c r="BN11" t="inlineStr">
+      <c r="BO11" t="inlineStr">
         <is>
           <t>11.92388165594906</t>
         </is>
       </c>
-      <c r="BO11" t="inlineStr">
+      <c r="BP11" t="inlineStr">
         <is>
           <t>2.060463205899802</t>
         </is>
       </c>
-      <c r="BP11" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="BQ11" t="inlineStr">
         <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR11" t="inlineStr">
+        <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="BR11" t="inlineStr">
-        <is>
-          <t>1.89</t>
-        </is>
-      </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>6.07</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
+          <t>6.18</t>
+        </is>
+      </c>
+      <c r="BU11" t="inlineStr">
+        <is>
           <t>8.56</t>
         </is>
       </c>
-      <c r="BU11" t="inlineStr">
-        <is>
-          <t>10.28</t>
-        </is>
-      </c>
       <c r="BV11" t="inlineStr">
         <is>
+          <t>10.1</t>
+        </is>
+      </c>
+      <c r="BW11" t="inlineStr">
+        <is>
           <t>33.67%</t>
         </is>
       </c>
-      <c r="BW11" t="inlineStr">
+      <c r="BX11" t="inlineStr">
         <is>
           <t>12.48%</t>
         </is>
       </c>
-      <c r="BX11" t="inlineStr">
-        <is>
-          <t>42.77</t>
-        </is>
-      </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>4286</t>
+          <t>41.57</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
+          <t>4211</t>
+        </is>
+      </c>
+      <c r="CA11" t="inlineStr">
+        <is>
           <t>真空蒸鍍薄膜95.00%、光電材料5.00% (2024年)</t>
         </is>
       </c>
-      <c r="CA11" t="inlineStr">
+      <c r="CB11" t="inlineStr">
         <is>
           <t>岱稜-其他電子業-上櫃</t>
         </is>
       </c>
-      <c r="CB11" t="inlineStr">
+      <c r="CC11" t="inlineStr">
         <is>
           <t>其他電子業平上櫃</t>
         </is>
       </c>
-      <c r="CC11" t="inlineStr">
-        <is>
-          <t>47.8</t>
-        </is>
-      </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>47.8</t>
+          <t>46.85</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>46.5</t>
+          <t>47.1</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>46.65</t>
+          <t>46.25</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
+          <t>47.0</t>
+        </is>
+      </c>
+      <c r="CH11" t="inlineStr">
+        <is>
           <t>24.66</t>
         </is>
       </c>
-      <c r="CH11" t="inlineStr">
+      <c r="CI11" t="inlineStr">
         <is>
           <t>** 觸控面板 - PET膜** 其他 - 其他電子產品及電子服務產業、其他** 醫療器材 - 塑化材料</t>
         </is>
       </c>
-      <c r="CI11" t="inlineStr">
+      <c r="CJ11" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -5188,12 +5243,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>3.8</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>464.0</t>
+          <t>170.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5203,7 +5258,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>47.0</t>
+          <t>46.65</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5213,17 +5268,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-3.18</t>
+          <t>-4.25</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-0.3</t>
+          <t>-0.96</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>15.69</t>
+          <t>23.31</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5288,7 +5343,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-5.53</t>
+          <t>-6.23</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5298,17 +5353,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>9.39</t>
+          <t>3.76</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>-2.14</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5319,288 +5374,293 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>177</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>81.58</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>38.6</t>
+          <t>65.79</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-0.37</t>
+          <t>0.33</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-4.22</t>
+          <t>-4.26</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>45.62</t>
+          <t>45.88</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>45.79</t>
+          <t>45.73</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
+          <t>47.76</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>47.37</t>
+        </is>
+      </c>
+      <c r="AP12" t="inlineStr">
+        <is>
+          <t>31.68</t>
+        </is>
+      </c>
+      <c r="AQ12" t="inlineStr">
+        <is>
+          <t>-0.45</t>
+        </is>
+      </c>
+      <c r="AR12" t="inlineStr">
+        <is>
+          <t>-0.66</t>
+        </is>
+      </c>
+      <c r="AS12" t="inlineStr">
+        <is>
+          <t>4.28</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr">
+        <is>
+          <t>-115.40</t>
+        </is>
+      </c>
+      <c r="AU12" t="inlineStr">
+        <is>
+          <t>2025/10/28</t>
+        </is>
+      </c>
+      <c r="AV12" t="inlineStr">
+        <is>
+          <t>77005.29094827587</t>
+        </is>
+      </c>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>8007.0</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>10142.2</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>8225.2</t>
+        </is>
+      </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>21859.62</t>
+        </is>
+      </c>
+      <c r="BA12" t="inlineStr">
+        <is>
+          <t>1917</t>
+        </is>
+      </c>
+      <c r="BB12" t="inlineStr">
+        <is>
+          <t>-1630.473518740948</t>
+        </is>
+      </c>
+      <c r="BC12" t="inlineStr">
+        <is>
+          <t>-764.9559907053081</t>
+        </is>
+      </c>
+      <c r="BD12" t="n">
+        <v>8007</v>
+      </c>
+      <c r="BE12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF12" t="inlineStr">
+        <is>
+          <t>48.75</t>
+        </is>
+      </c>
+      <c r="BG12" t="inlineStr">
+        <is>
+          <t>2025/08/25</t>
+        </is>
+      </c>
+      <c r="BH12" t="inlineStr">
+        <is>
+          <t>-4.31</t>
+        </is>
+      </c>
+      <c r="BI12" t="inlineStr">
+        <is>
+          <t>岱稜</t>
+        </is>
+      </c>
+      <c r="BJ12" t="inlineStr">
+        <is>
+          <t>岱稜</t>
+        </is>
+      </c>
+      <c r="BK12" t="inlineStr">
+        <is>
+          <t>其他電子業</t>
+        </is>
+      </c>
+      <c r="BL12" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BM12" t="inlineStr">
+        <is>
+          <t>1.05</t>
+        </is>
+      </c>
+      <c r="BN12" t="inlineStr">
+        <is>
+          <t>-1.004452687200723</t>
+        </is>
+      </c>
+      <c r="BO12" t="inlineStr">
+        <is>
+          <t>11.92388165594906</t>
+        </is>
+      </c>
+      <c r="BP12" t="inlineStr">
+        <is>
+          <t>2.060463205899802</t>
+        </is>
+      </c>
+      <c r="BQ12" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR12" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS12" t="inlineStr">
+        <is>
+          <t>1.89</t>
+        </is>
+      </c>
+      <c r="BT12" t="inlineStr">
+        <is>
+          <t>6.18</t>
+        </is>
+      </c>
+      <c r="BU12" t="inlineStr">
+        <is>
+          <t>8.56</t>
+        </is>
+      </c>
+      <c r="BV12" t="inlineStr">
+        <is>
+          <t>10.1</t>
+        </is>
+      </c>
+      <c r="BW12" t="inlineStr">
+        <is>
+          <t>33.67%</t>
+        </is>
+      </c>
+      <c r="BX12" t="inlineStr">
+        <is>
+          <t>12.48%</t>
+        </is>
+      </c>
+      <c r="BY12" t="inlineStr">
+        <is>
+          <t>41.57</t>
+        </is>
+      </c>
+      <c r="BZ12" t="inlineStr">
+        <is>
+          <t>4211</t>
+        </is>
+      </c>
+      <c r="CA12" t="inlineStr">
+        <is>
+          <t>真空蒸鍍薄膜95.00%、光電材料5.00% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB12" t="inlineStr">
+        <is>
+          <t>岱稜-其他電子業-上櫃</t>
+        </is>
+      </c>
+      <c r="CC12" t="inlineStr">
+        <is>
+          <t>其他電子業平上櫃</t>
+        </is>
+      </c>
+      <c r="CD12" t="inlineStr">
+        <is>
           <t>47.8</t>
         </is>
       </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>47.35</t>
-        </is>
-      </c>
-      <c r="AP12" t="inlineStr">
-        <is>
-          <t>21.78</t>
-        </is>
-      </c>
-      <c r="AQ12" t="inlineStr">
-        <is>
-          <t>-0.56</t>
-        </is>
-      </c>
-      <c r="AR12" t="inlineStr">
-        <is>
-          <t>-0.71</t>
-        </is>
-      </c>
-      <c r="AS12" t="inlineStr">
-        <is>
-          <t>4.28</t>
-        </is>
-      </c>
-      <c r="AT12" t="inlineStr">
-        <is>
-          <t>-116.62</t>
-        </is>
-      </c>
-      <c r="AU12" t="inlineStr">
-        <is>
-          <t>2025/10/28</t>
-        </is>
-      </c>
-      <c r="AV12" t="inlineStr">
-        <is>
-          <t>77098.98345323741</t>
-        </is>
-      </c>
-      <c r="AW12" t="inlineStr">
-        <is>
-          <t>21744.0</t>
-        </is>
-      </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>9374.6</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr">
-        <is>
-          <t>8103.2</t>
-        </is>
-      </c>
-      <c r="AZ12" t="inlineStr">
-        <is>
-          <t>22013.86</t>
-        </is>
-      </c>
-      <c r="BA12" t="inlineStr">
-        <is>
-          <t>1271</t>
-        </is>
-      </c>
-      <c r="BB12" t="inlineStr">
-        <is>
-          <t>-1787.840342020155</t>
-        </is>
-      </c>
-      <c r="BC12" t="n">
-        <v>-651.7</v>
-      </c>
-      <c r="BD12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BE12" t="inlineStr">
-        <is>
-          <t>48.75</t>
-        </is>
-      </c>
-      <c r="BF12" t="inlineStr">
-        <is>
-          <t>2025/08/25</t>
-        </is>
-      </c>
-      <c r="BG12" t="inlineStr">
-        <is>
-          <t>-3.59</t>
-        </is>
-      </c>
-      <c r="BH12" t="inlineStr">
-        <is>
-          <t>岱稜</t>
-        </is>
-      </c>
-      <c r="BI12" t="inlineStr">
-        <is>
-          <t>岱稜</t>
-        </is>
-      </c>
-      <c r="BJ12" t="inlineStr">
-        <is>
-          <t>其他電子業</t>
-        </is>
-      </c>
-      <c r="BK12" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BL12" t="inlineStr">
-        <is>
-          <t>1.07</t>
-        </is>
-      </c>
-      <c r="BM12" t="inlineStr">
-        <is>
-          <t>-1.004452687200723</t>
-        </is>
-      </c>
-      <c r="BN12" t="inlineStr">
-        <is>
-          <t>11.92388165594906</t>
-        </is>
-      </c>
-      <c r="BO12" t="inlineStr">
-        <is>
-          <t>2.060463205899802</t>
-        </is>
-      </c>
-      <c r="BP12" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BQ12" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="BR12" t="inlineStr">
-        <is>
-          <t>1.91</t>
-        </is>
-      </c>
-      <c r="BS12" t="inlineStr">
-        <is>
-          <t>6.07</t>
-        </is>
-      </c>
-      <c r="BT12" t="inlineStr">
-        <is>
-          <t>8.56</t>
-        </is>
-      </c>
-      <c r="BU12" t="inlineStr">
-        <is>
-          <t>10.28</t>
-        </is>
-      </c>
-      <c r="BV12" t="inlineStr">
-        <is>
-          <t>33.67%</t>
-        </is>
-      </c>
-      <c r="BW12" t="inlineStr">
-        <is>
-          <t>12.48%</t>
-        </is>
-      </c>
-      <c r="BX12" t="inlineStr">
-        <is>
-          <t>42.77</t>
-        </is>
-      </c>
-      <c r="BY12" t="inlineStr">
-        <is>
-          <t>4286</t>
-        </is>
-      </c>
-      <c r="BZ12" t="inlineStr">
-        <is>
-          <t>真空蒸鍍薄膜95.00%、光電材料5.00% (2024年)</t>
-        </is>
-      </c>
-      <c r="CA12" t="inlineStr">
-        <is>
-          <t>岱稜-其他電子業-上櫃</t>
-        </is>
-      </c>
-      <c r="CB12" t="inlineStr">
-        <is>
-          <t>其他電子業平上櫃</t>
-        </is>
-      </c>
-      <c r="CC12" t="inlineStr">
-        <is>
-          <t>46.0</t>
-        </is>
-      </c>
-      <c r="CD12" t="inlineStr">
-        <is>
-          <t>47.7</t>
-        </is>
-      </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>45.9</t>
+          <t>47.8</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>47.0</t>
+          <t>46.5</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
+          <t>46.65</t>
+        </is>
+      </c>
+      <c r="CH12" t="inlineStr">
+        <is>
           <t>24.66</t>
         </is>
       </c>
-      <c r="CH12" t="inlineStr">
+      <c r="CI12" t="inlineStr">
         <is>
           <t>** 觸控面板 - PET膜** 其他 - 其他電子產品及電子服務產業、其他** 醫療器材 - 塑化材料</t>
         </is>
       </c>
-      <c r="CI12" t="inlineStr">
+      <c r="CJ12" t="inlineStr">
         <is>
           <t>False</t>
         </is>

--- a/Result/checksun_type/PET膜.xlsx
+++ b/Result/checksun_type/PET膜.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-1.77</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>177.0</t>
+          <t>98.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>44.75</t>
+          <t>45.3</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-39.89</t>
+          <t>-46.16</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-10.05</t>
+          <t>-8.94</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>3.91</t>
+          <t>3.37</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,77 +1014,77 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>177</t>
+          <t>98</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>19.3</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>11.9</t>
+          <t>15.36</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-1.32</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-1.47</t>
+          <t>-1.96</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-2.34</t>
+          <t>-2.17</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>-1.05</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>45.35</t>
+          <t>45.09</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>46.03</t>
+          <t>45.99</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>47.13</t>
+          <t>47.02</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>47.5</t>
+          <t>47.51</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-41.45</t>
+          <t>-35.53</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-0.36</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-106.01</t>
+          <t>-106.59</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1104,46 +1104,46 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>77005.29094827587</t>
+          <t>76904.2962697274</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>7926.0</t>
+          <t>4408.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>8091.0</t>
+          <t>6984.0</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>13461.2</t>
+          <t>12971.6</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>15558.56</t>
+          <t>15065.26</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-5370</t>
+          <t>-5987</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-395.7538757808097</t>
+          <t>-555.4712818600863</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-1162.725574290193</t>
+          <t>-1433.917015296107</t>
         </is>
       </c>
       <c r="BD2" t="n">
-        <v>7926</v>
+        <v>4408</v>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-8.21</t>
+          <t>-7.08</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1207,7 +1207,7 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1217,12 +1217,12 @@
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>1.84</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>6.18</t>
+          <t>6.11</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>10.1</t>
+          <t>10.23</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1247,12 +1247,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>41.57</t>
+          <t>42.08</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>4211</t>
+          <t>4262</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1272,22 +1272,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>45.2</t>
+          <t>44.95</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>45.2</t>
+          <t>45.45</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>44.6</t>
+          <t>44.9</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>44.75</t>
+          <t>45.3</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1319,12 +1319,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>-1.77</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>177.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>45.55</t>
+          <t>44.75</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1344,17 +1344,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-1.79</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-38.31</t>
+          <t>-39.89</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1419,7 +1419,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-8.44</t>
+          <t>-10.05</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1429,17 +1429,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>6.09</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-0.98</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1450,17 +1450,17 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>177</t>
+          <t>98</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>26.79</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
@@ -1470,37 +1470,37 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>-1.32</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>-1.47</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-2.47</t>
+          <t>-2.34</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-0.50</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>45.81</t>
+          <t>45.35</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>46.09</t>
+          <t>46.03</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>47.26</t>
+          <t>47.13</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
@@ -1510,17 +1510,17 @@
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-20.83</t>
+          <t>-41.45</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>-0.36</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-105.39</t>
+          <t>-106.01</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1540,46 +1540,46 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>77005.29094827587</t>
+          <t>76904.2962697274</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>3204.0</t>
+          <t>7926.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>8309.4</t>
+          <t>8091.0</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>13469.3</t>
+          <t>13461.2</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>16218.6</t>
+          <t>15558.56</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-5159</t>
+          <t>-5370</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-256.304476051831</t>
+          <t>-395.7538757808097</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-1110.711888057096</t>
+          <t>-1162.725574290193</t>
         </is>
       </c>
       <c r="BD3" t="n">
-        <v>3204</v>
+        <v>7926</v>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-6.56</t>
+          <t>-8.21</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1643,7 +1643,7 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>6.18</t>
+          <t>6.11</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1668,7 +1668,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>10.1</t>
+          <t>10.23</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1683,12 +1683,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>41.57</t>
+          <t>42.08</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>4211</t>
+          <t>4262</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1708,22 +1708,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>45.4</t>
+          <t>45.2</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>46.25</t>
+          <t>45.2</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>45.3</t>
+          <t>44.6</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>45.55</t>
+          <t>44.75</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1755,12 +1755,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>112.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1770,7 +1770,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>45.05</t>
+          <t>45.55</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1780,17 +1780,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>-0.55</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-30.74</t>
+          <t>-38.31</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1855,7 +1855,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-9.45</t>
+          <t>-8.44</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1865,17 +1865,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>2.48</t>
+          <t>2.41</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1886,77 +1886,77 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>177</t>
+          <t>98</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>8.93</t>
+          <t>26.79</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>22.13</t>
+          <t>11.9</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-2.32</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-2.65</t>
+          <t>-2.47</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.50</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>46.12</t>
+          <t>45.81</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>46.12</t>
+          <t>46.09</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>47.37</t>
+          <t>47.26</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>47.49</t>
+          <t>47.5</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-13.12</t>
+          <t>-20.83</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-105.11</t>
+          <t>-105.39</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1976,46 +1976,46 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>77005.29094827587</t>
+          <t>76904.2962697274</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>5046.0</t>
+          <t>3204.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>10612.2</t>
+          <t>8309.4</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>15323.3</t>
+          <t>13469.3</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>16780.18</t>
+          <t>16218.6</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-4711</t>
+          <t>-5159</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-100.9576738690555</t>
+          <t>-256.304476051831</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-490.8097688649177</t>
+          <t>-1110.711888057096</t>
         </is>
       </c>
       <c r="BD4" t="n">
-        <v>5046</v>
+        <v>3204</v>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2034,7 +2034,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-7.59</t>
+          <t>-6.56</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2079,7 +2079,7 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2089,12 +2089,12 @@
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>6.18</t>
+          <t>6.11</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2104,7 +2104,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>10.1</t>
+          <t>10.23</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>41.57</t>
+          <t>42.08</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>4211</t>
+          <t>4262</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2144,22 +2144,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>44.55</t>
+          <t>45.4</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>45.4</t>
+          <t>46.25</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>44.55</t>
+          <t>45.3</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>45.05</t>
+          <t>45.55</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-3.84</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>315.0</t>
+          <t>112.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2206,7 +2206,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>44.8</t>
+          <t>45.05</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2216,17 +2216,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-9.12</t>
+          <t>-30.74</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2291,7 +2291,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-9.95</t>
+          <t>-9.45</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2301,17 +2301,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>6.97</t>
+          <t>3.85</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-4.69</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2322,57 +2322,57 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>177</t>
+          <t>98</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>8.93</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>45.15</t>
+          <t>22.13</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-3.92</t>
+          <t>-2.32</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-2.8</t>
+          <t>-2.65</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>46.63</t>
+          <t>46.12</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>46.15</t>
+          <t>46.12</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>47.48</t>
+          <t>47.37</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
@@ -2382,17 +2382,17 @@
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>27.78</t>
+          <t>-13.12</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2402,7 +2402,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-104.94</t>
+          <t>-105.11</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2412,46 +2412,46 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>77005.29094827587</t>
+          <t>76904.2962697274</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>14336.0</t>
+          <t>5046.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>14123.0</t>
+          <t>10612.2</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>15541.1</t>
+          <t>15323.3</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>17446.4</t>
+          <t>16780.18</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-1418</t>
+          <t>-4711</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-30.07547477889878</t>
+          <t>-100.9576738690555</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>214.9364645833703</t>
+          <t>-490.8097688649177</t>
         </is>
       </c>
       <c r="BD5" t="n">
-        <v>14336</v>
+        <v>5046</v>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-8.10</t>
+          <t>-7.59</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2515,7 +2515,7 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2525,12 +2525,12 @@
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>6.18</t>
+          <t>6.11</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2540,7 +2540,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>10.1</t>
+          <t>10.23</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2555,12 +2555,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>41.57</t>
+          <t>42.08</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>4211</t>
+          <t>4262</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2580,22 +2580,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>46.9</t>
+          <t>44.55</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>46.9</t>
+          <t>45.4</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>44.8</t>
+          <t>44.55</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>44.8</t>
+          <t>45.05</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-0.95</t>
+          <t>-3.84</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>213.0</t>
+          <t>315.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2642,7 +2642,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>46.6</t>
+          <t>44.8</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2652,17 +2652,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-4.13</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>26.53</t>
+          <t>-9.12</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2727,7 +2727,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-6.33</t>
+          <t>-9.95</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2737,17 +2737,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>4.71</t>
+          <t>10.83</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>-4.69</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2758,77 +2758,77 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>177</t>
+          <t>98</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>57.45</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>71.82</t>
+          <t>45.15</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-1.17</t>
+          <t>-3.92</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-2.88</t>
+          <t>-2.8</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>47.15</t>
+          <t>46.63</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>46.22</t>
+          <t>46.15</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>47.59</t>
+          <t>47.48</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>47.5</t>
+          <t>47.49</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>98.12</t>
+          <t>27.78</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-0.00</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2838,7 +2838,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-105.28</t>
+          <t>-104.94</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2848,46 +2848,46 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>77005.29094827587</t>
+          <t>76904.2962697274</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>9943.0</t>
+          <t>14336.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>18959.2</t>
+          <t>14123.0</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>14983.4</t>
+          <t>15541.1</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>17743.28</t>
+          <t>17446.4</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>3975</t>
+          <t>-1418</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-74.62310011749315</t>
+          <t>-30.07547477889878</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>220.1119243458033</t>
+          <t>214.9364645833703</t>
         </is>
       </c>
       <c r="BD6" t="n">
-        <v>9943</v>
+        <v>14336</v>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-4.41</t>
+          <t>-8.10</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2951,7 +2951,7 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>1.89</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>6.18</t>
+          <t>6.11</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2976,7 +2976,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>10.1</t>
+          <t>10.23</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2991,12 +2991,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>41.57</t>
+          <t>42.08</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>4211</t>
+          <t>4262</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -3016,22 +3016,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>47.15</t>
+          <t>46.9</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>47.2</t>
+          <t>46.9</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>46.4</t>
+          <t>44.8</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>46.6</t>
+          <t>44.8</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>-0.95</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>192.0</t>
+          <t>213.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>47.05</t>
+          <t>46.6</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3088,17 +3088,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-5.14</t>
+          <t>-2.87</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>29.99</t>
+          <t>26.53</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3163,7 +3163,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-5.43</t>
+          <t>-6.33</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3173,17 +3173,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>4.25</t>
+          <t>7.32</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3194,77 +3194,77 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>177</t>
+          <t>98</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>57.45</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>71.82</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>-1.17</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-3.21</t>
+          <t>-2.88</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>47.23</t>
+          <t>47.15</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>46.15</t>
+          <t>46.22</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>47.68</t>
+          <t>47.59</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>47.48</t>
+          <t>47.5</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>100.64</t>
+          <t>98.12</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.00</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3274,7 +3274,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-106.58</t>
+          <t>-105.28</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3284,46 +3284,46 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>77005.29094827587</t>
+          <t>76904.2962697274</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>9018.0</t>
+          <t>9943.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>18831.4</t>
+          <t>18959.2</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>14486.8</t>
+          <t>14983.4</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>18676.0</t>
+          <t>17743.28</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>4344</t>
+          <t>3975</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-128.211286383547</t>
+          <t>-74.62310011749315</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>690.3228695655016</t>
+          <t>220.1119243458033</t>
         </is>
       </c>
       <c r="BD7" t="n">
-        <v>9018</v>
+        <v>9943</v>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-3.49</t>
+          <t>-4.41</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3392,17 +3392,17 @@
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>1.89</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>6.18</t>
+          <t>6.11</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3412,7 +3412,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>10.1</t>
+          <t>10.23</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>41.57</t>
+          <t>42.08</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>4211</t>
+          <t>4262</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3452,22 +3452,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>46.5</t>
+          <t>47.15</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>47.5</t>
+          <t>47.2</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>46.35</t>
+          <t>46.4</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>47.05</t>
+          <t>46.6</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3499,12 +3499,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-1.05</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>311.0</t>
+          <t>192.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>47.1</t>
+          <t>47.05</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3524,17 +3524,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-5.25</t>
+          <t>-3.86</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>33.05</t>
+          <t>29.99</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-5.33</t>
+          <t>-5.43</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3609,17 +3609,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>6.88</t>
+          <t>6.60</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-0.95</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3630,77 +3630,77 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>177</t>
+          <t>98</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>93.33</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>2.36</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-3.53</t>
+          <t>-3.21</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>0.60</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>47.15</t>
+          <t>47.23</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>46.06</t>
+          <t>46.15</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>47.75</t>
+          <t>47.68</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>47.47</t>
+          <t>47.48</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>89.68</t>
+          <t>100.64</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3710,7 +3710,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-108.23</t>
+          <t>-106.58</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3720,46 +3720,46 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>77005.29094827587</t>
+          <t>76904.2962697274</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>14718.0</t>
+          <t>9018.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>18629.2</t>
+          <t>18831.4</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>14001.9</t>
+          <t>14486.8</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>20406.5</t>
+          <t>18676.0</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>4627</t>
+          <t>4344</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-277.0356783742832</t>
+          <t>-128.211286383547</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>1436.505545966302</t>
+          <t>690.3228695655016</t>
         </is>
       </c>
       <c r="BD8" t="n">
-        <v>14718</v>
+        <v>9018</v>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3778,7 +3778,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-3.38</t>
+          <t>-3.49</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3828,7 +3828,7 @@
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
@@ -3838,7 +3838,7 @@
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>6.18</t>
+          <t>6.11</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3848,7 +3848,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>10.1</t>
+          <t>10.23</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>41.57</t>
+          <t>42.08</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>4211</t>
+          <t>4262</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3888,22 +3888,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>47.6</t>
+          <t>46.5</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>47.8</t>
+          <t>47.5</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>46.85</t>
+          <t>46.35</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>47.1</t>
+          <t>47.05</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3935,12 +3935,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>-1.05</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>474.0</t>
+          <t>311.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3950,7 +3950,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>47.6</t>
+          <t>47.1</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3960,17 +3960,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-6.37</t>
+          <t>-3.97</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>50.85</t>
+          <t>33.05</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4035,7 +4035,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-4.32</t>
+          <t>-5.33</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4045,17 +4045,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10.48</t>
+          <t>10.69</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-0.95</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4066,77 +4066,77 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>177</t>
+          <t>98</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>93.33</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>2.67</t>
+          <t>2.36</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-3.93</t>
+          <t>-3.53</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.60</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>47.13</t>
+          <t>47.15</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>45.9</t>
+          <t>46.06</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>47.78</t>
+          <t>47.75</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>47.45</t>
+          <t>47.47</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>79.21</t>
+          <t>89.68</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4146,7 +4146,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-110.08</t>
+          <t>-108.23</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4156,46 +4156,46 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>77005.29094827587</t>
+          <t>76904.2962697274</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>22600.0</t>
+          <t>14718.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>20034.4</t>
+          <t>18629.2</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>13280.9</t>
+          <t>14001.9</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>20741.92</t>
+          <t>20406.5</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>6753</t>
+          <t>4627</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-588.5886282543895</t>
+          <t>-277.0356783742832</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>1840.462742754364</t>
+          <t>1436.505545966302</t>
         </is>
       </c>
       <c r="BD9" t="n">
-        <v>22600</v>
+        <v>14718</v>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4214,7 +4214,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-2.36</t>
+          <t>-3.38</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4259,7 +4259,7 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4269,12 +4269,12 @@
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>6.18</t>
+          <t>6.11</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4284,7 +4284,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>10.1</t>
+          <t>10.23</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4299,12 +4299,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>41.57</t>
+          <t>42.08</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>4211</t>
+          <t>4262</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4324,22 +4324,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>47.85</t>
+          <t>47.6</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>48.1</t>
+          <t>47.8</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>47.25</t>
+          <t>46.85</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>47.6</t>
+          <t>47.1</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4371,12 +4371,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>812.0</t>
+          <t>474.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4386,7 +4386,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>47.4</t>
+          <t>47.6</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4396,17 +4396,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-5.92</t>
+          <t>-5.08</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>43.35</t>
+          <t>50.85</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4471,7 +4471,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-4.72</t>
+          <t>-4.32</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4481,17 +4481,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>17.96</t>
+          <t>16.30</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4502,12 +4502,12 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>177</t>
+          <t>98</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
@@ -4517,62 +4517,62 @@
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>93.86</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>2.67</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-4.23</t>
+          <t>-3.93</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>46.66</t>
+          <t>47.13</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>45.74</t>
+          <t>45.9</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>47.76</t>
+          <t>47.78</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>47.42</t>
+          <t>47.45</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>59.88</t>
+          <t>79.21</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4582,7 +4582,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-112.07</t>
+          <t>-110.08</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4592,46 +4592,46 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>77005.29094827587</t>
+          <t>76904.2962697274</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>38517.0</t>
+          <t>22600.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>16959.2</t>
+          <t>20034.4</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>11830.5</t>
+          <t>13280.9</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>20783.02</t>
+          <t>20741.92</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>5128</t>
+          <t>6753</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-1030.234332074163</t>
+          <t>-588.5886282543895</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>1507.31364021037</t>
+          <t>1840.462742754364</t>
         </is>
       </c>
       <c r="BD10" t="n">
-        <v>38517</v>
+        <v>22600</v>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4650,7 +4650,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-2.77</t>
+          <t>-2.36</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4695,7 +4695,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4705,12 +4705,12 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>6.18</t>
+          <t>6.11</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4720,7 +4720,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>10.1</t>
+          <t>10.23</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4735,12 +4735,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>41.57</t>
+          <t>42.08</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>4211</t>
+          <t>4262</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4760,22 +4760,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>47.5</t>
+          <t>47.85</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>47.85</t>
+          <t>48.1</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>46.5</t>
+          <t>47.25</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>47.4</t>
+          <t>47.6</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4807,12 +4807,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>199.0</t>
+          <t>812.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4822,7 +4822,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>47.0</t>
+          <t>47.4</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4832,17 +4832,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-5.03</t>
+          <t>-4.64</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>32.28</t>
+          <t>43.35</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-5.53</t>
+          <t>-4.72</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4917,17 +4917,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>4.40</t>
+          <t>27.92</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4938,12 +4938,12 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>177</t>
+          <t>98</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
@@ -4958,57 +4958,57 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-4.34</t>
+          <t>-4.23</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>46.2</t>
+          <t>46.66</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>45.67</t>
+          <t>45.74</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>47.75</t>
+          <t>47.76</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>47.39</t>
+          <t>47.42</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>43.77</t>
+          <t>59.88</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -5018,7 +5018,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-113.88</t>
+          <t>-112.07</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -5028,46 +5028,46 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>77005.29094827587</t>
+          <t>76904.2962697274</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>9304.0</t>
+          <t>38517.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>11007.6</t>
+          <t>16959.2</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>8321.2</t>
+          <t>11830.5</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>21296.56</t>
+          <t>20783.02</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>2686</t>
+          <t>5128</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-1491.606690671351</t>
+          <t>-1030.234332074163</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-727.839136288565</t>
+          <t>1507.31364021037</t>
         </is>
       </c>
       <c r="BD11" t="n">
-        <v>9304</v>
+        <v>38517</v>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5086,7 +5086,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-3.59</t>
+          <t>-2.77</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5131,7 +5131,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>6.18</t>
+          <t>6.11</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5156,7 +5156,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>10.1</t>
+          <t>10.23</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5171,12 +5171,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>41.57</t>
+          <t>42.08</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>4211</t>
+          <t>4262</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5196,22 +5196,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>46.85</t>
+          <t>47.5</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>47.1</t>
+          <t>47.85</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>46.25</t>
+          <t>46.5</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>47.0</t>
+          <t>47.4</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5243,12 +5243,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>170.0</t>
+          <t>199.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5258,7 +5258,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>46.65</t>
+          <t>47.0</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5268,17 +5268,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-4.25</t>
+          <t>-3.75</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>23.31</t>
+          <t>32.28</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5343,7 +5343,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-6.23</t>
+          <t>-5.53</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5353,17 +5353,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>3.76</t>
+          <t>6.84</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-2.14</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5374,77 +5374,77 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>177</t>
+          <t>98</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>81.58</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>65.79</t>
+          <t>93.86</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-4.26</t>
+          <t>-4.34</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>45.88</t>
+          <t>46.2</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>45.73</t>
+          <t>45.67</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>47.76</t>
+          <t>47.75</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>47.37</t>
+          <t>47.39</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>31.68</t>
+          <t>43.77</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5454,7 +5454,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-115.40</t>
+          <t>-113.88</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5464,46 +5464,46 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>77005.29094827587</t>
+          <t>76904.2962697274</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>8007.0</t>
+          <t>9304.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>10142.2</t>
+          <t>11007.6</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>8225.2</t>
+          <t>8321.2</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>21859.62</t>
+          <t>21296.56</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>1917</t>
+          <t>2686</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-1630.473518740948</t>
+          <t>-1491.606690671351</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-764.9559907053081</t>
+          <t>-727.839136288565</t>
         </is>
       </c>
       <c r="BD12" t="n">
-        <v>8007</v>
+        <v>9304</v>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5522,7 +5522,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-4.31</t>
+          <t>-3.59</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5567,7 +5567,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>1.89</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>6.18</t>
+          <t>6.11</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5592,7 +5592,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>10.1</t>
+          <t>10.23</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5607,12 +5607,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>41.57</t>
+          <t>42.08</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>4211</t>
+          <t>4262</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5632,22 +5632,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>47.8</t>
+          <t>46.85</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>47.8</t>
+          <t>47.1</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>46.5</t>
+          <t>46.25</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>46.65</t>
+          <t>47.0</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/PET膜.xlsx
+++ b/Result/checksun_type/PET膜.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>98.0</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>45.3</t>
+          <t>45.35</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>-1.31</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-46.16</t>
+          <t>-48.83</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-8.94</t>
+          <t>-8.84</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>3.37</t>
+          <t>2.79</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>-1.32</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,77 +1014,77 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>81</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>19.3</t>
+          <t>25.53</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>15.36</t>
+          <t>14.94</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>0.33</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-1.96</t>
+          <t>-1.67</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-2.17</t>
+          <t>-2.0</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-1.05</t>
+          <t>-1.30</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>45.09</t>
+          <t>45.2</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>45.99</t>
+          <t>45.97</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>47.02</t>
+          <t>46.91</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>47.51</t>
+          <t>47.52</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-35.53</t>
+          <t>-28.10</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-106.59</t>
+          <t>-107.09</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1104,46 +1104,46 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>76904.2962697274</t>
+          <t>76802.06088825215</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>4408.0</t>
+          <t>3696.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>6984.0</t>
+          <t>4856.0</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>12971.6</t>
+          <t>9489.5</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>15065.26</t>
+          <t>14335.48</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-5987</t>
+          <t>-4633</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-555.4712818600863</t>
+          <t>-722.5223305920491</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-1433.917015296107</t>
+          <t>-1641.303098617845</t>
         </is>
       </c>
       <c r="BD2" t="n">
-        <v>4408</v>
+        <v>3696</v>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-7.08</t>
+          <t>-6.97</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1207,7 +1207,7 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1222,7 +1222,7 @@
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>6.11</t>
+          <t>6.1</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>10.23</t>
+          <t>10.24</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1247,12 +1247,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>42.08</t>
+          <t>42.67</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>4262</t>
+          <t>4267</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1272,22 +1272,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>44.95</t>
+          <t>46.0</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>45.45</t>
+          <t>46.0</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>44.9</t>
+          <t>45.3</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>45.3</t>
+          <t>45.35</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1319,12 +1319,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-1.77</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>177.0</t>
+          <t>98.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>44.75</t>
+          <t>45.3</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1344,17 +1344,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>-1.31</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-39.89</t>
+          <t>-46.16</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1419,7 +1419,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-10.05</t>
+          <t>-8.94</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1429,17 +1429,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>6.09</t>
+          <t>3.37</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1450,77 +1450,77 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>81</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>19.3</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>11.9</t>
+          <t>15.36</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-1.32</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-1.47</t>
+          <t>-1.96</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-2.34</t>
+          <t>-2.17</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>-1.05</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>45.35</t>
+          <t>45.09</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>46.03</t>
+          <t>45.99</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>47.13</t>
+          <t>47.02</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>47.5</t>
+          <t>47.51</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-41.45</t>
+          <t>-35.53</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-0.36</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-106.01</t>
+          <t>-106.59</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1540,46 +1540,46 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>76904.2962697274</t>
+          <t>76802.06088825215</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>7926.0</t>
+          <t>4408.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>8091.0</t>
+          <t>6984.0</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>13461.2</t>
+          <t>12971.6</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>15558.56</t>
+          <t>15065.26</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-5370</t>
+          <t>-5987</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-395.7538757808097</t>
+          <t>-555.4712818600863</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-1162.725574290193</t>
+          <t>-1433.917015296107</t>
         </is>
       </c>
       <c r="BD3" t="n">
-        <v>7926</v>
+        <v>4408</v>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-8.21</t>
+          <t>-7.08</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1643,7 +1643,7 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>1.84</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>6.11</t>
+          <t>6.1</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1668,7 +1668,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>10.23</t>
+          <t>10.24</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1683,12 +1683,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>42.08</t>
+          <t>42.67</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>4262</t>
+          <t>4267</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1708,22 +1708,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>45.2</t>
+          <t>44.95</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>45.2</t>
+          <t>45.45</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>44.6</t>
+          <t>44.9</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>44.75</t>
+          <t>45.3</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1755,12 +1755,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>-1.77</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>177.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1770,7 +1770,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>45.55</t>
+          <t>44.75</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1780,17 +1780,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-0.55</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>-1.31</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-38.31</t>
+          <t>-39.89</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1855,7 +1855,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-8.44</t>
+          <t>-10.05</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1865,17 +1865,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>2.41</t>
+          <t>6.09</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-0.98</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1886,17 +1886,17 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>81</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>26.79</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
@@ -1906,37 +1906,37 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>-1.32</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>-1.47</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-2.47</t>
+          <t>-2.34</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-0.50</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>45.81</t>
+          <t>45.35</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>46.09</t>
+          <t>46.03</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>47.26</t>
+          <t>47.13</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
@@ -1946,17 +1946,17 @@
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-20.83</t>
+          <t>-41.45</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>-0.36</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-105.39</t>
+          <t>-106.01</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1976,46 +1976,46 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>76904.2962697274</t>
+          <t>76802.06088825215</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>3204.0</t>
+          <t>7926.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>8309.4</t>
+          <t>8091.0</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>13469.3</t>
+          <t>13461.2</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>16218.6</t>
+          <t>15558.56</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-5159</t>
+          <t>-5370</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-256.304476051831</t>
+          <t>-395.7538757808097</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-1110.711888057096</t>
+          <t>-1162.725574290193</t>
         </is>
       </c>
       <c r="BD4" t="n">
-        <v>3204</v>
+        <v>7926</v>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2034,7 +2034,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-6.56</t>
+          <t>-8.21</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2079,7 +2079,7 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2089,12 +2089,12 @@
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>6.11</t>
+          <t>6.1</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2104,7 +2104,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>10.23</t>
+          <t>10.24</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>42.08</t>
+          <t>42.67</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>4262</t>
+          <t>4267</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2144,22 +2144,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>45.4</t>
+          <t>45.2</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>46.25</t>
+          <t>45.2</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>45.3</t>
+          <t>44.6</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>45.55</t>
+          <t>44.75</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>112.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2206,7 +2206,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>45.05</t>
+          <t>45.55</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2216,17 +2216,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>-0.44</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>-1.31</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-30.74</t>
+          <t>-38.31</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2291,7 +2291,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-9.45</t>
+          <t>-8.44</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2301,17 +2301,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>3.85</t>
+          <t>2.41</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2322,77 +2322,77 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>81</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>8.93</t>
+          <t>26.79</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>22.13</t>
+          <t>11.9</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-2.32</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-2.65</t>
+          <t>-2.47</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.50</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>46.12</t>
+          <t>45.81</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>46.12</t>
+          <t>46.09</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>47.37</t>
+          <t>47.26</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>47.49</t>
+          <t>47.5</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-13.12</t>
+          <t>-20.83</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2402,7 +2402,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-105.11</t>
+          <t>-105.39</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2412,46 +2412,46 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>76904.2962697274</t>
+          <t>76802.06088825215</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>5046.0</t>
+          <t>3204.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>10612.2</t>
+          <t>8309.4</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>15323.3</t>
+          <t>13469.3</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>16780.18</t>
+          <t>16218.6</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-4711</t>
+          <t>-5159</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-100.9576738690555</t>
+          <t>-256.304476051831</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-490.8097688649177</t>
+          <t>-1110.711888057096</t>
         </is>
       </c>
       <c r="BD5" t="n">
-        <v>5046</v>
+        <v>3204</v>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-7.59</t>
+          <t>-6.56</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2515,7 +2515,7 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2525,12 +2525,12 @@
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>6.11</t>
+          <t>6.1</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2540,7 +2540,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>10.23</t>
+          <t>10.24</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2555,12 +2555,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>42.08</t>
+          <t>42.67</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>4262</t>
+          <t>4267</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2580,22 +2580,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>44.55</t>
+          <t>45.4</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>45.4</t>
+          <t>46.25</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>44.55</t>
+          <t>45.3</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>45.05</t>
+          <t>45.55</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-3.84</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>315.0</t>
+          <t>112.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2642,7 +2642,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>44.8</t>
+          <t>45.05</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2652,17 +2652,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>-1.31</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-9.12</t>
+          <t>-30.74</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2727,7 +2727,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-9.95</t>
+          <t>-9.45</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2737,17 +2737,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10.83</t>
+          <t>3.85</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-4.69</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2758,57 +2758,57 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>81</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>8.93</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>45.15</t>
+          <t>22.13</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-3.92</t>
+          <t>-2.32</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-2.8</t>
+          <t>-2.65</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>46.63</t>
+          <t>46.12</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>46.15</t>
+          <t>46.12</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>47.48</t>
+          <t>47.37</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
@@ -2818,17 +2818,17 @@
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>27.78</t>
+          <t>-13.12</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2838,7 +2838,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-104.94</t>
+          <t>-105.11</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2848,46 +2848,46 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>76904.2962697274</t>
+          <t>76802.06088825215</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>14336.0</t>
+          <t>5046.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>14123.0</t>
+          <t>10612.2</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>15541.1</t>
+          <t>15323.3</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>17446.4</t>
+          <t>16780.18</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-1418</t>
+          <t>-4711</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-30.07547477889878</t>
+          <t>-100.9576738690555</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>214.9364645833703</t>
+          <t>-490.8097688649177</t>
         </is>
       </c>
       <c r="BD6" t="n">
-        <v>14336</v>
+        <v>5046</v>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-8.10</t>
+          <t>-7.59</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2951,7 +2951,7 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>6.11</t>
+          <t>6.1</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2976,7 +2976,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>10.23</t>
+          <t>10.24</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2991,12 +2991,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>42.08</t>
+          <t>42.67</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>4262</t>
+          <t>4267</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -3016,22 +3016,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>46.9</t>
+          <t>44.55</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>46.9</t>
+          <t>45.4</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>44.8</t>
+          <t>44.55</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>44.8</t>
+          <t>45.05</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-0.95</t>
+          <t>-3.84</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>213.0</t>
+          <t>315.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>46.6</t>
+          <t>44.8</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3088,17 +3088,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-2.87</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>-1.31</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>26.53</t>
+          <t>-9.12</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3163,7 +3163,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-6.33</t>
+          <t>-9.95</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3173,17 +3173,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>7.32</t>
+          <t>10.83</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>-4.69</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3194,77 +3194,77 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>81</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>57.45</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>71.82</t>
+          <t>45.15</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-1.17</t>
+          <t>-3.92</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-2.88</t>
+          <t>-2.8</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>47.15</t>
+          <t>46.63</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>46.22</t>
+          <t>46.15</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>47.59</t>
+          <t>47.48</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>47.5</t>
+          <t>47.49</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>98.12</t>
+          <t>27.78</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-0.00</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3274,7 +3274,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-105.28</t>
+          <t>-104.94</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3284,46 +3284,46 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>76904.2962697274</t>
+          <t>76802.06088825215</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>9943.0</t>
+          <t>14336.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>18959.2</t>
+          <t>14123.0</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>14983.4</t>
+          <t>15541.1</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>17743.28</t>
+          <t>17446.4</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>3975</t>
+          <t>-1418</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-74.62310011749315</t>
+          <t>-30.07547477889878</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>220.1119243458033</t>
+          <t>214.9364645833703</t>
         </is>
       </c>
       <c r="BD7" t="n">
-        <v>9943</v>
+        <v>14336</v>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-4.41</t>
+          <t>-8.10</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3387,7 +3387,7 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3397,12 +3397,12 @@
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>1.89</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>6.11</t>
+          <t>6.1</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3412,7 +3412,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>10.23</t>
+          <t>10.24</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>42.08</t>
+          <t>42.67</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>4262</t>
+          <t>4267</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3452,22 +3452,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>47.15</t>
+          <t>46.9</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>47.2</t>
+          <t>46.9</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>46.4</t>
+          <t>44.8</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>46.6</t>
+          <t>44.8</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3499,12 +3499,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>-0.95</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>192.0</t>
+          <t>213.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>47.05</t>
+          <t>46.6</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3524,17 +3524,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-3.86</t>
+          <t>-2.76</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>-1.31</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>29.99</t>
+          <t>26.53</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-5.43</t>
+          <t>-6.33</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3609,17 +3609,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>6.60</t>
+          <t>7.32</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3630,77 +3630,77 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>81</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>57.45</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>71.82</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>-1.17</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-3.21</t>
+          <t>-2.88</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>47.23</t>
+          <t>47.15</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>46.15</t>
+          <t>46.22</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>47.68</t>
+          <t>47.59</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>47.48</t>
+          <t>47.5</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>100.64</t>
+          <t>98.12</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.00</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3710,7 +3710,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-106.58</t>
+          <t>-105.28</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3720,46 +3720,46 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>76904.2962697274</t>
+          <t>76802.06088825215</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>9018.0</t>
+          <t>9943.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>18831.4</t>
+          <t>18959.2</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>14486.8</t>
+          <t>14983.4</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>18676.0</t>
+          <t>17743.28</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>4344</t>
+          <t>3975</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-128.211286383547</t>
+          <t>-74.62310011749315</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>690.3228695655016</t>
+          <t>220.1119243458033</t>
         </is>
       </c>
       <c r="BD8" t="n">
-        <v>9018</v>
+        <v>9943</v>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3778,7 +3778,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-3.49</t>
+          <t>-4.41</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3828,17 +3828,17 @@
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>1.89</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>6.11</t>
+          <t>6.1</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3848,7 +3848,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>10.23</t>
+          <t>10.24</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>42.08</t>
+          <t>42.67</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>4262</t>
+          <t>4267</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3888,22 +3888,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>46.5</t>
+          <t>47.15</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>47.5</t>
+          <t>47.2</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>46.35</t>
+          <t>46.4</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>47.05</t>
+          <t>46.6</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3935,12 +3935,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-1.05</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>311.0</t>
+          <t>192.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3950,7 +3950,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>47.1</t>
+          <t>47.05</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3960,17 +3960,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-3.97</t>
+          <t>-3.75</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>-1.31</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>33.05</t>
+          <t>29.99</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4035,7 +4035,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-5.33</t>
+          <t>-5.43</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4045,17 +4045,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10.69</t>
+          <t>6.60</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-0.95</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4066,77 +4066,77 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>81</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>93.33</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>2.36</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-3.53</t>
+          <t>-3.21</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>0.60</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>47.15</t>
+          <t>47.23</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>46.06</t>
+          <t>46.15</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>47.75</t>
+          <t>47.68</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>47.47</t>
+          <t>47.48</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>89.68</t>
+          <t>100.64</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4146,7 +4146,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-108.23</t>
+          <t>-106.58</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4156,46 +4156,46 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>76904.2962697274</t>
+          <t>76802.06088825215</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>14718.0</t>
+          <t>9018.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>18629.2</t>
+          <t>18831.4</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>14001.9</t>
+          <t>14486.8</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>20406.5</t>
+          <t>18676.0</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>4627</t>
+          <t>4344</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-277.0356783742832</t>
+          <t>-128.211286383547</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>1436.505545966302</t>
+          <t>690.3228695655016</t>
         </is>
       </c>
       <c r="BD9" t="n">
-        <v>14718</v>
+        <v>9018</v>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4214,7 +4214,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-3.38</t>
+          <t>-3.49</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4264,7 +4264,7 @@
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
@@ -4274,7 +4274,7 @@
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>6.11</t>
+          <t>6.1</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4284,7 +4284,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>10.23</t>
+          <t>10.24</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4299,12 +4299,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>42.08</t>
+          <t>42.67</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>4262</t>
+          <t>4267</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4324,22 +4324,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>47.6</t>
+          <t>46.5</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>47.8</t>
+          <t>47.5</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>46.85</t>
+          <t>46.35</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>47.1</t>
+          <t>47.05</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4371,12 +4371,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>-1.05</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>474.0</t>
+          <t>311.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4386,7 +4386,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>47.6</t>
+          <t>47.1</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4396,17 +4396,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-5.08</t>
+          <t>-3.86</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>-1.31</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>50.85</t>
+          <t>33.05</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4471,7 +4471,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-4.32</t>
+          <t>-5.33</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4481,17 +4481,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16.30</t>
+          <t>10.69</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-0.95</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4502,77 +4502,77 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>81</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>93.33</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>2.67</t>
+          <t>2.36</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-3.93</t>
+          <t>-3.53</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.60</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>47.13</t>
+          <t>47.15</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>45.9</t>
+          <t>46.06</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>47.78</t>
+          <t>47.75</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>47.45</t>
+          <t>47.47</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>79.21</t>
+          <t>89.68</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4582,7 +4582,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-110.08</t>
+          <t>-108.23</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4592,46 +4592,46 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>76904.2962697274</t>
+          <t>76802.06088825215</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>22600.0</t>
+          <t>14718.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>20034.4</t>
+          <t>18629.2</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>13280.9</t>
+          <t>14001.9</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>20741.92</t>
+          <t>20406.5</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>6753</t>
+          <t>4627</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-588.5886282543895</t>
+          <t>-277.0356783742832</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>1840.462742754364</t>
+          <t>1436.505545966302</t>
         </is>
       </c>
       <c r="BD10" t="n">
-        <v>22600</v>
+        <v>14718</v>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4650,7 +4650,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-2.36</t>
+          <t>-3.38</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4695,7 +4695,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4705,12 +4705,12 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>6.11</t>
+          <t>6.1</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4720,7 +4720,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>10.23</t>
+          <t>10.24</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4735,12 +4735,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>42.08</t>
+          <t>42.67</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>4262</t>
+          <t>4267</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4760,22 +4760,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>47.85</t>
+          <t>47.6</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>48.1</t>
+          <t>47.8</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>47.25</t>
+          <t>46.85</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>47.6</t>
+          <t>47.1</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4807,12 +4807,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>812.0</t>
+          <t>474.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4822,7 +4822,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>47.4</t>
+          <t>47.6</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4832,17 +4832,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-4.64</t>
+          <t>-4.96</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>-1.31</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>43.35</t>
+          <t>50.85</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-4.72</t>
+          <t>-4.32</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4917,17 +4917,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>27.92</t>
+          <t>16.30</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4938,12 +4938,12 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>81</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
@@ -4953,62 +4953,62 @@
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>93.86</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>2.67</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-4.23</t>
+          <t>-3.93</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>46.66</t>
+          <t>47.13</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>45.74</t>
+          <t>45.9</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>47.76</t>
+          <t>47.78</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>47.42</t>
+          <t>47.45</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>59.88</t>
+          <t>79.21</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -5018,7 +5018,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-112.07</t>
+          <t>-110.08</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -5028,46 +5028,46 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>76904.2962697274</t>
+          <t>76802.06088825215</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>38517.0</t>
+          <t>22600.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>16959.2</t>
+          <t>20034.4</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>11830.5</t>
+          <t>13280.9</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>20783.02</t>
+          <t>20741.92</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>5128</t>
+          <t>6753</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-1030.234332074163</t>
+          <t>-588.5886282543895</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>1507.31364021037</t>
+          <t>1840.462742754364</t>
         </is>
       </c>
       <c r="BD11" t="n">
-        <v>38517</v>
+        <v>22600</v>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5086,7 +5086,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-2.77</t>
+          <t>-2.36</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5131,7 +5131,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>6.11</t>
+          <t>6.1</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5156,7 +5156,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>10.23</t>
+          <t>10.24</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5171,12 +5171,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>42.08</t>
+          <t>42.67</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>4262</t>
+          <t>4267</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5196,22 +5196,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>47.5</t>
+          <t>47.85</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>47.85</t>
+          <t>48.1</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>46.5</t>
+          <t>47.25</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>47.4</t>
+          <t>47.6</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5243,12 +5243,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>199.0</t>
+          <t>812.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5258,7 +5258,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>47.0</t>
+          <t>47.4</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5268,17 +5268,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-3.75</t>
+          <t>-4.52</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>-1.31</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>32.28</t>
+          <t>43.35</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5343,7 +5343,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-5.53</t>
+          <t>-4.72</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5353,17 +5353,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>6.84</t>
+          <t>27.92</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5374,12 +5374,12 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>81</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
@@ -5394,57 +5394,57 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-4.34</t>
+          <t>-4.23</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>46.2</t>
+          <t>46.66</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>45.67</t>
+          <t>45.74</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>47.75</t>
+          <t>47.76</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>47.39</t>
+          <t>47.42</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>43.77</t>
+          <t>59.88</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5454,7 +5454,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-113.88</t>
+          <t>-112.07</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5464,46 +5464,46 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>76904.2962697274</t>
+          <t>76802.06088825215</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>9304.0</t>
+          <t>38517.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>11007.6</t>
+          <t>16959.2</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>8321.2</t>
+          <t>11830.5</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>21296.56</t>
+          <t>20783.02</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>2686</t>
+          <t>5128</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-1491.606690671351</t>
+          <t>-1030.234332074163</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-727.839136288565</t>
+          <t>1507.31364021037</t>
         </is>
       </c>
       <c r="BD12" t="n">
-        <v>9304</v>
+        <v>38517</v>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5522,7 +5522,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-3.59</t>
+          <t>-2.77</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5567,7 +5567,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>6.11</t>
+          <t>6.1</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5592,7 +5592,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>10.23</t>
+          <t>10.24</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5607,12 +5607,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>42.08</t>
+          <t>42.67</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>4262</t>
+          <t>4267</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5632,22 +5632,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>46.85</t>
+          <t>47.5</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>47.1</t>
+          <t>47.85</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>46.25</t>
+          <t>46.5</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>47.0</t>
+          <t>47.4</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/PET膜.xlsx
+++ b/Result/checksun_type/PET膜.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>148.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>45.35</t>
+          <t>45.8</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-1.31</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-48.83</t>
+          <t>-34.26</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-8.84</t>
+          <t>-7.94</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>2.79</t>
+          <t>5.09</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-1.32</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,47 +1014,47 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>148</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>25.53</t>
+          <t>45.65</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>14.94</t>
+          <t>30.16</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-1.67</t>
+          <t>-1.35</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-2.0</t>
+          <t>-1.85</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-1.30</t>
+          <t>-1.48</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>45.2</t>
+          <t>45.35</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
@@ -1064,27 +1064,27 @@
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>46.91</t>
+          <t>46.84</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>47.52</t>
+          <t>47.54</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-28.10</t>
+          <t>-12.73</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-107.09</t>
+          <t>-107.33</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1104,46 +1104,46 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>76802.06088825215</t>
+          <t>76706.66738197426</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>3696.0</t>
+          <t>6748.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>4856.0</t>
+          <t>5196.4</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>9489.5</t>
+          <t>7904.3</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>14335.48</t>
+          <t>13455.3</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-4633</t>
+          <t>-2707</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-722.5223305920491</t>
+          <t>-844.6790150359823</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-1641.303098617845</t>
+          <t>-1516.540779477615</t>
         </is>
       </c>
       <c r="BD2" t="n">
-        <v>3696</v>
+        <v>6748</v>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-6.97</t>
+          <t>-6.05</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
@@ -1207,7 +1207,7 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1217,12 +1217,12 @@
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>6.1</t>
+          <t>6.04</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>10.24</t>
+          <t>10.34</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1247,12 +1247,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>42.67</t>
+          <t>43.25</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>4267</t>
+          <t>4309</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1272,22 +1272,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>46.0</t>
+          <t>45.45</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>46.0</t>
+          <t>46.15</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>45.3</t>
+          <t>45.35</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>45.35</t>
+          <t>45.8</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1319,12 +1319,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>98.0</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>45.3</t>
+          <t>45.35</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1344,17 +1344,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-1.31</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-46.16</t>
+          <t>-48.83</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1419,7 +1419,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-8.94</t>
+          <t>-8.84</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1429,17 +1429,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>3.37</t>
+          <t>2.79</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>-1.32</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1450,77 +1450,77 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>148</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>19.3</t>
+          <t>25.53</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>15.36</t>
+          <t>14.94</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>0.33</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-1.96</t>
+          <t>-1.67</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-2.17</t>
+          <t>-2.0</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-1.05</t>
+          <t>-1.30</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>45.09</t>
+          <t>45.2</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>45.99</t>
+          <t>45.97</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>47.02</t>
+          <t>46.91</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>47.51</t>
+          <t>47.52</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-35.53</t>
+          <t>-28.10</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-106.59</t>
+          <t>-107.09</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1540,46 +1540,46 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>76802.06088825215</t>
+          <t>76706.66738197426</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>4408.0</t>
+          <t>3696.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>6984.0</t>
+          <t>4856.0</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>12971.6</t>
+          <t>9489.5</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>15065.26</t>
+          <t>14335.48</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-5987</t>
+          <t>-4633</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-555.4712818600863</t>
+          <t>-722.5223305920491</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-1433.917015296107</t>
+          <t>-1641.303098617845</t>
         </is>
       </c>
       <c r="BD3" t="n">
-        <v>4408</v>
+        <v>3696</v>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-7.08</t>
+          <t>-6.97</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1623,7 +1623,7 @@
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
@@ -1643,7 +1643,7 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>6.1</t>
+          <t>6.04</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1668,7 +1668,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>10.24</t>
+          <t>10.34</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1683,12 +1683,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>42.67</t>
+          <t>43.25</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>4267</t>
+          <t>4309</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1708,22 +1708,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>44.95</t>
+          <t>46.0</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>45.45</t>
+          <t>46.0</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>44.9</t>
+          <t>45.3</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>45.3</t>
+          <t>45.35</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1755,12 +1755,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-1.77</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>177.0</t>
+          <t>98.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1770,7 +1770,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>44.75</t>
+          <t>45.3</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1780,17 +1780,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-1.31</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-39.89</t>
+          <t>-46.16</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1855,7 +1855,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-10.05</t>
+          <t>-8.94</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1865,17 +1865,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>6.09</t>
+          <t>3.37</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1886,77 +1886,77 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>148</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>19.3</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>11.9</t>
+          <t>15.36</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-1.32</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-1.47</t>
+          <t>-1.96</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-2.34</t>
+          <t>-2.17</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>-1.05</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>45.35</t>
+          <t>45.09</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>46.03</t>
+          <t>45.99</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>47.13</t>
+          <t>47.02</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>47.5</t>
+          <t>47.51</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-41.45</t>
+          <t>-35.53</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-0.36</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-106.01</t>
+          <t>-106.59</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1976,46 +1976,46 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>76802.06088825215</t>
+          <t>76706.66738197426</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>7926.0</t>
+          <t>4408.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>8091.0</t>
+          <t>6984.0</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>13461.2</t>
+          <t>12971.6</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>15558.56</t>
+          <t>15065.26</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-5370</t>
+          <t>-5987</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-395.7538757808097</t>
+          <t>-555.4712818600863</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-1162.725574290193</t>
+          <t>-1433.917015296107</t>
         </is>
       </c>
       <c r="BD4" t="n">
-        <v>7926</v>
+        <v>4408</v>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2034,7 +2034,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-8.21</t>
+          <t>-7.08</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2059,7 +2059,7 @@
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
@@ -2079,7 +2079,7 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2089,12 +2089,12 @@
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>1.84</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>6.1</t>
+          <t>6.04</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2104,7 +2104,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>10.24</t>
+          <t>10.34</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>42.67</t>
+          <t>43.25</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>4267</t>
+          <t>4309</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2144,22 +2144,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>45.2</t>
+          <t>44.95</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>45.2</t>
+          <t>45.45</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>44.6</t>
+          <t>44.9</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>44.75</t>
+          <t>45.3</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>-1.77</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>177.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2206,7 +2206,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>45.55</t>
+          <t>44.75</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2216,17 +2216,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-1.31</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-38.31</t>
+          <t>-39.89</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2291,7 +2291,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-8.44</t>
+          <t>-10.05</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2301,17 +2301,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>2.41</t>
+          <t>6.09</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-0.98</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2322,17 +2322,17 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>148</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>26.79</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
@@ -2342,37 +2342,37 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>-1.32</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>-1.47</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-2.47</t>
+          <t>-2.34</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-0.50</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>45.81</t>
+          <t>45.35</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>46.09</t>
+          <t>46.03</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>47.26</t>
+          <t>47.13</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
@@ -2382,17 +2382,17 @@
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-20.83</t>
+          <t>-41.45</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>-0.36</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2402,7 +2402,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-105.39</t>
+          <t>-106.01</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2412,46 +2412,46 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>76802.06088825215</t>
+          <t>76706.66738197426</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>3204.0</t>
+          <t>7926.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>8309.4</t>
+          <t>8091.0</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>13469.3</t>
+          <t>13461.2</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>16218.6</t>
+          <t>15558.56</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-5159</t>
+          <t>-5370</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-256.304476051831</t>
+          <t>-395.7538757808097</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-1110.711888057096</t>
+          <t>-1162.725574290193</t>
         </is>
       </c>
       <c r="BD5" t="n">
-        <v>3204</v>
+        <v>7926</v>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-6.56</t>
+          <t>-8.21</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2495,7 +2495,7 @@
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
@@ -2515,7 +2515,7 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2525,12 +2525,12 @@
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>6.1</t>
+          <t>6.04</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2540,7 +2540,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>10.24</t>
+          <t>10.34</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2555,12 +2555,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>42.67</t>
+          <t>43.25</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>4267</t>
+          <t>4309</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2580,22 +2580,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>45.4</t>
+          <t>45.2</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>46.25</t>
+          <t>45.2</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>45.3</t>
+          <t>44.6</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>45.55</t>
+          <t>44.75</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>112.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2642,7 +2642,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>45.05</t>
+          <t>45.55</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2652,17 +2652,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-1.31</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-30.74</t>
+          <t>-38.31</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2727,7 +2727,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-9.45</t>
+          <t>-8.44</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2737,17 +2737,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>3.85</t>
+          <t>2.41</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2758,77 +2758,77 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>148</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>8.93</t>
+          <t>26.79</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>22.13</t>
+          <t>11.9</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-2.32</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-2.65</t>
+          <t>-2.47</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.50</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>46.12</t>
+          <t>45.81</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>46.12</t>
+          <t>46.09</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>47.37</t>
+          <t>47.26</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>47.49</t>
+          <t>47.5</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-13.12</t>
+          <t>-20.83</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2838,7 +2838,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-105.11</t>
+          <t>-105.39</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2848,46 +2848,46 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>76802.06088825215</t>
+          <t>76706.66738197426</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>5046.0</t>
+          <t>3204.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>10612.2</t>
+          <t>8309.4</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>15323.3</t>
+          <t>13469.3</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>16780.18</t>
+          <t>16218.6</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-4711</t>
+          <t>-5159</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-100.9576738690555</t>
+          <t>-256.304476051831</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-490.8097688649177</t>
+          <t>-1110.711888057096</t>
         </is>
       </c>
       <c r="BD6" t="n">
-        <v>5046</v>
+        <v>3204</v>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-7.59</t>
+          <t>-6.56</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
@@ -2951,7 +2951,7 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>6.1</t>
+          <t>6.04</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2976,7 +2976,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>10.24</t>
+          <t>10.34</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2991,12 +2991,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>42.67</t>
+          <t>43.25</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>4267</t>
+          <t>4309</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -3016,22 +3016,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>44.55</t>
+          <t>45.4</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>45.4</t>
+          <t>46.25</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>44.55</t>
+          <t>45.3</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>45.05</t>
+          <t>45.55</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-3.84</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>315.0</t>
+          <t>112.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>44.8</t>
+          <t>45.05</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3088,17 +3088,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-1.31</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-9.12</t>
+          <t>-30.74</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3163,7 +3163,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-9.95</t>
+          <t>-9.45</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3173,17 +3173,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10.83</t>
+          <t>3.85</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-4.69</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3194,182 +3194,182 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>148</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>8.93</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>45.15</t>
+          <t>22.13</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-3.92</t>
+          <t>-2.32</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>-2.65</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>-0.25</t>
+        </is>
+      </c>
+      <c r="AL7" t="inlineStr">
+        <is>
+          <t>46.12</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>46.12</t>
+        </is>
+      </c>
+      <c r="AN7" t="inlineStr">
+        <is>
+          <t>47.37</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>47.49</t>
+        </is>
+      </c>
+      <c r="AP7" t="inlineStr">
+        <is>
+          <t>-13.12</t>
+        </is>
+      </c>
+      <c r="AQ7" t="inlineStr">
+        <is>
+          <t>-0.25</t>
+        </is>
+      </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>-0.22</t>
+        </is>
+      </c>
+      <c r="AS7" t="inlineStr">
+        <is>
+          <t>4.28</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr">
+        <is>
+          <t>-105.11</t>
+        </is>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
+          <t>2025/10/28</t>
+        </is>
+      </c>
+      <c r="AV7" t="inlineStr">
+        <is>
+          <t>76706.66738197426</t>
+        </is>
+      </c>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>5046.0</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>10612.2</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>15323.3</t>
+        </is>
+      </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>16780.18</t>
+        </is>
+      </c>
+      <c r="BA7" t="inlineStr">
+        <is>
+          <t>-4711</t>
+        </is>
+      </c>
+      <c r="BB7" t="inlineStr">
+        <is>
+          <t>-100.9576738690555</t>
+        </is>
+      </c>
+      <c r="BC7" t="inlineStr">
+        <is>
+          <t>-490.8097688649177</t>
+        </is>
+      </c>
+      <c r="BD7" t="n">
+        <v>5046</v>
+      </c>
+      <c r="BE7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF7" t="inlineStr">
+        <is>
+          <t>48.75</t>
+        </is>
+      </c>
+      <c r="BG7" t="inlineStr">
+        <is>
+          <t>2025/08/25</t>
+        </is>
+      </c>
+      <c r="BH7" t="inlineStr">
+        <is>
+          <t>-7.59</t>
+        </is>
+      </c>
+      <c r="BI7" t="inlineStr">
+        <is>
+          <t>岱稜</t>
+        </is>
+      </c>
+      <c r="BJ7" t="inlineStr">
+        <is>
+          <t>岱稜</t>
+        </is>
+      </c>
+      <c r="BK7" t="inlineStr">
+        <is>
+          <t>其他電子業</t>
+        </is>
+      </c>
+      <c r="BL7" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BM7" t="inlineStr">
+        <is>
           <t>1.04</t>
         </is>
       </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>-2.8</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>-0.03</t>
-        </is>
-      </c>
-      <c r="AL7" t="inlineStr">
-        <is>
-          <t>46.63</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>46.15</t>
-        </is>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>47.48</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>47.49</t>
-        </is>
-      </c>
-      <c r="AP7" t="inlineStr">
-        <is>
-          <t>27.78</t>
-        </is>
-      </c>
-      <c r="AQ7" t="inlineStr">
-        <is>
-          <t>-0.15</t>
-        </is>
-      </c>
-      <c r="AR7" t="inlineStr">
-        <is>
-          <t>-0.21</t>
-        </is>
-      </c>
-      <c r="AS7" t="inlineStr">
-        <is>
-          <t>4.28</t>
-        </is>
-      </c>
-      <c r="AT7" t="inlineStr">
-        <is>
-          <t>-104.94</t>
-        </is>
-      </c>
-      <c r="AU7" t="inlineStr">
-        <is>
-          <t>2025/10/28</t>
-        </is>
-      </c>
-      <c r="AV7" t="inlineStr">
-        <is>
-          <t>76802.06088825215</t>
-        </is>
-      </c>
-      <c r="AW7" t="inlineStr">
-        <is>
-          <t>14336.0</t>
-        </is>
-      </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>14123.0</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr">
-        <is>
-          <t>15541.1</t>
-        </is>
-      </c>
-      <c r="AZ7" t="inlineStr">
-        <is>
-          <t>17446.4</t>
-        </is>
-      </c>
-      <c r="BA7" t="inlineStr">
-        <is>
-          <t>-1418</t>
-        </is>
-      </c>
-      <c r="BB7" t="inlineStr">
-        <is>
-          <t>-30.07547477889878</t>
-        </is>
-      </c>
-      <c r="BC7" t="inlineStr">
-        <is>
-          <t>214.9364645833703</t>
-        </is>
-      </c>
-      <c r="BD7" t="n">
-        <v>14336</v>
-      </c>
-      <c r="BE7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF7" t="inlineStr">
-        <is>
-          <t>48.75</t>
-        </is>
-      </c>
-      <c r="BG7" t="inlineStr">
-        <is>
-          <t>2025/08/25</t>
-        </is>
-      </c>
-      <c r="BH7" t="inlineStr">
-        <is>
-          <t>-8.10</t>
-        </is>
-      </c>
-      <c r="BI7" t="inlineStr">
-        <is>
-          <t>岱稜</t>
-        </is>
-      </c>
-      <c r="BJ7" t="inlineStr">
-        <is>
-          <t>岱稜</t>
-        </is>
-      </c>
-      <c r="BK7" t="inlineStr">
-        <is>
-          <t>其他電子業</t>
-        </is>
-      </c>
-      <c r="BL7" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BM7" t="inlineStr">
-        <is>
-          <t>1.05</t>
-        </is>
-      </c>
       <c r="BN7" t="inlineStr">
         <is>
           <t>-1.004452687200723</t>
@@ -3387,7 +3387,7 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3397,12 +3397,12 @@
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>6.1</t>
+          <t>6.04</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3412,7 +3412,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>10.24</t>
+          <t>10.34</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>42.67</t>
+          <t>43.25</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>4267</t>
+          <t>4309</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3452,22 +3452,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>46.9</t>
+          <t>44.55</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>46.9</t>
+          <t>45.4</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>44.8</t>
+          <t>44.55</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>44.8</t>
+          <t>45.05</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3499,12 +3499,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-0.95</t>
+          <t>-3.84</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>213.0</t>
+          <t>315.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>46.6</t>
+          <t>44.8</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3524,17 +3524,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-2.76</t>
+          <t>2.18</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-1.31</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>26.53</t>
+          <t>-9.12</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-6.33</t>
+          <t>-9.95</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3609,17 +3609,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>7.32</t>
+          <t>10.83</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>-4.69</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3630,77 +3630,77 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>148</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>57.45</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>71.82</t>
+          <t>45.15</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-1.17</t>
+          <t>-3.92</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-2.88</t>
+          <t>-2.8</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>47.15</t>
+          <t>46.63</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>46.22</t>
+          <t>46.15</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>47.59</t>
+          <t>47.48</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>47.5</t>
+          <t>47.49</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>98.12</t>
+          <t>27.78</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-0.00</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3710,7 +3710,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-105.28</t>
+          <t>-104.94</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3720,46 +3720,46 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>76802.06088825215</t>
+          <t>76706.66738197426</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>9943.0</t>
+          <t>14336.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>18959.2</t>
+          <t>14123.0</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>14983.4</t>
+          <t>15541.1</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>17743.28</t>
+          <t>17446.4</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>3975</t>
+          <t>-1418</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-74.62310011749315</t>
+          <t>-30.07547477889878</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>220.1119243458033</t>
+          <t>214.9364645833703</t>
         </is>
       </c>
       <c r="BD8" t="n">
-        <v>9943</v>
+        <v>14336</v>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3778,7 +3778,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-4.41</t>
+          <t>-8.10</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3803,7 +3803,7 @@
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
@@ -3823,7 +3823,7 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -3833,12 +3833,12 @@
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>1.89</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>6.1</t>
+          <t>6.04</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3848,7 +3848,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>10.24</t>
+          <t>10.34</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>42.67</t>
+          <t>43.25</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>4267</t>
+          <t>4309</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3888,22 +3888,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>47.15</t>
+          <t>46.9</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>47.2</t>
+          <t>46.9</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>46.4</t>
+          <t>44.8</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>46.6</t>
+          <t>44.8</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3935,12 +3935,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>-0.95</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>192.0</t>
+          <t>213.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3950,7 +3950,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>47.05</t>
+          <t>46.6</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3960,17 +3960,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-3.75</t>
+          <t>-1.75</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-1.31</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>29.99</t>
+          <t>26.53</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4035,7 +4035,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-5.43</t>
+          <t>-6.33</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4045,17 +4045,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>6.60</t>
+          <t>7.32</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4066,77 +4066,77 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>148</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>57.45</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>71.82</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>-1.17</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-3.21</t>
+          <t>-2.88</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>47.23</t>
+          <t>47.15</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>46.15</t>
+          <t>46.22</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>47.68</t>
+          <t>47.59</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>47.48</t>
+          <t>47.5</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>100.64</t>
+          <t>98.12</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.00</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4146,7 +4146,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-106.58</t>
+          <t>-105.28</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4156,46 +4156,46 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>76802.06088825215</t>
+          <t>76706.66738197426</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>9018.0</t>
+          <t>9943.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>18831.4</t>
+          <t>18959.2</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>14486.8</t>
+          <t>14983.4</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>18676.0</t>
+          <t>17743.28</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>4344</t>
+          <t>3975</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-128.211286383547</t>
+          <t>-74.62310011749315</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>690.3228695655016</t>
+          <t>220.1119243458033</t>
         </is>
       </c>
       <c r="BD9" t="n">
-        <v>9018</v>
+        <v>9943</v>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4214,7 +4214,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-3.49</t>
+          <t>-4.41</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
@@ -4264,17 +4264,17 @@
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>1.89</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>6.1</t>
+          <t>6.04</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4284,7 +4284,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>10.24</t>
+          <t>10.34</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4299,12 +4299,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>42.67</t>
+          <t>43.25</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>4267</t>
+          <t>4309</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4324,22 +4324,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>46.5</t>
+          <t>47.15</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>47.5</t>
+          <t>47.2</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>46.35</t>
+          <t>46.4</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>47.05</t>
+          <t>46.6</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4371,12 +4371,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-1.05</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>311.0</t>
+          <t>192.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4386,7 +4386,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>47.1</t>
+          <t>47.05</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4396,17 +4396,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-3.86</t>
+          <t>-2.73</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-1.31</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>33.05</t>
+          <t>29.99</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4471,7 +4471,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-5.33</t>
+          <t>-5.43</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4481,17 +4481,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10.69</t>
+          <t>6.60</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-0.95</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4502,77 +4502,77 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>148</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>93.33</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>2.36</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-3.53</t>
+          <t>-3.21</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>0.60</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>47.15</t>
+          <t>47.23</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>46.06</t>
+          <t>46.15</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>47.75</t>
+          <t>47.68</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>47.47</t>
+          <t>47.48</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>89.68</t>
+          <t>100.64</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4582,7 +4582,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-108.23</t>
+          <t>-106.58</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4592,46 +4592,46 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>76802.06088825215</t>
+          <t>76706.66738197426</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>14718.0</t>
+          <t>9018.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>18629.2</t>
+          <t>18831.4</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>14001.9</t>
+          <t>14486.8</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>20406.5</t>
+          <t>18676.0</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>4627</t>
+          <t>4344</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-277.0356783742832</t>
+          <t>-128.211286383547</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>1436.505545966302</t>
+          <t>690.3228695655016</t>
         </is>
       </c>
       <c r="BD10" t="n">
-        <v>14718</v>
+        <v>9018</v>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4650,7 +4650,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-3.38</t>
+          <t>-3.49</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4675,7 +4675,7 @@
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
@@ -4710,7 +4710,7 @@
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>6.1</t>
+          <t>6.04</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4720,7 +4720,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>10.24</t>
+          <t>10.34</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4735,12 +4735,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>42.67</t>
+          <t>43.25</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>4267</t>
+          <t>4309</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4760,22 +4760,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>47.6</t>
+          <t>46.5</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>47.8</t>
+          <t>47.5</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>46.85</t>
+          <t>46.35</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>47.1</t>
+          <t>47.05</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4807,12 +4807,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>-1.05</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>474.0</t>
+          <t>311.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4822,7 +4822,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>47.6</t>
+          <t>47.1</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4832,17 +4832,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-4.96</t>
+          <t>-2.84</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-1.31</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>50.85</t>
+          <t>33.05</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-4.32</t>
+          <t>-5.33</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4917,17 +4917,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16.30</t>
+          <t>10.69</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-0.95</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4938,77 +4938,77 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>148</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>93.33</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>2.67</t>
+          <t>2.36</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-3.93</t>
+          <t>-3.53</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.60</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>47.13</t>
+          <t>47.15</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>45.9</t>
+          <t>46.06</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>47.78</t>
+          <t>47.75</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>47.45</t>
+          <t>47.47</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>79.21</t>
+          <t>89.68</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -5018,7 +5018,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-110.08</t>
+          <t>-108.23</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -5028,46 +5028,46 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>76802.06088825215</t>
+          <t>76706.66738197426</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>22600.0</t>
+          <t>14718.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>20034.4</t>
+          <t>18629.2</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>13280.9</t>
+          <t>14001.9</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>20741.92</t>
+          <t>20406.5</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>6753</t>
+          <t>4627</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-588.5886282543895</t>
+          <t>-277.0356783742832</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>1840.462742754364</t>
+          <t>1436.505545966302</t>
         </is>
       </c>
       <c r="BD11" t="n">
-        <v>22600</v>
+        <v>14718</v>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5086,7 +5086,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-2.36</t>
+          <t>-3.38</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5111,7 +5111,7 @@
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
@@ -5131,7 +5131,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>6.1</t>
+          <t>6.04</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5156,7 +5156,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>10.24</t>
+          <t>10.34</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5171,12 +5171,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>42.67</t>
+          <t>43.25</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>4267</t>
+          <t>4309</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5196,22 +5196,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>47.85</t>
+          <t>47.6</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>48.1</t>
+          <t>47.8</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>47.25</t>
+          <t>46.85</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>47.6</t>
+          <t>47.1</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5243,12 +5243,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>812.0</t>
+          <t>474.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5258,7 +5258,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>47.4</t>
+          <t>47.6</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5268,17 +5268,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-4.52</t>
+          <t>-3.93</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-1.31</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>43.35</t>
+          <t>50.85</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5343,7 +5343,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-4.72</t>
+          <t>-4.32</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5353,17 +5353,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>27.92</t>
+          <t>16.30</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5374,12 +5374,12 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>148</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
@@ -5389,62 +5389,62 @@
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>93.86</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>2.67</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-4.23</t>
+          <t>-3.93</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>46.66</t>
+          <t>47.13</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>45.74</t>
+          <t>45.9</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>47.76</t>
+          <t>47.78</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>47.42</t>
+          <t>47.45</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>59.88</t>
+          <t>79.21</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5454,7 +5454,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-112.07</t>
+          <t>-110.08</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5464,46 +5464,46 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>76802.06088825215</t>
+          <t>76706.66738197426</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>38517.0</t>
+          <t>22600.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>16959.2</t>
+          <t>20034.4</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>11830.5</t>
+          <t>13280.9</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>20783.02</t>
+          <t>20741.92</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>5128</t>
+          <t>6753</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-1030.234332074163</t>
+          <t>-588.5886282543895</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>1507.31364021037</t>
+          <t>1840.462742754364</t>
         </is>
       </c>
       <c r="BD12" t="n">
-        <v>38517</v>
+        <v>22600</v>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5522,7 +5522,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-2.77</t>
+          <t>-2.36</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5547,7 +5547,7 @@
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
@@ -5567,7 +5567,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>6.1</t>
+          <t>6.04</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5592,7 +5592,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>10.24</t>
+          <t>10.34</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5607,12 +5607,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>42.67</t>
+          <t>43.25</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>4267</t>
+          <t>4309</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5632,22 +5632,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>47.5</t>
+          <t>47.85</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>47.85</t>
+          <t>48.1</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>46.5</t>
+          <t>47.25</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>47.4</t>
+          <t>47.6</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/PET膜.xlsx
+++ b/Result/checksun_type/PET膜.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1057,15 +1057,11 @@
           <t>45.35</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>45.97</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>46.84</t>
-        </is>
+      <c r="AM2" t="n">
+        <v>45.97</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>46.84</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
@@ -1112,20 +1108,16 @@
           <t>6748.0</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>5196.4</t>
-        </is>
+      <c r="AX2" t="n">
+        <v>5196.4</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
           <t>7904.3</t>
         </is>
       </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>13455.3</t>
-        </is>
+      <c r="AZ2" t="n">
+        <v>13455.3</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
@@ -1142,8 +1134,10 @@
           <t>-1516.540779477615</t>
         </is>
       </c>
-      <c r="BD2" t="n">
-        <v>6748</v>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>6748.0</t>
+        </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1309,7 +1303,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1493,15 +1487,11 @@
           <t>45.2</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>45.97</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>46.91</t>
-        </is>
+      <c r="AM3" t="n">
+        <v>45.97</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>46.91</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
@@ -1548,20 +1538,16 @@
           <t>3696.0</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>4856.0</t>
-        </is>
+      <c r="AX3" t="n">
+        <v>4856</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
           <t>9489.5</t>
         </is>
       </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>14335.48</t>
-        </is>
+      <c r="AZ3" t="n">
+        <v>14335.48</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
@@ -1578,8 +1564,10 @@
           <t>-1641.303098617845</t>
         </is>
       </c>
-      <c r="BD3" t="n">
-        <v>3696</v>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>3696.0</t>
+        </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1745,7 +1733,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1929,15 +1917,11 @@
           <t>45.09</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>45.99</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>47.02</t>
-        </is>
+      <c r="AM4" t="n">
+        <v>45.99</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>47.02</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
@@ -1984,20 +1968,16 @@
           <t>4408.0</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>6984.0</t>
-        </is>
+      <c r="AX4" t="n">
+        <v>6984</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
           <t>12971.6</t>
         </is>
       </c>
-      <c r="AZ4" t="inlineStr">
-        <is>
-          <t>15065.26</t>
-        </is>
+      <c r="AZ4" t="n">
+        <v>15065.26</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
@@ -2014,8 +1994,10 @@
           <t>-1433.917015296107</t>
         </is>
       </c>
-      <c r="BD4" t="n">
-        <v>4408</v>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>4408.0</t>
+        </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2181,7 +2163,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2365,15 +2347,11 @@
           <t>45.35</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>46.03</t>
-        </is>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>47.13</t>
-        </is>
+      <c r="AM5" t="n">
+        <v>46.03</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>47.13</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
@@ -2420,20 +2398,16 @@
           <t>7926.0</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>8091.0</t>
-        </is>
+      <c r="AX5" t="n">
+        <v>8091</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
           <t>13461.2</t>
         </is>
       </c>
-      <c r="AZ5" t="inlineStr">
-        <is>
-          <t>15558.56</t>
-        </is>
+      <c r="AZ5" t="n">
+        <v>15558.56</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
@@ -2450,8 +2424,10 @@
           <t>-1162.725574290193</t>
         </is>
       </c>
-      <c r="BD5" t="n">
-        <v>7926</v>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>7926.0</t>
+        </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2617,7 +2593,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2801,15 +2777,11 @@
           <t>45.81</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>46.09</t>
-        </is>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>47.26</t>
-        </is>
+      <c r="AM6" t="n">
+        <v>46.09</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>47.26</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
@@ -2856,20 +2828,16 @@
           <t>3204.0</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>8309.4</t>
-        </is>
+      <c r="AX6" t="n">
+        <v>8309.4</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
           <t>13469.3</t>
         </is>
       </c>
-      <c r="AZ6" t="inlineStr">
-        <is>
-          <t>16218.6</t>
-        </is>
+      <c r="AZ6" t="n">
+        <v>16218.6</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
@@ -2886,8 +2854,10 @@
           <t>-1110.711888057096</t>
         </is>
       </c>
-      <c r="BD6" t="n">
-        <v>3204</v>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>3204.0</t>
+        </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -3053,7 +3023,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3237,15 +3207,11 @@
           <t>46.12</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>46.12</t>
-        </is>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>47.37</t>
-        </is>
+      <c r="AM7" t="n">
+        <v>46.12</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>47.37</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
@@ -3292,20 +3258,16 @@
           <t>5046.0</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>10612.2</t>
-        </is>
+      <c r="AX7" t="n">
+        <v>10612.2</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
           <t>15323.3</t>
         </is>
       </c>
-      <c r="AZ7" t="inlineStr">
-        <is>
-          <t>16780.18</t>
-        </is>
+      <c r="AZ7" t="n">
+        <v>16780.18</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
@@ -3322,8 +3284,10 @@
           <t>-490.8097688649177</t>
         </is>
       </c>
-      <c r="BD7" t="n">
-        <v>5046</v>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>5046.0</t>
+        </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3489,7 +3453,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3673,15 +3637,11 @@
           <t>46.63</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>46.15</t>
-        </is>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>47.48</t>
-        </is>
+      <c r="AM8" t="n">
+        <v>46.15</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>47.48</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
@@ -3728,20 +3688,16 @@
           <t>14336.0</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>14123.0</t>
-        </is>
+      <c r="AX8" t="n">
+        <v>14123</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
           <t>15541.1</t>
         </is>
       </c>
-      <c r="AZ8" t="inlineStr">
-        <is>
-          <t>17446.4</t>
-        </is>
+      <c r="AZ8" t="n">
+        <v>17446.4</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
@@ -3758,8 +3714,10 @@
           <t>214.9364645833703</t>
         </is>
       </c>
-      <c r="BD8" t="n">
-        <v>14336</v>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>14336.0</t>
+        </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3925,7 +3883,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4109,15 +4067,11 @@
           <t>47.15</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>46.22</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>47.59</t>
-        </is>
+      <c r="AM9" t="n">
+        <v>46.22</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>47.59</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
@@ -4164,20 +4118,16 @@
           <t>9943.0</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>18959.2</t>
-        </is>
+      <c r="AX9" t="n">
+        <v>18959.2</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
           <t>14983.4</t>
         </is>
       </c>
-      <c r="AZ9" t="inlineStr">
-        <is>
-          <t>17743.28</t>
-        </is>
+      <c r="AZ9" t="n">
+        <v>17743.28</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
@@ -4194,8 +4144,10 @@
           <t>220.1119243458033</t>
         </is>
       </c>
-      <c r="BD9" t="n">
-        <v>9943</v>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>9943.0</t>
+        </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4361,7 +4313,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4545,15 +4497,11 @@
           <t>47.23</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>46.15</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>47.68</t>
-        </is>
+      <c r="AM10" t="n">
+        <v>46.15</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>47.68</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
@@ -4600,20 +4548,16 @@
           <t>9018.0</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>18831.4</t>
-        </is>
+      <c r="AX10" t="n">
+        <v>18831.4</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
           <t>14486.8</t>
         </is>
       </c>
-      <c r="AZ10" t="inlineStr">
-        <is>
-          <t>18676.0</t>
-        </is>
+      <c r="AZ10" t="n">
+        <v>18676</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
@@ -4630,8 +4574,10 @@
           <t>690.3228695655016</t>
         </is>
       </c>
-      <c r="BD10" t="n">
-        <v>9018</v>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>9018.0</t>
+        </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4797,7 +4743,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4981,15 +4927,11 @@
           <t>47.15</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>46.06</t>
-        </is>
-      </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>47.75</t>
-        </is>
+      <c r="AM11" t="n">
+        <v>46.06</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>47.75</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
@@ -5036,20 +4978,16 @@
           <t>14718.0</t>
         </is>
       </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>18629.2</t>
-        </is>
+      <c r="AX11" t="n">
+        <v>18629.2</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
           <t>14001.9</t>
         </is>
       </c>
-      <c r="AZ11" t="inlineStr">
-        <is>
-          <t>20406.5</t>
-        </is>
+      <c r="AZ11" t="n">
+        <v>20406.5</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
@@ -5066,8 +5004,10 @@
           <t>1436.505545966302</t>
         </is>
       </c>
-      <c r="BD11" t="n">
-        <v>14718</v>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>14718.0</t>
+        </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5233,7 +5173,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5417,15 +5357,11 @@
           <t>47.13</t>
         </is>
       </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>45.9</t>
-        </is>
-      </c>
-      <c r="AN12" t="inlineStr">
-        <is>
-          <t>47.78</t>
-        </is>
+      <c r="AM12" t="n">
+        <v>45.9</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>47.78</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
@@ -5472,20 +5408,16 @@
           <t>22600.0</t>
         </is>
       </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>20034.4</t>
-        </is>
+      <c r="AX12" t="n">
+        <v>20034.4</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
           <t>13280.9</t>
         </is>
       </c>
-      <c r="AZ12" t="inlineStr">
-        <is>
-          <t>20741.92</t>
-        </is>
+      <c r="AZ12" t="n">
+        <v>20741.92</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
@@ -5502,8 +5434,10 @@
           <t>1840.462742754364</t>
         </is>
       </c>
-      <c r="BD12" t="n">
-        <v>22600</v>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>22600.0</t>
+        </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>

--- a/Result/checksun_type/PET膜.xlsx
+++ b/Result/checksun_type/PET膜.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>148.0</t>
+          <t>116.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>45.8</t>
+          <t>46.0</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-34.26</t>
+          <t>-19.32</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-7.94</t>
+          <t>-7.54</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>5.09</t>
+          <t>3.99</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1019,63 +1019,63 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>148</t>
+          <t>116</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>45.65</t>
+          <t>67.57</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>30.16</t>
+          <t>46.25</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-1.35</t>
+          <t>-1.23</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-1.85</t>
+          <t>-1.61</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-1.48</t>
+          <t>-1.65</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>45.35</t>
+          <t>45.44</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>45.97</v>
+        <v>46</v>
       </c>
       <c r="AN2" t="n">
-        <v>46.84</v>
+        <v>46.76</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>47.54</t>
+          <t>47.55</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-12.73</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
@@ -1090,53 +1090,53 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-107.33</t>
+          <t>-107.29</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
         <is>
-          <t>2025/10/28</t>
+          <t>2025/11/27</t>
         </is>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>76706.66738197426</t>
+          <t>76608.48</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>6748.0</t>
+          <t>5317.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>5196.4</v>
+        <v>5619</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>7904.3</t>
+          <t>6964.2</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>13455.3</v>
+        <v>13246.56</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-2707</t>
+          <t>-1345</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-844.6790150359823</t>
+          <t>-945.2851106600637</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-1516.540779477615</t>
+          <t>-1498.618636592511</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>6748.0</t>
+          <t>5317.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-6.05</t>
+          <t>-5.64</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1201,7 +1201,7 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1211,12 +1211,12 @@
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>6.04</t>
+          <t>6.01</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>10.34</t>
+          <t>10.38</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>43.25</t>
+          <t>43.4</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>4309</t>
+          <t>4328</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,22 +1266,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>45.45</t>
+          <t>45.8</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>46.15</t>
+          <t>46.1</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>45.35</t>
+          <t>45.7</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>45.8</t>
+          <t>46.0</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>148.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>45.35</t>
+          <t>45.8</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1338,17 +1338,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-48.83</t>
+          <t>-34.26</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-8.84</t>
+          <t>-7.94</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>2.79</t>
+          <t>5.09</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-1.32</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1449,68 +1449,68 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>148</t>
+          <t>116</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>25.53</t>
+          <t>45.65</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>14.94</t>
+          <t>30.16</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-1.67</t>
+          <t>-1.35</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-2.0</t>
+          <t>-1.85</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-1.30</t>
+          <t>-1.48</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>45.2</t>
+          <t>45.35</t>
         </is>
       </c>
       <c r="AM3" t="n">
         <v>45.97</v>
       </c>
       <c r="AN3" t="n">
-        <v>46.91</v>
+        <v>46.84</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>47.52</t>
+          <t>47.54</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-28.10</t>
+          <t>-12.73</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,53 +1520,53 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-107.09</t>
+          <t>-107.33</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>2025/10/28</t>
+          <t>2025/11/27</t>
         </is>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>76706.66738197426</t>
+          <t>76608.48</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>3696.0</t>
+          <t>6748.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>4856</v>
+        <v>5196.4</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>9489.5</t>
+          <t>7904.3</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>14335.48</v>
+        <v>13455.3</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-4633</t>
+          <t>-2707</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-722.5223305920491</t>
+          <t>-844.6790150359823</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-1641.303098617845</t>
+          <t>-1516.540779477615</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>3696.0</t>
+          <t>6748.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-6.97</t>
+          <t>-6.05</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1631,7 +1631,7 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1641,12 +1641,12 @@
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>6.04</t>
+          <t>6.01</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>10.34</t>
+          <t>10.38</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>43.25</t>
+          <t>43.4</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>4309</t>
+          <t>4328</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,22 +1696,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>46.0</t>
+          <t>45.45</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>46.0</t>
+          <t>46.15</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>45.3</t>
+          <t>45.35</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>45.35</t>
+          <t>45.8</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>98.0</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>45.3</t>
+          <t>45.35</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,17 +1768,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-46.16</t>
+          <t>-48.83</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-8.94</t>
+          <t>-8.84</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>3.37</t>
+          <t>2.79</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>-1.32</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1879,68 +1879,68 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>148</t>
+          <t>116</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>19.3</t>
+          <t>25.53</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>15.36</t>
+          <t>14.94</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>0.33</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-1.96</t>
+          <t>-1.67</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-2.17</t>
+          <t>-2.0</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-1.05</t>
+          <t>-1.30</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>45.09</t>
+          <t>45.2</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>45.99</v>
+        <v>45.97</v>
       </c>
       <c r="AN4" t="n">
-        <v>47.02</v>
+        <v>46.91</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>47.51</t>
+          <t>47.52</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-35.53</t>
+          <t>-28.10</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,53 +1950,53 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-106.59</t>
+          <t>-107.09</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>2025/10/28</t>
+          <t>2025/11/27</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>76706.66738197426</t>
+          <t>76608.48</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>4408.0</t>
+          <t>3696.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>6984</v>
+        <v>4856</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>12971.6</t>
+          <t>9489.5</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>15065.26</v>
+        <v>14335.48</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-5987</t>
+          <t>-4633</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-555.4712818600863</t>
+          <t>-722.5223305920491</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-1433.917015296107</t>
+          <t>-1641.303098617845</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>4408.0</t>
+          <t>3696.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-7.08</t>
+          <t>-6.97</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2076,7 +2076,7 @@
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>6.04</t>
+          <t>6.01</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>10.34</t>
+          <t>10.38</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>43.25</t>
+          <t>43.4</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>4309</t>
+          <t>4328</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,22 +2126,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>44.95</t>
+          <t>46.0</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>45.45</t>
+          <t>46.0</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>44.9</t>
+          <t>45.3</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>45.3</t>
+          <t>45.35</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-1.77</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>177.0</t>
+          <t>98.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>44.75</t>
+          <t>45.3</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,17 +2198,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-39.89</t>
+          <t>-46.16</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-10.05</t>
+          <t>-8.94</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>6.09</t>
+          <t>3.37</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2309,68 +2309,68 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>148</t>
+          <t>116</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>19.3</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>11.9</t>
+          <t>15.36</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-1.32</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-1.47</t>
+          <t>-1.96</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-2.34</t>
+          <t>-2.17</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>-1.05</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>45.35</t>
+          <t>45.09</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>46.03</v>
+        <v>45.99</v>
       </c>
       <c r="AN5" t="n">
-        <v>47.13</v>
+        <v>47.02</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>47.5</t>
+          <t>47.51</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-41.45</t>
+          <t>-35.53</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-0.36</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,53 +2380,53 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-106.01</t>
+          <t>-106.59</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>2025/10/28</t>
+          <t>2025/11/27</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>76706.66738197426</t>
+          <t>76608.48</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>7926.0</t>
+          <t>4408.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>8091</v>
+        <v>6984</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>13461.2</t>
+          <t>12971.6</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>15558.56</v>
+        <v>15065.26</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-5370</t>
+          <t>-5987</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-395.7538757808097</t>
+          <t>-555.4712818600863</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-1162.725574290193</t>
+          <t>-1433.917015296107</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>7926.0</t>
+          <t>4408.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-8.21</t>
+          <t>-7.08</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2501,12 +2501,12 @@
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>1.84</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>6.04</t>
+          <t>6.01</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>10.34</t>
+          <t>10.38</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>43.25</t>
+          <t>43.4</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>4309</t>
+          <t>4328</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,22 +2556,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>45.2</t>
+          <t>44.95</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>45.2</t>
+          <t>45.45</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>44.6</t>
+          <t>44.9</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>44.75</t>
+          <t>45.3</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>-1.77</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>177.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>45.55</t>
+          <t>44.75</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,17 +2628,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>2.72</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-38.31</t>
+          <t>-39.89</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-8.44</t>
+          <t>-10.05</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>2.41</t>
+          <t>6.09</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-0.98</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2739,12 +2739,12 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>148</t>
+          <t>116</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>26.79</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
@@ -2754,34 +2754,34 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>-1.32</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>-1.47</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-2.47</t>
+          <t>-2.34</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-0.50</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>45.81</t>
+          <t>45.35</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>46.09</v>
+        <v>46.03</v>
       </c>
       <c r="AN6" t="n">
-        <v>47.26</v>
+        <v>47.13</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
@@ -2790,17 +2790,17 @@
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-20.83</t>
+          <t>-41.45</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>-0.36</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,53 +2810,53 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-105.39</t>
+          <t>-106.01</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>2025/10/28</t>
+          <t>2025/11/27</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>76706.66738197426</t>
+          <t>76608.48</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>3204.0</t>
+          <t>7926.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>8309.4</v>
+        <v>8091</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>13469.3</t>
+          <t>13461.2</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>16218.6</v>
+        <v>15558.56</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-5159</t>
+          <t>-5370</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-256.304476051831</t>
+          <t>-395.7538757808097</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-1110.711888057096</t>
+          <t>-1162.725574290193</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>3204.0</t>
+          <t>7926.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-6.56</t>
+          <t>-8.21</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2921,7 +2921,7 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -2931,12 +2931,12 @@
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>6.04</t>
+          <t>6.01</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>10.34</t>
+          <t>10.38</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>43.25</t>
+          <t>43.4</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>4309</t>
+          <t>4328</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>45.4</t>
+          <t>45.2</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>46.25</t>
+          <t>45.2</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>45.3</t>
+          <t>44.6</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>45.55</t>
+          <t>44.75</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>112.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>45.05</t>
+          <t>45.55</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-30.74</t>
+          <t>-38.31</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-9.45</t>
+          <t>-8.44</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>3.85</t>
+          <t>2.41</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3169,68 +3169,68 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>148</t>
+          <t>116</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>8.93</t>
+          <t>26.79</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>22.13</t>
+          <t>11.9</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-2.32</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-2.65</t>
+          <t>-2.47</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.50</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>46.12</t>
+          <t>45.81</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>46.12</v>
+        <v>46.09</v>
       </c>
       <c r="AN7" t="n">
-        <v>47.37</v>
+        <v>47.26</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>47.49</t>
+          <t>47.5</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-13.12</t>
+          <t>-20.83</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,53 +3240,53 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-105.11</t>
+          <t>-105.39</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>2025/10/28</t>
+          <t>2025/11/27</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>76706.66738197426</t>
+          <t>76608.48</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>5046.0</t>
+          <t>3204.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>10612.2</v>
+        <v>8309.4</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>15323.3</t>
+          <t>13469.3</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>16780.18</v>
+        <v>16218.6</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-4711</t>
+          <t>-5159</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-100.9576738690555</t>
+          <t>-256.304476051831</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-490.8097688649177</t>
+          <t>-1110.711888057096</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>5046.0</t>
+          <t>3204.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-7.59</t>
+          <t>-6.56</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3351,7 +3351,7 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3361,12 +3361,12 @@
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>6.04</t>
+          <t>6.01</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>10.34</t>
+          <t>10.38</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>43.25</t>
+          <t>43.4</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>4309</t>
+          <t>4328</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3416,22 +3416,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>44.55</t>
+          <t>45.4</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>45.4</t>
+          <t>46.25</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>44.55</t>
+          <t>45.3</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>45.05</t>
+          <t>45.55</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3453,7 +3453,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>【d】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-3.84</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>315.0</t>
+          <t>112.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>44.8</t>
+          <t>45.05</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2.18</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-9.12</t>
+          <t>-30.74</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-9.95</t>
+          <t>-9.45</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10.83</t>
+          <t>3.85</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-4.69</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3599,171 +3599,171 @@
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>148</t>
+          <t>116</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>8.93</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>45.15</t>
+          <t>22.13</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-3.92</t>
+          <t>-2.32</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>-2.65</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>-0.25</t>
+        </is>
+      </c>
+      <c r="AL8" t="inlineStr">
+        <is>
+          <t>46.12</t>
+        </is>
+      </c>
+      <c r="AM8" t="n">
+        <v>46.12</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>47.37</v>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>47.49</t>
+        </is>
+      </c>
+      <c r="AP8" t="inlineStr">
+        <is>
+          <t>-13.12</t>
+        </is>
+      </c>
+      <c r="AQ8" t="inlineStr">
+        <is>
+          <t>-0.25</t>
+        </is>
+      </c>
+      <c r="AR8" t="inlineStr">
+        <is>
+          <t>-0.22</t>
+        </is>
+      </c>
+      <c r="AS8" t="inlineStr">
+        <is>
+          <t>4.28</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr">
+        <is>
+          <t>-105.11</t>
+        </is>
+      </c>
+      <c r="AU8" t="inlineStr">
+        <is>
+          <t>2025/11/27</t>
+        </is>
+      </c>
+      <c r="AV8" t="inlineStr">
+        <is>
+          <t>76608.48</t>
+        </is>
+      </c>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>5046.0</t>
+        </is>
+      </c>
+      <c r="AX8" t="n">
+        <v>10612.2</v>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>15323.3</t>
+        </is>
+      </c>
+      <c r="AZ8" t="n">
+        <v>16780.18</v>
+      </c>
+      <c r="BA8" t="inlineStr">
+        <is>
+          <t>-4711</t>
+        </is>
+      </c>
+      <c r="BB8" t="inlineStr">
+        <is>
+          <t>-100.9576738690555</t>
+        </is>
+      </c>
+      <c r="BC8" t="inlineStr">
+        <is>
+          <t>-490.8097688649177</t>
+        </is>
+      </c>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>5046.0</t>
+        </is>
+      </c>
+      <c r="BE8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF8" t="inlineStr">
+        <is>
+          <t>48.75</t>
+        </is>
+      </c>
+      <c r="BG8" t="inlineStr">
+        <is>
+          <t>2025/08/25</t>
+        </is>
+      </c>
+      <c r="BH8" t="inlineStr">
+        <is>
+          <t>-7.59</t>
+        </is>
+      </c>
+      <c r="BI8" t="inlineStr">
+        <is>
+          <t>岱稜</t>
+        </is>
+      </c>
+      <c r="BJ8" t="inlineStr">
+        <is>
+          <t>岱稜</t>
+        </is>
+      </c>
+      <c r="BK8" t="inlineStr">
+        <is>
+          <t>其他電子業</t>
+        </is>
+      </c>
+      <c r="BL8" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BM8" t="inlineStr">
+        <is>
           <t>1.04</t>
         </is>
       </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>-2.8</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>-0.03</t>
-        </is>
-      </c>
-      <c r="AL8" t="inlineStr">
-        <is>
-          <t>46.63</t>
-        </is>
-      </c>
-      <c r="AM8" t="n">
-        <v>46.15</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>47.48</v>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>47.49</t>
-        </is>
-      </c>
-      <c r="AP8" t="inlineStr">
-        <is>
-          <t>27.78</t>
-        </is>
-      </c>
-      <c r="AQ8" t="inlineStr">
-        <is>
-          <t>-0.15</t>
-        </is>
-      </c>
-      <c r="AR8" t="inlineStr">
-        <is>
-          <t>-0.21</t>
-        </is>
-      </c>
-      <c r="AS8" t="inlineStr">
-        <is>
-          <t>4.28</t>
-        </is>
-      </c>
-      <c r="AT8" t="inlineStr">
-        <is>
-          <t>-104.94</t>
-        </is>
-      </c>
-      <c r="AU8" t="inlineStr">
-        <is>
-          <t>2025/10/28</t>
-        </is>
-      </c>
-      <c r="AV8" t="inlineStr">
-        <is>
-          <t>76706.66738197426</t>
-        </is>
-      </c>
-      <c r="AW8" t="inlineStr">
-        <is>
-          <t>14336.0</t>
-        </is>
-      </c>
-      <c r="AX8" t="n">
-        <v>14123</v>
-      </c>
-      <c r="AY8" t="inlineStr">
-        <is>
-          <t>15541.1</t>
-        </is>
-      </c>
-      <c r="AZ8" t="n">
-        <v>17446.4</v>
-      </c>
-      <c r="BA8" t="inlineStr">
-        <is>
-          <t>-1418</t>
-        </is>
-      </c>
-      <c r="BB8" t="inlineStr">
-        <is>
-          <t>-30.07547477889878</t>
-        </is>
-      </c>
-      <c r="BC8" t="inlineStr">
-        <is>
-          <t>214.9364645833703</t>
-        </is>
-      </c>
-      <c r="BD8" t="inlineStr">
-        <is>
-          <t>14336.0</t>
-        </is>
-      </c>
-      <c r="BE8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF8" t="inlineStr">
-        <is>
-          <t>48.75</t>
-        </is>
-      </c>
-      <c r="BG8" t="inlineStr">
-        <is>
-          <t>2025/08/25</t>
-        </is>
-      </c>
-      <c r="BH8" t="inlineStr">
-        <is>
-          <t>-8.10</t>
-        </is>
-      </c>
-      <c r="BI8" t="inlineStr">
-        <is>
-          <t>岱稜</t>
-        </is>
-      </c>
-      <c r="BJ8" t="inlineStr">
-        <is>
-          <t>岱稜</t>
-        </is>
-      </c>
-      <c r="BK8" t="inlineStr">
-        <is>
-          <t>其他電子業</t>
-        </is>
-      </c>
-      <c r="BL8" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BM8" t="inlineStr">
-        <is>
-          <t>1.04</t>
-        </is>
-      </c>
       <c r="BN8" t="inlineStr">
         <is>
           <t>-1.004452687200723</t>
@@ -3781,7 +3781,7 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -3791,12 +3791,12 @@
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>6.04</t>
+          <t>6.01</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>10.34</t>
+          <t>10.38</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3821,12 +3821,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>43.25</t>
+          <t>43.4</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>4309</t>
+          <t>4328</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3846,22 +3846,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>46.9</t>
+          <t>44.55</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>46.9</t>
+          <t>45.4</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>44.8</t>
+          <t>44.55</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>44.8</t>
+          <t>45.05</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-0.95</t>
+          <t>-3.84</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>213.0</t>
+          <t>315.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>46.6</t>
+          <t>44.8</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-1.75</t>
+          <t>2.61</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>26.53</t>
+          <t>-9.12</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-6.33</t>
+          <t>-9.95</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>7.32</t>
+          <t>10.83</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>-4.69</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4029,68 +4029,68 @@
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>148</t>
+          <t>116</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>57.45</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>71.82</t>
+          <t>45.15</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-1.17</t>
+          <t>-3.92</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-2.88</t>
+          <t>-2.8</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>47.15</t>
+          <t>46.63</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>46.22</v>
+        <v>46.15</v>
       </c>
       <c r="AN9" t="n">
-        <v>47.59</v>
+        <v>47.48</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>47.5</t>
+          <t>47.49</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>98.12</t>
+          <t>27.78</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-0.00</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4100,53 +4100,53 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-105.28</t>
+          <t>-104.94</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>2025/10/28</t>
+          <t>2025/11/27</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>76706.66738197426</t>
+          <t>76608.48</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>9943.0</t>
+          <t>14336.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>18959.2</v>
+        <v>14123</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>14983.4</t>
+          <t>15541.1</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>17743.28</v>
+        <v>17446.4</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>3975</t>
+          <t>-1418</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-74.62310011749315</t>
+          <t>-30.07547477889878</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>220.1119243458033</t>
+          <t>214.9364645833703</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>9943.0</t>
+          <t>14336.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-4.41</t>
+          <t>-8.10</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4211,7 +4211,7 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4221,12 +4221,12 @@
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>1.89</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>6.04</t>
+          <t>6.01</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>10.34</t>
+          <t>10.38</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>43.25</t>
+          <t>43.4</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>4309</t>
+          <t>4328</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4276,22 +4276,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>47.15</t>
+          <t>46.9</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>47.2</t>
+          <t>46.9</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>46.4</t>
+          <t>44.8</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>46.6</t>
+          <t>44.8</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>-0.95</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>192.0</t>
+          <t>213.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>47.05</t>
+          <t>46.6</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,17 +4348,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-2.73</t>
+          <t>-1.3</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>29.99</t>
+          <t>26.53</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-5.43</t>
+          <t>-6.33</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>6.60</t>
+          <t>7.32</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4459,68 +4459,68 @@
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>148</t>
+          <t>116</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>57.45</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>71.82</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>-1.17</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-3.21</t>
+          <t>-2.88</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>47.23</t>
+          <t>47.15</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>46.15</v>
+        <v>46.22</v>
       </c>
       <c r="AN10" t="n">
-        <v>47.68</v>
+        <v>47.59</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>47.48</t>
+          <t>47.5</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>100.64</t>
+          <t>98.12</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.00</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4530,53 +4530,53 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-106.58</t>
+          <t>-105.28</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>2025/10/28</t>
+          <t>2025/11/27</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>76706.66738197426</t>
+          <t>76608.48</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>9018.0</t>
+          <t>9943.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>18831.4</v>
+        <v>18959.2</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>14486.8</t>
+          <t>14983.4</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>18676</v>
+        <v>17743.28</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>4344</t>
+          <t>3975</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-128.211286383547</t>
+          <t>-74.62310011749315</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>690.3228695655016</t>
+          <t>220.1119243458033</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>9018.0</t>
+          <t>9943.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-3.49</t>
+          <t>-4.41</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4651,12 +4651,12 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>1.89</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>6.04</t>
+          <t>6.01</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>10.34</t>
+          <t>10.38</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>43.25</t>
+          <t>43.4</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>4309</t>
+          <t>4328</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4706,22 +4706,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>46.5</t>
+          <t>47.15</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>47.5</t>
+          <t>47.2</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>46.35</t>
+          <t>46.4</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>47.05</t>
+          <t>46.6</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-1.05</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>311.0</t>
+          <t>192.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>47.1</t>
+          <t>47.05</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,17 +4778,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-2.84</t>
+          <t>-2.28</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>33.05</t>
+          <t>29.99</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-5.33</t>
+          <t>-5.43</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10.69</t>
+          <t>6.60</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-0.95</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4889,68 +4889,68 @@
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>148</t>
+          <t>116</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>93.33</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>2.36</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-3.53</t>
+          <t>-3.21</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>0.60</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>47.15</t>
+          <t>47.23</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>46.06</v>
+        <v>46.15</v>
       </c>
       <c r="AN11" t="n">
-        <v>47.75</v>
+        <v>47.68</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>47.47</t>
+          <t>47.48</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>89.68</t>
+          <t>100.64</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4960,53 +4960,53 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-108.23</t>
+          <t>-106.58</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>2025/10/28</t>
+          <t>2025/11/27</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>76706.66738197426</t>
+          <t>76608.48</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>14718.0</t>
+          <t>9018.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>18629.2</v>
+        <v>18831.4</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>14001.9</t>
+          <t>14486.8</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>20406.5</v>
+        <v>18676</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>4627</t>
+          <t>4344</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-277.0356783742832</t>
+          <t>-128.211286383547</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>1436.505545966302</t>
+          <t>690.3228695655016</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>14718.0</t>
+          <t>9018.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-3.38</t>
+          <t>-3.49</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5086,7 +5086,7 @@
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>6.04</t>
+          <t>6.01</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>10.34</t>
+          <t>10.38</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>43.25</t>
+          <t>43.4</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>4309</t>
+          <t>4328</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5136,22 +5136,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>47.6</t>
+          <t>46.5</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>47.8</t>
+          <t>47.5</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>46.85</t>
+          <t>46.35</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>47.1</t>
+          <t>47.05</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>-1.05</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>474.0</t>
+          <t>311.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>47.6</t>
+          <t>47.1</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,17 +5208,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-3.93</t>
+          <t>-2.39</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>50.85</t>
+          <t>33.05</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-4.32</t>
+          <t>-5.33</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>16.30</t>
+          <t>10.69</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-0.95</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5319,68 +5319,68 @@
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>148</t>
+          <t>116</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>93.33</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>2.67</t>
+          <t>2.36</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-3.93</t>
+          <t>-3.53</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.60</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>47.13</t>
+          <t>47.15</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>45.9</v>
+        <v>46.06</v>
       </c>
       <c r="AN12" t="n">
-        <v>47.78</v>
+        <v>47.75</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>47.45</t>
+          <t>47.47</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>79.21</t>
+          <t>89.68</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5390,53 +5390,53 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-110.08</t>
+          <t>-108.23</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>2025/10/28</t>
+          <t>2025/11/27</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>76706.66738197426</t>
+          <t>76608.48</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>22600.0</t>
+          <t>14718.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>20034.4</v>
+        <v>18629.2</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>13280.9</t>
+          <t>14001.9</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>20741.92</v>
+        <v>20406.5</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>6753</t>
+          <t>4627</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-588.5886282543895</t>
+          <t>-277.0356783742832</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>1840.462742754364</t>
+          <t>1436.505545966302</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>22600.0</t>
+          <t>14718.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-2.36</t>
+          <t>-3.38</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>6.04</t>
+          <t>6.01</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>10.34</t>
+          <t>10.38</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>43.25</t>
+          <t>43.4</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>4309</t>
+          <t>4328</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5566,22 +5566,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>47.85</t>
+          <t>47.6</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>48.1</t>
+          <t>47.8</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>47.25</t>
+          <t>46.85</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>47.6</t>
+          <t>47.1</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/PET膜.xlsx
+++ b/Result/checksun_type/PET膜.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>116.0</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>-1.36</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-19.32</t>
+          <t>-26.22</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>3.99</t>
+          <t>2.58</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,73 +1014,73 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>116</t>
+          <t>75</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>67.57</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>46.25</t>
+          <t>71.07</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>0.68</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-1.23</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-1.61</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-1.65</t>
+          <t>-1.76</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>45.44</t>
+          <t>45.69</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>46</v>
+        <v>46.04</v>
       </c>
       <c r="AN2" t="n">
-        <v>46.76</v>
+        <v>46.7</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>47.55</t>
+          <t>47.54</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>12.46</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-107.29</t>
+          <t>-107.07</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,43 +1100,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>76608.48</t>
+          <t>76506.6419400856</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>5317.0</t>
+          <t>3480.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>5619</v>
+        <v>4729.8</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>6964.2</t>
+          <t>6410.4</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>13246.56</v>
+        <v>12782.88</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-1345</t>
+          <t>-1680</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-945.2851106600637</t>
+          <t>-1043.91550450592</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-1498.618636592511</t>
+          <t>-1586.382670658128</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>5317.0</t>
+          <t>3480.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1181,7 +1181,7 @@
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
@@ -1201,7 +1201,7 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1241,7 +1241,7 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>43.4</t>
+          <t>44.86</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
@@ -1266,17 +1266,17 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>45.8</t>
+          <t>46.4</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>46.1</t>
+          <t>46.45</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>45.7</t>
+          <t>46.0</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1303,7 +1303,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>148.0</t>
+          <t>116.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>45.8</t>
+          <t>46.0</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1338,17 +1338,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>-1.36</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-34.26</t>
+          <t>-19.32</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-7.94</t>
+          <t>-7.54</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>5.09</t>
+          <t>3.99</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,68 +1444,68 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>116</t>
+          <t>75</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>45.65</t>
+          <t>67.57</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>30.16</t>
+          <t>46.25</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-1.35</t>
+          <t>-1.23</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-1.85</t>
+          <t>-1.61</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-1.48</t>
+          <t>-1.65</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>45.35</t>
+          <t>45.44</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>45.97</v>
+        <v>46</v>
       </c>
       <c r="AN3" t="n">
-        <v>46.84</v>
+        <v>46.76</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>47.54</t>
+          <t>47.55</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-12.73</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-107.33</t>
+          <t>-107.29</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1530,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>76608.48</t>
+          <t>76506.6419400856</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>6748.0</t>
+          <t>5317.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>5196.4</v>
+        <v>5619</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>7904.3</t>
+          <t>6964.2</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>13455.3</v>
+        <v>13246.56</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-2707</t>
+          <t>-1345</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-844.6790150359823</t>
+          <t>-945.2851106600637</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-1516.540779477615</t>
+          <t>-1498.618636592511</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>6748.0</t>
+          <t>5317.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-6.05</t>
+          <t>-5.64</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
@@ -1631,7 +1631,7 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1671,7 +1671,7 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>43.4</t>
+          <t>44.86</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1696,22 +1696,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>45.45</t>
+          <t>45.8</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>46.15</t>
+          <t>46.1</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>45.35</t>
+          <t>45.7</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>45.8</t>
+          <t>46.0</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>148.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>45.35</t>
+          <t>45.8</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,17 +1768,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>-1.36</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-48.83</t>
+          <t>-34.26</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-8.84</t>
+          <t>-7.94</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>2.79</t>
+          <t>5.09</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-1.32</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,73 +1874,73 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>116</t>
+          <t>75</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>25.53</t>
+          <t>45.65</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>14.94</t>
+          <t>30.16</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-1.67</t>
+          <t>-1.35</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-2.0</t>
+          <t>-1.85</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-1.30</t>
+          <t>-1.48</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>45.2</t>
+          <t>45.35</t>
         </is>
       </c>
       <c r="AM4" t="n">
         <v>45.97</v>
       </c>
       <c r="AN4" t="n">
-        <v>46.91</v>
+        <v>46.84</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>47.52</t>
+          <t>47.54</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-28.10</t>
+          <t>-12.73</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-107.09</t>
+          <t>-107.33</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1960,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>76608.48</t>
+          <t>76506.6419400856</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>3696.0</t>
+          <t>6748.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>4856</v>
+        <v>5196.4</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>9489.5</t>
+          <t>7904.3</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>14335.48</v>
+        <v>13455.3</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-4633</t>
+          <t>-2707</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-722.5223305920491</t>
+          <t>-844.6790150359823</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-1641.303098617845</t>
+          <t>-1516.540779477615</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>3696.0</t>
+          <t>6748.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-6.97</t>
+          <t>-6.05</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2041,7 +2041,7 @@
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2101,7 +2101,7 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>43.4</t>
+          <t>44.86</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -2126,22 +2126,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>46.0</t>
+          <t>45.45</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>46.0</t>
+          <t>46.15</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>45.3</t>
+          <t>45.35</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>45.35</t>
+          <t>45.8</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>98.0</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>45.3</t>
+          <t>45.35</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,17 +2198,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>-1.36</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-46.16</t>
+          <t>-48.83</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-8.94</t>
+          <t>-8.84</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>3.37</t>
+          <t>2.79</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>-1.32</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,73 +2304,73 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>116</t>
+          <t>75</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>19.3</t>
+          <t>25.53</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>15.36</t>
+          <t>14.94</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>0.33</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-1.96</t>
+          <t>-1.67</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-2.17</t>
+          <t>-2.0</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-1.05</t>
+          <t>-1.30</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>45.09</t>
+          <t>45.2</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>45.99</v>
+        <v>45.97</v>
       </c>
       <c r="AN5" t="n">
-        <v>47.02</v>
+        <v>46.91</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>47.51</t>
+          <t>47.52</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-35.53</t>
+          <t>-28.10</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-106.59</t>
+          <t>-107.09</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2390,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>76608.48</t>
+          <t>76506.6419400856</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>4408.0</t>
+          <t>3696.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>6984</v>
+        <v>4856</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>12971.6</t>
+          <t>9489.5</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>15065.26</v>
+        <v>14335.48</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-5987</t>
+          <t>-4633</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-555.4712818600863</t>
+          <t>-722.5223305920491</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-1433.917015296107</t>
+          <t>-1641.303098617845</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>4408.0</t>
+          <t>3696.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-7.08</t>
+          <t>-6.97</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2531,7 +2531,7 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>43.4</t>
+          <t>44.86</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
@@ -2556,22 +2556,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>44.95</t>
+          <t>46.0</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>45.45</t>
+          <t>46.0</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>44.9</t>
+          <t>45.3</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>45.3</t>
+          <t>45.35</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-1.77</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>177.0</t>
+          <t>98.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>44.75</t>
+          <t>45.3</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,17 +2628,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2.72</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>-1.36</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-39.89</t>
+          <t>-46.16</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-10.05</t>
+          <t>-8.94</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>6.09</t>
+          <t>3.37</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,73 +2734,73 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>116</t>
+          <t>75</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>19.3</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>11.9</t>
+          <t>15.36</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-1.32</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-1.47</t>
+          <t>-1.96</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-2.34</t>
+          <t>-2.17</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>-1.05</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>45.35</t>
+          <t>45.09</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>46.03</v>
+        <v>45.99</v>
       </c>
       <c r="AN6" t="n">
-        <v>47.13</v>
+        <v>47.02</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>47.5</t>
+          <t>47.51</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-41.45</t>
+          <t>-35.53</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-0.36</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-106.01</t>
+          <t>-106.59</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2820,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>76608.48</t>
+          <t>76506.6419400856</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>7926.0</t>
+          <t>4408.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>8091</v>
+        <v>6984</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>13461.2</t>
+          <t>12971.6</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>15558.56</v>
+        <v>15065.26</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-5370</t>
+          <t>-5987</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-395.7538757808097</t>
+          <t>-555.4712818600863</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-1162.725574290193</t>
+          <t>-1433.917015296107</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>7926.0</t>
+          <t>4408.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-8.21</t>
+          <t>-7.08</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
@@ -2921,7 +2921,7 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>1.84</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2961,7 +2961,7 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>43.4</t>
+          <t>44.86</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>45.2</t>
+          <t>44.95</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>45.2</t>
+          <t>45.45</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>44.6</t>
+          <t>44.9</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>44.75</t>
+          <t>45.3</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>-1.77</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>177.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>45.55</t>
+          <t>44.75</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>2.72</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>-1.36</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-38.31</t>
+          <t>-39.89</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-8.44</t>
+          <t>-10.05</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>2.41</t>
+          <t>6.09</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-0.98</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,17 +3164,17 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>116</t>
+          <t>75</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>26.79</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
@@ -3184,34 +3184,34 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>-1.32</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>-1.47</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-2.47</t>
+          <t>-2.34</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-0.50</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>45.81</t>
+          <t>45.35</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>46.09</v>
+        <v>46.03</v>
       </c>
       <c r="AN7" t="n">
-        <v>47.26</v>
+        <v>47.13</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
@@ -3220,17 +3220,17 @@
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-20.83</t>
+          <t>-41.45</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>-0.36</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-105.39</t>
+          <t>-106.01</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3250,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>76608.48</t>
+          <t>76506.6419400856</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>3204.0</t>
+          <t>7926.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>8309.4</v>
+        <v>8091</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>13469.3</t>
+          <t>13461.2</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>16218.6</v>
+        <v>15558.56</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-5159</t>
+          <t>-5370</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-256.304476051831</t>
+          <t>-395.7538757808097</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-1110.711888057096</t>
+          <t>-1162.725574290193</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>3204.0</t>
+          <t>7926.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-6.56</t>
+          <t>-8.21</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
@@ -3351,7 +3351,7 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3361,7 +3361,7 @@
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>43.4</t>
+          <t>44.86</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3416,22 +3416,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>45.4</t>
+          <t>45.2</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>46.25</t>
+          <t>45.2</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>45.3</t>
+          <t>44.6</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>45.55</t>
+          <t>44.75</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>112.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>45.05</t>
+          <t>45.55</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>-1.36</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-30.74</t>
+          <t>-38.31</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-9.45</t>
+          <t>-8.44</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>3.85</t>
+          <t>2.41</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,73 +3594,73 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>116</t>
+          <t>75</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>8.93</t>
+          <t>26.79</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>22.13</t>
+          <t>11.9</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-2.32</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-2.65</t>
+          <t>-2.47</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.50</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>46.12</t>
+          <t>45.81</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>46.12</v>
+        <v>46.09</v>
       </c>
       <c r="AN8" t="n">
-        <v>47.37</v>
+        <v>47.26</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>47.49</t>
+          <t>47.5</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-13.12</t>
+          <t>-20.83</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-105.11</t>
+          <t>-105.39</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3680,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>76608.48</t>
+          <t>76506.6419400856</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>5046.0</t>
+          <t>3204.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>10612.2</v>
+        <v>8309.4</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>15323.3</t>
+          <t>13469.3</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>16780.18</v>
+        <v>16218.6</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-4711</t>
+          <t>-5159</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-100.9576738690555</t>
+          <t>-256.304476051831</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-490.8097688649177</t>
+          <t>-1110.711888057096</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>5046.0</t>
+          <t>3204.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-7.59</t>
+          <t>-6.56</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3761,7 +3761,7 @@
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
@@ -3781,7 +3781,7 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -3791,7 +3791,7 @@
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>43.4</t>
+          <t>44.86</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
@@ -3846,22 +3846,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>44.55</t>
+          <t>45.4</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>45.4</t>
+          <t>46.25</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>44.55</t>
+          <t>45.3</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>45.05</t>
+          <t>45.55</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3883,7 +3883,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>【d】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-3.84</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>315.0</t>
+          <t>112.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>44.8</t>
+          <t>45.05</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2.61</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>-1.36</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-9.12</t>
+          <t>-30.74</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-9.95</t>
+          <t>-9.45</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10.83</t>
+          <t>3.85</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-4.69</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,54 +4024,54 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>116</t>
+          <t>75</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>8.93</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>45.15</t>
+          <t>22.13</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-3.92</t>
+          <t>-2.32</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-2.8</t>
+          <t>-2.65</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>46.63</t>
+          <t>46.12</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>46.15</v>
+        <v>46.12</v>
       </c>
       <c r="AN9" t="n">
-        <v>47.48</v>
+        <v>47.37</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
@@ -4080,17 +4080,17 @@
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>27.78</t>
+          <t>-13.12</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-104.94</t>
+          <t>-105.11</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4110,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>76608.48</t>
+          <t>76506.6419400856</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>14336.0</t>
+          <t>5046.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>14123</v>
+        <v>10612.2</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>15541.1</t>
+          <t>15323.3</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>17446.4</v>
+        <v>16780.18</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-1418</t>
+          <t>-4711</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-30.07547477889878</t>
+          <t>-100.9576738690555</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>214.9364645833703</t>
+          <t>-490.8097688649177</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>14336.0</t>
+          <t>5046.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-8.10</t>
+          <t>-7.59</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4191,7 +4191,7 @@
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
@@ -4211,7 +4211,7 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4221,7 +4221,7 @@
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4251,7 +4251,7 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>43.4</t>
+          <t>44.86</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
@@ -4276,22 +4276,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>46.9</t>
+          <t>44.55</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>46.9</t>
+          <t>45.4</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>44.8</t>
+          <t>44.55</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>44.8</t>
+          <t>45.05</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-0.95</t>
+          <t>-3.84</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>213.0</t>
+          <t>315.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>46.6</t>
+          <t>44.8</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,17 +4348,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-1.3</t>
+          <t>2.61</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>-1.36</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>26.53</t>
+          <t>-9.12</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-6.33</t>
+          <t>-9.95</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>7.32</t>
+          <t>10.83</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>-4.69</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,73 +4454,73 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>116</t>
+          <t>75</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>57.45</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>71.82</t>
+          <t>45.15</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-1.17</t>
+          <t>-3.92</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-2.88</t>
+          <t>-2.8</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>47.15</t>
+          <t>46.63</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>46.22</v>
+        <v>46.15</v>
       </c>
       <c r="AN10" t="n">
-        <v>47.59</v>
+        <v>47.48</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>47.5</t>
+          <t>47.49</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>98.12</t>
+          <t>27.78</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-0.00</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-105.28</t>
+          <t>-104.94</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4540,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>76608.48</t>
+          <t>76506.6419400856</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>9943.0</t>
+          <t>14336.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>18959.2</v>
+        <v>14123</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>14983.4</t>
+          <t>15541.1</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>17743.28</v>
+        <v>17446.4</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>3975</t>
+          <t>-1418</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-74.62310011749315</t>
+          <t>-30.07547477889878</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>220.1119243458033</t>
+          <t>214.9364645833703</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>9943.0</t>
+          <t>14336.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-4.41</t>
+          <t>-8.10</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4621,7 +4621,7 @@
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
@@ -4641,17 +4641,17 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>1.89</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4681,7 +4681,7 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>43.4</t>
+          <t>44.86</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -4706,22 +4706,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>47.15</t>
+          <t>46.9</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>47.2</t>
+          <t>46.9</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>46.4</t>
+          <t>44.8</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>46.6</t>
+          <t>44.8</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>-0.95</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>192.0</t>
+          <t>213.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>47.05</t>
+          <t>46.6</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,17 +4778,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-2.28</t>
+          <t>-1.3</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>-1.36</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>29.99</t>
+          <t>26.53</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-5.43</t>
+          <t>-6.33</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>6.60</t>
+          <t>7.32</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,73 +4884,73 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>116</t>
+          <t>75</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>57.45</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>71.82</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>-1.17</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-3.21</t>
+          <t>-2.88</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>47.23</t>
+          <t>47.15</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>46.15</v>
+        <v>46.22</v>
       </c>
       <c r="AN11" t="n">
-        <v>47.68</v>
+        <v>47.59</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>47.48</t>
+          <t>47.5</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>100.64</t>
+          <t>98.12</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.00</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-106.58</t>
+          <t>-105.28</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4970,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>76608.48</t>
+          <t>76506.6419400856</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>9018.0</t>
+          <t>9943.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>18831.4</v>
+        <v>18959.2</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>14486.8</t>
+          <t>14983.4</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>18676</v>
+        <v>17743.28</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>4344</t>
+          <t>3975</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-128.211286383547</t>
+          <t>-74.62310011749315</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>690.3228695655016</t>
+          <t>220.1119243458033</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>9018.0</t>
+          <t>9943.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-3.49</t>
+          <t>-4.41</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5051,7 +5051,7 @@
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
@@ -5081,7 +5081,7 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>1.89</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5111,7 +5111,7 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>43.4</t>
+          <t>44.86</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5136,22 +5136,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>46.5</t>
+          <t>47.15</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>47.5</t>
+          <t>47.2</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>46.35</t>
+          <t>46.4</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>47.05</t>
+          <t>46.6</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-1.05</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>311.0</t>
+          <t>192.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>47.1</t>
+          <t>47.05</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,17 +5208,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-2.39</t>
+          <t>-2.28</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>-1.36</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>33.05</t>
+          <t>29.99</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-5.33</t>
+          <t>-5.43</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10.69</t>
+          <t>6.60</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-0.95</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,73 +5314,73 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>116</t>
+          <t>75</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>93.33</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>2.36</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-3.53</t>
+          <t>-3.21</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>0.60</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>47.15</t>
+          <t>47.23</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>46.06</v>
+        <v>46.15</v>
       </c>
       <c r="AN12" t="n">
-        <v>47.75</v>
+        <v>47.68</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>47.47</t>
+          <t>47.48</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>89.68</t>
+          <t>100.64</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-108.23</t>
+          <t>-106.58</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,43 +5400,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>76608.48</t>
+          <t>76506.6419400856</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>14718.0</t>
+          <t>9018.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>18629.2</v>
+        <v>18831.4</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>14001.9</t>
+          <t>14486.8</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>20406.5</v>
+        <v>18676</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>4627</t>
+          <t>4344</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-277.0356783742832</t>
+          <t>-128.211286383547</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>1436.505545966302</t>
+          <t>690.3228695655016</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>14718.0</t>
+          <t>9018.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-3.38</t>
+          <t>-3.49</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
@@ -5541,7 +5541,7 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>43.4</t>
+          <t>44.86</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -5566,22 +5566,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>47.6</t>
+          <t>46.5</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>47.8</t>
+          <t>47.5</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>46.85</t>
+          <t>46.35</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>47.1</t>
+          <t>47.05</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/PET膜.xlsx
+++ b/Result/checksun_type/PET膜.xlsx
@@ -883,42 +883,42 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>-0.43</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>45.8</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>75.0</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>46.0</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-1.36</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-26.22</t>
+          <t>-20.54</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-7.54</t>
+          <t>-7.94</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>2.58</t>
+          <t>2.82</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-0.98</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1019,68 +1019,68 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>82</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>71.07</t>
+          <t>83.86</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>0.68</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-1.76</t>
+          <t>-1.87</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>45.69</t>
+          <t>45.79</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>46.04</v>
+        <v>46.06</v>
       </c>
       <c r="AN2" t="n">
-        <v>46.7</v>
+        <v>46.64</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>47.54</t>
+          <t>47.53</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>12.46</t>
+          <t>15.60</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-107.07</t>
+          <t>-106.80</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,43 +1100,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>76506.6419400856</t>
+          <t>76405.7329059829</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>3480.0</t>
+          <t>3779.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>4729.8</v>
+        <v>4604</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>6410.4</t>
+          <t>5794.0</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>12782.88</v>
+        <v>12544.52</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-1680</t>
+          <t>-1190</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-1043.91550450592</t>
+          <t>-1127.272031156948</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-1586.382670658128</t>
+          <t>-1585.732927737606</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>3480.0</t>
+          <t>3779.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-5.64</t>
+          <t>-6.05</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1181,7 +1181,7 @@
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
@@ -1201,7 +1201,7 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1211,12 +1211,12 @@
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>6.01</t>
+          <t>6.04</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>10.38</t>
+          <t>10.34</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>44.86</t>
+          <t>44.93</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>4328</t>
+          <t>4309</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,22 +1266,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>46.4</t>
+          <t>46.0</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>46.45</t>
+          <t>46.05</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>46.0</t>
+          <t>45.55</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>46.0</t>
+          <t>45.8</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>116.0</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1338,17 +1338,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.44</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-1.36</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-19.32</t>
+          <t>-26.22</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>3.99</t>
+          <t>2.58</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1449,68 +1449,68 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>82</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>67.57</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>46.25</t>
+          <t>71.07</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>0.68</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-1.23</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-1.61</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-1.65</t>
+          <t>-1.76</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>45.44</t>
+          <t>45.69</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>46</v>
+        <v>46.04</v>
       </c>
       <c r="AN3" t="n">
-        <v>46.76</v>
+        <v>46.7</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>47.55</t>
+          <t>47.54</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>12.46</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-107.29</t>
+          <t>-107.07</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1530,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>76506.6419400856</t>
+          <t>76405.7329059829</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>5317.0</t>
+          <t>3480.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>5619</v>
+        <v>4729.8</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>6964.2</t>
+          <t>6410.4</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>13246.56</v>
+        <v>12782.88</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-1345</t>
+          <t>-1680</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-945.2851106600637</t>
+          <t>-1043.91550450592</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-1498.618636592511</t>
+          <t>-1586.382670658128</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>5317.0</t>
+          <t>3480.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
@@ -1631,7 +1631,7 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1646,7 +1646,7 @@
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>6.01</t>
+          <t>6.04</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>10.38</t>
+          <t>10.34</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>44.86</t>
+          <t>44.93</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>4328</t>
+          <t>4309</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,17 +1696,17 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>45.8</t>
+          <t>46.4</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>46.1</t>
+          <t>46.45</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>45.7</t>
+          <t>46.0</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1733,7 +1733,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>148.0</t>
+          <t>116.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>45.8</t>
+          <t>46.0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,17 +1768,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>-0.44</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-1.36</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-34.26</t>
+          <t>-19.32</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-7.94</t>
+          <t>-7.54</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>5.09</t>
+          <t>3.99</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1879,63 +1879,63 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>82</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>45.65</t>
+          <t>67.57</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>30.16</t>
+          <t>46.25</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-1.35</t>
+          <t>-1.23</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-1.85</t>
+          <t>-1.61</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-1.48</t>
+          <t>-1.65</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>45.35</t>
+          <t>45.44</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>45.97</v>
+        <v>46</v>
       </c>
       <c r="AN4" t="n">
-        <v>46.84</v>
+        <v>46.76</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>47.54</t>
+          <t>47.55</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-12.73</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-107.33</t>
+          <t>-107.29</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1960,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>76506.6419400856</t>
+          <t>76405.7329059829</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>6748.0</t>
+          <t>5317.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>5196.4</v>
+        <v>5619</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>7904.3</t>
+          <t>6964.2</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>13455.3</v>
+        <v>13246.56</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-2707</t>
+          <t>-1345</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-844.6790150359823</t>
+          <t>-945.2851106600637</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-1516.540779477615</t>
+          <t>-1498.618636592511</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>6748.0</t>
+          <t>5317.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-6.05</t>
+          <t>-5.64</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2041,7 +2041,7 @@
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2071,12 +2071,12 @@
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>6.01</t>
+          <t>6.04</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>10.38</t>
+          <t>10.34</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>44.86</t>
+          <t>44.93</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>4328</t>
+          <t>4309</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,22 +2126,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>45.45</t>
+          <t>45.8</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>46.15</t>
+          <t>46.1</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>45.35</t>
+          <t>45.7</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>45.8</t>
+          <t>46.0</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>148.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>45.35</t>
+          <t>45.8</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,17 +2198,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-1.36</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-48.83</t>
+          <t>-34.26</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-8.84</t>
+          <t>-7.94</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>2.79</t>
+          <t>5.09</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-1.32</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2309,68 +2309,68 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>82</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>25.53</t>
+          <t>45.65</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>14.94</t>
+          <t>30.16</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-1.67</t>
+          <t>-1.35</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-2.0</t>
+          <t>-1.85</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-1.30</t>
+          <t>-1.48</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>45.2</t>
+          <t>45.35</t>
         </is>
       </c>
       <c r="AM5" t="n">
         <v>45.97</v>
       </c>
       <c r="AN5" t="n">
-        <v>46.91</v>
+        <v>46.84</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>47.52</t>
+          <t>47.54</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-28.10</t>
+          <t>-12.73</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-107.09</t>
+          <t>-107.33</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2390,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>76506.6419400856</t>
+          <t>76405.7329059829</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>3696.0</t>
+          <t>6748.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>4856</v>
+        <v>5196.4</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>9489.5</t>
+          <t>7904.3</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>14335.48</v>
+        <v>13455.3</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-4633</t>
+          <t>-2707</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-722.5223305920491</t>
+          <t>-844.6790150359823</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-1641.303098617845</t>
+          <t>-1516.540779477615</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>3696.0</t>
+          <t>6748.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-6.97</t>
+          <t>-6.05</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2501,12 +2501,12 @@
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>6.01</t>
+          <t>6.04</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>10.38</t>
+          <t>10.34</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>44.86</t>
+          <t>44.93</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>4328</t>
+          <t>4309</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,22 +2556,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>46.0</t>
+          <t>45.45</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>46.0</t>
+          <t>46.15</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>45.3</t>
+          <t>45.35</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>45.35</t>
+          <t>45.8</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>98.0</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>45.3</t>
+          <t>45.35</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,17 +2628,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-1.36</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-46.16</t>
+          <t>-48.83</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-8.94</t>
+          <t>-8.84</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>3.37</t>
+          <t>2.79</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>-1.32</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2739,68 +2739,68 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>82</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>19.3</t>
+          <t>25.53</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>15.36</t>
+          <t>14.94</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>0.33</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-1.96</t>
+          <t>-1.67</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-2.17</t>
+          <t>-2.0</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-1.05</t>
+          <t>-1.30</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>45.09</t>
+          <t>45.2</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>45.99</v>
+        <v>45.97</v>
       </c>
       <c r="AN6" t="n">
-        <v>47.02</v>
+        <v>46.91</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>47.51</t>
+          <t>47.52</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-35.53</t>
+          <t>-28.10</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-106.59</t>
+          <t>-107.09</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2820,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>76506.6419400856</t>
+          <t>76405.7329059829</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>4408.0</t>
+          <t>3696.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>6984</v>
+        <v>4856</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>12971.6</t>
+          <t>9489.5</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>15065.26</v>
+        <v>14335.48</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-5987</t>
+          <t>-4633</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-555.4712818600863</t>
+          <t>-722.5223305920491</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-1433.917015296107</t>
+          <t>-1641.303098617845</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>4408.0</t>
+          <t>3696.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-7.08</t>
+          <t>-6.97</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
@@ -2921,7 +2921,7 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>6.01</t>
+          <t>6.04</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>10.38</t>
+          <t>10.34</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>44.86</t>
+          <t>44.93</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>4328</t>
+          <t>4309</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>44.95</t>
+          <t>46.0</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>45.45</t>
+          <t>46.0</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>44.9</t>
+          <t>45.3</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>45.3</t>
+          <t>45.35</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-1.77</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>177.0</t>
+          <t>98.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>44.75</t>
+          <t>45.3</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2.72</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-1.36</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-39.89</t>
+          <t>-46.16</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-10.05</t>
+          <t>-8.94</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>6.09</t>
+          <t>3.37</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3169,68 +3169,68 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>82</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>19.3</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>11.9</t>
+          <t>15.36</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-1.32</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-1.47</t>
+          <t>-1.96</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-2.34</t>
+          <t>-2.17</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>-1.05</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>45.35</t>
+          <t>45.09</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>46.03</v>
+        <v>45.99</v>
       </c>
       <c r="AN7" t="n">
-        <v>47.13</v>
+        <v>47.02</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>47.5</t>
+          <t>47.51</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-41.45</t>
+          <t>-35.53</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-0.36</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-106.01</t>
+          <t>-106.59</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3250,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>76506.6419400856</t>
+          <t>76405.7329059829</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>7926.0</t>
+          <t>4408.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>8091</v>
+        <v>6984</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>13461.2</t>
+          <t>12971.6</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>15558.56</v>
+        <v>15065.26</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-5370</t>
+          <t>-5987</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-395.7538757808097</t>
+          <t>-555.4712818600863</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-1162.725574290193</t>
+          <t>-1433.917015296107</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>7926.0</t>
+          <t>4408.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-8.21</t>
+          <t>-7.08</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
@@ -3351,7 +3351,7 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3361,12 +3361,12 @@
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>1.84</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>6.01</t>
+          <t>6.04</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>10.38</t>
+          <t>10.34</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>44.86</t>
+          <t>44.93</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>4328</t>
+          <t>4309</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3416,22 +3416,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>45.2</t>
+          <t>44.95</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>45.2</t>
+          <t>45.45</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>44.6</t>
+          <t>44.9</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>44.75</t>
+          <t>45.3</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>-1.77</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>177.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>45.55</t>
+          <t>44.75</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-1.36</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-38.31</t>
+          <t>-39.89</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-8.44</t>
+          <t>-10.05</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>2.41</t>
+          <t>6.09</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-0.98</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3599,12 +3599,12 @@
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>82</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>26.79</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
@@ -3614,34 +3614,34 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>-1.32</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>-1.47</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-2.47</t>
+          <t>-2.34</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-0.50</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>45.81</t>
+          <t>45.35</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>46.09</v>
+        <v>46.03</v>
       </c>
       <c r="AN8" t="n">
-        <v>47.26</v>
+        <v>47.13</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
@@ -3650,17 +3650,17 @@
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-20.83</t>
+          <t>-41.45</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>-0.36</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-105.39</t>
+          <t>-106.01</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3680,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>76506.6419400856</t>
+          <t>76405.7329059829</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>3204.0</t>
+          <t>7926.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>8309.4</v>
+        <v>8091</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>13469.3</t>
+          <t>13461.2</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>16218.6</v>
+        <v>15558.56</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-5159</t>
+          <t>-5370</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-256.304476051831</t>
+          <t>-395.7538757808097</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-1110.711888057096</t>
+          <t>-1162.725574290193</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>3204.0</t>
+          <t>7926.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-6.56</t>
+          <t>-8.21</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3761,7 +3761,7 @@
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
@@ -3781,7 +3781,7 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -3791,12 +3791,12 @@
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>6.01</t>
+          <t>6.04</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>10.38</t>
+          <t>10.34</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3821,12 +3821,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>44.86</t>
+          <t>44.93</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>4328</t>
+          <t>4309</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3846,22 +3846,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>45.4</t>
+          <t>45.2</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>46.25</t>
+          <t>45.2</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>45.3</t>
+          <t>44.6</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>45.55</t>
+          <t>44.75</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>112.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>45.05</t>
+          <t>45.55</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-1.36</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-30.74</t>
+          <t>-38.31</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-9.45</t>
+          <t>-8.44</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>3.85</t>
+          <t>2.41</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4029,68 +4029,68 @@
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>82</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>8.93</t>
+          <t>26.79</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>22.13</t>
+          <t>11.9</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-2.32</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-2.65</t>
+          <t>-2.47</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.50</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>46.12</t>
+          <t>45.81</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>46.12</v>
+        <v>46.09</v>
       </c>
       <c r="AN9" t="n">
-        <v>47.37</v>
+        <v>47.26</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>47.49</t>
+          <t>47.5</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-13.12</t>
+          <t>-20.83</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-105.11</t>
+          <t>-105.39</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4110,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>76506.6419400856</t>
+          <t>76405.7329059829</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>5046.0</t>
+          <t>3204.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>10612.2</v>
+        <v>8309.4</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>15323.3</t>
+          <t>13469.3</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>16780.18</v>
+        <v>16218.6</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-4711</t>
+          <t>-5159</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-100.9576738690555</t>
+          <t>-256.304476051831</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-490.8097688649177</t>
+          <t>-1110.711888057096</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>5046.0</t>
+          <t>3204.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-7.59</t>
+          <t>-6.56</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4191,7 +4191,7 @@
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
@@ -4211,7 +4211,7 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4221,12 +4221,12 @@
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>6.01</t>
+          <t>6.04</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>10.38</t>
+          <t>10.34</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>44.86</t>
+          <t>44.93</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>4328</t>
+          <t>4309</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4276,22 +4276,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>44.55</t>
+          <t>45.4</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>45.4</t>
+          <t>46.25</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>44.55</t>
+          <t>45.3</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>45.05</t>
+          <t>45.55</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4313,7 +4313,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>【d】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-3.84</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>315.0</t>
+          <t>112.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>44.8</t>
+          <t>45.05</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,17 +4348,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2.61</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-1.36</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-9.12</t>
+          <t>-30.74</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-9.95</t>
+          <t>-9.45</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10.83</t>
+          <t>3.85</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-4.69</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4459,171 +4459,171 @@
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>82</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>8.93</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>45.15</t>
+          <t>22.13</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-3.92</t>
+          <t>-2.32</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>-2.65</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>-0.25</t>
+        </is>
+      </c>
+      <c r="AL10" t="inlineStr">
+        <is>
+          <t>46.12</t>
+        </is>
+      </c>
+      <c r="AM10" t="n">
+        <v>46.12</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>47.37</v>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>47.49</t>
+        </is>
+      </c>
+      <c r="AP10" t="inlineStr">
+        <is>
+          <t>-13.12</t>
+        </is>
+      </c>
+      <c r="AQ10" t="inlineStr">
+        <is>
+          <t>-0.25</t>
+        </is>
+      </c>
+      <c r="AR10" t="inlineStr">
+        <is>
+          <t>-0.22</t>
+        </is>
+      </c>
+      <c r="AS10" t="inlineStr">
+        <is>
+          <t>4.28</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr">
+        <is>
+          <t>-105.11</t>
+        </is>
+      </c>
+      <c r="AU10" t="inlineStr">
+        <is>
+          <t>2025/11/27</t>
+        </is>
+      </c>
+      <c r="AV10" t="inlineStr">
+        <is>
+          <t>76405.7329059829</t>
+        </is>
+      </c>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>5046.0</t>
+        </is>
+      </c>
+      <c r="AX10" t="n">
+        <v>10612.2</v>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>15323.3</t>
+        </is>
+      </c>
+      <c r="AZ10" t="n">
+        <v>16780.18</v>
+      </c>
+      <c r="BA10" t="inlineStr">
+        <is>
+          <t>-4711</t>
+        </is>
+      </c>
+      <c r="BB10" t="inlineStr">
+        <is>
+          <t>-100.9576738690555</t>
+        </is>
+      </c>
+      <c r="BC10" t="inlineStr">
+        <is>
+          <t>-490.8097688649177</t>
+        </is>
+      </c>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>5046.0</t>
+        </is>
+      </c>
+      <c r="BE10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF10" t="inlineStr">
+        <is>
+          <t>48.75</t>
+        </is>
+      </c>
+      <c r="BG10" t="inlineStr">
+        <is>
+          <t>2025/08/25</t>
+        </is>
+      </c>
+      <c r="BH10" t="inlineStr">
+        <is>
+          <t>-7.59</t>
+        </is>
+      </c>
+      <c r="BI10" t="inlineStr">
+        <is>
+          <t>岱稜</t>
+        </is>
+      </c>
+      <c r="BJ10" t="inlineStr">
+        <is>
+          <t>岱稜</t>
+        </is>
+      </c>
+      <c r="BK10" t="inlineStr">
+        <is>
+          <t>其他電子業</t>
+        </is>
+      </c>
+      <c r="BL10" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BM10" t="inlineStr">
+        <is>
           <t>1.04</t>
         </is>
       </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>-2.8</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>-0.03</t>
-        </is>
-      </c>
-      <c r="AL10" t="inlineStr">
-        <is>
-          <t>46.63</t>
-        </is>
-      </c>
-      <c r="AM10" t="n">
-        <v>46.15</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>47.48</v>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>47.49</t>
-        </is>
-      </c>
-      <c r="AP10" t="inlineStr">
-        <is>
-          <t>27.78</t>
-        </is>
-      </c>
-      <c r="AQ10" t="inlineStr">
-        <is>
-          <t>-0.15</t>
-        </is>
-      </c>
-      <c r="AR10" t="inlineStr">
-        <is>
-          <t>-0.21</t>
-        </is>
-      </c>
-      <c r="AS10" t="inlineStr">
-        <is>
-          <t>4.28</t>
-        </is>
-      </c>
-      <c r="AT10" t="inlineStr">
-        <is>
-          <t>-104.94</t>
-        </is>
-      </c>
-      <c r="AU10" t="inlineStr">
-        <is>
-          <t>2025/11/27</t>
-        </is>
-      </c>
-      <c r="AV10" t="inlineStr">
-        <is>
-          <t>76506.6419400856</t>
-        </is>
-      </c>
-      <c r="AW10" t="inlineStr">
-        <is>
-          <t>14336.0</t>
-        </is>
-      </c>
-      <c r="AX10" t="n">
-        <v>14123</v>
-      </c>
-      <c r="AY10" t="inlineStr">
-        <is>
-          <t>15541.1</t>
-        </is>
-      </c>
-      <c r="AZ10" t="n">
-        <v>17446.4</v>
-      </c>
-      <c r="BA10" t="inlineStr">
-        <is>
-          <t>-1418</t>
-        </is>
-      </c>
-      <c r="BB10" t="inlineStr">
-        <is>
-          <t>-30.07547477889878</t>
-        </is>
-      </c>
-      <c r="BC10" t="inlineStr">
-        <is>
-          <t>214.9364645833703</t>
-        </is>
-      </c>
-      <c r="BD10" t="inlineStr">
-        <is>
-          <t>14336.0</t>
-        </is>
-      </c>
-      <c r="BE10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF10" t="inlineStr">
-        <is>
-          <t>48.75</t>
-        </is>
-      </c>
-      <c r="BG10" t="inlineStr">
-        <is>
-          <t>2025/08/25</t>
-        </is>
-      </c>
-      <c r="BH10" t="inlineStr">
-        <is>
-          <t>-8.10</t>
-        </is>
-      </c>
-      <c r="BI10" t="inlineStr">
-        <is>
-          <t>岱稜</t>
-        </is>
-      </c>
-      <c r="BJ10" t="inlineStr">
-        <is>
-          <t>岱稜</t>
-        </is>
-      </c>
-      <c r="BK10" t="inlineStr">
-        <is>
-          <t>其他電子業</t>
-        </is>
-      </c>
-      <c r="BL10" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BM10" t="inlineStr">
-        <is>
-          <t>1.03</t>
-        </is>
-      </c>
       <c r="BN10" t="inlineStr">
         <is>
           <t>-1.004452687200723</t>
@@ -4641,7 +4641,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4651,12 +4651,12 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>6.01</t>
+          <t>6.04</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>10.38</t>
+          <t>10.34</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>44.86</t>
+          <t>44.93</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>4328</t>
+          <t>4309</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4706,22 +4706,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>46.9</t>
+          <t>44.55</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>46.9</t>
+          <t>45.4</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>44.8</t>
+          <t>44.55</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>44.8</t>
+          <t>45.05</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-0.95</t>
+          <t>-3.84</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>213.0</t>
+          <t>315.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>46.6</t>
+          <t>44.8</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,17 +4778,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-1.3</t>
+          <t>2.18</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-1.36</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>26.53</t>
+          <t>-9.12</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-6.33</t>
+          <t>-9.95</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>7.32</t>
+          <t>10.83</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>-4.69</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4889,68 +4889,68 @@
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>82</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>57.45</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>71.82</t>
+          <t>45.15</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-1.17</t>
+          <t>-3.92</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-2.88</t>
+          <t>-2.8</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>47.15</t>
+          <t>46.63</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>46.22</v>
+        <v>46.15</v>
       </c>
       <c r="AN11" t="n">
-        <v>47.59</v>
+        <v>47.48</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>47.5</t>
+          <t>47.49</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>98.12</t>
+          <t>27.78</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-0.00</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-105.28</t>
+          <t>-104.94</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4970,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>76506.6419400856</t>
+          <t>76405.7329059829</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>9943.0</t>
+          <t>14336.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>18959.2</v>
+        <v>14123</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>14983.4</t>
+          <t>15541.1</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>17743.28</v>
+        <v>17446.4</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>3975</t>
+          <t>-1418</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-74.62310011749315</t>
+          <t>-30.07547477889878</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>220.1119243458033</t>
+          <t>214.9364645833703</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>9943.0</t>
+          <t>14336.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-4.41</t>
+          <t>-8.10</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5051,7 +5051,7 @@
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5081,12 +5081,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>1.89</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>6.01</t>
+          <t>6.04</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>10.38</t>
+          <t>10.34</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>44.86</t>
+          <t>44.93</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>4328</t>
+          <t>4309</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5136,22 +5136,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>47.15</t>
+          <t>46.9</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>47.2</t>
+          <t>46.9</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>46.4</t>
+          <t>44.8</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>46.6</t>
+          <t>44.8</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>-0.95</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>192.0</t>
+          <t>213.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>47.05</t>
+          <t>46.6</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,17 +5208,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-2.28</t>
+          <t>-1.75</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-1.36</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>29.99</t>
+          <t>26.53</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-5.43</t>
+          <t>-6.33</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>6.60</t>
+          <t>7.32</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5319,68 +5319,68 @@
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>82</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>57.45</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>71.82</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>-1.17</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-3.21</t>
+          <t>-2.88</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>47.23</t>
+          <t>47.15</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>46.15</v>
+        <v>46.22</v>
       </c>
       <c r="AN12" t="n">
-        <v>47.68</v>
+        <v>47.59</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>47.48</t>
+          <t>47.5</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>100.64</t>
+          <t>98.12</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.00</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-106.58</t>
+          <t>-105.28</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,43 +5400,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>76506.6419400856</t>
+          <t>76405.7329059829</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>9018.0</t>
+          <t>9943.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>18831.4</v>
+        <v>18959.2</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>14486.8</t>
+          <t>14983.4</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>18676</v>
+        <v>17743.28</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>4344</t>
+          <t>3975</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-128.211286383547</t>
+          <t>-74.62310011749315</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>690.3228695655016</t>
+          <t>220.1119243458033</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>9018.0</t>
+          <t>9943.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-3.49</t>
+          <t>-4.41</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>1.89</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>6.01</t>
+          <t>6.04</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>10.38</t>
+          <t>10.34</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>44.86</t>
+          <t>44.93</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>4328</t>
+          <t>4309</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5566,22 +5566,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>46.5</t>
+          <t>47.15</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>47.5</t>
+          <t>47.2</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>46.35</t>
+          <t>46.4</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>47.05</t>
+          <t>46.6</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/PET膜.xlsx
+++ b/Result/checksun_type/PET膜.xlsx
@@ -883,127 +883,127 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>83.0</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>45.8</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>-1.04</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>-2.42</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>2025-09-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>2025-09-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>2025-03-06 00:00:00</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>2025-03-10 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>51.1</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>49.75</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>57.7</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>56.5</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>-7.94</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>-9.56</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>2025-12-02</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>2.85</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
           <t>-0.43</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>82.0</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>45.8</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>-0.66</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>-20.54</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>2025-09-02 00:00:00</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>2025-09-12 00:00:00</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>2025-03-06 00:00:00</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>2025-03-10 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>51.1</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>49.75</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>57.7</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>56.5</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>-7.94</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>-9.56</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>2025-12-01</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>2.82</t>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>0.00</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>83</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
@@ -1029,58 +1029,58 @@
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>83.86</t>
+          <t>89.33</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-1.87</t>
+          <t>-1.95</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>45.79</t>
+          <t>45.88</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>46.06</v>
+        <v>46.09</v>
       </c>
       <c r="AN2" t="n">
-        <v>46.64</v>
+        <v>46.59</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>47.53</t>
+          <t>47.52</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>15.60</t>
+          <t>18.14</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-106.80</t>
+          <t>-106.51</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,43 +1100,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>76405.7329059829</t>
+          <t>76305.17496443812</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>3779.0</t>
+          <t>3809.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>4604</v>
+        <v>4626.6</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>5794.0</t>
+          <t>4741.3</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>12544.52</v>
+        <v>12259.36</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-1190</t>
+          <t>-114</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-1127.272031156948</t>
+          <t>-1191.289377825079</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-1585.732927737606</t>
+          <t>-1543.3847844998</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>3779.0</t>
+          <t>3809.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1201,7 +1201,7 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1241,7 +1241,7 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>44.93</t>
+          <t>45.09</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
@@ -1266,17 +1266,17 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>46.0</t>
+          <t>46.2</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>46.05</t>
+          <t>46.2</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>45.55</t>
+          <t>45.6</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1313,42 +1313,42 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
+          <t>-0.43</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>45.8</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>75.0</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>46.0</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>-0.44</t>
-        </is>
-      </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-1.04</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-26.22</t>
+          <t>-20.54</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-7.54</t>
+          <t>-7.94</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>2.58</t>
+          <t>2.82</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-0.98</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1449,68 +1449,68 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>83</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>71.07</t>
+          <t>83.86</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>0.68</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-1.76</t>
+          <t>-1.87</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>45.69</t>
+          <t>45.79</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>46.04</v>
+        <v>46.06</v>
       </c>
       <c r="AN3" t="n">
-        <v>46.7</v>
+        <v>46.64</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>47.54</t>
+          <t>47.53</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>12.46</t>
+          <t>15.60</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-107.07</t>
+          <t>-106.80</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1530,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>76405.7329059829</t>
+          <t>76305.17496443812</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>3480.0</t>
+          <t>3779.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>4729.8</v>
+        <v>4604</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>6410.4</t>
+          <t>5794.0</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>12782.88</v>
+        <v>12544.52</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-1680</t>
+          <t>-1190</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-1043.91550450592</t>
+          <t>-1127.272031156948</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-1586.382670658128</t>
+          <t>-1585.732927737606</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>3480.0</t>
+          <t>3779.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-5.64</t>
+          <t>-6.05</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1631,7 +1631,7 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1671,7 +1671,7 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>44.93</t>
+          <t>45.09</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1696,22 +1696,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>46.4</t>
+          <t>46.0</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>46.45</t>
+          <t>46.05</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>46.0</t>
+          <t>45.55</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>46.0</t>
+          <t>45.8</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>116.0</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1773,12 +1773,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-1.04</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-19.32</t>
+          <t>-26.22</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>3.99</t>
+          <t>2.58</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1879,68 +1879,68 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>83</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>67.57</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>46.25</t>
+          <t>71.07</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>0.68</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-1.23</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-1.61</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-1.65</t>
+          <t>-1.76</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>45.44</t>
+          <t>45.69</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>46</v>
+        <v>46.04</v>
       </c>
       <c r="AN4" t="n">
-        <v>46.76</v>
+        <v>46.7</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>47.55</t>
+          <t>47.54</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>12.46</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-107.29</t>
+          <t>-107.07</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1960,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>76405.7329059829</t>
+          <t>76305.17496443812</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>5317.0</t>
+          <t>3480.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>5619</v>
+        <v>4729.8</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>6964.2</t>
+          <t>6410.4</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>13246.56</v>
+        <v>12782.88</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-1345</t>
+          <t>-1680</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-945.2851106600637</t>
+          <t>-1043.91550450592</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-1498.618636592511</t>
+          <t>-1586.382670658128</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>5317.0</t>
+          <t>3480.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2101,7 +2101,7 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>44.93</t>
+          <t>45.09</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -2126,17 +2126,17 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>45.8</t>
+          <t>46.4</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>46.1</t>
+          <t>46.45</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>45.7</t>
+          <t>46.0</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2163,7 +2163,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>148.0</t>
+          <t>116.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>45.8</t>
+          <t>46.0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,17 +2198,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.44</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-1.04</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-34.26</t>
+          <t>-19.32</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-7.94</t>
+          <t>-7.54</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>5.09</t>
+          <t>3.99</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2309,63 +2309,63 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>83</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>45.65</t>
+          <t>67.57</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>30.16</t>
+          <t>46.25</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-1.35</t>
+          <t>-1.23</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-1.85</t>
+          <t>-1.61</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-1.48</t>
+          <t>-1.65</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>45.35</t>
+          <t>45.44</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>45.97</v>
+        <v>46</v>
       </c>
       <c r="AN5" t="n">
-        <v>46.84</v>
+        <v>46.76</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>47.54</t>
+          <t>47.55</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-12.73</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-107.33</t>
+          <t>-107.29</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2390,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>76405.7329059829</t>
+          <t>76305.17496443812</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>6748.0</t>
+          <t>5317.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>5196.4</v>
+        <v>5619</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>7904.3</t>
+          <t>6964.2</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>13455.3</v>
+        <v>13246.56</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-2707</t>
+          <t>-1345</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-844.6790150359823</t>
+          <t>-945.2851106600637</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-1516.540779477615</t>
+          <t>-1498.618636592511</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>6748.0</t>
+          <t>5317.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-6.05</t>
+          <t>-5.64</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2501,7 +2501,7 @@
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2531,7 +2531,7 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>44.93</t>
+          <t>45.09</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
@@ -2556,22 +2556,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>45.45</t>
+          <t>45.8</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>46.15</t>
+          <t>46.1</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>45.35</t>
+          <t>45.7</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>45.8</t>
+          <t>46.0</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>148.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>45.35</t>
+          <t>45.8</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,17 +2628,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-1.04</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-48.83</t>
+          <t>-34.26</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-8.84</t>
+          <t>-7.94</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>2.79</t>
+          <t>5.09</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-1.32</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2739,68 +2739,68 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>83</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>25.53</t>
+          <t>45.65</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>14.94</t>
+          <t>30.16</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-1.67</t>
+          <t>-1.35</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-2.0</t>
+          <t>-1.85</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-1.30</t>
+          <t>-1.48</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>45.2</t>
+          <t>45.35</t>
         </is>
       </c>
       <c r="AM6" t="n">
         <v>45.97</v>
       </c>
       <c r="AN6" t="n">
-        <v>46.91</v>
+        <v>46.84</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>47.52</t>
+          <t>47.54</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-28.10</t>
+          <t>-12.73</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-107.09</t>
+          <t>-107.33</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2820,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>76405.7329059829</t>
+          <t>76305.17496443812</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>3696.0</t>
+          <t>6748.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>4856</v>
+        <v>5196.4</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>9489.5</t>
+          <t>7904.3</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>14335.48</v>
+        <v>13455.3</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-4633</t>
+          <t>-2707</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-722.5223305920491</t>
+          <t>-844.6790150359823</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-1641.303098617845</t>
+          <t>-1516.540779477615</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>3696.0</t>
+          <t>6748.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-6.97</t>
+          <t>-6.05</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2921,7 +2921,7 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2961,7 +2961,7 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>44.93</t>
+          <t>45.09</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>46.0</t>
+          <t>45.45</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>46.0</t>
+          <t>46.15</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>45.3</t>
+          <t>45.35</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>45.35</t>
+          <t>45.8</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>98.0</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>45.3</t>
+          <t>45.35</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-1.04</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-46.16</t>
+          <t>-48.83</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-8.94</t>
+          <t>-8.84</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>3.37</t>
+          <t>2.79</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>-1.32</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3169,231 +3169,231 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>83</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>19.3</t>
+          <t>25.53</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>15.36</t>
+          <t>14.94</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>0.33</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-1.96</t>
+          <t>-1.67</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-2.17</t>
+          <t>-2.0</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-1.05</t>
+          <t>-1.30</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
+          <t>45.2</t>
+        </is>
+      </c>
+      <c r="AM7" t="n">
+        <v>45.97</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>46.91</v>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>47.52</t>
+        </is>
+      </c>
+      <c r="AP7" t="inlineStr">
+        <is>
+          <t>-28.10</t>
+        </is>
+      </c>
+      <c r="AQ7" t="inlineStr">
+        <is>
+          <t>-0.39</t>
+        </is>
+      </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>-0.30</t>
+        </is>
+      </c>
+      <c r="AS7" t="inlineStr">
+        <is>
+          <t>4.28</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr">
+        <is>
+          <t>-107.09</t>
+        </is>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
+          <t>2025/11/27</t>
+        </is>
+      </c>
+      <c r="AV7" t="inlineStr">
+        <is>
+          <t>76305.17496443812</t>
+        </is>
+      </c>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>3696.0</t>
+        </is>
+      </c>
+      <c r="AX7" t="n">
+        <v>4856</v>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>9489.5</t>
+        </is>
+      </c>
+      <c r="AZ7" t="n">
+        <v>14335.48</v>
+      </c>
+      <c r="BA7" t="inlineStr">
+        <is>
+          <t>-4633</t>
+        </is>
+      </c>
+      <c r="BB7" t="inlineStr">
+        <is>
+          <t>-722.5223305920491</t>
+        </is>
+      </c>
+      <c r="BC7" t="inlineStr">
+        <is>
+          <t>-1641.303098617845</t>
+        </is>
+      </c>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>3696.0</t>
+        </is>
+      </c>
+      <c r="BE7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF7" t="inlineStr">
+        <is>
+          <t>48.75</t>
+        </is>
+      </c>
+      <c r="BG7" t="inlineStr">
+        <is>
+          <t>2025/08/25</t>
+        </is>
+      </c>
+      <c r="BH7" t="inlineStr">
+        <is>
+          <t>-6.97</t>
+        </is>
+      </c>
+      <c r="BI7" t="inlineStr">
+        <is>
+          <t>岱稜</t>
+        </is>
+      </c>
+      <c r="BJ7" t="inlineStr">
+        <is>
+          <t>岱稜</t>
+        </is>
+      </c>
+      <c r="BK7" t="inlineStr">
+        <is>
+          <t>其他電子業</t>
+        </is>
+      </c>
+      <c r="BL7" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BM7" t="inlineStr">
+        <is>
+          <t>1.04</t>
+        </is>
+      </c>
+      <c r="BN7" t="inlineStr">
+        <is>
+          <t>-1.004452687200723</t>
+        </is>
+      </c>
+      <c r="BO7" t="inlineStr">
+        <is>
+          <t>11.92388165594906</t>
+        </is>
+      </c>
+      <c r="BP7" t="inlineStr">
+        <is>
+          <t>2.060463205899802</t>
+        </is>
+      </c>
+      <c r="BQ7" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR7" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS7" t="inlineStr">
+        <is>
+          <t>1.84</t>
+        </is>
+      </c>
+      <c r="BT7" t="inlineStr">
+        <is>
+          <t>6.04</t>
+        </is>
+      </c>
+      <c r="BU7" t="inlineStr">
+        <is>
+          <t>8.56</t>
+        </is>
+      </c>
+      <c r="BV7" t="inlineStr">
+        <is>
+          <t>10.34</t>
+        </is>
+      </c>
+      <c r="BW7" t="inlineStr">
+        <is>
+          <t>33.67%</t>
+        </is>
+      </c>
+      <c r="BX7" t="inlineStr">
+        <is>
+          <t>12.48%</t>
+        </is>
+      </c>
+      <c r="BY7" t="inlineStr">
+        <is>
           <t>45.09</t>
         </is>
       </c>
-      <c r="AM7" t="n">
-        <v>45.99</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>47.02</v>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>47.51</t>
-        </is>
-      </c>
-      <c r="AP7" t="inlineStr">
-        <is>
-          <t>-35.53</t>
-        </is>
-      </c>
-      <c r="AQ7" t="inlineStr">
-        <is>
-          <t>-0.38</t>
-        </is>
-      </c>
-      <c r="AR7" t="inlineStr">
-        <is>
-          <t>-0.28</t>
-        </is>
-      </c>
-      <c r="AS7" t="inlineStr">
-        <is>
-          <t>4.28</t>
-        </is>
-      </c>
-      <c r="AT7" t="inlineStr">
-        <is>
-          <t>-106.59</t>
-        </is>
-      </c>
-      <c r="AU7" t="inlineStr">
-        <is>
-          <t>2025/11/27</t>
-        </is>
-      </c>
-      <c r="AV7" t="inlineStr">
-        <is>
-          <t>76405.7329059829</t>
-        </is>
-      </c>
-      <c r="AW7" t="inlineStr">
-        <is>
-          <t>4408.0</t>
-        </is>
-      </c>
-      <c r="AX7" t="n">
-        <v>6984</v>
-      </c>
-      <c r="AY7" t="inlineStr">
-        <is>
-          <t>12971.6</t>
-        </is>
-      </c>
-      <c r="AZ7" t="n">
-        <v>15065.26</v>
-      </c>
-      <c r="BA7" t="inlineStr">
-        <is>
-          <t>-5987</t>
-        </is>
-      </c>
-      <c r="BB7" t="inlineStr">
-        <is>
-          <t>-555.4712818600863</t>
-        </is>
-      </c>
-      <c r="BC7" t="inlineStr">
-        <is>
-          <t>-1433.917015296107</t>
-        </is>
-      </c>
-      <c r="BD7" t="inlineStr">
-        <is>
-          <t>4408.0</t>
-        </is>
-      </c>
-      <c r="BE7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF7" t="inlineStr">
-        <is>
-          <t>48.75</t>
-        </is>
-      </c>
-      <c r="BG7" t="inlineStr">
-        <is>
-          <t>2025/08/25</t>
-        </is>
-      </c>
-      <c r="BH7" t="inlineStr">
-        <is>
-          <t>-7.08</t>
-        </is>
-      </c>
-      <c r="BI7" t="inlineStr">
-        <is>
-          <t>岱稜</t>
-        </is>
-      </c>
-      <c r="BJ7" t="inlineStr">
-        <is>
-          <t>岱稜</t>
-        </is>
-      </c>
-      <c r="BK7" t="inlineStr">
-        <is>
-          <t>其他電子業</t>
-        </is>
-      </c>
-      <c r="BL7" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BM7" t="inlineStr">
-        <is>
-          <t>1.04</t>
-        </is>
-      </c>
-      <c r="BN7" t="inlineStr">
-        <is>
-          <t>-1.004452687200723</t>
-        </is>
-      </c>
-      <c r="BO7" t="inlineStr">
-        <is>
-          <t>11.92388165594906</t>
-        </is>
-      </c>
-      <c r="BP7" t="inlineStr">
-        <is>
-          <t>2.060463205899802</t>
-        </is>
-      </c>
-      <c r="BQ7" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR7" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="BS7" t="inlineStr">
-        <is>
-          <t>1.84</t>
-        </is>
-      </c>
-      <c r="BT7" t="inlineStr">
-        <is>
-          <t>6.04</t>
-        </is>
-      </c>
-      <c r="BU7" t="inlineStr">
-        <is>
-          <t>8.56</t>
-        </is>
-      </c>
-      <c r="BV7" t="inlineStr">
-        <is>
-          <t>10.34</t>
-        </is>
-      </c>
-      <c r="BW7" t="inlineStr">
-        <is>
-          <t>33.67%</t>
-        </is>
-      </c>
-      <c r="BX7" t="inlineStr">
-        <is>
-          <t>12.48%</t>
-        </is>
-      </c>
-      <c r="BY7" t="inlineStr">
-        <is>
-          <t>44.93</t>
-        </is>
-      </c>
       <c r="BZ7" t="inlineStr">
         <is>
           <t>4309</t>
@@ -3416,22 +3416,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>44.95</t>
+          <t>46.0</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>45.45</t>
+          <t>46.0</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>44.9</t>
+          <t>45.3</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>45.3</t>
+          <t>45.35</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-1.77</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>177.0</t>
+          <t>98.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>44.75</t>
+          <t>45.3</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-1.04</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-39.89</t>
+          <t>-46.16</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-10.05</t>
+          <t>-8.94</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>6.09</t>
+          <t>3.37</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3599,68 +3599,68 @@
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>83</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>19.3</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>11.9</t>
+          <t>15.36</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-1.32</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-1.47</t>
+          <t>-1.96</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-2.34</t>
+          <t>-2.17</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>-1.05</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>45.35</t>
+          <t>45.09</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>46.03</v>
+        <v>45.99</v>
       </c>
       <c r="AN8" t="n">
-        <v>47.13</v>
+        <v>47.02</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>47.5</t>
+          <t>47.51</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-41.45</t>
+          <t>-35.53</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-0.36</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-106.01</t>
+          <t>-106.59</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3680,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>76405.7329059829</t>
+          <t>76305.17496443812</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>7926.0</t>
+          <t>4408.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>8091</v>
+        <v>6984</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>13461.2</t>
+          <t>12971.6</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>15558.56</v>
+        <v>15065.26</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-5370</t>
+          <t>-5987</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-395.7538757808097</t>
+          <t>-555.4712818600863</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-1162.725574290193</t>
+          <t>-1433.917015296107</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>7926.0</t>
+          <t>4408.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-8.21</t>
+          <t>-7.08</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3781,7 +3781,7 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -3791,7 +3791,7 @@
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>1.84</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>44.93</t>
+          <t>45.09</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
@@ -3846,22 +3846,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>45.2</t>
+          <t>44.95</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>45.2</t>
+          <t>45.45</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>44.6</t>
+          <t>44.9</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>44.75</t>
+          <t>45.3</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>-1.77</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>177.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>45.55</t>
+          <t>44.75</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-1.04</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-38.31</t>
+          <t>-39.89</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-8.44</t>
+          <t>-10.05</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>2.41</t>
+          <t>6.09</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-0.98</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4029,12 +4029,12 @@
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>83</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>26.79</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
@@ -4044,34 +4044,34 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>-1.32</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>-1.47</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-2.47</t>
+          <t>-2.34</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-0.50</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>45.81</t>
+          <t>45.35</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>46.09</v>
+        <v>46.03</v>
       </c>
       <c r="AN9" t="n">
-        <v>47.26</v>
+        <v>47.13</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
@@ -4080,17 +4080,17 @@
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-20.83</t>
+          <t>-41.45</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>-0.36</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-105.39</t>
+          <t>-106.01</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4110,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>76405.7329059829</t>
+          <t>76305.17496443812</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>3204.0</t>
+          <t>7926.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>8309.4</v>
+        <v>8091</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>13469.3</t>
+          <t>13461.2</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>16218.6</v>
+        <v>15558.56</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-5159</t>
+          <t>-5370</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-256.304476051831</t>
+          <t>-395.7538757808097</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-1110.711888057096</t>
+          <t>-1162.725574290193</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>3204.0</t>
+          <t>7926.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-6.56</t>
+          <t>-8.21</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4211,7 +4211,7 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4221,7 +4221,7 @@
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4251,7 +4251,7 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>44.93</t>
+          <t>45.09</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
@@ -4276,22 +4276,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>45.4</t>
+          <t>45.2</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>46.25</t>
+          <t>45.2</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>45.3</t>
+          <t>44.6</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>45.55</t>
+          <t>44.75</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>112.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>45.05</t>
+          <t>45.55</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,17 +4348,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-1.04</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-30.74</t>
+          <t>-38.31</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-9.45</t>
+          <t>-8.44</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>3.85</t>
+          <t>2.41</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4459,68 +4459,68 @@
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>83</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>8.93</t>
+          <t>26.79</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>22.13</t>
+          <t>11.9</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-2.32</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-2.65</t>
+          <t>-2.47</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.50</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>46.12</t>
+          <t>45.81</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>46.12</v>
+        <v>46.09</v>
       </c>
       <c r="AN10" t="n">
-        <v>47.37</v>
+        <v>47.26</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>47.49</t>
+          <t>47.5</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-13.12</t>
+          <t>-20.83</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-105.11</t>
+          <t>-105.39</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4540,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>76405.7329059829</t>
+          <t>76305.17496443812</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>5046.0</t>
+          <t>3204.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>10612.2</v>
+        <v>8309.4</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>15323.3</t>
+          <t>13469.3</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>16780.18</v>
+        <v>16218.6</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-4711</t>
+          <t>-5159</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-100.9576738690555</t>
+          <t>-256.304476051831</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-490.8097688649177</t>
+          <t>-1110.711888057096</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>5046.0</t>
+          <t>3204.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-7.59</t>
+          <t>-6.56</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4641,17 +4641,17 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4681,7 +4681,7 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>44.93</t>
+          <t>45.09</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -4706,22 +4706,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>44.55</t>
+          <t>45.4</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>45.4</t>
+          <t>46.25</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>44.55</t>
+          <t>45.3</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>45.05</t>
+          <t>45.55</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4743,7 +4743,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>【d】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-3.84</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>315.0</t>
+          <t>112.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>44.8</t>
+          <t>45.05</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,17 +4778,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2.18</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-1.04</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-9.12</t>
+          <t>-30.74</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-9.95</t>
+          <t>-9.45</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10.83</t>
+          <t>3.85</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-4.69</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4889,171 +4889,171 @@
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>83</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>8.93</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>45.15</t>
+          <t>22.13</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-3.92</t>
+          <t>-2.32</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>-2.65</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>-0.25</t>
+        </is>
+      </c>
+      <c r="AL11" t="inlineStr">
+        <is>
+          <t>46.12</t>
+        </is>
+      </c>
+      <c r="AM11" t="n">
+        <v>46.12</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>47.37</v>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>47.49</t>
+        </is>
+      </c>
+      <c r="AP11" t="inlineStr">
+        <is>
+          <t>-13.12</t>
+        </is>
+      </c>
+      <c r="AQ11" t="inlineStr">
+        <is>
+          <t>-0.25</t>
+        </is>
+      </c>
+      <c r="AR11" t="inlineStr">
+        <is>
+          <t>-0.22</t>
+        </is>
+      </c>
+      <c r="AS11" t="inlineStr">
+        <is>
+          <t>4.28</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr">
+        <is>
+          <t>-105.11</t>
+        </is>
+      </c>
+      <c r="AU11" t="inlineStr">
+        <is>
+          <t>2025/11/27</t>
+        </is>
+      </c>
+      <c r="AV11" t="inlineStr">
+        <is>
+          <t>76305.17496443812</t>
+        </is>
+      </c>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>5046.0</t>
+        </is>
+      </c>
+      <c r="AX11" t="n">
+        <v>10612.2</v>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>15323.3</t>
+        </is>
+      </c>
+      <c r="AZ11" t="n">
+        <v>16780.18</v>
+      </c>
+      <c r="BA11" t="inlineStr">
+        <is>
+          <t>-4711</t>
+        </is>
+      </c>
+      <c r="BB11" t="inlineStr">
+        <is>
+          <t>-100.9576738690555</t>
+        </is>
+      </c>
+      <c r="BC11" t="inlineStr">
+        <is>
+          <t>-490.8097688649177</t>
+        </is>
+      </c>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>5046.0</t>
+        </is>
+      </c>
+      <c r="BE11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF11" t="inlineStr">
+        <is>
+          <t>48.75</t>
+        </is>
+      </c>
+      <c r="BG11" t="inlineStr">
+        <is>
+          <t>2025/08/25</t>
+        </is>
+      </c>
+      <c r="BH11" t="inlineStr">
+        <is>
+          <t>-7.59</t>
+        </is>
+      </c>
+      <c r="BI11" t="inlineStr">
+        <is>
+          <t>岱稜</t>
+        </is>
+      </c>
+      <c r="BJ11" t="inlineStr">
+        <is>
+          <t>岱稜</t>
+        </is>
+      </c>
+      <c r="BK11" t="inlineStr">
+        <is>
+          <t>其他電子業</t>
+        </is>
+      </c>
+      <c r="BL11" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BM11" t="inlineStr">
+        <is>
           <t>1.04</t>
         </is>
       </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>-2.8</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>-0.03</t>
-        </is>
-      </c>
-      <c r="AL11" t="inlineStr">
-        <is>
-          <t>46.63</t>
-        </is>
-      </c>
-      <c r="AM11" t="n">
-        <v>46.15</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>47.48</v>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>47.49</t>
-        </is>
-      </c>
-      <c r="AP11" t="inlineStr">
-        <is>
-          <t>27.78</t>
-        </is>
-      </c>
-      <c r="AQ11" t="inlineStr">
-        <is>
-          <t>-0.15</t>
-        </is>
-      </c>
-      <c r="AR11" t="inlineStr">
-        <is>
-          <t>-0.21</t>
-        </is>
-      </c>
-      <c r="AS11" t="inlineStr">
-        <is>
-          <t>4.28</t>
-        </is>
-      </c>
-      <c r="AT11" t="inlineStr">
-        <is>
-          <t>-104.94</t>
-        </is>
-      </c>
-      <c r="AU11" t="inlineStr">
-        <is>
-          <t>2025/11/27</t>
-        </is>
-      </c>
-      <c r="AV11" t="inlineStr">
-        <is>
-          <t>76405.7329059829</t>
-        </is>
-      </c>
-      <c r="AW11" t="inlineStr">
-        <is>
-          <t>14336.0</t>
-        </is>
-      </c>
-      <c r="AX11" t="n">
-        <v>14123</v>
-      </c>
-      <c r="AY11" t="inlineStr">
-        <is>
-          <t>15541.1</t>
-        </is>
-      </c>
-      <c r="AZ11" t="n">
-        <v>17446.4</v>
-      </c>
-      <c r="BA11" t="inlineStr">
-        <is>
-          <t>-1418</t>
-        </is>
-      </c>
-      <c r="BB11" t="inlineStr">
-        <is>
-          <t>-30.07547477889878</t>
-        </is>
-      </c>
-      <c r="BC11" t="inlineStr">
-        <is>
-          <t>214.9364645833703</t>
-        </is>
-      </c>
-      <c r="BD11" t="inlineStr">
-        <is>
-          <t>14336.0</t>
-        </is>
-      </c>
-      <c r="BE11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF11" t="inlineStr">
-        <is>
-          <t>48.75</t>
-        </is>
-      </c>
-      <c r="BG11" t="inlineStr">
-        <is>
-          <t>2025/08/25</t>
-        </is>
-      </c>
-      <c r="BH11" t="inlineStr">
-        <is>
-          <t>-8.10</t>
-        </is>
-      </c>
-      <c r="BI11" t="inlineStr">
-        <is>
-          <t>岱稜</t>
-        </is>
-      </c>
-      <c r="BJ11" t="inlineStr">
-        <is>
-          <t>岱稜</t>
-        </is>
-      </c>
-      <c r="BK11" t="inlineStr">
-        <is>
-          <t>其他電子業</t>
-        </is>
-      </c>
-      <c r="BL11" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BM11" t="inlineStr">
-        <is>
-          <t>1.04</t>
-        </is>
-      </c>
       <c r="BN11" t="inlineStr">
         <is>
           <t>-1.004452687200723</t>
@@ -5071,7 +5071,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5081,7 +5081,7 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5111,7 +5111,7 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>44.93</t>
+          <t>45.09</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5136,22 +5136,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>46.9</t>
+          <t>44.55</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>46.9</t>
+          <t>45.4</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>44.8</t>
+          <t>44.55</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>44.8</t>
+          <t>45.05</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-0.95</t>
+          <t>-3.84</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>213.0</t>
+          <t>315.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>46.6</t>
+          <t>44.8</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,17 +5208,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-1.75</t>
+          <t>2.18</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-1.04</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>26.53</t>
+          <t>-9.12</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-6.33</t>
+          <t>-9.95</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>7.32</t>
+          <t>10.83</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>-4.69</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5319,68 +5319,68 @@
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>83</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>57.45</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>71.82</t>
+          <t>45.15</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-1.17</t>
+          <t>-3.92</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-2.88</t>
+          <t>-2.8</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>47.15</t>
+          <t>46.63</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>46.22</v>
+        <v>46.15</v>
       </c>
       <c r="AN12" t="n">
-        <v>47.59</v>
+        <v>47.48</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>47.5</t>
+          <t>47.49</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>98.12</t>
+          <t>27.78</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.00</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-105.28</t>
+          <t>-104.94</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,43 +5400,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>76405.7329059829</t>
+          <t>76305.17496443812</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>9943.0</t>
+          <t>14336.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>18959.2</v>
+        <v>14123</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>14983.4</t>
+          <t>15541.1</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>17743.28</v>
+        <v>17446.4</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>3975</t>
+          <t>-1418</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-74.62310011749315</t>
+          <t>-30.07547477889878</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>220.1119243458033</t>
+          <t>214.9364645833703</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>9943.0</t>
+          <t>14336.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-4.41</t>
+          <t>-8.10</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5511,7 +5511,7 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>1.89</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5541,7 +5541,7 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>44.93</t>
+          <t>45.09</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -5566,22 +5566,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>47.15</t>
+          <t>46.9</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>47.2</t>
+          <t>46.9</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>46.4</t>
+          <t>44.8</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>46.6</t>
+          <t>44.8</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/PET膜.xlsx
+++ b/Result/checksun_type/PET膜.xlsx
@@ -888,7 +888,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-1.04</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-2.42</t>
+          <t>-14.39</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>2.85</t>
+          <t>2.30</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,12 +1014,12 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>67</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
@@ -1029,7 +1029,7 @@
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>89.33</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
@@ -1039,17 +1039,17 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-1.07</t>
+          <t>-0.87</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-1.95</t>
+          <t>-2.06</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
@@ -1058,29 +1058,29 @@
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>46.09</v>
+        <v>46.12</v>
       </c>
       <c r="AN2" t="n">
-        <v>46.59</v>
+        <v>46.52</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>47.52</t>
+          <t>47.5</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>18.14</t>
+          <t>20.22</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-106.51</t>
+          <t>-106.20</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,43 +1100,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>76305.17496443812</t>
+          <t>76203.3046875</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>3809.0</t>
+          <t>3059.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>4626.6</v>
+        <v>3888.8</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>4741.3</t>
+          <t>4542.6</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>12259.36</v>
+        <v>12062.18</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-114</t>
+          <t>-653</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-1191.289377825079</t>
+          <t>-1243.615083485966</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-1543.3847844998</t>
+          <t>-1531.406464620841</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>3809.0</t>
+          <t>3059.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1201,7 +1201,7 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1241,7 +1241,7 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>45.09</t>
+          <t>46.04</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
@@ -1266,17 +1266,17 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>46.2</t>
+          <t>45.8</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>46.2</t>
+          <t>46.0</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>45.6</t>
+          <t>45.7</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1313,127 +1313,127 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>83.0</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>45.8</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>-2.42</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>2025-09-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>2025-09-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>2025-03-06 00:00:00</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>2025-03-10 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>51.1</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>49.75</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>57.7</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>56.5</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>-7.94</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>-9.56</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-12-02</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>2.85</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
           <t>-0.43</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>82.0</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>45.8</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>-1.04</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>-20.54</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>2025-09-02 00:00:00</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>2025-09-12 00:00:00</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>2025-03-06 00:00:00</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>2025-03-10 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>51.1</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>49.75</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>57.7</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>56.5</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>-7.94</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>-9.56</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>2025-12-01</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>2.82</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>0.00</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,12 +1444,12 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>67</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
@@ -1459,58 +1459,58 @@
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>83.86</t>
+          <t>89.33</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-1.87</t>
+          <t>-1.95</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>45.79</t>
+          <t>45.88</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>46.06</v>
+        <v>46.09</v>
       </c>
       <c r="AN3" t="n">
-        <v>46.64</v>
+        <v>46.59</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>47.53</t>
+          <t>47.52</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>15.60</t>
+          <t>18.14</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-106.80</t>
+          <t>-106.51</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1530,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>76305.17496443812</t>
+          <t>76203.3046875</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>3779.0</t>
+          <t>3809.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>4604</v>
+        <v>4626.6</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>5794.0</t>
+          <t>4741.3</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>12544.52</v>
+        <v>12259.36</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-1190</t>
+          <t>-114</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-1127.272031156948</t>
+          <t>-1191.289377825079</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-1585.732927737606</t>
+          <t>-1543.3847844998</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>3779.0</t>
+          <t>3809.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1631,7 +1631,7 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1671,7 +1671,7 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>45.09</t>
+          <t>46.04</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1696,17 +1696,17 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>46.0</t>
+          <t>46.2</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>46.05</t>
+          <t>46.2</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>45.55</t>
+          <t>45.6</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1743,42 +1743,42 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
+          <t>-0.43</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>45.8</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>75.0</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>46.0</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>-0.44</t>
-        </is>
-      </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-1.04</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-26.22</t>
+          <t>-20.54</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-7.54</t>
+          <t>-7.94</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>2.58</t>
+          <t>2.82</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-0.98</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,73 +1874,73 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>67</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>71.07</t>
+          <t>83.86</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>0.68</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-1.76</t>
+          <t>-1.87</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>45.69</t>
+          <t>45.79</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>46.04</v>
+        <v>46.06</v>
       </c>
       <c r="AN4" t="n">
-        <v>46.7</v>
+        <v>46.64</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>47.54</t>
+          <t>47.53</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>12.46</t>
+          <t>15.60</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-107.07</t>
+          <t>-106.80</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1960,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>76305.17496443812</t>
+          <t>76203.3046875</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>3480.0</t>
+          <t>3779.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>4729.8</v>
+        <v>4604</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>6410.4</t>
+          <t>5794.0</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>12782.88</v>
+        <v>12544.52</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-1680</t>
+          <t>-1190</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-1043.91550450592</t>
+          <t>-1127.272031156948</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-1586.382670658128</t>
+          <t>-1585.732927737606</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>3480.0</t>
+          <t>3779.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-5.64</t>
+          <t>-6.05</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2101,7 +2101,7 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>45.09</t>
+          <t>46.04</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -2126,22 +2126,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>46.4</t>
+          <t>46.0</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>46.45</t>
+          <t>46.05</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>46.0</t>
+          <t>45.55</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>46.0</t>
+          <t>45.8</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>116.0</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2203,12 +2203,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-1.04</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-19.32</t>
+          <t>-26.22</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>3.99</t>
+          <t>2.58</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,73 +2304,73 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>67</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>67.57</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>46.25</t>
+          <t>71.07</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>0.68</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-1.23</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-1.61</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-1.65</t>
+          <t>-1.76</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>45.44</t>
+          <t>45.69</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>46</v>
+        <v>46.04</v>
       </c>
       <c r="AN5" t="n">
-        <v>46.76</v>
+        <v>46.7</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>47.55</t>
+          <t>47.54</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>12.46</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-107.29</t>
+          <t>-107.07</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2390,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>76305.17496443812</t>
+          <t>76203.3046875</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>5317.0</t>
+          <t>3480.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>5619</v>
+        <v>4729.8</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>6964.2</t>
+          <t>6410.4</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>13246.56</v>
+        <v>12782.88</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-1345</t>
+          <t>-1680</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-945.2851106600637</t>
+          <t>-1043.91550450592</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-1498.618636592511</t>
+          <t>-1586.382670658128</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>5317.0</t>
+          <t>3480.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2531,7 +2531,7 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>45.09</t>
+          <t>46.04</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
@@ -2556,17 +2556,17 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>45.8</t>
+          <t>46.4</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>46.1</t>
+          <t>46.45</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>45.7</t>
+          <t>46.0</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2593,7 +2593,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>148.0</t>
+          <t>116.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>45.8</t>
+          <t>46.0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,17 +2628,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
+          <t>-0.44</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>-1.04</t>
-        </is>
-      </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-34.26</t>
+          <t>-19.32</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-7.94</t>
+          <t>-7.54</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>5.09</t>
+          <t>3.99</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,68 +2734,68 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>67</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>45.65</t>
+          <t>67.57</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>30.16</t>
+          <t>46.25</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-1.35</t>
+          <t>-1.23</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-1.85</t>
+          <t>-1.61</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-1.48</t>
+          <t>-1.65</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>45.35</t>
+          <t>45.44</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>45.97</v>
+        <v>46</v>
       </c>
       <c r="AN6" t="n">
-        <v>46.84</v>
+        <v>46.76</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>47.54</t>
+          <t>47.55</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-12.73</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-107.33</t>
+          <t>-107.29</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2820,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>76305.17496443812</t>
+          <t>76203.3046875</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>6748.0</t>
+          <t>5317.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>5196.4</v>
+        <v>5619</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>7904.3</t>
+          <t>6964.2</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>13455.3</v>
+        <v>13246.56</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-2707</t>
+          <t>-1345</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-844.6790150359823</t>
+          <t>-945.2851106600637</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-1516.540779477615</t>
+          <t>-1498.618636592511</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>6748.0</t>
+          <t>5317.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-6.05</t>
+          <t>-5.64</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2921,7 +2921,7 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2961,7 +2961,7 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>45.09</t>
+          <t>46.04</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>45.45</t>
+          <t>45.8</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>46.15</t>
+          <t>46.1</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>45.35</t>
+          <t>45.7</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>45.8</t>
+          <t>46.0</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>148.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>45.35</t>
+          <t>45.8</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-1.04</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-48.83</t>
+          <t>-34.26</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-8.84</t>
+          <t>-7.94</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>2.79</t>
+          <t>5.09</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-1.32</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,73 +3164,73 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>67</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>25.53</t>
+          <t>45.65</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>14.94</t>
+          <t>30.16</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-1.67</t>
+          <t>-1.35</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-2.0</t>
+          <t>-1.85</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-1.30</t>
+          <t>-1.48</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>45.2</t>
+          <t>45.35</t>
         </is>
       </c>
       <c r="AM7" t="n">
         <v>45.97</v>
       </c>
       <c r="AN7" t="n">
-        <v>46.91</v>
+        <v>46.84</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>47.52</t>
+          <t>47.54</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-28.10</t>
+          <t>-12.73</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-107.09</t>
+          <t>-107.33</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3250,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>76305.17496443812</t>
+          <t>76203.3046875</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>3696.0</t>
+          <t>6748.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>4856</v>
+        <v>5196.4</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>9489.5</t>
+          <t>7904.3</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>14335.48</v>
+        <v>13455.3</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-4633</t>
+          <t>-2707</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-722.5223305920491</t>
+          <t>-844.6790150359823</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-1641.303098617845</t>
+          <t>-1516.540779477615</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>3696.0</t>
+          <t>6748.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-6.97</t>
+          <t>-6.05</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3351,7 +3351,7 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3361,7 +3361,7 @@
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>45.09</t>
+          <t>46.04</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3416,22 +3416,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>46.0</t>
+          <t>45.45</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>46.0</t>
+          <t>46.15</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>45.3</t>
+          <t>45.35</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>45.35</t>
+          <t>45.8</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>98.0</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>45.3</t>
+          <t>45.35</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-1.04</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-46.16</t>
+          <t>-48.83</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-8.94</t>
+          <t>-8.84</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>3.37</t>
+          <t>2.79</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>-1.32</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,73 +3594,73 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>67</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>19.3</t>
+          <t>25.53</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>15.36</t>
+          <t>14.94</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>0.33</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-1.96</t>
+          <t>-1.67</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-2.17</t>
+          <t>-2.0</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-1.05</t>
+          <t>-1.30</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>45.09</t>
+          <t>45.2</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>45.99</v>
+        <v>45.97</v>
       </c>
       <c r="AN8" t="n">
-        <v>47.02</v>
+        <v>46.91</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>47.51</t>
+          <t>47.52</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-35.53</t>
+          <t>-28.10</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-106.59</t>
+          <t>-107.09</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3680,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>76305.17496443812</t>
+          <t>76203.3046875</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>4408.0</t>
+          <t>3696.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>6984</v>
+        <v>4856</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>12971.6</t>
+          <t>9489.5</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>15065.26</v>
+        <v>14335.48</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-5987</t>
+          <t>-4633</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-555.4712818600863</t>
+          <t>-722.5223305920491</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-1433.917015296107</t>
+          <t>-1641.303098617845</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>4408.0</t>
+          <t>3696.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-7.08</t>
+          <t>-6.97</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3781,7 +3781,7 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>45.09</t>
+          <t>46.04</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
@@ -3846,22 +3846,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>44.95</t>
+          <t>46.0</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>45.45</t>
+          <t>46.0</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>44.9</t>
+          <t>45.3</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>45.3</t>
+          <t>45.35</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-1.77</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>177.0</t>
+          <t>98.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>44.75</t>
+          <t>45.3</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-1.04</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-39.89</t>
+          <t>-46.16</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-10.05</t>
+          <t>-8.94</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>6.09</t>
+          <t>3.37</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,73 +4024,73 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>67</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>19.3</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>11.9</t>
+          <t>15.36</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-1.32</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-1.47</t>
+          <t>-1.96</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-2.34</t>
+          <t>-2.17</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>-1.05</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>45.35</t>
+          <t>45.09</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>46.03</v>
+        <v>45.99</v>
       </c>
       <c r="AN9" t="n">
-        <v>47.13</v>
+        <v>47.02</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>47.5</t>
+          <t>47.51</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-41.45</t>
+          <t>-35.53</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-0.36</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-106.01</t>
+          <t>-106.59</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4110,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>76305.17496443812</t>
+          <t>76203.3046875</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>7926.0</t>
+          <t>4408.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>8091</v>
+        <v>6984</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>13461.2</t>
+          <t>12971.6</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>15558.56</v>
+        <v>15065.26</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-5370</t>
+          <t>-5987</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-395.7538757808097</t>
+          <t>-555.4712818600863</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-1162.725574290193</t>
+          <t>-1433.917015296107</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>7926.0</t>
+          <t>4408.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-8.21</t>
+          <t>-7.08</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4211,7 +4211,7 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4221,7 +4221,7 @@
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>1.84</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4251,7 +4251,7 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>45.09</t>
+          <t>46.04</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
@@ -4276,22 +4276,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>45.2</t>
+          <t>44.95</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>45.2</t>
+          <t>45.45</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>44.6</t>
+          <t>44.9</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>44.75</t>
+          <t>45.3</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>-1.77</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>177.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>45.55</t>
+          <t>44.75</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,17 +4348,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-1.04</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-38.31</t>
+          <t>-39.89</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-8.44</t>
+          <t>-10.05</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>2.41</t>
+          <t>6.09</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-0.98</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,17 +4454,17 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>67</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>26.79</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
@@ -4474,34 +4474,34 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>-1.32</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>-1.47</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-2.47</t>
+          <t>-2.34</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-0.50</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>45.81</t>
+          <t>45.35</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>46.09</v>
+        <v>46.03</v>
       </c>
       <c r="AN10" t="n">
-        <v>47.26</v>
+        <v>47.13</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
@@ -4510,17 +4510,17 @@
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-20.83</t>
+          <t>-41.45</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>-0.36</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-105.39</t>
+          <t>-106.01</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4540,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>76305.17496443812</t>
+          <t>76203.3046875</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>3204.0</t>
+          <t>7926.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>8309.4</v>
+        <v>8091</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>13469.3</t>
+          <t>13461.2</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>16218.6</v>
+        <v>15558.56</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-5159</t>
+          <t>-5370</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-256.304476051831</t>
+          <t>-395.7538757808097</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-1110.711888057096</t>
+          <t>-1162.725574290193</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>3204.0</t>
+          <t>7926.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-6.56</t>
+          <t>-8.21</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4641,7 +4641,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4681,7 +4681,7 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>45.09</t>
+          <t>46.04</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -4706,22 +4706,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>45.4</t>
+          <t>45.2</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>46.25</t>
+          <t>45.2</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>45.3</t>
+          <t>44.6</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>45.55</t>
+          <t>44.75</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>112.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>45.05</t>
+          <t>45.55</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,17 +4778,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-1.04</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-30.74</t>
+          <t>-38.31</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-9.45</t>
+          <t>-8.44</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>3.85</t>
+          <t>2.41</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,73 +4884,73 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>67</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>8.93</t>
+          <t>26.79</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>22.13</t>
+          <t>11.9</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-2.32</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-2.65</t>
+          <t>-2.47</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.50</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>46.12</t>
+          <t>45.81</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>46.12</v>
+        <v>46.09</v>
       </c>
       <c r="AN11" t="n">
-        <v>47.37</v>
+        <v>47.26</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>47.49</t>
+          <t>47.5</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-13.12</t>
+          <t>-20.83</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-105.11</t>
+          <t>-105.39</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4970,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>76305.17496443812</t>
+          <t>76203.3046875</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>5046.0</t>
+          <t>3204.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>10612.2</v>
+        <v>8309.4</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>15323.3</t>
+          <t>13469.3</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>16780.18</v>
+        <v>16218.6</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-4711</t>
+          <t>-5159</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-100.9576738690555</t>
+          <t>-256.304476051831</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-490.8097688649177</t>
+          <t>-1110.711888057096</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>5046.0</t>
+          <t>3204.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-7.59</t>
+          <t>-6.56</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5081,7 +5081,7 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5111,7 +5111,7 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>45.09</t>
+          <t>46.04</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5136,22 +5136,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>44.55</t>
+          <t>45.4</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>45.4</t>
+          <t>46.25</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>44.55</t>
+          <t>45.3</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>45.05</t>
+          <t>45.55</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5173,7 +5173,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>【d】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-3.84</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>315.0</t>
+          <t>112.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>44.8</t>
+          <t>45.05</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,17 +5208,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2.18</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-1.04</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-9.12</t>
+          <t>-30.74</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-9.95</t>
+          <t>-9.45</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10.83</t>
+          <t>3.85</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-4.69</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,176 +5314,176 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>67</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>8.93</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>45.15</t>
+          <t>22.13</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-3.92</t>
+          <t>-2.32</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>-2.65</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>-0.25</t>
+        </is>
+      </c>
+      <c r="AL12" t="inlineStr">
+        <is>
+          <t>46.12</t>
+        </is>
+      </c>
+      <c r="AM12" t="n">
+        <v>46.12</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>47.37</v>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>47.49</t>
+        </is>
+      </c>
+      <c r="AP12" t="inlineStr">
+        <is>
+          <t>-13.12</t>
+        </is>
+      </c>
+      <c r="AQ12" t="inlineStr">
+        <is>
+          <t>-0.25</t>
+        </is>
+      </c>
+      <c r="AR12" t="inlineStr">
+        <is>
+          <t>-0.22</t>
+        </is>
+      </c>
+      <c r="AS12" t="inlineStr">
+        <is>
+          <t>4.28</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr">
+        <is>
+          <t>-105.11</t>
+        </is>
+      </c>
+      <c r="AU12" t="inlineStr">
+        <is>
+          <t>2025/11/27</t>
+        </is>
+      </c>
+      <c r="AV12" t="inlineStr">
+        <is>
+          <t>76203.3046875</t>
+        </is>
+      </c>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>5046.0</t>
+        </is>
+      </c>
+      <c r="AX12" t="n">
+        <v>10612.2</v>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>15323.3</t>
+        </is>
+      </c>
+      <c r="AZ12" t="n">
+        <v>16780.18</v>
+      </c>
+      <c r="BA12" t="inlineStr">
+        <is>
+          <t>-4711</t>
+        </is>
+      </c>
+      <c r="BB12" t="inlineStr">
+        <is>
+          <t>-100.9576738690555</t>
+        </is>
+      </c>
+      <c r="BC12" t="inlineStr">
+        <is>
+          <t>-490.8097688649177</t>
+        </is>
+      </c>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>5046.0</t>
+        </is>
+      </c>
+      <c r="BE12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF12" t="inlineStr">
+        <is>
+          <t>48.75</t>
+        </is>
+      </c>
+      <c r="BG12" t="inlineStr">
+        <is>
+          <t>2025/08/25</t>
+        </is>
+      </c>
+      <c r="BH12" t="inlineStr">
+        <is>
+          <t>-7.59</t>
+        </is>
+      </c>
+      <c r="BI12" t="inlineStr">
+        <is>
+          <t>岱稜</t>
+        </is>
+      </c>
+      <c r="BJ12" t="inlineStr">
+        <is>
+          <t>岱稜</t>
+        </is>
+      </c>
+      <c r="BK12" t="inlineStr">
+        <is>
+          <t>其他電子業</t>
+        </is>
+      </c>
+      <c r="BL12" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BM12" t="inlineStr">
+        <is>
           <t>1.04</t>
         </is>
       </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>-2.8</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>-0.03</t>
-        </is>
-      </c>
-      <c r="AL12" t="inlineStr">
-        <is>
-          <t>46.63</t>
-        </is>
-      </c>
-      <c r="AM12" t="n">
-        <v>46.15</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>47.48</v>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>47.49</t>
-        </is>
-      </c>
-      <c r="AP12" t="inlineStr">
-        <is>
-          <t>27.78</t>
-        </is>
-      </c>
-      <c r="AQ12" t="inlineStr">
-        <is>
-          <t>-0.15</t>
-        </is>
-      </c>
-      <c r="AR12" t="inlineStr">
-        <is>
-          <t>-0.21</t>
-        </is>
-      </c>
-      <c r="AS12" t="inlineStr">
-        <is>
-          <t>4.28</t>
-        </is>
-      </c>
-      <c r="AT12" t="inlineStr">
-        <is>
-          <t>-104.94</t>
-        </is>
-      </c>
-      <c r="AU12" t="inlineStr">
-        <is>
-          <t>2025/11/27</t>
-        </is>
-      </c>
-      <c r="AV12" t="inlineStr">
-        <is>
-          <t>76305.17496443812</t>
-        </is>
-      </c>
-      <c r="AW12" t="inlineStr">
-        <is>
-          <t>14336.0</t>
-        </is>
-      </c>
-      <c r="AX12" t="n">
-        <v>14123</v>
-      </c>
-      <c r="AY12" t="inlineStr">
-        <is>
-          <t>15541.1</t>
-        </is>
-      </c>
-      <c r="AZ12" t="n">
-        <v>17446.4</v>
-      </c>
-      <c r="BA12" t="inlineStr">
-        <is>
-          <t>-1418</t>
-        </is>
-      </c>
-      <c r="BB12" t="inlineStr">
-        <is>
-          <t>-30.07547477889878</t>
-        </is>
-      </c>
-      <c r="BC12" t="inlineStr">
-        <is>
-          <t>214.9364645833703</t>
-        </is>
-      </c>
-      <c r="BD12" t="inlineStr">
-        <is>
-          <t>14336.0</t>
-        </is>
-      </c>
-      <c r="BE12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF12" t="inlineStr">
-        <is>
-          <t>48.75</t>
-        </is>
-      </c>
-      <c r="BG12" t="inlineStr">
-        <is>
-          <t>2025/08/25</t>
-        </is>
-      </c>
-      <c r="BH12" t="inlineStr">
-        <is>
-          <t>-8.10</t>
-        </is>
-      </c>
-      <c r="BI12" t="inlineStr">
-        <is>
-          <t>岱稜</t>
-        </is>
-      </c>
-      <c r="BJ12" t="inlineStr">
-        <is>
-          <t>岱稜</t>
-        </is>
-      </c>
-      <c r="BK12" t="inlineStr">
-        <is>
-          <t>其他電子業</t>
-        </is>
-      </c>
-      <c r="BL12" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BM12" t="inlineStr">
-        <is>
-          <t>1.04</t>
-        </is>
-      </c>
       <c r="BN12" t="inlineStr">
         <is>
           <t>-1.004452687200723</t>
@@ -5501,7 +5501,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5511,7 +5511,7 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5541,7 +5541,7 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>45.09</t>
+          <t>46.04</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -5566,22 +5566,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>46.9</t>
+          <t>44.55</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>46.9</t>
+          <t>45.4</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>44.8</t>
+          <t>44.55</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>44.8</t>
+          <t>45.05</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/PET膜.xlsx
+++ b/Result/checksun_type/PET膜.xlsx
@@ -883,42 +883,42 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>-0.65</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>101.0</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>45.5</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>67.0</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>45.8</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-14.39</t>
+          <t>-20.03</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-7.94</t>
+          <t>-8.54</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>2.30</t>
+          <t>3.47</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,68 +1014,68 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>101</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>28.57</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>65.52</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-0.87</t>
+          <t>-0.89</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-2.06</t>
+          <t>-2.14</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>45.88</t>
+          <t>45.77999999999999</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>46.12</v>
+        <v>46.04</v>
       </c>
       <c r="AN2" t="n">
-        <v>46.52</v>
+        <v>46.46</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>47.5</t>
+          <t>47.48</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>20.22</t>
+          <t>14.06</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-106.20</t>
+          <t>-105.99</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,43 +1100,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>76203.3046875</t>
+          <t>76104.98085106382</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>3059.0</t>
+          <t>4590.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>3888.8</v>
+        <v>3743.4</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>4542.6</t>
+          <t>4681.2</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>12062.18</v>
+        <v>12007.9</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-653</t>
+          <t>-937</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-1243.615083485966</t>
+          <t>-1263.045298194286</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-1531.406464620841</t>
+          <t>-1369.911479090048</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>3059.0</t>
+          <t>4590.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-6.05</t>
+          <t>-6.67</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1201,7 +1201,7 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1211,12 +1211,12 @@
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>6.04</t>
+          <t>6.08</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>10.34</t>
+          <t>10.27</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>46.04</t>
+          <t>46.3</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>4309</t>
+          <t>4281</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,22 +1266,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>45.8</t>
+          <t>46.0</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>46.0</t>
+          <t>46.05</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>45.7</t>
+          <t>45.15</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>45.8</t>
+          <t>45.5</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1338,17 +1338,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
+          <t>-0.66</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-2.42</t>
+          <t>-14.39</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>2.85</t>
+          <t>2.30</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,12 +1444,12 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>101</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
@@ -1459,7 +1459,7 @@
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>89.33</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
@@ -1469,17 +1469,17 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-1.07</t>
+          <t>-0.87</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-1.95</t>
+          <t>-2.06</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
@@ -1488,29 +1488,29 @@
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>46.09</v>
+        <v>46.12</v>
       </c>
       <c r="AN3" t="n">
-        <v>46.59</v>
+        <v>46.52</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>47.52</t>
+          <t>47.5</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>18.14</t>
+          <t>20.22</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-106.51</t>
+          <t>-106.20</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1530,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>76203.3046875</t>
+          <t>76104.98085106382</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>3809.0</t>
+          <t>3059.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>4626.6</v>
+        <v>3888.8</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>4741.3</t>
+          <t>4542.6</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>12259.36</v>
+        <v>12062.18</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-114</t>
+          <t>-653</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-1191.289377825079</t>
+          <t>-1243.615083485966</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-1543.3847844998</t>
+          <t>-1531.406464620841</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>3809.0</t>
+          <t>3059.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1631,7 +1631,7 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1646,7 +1646,7 @@
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>6.04</t>
+          <t>6.08</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>10.34</t>
+          <t>10.27</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>46.04</t>
+          <t>46.3</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>4309</t>
+          <t>4281</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,17 +1696,17 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>46.2</t>
+          <t>45.8</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>46.2</t>
+          <t>46.0</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>45.6</t>
+          <t>45.7</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1743,127 +1743,127 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>83.0</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>45.8</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>-0.66</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>-2.42</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>2025-09-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>2025-09-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>2025-03-06 00:00:00</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>2025-03-10 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>51.1</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>49.75</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>57.7</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>56.5</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>-7.94</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>-9.56</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-12-02</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>2.85</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
           <t>-0.43</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>82.0</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>45.8</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>-20.54</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>2025-09-02 00:00:00</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>2025-09-12 00:00:00</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>2025-03-06 00:00:00</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>2025-03-10 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>51.1</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>49.75</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>57.7</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>56.5</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>-7.94</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>-9.56</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>2025-12-01</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>2.82</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>0.00</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,12 +1874,12 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>101</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
@@ -1889,58 +1889,58 @@
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>83.86</t>
+          <t>89.33</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-1.87</t>
+          <t>-1.95</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>45.79</t>
+          <t>45.88</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>46.06</v>
+        <v>46.09</v>
       </c>
       <c r="AN4" t="n">
-        <v>46.64</v>
+        <v>46.59</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>47.53</t>
+          <t>47.52</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>15.60</t>
+          <t>18.14</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-106.80</t>
+          <t>-106.51</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1960,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>76203.3046875</t>
+          <t>76104.98085106382</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>3779.0</t>
+          <t>3809.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>4604</v>
+        <v>4626.6</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>5794.0</t>
+          <t>4741.3</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>12544.52</v>
+        <v>12259.36</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-1190</t>
+          <t>-114</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-1127.272031156948</t>
+          <t>-1191.289377825079</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-1585.732927737606</t>
+          <t>-1543.3847844998</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>3779.0</t>
+          <t>3809.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2076,7 +2076,7 @@
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>6.04</t>
+          <t>6.08</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>10.34</t>
+          <t>10.27</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>46.04</t>
+          <t>46.3</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>4309</t>
+          <t>4281</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,17 +2126,17 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>46.0</t>
+          <t>46.2</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>46.05</t>
+          <t>46.2</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>45.55</t>
+          <t>45.6</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2173,42 +2173,42 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
+          <t>-0.43</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>45.8</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>-0.66</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>75.0</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>46.0</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>-0.44</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-26.22</t>
+          <t>-20.54</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-7.54</t>
+          <t>-7.94</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>2.58</t>
+          <t>2.82</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-0.98</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,73 +2304,73 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>101</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>71.07</t>
+          <t>83.86</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>0.68</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-1.76</t>
+          <t>-1.87</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>45.69</t>
+          <t>45.79</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>46.04</v>
+        <v>46.06</v>
       </c>
       <c r="AN5" t="n">
-        <v>46.7</v>
+        <v>46.64</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>47.54</t>
+          <t>47.53</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>12.46</t>
+          <t>15.60</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-107.07</t>
+          <t>-106.80</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2390,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>76203.3046875</t>
+          <t>76104.98085106382</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>3480.0</t>
+          <t>3779.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>4729.8</v>
+        <v>4604</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>6410.4</t>
+          <t>5794.0</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>12782.88</v>
+        <v>12544.52</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-1680</t>
+          <t>-1190</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-1043.91550450592</t>
+          <t>-1127.272031156948</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-1586.382670658128</t>
+          <t>-1585.732927737606</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>3480.0</t>
+          <t>3779.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-5.64</t>
+          <t>-6.05</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2501,12 +2501,12 @@
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>6.04</t>
+          <t>6.08</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>10.34</t>
+          <t>10.27</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>46.04</t>
+          <t>46.3</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>4309</t>
+          <t>4281</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,22 +2556,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>46.4</t>
+          <t>46.0</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>46.45</t>
+          <t>46.05</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>46.0</t>
+          <t>45.55</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>46.0</t>
+          <t>45.8</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>116.0</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2628,7 +2628,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>-1.1</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -2638,7 +2638,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-19.32</t>
+          <t>-26.22</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>3.99</t>
+          <t>2.58</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,73 +2734,73 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>101</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>67.57</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>46.25</t>
+          <t>71.07</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>0.68</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-1.23</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-1.61</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-1.65</t>
+          <t>-1.76</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>45.44</t>
+          <t>45.69</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>46</v>
+        <v>46.04</v>
       </c>
       <c r="AN6" t="n">
-        <v>46.76</v>
+        <v>46.7</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>47.55</t>
+          <t>47.54</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>12.46</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-107.29</t>
+          <t>-107.07</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2820,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>76203.3046875</t>
+          <t>76104.98085106382</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>5317.0</t>
+          <t>3480.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>5619</v>
+        <v>4729.8</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>6964.2</t>
+          <t>6410.4</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>13246.56</v>
+        <v>12782.88</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-1345</t>
+          <t>-1680</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-945.2851106600637</t>
+          <t>-1043.91550450592</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-1498.618636592511</t>
+          <t>-1586.382670658128</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>5317.0</t>
+          <t>3480.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2921,7 +2921,7 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>6.04</t>
+          <t>6.08</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>10.34</t>
+          <t>10.27</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>46.04</t>
+          <t>46.3</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>4309</t>
+          <t>4281</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,17 +2986,17 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>45.8</t>
+          <t>46.4</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>46.1</t>
+          <t>46.45</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>45.7</t>
+          <t>46.0</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -3023,7 +3023,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>148.0</t>
+          <t>116.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>45.8</t>
+          <t>46.0</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
+          <t>-1.1</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-34.26</t>
+          <t>-19.32</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-7.94</t>
+          <t>-7.54</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>5.09</t>
+          <t>3.99</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,68 +3164,68 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>101</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>45.65</t>
+          <t>67.57</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>30.16</t>
+          <t>46.25</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-1.35</t>
+          <t>-1.23</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-1.85</t>
+          <t>-1.61</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-1.48</t>
+          <t>-1.65</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>45.35</t>
+          <t>45.44</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>45.97</v>
+        <v>46</v>
       </c>
       <c r="AN7" t="n">
-        <v>46.84</v>
+        <v>46.76</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>47.54</t>
+          <t>47.55</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-12.73</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-107.33</t>
+          <t>-107.29</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3250,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>76203.3046875</t>
+          <t>76104.98085106382</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>6748.0</t>
+          <t>5317.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>5196.4</v>
+        <v>5619</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>7904.3</t>
+          <t>6964.2</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>13455.3</v>
+        <v>13246.56</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-2707</t>
+          <t>-1345</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-844.6790150359823</t>
+          <t>-945.2851106600637</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-1516.540779477615</t>
+          <t>-1498.618636592511</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>6748.0</t>
+          <t>5317.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-6.05</t>
+          <t>-5.64</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3351,7 +3351,7 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3361,12 +3361,12 @@
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>6.04</t>
+          <t>6.08</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>10.34</t>
+          <t>10.27</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>46.04</t>
+          <t>46.3</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>4309</t>
+          <t>4281</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3416,22 +3416,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>45.45</t>
+          <t>45.8</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>46.15</t>
+          <t>46.1</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>45.35</t>
+          <t>45.7</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>45.8</t>
+          <t>46.0</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>148.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>45.35</t>
+          <t>45.8</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,7 +3488,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -3498,7 +3498,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-48.83</t>
+          <t>-34.26</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-8.84</t>
+          <t>-7.94</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>2.79</t>
+          <t>5.09</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-1.32</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,73 +3594,73 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>101</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>25.53</t>
+          <t>45.65</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>14.94</t>
+          <t>30.16</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-1.67</t>
+          <t>-1.35</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-2.0</t>
+          <t>-1.85</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-1.30</t>
+          <t>-1.48</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>45.2</t>
+          <t>45.35</t>
         </is>
       </c>
       <c r="AM8" t="n">
         <v>45.97</v>
       </c>
       <c r="AN8" t="n">
-        <v>46.91</v>
+        <v>46.84</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>47.52</t>
+          <t>47.54</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-28.10</t>
+          <t>-12.73</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-107.09</t>
+          <t>-107.33</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3680,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>76203.3046875</t>
+          <t>76104.98085106382</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>3696.0</t>
+          <t>6748.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>4856</v>
+        <v>5196.4</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>9489.5</t>
+          <t>7904.3</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>14335.48</v>
+        <v>13455.3</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-4633</t>
+          <t>-2707</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-722.5223305920491</t>
+          <t>-844.6790150359823</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-1641.303098617845</t>
+          <t>-1516.540779477615</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>3696.0</t>
+          <t>6748.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-6.97</t>
+          <t>-6.05</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3781,7 +3781,7 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -3791,12 +3791,12 @@
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>6.04</t>
+          <t>6.08</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>10.34</t>
+          <t>10.27</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3821,12 +3821,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>46.04</t>
+          <t>46.3</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>4309</t>
+          <t>4281</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3846,22 +3846,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>46.0</t>
+          <t>45.45</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>46.0</t>
+          <t>46.15</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>45.3</t>
+          <t>45.35</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>45.35</t>
+          <t>45.8</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>98.0</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>45.3</t>
+          <t>45.35</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,7 +3918,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>0.33</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -3928,7 +3928,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-46.16</t>
+          <t>-48.83</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-8.94</t>
+          <t>-8.84</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>3.37</t>
+          <t>2.79</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>-1.32</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,73 +4024,73 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>101</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>19.3</t>
+          <t>25.53</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>15.36</t>
+          <t>14.94</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>0.33</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-1.96</t>
+          <t>-1.67</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-2.17</t>
+          <t>-2.0</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-1.05</t>
+          <t>-1.30</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>45.09</t>
+          <t>45.2</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>45.99</v>
+        <v>45.97</v>
       </c>
       <c r="AN9" t="n">
-        <v>47.02</v>
+        <v>46.91</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>47.51</t>
+          <t>47.52</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-35.53</t>
+          <t>-28.10</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-106.59</t>
+          <t>-107.09</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4110,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>76203.3046875</t>
+          <t>76104.98085106382</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>4408.0</t>
+          <t>3696.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>6984</v>
+        <v>4856</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>12971.6</t>
+          <t>9489.5</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>15065.26</v>
+        <v>14335.48</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-5987</t>
+          <t>-4633</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-555.4712818600863</t>
+          <t>-722.5223305920491</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-1433.917015296107</t>
+          <t>-1641.303098617845</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>4408.0</t>
+          <t>3696.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-7.08</t>
+          <t>-6.97</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4211,7 +4211,7 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4226,7 +4226,7 @@
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>6.04</t>
+          <t>6.08</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>10.34</t>
+          <t>10.27</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>46.04</t>
+          <t>46.3</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>4309</t>
+          <t>4281</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4276,22 +4276,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>44.95</t>
+          <t>46.0</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>45.45</t>
+          <t>46.0</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>44.9</t>
+          <t>45.3</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>45.3</t>
+          <t>45.35</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-1.77</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>177.0</t>
+          <t>98.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>44.75</t>
+          <t>45.3</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,7 +4348,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -4358,7 +4358,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-39.89</t>
+          <t>-46.16</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-10.05</t>
+          <t>-8.94</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>6.09</t>
+          <t>3.37</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,73 +4454,73 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>101</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>19.3</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>11.9</t>
+          <t>15.36</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-1.32</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-1.47</t>
+          <t>-1.96</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-2.34</t>
+          <t>-2.17</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>-1.05</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>45.35</t>
+          <t>45.09</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>46.03</v>
+        <v>45.99</v>
       </c>
       <c r="AN10" t="n">
-        <v>47.13</v>
+        <v>47.02</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>47.5</t>
+          <t>47.51</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-41.45</t>
+          <t>-35.53</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-0.36</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-106.01</t>
+          <t>-106.59</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4540,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>76203.3046875</t>
+          <t>76104.98085106382</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>7926.0</t>
+          <t>4408.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>8091</v>
+        <v>6984</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>13461.2</t>
+          <t>12971.6</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>15558.56</v>
+        <v>15065.26</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-5370</t>
+          <t>-5987</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-395.7538757808097</t>
+          <t>-555.4712818600863</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-1162.725574290193</t>
+          <t>-1433.917015296107</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>7926.0</t>
+          <t>4408.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-8.21</t>
+          <t>-7.08</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4641,7 +4641,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4651,12 +4651,12 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>1.84</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>6.04</t>
+          <t>6.08</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>10.34</t>
+          <t>10.27</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>46.04</t>
+          <t>46.3</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>4309</t>
+          <t>4281</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4706,22 +4706,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>45.2</t>
+          <t>44.95</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>45.2</t>
+          <t>45.45</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>44.6</t>
+          <t>44.9</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>44.75</t>
+          <t>45.3</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>-1.77</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>177.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>45.55</t>
+          <t>44.75</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,7 +4778,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -4788,7 +4788,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-38.31</t>
+          <t>-39.89</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-8.44</t>
+          <t>-10.05</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>2.41</t>
+          <t>6.09</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-0.98</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,17 +4884,17 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>101</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>26.79</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
@@ -4904,34 +4904,34 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>-1.32</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>-1.47</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-2.47</t>
+          <t>-2.34</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-0.50</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>45.81</t>
+          <t>45.35</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>46.09</v>
+        <v>46.03</v>
       </c>
       <c r="AN11" t="n">
-        <v>47.26</v>
+        <v>47.13</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
@@ -4940,17 +4940,17 @@
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-20.83</t>
+          <t>-41.45</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>-0.36</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-105.39</t>
+          <t>-106.01</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4970,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>76203.3046875</t>
+          <t>76104.98085106382</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>3204.0</t>
+          <t>7926.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>8309.4</v>
+        <v>8091</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>13469.3</t>
+          <t>13461.2</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>16218.6</v>
+        <v>15558.56</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-5159</t>
+          <t>-5370</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-256.304476051831</t>
+          <t>-395.7538757808097</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-1110.711888057096</t>
+          <t>-1162.725574290193</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>3204.0</t>
+          <t>7926.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-6.56</t>
+          <t>-8.21</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5081,12 +5081,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>6.04</t>
+          <t>6.08</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>10.34</t>
+          <t>10.27</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>46.04</t>
+          <t>46.3</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>4309</t>
+          <t>4281</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5136,22 +5136,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>45.4</t>
+          <t>45.2</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>46.25</t>
+          <t>45.2</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>45.3</t>
+          <t>44.6</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>45.55</t>
+          <t>44.75</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>112.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>45.05</t>
+          <t>45.55</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,7 +5208,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -5218,7 +5218,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-30.74</t>
+          <t>-38.31</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-9.45</t>
+          <t>-8.44</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>3.85</t>
+          <t>2.41</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,73 +5314,73 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>101</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>8.93</t>
+          <t>26.79</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>22.13</t>
+          <t>11.9</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-2.32</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-2.65</t>
+          <t>-2.47</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.50</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>46.12</t>
+          <t>45.81</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>46.12</v>
+        <v>46.09</v>
       </c>
       <c r="AN12" t="n">
-        <v>47.37</v>
+        <v>47.26</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>47.49</t>
+          <t>47.5</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-13.12</t>
+          <t>-20.83</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-105.11</t>
+          <t>-105.39</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,43 +5400,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>76203.3046875</t>
+          <t>76104.98085106382</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>5046.0</t>
+          <t>3204.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>10612.2</v>
+        <v>8309.4</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>15323.3</t>
+          <t>13469.3</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>16780.18</v>
+        <v>16218.6</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-4711</t>
+          <t>-5159</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-100.9576738690555</t>
+          <t>-256.304476051831</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-490.8097688649177</t>
+          <t>-1110.711888057096</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>5046.0</t>
+          <t>3204.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-7.59</t>
+          <t>-6.56</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>6.04</t>
+          <t>6.08</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>10.34</t>
+          <t>10.27</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>46.04</t>
+          <t>46.3</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>4309</t>
+          <t>4281</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5566,22 +5566,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>44.55</t>
+          <t>45.4</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>45.4</t>
+          <t>46.25</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>44.55</t>
+          <t>45.3</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>45.05</t>
+          <t>45.55</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/PET膜.xlsx
+++ b/Result/checksun_type/PET膜.xlsx
@@ -871,11 +871,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>【d】</t>
-        </is>
-      </c>
+      <c r="A2" t="inlineStr"/>
       <c r="B2" t="inlineStr">
         <is>
           <t>3303</t>
@@ -883,12 +879,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>-0.55</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>104.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +894,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>45.5</t>
+          <t>45.25</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -918,7 +914,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-20.03</t>
+          <t>-8.48</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +979,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-8.54</t>
+          <t>-9.05</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +989,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>3.47</t>
+          <t>3.58</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,74 +1010,66 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>104</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>28.57</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>65.52</t>
-        </is>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>-0.61</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>-0.58</t>
-        </is>
+          <t>37.52</t>
+        </is>
+      </c>
+      <c r="AH2" t="n">
+        <v>-0.83</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>-0.75</v>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-0.89</t>
+          <t>-0.9</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-2.14</t>
+          <t>-2.24</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>45.77999999999999</t>
+          <t>45.63</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>46.04</v>
+        <v>45.98</v>
       </c>
       <c r="AN2" t="n">
-        <v>46.46</v>
+        <v>46.39</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>47.48</t>
+          <t>47.46</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>14.06</t>
-        </is>
-      </c>
-      <c r="AQ2" t="inlineStr">
-        <is>
-          <t>-0.22</t>
-        </is>
-      </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>-0.26</t>
-        </is>
+          <t>3.73</t>
+        </is>
+      </c>
+      <c r="AQ2" t="n">
+        <v>-0.24</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>-0.25</v>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
@@ -1090,7 +1078,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-105.99</t>
+          <t>-105.93</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,43 +1088,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>76104.98085106382</t>
+          <t>76007.19900849859</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>4590.0</t>
+          <t>4714.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>3743.4</v>
+        <v>3990.2</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>4681.2</t>
+          <t>4360.0</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>12007.9</v>
+        <v>11948.92</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-937</t>
+          <t>-369</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-1263.045298194286</t>
+          <t>-1255.394821893818</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-1369.911479090048</t>
+          <t>-1213.317202241243</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>4590.0</t>
+          <t>4714.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1156,7 +1144,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-6.67</t>
+          <t>-7.18</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1201,7 +1189,7 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1211,12 +1199,12 @@
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>6.08</t>
+          <t>6.11</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1226,7 +1214,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>10.27</t>
+          <t>10.21</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1241,12 +1229,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>46.3</t>
+          <t>46.08</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>4281</t>
+          <t>4258</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,22 +1254,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>46.0</t>
+          <t>45.5</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>46.05</t>
+          <t>45.5</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>45.15</t>
+          <t>44.9</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>45.5</t>
+          <t>45.25</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1301,11 +1289,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>【d】</t>
-        </is>
-      </c>
+      <c r="A3" t="inlineStr"/>
       <c r="B3" t="inlineStr">
         <is>
           <t>3303</t>
@@ -1313,42 +1297,42 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
+          <t>-0.65</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>101.0</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>45.5</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>-0.55</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>67.0</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>45.8</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>-0.66</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-14.39</t>
+          <t>-20.03</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1413,7 +1397,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-7.94</t>
+          <t>-8.54</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1423,17 +1407,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>2.30</t>
+          <t>3.47</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,74 +1428,66 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>104</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>28.57</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>84.0</t>
-        </is>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>-0.17</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>-0.52</t>
-        </is>
+          <t>65.52</t>
+        </is>
+      </c>
+      <c r="AH3" t="n">
+        <v>-0.61</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>-0.58</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-0.87</t>
+          <t>-0.89</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-2.06</t>
+          <t>-2.14</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>45.88</t>
+          <t>45.77999999999999</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>46.12</v>
+        <v>46.04</v>
       </c>
       <c r="AN3" t="n">
-        <v>46.52</v>
+        <v>46.46</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>47.5</t>
+          <t>47.48</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>20.22</t>
-        </is>
-      </c>
-      <c r="AQ3" t="inlineStr">
-        <is>
-          <t>-0.21</t>
-        </is>
-      </c>
-      <c r="AR3" t="inlineStr">
-        <is>
-          <t>-0.26</t>
-        </is>
+          <t>14.06</t>
+        </is>
+      </c>
+      <c r="AQ3" t="n">
+        <v>-0.22</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>-0.26</v>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
@@ -1520,7 +1496,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-106.20</t>
+          <t>-105.99</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1506,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>76104.98085106382</t>
+          <t>76007.19900849859</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>3059.0</t>
+          <t>4590.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>3888.8</v>
+        <v>3743.4</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>4542.6</t>
+          <t>4681.2</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>12062.18</v>
+        <v>12007.9</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-653</t>
+          <t>-937</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-1243.615083485966</t>
+          <t>-1263.045298194286</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-1531.406464620841</t>
+          <t>-1369.911479090048</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>3059.0</t>
+          <t>4590.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1586,7 +1562,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-6.05</t>
+          <t>-6.67</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1631,7 +1607,7 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1641,12 +1617,12 @@
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>6.08</t>
+          <t>6.11</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1656,7 +1632,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>10.27</t>
+          <t>10.21</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1671,12 +1647,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>46.3</t>
+          <t>46.08</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>4281</t>
+          <t>4258</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,22 +1672,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>45.8</t>
+          <t>46.0</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>46.0</t>
+          <t>46.05</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>45.7</t>
+          <t>45.15</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>45.8</t>
+          <t>45.5</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1731,11 +1707,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>【d】</t>
-        </is>
-      </c>
+      <c r="A4" t="inlineStr"/>
       <c r="B4" t="inlineStr">
         <is>
           <t>3303</t>
@@ -1748,7 +1720,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1768,7 +1740,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-1.22</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1778,7 +1750,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-2.42</t>
+          <t>-14.39</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1853,17 +1825,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>2.85</t>
+          <t>2.30</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,12 +1846,12 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>104</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
@@ -1889,27 +1861,23 @@
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>89.33</t>
-        </is>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>-0.17</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>-0.46</t>
-        </is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="AH4" t="n">
+        <v>-0.17</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>-0.52</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-1.07</t>
+          <t>-0.87</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-1.95</t>
+          <t>-2.06</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
@@ -1918,30 +1886,26 @@
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>46.09</v>
+        <v>46.12</v>
       </c>
       <c r="AN4" t="n">
-        <v>46.59</v>
+        <v>46.52</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>47.52</t>
+          <t>47.5</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>18.14</t>
-        </is>
-      </c>
-      <c r="AQ4" t="inlineStr">
-        <is>
-          <t>-0.23</t>
-        </is>
-      </c>
-      <c r="AR4" t="inlineStr">
-        <is>
-          <t>-0.28</t>
-        </is>
+          <t>20.22</t>
+        </is>
+      </c>
+      <c r="AQ4" t="n">
+        <v>-0.21</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>-0.26</v>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
@@ -1950,7 +1914,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-106.51</t>
+          <t>-106.20</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1924,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>76104.98085106382</t>
+          <t>76007.19900849859</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>3809.0</t>
+          <t>3059.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>4626.6</v>
+        <v>3888.8</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>4741.3</t>
+          <t>4542.6</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>12259.36</v>
+        <v>12062.18</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-114</t>
+          <t>-653</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-1191.289377825079</t>
+          <t>-1243.615083485966</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-1543.3847844998</t>
+          <t>-1531.406464620841</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>3809.0</t>
+          <t>3059.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2061,7 +2025,7 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2076,7 +2040,7 @@
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>6.08</t>
+          <t>6.11</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2086,7 +2050,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>10.27</t>
+          <t>10.21</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2101,12 +2065,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>46.3</t>
+          <t>46.08</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>4281</t>
+          <t>4258</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,17 +2090,17 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>46.2</t>
+          <t>45.8</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>46.2</t>
+          <t>46.0</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>45.6</t>
+          <t>45.7</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2161,11 +2125,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>【d】</t>
-        </is>
-      </c>
+      <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr">
         <is>
           <t>3303</t>
@@ -2173,127 +2133,127 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>83.0</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>45.8</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>-1.22</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>-2.42</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>2025-09-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>2025-09-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>2025-03-06 00:00:00</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>2025-03-10 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>51.1</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>49.75</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>57.7</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>56.5</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>-7.94</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>-9.56</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-12-02</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>2.85</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
           <t>-0.43</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>82.0</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>45.8</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>-0.66</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>-20.54</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>2025-09-02 00:00:00</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>2025-09-12 00:00:00</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>2025-03-06 00:00:00</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>2025-03-10 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>51.1</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>49.75</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>57.7</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>56.5</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>-7.94</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>-9.56</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>2025-12-01</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>2.82</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>0.00</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,12 +2264,12 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>104</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
@@ -2319,59 +2279,51 @@
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>83.86</t>
-        </is>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>0.02</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>-0.58</t>
-        </is>
+          <t>89.33</t>
+        </is>
+      </c>
+      <c r="AH5" t="n">
+        <v>-0.17</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>-0.46</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-1.87</t>
+          <t>-1.95</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>45.79</t>
+          <t>45.88</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>46.06</v>
+        <v>46.09</v>
       </c>
       <c r="AN5" t="n">
-        <v>46.64</v>
+        <v>46.59</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>47.53</t>
+          <t>47.52</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>15.60</t>
-        </is>
-      </c>
-      <c r="AQ5" t="inlineStr">
-        <is>
-          <t>-0.25</t>
-        </is>
-      </c>
-      <c r="AR5" t="inlineStr">
-        <is>
-          <t>-0.29</t>
-        </is>
+          <t>18.14</t>
+        </is>
+      </c>
+      <c r="AQ5" t="n">
+        <v>-0.23</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>-0.28</v>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
@@ -2380,7 +2332,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-106.80</t>
+          <t>-106.51</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2342,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>76104.98085106382</t>
+          <t>76007.19900849859</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>3779.0</t>
+          <t>3809.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>4604</v>
+        <v>4626.6</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>5794.0</t>
+          <t>4741.3</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>12544.52</v>
+        <v>12259.36</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-1190</t>
+          <t>-114</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-1127.272031156948</t>
+          <t>-1191.289377825079</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-1585.732927737606</t>
+          <t>-1543.3847844998</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>3779.0</t>
+          <t>3809.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2491,7 +2443,7 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2506,7 +2458,7 @@
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>6.08</t>
+          <t>6.11</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2516,7 +2468,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>10.27</t>
+          <t>10.21</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2531,12 +2483,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>46.3</t>
+          <t>46.08</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>4281</t>
+          <t>4258</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,17 +2508,17 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>46.0</t>
+          <t>46.2</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>46.05</t>
+          <t>46.2</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>45.55</t>
+          <t>45.6</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2591,11 +2543,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>【d】</t>
-        </is>
-      </c>
+      <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr">
         <is>
           <t>3303</t>
@@ -2603,42 +2551,42 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
+          <t>-0.43</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>45.8</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>-1.22</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>75.0</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>46.0</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>-1.1</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-26.22</t>
+          <t>-20.54</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2703,7 +2651,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-7.54</t>
+          <t>-7.94</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,17 +2661,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>2.58</t>
+          <t>2.82</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-0.98</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,74 +2682,66 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>104</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>71.07</t>
-        </is>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>0.68</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>-0.75</t>
-        </is>
+          <t>83.86</t>
+        </is>
+      </c>
+      <c r="AH6" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>-0.58</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-1.76</t>
+          <t>-1.87</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>45.69</t>
+          <t>45.79</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>46.04</v>
+        <v>46.06</v>
       </c>
       <c r="AN6" t="n">
-        <v>46.7</v>
+        <v>46.64</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>47.54</t>
+          <t>47.53</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>12.46</t>
-        </is>
-      </c>
-      <c r="AQ6" t="inlineStr">
-        <is>
-          <t>-0.26</t>
-        </is>
-      </c>
-      <c r="AR6" t="inlineStr">
-        <is>
-          <t>-0.30</t>
-        </is>
+          <t>15.60</t>
+        </is>
+      </c>
+      <c r="AQ6" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>-0.29</v>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
@@ -2810,7 +2750,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-107.07</t>
+          <t>-106.80</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2760,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>76104.98085106382</t>
+          <t>76007.19900849859</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>3480.0</t>
+          <t>3779.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>4729.8</v>
+        <v>4604</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>6410.4</t>
+          <t>5794.0</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>12782.88</v>
+        <v>12544.52</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-1680</t>
+          <t>-1190</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-1043.91550450592</t>
+          <t>-1127.272031156948</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-1586.382670658128</t>
+          <t>-1585.732927737606</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>3480.0</t>
+          <t>3779.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2816,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-5.64</t>
+          <t>-6.05</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2921,7 +2861,7 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -2931,12 +2871,12 @@
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>6.08</t>
+          <t>6.11</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2946,7 +2886,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>10.27</t>
+          <t>10.21</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2961,12 +2901,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>46.3</t>
+          <t>46.08</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>4281</t>
+          <t>4258</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,22 +2926,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>46.4</t>
+          <t>46.0</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>46.45</t>
+          <t>46.05</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>46.0</t>
+          <t>45.55</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>46.0</t>
+          <t>45.8</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3021,11 +2961,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>【d】</t>
-        </is>
-      </c>
+      <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr">
         <is>
           <t>3303</t>
@@ -3033,12 +2969,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>116.0</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3058,7 +2994,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-1.1</t>
+          <t>-1.66</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -3068,7 +3004,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-19.32</t>
+          <t>-26.22</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3143,17 +3079,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>3.99</t>
+          <t>2.58</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,74 +3100,66 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>104</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>67.57</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>46.25</t>
-        </is>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>1.23</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>-1.23</t>
-        </is>
+          <t>71.07</t>
+        </is>
+      </c>
+      <c r="AH7" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>-0.75</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-1.61</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-1.65</t>
+          <t>-1.76</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>45.44</t>
+          <t>45.69</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>46</v>
+        <v>46.04</v>
       </c>
       <c r="AN7" t="n">
-        <v>46.76</v>
+        <v>46.7</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>47.55</t>
+          <t>47.54</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>2.00</t>
-        </is>
-      </c>
-      <c r="AQ7" t="inlineStr">
-        <is>
-          <t>-0.31</t>
-        </is>
-      </c>
-      <c r="AR7" t="inlineStr">
-        <is>
-          <t>-0.31</t>
-        </is>
+          <t>12.46</t>
+        </is>
+      </c>
+      <c r="AQ7" t="n">
+        <v>-0.26</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>-0.3</v>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
@@ -3240,7 +3168,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-107.29</t>
+          <t>-107.07</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3178,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>76104.98085106382</t>
+          <t>76007.19900849859</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>5317.0</t>
+          <t>3480.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>5619</v>
+        <v>4729.8</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>6964.2</t>
+          <t>6410.4</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>13246.56</v>
+        <v>12782.88</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-1345</t>
+          <t>-1680</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-945.2851106600637</t>
+          <t>-1043.91550450592</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-1498.618636592511</t>
+          <t>-1586.382670658128</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>5317.0</t>
+          <t>3480.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3351,7 +3279,7 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3366,7 +3294,7 @@
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>6.08</t>
+          <t>6.11</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3376,7 +3304,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>10.27</t>
+          <t>10.21</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3391,12 +3319,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>46.3</t>
+          <t>46.08</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>4281</t>
+          <t>4258</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3416,17 +3344,17 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>45.8</t>
+          <t>46.4</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>46.1</t>
+          <t>46.45</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>45.7</t>
+          <t>46.0</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3451,11 +3379,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>【e】</t>
-        </is>
-      </c>
+      <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr">
         <is>
           <t>3303</t>
@@ -3463,12 +3387,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>148.0</t>
+          <t>116.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3402,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>45.8</t>
+          <t>46.0</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,7 +3412,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-1.66</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -3498,7 +3422,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-34.26</t>
+          <t>-19.32</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3563,7 +3487,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-7.94</t>
+          <t>-7.54</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3497,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>5.09</t>
+          <t>3.99</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,74 +3518,66 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>104</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>45.65</t>
+          <t>67.57</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>30.16</t>
-        </is>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>0.99</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>-1.35</t>
-        </is>
+          <t>46.25</t>
+        </is>
+      </c>
+      <c r="AH8" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>-1.23</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-1.85</t>
+          <t>-1.61</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-1.48</t>
+          <t>-1.65</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>45.35</t>
+          <t>45.44</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>45.97</v>
+        <v>46</v>
       </c>
       <c r="AN8" t="n">
-        <v>46.84</v>
+        <v>46.76</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>47.54</t>
+          <t>47.55</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-12.73</t>
-        </is>
-      </c>
-      <c r="AQ8" t="inlineStr">
-        <is>
-          <t>-0.35</t>
-        </is>
-      </c>
-      <c r="AR8" t="inlineStr">
-        <is>
-          <t>-0.31</t>
-        </is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="AQ8" t="n">
+        <v>-0.31</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>-0.31</v>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
@@ -3670,7 +3586,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-107.33</t>
+          <t>-107.29</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3596,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>76104.98085106382</t>
+          <t>76007.19900849859</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>6748.0</t>
+          <t>5317.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>5196.4</v>
+        <v>5619</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>7904.3</t>
+          <t>6964.2</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>13455.3</v>
+        <v>13246.56</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-2707</t>
+          <t>-1345</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-844.6790150359823</t>
+          <t>-945.2851106600637</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-1516.540779477615</t>
+          <t>-1498.618636592511</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>6748.0</t>
+          <t>5317.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3652,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-6.05</t>
+          <t>-5.64</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3781,7 +3697,7 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -3791,12 +3707,12 @@
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>6.08</t>
+          <t>6.11</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3806,7 +3722,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>10.27</t>
+          <t>10.21</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3821,12 +3737,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>46.3</t>
+          <t>46.08</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>4281</t>
+          <t>4258</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3846,22 +3762,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>45.45</t>
+          <t>45.8</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>46.15</t>
+          <t>46.1</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>45.35</t>
+          <t>45.7</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>45.8</t>
+          <t>46.0</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3893,12 +3809,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>148.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3824,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>45.35</t>
+          <t>45.8</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,7 +3834,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>-1.22</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -3928,7 +3844,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-48.83</t>
+          <t>-34.26</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3993,7 +3909,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-8.84</t>
+          <t>-7.94</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +3919,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>2.79</t>
+          <t>5.09</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-1.32</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,74 +3940,66 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>104</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>25.53</t>
+          <t>45.65</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>14.94</t>
-        </is>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>0.33</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>-1.67</t>
-        </is>
+          <t>30.16</t>
+        </is>
+      </c>
+      <c r="AH9" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>-1.35</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-2.0</t>
+          <t>-1.85</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-1.30</t>
+          <t>-1.48</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>45.2</t>
+          <t>45.35</t>
         </is>
       </c>
       <c r="AM9" t="n">
         <v>45.97</v>
       </c>
       <c r="AN9" t="n">
-        <v>46.91</v>
+        <v>46.84</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>47.52</t>
+          <t>47.54</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-28.10</t>
-        </is>
-      </c>
-      <c r="AQ9" t="inlineStr">
-        <is>
-          <t>-0.39</t>
-        </is>
-      </c>
-      <c r="AR9" t="inlineStr">
-        <is>
-          <t>-0.30</t>
-        </is>
+          <t>-12.73</t>
+        </is>
+      </c>
+      <c r="AQ9" t="n">
+        <v>-0.35</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>-0.31</v>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
@@ -4100,7 +4008,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-107.09</t>
+          <t>-107.33</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4018,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>76104.98085106382</t>
+          <t>76007.19900849859</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>3696.0</t>
+          <t>6748.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>4856</v>
+        <v>5196.4</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>9489.5</t>
+          <t>7904.3</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>14335.48</v>
+        <v>13455.3</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-4633</t>
+          <t>-2707</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-722.5223305920491</t>
+          <t>-844.6790150359823</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-1641.303098617845</t>
+          <t>-1516.540779477615</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>3696.0</t>
+          <t>6748.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4074,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-6.97</t>
+          <t>-6.05</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4211,7 +4119,7 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4221,12 +4129,12 @@
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>6.08</t>
+          <t>6.11</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4236,7 +4144,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>10.27</t>
+          <t>10.21</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4251,12 +4159,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>46.3</t>
+          <t>46.08</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>4281</t>
+          <t>4258</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4276,22 +4184,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>46.0</t>
+          <t>45.45</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>46.0</t>
+          <t>46.15</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>45.3</t>
+          <t>45.35</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>45.35</t>
+          <t>45.8</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4323,12 +4231,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>98.0</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4246,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>45.3</t>
+          <t>45.35</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,7 +4256,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -4358,7 +4266,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-46.16</t>
+          <t>-48.83</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4423,7 +4331,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-8.94</t>
+          <t>-8.84</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4341,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>3.37</t>
+          <t>2.79</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>-1.32</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,74 +4362,66 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>104</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>19.3</t>
+          <t>25.53</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>15.36</t>
-        </is>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>0.47</t>
-        </is>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>-1.96</t>
-        </is>
+          <t>14.94</t>
+        </is>
+      </c>
+      <c r="AH10" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>-1.67</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-2.17</t>
+          <t>-2.0</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-1.05</t>
+          <t>-1.30</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>45.09</t>
+          <t>45.2</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>45.99</v>
+        <v>45.97</v>
       </c>
       <c r="AN10" t="n">
-        <v>47.02</v>
+        <v>46.91</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>47.51</t>
+          <t>47.52</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-35.53</t>
-        </is>
-      </c>
-      <c r="AQ10" t="inlineStr">
-        <is>
-          <t>-0.38</t>
-        </is>
-      </c>
-      <c r="AR10" t="inlineStr">
-        <is>
-          <t>-0.28</t>
-        </is>
+          <t>-28.10</t>
+        </is>
+      </c>
+      <c r="AQ10" t="n">
+        <v>-0.39</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>-0.3</v>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
@@ -4530,7 +4430,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-106.59</t>
+          <t>-107.09</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4440,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>76104.98085106382</t>
+          <t>76007.19900849859</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>4408.0</t>
+          <t>3696.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>6984</v>
+        <v>4856</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>12971.6</t>
+          <t>9489.5</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>15065.26</v>
+        <v>14335.48</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-5987</t>
+          <t>-4633</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-555.4712818600863</t>
+          <t>-722.5223305920491</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-1433.917015296107</t>
+          <t>-1641.303098617845</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>4408.0</t>
+          <t>3696.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4496,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-7.08</t>
+          <t>-6.97</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4641,7 +4541,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4656,7 +4556,7 @@
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>6.08</t>
+          <t>6.11</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4666,7 +4566,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>10.27</t>
+          <t>10.21</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4681,12 +4581,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>46.3</t>
+          <t>46.08</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>4281</t>
+          <t>4258</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4706,22 +4606,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>44.95</t>
+          <t>46.0</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>45.45</t>
+          <t>46.0</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>44.9</t>
+          <t>45.3</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>45.3</t>
+          <t>45.35</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4753,12 +4653,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-1.77</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>177.0</t>
+          <t>98.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4668,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>44.75</t>
+          <t>45.3</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,7 +4678,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -4788,7 +4688,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-39.89</t>
+          <t>-46.16</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4853,7 +4753,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-10.05</t>
+          <t>-8.94</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4763,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>6.09</t>
+          <t>3.37</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,74 +4784,66 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>104</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>19.3</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>11.9</t>
-        </is>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>-1.32</t>
-        </is>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>-1.47</t>
-        </is>
+          <t>15.36</t>
+        </is>
+      </c>
+      <c r="AH11" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>-1.96</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-2.34</t>
+          <t>-2.17</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>-1.05</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>45.35</t>
+          <t>45.09</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>46.03</v>
+        <v>45.99</v>
       </c>
       <c r="AN11" t="n">
-        <v>47.13</v>
+        <v>47.02</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>47.5</t>
+          <t>47.51</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-41.45</t>
-        </is>
-      </c>
-      <c r="AQ11" t="inlineStr">
-        <is>
-          <t>-0.36</t>
-        </is>
-      </c>
-      <c r="AR11" t="inlineStr">
-        <is>
-          <t>-0.26</t>
-        </is>
+          <t>-35.53</t>
+        </is>
+      </c>
+      <c r="AQ11" t="n">
+        <v>-0.38</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>-0.28</v>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
@@ -4960,7 +4852,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-106.01</t>
+          <t>-106.59</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4862,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>76104.98085106382</t>
+          <t>76007.19900849859</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>7926.0</t>
+          <t>4408.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>8091</v>
+        <v>6984</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>13461.2</t>
+          <t>12971.6</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>15558.56</v>
+        <v>15065.26</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-5370</t>
+          <t>-5987</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-395.7538757808097</t>
+          <t>-555.4712818600863</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-1162.725574290193</t>
+          <t>-1433.917015296107</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>7926.0</t>
+          <t>4408.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +4918,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-8.21</t>
+          <t>-7.08</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5071,7 +4963,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5081,12 +4973,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>1.84</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>6.08</t>
+          <t>6.11</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5096,7 +4988,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>10.27</t>
+          <t>10.21</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5111,12 +5003,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>46.3</t>
+          <t>46.08</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>4281</t>
+          <t>4258</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5136,22 +5028,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>45.2</t>
+          <t>44.95</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>45.2</t>
+          <t>45.45</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>44.6</t>
+          <t>44.9</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>44.75</t>
+          <t>45.3</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5183,34 +5075,34 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
+          <t>-1.77</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>177.0</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>44.75</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
           <t>1.1</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>70.0</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>45.55</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>-0.11</t>
-        </is>
-      </c>
       <c r="I12" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -5218,7 +5110,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-38.31</t>
+          <t>-39.89</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5283,7 +5175,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-8.44</t>
+          <t>-10.05</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5185,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>2.41</t>
+          <t>6.09</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-0.98</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,17 +5206,17 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>104</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>26.79</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
@@ -5332,36 +5224,32 @@
           <t>11.9</t>
         </is>
       </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>-0.57</t>
-        </is>
-      </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>-0.61</t>
-        </is>
+      <c r="AH12" t="n">
+        <v>-1.32</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>-1.47</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-2.47</t>
+          <t>-2.34</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-0.50</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>45.81</t>
+          <t>45.35</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>46.09</v>
+        <v>46.03</v>
       </c>
       <c r="AN12" t="n">
-        <v>47.26</v>
+        <v>47.13</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
@@ -5370,18 +5258,14 @@
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-20.83</t>
-        </is>
-      </c>
-      <c r="AQ12" t="inlineStr">
-        <is>
-          <t>-0.28</t>
-        </is>
-      </c>
-      <c r="AR12" t="inlineStr">
-        <is>
-          <t>-0.23</t>
-        </is>
+          <t>-41.45</t>
+        </is>
+      </c>
+      <c r="AQ12" t="n">
+        <v>-0.36</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>-0.26</v>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
@@ -5390,7 +5274,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-105.39</t>
+          <t>-106.01</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,43 +5284,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>76104.98085106382</t>
+          <t>76007.19900849859</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>3204.0</t>
+          <t>7926.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>8309.4</v>
+        <v>8091</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>13469.3</t>
+          <t>13461.2</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>16218.6</v>
+        <v>15558.56</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-5159</t>
+          <t>-5370</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-256.304476051831</t>
+          <t>-395.7538757808097</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-1110.711888057096</t>
+          <t>-1162.725574290193</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>3204.0</t>
+          <t>7926.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5340,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-6.56</t>
+          <t>-8.21</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5501,7 +5385,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5511,12 +5395,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>6.08</t>
+          <t>6.11</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5526,7 +5410,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>10.27</t>
+          <t>10.21</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5541,12 +5425,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>46.3</t>
+          <t>46.08</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>4281</t>
+          <t>4258</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5566,22 +5450,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>45.4</t>
+          <t>45.2</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>46.25</t>
+          <t>45.2</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>45.3</t>
+          <t>44.6</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>45.55</t>
+          <t>44.75</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/PET膜.xlsx
+++ b/Result/checksun_type/PET膜.xlsx
@@ -871,7 +871,11 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr"/>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>3303</t>
@@ -879,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-0.55</t>
+          <t>-0.44</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>104.0</t>
+          <t>246.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -894,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>45.25</t>
+          <t>45.05</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -914,7 +918,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-8.48</t>
+          <t>8.33</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -979,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-9.05</t>
+          <t>-9.45</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -989,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>3.58</t>
+          <t>9.67</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1010,12 +1014,12 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>246</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
@@ -1025,51 +1029,51 @@
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>37.52</t>
+          <t>9.52</t>
         </is>
       </c>
       <c r="AH2" t="n">
-        <v>-0.83</v>
+        <v>-0.95</v>
       </c>
       <c r="AI2" t="n">
-        <v>-0.75</v>
+        <v>-0.87</v>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-0.9</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-2.24</t>
+          <t>-2.29</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>45.63</t>
+          <t>45.48</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>45.98</v>
+        <v>45.88</v>
       </c>
       <c r="AN2" t="n">
-        <v>46.39</v>
+        <v>46.32</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>47.46</t>
+          <t>47.41</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>3.73</t>
+          <t>-7.02</t>
         </is>
       </c>
       <c r="AQ2" t="n">
-        <v>-0.24</v>
+        <v>-0.28</v>
       </c>
       <c r="AR2" t="n">
-        <v>-0.25</v>
+        <v>-0.26</v>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
@@ -1078,7 +1082,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-105.93</t>
+          <t>-106.04</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1088,43 +1092,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>76007.19900849859</t>
+          <t>75923.10254596888</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>4714.0</t>
+          <t>11034.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>3990.2</v>
+        <v>5441.2</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>4360.0</t>
+          <t>5022.6</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>11948.92</v>
+        <v>11858.6</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-369</t>
+          <t>418</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-1255.394821893818</t>
+          <t>-1154.46766135493</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-1213.317202241243</t>
+          <t>-599.3682783910481</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>4714.0</t>
+          <t>11034.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1144,7 +1148,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-7.18</t>
+          <t>-7.59</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1189,12 +1193,12 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
@@ -1204,7 +1208,7 @@
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>6.11</t>
+          <t>6.14</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1214,7 +1218,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>10.21</t>
+          <t>10.17</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1229,12 +1233,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>46.08</t>
+          <t>46.32</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>4258</t>
+          <t>4239</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1254,22 +1258,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>45.5</t>
+          <t>45.25</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>45.5</t>
+          <t>45.45</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>44.9</t>
+          <t>44.5</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>45.25</t>
+          <t>45.05</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1289,7 +1293,11 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr"/>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B3" t="inlineStr">
         <is>
           <t>3303</t>
@@ -1297,12 +1305,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>-0.55</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>104.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1312,7 +1320,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>45.5</t>
+          <t>45.25</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1322,7 +1330,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-0.55</t>
+          <t>-0.44</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -1332,7 +1340,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-20.03</t>
+          <t>-8.48</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1397,7 +1405,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-8.54</t>
+          <t>-9.05</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1407,17 +1415,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>3.47</t>
+          <t>4.09</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1428,66 +1436,66 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>246</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>28.57</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>65.52</t>
+          <t>37.52</t>
         </is>
       </c>
       <c r="AH3" t="n">
-        <v>-0.61</v>
+        <v>-0.83</v>
       </c>
       <c r="AI3" t="n">
-        <v>-0.58</v>
+        <v>-0.75</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-0.89</t>
+          <t>-0.9</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-2.14</t>
+          <t>-2.24</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>45.77999999999999</t>
+          <t>45.63</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>46.04</v>
+        <v>45.98</v>
       </c>
       <c r="AN3" t="n">
-        <v>46.46</v>
+        <v>46.39</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>47.48</t>
+          <t>47.46</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>14.06</t>
+          <t>3.73</t>
         </is>
       </c>
       <c r="AQ3" t="n">
-        <v>-0.22</v>
+        <v>-0.24</v>
       </c>
       <c r="AR3" t="n">
-        <v>-0.26</v>
+        <v>-0.25</v>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
@@ -1496,7 +1504,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-105.99</t>
+          <t>-105.93</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1506,43 +1514,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>76007.19900849859</t>
+          <t>75923.10254596888</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>4590.0</t>
+          <t>4714.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>3743.4</v>
+        <v>3990.2</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>4681.2</t>
+          <t>4360.0</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>12007.9</v>
+        <v>11948.92</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-937</t>
+          <t>-369</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-1263.045298194286</t>
+          <t>-1255.394821893818</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-1369.911479090048</t>
+          <t>-1213.317202241243</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>4590.0</t>
+          <t>4714.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1562,7 +1570,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-6.67</t>
+          <t>-7.18</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1607,7 +1615,7 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1617,12 +1625,12 @@
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>6.11</t>
+          <t>6.14</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1632,7 +1640,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>10.21</t>
+          <t>10.17</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1647,12 +1655,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>46.08</t>
+          <t>46.32</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>4258</t>
+          <t>4239</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1672,22 +1680,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>46.0</t>
+          <t>45.5</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>46.05</t>
+          <t>45.5</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>45.15</t>
+          <t>44.9</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>45.5</t>
+          <t>45.25</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1707,7 +1715,11 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr"/>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B4" t="inlineStr">
         <is>
           <t>3303</t>
@@ -1715,42 +1727,42 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
+          <t>-0.65</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>101.0</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>45.5</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>-1.0</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>67.0</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>45.8</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>-1.22</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-14.39</t>
+          <t>-20.03</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1815,7 +1827,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-7.94</t>
+          <t>-8.54</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1825,17 +1837,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>2.30</t>
+          <t>3.97</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1846,63 +1858,63 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>246</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>28.57</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>65.52</t>
         </is>
       </c>
       <c r="AH4" t="n">
-        <v>-0.17</v>
+        <v>-0.61</v>
       </c>
       <c r="AI4" t="n">
-        <v>-0.52</v>
+        <v>-0.58</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-0.87</t>
+          <t>-0.89</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-2.06</t>
+          <t>-2.14</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>45.88</t>
+          <t>45.77999999999999</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>46.12</v>
+        <v>46.04</v>
       </c>
       <c r="AN4" t="n">
-        <v>46.52</v>
+        <v>46.46</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>47.5</t>
+          <t>47.48</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>20.22</t>
+          <t>14.06</t>
         </is>
       </c>
       <c r="AQ4" t="n">
-        <v>-0.21</v>
+        <v>-0.22</v>
       </c>
       <c r="AR4" t="n">
         <v>-0.26</v>
@@ -1914,7 +1926,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-106.20</t>
+          <t>-105.99</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1924,43 +1936,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>76007.19900849859</t>
+          <t>75923.10254596888</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>3059.0</t>
+          <t>4590.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>3888.8</v>
+        <v>3743.4</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>4542.6</t>
+          <t>4681.2</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>12062.18</v>
+        <v>12007.9</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-653</t>
+          <t>-937</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-1243.615083485966</t>
+          <t>-1263.045298194286</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-1531.406464620841</t>
+          <t>-1369.911479090048</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>3059.0</t>
+          <t>4590.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -1980,7 +1992,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-6.05</t>
+          <t>-6.67</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2025,7 +2037,7 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2035,12 +2047,12 @@
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>6.11</t>
+          <t>6.14</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2050,7 +2062,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>10.21</t>
+          <t>10.17</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2065,12 +2077,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>46.08</t>
+          <t>46.32</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>4258</t>
+          <t>4239</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2090,22 +2102,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>45.8</t>
+          <t>46.0</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>46.0</t>
+          <t>46.05</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>45.7</t>
+          <t>45.15</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>45.8</t>
+          <t>45.5</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2125,7 +2137,11 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr"/>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B5" t="inlineStr">
         <is>
           <t>3303</t>
@@ -2138,7 +2154,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2158,7 +2174,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-1.22</t>
+          <t>-1.66</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -2168,7 +2184,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-2.42</t>
+          <t>-14.39</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2243,17 +2259,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>2.85</t>
+          <t>2.63</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2264,12 +2280,12 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>246</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
@@ -2279,23 +2295,23 @@
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>89.33</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AH5" t="n">
         <v>-0.17</v>
       </c>
       <c r="AI5" t="n">
-        <v>-0.46</v>
+        <v>-0.52</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-1.07</t>
+          <t>-0.87</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-1.95</t>
+          <t>-2.06</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
@@ -2304,26 +2320,26 @@
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>46.09</v>
+        <v>46.12</v>
       </c>
       <c r="AN5" t="n">
-        <v>46.59</v>
+        <v>46.52</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>47.52</t>
+          <t>47.5</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>18.14</t>
+          <t>20.22</t>
         </is>
       </c>
       <c r="AQ5" t="n">
-        <v>-0.23</v>
+        <v>-0.21</v>
       </c>
       <c r="AR5" t="n">
-        <v>-0.28</v>
+        <v>-0.26</v>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
@@ -2332,7 +2348,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-106.51</t>
+          <t>-106.20</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2342,43 +2358,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>76007.19900849859</t>
+          <t>75923.10254596888</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>3809.0</t>
+          <t>3059.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>4626.6</v>
+        <v>3888.8</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>4741.3</t>
+          <t>4542.6</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>12259.36</v>
+        <v>12062.18</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-114</t>
+          <t>-653</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-1191.289377825079</t>
+          <t>-1243.615083485966</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-1543.3847844998</t>
+          <t>-1531.406464620841</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>3809.0</t>
+          <t>3059.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2443,7 +2459,7 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2458,7 +2474,7 @@
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>6.11</t>
+          <t>6.14</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2468,7 +2484,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>10.21</t>
+          <t>10.17</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2483,12 +2499,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>46.08</t>
+          <t>46.32</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>4258</t>
+          <t>4239</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2508,17 +2524,17 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>46.2</t>
+          <t>45.8</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>46.2</t>
+          <t>46.0</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>45.6</t>
+          <t>45.7</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2543,7 +2559,11 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr"/>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B6" t="inlineStr">
         <is>
           <t>3303</t>
@@ -2551,127 +2571,127 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>83.0</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>45.8</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>-1.66</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>-2.42</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>2025-09-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>2025-09-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>2025-03-06 00:00:00</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>2025-03-10 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>51.1</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>49.75</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>57.7</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>56.5</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>-7.94</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>-9.56</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-12-02</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>3.26</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
           <t>-0.43</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>82.0</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>45.8</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>-1.22</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>-20.54</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>2025-09-02 00:00:00</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>2025-09-12 00:00:00</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>2025-03-06 00:00:00</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>2025-03-10 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>51.1</t>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>49.75</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>57.7</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>56.5</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>-7.94</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>-9.56</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>2025-12-01</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>2.82</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>0.00</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2682,12 +2702,12 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>246</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
@@ -2697,51 +2717,51 @@
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>83.86</t>
+          <t>89.33</t>
         </is>
       </c>
       <c r="AH6" t="n">
-        <v>0.02</v>
+        <v>-0.17</v>
       </c>
       <c r="AI6" t="n">
-        <v>-0.58</v>
+        <v>-0.46</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-1.87</t>
+          <t>-1.95</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>45.79</t>
+          <t>45.88</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>46.06</v>
+        <v>46.09</v>
       </c>
       <c r="AN6" t="n">
-        <v>46.64</v>
+        <v>46.59</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>47.53</t>
+          <t>47.52</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>15.60</t>
+          <t>18.14</t>
         </is>
       </c>
       <c r="AQ6" t="n">
-        <v>-0.25</v>
+        <v>-0.23</v>
       </c>
       <c r="AR6" t="n">
-        <v>-0.29</v>
+        <v>-0.28</v>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
@@ -2750,7 +2770,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-106.80</t>
+          <t>-106.51</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2760,43 +2780,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>76007.19900849859</t>
+          <t>75923.10254596888</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>3779.0</t>
+          <t>3809.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>4604</v>
+        <v>4626.6</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>5794.0</t>
+          <t>4741.3</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>12544.52</v>
+        <v>12259.36</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-1190</t>
+          <t>-114</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-1127.272031156948</t>
+          <t>-1191.289377825079</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-1585.732927737606</t>
+          <t>-1543.3847844998</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>3779.0</t>
+          <t>3809.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2861,7 +2881,7 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -2876,7 +2896,7 @@
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>6.11</t>
+          <t>6.14</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2886,7 +2906,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>10.21</t>
+          <t>10.17</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2901,12 +2921,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>46.08</t>
+          <t>46.32</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>4258</t>
+          <t>4239</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2926,17 +2946,17 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>46.0</t>
+          <t>46.2</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>46.05</t>
+          <t>46.2</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>45.55</t>
+          <t>45.6</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -2961,7 +2981,11 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr"/>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B7" t="inlineStr">
         <is>
           <t>3303</t>
@@ -2969,42 +2993,42 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
+          <t>-0.43</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>45.8</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>-1.66</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>75.0</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>46.0</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>-1.66</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-26.22</t>
+          <t>-20.54</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3069,7 +3093,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-7.54</t>
+          <t>-7.94</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3079,17 +3103,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>2.58</t>
+          <t>3.22</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-0.98</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3100,66 +3124,66 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>246</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>71.07</t>
+          <t>83.86</t>
         </is>
       </c>
       <c r="AH7" t="n">
-        <v>0.68</v>
+        <v>0.02</v>
       </c>
       <c r="AI7" t="n">
-        <v>-0.75</v>
+        <v>-0.58</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-1.76</t>
+          <t>-1.87</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>45.69</t>
+          <t>45.79</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>46.04</v>
+        <v>46.06</v>
       </c>
       <c r="AN7" t="n">
-        <v>46.7</v>
+        <v>46.64</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>47.54</t>
+          <t>47.53</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>12.46</t>
+          <t>15.60</t>
         </is>
       </c>
       <c r="AQ7" t="n">
-        <v>-0.26</v>
+        <v>-0.25</v>
       </c>
       <c r="AR7" t="n">
-        <v>-0.3</v>
+        <v>-0.29</v>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
@@ -3168,7 +3192,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-107.07</t>
+          <t>-106.80</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3178,43 +3202,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>76007.19900849859</t>
+          <t>75923.10254596888</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>3480.0</t>
+          <t>3779.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>4729.8</v>
+        <v>4604</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>6410.4</t>
+          <t>5794.0</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>12782.88</v>
+        <v>12544.52</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-1680</t>
+          <t>-1190</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-1043.91550450592</t>
+          <t>-1127.272031156948</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-1586.382670658128</t>
+          <t>-1585.732927737606</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>3480.0</t>
+          <t>3779.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3234,7 +3258,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-5.64</t>
+          <t>-6.05</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3279,7 +3303,7 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3289,12 +3313,12 @@
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>6.11</t>
+          <t>6.14</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3304,7 +3328,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>10.21</t>
+          <t>10.17</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3319,12 +3343,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>46.08</t>
+          <t>46.32</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>4258</t>
+          <t>4239</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3344,22 +3368,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>46.4</t>
+          <t>46.0</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>46.45</t>
+          <t>46.05</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>46.0</t>
+          <t>45.55</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>46.0</t>
+          <t>45.8</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3379,7 +3403,11 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr"/>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B8" t="inlineStr">
         <is>
           <t>3303</t>
@@ -3387,12 +3415,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>116.0</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3412,7 +3440,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-1.66</t>
+          <t>-2.11</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -3422,7 +3450,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-19.32</t>
+          <t>-26.22</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3497,17 +3525,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>3.99</t>
+          <t>2.95</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3518,66 +3546,66 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>246</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>67.57</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>46.25</t>
+          <t>71.07</t>
         </is>
       </c>
       <c r="AH8" t="n">
-        <v>1.23</v>
+        <v>0.68</v>
       </c>
       <c r="AI8" t="n">
-        <v>-1.23</v>
+        <v>-0.75</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-1.61</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-1.65</t>
+          <t>-1.76</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>45.44</t>
+          <t>45.69</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>46</v>
+        <v>46.04</v>
       </c>
       <c r="AN8" t="n">
-        <v>46.76</v>
+        <v>46.7</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>47.55</t>
+          <t>47.54</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>12.46</t>
         </is>
       </c>
       <c r="AQ8" t="n">
-        <v>-0.31</v>
+        <v>-0.26</v>
       </c>
       <c r="AR8" t="n">
-        <v>-0.31</v>
+        <v>-0.3</v>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
@@ -3586,7 +3614,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-107.29</t>
+          <t>-107.07</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3596,43 +3624,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>76007.19900849859</t>
+          <t>75923.10254596888</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>5317.0</t>
+          <t>3480.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>5619</v>
+        <v>4729.8</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>6964.2</t>
+          <t>6410.4</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>13246.56</v>
+        <v>12782.88</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-1345</t>
+          <t>-1680</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-945.2851106600637</t>
+          <t>-1043.91550450592</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-1498.618636592511</t>
+          <t>-1586.382670658128</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>5317.0</t>
+          <t>3480.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3697,7 +3725,7 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -3712,7 +3740,7 @@
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>6.11</t>
+          <t>6.14</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3722,7 +3750,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>10.21</t>
+          <t>10.17</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3737,12 +3765,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>46.08</t>
+          <t>46.32</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>4258</t>
+          <t>4239</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3762,17 +3790,17 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>45.8</t>
+          <t>46.4</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>46.1</t>
+          <t>46.45</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>45.7</t>
+          <t>46.0</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -3799,7 +3827,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d2】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -3809,12 +3837,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>148.0</t>
+          <t>116.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3824,7 +3852,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>45.8</t>
+          <t>46.0</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3834,7 +3862,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-1.22</t>
+          <t>-2.11</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -3844,7 +3872,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-34.26</t>
+          <t>-19.32</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3909,7 +3937,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-7.94</t>
+          <t>-7.54</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -3919,17 +3947,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>5.09</t>
+          <t>4.56</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -3940,63 +3968,63 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>246</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>45.65</t>
+          <t>67.57</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>30.16</t>
+          <t>46.25</t>
         </is>
       </c>
       <c r="AH9" t="n">
-        <v>0.99</v>
+        <v>1.23</v>
       </c>
       <c r="AI9" t="n">
-        <v>-1.35</v>
+        <v>-1.23</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-1.85</t>
+          <t>-1.61</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-1.48</t>
+          <t>-1.65</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>45.35</t>
+          <t>45.44</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>45.97</v>
+        <v>46</v>
       </c>
       <c r="AN9" t="n">
-        <v>46.84</v>
+        <v>46.76</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>47.54</t>
+          <t>47.55</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-12.73</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="AQ9" t="n">
-        <v>-0.35</v>
+        <v>-0.31</v>
       </c>
       <c r="AR9" t="n">
         <v>-0.31</v>
@@ -4008,7 +4036,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-107.33</t>
+          <t>-107.29</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4018,43 +4046,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>76007.19900849859</t>
+          <t>75923.10254596888</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>6748.0</t>
+          <t>5317.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>5196.4</v>
+        <v>5619</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>7904.3</t>
+          <t>6964.2</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>13455.3</v>
+        <v>13246.56</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-2707</t>
+          <t>-1345</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-844.6790150359823</t>
+          <t>-945.2851106600637</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-1516.540779477615</t>
+          <t>-1498.618636592511</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>6748.0</t>
+          <t>5317.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4074,7 +4102,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-6.05</t>
+          <t>-5.64</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4119,7 +4147,7 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4129,12 +4157,12 @@
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>6.11</t>
+          <t>6.14</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4144,7 +4172,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>10.21</t>
+          <t>10.17</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4159,12 +4187,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>46.08</t>
+          <t>46.32</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>4258</t>
+          <t>4239</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4184,22 +4212,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>45.45</t>
+          <t>45.8</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>46.15</t>
+          <t>46.1</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>45.35</t>
+          <t>45.7</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>45.8</t>
+          <t>46.0</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4231,12 +4259,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>148.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4246,7 +4274,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>45.35</t>
+          <t>45.8</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4256,7 +4284,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-1.66</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -4266,7 +4294,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-48.83</t>
+          <t>-34.26</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4331,7 +4359,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-8.84</t>
+          <t>-7.94</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4341,17 +4369,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>2.79</t>
+          <t>5.82</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-1.32</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4362,66 +4390,66 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>246</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>25.53</t>
+          <t>45.65</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>14.94</t>
+          <t>30.16</t>
         </is>
       </c>
       <c r="AH10" t="n">
-        <v>0.33</v>
+        <v>0.99</v>
       </c>
       <c r="AI10" t="n">
-        <v>-1.67</v>
+        <v>-1.35</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-2.0</t>
+          <t>-1.85</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-1.30</t>
+          <t>-1.48</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>45.2</t>
+          <t>45.35</t>
         </is>
       </c>
       <c r="AM10" t="n">
         <v>45.97</v>
       </c>
       <c r="AN10" t="n">
-        <v>46.91</v>
+        <v>46.84</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>47.52</t>
+          <t>47.54</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-28.10</t>
+          <t>-12.73</t>
         </is>
       </c>
       <c r="AQ10" t="n">
-        <v>-0.39</v>
+        <v>-0.35</v>
       </c>
       <c r="AR10" t="n">
-        <v>-0.3</v>
+        <v>-0.31</v>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
@@ -4430,7 +4458,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-107.09</t>
+          <t>-107.33</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4440,43 +4468,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>76007.19900849859</t>
+          <t>75923.10254596888</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>3696.0</t>
+          <t>6748.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>4856</v>
+        <v>5196.4</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>9489.5</t>
+          <t>7904.3</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>14335.48</v>
+        <v>13455.3</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-4633</t>
+          <t>-2707</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-722.5223305920491</t>
+          <t>-844.6790150359823</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-1641.303098617845</t>
+          <t>-1516.540779477615</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>3696.0</t>
+          <t>6748.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4496,7 +4524,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-6.97</t>
+          <t>-6.05</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4541,7 +4569,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4551,12 +4579,12 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>6.11</t>
+          <t>6.14</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4566,7 +4594,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>10.21</t>
+          <t>10.17</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4581,12 +4609,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>46.08</t>
+          <t>46.32</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>4258</t>
+          <t>4239</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4606,22 +4634,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>46.0</t>
+          <t>45.45</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>46.0</t>
+          <t>46.15</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>45.3</t>
+          <t>45.35</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>45.35</t>
+          <t>45.8</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4653,12 +4681,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>98.0</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4668,7 +4696,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>45.3</t>
+          <t>45.35</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4678,7 +4706,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -4688,7 +4716,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-46.16</t>
+          <t>-48.83</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4753,7 +4781,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-8.94</t>
+          <t>-8.84</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4763,17 +4791,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>3.37</t>
+          <t>3.18</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>-1.32</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4784,66 +4812,66 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>246</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>19.3</t>
+          <t>25.53</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>15.36</t>
+          <t>14.94</t>
         </is>
       </c>
       <c r="AH11" t="n">
-        <v>0.47</v>
+        <v>0.33</v>
       </c>
       <c r="AI11" t="n">
-        <v>-1.96</v>
+        <v>-1.67</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-2.17</t>
+          <t>-2.0</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-1.05</t>
+          <t>-1.30</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>45.09</t>
+          <t>45.2</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>45.99</v>
+        <v>45.97</v>
       </c>
       <c r="AN11" t="n">
-        <v>47.02</v>
+        <v>46.91</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>47.51</t>
+          <t>47.52</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-35.53</t>
+          <t>-28.10</t>
         </is>
       </c>
       <c r="AQ11" t="n">
-        <v>-0.38</v>
+        <v>-0.39</v>
       </c>
       <c r="AR11" t="n">
-        <v>-0.28</v>
+        <v>-0.3</v>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
@@ -4852,7 +4880,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-106.59</t>
+          <t>-107.09</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4862,43 +4890,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>76007.19900849859</t>
+          <t>75923.10254596888</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>4408.0</t>
+          <t>3696.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>6984</v>
+        <v>4856</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>12971.6</t>
+          <t>9489.5</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>15065.26</v>
+        <v>14335.48</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-5987</t>
+          <t>-4633</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-555.4712818600863</t>
+          <t>-722.5223305920491</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-1433.917015296107</t>
+          <t>-1641.303098617845</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>4408.0</t>
+          <t>3696.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -4918,7 +4946,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-7.08</t>
+          <t>-6.97</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -4963,7 +4991,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -4978,7 +5006,7 @@
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>6.11</t>
+          <t>6.14</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -4988,7 +5016,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>10.21</t>
+          <t>10.17</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5003,12 +5031,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>46.08</t>
+          <t>46.32</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>4258</t>
+          <t>4239</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5028,22 +5056,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>44.95</t>
+          <t>46.0</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>45.45</t>
+          <t>46.0</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>44.9</t>
+          <t>45.3</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>45.3</t>
+          <t>45.35</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5075,12 +5103,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-1.77</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>177.0</t>
+          <t>98.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5090,7 +5118,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>44.75</t>
+          <t>45.3</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5100,7 +5128,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>-0.55</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -5110,7 +5138,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-39.89</t>
+          <t>-46.16</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5175,7 +5203,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-10.05</t>
+          <t>-8.94</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5185,17 +5213,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>6.09</t>
+          <t>3.85</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5206,66 +5234,66 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>246</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>19.3</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>11.9</t>
+          <t>15.36</t>
         </is>
       </c>
       <c r="AH12" t="n">
-        <v>-1.32</v>
+        <v>0.47</v>
       </c>
       <c r="AI12" t="n">
-        <v>-1.47</v>
+        <v>-1.96</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-2.34</t>
+          <t>-2.17</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>-1.05</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>45.35</t>
+          <t>45.09</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>46.03</v>
+        <v>45.99</v>
       </c>
       <c r="AN12" t="n">
-        <v>47.13</v>
+        <v>47.02</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>47.5</t>
+          <t>47.51</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-41.45</t>
+          <t>-35.53</t>
         </is>
       </c>
       <c r="AQ12" t="n">
-        <v>-0.36</v>
+        <v>-0.38</v>
       </c>
       <c r="AR12" t="n">
-        <v>-0.26</v>
+        <v>-0.28</v>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
@@ -5274,7 +5302,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-106.01</t>
+          <t>-106.59</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5284,43 +5312,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>76007.19900849859</t>
+          <t>75923.10254596888</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>7926.0</t>
+          <t>4408.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>8091</v>
+        <v>6984</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>13461.2</t>
+          <t>12971.6</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>15558.56</v>
+        <v>15065.26</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-5370</t>
+          <t>-5987</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-395.7538757808097</t>
+          <t>-555.4712818600863</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-1162.725574290193</t>
+          <t>-1433.917015296107</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>7926.0</t>
+          <t>4408.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5340,7 +5368,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-8.21</t>
+          <t>-7.08</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5385,7 +5413,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5395,12 +5423,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>1.84</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>6.11</t>
+          <t>6.14</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5410,7 +5438,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>10.21</t>
+          <t>10.17</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5425,12 +5453,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>46.08</t>
+          <t>46.32</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>4258</t>
+          <t>4239</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5450,22 +5478,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>45.2</t>
+          <t>44.95</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>45.2</t>
+          <t>45.45</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>44.6</t>
+          <t>44.9</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>44.75</t>
+          <t>45.3</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/PET膜.xlsx
+++ b/Result/checksun_type/PET膜.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>246.0</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>45.05</t>
+          <t>45.55</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>8.33</t>
+          <t>9.71</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-9.45</t>
+          <t>-8.44</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>9.67</t>
+          <t>4.05</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>-1.09</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,63 +1014,63 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>246</t>
+          <t>103</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>52.63</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>9.52</t>
+          <t>17.54</t>
         </is>
       </c>
       <c r="AH2" t="n">
-        <v>-0.95</v>
+        <v>0.26</v>
       </c>
       <c r="AI2" t="n">
-        <v>-0.87</v>
+        <v>-0.78</v>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-0.97</t>
+          <t>-1.04</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-2.29</t>
+          <t>-2.32</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>45.48</t>
+          <t>45.42999999999999</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>45.88</v>
+        <v>45.78</v>
       </c>
       <c r="AN2" t="n">
-        <v>46.32</v>
+        <v>46.27</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>47.41</t>
+          <t>47.37</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-7.02</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AQ2" t="n">
-        <v>-0.28</v>
+        <v>-0.26</v>
       </c>
       <c r="AR2" t="n">
         <v>-0.26</v>
@@ -1092,43 +1092,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>75923.10254596888</t>
+          <t>75825.85381355931</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>11034.0</t>
+          <t>4714.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>5441.2</v>
+        <v>5622.2</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>5022.6</t>
+          <t>5124.4</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>11858.6</v>
+        <v>11707.74</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>418</t>
+          <t>497</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-1154.46766135493</t>
+          <t>-1073.567994182808</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-599.3682783910481</t>
+          <t>-628.6198247361344</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>11034.0</t>
+          <t>4714.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-7.59</t>
+          <t>-6.56</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1193,22 +1193,22 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>6.14</t>
+          <t>6.07</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>10.17</t>
+          <t>10.28</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1233,12 +1233,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>46.32</t>
+          <t>46.46</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>4239</t>
+          <t>4286</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1258,22 +1258,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>45.25</t>
+          <t>45.65</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>45.45</t>
+          <t>46.3</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>44.5</t>
+          <t>45.3</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>45.05</t>
+          <t>45.55</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1295,7 +1295,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>【d2】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1305,12 +1305,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-0.55</t>
+          <t>-0.44</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>104.0</t>
+          <t>246.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>45.25</t>
+          <t>45.05</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1330,7 +1330,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -1340,7 +1340,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-8.48</t>
+          <t>8.33</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1405,7 +1405,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-9.05</t>
+          <t>-9.45</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1415,17 +1415,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>4.09</t>
+          <t>9.67</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1436,12 +1436,12 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>246</t>
+          <t>103</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
@@ -1451,51 +1451,51 @@
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>37.52</t>
+          <t>9.52</t>
         </is>
       </c>
       <c r="AH3" t="n">
-        <v>-0.83</v>
+        <v>-0.95</v>
       </c>
       <c r="AI3" t="n">
-        <v>-0.75</v>
+        <v>-0.87</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-0.9</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-2.24</t>
+          <t>-2.29</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>45.63</t>
+          <t>45.48</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>45.98</v>
+        <v>45.88</v>
       </c>
       <c r="AN3" t="n">
-        <v>46.39</v>
+        <v>46.32</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>47.46</t>
+          <t>47.41</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>3.73</t>
+          <t>-7.02</t>
         </is>
       </c>
       <c r="AQ3" t="n">
-        <v>-0.24</v>
+        <v>-0.28</v>
       </c>
       <c r="AR3" t="n">
-        <v>-0.25</v>
+        <v>-0.26</v>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-105.93</t>
+          <t>-106.04</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1514,43 +1514,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>75923.10254596888</t>
+          <t>75825.85381355931</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>4714.0</t>
+          <t>11034.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>3990.2</v>
+        <v>5441.2</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>4360.0</t>
+          <t>5022.6</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>11948.92</v>
+        <v>11858.6</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-369</t>
+          <t>418</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-1255.394821893818</t>
+          <t>-1154.46766135493</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-1213.317202241243</t>
+          <t>-599.3682783910481</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>4714.0</t>
+          <t>11034.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1570,7 +1570,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-7.18</t>
+          <t>-7.59</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1615,12 +1615,12 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
@@ -1630,7 +1630,7 @@
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>6.14</t>
+          <t>6.07</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1640,7 +1640,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>10.17</t>
+          <t>10.28</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>46.32</t>
+          <t>46.46</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>4239</t>
+          <t>4286</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1680,22 +1680,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>45.5</t>
+          <t>45.25</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>45.5</t>
+          <t>45.45</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>44.9</t>
+          <t>44.5</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>45.25</t>
+          <t>45.05</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1727,12 +1727,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>-0.55</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>104.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1742,7 +1742,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>45.5</t>
+          <t>45.25</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1752,7 +1752,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1762,7 +1762,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-20.03</t>
+          <t>-8.48</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1827,7 +1827,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-8.54</t>
+          <t>-9.05</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1837,17 +1837,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>3.97</t>
+          <t>4.09</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1858,66 +1858,66 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>246</t>
+          <t>103</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>28.57</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>65.52</t>
+          <t>37.52</t>
         </is>
       </c>
       <c r="AH4" t="n">
-        <v>-0.61</v>
+        <v>-0.83</v>
       </c>
       <c r="AI4" t="n">
-        <v>-0.58</v>
+        <v>-0.75</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-0.89</t>
+          <t>-0.9</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-2.14</t>
+          <t>-2.24</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>45.77999999999999</t>
+          <t>45.63</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>46.04</v>
+        <v>45.98</v>
       </c>
       <c r="AN4" t="n">
-        <v>46.46</v>
+        <v>46.39</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>47.48</t>
+          <t>47.46</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>14.06</t>
+          <t>3.73</t>
         </is>
       </c>
       <c r="AQ4" t="n">
-        <v>-0.22</v>
+        <v>-0.24</v>
       </c>
       <c r="AR4" t="n">
-        <v>-0.26</v>
+        <v>-0.25</v>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-105.99</t>
+          <t>-105.93</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1936,43 +1936,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>75923.10254596888</t>
+          <t>75825.85381355931</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>4590.0</t>
+          <t>4714.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>3743.4</v>
+        <v>3990.2</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>4681.2</t>
+          <t>4360.0</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>12007.9</v>
+        <v>11948.92</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-937</t>
+          <t>-369</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-1263.045298194286</t>
+          <t>-1255.394821893818</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-1369.911479090048</t>
+          <t>-1213.317202241243</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>4590.0</t>
+          <t>4714.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -1992,7 +1992,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-6.67</t>
+          <t>-7.18</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2037,7 +2037,7 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2047,12 +2047,12 @@
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>6.14</t>
+          <t>6.07</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2062,7 +2062,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>10.17</t>
+          <t>10.28</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2077,12 +2077,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>46.32</t>
+          <t>46.46</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>4239</t>
+          <t>4286</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2102,22 +2102,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>46.0</t>
+          <t>45.5</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>46.05</t>
+          <t>45.5</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>45.15</t>
+          <t>44.9</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>45.5</t>
+          <t>45.25</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2149,42 +2149,42 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
+          <t>-0.65</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>101.0</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>45.5</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0.11</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>67.0</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>45.8</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>-1.66</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-14.39</t>
+          <t>-20.03</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2249,7 +2249,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-7.94</t>
+          <t>-8.54</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2259,17 +2259,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>2.63</t>
+          <t>3.97</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2280,63 +2280,63 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>246</t>
+          <t>103</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>28.57</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>65.52</t>
         </is>
       </c>
       <c r="AH5" t="n">
-        <v>-0.17</v>
+        <v>-0.61</v>
       </c>
       <c r="AI5" t="n">
-        <v>-0.52</v>
+        <v>-0.58</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-0.87</t>
+          <t>-0.89</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-2.06</t>
+          <t>-2.14</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>45.88</t>
+          <t>45.77999999999999</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>46.12</v>
+        <v>46.04</v>
       </c>
       <c r="AN5" t="n">
-        <v>46.52</v>
+        <v>46.46</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>47.5</t>
+          <t>47.48</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>20.22</t>
+          <t>14.06</t>
         </is>
       </c>
       <c r="AQ5" t="n">
-        <v>-0.21</v>
+        <v>-0.22</v>
       </c>
       <c r="AR5" t="n">
         <v>-0.26</v>
@@ -2348,7 +2348,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-106.20</t>
+          <t>-105.99</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2358,43 +2358,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>75923.10254596888</t>
+          <t>75825.85381355931</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>3059.0</t>
+          <t>4590.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>3888.8</v>
+        <v>3743.4</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>4542.6</t>
+          <t>4681.2</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>12062.18</v>
+        <v>12007.9</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-653</t>
+          <t>-937</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-1243.615083485966</t>
+          <t>-1263.045298194286</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-1531.406464620841</t>
+          <t>-1369.911479090048</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>3059.0</t>
+          <t>4590.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2414,7 +2414,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-6.05</t>
+          <t>-6.67</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2459,7 +2459,7 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2469,12 +2469,12 @@
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>6.14</t>
+          <t>6.07</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2484,7 +2484,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>10.17</t>
+          <t>10.28</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>46.32</t>
+          <t>46.46</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>4239</t>
+          <t>4286</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2524,22 +2524,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>45.8</t>
+          <t>46.0</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>46.0</t>
+          <t>46.05</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>45.7</t>
+          <t>45.15</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>45.8</t>
+          <t>45.5</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2576,7 +2576,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-1.66</t>
+          <t>-0.55</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -2606,7 +2606,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-2.42</t>
+          <t>-14.39</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2681,17 +2681,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>3.26</t>
+          <t>2.63</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2702,12 +2702,12 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>246</t>
+          <t>103</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
@@ -2717,23 +2717,23 @@
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>89.33</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AH6" t="n">
         <v>-0.17</v>
       </c>
       <c r="AI6" t="n">
-        <v>-0.46</v>
+        <v>-0.52</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-1.07</t>
+          <t>-0.87</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-1.95</t>
+          <t>-2.06</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
@@ -2742,26 +2742,26 @@
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>46.09</v>
+        <v>46.12</v>
       </c>
       <c r="AN6" t="n">
-        <v>46.59</v>
+        <v>46.52</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>47.52</t>
+          <t>47.5</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>18.14</t>
+          <t>20.22</t>
         </is>
       </c>
       <c r="AQ6" t="n">
-        <v>-0.23</v>
+        <v>-0.21</v>
       </c>
       <c r="AR6" t="n">
-        <v>-0.28</v>
+        <v>-0.26</v>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
@@ -2770,7 +2770,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-106.51</t>
+          <t>-106.20</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2780,43 +2780,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>75923.10254596888</t>
+          <t>75825.85381355931</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>3809.0</t>
+          <t>3059.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>4626.6</v>
+        <v>3888.8</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>4741.3</t>
+          <t>4542.6</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>12259.36</v>
+        <v>12062.18</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-114</t>
+          <t>-653</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-1191.289377825079</t>
+          <t>-1243.615083485966</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-1543.3847844998</t>
+          <t>-1531.406464620841</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>3809.0</t>
+          <t>3059.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2881,7 +2881,7 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -2896,7 +2896,7 @@
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>6.14</t>
+          <t>6.07</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2906,7 +2906,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>10.17</t>
+          <t>10.28</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2921,12 +2921,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>46.32</t>
+          <t>46.46</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>4239</t>
+          <t>4286</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2946,17 +2946,17 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>46.2</t>
+          <t>45.8</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>46.2</t>
+          <t>46.0</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>45.6</t>
+          <t>45.7</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -2993,127 +2993,127 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>83.0</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>45.8</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>-0.55</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>-2.42</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>2025-09-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>2025-09-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>2025-03-06 00:00:00</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>2025-03-10 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>51.1</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>49.75</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>57.7</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>56.5</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>-7.94</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>-9.56</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-12-02</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>3.26</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
           <t>-0.43</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>82.0</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>45.8</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>-1.66</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>-20.54</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>2025-09-02 00:00:00</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>2025-09-12 00:00:00</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>2025-03-06 00:00:00</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>2025-03-10 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>51.1</t>
-        </is>
-      </c>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>49.75</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>57.7</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>56.5</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>-7.94</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>-9.56</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>2025-12-01</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>3.22</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>0.00</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3124,12 +3124,12 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>246</t>
+          <t>103</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
@@ -3139,51 +3139,51 @@
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>83.86</t>
+          <t>89.33</t>
         </is>
       </c>
       <c r="AH7" t="n">
-        <v>0.02</v>
+        <v>-0.17</v>
       </c>
       <c r="AI7" t="n">
-        <v>-0.58</v>
+        <v>-0.46</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-1.87</t>
+          <t>-1.95</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>45.79</t>
+          <t>45.88</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>46.06</v>
+        <v>46.09</v>
       </c>
       <c r="AN7" t="n">
-        <v>46.64</v>
+        <v>46.59</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>47.53</t>
+          <t>47.52</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>15.60</t>
+          <t>18.14</t>
         </is>
       </c>
       <c r="AQ7" t="n">
-        <v>-0.25</v>
+        <v>-0.23</v>
       </c>
       <c r="AR7" t="n">
-        <v>-0.29</v>
+        <v>-0.28</v>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
@@ -3192,7 +3192,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-106.80</t>
+          <t>-106.51</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3202,43 +3202,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>75923.10254596888</t>
+          <t>75825.85381355931</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>3779.0</t>
+          <t>3809.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>4604</v>
+        <v>4626.6</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>5794.0</t>
+          <t>4741.3</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>12544.52</v>
+        <v>12259.36</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-1190</t>
+          <t>-114</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-1127.272031156948</t>
+          <t>-1191.289377825079</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-1585.732927737606</t>
+          <t>-1543.3847844998</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>3779.0</t>
+          <t>3809.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3303,7 +3303,7 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3318,7 +3318,7 @@
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>6.14</t>
+          <t>6.07</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3328,7 +3328,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>10.17</t>
+          <t>10.28</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3343,12 +3343,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>46.32</t>
+          <t>46.46</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>4239</t>
+          <t>4286</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3368,17 +3368,17 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>46.0</t>
+          <t>46.2</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>46.05</t>
+          <t>46.2</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>45.55</t>
+          <t>45.6</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3415,42 +3415,42 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
+          <t>-0.43</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>45.8</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>-0.55</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>75.0</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>46.0</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>-2.11</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-26.22</t>
+          <t>-20.54</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3515,7 +3515,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-7.54</t>
+          <t>-7.94</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3525,17 +3525,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>2.95</t>
+          <t>3.22</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-0.98</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3546,66 +3546,66 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>246</t>
+          <t>103</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>71.07</t>
+          <t>83.86</t>
         </is>
       </c>
       <c r="AH8" t="n">
-        <v>0.68</v>
+        <v>0.02</v>
       </c>
       <c r="AI8" t="n">
-        <v>-0.75</v>
+        <v>-0.58</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-1.76</t>
+          <t>-1.87</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>45.69</t>
+          <t>45.79</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>46.04</v>
+        <v>46.06</v>
       </c>
       <c r="AN8" t="n">
-        <v>46.7</v>
+        <v>46.64</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>47.54</t>
+          <t>47.53</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>12.46</t>
+          <t>15.60</t>
         </is>
       </c>
       <c r="AQ8" t="n">
-        <v>-0.26</v>
+        <v>-0.25</v>
       </c>
       <c r="AR8" t="n">
-        <v>-0.3</v>
+        <v>-0.29</v>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
@@ -3614,7 +3614,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-107.07</t>
+          <t>-106.80</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3624,43 +3624,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>75923.10254596888</t>
+          <t>75825.85381355931</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>3480.0</t>
+          <t>3779.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>4729.8</v>
+        <v>4604</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>6410.4</t>
+          <t>5794.0</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>12782.88</v>
+        <v>12544.52</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-1680</t>
+          <t>-1190</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-1043.91550450592</t>
+          <t>-1127.272031156948</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-1586.382670658128</t>
+          <t>-1585.732927737606</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>3480.0</t>
+          <t>3779.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3680,7 +3680,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-5.64</t>
+          <t>-6.05</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3725,7 +3725,7 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -3735,12 +3735,12 @@
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>6.14</t>
+          <t>6.07</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3750,7 +3750,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>10.17</t>
+          <t>10.28</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>46.32</t>
+          <t>46.46</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>4239</t>
+          <t>4286</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3790,22 +3790,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>46.4</t>
+          <t>46.0</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>46.45</t>
+          <t>46.05</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>46.0</t>
+          <t>45.55</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>46.0</t>
+          <t>45.8</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>116.0</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3862,7 +3862,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-2.11</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -3872,7 +3872,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-19.32</t>
+          <t>-26.22</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3947,17 +3947,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>4.56</t>
+          <t>2.95</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -3968,66 +3968,66 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>246</t>
+          <t>103</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>67.57</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>46.25</t>
+          <t>71.07</t>
         </is>
       </c>
       <c r="AH9" t="n">
-        <v>1.23</v>
+        <v>0.68</v>
       </c>
       <c r="AI9" t="n">
-        <v>-1.23</v>
+        <v>-0.75</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-1.61</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-1.65</t>
+          <t>-1.76</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>45.44</t>
+          <t>45.69</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>46</v>
+        <v>46.04</v>
       </c>
       <c r="AN9" t="n">
-        <v>46.76</v>
+        <v>46.7</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>47.55</t>
+          <t>47.54</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>12.46</t>
         </is>
       </c>
       <c r="AQ9" t="n">
-        <v>-0.31</v>
+        <v>-0.26</v>
       </c>
       <c r="AR9" t="n">
-        <v>-0.31</v>
+        <v>-0.3</v>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
@@ -4036,7 +4036,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-107.29</t>
+          <t>-107.07</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4046,43 +4046,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>75923.10254596888</t>
+          <t>75825.85381355931</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>5317.0</t>
+          <t>3480.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>5619</v>
+        <v>4729.8</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>6964.2</t>
+          <t>6410.4</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>13246.56</v>
+        <v>12782.88</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-1345</t>
+          <t>-1680</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-945.2851106600637</t>
+          <t>-1043.91550450592</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-1498.618636592511</t>
+          <t>-1586.382670658128</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>5317.0</t>
+          <t>3480.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4147,7 +4147,7 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4162,7 +4162,7 @@
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>6.14</t>
+          <t>6.07</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4172,7 +4172,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>10.17</t>
+          <t>10.28</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4187,12 +4187,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>46.32</t>
+          <t>46.46</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>4239</t>
+          <t>4286</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4212,17 +4212,17 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>45.8</t>
+          <t>46.4</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>46.1</t>
+          <t>46.45</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>45.7</t>
+          <t>46.0</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4249,7 +4249,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d2】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4259,12 +4259,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>148.0</t>
+          <t>116.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4274,7 +4274,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>45.8</t>
+          <t>46.0</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4284,7 +4284,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-1.66</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -4294,7 +4294,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-34.26</t>
+          <t>-19.32</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4359,7 +4359,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-7.94</t>
+          <t>-7.54</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4369,17 +4369,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>5.82</t>
+          <t>4.56</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4390,63 +4390,63 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>246</t>
+          <t>103</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>45.65</t>
+          <t>67.57</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>30.16</t>
+          <t>46.25</t>
         </is>
       </c>
       <c r="AH10" t="n">
-        <v>0.99</v>
+        <v>1.23</v>
       </c>
       <c r="AI10" t="n">
-        <v>-1.35</v>
+        <v>-1.23</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-1.85</t>
+          <t>-1.61</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-1.48</t>
+          <t>-1.65</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>45.35</t>
+          <t>45.44</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>45.97</v>
+        <v>46</v>
       </c>
       <c r="AN10" t="n">
-        <v>46.84</v>
+        <v>46.76</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>47.54</t>
+          <t>47.55</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-12.73</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="AQ10" t="n">
-        <v>-0.35</v>
+        <v>-0.31</v>
       </c>
       <c r="AR10" t="n">
         <v>-0.31</v>
@@ -4458,7 +4458,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-107.33</t>
+          <t>-107.29</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4468,43 +4468,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>75923.10254596888</t>
+          <t>75825.85381355931</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>6748.0</t>
+          <t>5317.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>5196.4</v>
+        <v>5619</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>7904.3</t>
+          <t>6964.2</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>13455.3</v>
+        <v>13246.56</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-2707</t>
+          <t>-1345</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-844.6790150359823</t>
+          <t>-945.2851106600637</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-1516.540779477615</t>
+          <t>-1498.618636592511</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>6748.0</t>
+          <t>5317.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4524,7 +4524,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-6.05</t>
+          <t>-5.64</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4569,7 +4569,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4579,12 +4579,12 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>6.14</t>
+          <t>6.07</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4594,7 +4594,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>10.17</t>
+          <t>10.28</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4609,12 +4609,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>46.32</t>
+          <t>46.46</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>4239</t>
+          <t>4286</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4634,22 +4634,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>45.45</t>
+          <t>45.8</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>46.15</t>
+          <t>46.1</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>45.35</t>
+          <t>45.7</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>45.8</t>
+          <t>46.0</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>148.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4696,7 +4696,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>45.35</t>
+          <t>45.8</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4706,7 +4706,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>-0.55</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -4716,7 +4716,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-48.83</t>
+          <t>-34.26</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4781,7 +4781,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-8.84</t>
+          <t>-7.94</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4791,17 +4791,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>3.18</t>
+          <t>5.82</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-1.32</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4812,66 +4812,66 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>246</t>
+          <t>103</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>25.53</t>
+          <t>45.65</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>14.94</t>
+          <t>30.16</t>
         </is>
       </c>
       <c r="AH11" t="n">
-        <v>0.33</v>
+        <v>0.99</v>
       </c>
       <c r="AI11" t="n">
-        <v>-1.67</v>
+        <v>-1.35</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-2.0</t>
+          <t>-1.85</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-1.30</t>
+          <t>-1.48</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>45.2</t>
+          <t>45.35</t>
         </is>
       </c>
       <c r="AM11" t="n">
         <v>45.97</v>
       </c>
       <c r="AN11" t="n">
-        <v>46.91</v>
+        <v>46.84</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>47.52</t>
+          <t>47.54</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-28.10</t>
+          <t>-12.73</t>
         </is>
       </c>
       <c r="AQ11" t="n">
-        <v>-0.39</v>
+        <v>-0.35</v>
       </c>
       <c r="AR11" t="n">
-        <v>-0.3</v>
+        <v>-0.31</v>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
@@ -4880,7 +4880,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-107.09</t>
+          <t>-107.33</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4890,43 +4890,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>75923.10254596888</t>
+          <t>75825.85381355931</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>3696.0</t>
+          <t>6748.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>4856</v>
+        <v>5196.4</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>9489.5</t>
+          <t>7904.3</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>14335.48</v>
+        <v>13455.3</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-4633</t>
+          <t>-2707</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-722.5223305920491</t>
+          <t>-844.6790150359823</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-1641.303098617845</t>
+          <t>-1516.540779477615</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>3696.0</t>
+          <t>6748.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -4946,7 +4946,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-6.97</t>
+          <t>-6.05</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -4991,7 +4991,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5001,12 +5001,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>6.14</t>
+          <t>6.07</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5016,7 +5016,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>10.17</t>
+          <t>10.28</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5031,12 +5031,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>46.32</t>
+          <t>46.46</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>4239</t>
+          <t>4286</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5056,22 +5056,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>46.0</t>
+          <t>45.45</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>46.0</t>
+          <t>46.15</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>45.3</t>
+          <t>45.35</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>45.35</t>
+          <t>45.8</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5103,12 +5103,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>98.0</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5118,7 +5118,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>45.3</t>
+          <t>45.35</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5128,7 +5128,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-0.55</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -5138,7 +5138,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-46.16</t>
+          <t>-48.83</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-8.94</t>
+          <t>-8.84</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5213,17 +5213,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>3.85</t>
+          <t>3.18</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>-1.32</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5234,66 +5234,66 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>246</t>
+          <t>103</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>19.3</t>
+          <t>25.53</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>15.36</t>
+          <t>14.94</t>
         </is>
       </c>
       <c r="AH12" t="n">
-        <v>0.47</v>
+        <v>0.33</v>
       </c>
       <c r="AI12" t="n">
-        <v>-1.96</v>
+        <v>-1.67</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-2.17</t>
+          <t>-2.0</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-1.05</t>
+          <t>-1.30</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>45.09</t>
+          <t>45.2</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>45.99</v>
+        <v>45.97</v>
       </c>
       <c r="AN12" t="n">
-        <v>47.02</v>
+        <v>46.91</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>47.51</t>
+          <t>47.52</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-35.53</t>
+          <t>-28.10</t>
         </is>
       </c>
       <c r="AQ12" t="n">
-        <v>-0.38</v>
+        <v>-0.39</v>
       </c>
       <c r="AR12" t="n">
-        <v>-0.28</v>
+        <v>-0.3</v>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
@@ -5302,7 +5302,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-106.59</t>
+          <t>-107.09</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5312,43 +5312,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>75923.10254596888</t>
+          <t>75825.85381355931</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>4408.0</t>
+          <t>3696.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>6984</v>
+        <v>4856</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>12971.6</t>
+          <t>9489.5</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>15065.26</v>
+        <v>14335.48</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-5987</t>
+          <t>-4633</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-555.4712818600863</t>
+          <t>-722.5223305920491</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-1433.917015296107</t>
+          <t>-1641.303098617845</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>4408.0</t>
+          <t>3696.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5368,7 +5368,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-7.08</t>
+          <t>-6.97</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5413,7 +5413,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5428,7 +5428,7 @@
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>6.14</t>
+          <t>6.07</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5438,7 +5438,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>10.17</t>
+          <t>10.28</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5453,12 +5453,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>46.32</t>
+          <t>46.46</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>4239</t>
+          <t>4286</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5478,22 +5478,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>44.95</t>
+          <t>46.0</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>45.45</t>
+          <t>46.0</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>44.9</t>
+          <t>45.3</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>45.3</t>
+          <t>45.35</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/PET膜.xlsx
+++ b/Result/checksun_type/PET膜.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>-1.8</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>478.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>45.55</t>
+          <t>44.75</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>9.71</t>
+          <t>40.89</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-8.44</t>
+          <t>-10.05</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>4.05</t>
+          <t>18.79</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-1.09</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,17 +1014,17 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>478</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>52.63</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
@@ -1033,47 +1033,47 @@
         </is>
       </c>
       <c r="AH2" t="n">
-        <v>0.26</v>
+        <v>-1.04</v>
       </c>
       <c r="AI2" t="n">
-        <v>-0.78</v>
+        <v>-0.93</v>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-1.04</t>
+          <t>-1.16</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-2.32</t>
+          <t>-2.39</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>45.42999999999999</t>
+          <t>45.21999999999999</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>45.78</v>
+        <v>45.64</v>
       </c>
       <c r="AN2" t="n">
-        <v>46.27</v>
+        <v>46.18</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>47.37</t>
+          <t>47.31</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-14.07</t>
         </is>
       </c>
       <c r="AQ2" t="n">
-        <v>-0.26</v>
+        <v>-0.31</v>
       </c>
       <c r="AR2" t="n">
-        <v>-0.26</v>
+        <v>-0.27</v>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-106.04</t>
+          <t>-106.26</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1092,43 +1092,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>75825.85381355931</t>
+          <t>75763.96544428772</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>4714.0</t>
+          <t>21298.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>5622.2</v>
+        <v>9270</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>5124.4</t>
+          <t>6579.4</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>11707.74</v>
+        <v>11878.36</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>497</t>
+          <t>2690</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-1073.567994182808</t>
+          <t>-814.4929814714977</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-628.6198247361344</t>
+          <t>610.419588440709</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>4714.0</t>
+          <t>21298.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-6.56</t>
+          <t>-8.21</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1193,22 +1193,22 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>6.07</t>
+          <t>6.18</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>10.28</t>
+          <t>10.1</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1233,12 +1233,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>46.46</t>
+          <t>46.45</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>4286</t>
+          <t>4211</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1258,22 +1258,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>45.65</t>
+          <t>44.55</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>46.3</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>45.3</t>
+          <t>44.3</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>45.55</t>
+          <t>44.75</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1305,12 +1305,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>246.0</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>45.05</t>
+          <t>45.55</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1330,7 +1330,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>-1.79</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -1340,7 +1340,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>8.33</t>
+          <t>9.71</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1405,7 +1405,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-9.45</t>
+          <t>-8.44</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1415,17 +1415,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>9.67</t>
+          <t>4.05</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>-1.09</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1436,63 +1436,63 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>478</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>52.63</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>9.52</t>
+          <t>17.54</t>
         </is>
       </c>
       <c r="AH3" t="n">
-        <v>-0.95</v>
+        <v>0.26</v>
       </c>
       <c r="AI3" t="n">
-        <v>-0.87</v>
+        <v>-0.78</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-0.97</t>
+          <t>-1.04</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-2.29</t>
+          <t>-2.32</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>45.48</t>
+          <t>45.42999999999999</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>45.88</v>
+        <v>45.78</v>
       </c>
       <c r="AN3" t="n">
-        <v>46.32</v>
+        <v>46.27</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>47.41</t>
+          <t>47.37</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-7.02</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AQ3" t="n">
-        <v>-0.28</v>
+        <v>-0.26</v>
       </c>
       <c r="AR3" t="n">
         <v>-0.26</v>
@@ -1514,43 +1514,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>75825.85381355931</t>
+          <t>75763.96544428772</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>11034.0</t>
+          <t>4714.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>5441.2</v>
+        <v>5622.2</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>5022.6</t>
+          <t>5124.4</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>11858.6</v>
+        <v>11707.74</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>418</t>
+          <t>497</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-1154.46766135493</t>
+          <t>-1073.567994182808</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-599.3682783910481</t>
+          <t>-628.6198247361344</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>11034.0</t>
+          <t>4714.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1570,7 +1570,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-7.59</t>
+          <t>-6.56</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1615,22 +1615,22 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>6.07</t>
+          <t>6.18</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1640,7 +1640,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>10.28</t>
+          <t>10.1</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>46.46</t>
+          <t>46.45</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>4286</t>
+          <t>4211</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1680,22 +1680,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>45.25</t>
+          <t>45.65</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>45.45</t>
+          <t>46.3</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>44.5</t>
+          <t>45.3</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>45.05</t>
+          <t>45.55</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1717,7 +1717,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>【d2】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1727,12 +1727,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-0.55</t>
+          <t>-0.44</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>104.0</t>
+          <t>246.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1742,7 +1742,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>45.25</t>
+          <t>45.05</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1752,7 +1752,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1762,7 +1762,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-8.48</t>
+          <t>8.33</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1827,7 +1827,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-9.05</t>
+          <t>-9.45</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1837,17 +1837,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>4.09</t>
+          <t>9.67</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1858,12 +1858,12 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>478</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
@@ -1873,51 +1873,51 @@
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>37.52</t>
+          <t>9.52</t>
         </is>
       </c>
       <c r="AH4" t="n">
-        <v>-0.83</v>
+        <v>-0.95</v>
       </c>
       <c r="AI4" t="n">
-        <v>-0.75</v>
+        <v>-0.87</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-0.9</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-2.24</t>
+          <t>-2.29</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>45.63</t>
+          <t>45.48</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>45.98</v>
+        <v>45.88</v>
       </c>
       <c r="AN4" t="n">
-        <v>46.39</v>
+        <v>46.32</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>47.46</t>
+          <t>47.41</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>3.73</t>
+          <t>-7.02</t>
         </is>
       </c>
       <c r="AQ4" t="n">
-        <v>-0.24</v>
+        <v>-0.28</v>
       </c>
       <c r="AR4" t="n">
-        <v>-0.25</v>
+        <v>-0.26</v>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-105.93</t>
+          <t>-106.04</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1936,43 +1936,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>75825.85381355931</t>
+          <t>75763.96544428772</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>4714.0</t>
+          <t>11034.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>3990.2</v>
+        <v>5441.2</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>4360.0</t>
+          <t>5022.6</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>11948.92</v>
+        <v>11858.6</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-369</t>
+          <t>418</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-1255.394821893818</t>
+          <t>-1154.46766135493</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-1213.317202241243</t>
+          <t>-599.3682783910481</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>4714.0</t>
+          <t>11034.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -1992,7 +1992,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-7.18</t>
+          <t>-7.59</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2037,12 +2037,12 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
@@ -2052,7 +2052,7 @@
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>6.07</t>
+          <t>6.18</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2062,7 +2062,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>10.28</t>
+          <t>10.1</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2077,12 +2077,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>46.46</t>
+          <t>46.45</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>4286</t>
+          <t>4211</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2102,22 +2102,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>45.5</t>
+          <t>45.25</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>45.5</t>
+          <t>45.45</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>44.9</t>
+          <t>44.5</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>45.25</t>
+          <t>45.05</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2149,12 +2149,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>-0.55</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>104.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2164,7 +2164,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>45.5</t>
+          <t>45.25</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2174,7 +2174,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>-1.12</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -2184,7 +2184,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-20.03</t>
+          <t>-8.48</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2249,7 +2249,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-8.54</t>
+          <t>-9.05</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2259,17 +2259,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>3.97</t>
+          <t>4.09</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2280,66 +2280,66 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>478</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>28.57</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>65.52</t>
+          <t>37.52</t>
         </is>
       </c>
       <c r="AH5" t="n">
-        <v>-0.61</v>
+        <v>-0.83</v>
       </c>
       <c r="AI5" t="n">
-        <v>-0.58</v>
+        <v>-0.75</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-0.89</t>
+          <t>-0.9</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-2.14</t>
+          <t>-2.24</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>45.77999999999999</t>
+          <t>45.63</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>46.04</v>
+        <v>45.98</v>
       </c>
       <c r="AN5" t="n">
-        <v>46.46</v>
+        <v>46.39</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>47.48</t>
+          <t>47.46</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>14.06</t>
+          <t>3.73</t>
         </is>
       </c>
       <c r="AQ5" t="n">
-        <v>-0.22</v>
+        <v>-0.24</v>
       </c>
       <c r="AR5" t="n">
-        <v>-0.26</v>
+        <v>-0.25</v>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
@@ -2348,7 +2348,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-105.99</t>
+          <t>-105.93</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2358,43 +2358,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>75825.85381355931</t>
+          <t>75763.96544428772</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>4590.0</t>
+          <t>4714.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>3743.4</v>
+        <v>3990.2</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>4681.2</t>
+          <t>4360.0</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>12007.9</v>
+        <v>11948.92</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-937</t>
+          <t>-369</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-1263.045298194286</t>
+          <t>-1255.394821893818</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-1369.911479090048</t>
+          <t>-1213.317202241243</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>4590.0</t>
+          <t>4714.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2414,7 +2414,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-6.67</t>
+          <t>-7.18</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2459,7 +2459,7 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2469,12 +2469,12 @@
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>6.07</t>
+          <t>6.18</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2484,7 +2484,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>10.28</t>
+          <t>10.1</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>46.46</t>
+          <t>46.45</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>4286</t>
+          <t>4211</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2524,22 +2524,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>46.0</t>
+          <t>45.5</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>46.05</t>
+          <t>45.5</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>45.15</t>
+          <t>44.9</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>45.5</t>
+          <t>45.25</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2571,42 +2571,42 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
+          <t>-0.65</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>101.0</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>45.5</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>-1.68</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>67.0</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>45.8</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>-0.55</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-14.39</t>
+          <t>-20.03</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2671,7 +2671,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-7.94</t>
+          <t>-8.54</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2681,17 +2681,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>2.63</t>
+          <t>3.97</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2702,63 +2702,63 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>478</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>28.57</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>65.52</t>
         </is>
       </c>
       <c r="AH6" t="n">
-        <v>-0.17</v>
+        <v>-0.61</v>
       </c>
       <c r="AI6" t="n">
-        <v>-0.52</v>
+        <v>-0.58</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-0.87</t>
+          <t>-0.89</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-2.06</t>
+          <t>-2.14</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>45.88</t>
+          <t>45.77999999999999</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>46.12</v>
+        <v>46.04</v>
       </c>
       <c r="AN6" t="n">
-        <v>46.52</v>
+        <v>46.46</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>47.5</t>
+          <t>47.48</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>20.22</t>
+          <t>14.06</t>
         </is>
       </c>
       <c r="AQ6" t="n">
-        <v>-0.21</v>
+        <v>-0.22</v>
       </c>
       <c r="AR6" t="n">
         <v>-0.26</v>
@@ -2770,7 +2770,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-106.20</t>
+          <t>-105.99</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2780,43 +2780,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>75825.85381355931</t>
+          <t>75763.96544428772</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>3059.0</t>
+          <t>4590.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>3888.8</v>
+        <v>3743.4</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>4542.6</t>
+          <t>4681.2</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>12062.18</v>
+        <v>12007.9</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-653</t>
+          <t>-937</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-1243.615083485966</t>
+          <t>-1263.045298194286</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-1531.406464620841</t>
+          <t>-1369.911479090048</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>3059.0</t>
+          <t>4590.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2836,7 +2836,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-6.05</t>
+          <t>-6.67</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2881,7 +2881,7 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -2891,12 +2891,12 @@
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>6.07</t>
+          <t>6.18</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2906,7 +2906,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>10.28</t>
+          <t>10.1</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2921,12 +2921,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>46.46</t>
+          <t>46.45</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>4286</t>
+          <t>4211</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2946,22 +2946,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>45.8</t>
+          <t>46.0</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>46.0</t>
+          <t>46.05</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>45.7</t>
+          <t>45.15</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>45.8</t>
+          <t>45.5</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -2998,7 +2998,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3018,7 +3018,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-0.55</t>
+          <t>-2.35</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-2.42</t>
+          <t>-14.39</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3103,17 +3103,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>3.26</t>
+          <t>2.63</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3124,12 +3124,12 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>478</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
@@ -3139,23 +3139,23 @@
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>89.33</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AH7" t="n">
         <v>-0.17</v>
       </c>
       <c r="AI7" t="n">
-        <v>-0.46</v>
+        <v>-0.52</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-1.07</t>
+          <t>-0.87</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-1.95</t>
+          <t>-2.06</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
@@ -3164,26 +3164,26 @@
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>46.09</v>
+        <v>46.12</v>
       </c>
       <c r="AN7" t="n">
-        <v>46.59</v>
+        <v>46.52</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>47.52</t>
+          <t>47.5</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>18.14</t>
+          <t>20.22</t>
         </is>
       </c>
       <c r="AQ7" t="n">
-        <v>-0.23</v>
+        <v>-0.21</v>
       </c>
       <c r="AR7" t="n">
-        <v>-0.28</v>
+        <v>-0.26</v>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
@@ -3192,7 +3192,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-106.51</t>
+          <t>-106.20</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3202,43 +3202,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>75825.85381355931</t>
+          <t>75763.96544428772</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>3809.0</t>
+          <t>3059.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>4626.6</v>
+        <v>3888.8</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>4741.3</t>
+          <t>4542.6</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>12259.36</v>
+        <v>12062.18</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-114</t>
+          <t>-653</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-1191.289377825079</t>
+          <t>-1243.615083485966</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-1543.3847844998</t>
+          <t>-1531.406464620841</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>3809.0</t>
+          <t>3059.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3303,7 +3303,7 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3318,7 +3318,7 @@
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>6.07</t>
+          <t>6.18</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3328,7 +3328,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>10.28</t>
+          <t>10.1</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3343,12 +3343,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>46.46</t>
+          <t>46.45</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>4286</t>
+          <t>4211</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3368,17 +3368,17 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>46.2</t>
+          <t>45.8</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>46.2</t>
+          <t>46.0</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>45.6</t>
+          <t>45.7</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3415,127 +3415,127 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>83.0</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>45.8</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>-2.35</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>-2.42</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>2025-09-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>2025-09-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>2025-03-06 00:00:00</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>2025-03-10 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>51.1</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>49.75</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>57.7</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>56.5</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>-7.94</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>-9.56</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-12-02</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>3.26</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
           <t>-0.43</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>82.0</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>45.8</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>-0.55</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>-20.54</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>2025-09-02 00:00:00</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>2025-09-12 00:00:00</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>2025-03-06 00:00:00</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>2025-03-10 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>51.1</t>
-        </is>
-      </c>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t>49.75</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>57.7</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>56.5</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>-7.94</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>-9.56</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>2025-12-01</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>3.22</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>0.00</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3546,12 +3546,12 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>478</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
@@ -3561,51 +3561,51 @@
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>83.86</t>
+          <t>89.33</t>
         </is>
       </c>
       <c r="AH8" t="n">
-        <v>0.02</v>
+        <v>-0.17</v>
       </c>
       <c r="AI8" t="n">
-        <v>-0.58</v>
+        <v>-0.46</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-1.87</t>
+          <t>-1.95</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>45.79</t>
+          <t>45.88</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>46.06</v>
+        <v>46.09</v>
       </c>
       <c r="AN8" t="n">
-        <v>46.64</v>
+        <v>46.59</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>47.53</t>
+          <t>47.52</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>15.60</t>
+          <t>18.14</t>
         </is>
       </c>
       <c r="AQ8" t="n">
-        <v>-0.25</v>
+        <v>-0.23</v>
       </c>
       <c r="AR8" t="n">
-        <v>-0.29</v>
+        <v>-0.28</v>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
@@ -3614,7 +3614,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-106.80</t>
+          <t>-106.51</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3624,43 +3624,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>75825.85381355931</t>
+          <t>75763.96544428772</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>3779.0</t>
+          <t>3809.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>4604</v>
+        <v>4626.6</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>5794.0</t>
+          <t>4741.3</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>12544.52</v>
+        <v>12259.36</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-1190</t>
+          <t>-114</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-1127.272031156948</t>
+          <t>-1191.289377825079</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-1585.732927737606</t>
+          <t>-1543.3847844998</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>3779.0</t>
+          <t>3809.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3725,7 +3725,7 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -3740,7 +3740,7 @@
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>6.07</t>
+          <t>6.18</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3750,7 +3750,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>10.28</t>
+          <t>10.1</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>46.46</t>
+          <t>46.45</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>4286</t>
+          <t>4211</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3790,17 +3790,17 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>46.0</t>
+          <t>46.2</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>46.05</t>
+          <t>46.2</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>45.55</t>
+          <t>45.6</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -3837,42 +3837,42 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
+          <t>-0.43</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>45.8</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>-2.35</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>75.0</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>46.0</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>-0.99</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-26.22</t>
+          <t>-20.54</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3937,7 +3937,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-7.54</t>
+          <t>-7.94</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -3947,17 +3947,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>2.95</t>
+          <t>3.22</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-0.98</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -3968,66 +3968,66 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>478</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>71.07</t>
+          <t>83.86</t>
         </is>
       </c>
       <c r="AH9" t="n">
-        <v>0.68</v>
+        <v>0.02</v>
       </c>
       <c r="AI9" t="n">
-        <v>-0.75</v>
+        <v>-0.58</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-1.76</t>
+          <t>-1.87</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>45.69</t>
+          <t>45.79</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>46.04</v>
+        <v>46.06</v>
       </c>
       <c r="AN9" t="n">
-        <v>46.7</v>
+        <v>46.64</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>47.54</t>
+          <t>47.53</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>12.46</t>
+          <t>15.60</t>
         </is>
       </c>
       <c r="AQ9" t="n">
-        <v>-0.26</v>
+        <v>-0.25</v>
       </c>
       <c r="AR9" t="n">
-        <v>-0.3</v>
+        <v>-0.29</v>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
@@ -4036,7 +4036,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-107.07</t>
+          <t>-106.80</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4046,43 +4046,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>75825.85381355931</t>
+          <t>75763.96544428772</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>3480.0</t>
+          <t>3779.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>4729.8</v>
+        <v>4604</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>6410.4</t>
+          <t>5794.0</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>12782.88</v>
+        <v>12544.52</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-1680</t>
+          <t>-1190</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-1043.91550450592</t>
+          <t>-1127.272031156948</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-1586.382670658128</t>
+          <t>-1585.732927737606</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>3480.0</t>
+          <t>3779.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-5.64</t>
+          <t>-6.05</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4147,7 +4147,7 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4157,12 +4157,12 @@
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>6.07</t>
+          <t>6.18</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4172,7 +4172,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>10.28</t>
+          <t>10.1</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4187,12 +4187,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>46.46</t>
+          <t>46.45</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>4286</t>
+          <t>4211</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4212,22 +4212,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>46.4</t>
+          <t>46.0</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>46.45</t>
+          <t>46.05</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>46.0</t>
+          <t>45.55</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>46.0</t>
+          <t>45.8</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4259,12 +4259,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>116.0</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4284,7 +4284,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>-2.79</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -4294,7 +4294,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-19.32</t>
+          <t>-26.22</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4369,17 +4369,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>4.56</t>
+          <t>2.95</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4390,66 +4390,66 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>478</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>67.57</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>46.25</t>
+          <t>71.07</t>
         </is>
       </c>
       <c r="AH10" t="n">
-        <v>1.23</v>
+        <v>0.68</v>
       </c>
       <c r="AI10" t="n">
-        <v>-1.23</v>
+        <v>-0.75</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-1.61</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-1.65</t>
+          <t>-1.76</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>45.44</t>
+          <t>45.69</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>46</v>
+        <v>46.04</v>
       </c>
       <c r="AN10" t="n">
-        <v>46.76</v>
+        <v>46.7</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>47.55</t>
+          <t>47.54</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>12.46</t>
         </is>
       </c>
       <c r="AQ10" t="n">
-        <v>-0.31</v>
+        <v>-0.26</v>
       </c>
       <c r="AR10" t="n">
-        <v>-0.31</v>
+        <v>-0.3</v>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
@@ -4458,7 +4458,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-107.29</t>
+          <t>-107.07</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4468,43 +4468,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>75825.85381355931</t>
+          <t>75763.96544428772</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>5317.0</t>
+          <t>3480.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>5619</v>
+        <v>4729.8</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>6964.2</t>
+          <t>6410.4</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>13246.56</v>
+        <v>12782.88</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-1345</t>
+          <t>-1680</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-945.2851106600637</t>
+          <t>-1043.91550450592</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-1498.618636592511</t>
+          <t>-1586.382670658128</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>5317.0</t>
+          <t>3480.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4569,7 +4569,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4584,7 +4584,7 @@
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>6.07</t>
+          <t>6.18</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4594,7 +4594,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>10.28</t>
+          <t>10.1</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4609,12 +4609,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>46.46</t>
+          <t>46.45</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>4286</t>
+          <t>4211</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4634,17 +4634,17 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>45.8</t>
+          <t>46.4</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>46.1</t>
+          <t>46.45</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>45.7</t>
+          <t>46.0</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -4671,7 +4671,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d2】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>148.0</t>
+          <t>116.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4696,7 +4696,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>45.8</t>
+          <t>46.0</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4706,7 +4706,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-0.55</t>
+          <t>-2.79</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -4716,7 +4716,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-34.26</t>
+          <t>-19.32</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4781,7 +4781,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-7.94</t>
+          <t>-7.54</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4791,17 +4791,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>5.82</t>
+          <t>4.56</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4812,63 +4812,63 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>478</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>45.65</t>
+          <t>67.57</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>30.16</t>
+          <t>46.25</t>
         </is>
       </c>
       <c r="AH11" t="n">
-        <v>0.99</v>
+        <v>1.23</v>
       </c>
       <c r="AI11" t="n">
-        <v>-1.35</v>
+        <v>-1.23</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-1.85</t>
+          <t>-1.61</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-1.48</t>
+          <t>-1.65</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>45.35</t>
+          <t>45.44</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>45.97</v>
+        <v>46</v>
       </c>
       <c r="AN11" t="n">
-        <v>46.84</v>
+        <v>46.76</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>47.54</t>
+          <t>47.55</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-12.73</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="AQ11" t="n">
-        <v>-0.35</v>
+        <v>-0.31</v>
       </c>
       <c r="AR11" t="n">
         <v>-0.31</v>
@@ -4880,7 +4880,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-107.33</t>
+          <t>-107.29</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4890,43 +4890,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>75825.85381355931</t>
+          <t>75763.96544428772</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>6748.0</t>
+          <t>5317.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>5196.4</v>
+        <v>5619</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>7904.3</t>
+          <t>6964.2</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>13455.3</v>
+        <v>13246.56</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-2707</t>
+          <t>-1345</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-844.6790150359823</t>
+          <t>-945.2851106600637</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-1516.540779477615</t>
+          <t>-1498.618636592511</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>6748.0</t>
+          <t>5317.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -4946,7 +4946,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-6.05</t>
+          <t>-5.64</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -4991,7 +4991,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5001,12 +5001,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>6.07</t>
+          <t>6.18</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5016,7 +5016,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>10.28</t>
+          <t>10.1</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5031,12 +5031,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>46.46</t>
+          <t>46.45</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>4286</t>
+          <t>4211</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5056,22 +5056,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>45.45</t>
+          <t>45.8</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>46.15</t>
+          <t>46.1</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>45.35</t>
+          <t>45.7</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>45.8</t>
+          <t>46.0</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5103,12 +5103,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>148.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5118,7 +5118,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>45.35</t>
+          <t>45.8</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5128,7 +5128,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>-2.35</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -5138,7 +5138,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-48.83</t>
+          <t>-34.26</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-8.84</t>
+          <t>-7.94</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5213,17 +5213,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>3.18</t>
+          <t>5.82</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-1.32</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5234,66 +5234,66 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>478</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>25.53</t>
+          <t>45.65</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>14.94</t>
+          <t>30.16</t>
         </is>
       </c>
       <c r="AH12" t="n">
-        <v>0.33</v>
+        <v>0.99</v>
       </c>
       <c r="AI12" t="n">
-        <v>-1.67</v>
+        <v>-1.35</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-2.0</t>
+          <t>-1.85</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-1.30</t>
+          <t>-1.48</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>45.2</t>
+          <t>45.35</t>
         </is>
       </c>
       <c r="AM12" t="n">
         <v>45.97</v>
       </c>
       <c r="AN12" t="n">
-        <v>46.91</v>
+        <v>46.84</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>47.52</t>
+          <t>47.54</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-28.10</t>
+          <t>-12.73</t>
         </is>
       </c>
       <c r="AQ12" t="n">
-        <v>-0.39</v>
+        <v>-0.35</v>
       </c>
       <c r="AR12" t="n">
-        <v>-0.3</v>
+        <v>-0.31</v>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
@@ -5302,7 +5302,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-107.09</t>
+          <t>-107.33</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5312,43 +5312,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>75825.85381355931</t>
+          <t>75763.96544428772</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>3696.0</t>
+          <t>6748.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>4856</v>
+        <v>5196.4</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>9489.5</t>
+          <t>7904.3</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>14335.48</v>
+        <v>13455.3</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-4633</t>
+          <t>-2707</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-722.5223305920491</t>
+          <t>-844.6790150359823</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-1641.303098617845</t>
+          <t>-1516.540779477615</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>3696.0</t>
+          <t>6748.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5368,7 +5368,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-6.97</t>
+          <t>-6.05</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5413,7 +5413,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5423,12 +5423,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>6.07</t>
+          <t>6.18</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5438,7 +5438,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>10.28</t>
+          <t>10.1</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5453,12 +5453,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>46.46</t>
+          <t>46.45</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>4286</t>
+          <t>4211</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5478,22 +5478,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>46.0</t>
+          <t>45.45</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>46.0</t>
+          <t>46.15</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>45.3</t>
+          <t>45.35</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>45.35</t>
+          <t>45.8</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/PET膜.xlsx
+++ b/Result/checksun_type/PET膜.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-1.8</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>478.0</t>
+          <t>109.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>44.75</t>
+          <t>44.7</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>40.89</t>
+          <t>42.69</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-10.05</t>
+          <t>-10.15</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>18.79</t>
+          <t>4.28</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,12 +1014,12 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>478</t>
+          <t>109</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
@@ -1033,47 +1033,47 @@
         </is>
       </c>
       <c r="AH2" t="n">
-        <v>-1.04</v>
+        <v>-0.8</v>
       </c>
       <c r="AI2" t="n">
-        <v>-0.93</v>
+        <v>-1.02</v>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-1.16</t>
+          <t>-1.27</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-2.39</t>
+          <t>-2.44</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>45.21999999999999</t>
+          <t>45.06</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>45.64</v>
+        <v>45.52</v>
       </c>
       <c r="AN2" t="n">
-        <v>46.18</v>
+        <v>46.11</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>47.31</t>
+          <t>47.26</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-14.07</t>
+          <t>-21.20</t>
         </is>
       </c>
       <c r="AQ2" t="n">
-        <v>-0.31</v>
+        <v>-0.34</v>
       </c>
       <c r="AR2" t="n">
-        <v>-0.27</v>
+        <v>-0.28</v>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-106.26</t>
+          <t>-106.61</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1092,43 +1092,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>75763.96544428772</t>
+          <t>75667.49154929578</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>21298.0</t>
+          <t>4845.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>9270</v>
+        <v>9321</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>6579.4</t>
+          <t>6532.2</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>11878.36</v>
+        <v>11521.76</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>2690</t>
+          <t>2788</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-814.4929814714977</t>
+          <t>-654.0307246368856</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>610.419588440709</t>
+          <t>228.5116879534808</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>21298.0</t>
+          <t>4845.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-8.21</t>
+          <t>-8.31</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1193,12 +1193,12 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
@@ -1208,7 +1208,7 @@
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>6.18</t>
+          <t>6.19</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>10.1</t>
+          <t>10.09</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1233,12 +1233,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>46.45</t>
+          <t>47.2</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>4211</t>
+          <t>4206</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1258,22 +1258,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>44.55</t>
+          <t>44.75</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>44.75</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>44.3</t>
+          <t>44.5</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>44.75</t>
+          <t>44.7</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1305,12 +1305,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>-1.8</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>478.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>45.55</t>
+          <t>44.75</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1330,7 +1330,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-1.79</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -1340,7 +1340,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>9.71</t>
+          <t>40.89</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1405,7 +1405,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-8.44</t>
+          <t>-10.05</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1415,17 +1415,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>4.05</t>
+          <t>18.79</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-1.09</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1436,17 +1436,17 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>478</t>
+          <t>109</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>52.63</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
@@ -1455,47 +1455,47 @@
         </is>
       </c>
       <c r="AH3" t="n">
-        <v>0.26</v>
+        <v>-1.04</v>
       </c>
       <c r="AI3" t="n">
-        <v>-0.78</v>
+        <v>-0.93</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-1.04</t>
+          <t>-1.16</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-2.32</t>
+          <t>-2.39</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>45.42999999999999</t>
+          <t>45.21999999999999</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>45.78</v>
+        <v>45.64</v>
       </c>
       <c r="AN3" t="n">
-        <v>46.27</v>
+        <v>46.18</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>47.37</t>
+          <t>47.31</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-14.07</t>
         </is>
       </c>
       <c r="AQ3" t="n">
-        <v>-0.26</v>
+        <v>-0.31</v>
       </c>
       <c r="AR3" t="n">
-        <v>-0.26</v>
+        <v>-0.27</v>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-106.04</t>
+          <t>-106.26</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1514,43 +1514,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>75763.96544428772</t>
+          <t>75667.49154929578</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>4714.0</t>
+          <t>21298.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>5622.2</v>
+        <v>9270</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>5124.4</t>
+          <t>6579.4</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>11707.74</v>
+        <v>11878.36</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>497</t>
+          <t>2690</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-1073.567994182808</t>
+          <t>-814.4929814714977</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-628.6198247361344</t>
+          <t>610.419588440709</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>4714.0</t>
+          <t>21298.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1570,7 +1570,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-6.56</t>
+          <t>-8.21</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1615,22 +1615,22 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>6.18</t>
+          <t>6.19</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1640,7 +1640,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>10.1</t>
+          <t>10.09</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>46.45</t>
+          <t>47.2</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>4211</t>
+          <t>4206</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1680,22 +1680,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>45.65</t>
+          <t>44.55</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>46.3</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>45.3</t>
+          <t>44.3</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>45.55</t>
+          <t>44.75</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1727,12 +1727,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>246.0</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1742,7 +1742,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>45.05</t>
+          <t>45.55</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1752,7 +1752,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>-1.9</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1762,7 +1762,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>8.33</t>
+          <t>9.71</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1827,7 +1827,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-9.45</t>
+          <t>-8.44</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1837,17 +1837,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>9.67</t>
+          <t>4.05</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>-1.09</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1858,63 +1858,63 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>478</t>
+          <t>109</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>52.63</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>9.52</t>
+          <t>17.54</t>
         </is>
       </c>
       <c r="AH4" t="n">
-        <v>-0.95</v>
+        <v>0.26</v>
       </c>
       <c r="AI4" t="n">
-        <v>-0.87</v>
+        <v>-0.78</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-0.97</t>
+          <t>-1.04</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-2.29</t>
+          <t>-2.32</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>45.48</t>
+          <t>45.42999999999999</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>45.88</v>
+        <v>45.78</v>
       </c>
       <c r="AN4" t="n">
-        <v>46.32</v>
+        <v>46.27</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>47.41</t>
+          <t>47.37</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-7.02</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AQ4" t="n">
-        <v>-0.28</v>
+        <v>-0.26</v>
       </c>
       <c r="AR4" t="n">
         <v>-0.26</v>
@@ -1936,43 +1936,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>75763.96544428772</t>
+          <t>75667.49154929578</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>11034.0</t>
+          <t>4714.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>5441.2</v>
+        <v>5622.2</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>5022.6</t>
+          <t>5124.4</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>11858.6</v>
+        <v>11707.74</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>418</t>
+          <t>497</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-1154.46766135493</t>
+          <t>-1073.567994182808</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-599.3682783910481</t>
+          <t>-628.6198247361344</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>11034.0</t>
+          <t>4714.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -1992,7 +1992,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-7.59</t>
+          <t>-6.56</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2037,22 +2037,22 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>6.18</t>
+          <t>6.19</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2062,7 +2062,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>10.1</t>
+          <t>10.09</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2077,12 +2077,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>46.45</t>
+          <t>47.2</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>4211</t>
+          <t>4206</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2102,22 +2102,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>45.25</t>
+          <t>45.65</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>45.45</t>
+          <t>46.3</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>44.5</t>
+          <t>45.3</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>45.05</t>
+          <t>45.55</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2139,7 +2139,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>【d2】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2149,12 +2149,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-0.55</t>
+          <t>-0.44</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>104.0</t>
+          <t>246.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2164,7 +2164,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>45.25</t>
+          <t>45.05</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2174,7 +2174,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-1.12</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -2184,7 +2184,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-8.48</t>
+          <t>8.33</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2249,7 +2249,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-9.05</t>
+          <t>-9.45</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2259,17 +2259,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>4.09</t>
+          <t>9.67</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2280,12 +2280,12 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>478</t>
+          <t>109</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
@@ -2295,51 +2295,51 @@
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>37.52</t>
+          <t>9.52</t>
         </is>
       </c>
       <c r="AH5" t="n">
-        <v>-0.83</v>
+        <v>-0.95</v>
       </c>
       <c r="AI5" t="n">
-        <v>-0.75</v>
+        <v>-0.87</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-0.9</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-2.24</t>
+          <t>-2.29</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>45.63</t>
+          <t>45.48</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>45.98</v>
+        <v>45.88</v>
       </c>
       <c r="AN5" t="n">
-        <v>46.39</v>
+        <v>46.32</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>47.46</t>
+          <t>47.41</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>3.73</t>
+          <t>-7.02</t>
         </is>
       </c>
       <c r="AQ5" t="n">
-        <v>-0.24</v>
+        <v>-0.28</v>
       </c>
       <c r="AR5" t="n">
-        <v>-0.25</v>
+        <v>-0.26</v>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
@@ -2348,7 +2348,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-105.93</t>
+          <t>-106.04</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2358,43 +2358,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>75763.96544428772</t>
+          <t>75667.49154929578</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>4714.0</t>
+          <t>11034.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>3990.2</v>
+        <v>5441.2</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>4360.0</t>
+          <t>5022.6</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>11948.92</v>
+        <v>11858.6</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-369</t>
+          <t>418</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-1255.394821893818</t>
+          <t>-1154.46766135493</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-1213.317202241243</t>
+          <t>-599.3682783910481</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>4714.0</t>
+          <t>11034.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2414,7 +2414,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-7.18</t>
+          <t>-7.59</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2459,12 +2459,12 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
@@ -2474,7 +2474,7 @@
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>6.18</t>
+          <t>6.19</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2484,7 +2484,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>10.1</t>
+          <t>10.09</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>46.45</t>
+          <t>47.2</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>4211</t>
+          <t>4206</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2524,22 +2524,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>45.5</t>
+          <t>45.25</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>45.5</t>
+          <t>45.45</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>44.9</t>
+          <t>44.5</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>45.25</t>
+          <t>45.05</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2571,12 +2571,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>-0.55</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>104.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>45.5</t>
+          <t>45.25</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-1.68</t>
+          <t>-1.23</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -2606,7 +2606,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-20.03</t>
+          <t>-8.48</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2671,7 +2671,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-8.54</t>
+          <t>-9.05</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2681,17 +2681,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>3.97</t>
+          <t>4.09</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2702,66 +2702,66 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>478</t>
+          <t>109</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>28.57</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>65.52</t>
+          <t>37.52</t>
         </is>
       </c>
       <c r="AH6" t="n">
-        <v>-0.61</v>
+        <v>-0.83</v>
       </c>
       <c r="AI6" t="n">
-        <v>-0.58</v>
+        <v>-0.75</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-0.89</t>
+          <t>-0.9</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-2.14</t>
+          <t>-2.24</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>45.77999999999999</t>
+          <t>45.63</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>46.04</v>
+        <v>45.98</v>
       </c>
       <c r="AN6" t="n">
-        <v>46.46</v>
+        <v>46.39</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>47.48</t>
+          <t>47.46</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>14.06</t>
+          <t>3.73</t>
         </is>
       </c>
       <c r="AQ6" t="n">
-        <v>-0.22</v>
+        <v>-0.24</v>
       </c>
       <c r="AR6" t="n">
-        <v>-0.26</v>
+        <v>-0.25</v>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
@@ -2770,7 +2770,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-105.99</t>
+          <t>-105.93</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2780,43 +2780,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>75763.96544428772</t>
+          <t>75667.49154929578</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>4590.0</t>
+          <t>4714.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>3743.4</v>
+        <v>3990.2</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>4681.2</t>
+          <t>4360.0</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>12007.9</v>
+        <v>11948.92</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-937</t>
+          <t>-369</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-1263.045298194286</t>
+          <t>-1255.394821893818</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-1369.911479090048</t>
+          <t>-1213.317202241243</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>4590.0</t>
+          <t>4714.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2836,7 +2836,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-6.67</t>
+          <t>-7.18</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2881,7 +2881,7 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -2891,12 +2891,12 @@
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>6.18</t>
+          <t>6.19</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2906,7 +2906,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>10.1</t>
+          <t>10.09</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2921,12 +2921,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>46.45</t>
+          <t>47.2</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>4211</t>
+          <t>4206</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2946,22 +2946,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>46.0</t>
+          <t>45.5</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>46.05</t>
+          <t>45.5</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>45.15</t>
+          <t>44.9</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>45.5</t>
+          <t>45.25</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -2993,42 +2993,42 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
+          <t>-0.65</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>101.0</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>45.5</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>-1.79</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>67.0</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>45.8</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>-2.35</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-14.39</t>
+          <t>-20.03</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3093,7 +3093,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-7.94</t>
+          <t>-8.54</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3103,17 +3103,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>2.63</t>
+          <t>3.97</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3124,63 +3124,63 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>478</t>
+          <t>109</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>28.57</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>65.52</t>
         </is>
       </c>
       <c r="AH7" t="n">
-        <v>-0.17</v>
+        <v>-0.61</v>
       </c>
       <c r="AI7" t="n">
-        <v>-0.52</v>
+        <v>-0.58</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-0.87</t>
+          <t>-0.89</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-2.06</t>
+          <t>-2.14</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>45.88</t>
+          <t>45.77999999999999</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>46.12</v>
+        <v>46.04</v>
       </c>
       <c r="AN7" t="n">
-        <v>46.52</v>
+        <v>46.46</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>47.5</t>
+          <t>47.48</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>20.22</t>
+          <t>14.06</t>
         </is>
       </c>
       <c r="AQ7" t="n">
-        <v>-0.21</v>
+        <v>-0.22</v>
       </c>
       <c r="AR7" t="n">
         <v>-0.26</v>
@@ -3192,7 +3192,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-106.20</t>
+          <t>-105.99</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3202,43 +3202,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>75763.96544428772</t>
+          <t>75667.49154929578</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>3059.0</t>
+          <t>4590.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>3888.8</v>
+        <v>3743.4</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>4542.6</t>
+          <t>4681.2</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>12062.18</v>
+        <v>12007.9</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-653</t>
+          <t>-937</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-1243.615083485966</t>
+          <t>-1263.045298194286</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-1531.406464620841</t>
+          <t>-1369.911479090048</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>3059.0</t>
+          <t>4590.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3258,7 +3258,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-6.05</t>
+          <t>-6.67</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3303,7 +3303,7 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3313,12 +3313,12 @@
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>6.18</t>
+          <t>6.19</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3328,7 +3328,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>10.1</t>
+          <t>10.09</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3343,12 +3343,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>46.45</t>
+          <t>47.2</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>4211</t>
+          <t>4206</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3368,22 +3368,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>45.8</t>
+          <t>46.0</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>46.0</t>
+          <t>46.05</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>45.7</t>
+          <t>45.15</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>45.8</t>
+          <t>45.5</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3420,7 +3420,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3440,7 +3440,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-2.35</t>
+          <t>-2.46</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -3450,7 +3450,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-2.42</t>
+          <t>-14.39</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3525,17 +3525,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>3.26</t>
+          <t>2.63</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3546,12 +3546,12 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>478</t>
+          <t>109</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
@@ -3561,23 +3561,23 @@
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>89.33</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AH8" t="n">
         <v>-0.17</v>
       </c>
       <c r="AI8" t="n">
-        <v>-0.46</v>
+        <v>-0.52</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-1.07</t>
+          <t>-0.87</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-1.95</t>
+          <t>-2.06</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
@@ -3586,26 +3586,26 @@
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>46.09</v>
+        <v>46.12</v>
       </c>
       <c r="AN8" t="n">
-        <v>46.59</v>
+        <v>46.52</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>47.52</t>
+          <t>47.5</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>18.14</t>
+          <t>20.22</t>
         </is>
       </c>
       <c r="AQ8" t="n">
-        <v>-0.23</v>
+        <v>-0.21</v>
       </c>
       <c r="AR8" t="n">
-        <v>-0.28</v>
+        <v>-0.26</v>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
@@ -3614,7 +3614,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-106.51</t>
+          <t>-106.20</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3624,43 +3624,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>75763.96544428772</t>
+          <t>75667.49154929578</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>3809.0</t>
+          <t>3059.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>4626.6</v>
+        <v>3888.8</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>4741.3</t>
+          <t>4542.6</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>12259.36</v>
+        <v>12062.18</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-114</t>
+          <t>-653</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-1191.289377825079</t>
+          <t>-1243.615083485966</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-1543.3847844998</t>
+          <t>-1531.406464620841</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>3809.0</t>
+          <t>3059.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3725,7 +3725,7 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -3740,7 +3740,7 @@
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>6.18</t>
+          <t>6.19</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3750,7 +3750,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>10.1</t>
+          <t>10.09</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>46.45</t>
+          <t>47.2</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>4211</t>
+          <t>4206</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3790,17 +3790,17 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>46.2</t>
+          <t>45.8</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>46.2</t>
+          <t>46.0</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>45.6</t>
+          <t>45.7</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -3837,127 +3837,127 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>83.0</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>45.8</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>-2.46</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>-2.42</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>2025-09-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>2025-09-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>2025-03-06 00:00:00</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>2025-03-10 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>51.1</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>49.75</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>57.7</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>56.5</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>-7.94</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>-9.56</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-12-02</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>3.26</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
           <t>-0.43</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>82.0</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>45.8</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>-2.35</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>-20.54</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>2025-09-02 00:00:00</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>2025-09-12 00:00:00</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>2025-03-06 00:00:00</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>2025-03-10 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>51.1</t>
-        </is>
-      </c>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>49.75</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>57.7</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>56.5</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>-7.94</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>-9.56</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>2025-12-01</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>3.22</t>
-        </is>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>0.00</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -3968,12 +3968,12 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>478</t>
+          <t>109</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
@@ -3983,51 +3983,51 @@
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>83.86</t>
+          <t>89.33</t>
         </is>
       </c>
       <c r="AH9" t="n">
-        <v>0.02</v>
+        <v>-0.17</v>
       </c>
       <c r="AI9" t="n">
-        <v>-0.58</v>
+        <v>-0.46</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-1.87</t>
+          <t>-1.95</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>45.79</t>
+          <t>45.88</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>46.06</v>
+        <v>46.09</v>
       </c>
       <c r="AN9" t="n">
-        <v>46.64</v>
+        <v>46.59</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>47.53</t>
+          <t>47.52</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>15.60</t>
+          <t>18.14</t>
         </is>
       </c>
       <c r="AQ9" t="n">
-        <v>-0.25</v>
+        <v>-0.23</v>
       </c>
       <c r="AR9" t="n">
-        <v>-0.29</v>
+        <v>-0.28</v>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
@@ -4036,7 +4036,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-106.80</t>
+          <t>-106.51</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4046,43 +4046,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>75763.96544428772</t>
+          <t>75667.49154929578</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>3779.0</t>
+          <t>3809.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>4604</v>
+        <v>4626.6</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>5794.0</t>
+          <t>4741.3</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>12544.52</v>
+        <v>12259.36</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-1190</t>
+          <t>-114</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-1127.272031156948</t>
+          <t>-1191.289377825079</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-1585.732927737606</t>
+          <t>-1543.3847844998</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>3779.0</t>
+          <t>3809.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4147,7 +4147,7 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4162,7 +4162,7 @@
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>6.18</t>
+          <t>6.19</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4172,7 +4172,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>10.1</t>
+          <t>10.09</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4187,12 +4187,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>46.45</t>
+          <t>47.2</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>4211</t>
+          <t>4206</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4212,17 +4212,17 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>46.0</t>
+          <t>46.2</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>46.05</t>
+          <t>46.2</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>45.55</t>
+          <t>45.6</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4259,42 +4259,42 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
+          <t>-0.43</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>45.8</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>-2.46</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>75.0</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>46.0</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>-2.79</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-26.22</t>
+          <t>-20.54</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4359,7 +4359,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-7.54</t>
+          <t>-7.94</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4369,17 +4369,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>2.95</t>
+          <t>3.22</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-0.98</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4390,66 +4390,66 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>478</t>
+          <t>109</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>71.07</t>
+          <t>83.86</t>
         </is>
       </c>
       <c r="AH10" t="n">
-        <v>0.68</v>
+        <v>0.02</v>
       </c>
       <c r="AI10" t="n">
-        <v>-0.75</v>
+        <v>-0.58</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-1.76</t>
+          <t>-1.87</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>45.69</t>
+          <t>45.79</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>46.04</v>
+        <v>46.06</v>
       </c>
       <c r="AN10" t="n">
-        <v>46.7</v>
+        <v>46.64</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>47.54</t>
+          <t>47.53</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>12.46</t>
+          <t>15.60</t>
         </is>
       </c>
       <c r="AQ10" t="n">
-        <v>-0.26</v>
+        <v>-0.25</v>
       </c>
       <c r="AR10" t="n">
-        <v>-0.3</v>
+        <v>-0.29</v>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
@@ -4458,7 +4458,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-107.07</t>
+          <t>-106.80</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4468,43 +4468,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>75763.96544428772</t>
+          <t>75667.49154929578</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>3480.0</t>
+          <t>3779.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>4729.8</v>
+        <v>4604</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>6410.4</t>
+          <t>5794.0</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>12782.88</v>
+        <v>12544.52</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-1680</t>
+          <t>-1190</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-1043.91550450592</t>
+          <t>-1127.272031156948</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-1586.382670658128</t>
+          <t>-1585.732927737606</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>3480.0</t>
+          <t>3779.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4524,7 +4524,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-5.64</t>
+          <t>-6.05</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4569,7 +4569,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4579,12 +4579,12 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>6.18</t>
+          <t>6.19</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4594,7 +4594,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>10.1</t>
+          <t>10.09</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4609,12 +4609,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>46.45</t>
+          <t>47.2</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>4211</t>
+          <t>4206</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4634,22 +4634,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>46.4</t>
+          <t>46.0</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>46.45</t>
+          <t>46.05</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>46.0</t>
+          <t>45.55</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>46.0</t>
+          <t>45.8</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>116.0</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4706,7 +4706,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-2.79</t>
+          <t>-2.91</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -4716,7 +4716,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-19.32</t>
+          <t>-26.22</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4791,17 +4791,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>4.56</t>
+          <t>2.95</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4812,66 +4812,66 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>478</t>
+          <t>109</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>67.57</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>46.25</t>
+          <t>71.07</t>
         </is>
       </c>
       <c r="AH11" t="n">
-        <v>1.23</v>
+        <v>0.68</v>
       </c>
       <c r="AI11" t="n">
-        <v>-1.23</v>
+        <v>-0.75</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-1.61</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-1.65</t>
+          <t>-1.76</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>45.44</t>
+          <t>45.69</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>46</v>
+        <v>46.04</v>
       </c>
       <c r="AN11" t="n">
-        <v>46.76</v>
+        <v>46.7</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>47.55</t>
+          <t>47.54</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>12.46</t>
         </is>
       </c>
       <c r="AQ11" t="n">
-        <v>-0.31</v>
+        <v>-0.26</v>
       </c>
       <c r="AR11" t="n">
-        <v>-0.31</v>
+        <v>-0.3</v>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
@@ -4880,7 +4880,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-107.29</t>
+          <t>-107.07</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4890,43 +4890,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>75763.96544428772</t>
+          <t>75667.49154929578</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>5317.0</t>
+          <t>3480.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>5619</v>
+        <v>4729.8</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>6964.2</t>
+          <t>6410.4</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>13246.56</v>
+        <v>12782.88</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-1345</t>
+          <t>-1680</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-945.2851106600637</t>
+          <t>-1043.91550450592</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-1498.618636592511</t>
+          <t>-1586.382670658128</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>5317.0</t>
+          <t>3480.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -4991,7 +4991,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5006,7 +5006,7 @@
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>6.18</t>
+          <t>6.19</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5016,7 +5016,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>10.1</t>
+          <t>10.09</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5031,42 +5031,42 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
+          <t>47.2</t>
+        </is>
+      </c>
+      <c r="BZ11" t="inlineStr">
+        <is>
+          <t>4206</t>
+        </is>
+      </c>
+      <c r="CA11" t="inlineStr">
+        <is>
+          <t>真空蒸鍍薄膜95.00%、光電材料5.00% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB11" t="inlineStr">
+        <is>
+          <t>岱稜-其他電子業-上櫃</t>
+        </is>
+      </c>
+      <c r="CC11" t="inlineStr">
+        <is>
+          <t>其他電子業平上櫃</t>
+        </is>
+      </c>
+      <c r="CD11" t="inlineStr">
+        <is>
+          <t>46.4</t>
+        </is>
+      </c>
+      <c r="CE11" t="inlineStr">
+        <is>
           <t>46.45</t>
         </is>
       </c>
-      <c r="BZ11" t="inlineStr">
-        <is>
-          <t>4211</t>
-        </is>
-      </c>
-      <c r="CA11" t="inlineStr">
-        <is>
-          <t>真空蒸鍍薄膜95.00%、光電材料5.00% (2024年)</t>
-        </is>
-      </c>
-      <c r="CB11" t="inlineStr">
-        <is>
-          <t>岱稜-其他電子業-上櫃</t>
-        </is>
-      </c>
-      <c r="CC11" t="inlineStr">
-        <is>
-          <t>其他電子業平上櫃</t>
-        </is>
-      </c>
-      <c r="CD11" t="inlineStr">
-        <is>
-          <t>45.8</t>
-        </is>
-      </c>
-      <c r="CE11" t="inlineStr">
-        <is>
-          <t>46.1</t>
-        </is>
-      </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>45.7</t>
+          <t>46.0</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
@@ -5093,7 +5093,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d2】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5103,12 +5103,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>148.0</t>
+          <t>116.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5118,7 +5118,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>45.8</t>
+          <t>46.0</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5128,7 +5128,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-2.35</t>
+          <t>-2.91</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -5138,7 +5138,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-34.26</t>
+          <t>-19.32</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-7.94</t>
+          <t>-7.54</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5213,17 +5213,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>5.82</t>
+          <t>4.56</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5234,63 +5234,63 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>478</t>
+          <t>109</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>45.65</t>
+          <t>67.57</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>30.16</t>
+          <t>46.25</t>
         </is>
       </c>
       <c r="AH12" t="n">
-        <v>0.99</v>
+        <v>1.23</v>
       </c>
       <c r="AI12" t="n">
-        <v>-1.35</v>
+        <v>-1.23</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-1.85</t>
+          <t>-1.61</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-1.48</t>
+          <t>-1.65</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>45.35</t>
+          <t>45.44</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>45.97</v>
+        <v>46</v>
       </c>
       <c r="AN12" t="n">
-        <v>46.84</v>
+        <v>46.76</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>47.54</t>
+          <t>47.55</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-12.73</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="AQ12" t="n">
-        <v>-0.35</v>
+        <v>-0.31</v>
       </c>
       <c r="AR12" t="n">
         <v>-0.31</v>
@@ -5302,7 +5302,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-107.33</t>
+          <t>-107.29</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5312,43 +5312,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>75763.96544428772</t>
+          <t>75667.49154929578</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>6748.0</t>
+          <t>5317.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>5196.4</v>
+        <v>5619</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>7904.3</t>
+          <t>6964.2</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>13455.3</v>
+        <v>13246.56</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-2707</t>
+          <t>-1345</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-844.6790150359823</t>
+          <t>-945.2851106600637</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-1516.540779477615</t>
+          <t>-1498.618636592511</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>6748.0</t>
+          <t>5317.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5368,7 +5368,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-6.05</t>
+          <t>-5.64</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5413,7 +5413,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5423,12 +5423,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>6.18</t>
+          <t>6.19</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5438,7 +5438,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>10.1</t>
+          <t>10.09</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5453,12 +5453,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>46.45</t>
+          <t>47.2</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>4211</t>
+          <t>4206</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5478,22 +5478,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>45.45</t>
+          <t>45.8</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>46.15</t>
+          <t>46.1</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>45.35</t>
+          <t>45.7</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>45.8</t>
+          <t>46.0</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/PET膜.xlsx
+++ b/Result/checksun_type/PET膜.xlsx
@@ -923,12 +923,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>143.0</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -938,7 +938,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>45.3</t>
+          <t>45.2</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -958,7 +958,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>41.55</t>
+          <t>20.01</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -1023,7 +1023,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-8.94</t>
+          <t>-9.15</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -1068,22 +1068,22 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>5.62</t>
+          <t>3.07</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>-0.55</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
@@ -1094,63 +1094,63 @@
       <c r="AK2" t="inlineStr"/>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>143</t>
+          <t>78</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>54.55</t>
+          <t>45.45</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>18.18</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AP2" t="n">
-        <v>0.51</v>
+        <v>0.22</v>
       </c>
       <c r="AQ2" t="n">
-        <v>-0.8</v>
+        <v>-0.58</v>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-1.32</t>
+          <t>-1.27</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>-2.47</t>
+          <t>-2.57</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>45.07000000000001</t>
+          <t>45.1</t>
         </is>
       </c>
       <c r="AU2" t="n">
-        <v>45.44</v>
+        <v>45.36</v>
       </c>
       <c r="AV2" t="n">
-        <v>46.04</v>
+        <v>45.95</v>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>47.21</t>
+          <t>47.16</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>-10.29</t>
+          <t>-4.49</t>
         </is>
       </c>
       <c r="AY2" t="n">
-        <v>-0.32</v>
+        <v>-0.31</v>
       </c>
       <c r="AZ2" t="n">
         <v>-0.29</v>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-106.78</t>
+          <t>-106.86</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
@@ -1172,43 +1172,43 @@
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>75574.61814345993</t>
+          <t>75475.9297752809</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
-          <t>6423.0</t>
+          <t>3539.0</t>
         </is>
       </c>
       <c r="BF2" t="n">
-        <v>9662.799999999999</v>
+        <v>8163.8</v>
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>6826.5</t>
+          <t>6802.5</t>
         </is>
       </c>
       <c r="BH2" t="n">
-        <v>11523.86</v>
+        <v>11065.56</v>
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>2836</t>
+          <t>1361</t>
         </is>
       </c>
       <c r="BJ2" t="inlineStr">
         <is>
-          <t>-542.0547107829672</t>
+          <t>-497.5264159701541</t>
         </is>
       </c>
       <c r="BK2" t="inlineStr">
         <is>
-          <t>73.8133654135845</t>
+          <t>-252.6207944996822</t>
         </is>
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>6423.0</t>
+          <t>3539.0</t>
         </is>
       </c>
       <c r="BM2" t="inlineStr">
@@ -1228,7 +1228,7 @@
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>-7.08</t>
+          <t>-7.28</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
@@ -1253,7 +1253,7 @@
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
@@ -1273,22 +1273,22 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>6.11</t>
+          <t>6.12</t>
         </is>
       </c>
       <c r="CC2" t="inlineStr">
@@ -1298,7 +1298,7 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>10.23</t>
+          <t>10.2</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>47.2</t>
+          <t>47.76</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
         <is>
-          <t>4262</t>
+          <t>4253</t>
         </is>
       </c>
       <c r="CI2" t="inlineStr">
@@ -1338,22 +1338,22 @@
       </c>
       <c r="CL2" t="inlineStr">
         <is>
-          <t>44.8</t>
+          <t>45.05</t>
         </is>
       </c>
       <c r="CM2" t="inlineStr">
         <is>
-          <t>45.3</t>
+          <t>45.6</t>
         </is>
       </c>
       <c r="CN2" t="inlineStr">
         <is>
-          <t>44.75</t>
+          <t>45.05</t>
         </is>
       </c>
       <c r="CO2" t="inlineStr">
         <is>
-          <t>45.3</t>
+          <t>45.2</t>
         </is>
       </c>
       <c r="CP2" t="inlineStr">
@@ -1385,12 +1385,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>109.0</t>
+          <t>143.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>44.7</t>
+          <t>45.3</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1410,7 +1410,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -1420,7 +1420,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>42.69</t>
+          <t>41.55</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1485,7 +1485,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-10.15</t>
+          <t>-8.94</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1530,22 +1530,22 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>4.28</t>
+          <t>5.62</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
@@ -1556,66 +1556,66 @@
       <c r="AK3" t="inlineStr"/>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>143</t>
+          <t>78</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>54.55</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>17.54</t>
+          <t>18.18</t>
         </is>
       </c>
       <c r="AP3" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="AQ3" t="n">
         <v>-0.8</v>
       </c>
-      <c r="AQ3" t="n">
-        <v>-1.02</v>
-      </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-1.27</t>
+          <t>-1.32</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>-2.44</t>
+          <t>-2.47</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>45.06</t>
+          <t>45.07000000000001</t>
         </is>
       </c>
       <c r="AU3" t="n">
-        <v>45.52</v>
+        <v>45.44</v>
       </c>
       <c r="AV3" t="n">
-        <v>46.11</v>
+        <v>46.04</v>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>47.26</t>
+          <t>47.21</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>-21.20</t>
+          <t>-10.29</t>
         </is>
       </c>
       <c r="AY3" t="n">
-        <v>-0.34</v>
+        <v>-0.32</v>
       </c>
       <c r="AZ3" t="n">
-        <v>-0.28</v>
+        <v>-0.29</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
@@ -1624,7 +1624,7 @@
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-106.61</t>
+          <t>-106.78</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
@@ -1634,43 +1634,43 @@
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>75574.61814345993</t>
+          <t>75475.9297752809</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
-          <t>4845.0</t>
+          <t>6423.0</t>
         </is>
       </c>
       <c r="BF3" t="n">
-        <v>9321</v>
+        <v>9662.799999999999</v>
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>6532.2</t>
+          <t>6826.5</t>
         </is>
       </c>
       <c r="BH3" t="n">
-        <v>11521.76</v>
+        <v>11523.86</v>
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>2788</t>
+          <t>2836</t>
         </is>
       </c>
       <c r="BJ3" t="inlineStr">
         <is>
-          <t>-654.0307246368856</t>
+          <t>-542.0547107829672</t>
         </is>
       </c>
       <c r="BK3" t="inlineStr">
         <is>
-          <t>228.5116879534808</t>
+          <t>73.8133654135845</t>
         </is>
       </c>
       <c r="BL3" t="inlineStr">
         <is>
-          <t>4845.0</t>
+          <t>6423.0</t>
         </is>
       </c>
       <c r="BM3" t="inlineStr">
@@ -1690,7 +1690,7 @@
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>-8.31</t>
+          <t>-7.08</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
@@ -1715,7 +1715,7 @@
       </c>
       <c r="BU3" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="BV3" t="inlineStr">
@@ -1735,7 +1735,7 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1745,12 +1745,12 @@
       </c>
       <c r="CA3" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>1.84</t>
         </is>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>6.11</t>
+          <t>6.12</t>
         </is>
       </c>
       <c r="CC3" t="inlineStr">
@@ -1760,7 +1760,7 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>10.23</t>
+          <t>10.2</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
@@ -1775,12 +1775,12 @@
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>47.2</t>
+          <t>47.76</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
         <is>
-          <t>4262</t>
+          <t>4253</t>
         </is>
       </c>
       <c r="CI3" t="inlineStr">
@@ -1800,22 +1800,22 @@
       </c>
       <c r="CL3" t="inlineStr">
         <is>
+          <t>44.8</t>
+        </is>
+      </c>
+      <c r="CM3" t="inlineStr">
+        <is>
+          <t>45.3</t>
+        </is>
+      </c>
+      <c r="CN3" t="inlineStr">
+        <is>
           <t>44.75</t>
         </is>
       </c>
-      <c r="CM3" t="inlineStr">
-        <is>
-          <t>44.75</t>
-        </is>
-      </c>
-      <c r="CN3" t="inlineStr">
-        <is>
-          <t>44.5</t>
-        </is>
-      </c>
       <c r="CO3" t="inlineStr">
         <is>
-          <t>44.7</t>
+          <t>45.3</t>
         </is>
       </c>
       <c r="CP3" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-1.8</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>478.0</t>
+          <t>109.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1862,7 +1862,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>44.75</t>
+          <t>44.7</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1872,7 +1872,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1882,7 +1882,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>40.89</t>
+          <t>42.69</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1947,7 +1947,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-10.05</t>
+          <t>-10.15</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1992,22 +1992,22 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>18.79</t>
+          <t>4.28</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
@@ -2018,12 +2018,12 @@
       <c r="AK4" t="inlineStr"/>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>143</t>
+          <t>78</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
@@ -2037,47 +2037,47 @@
         </is>
       </c>
       <c r="AP4" t="n">
-        <v>-1.04</v>
+        <v>-0.8</v>
       </c>
       <c r="AQ4" t="n">
-        <v>-0.93</v>
+        <v>-1.02</v>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-1.16</t>
+          <t>-1.27</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>-2.39</t>
+          <t>-2.44</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>45.21999999999999</t>
+          <t>45.06</t>
         </is>
       </c>
       <c r="AU4" t="n">
-        <v>45.64</v>
+        <v>45.52</v>
       </c>
       <c r="AV4" t="n">
-        <v>46.18</v>
+        <v>46.11</v>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>47.31</t>
+          <t>47.26</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>-14.07</t>
+          <t>-21.20</t>
         </is>
       </c>
       <c r="AY4" t="n">
-        <v>-0.31</v>
+        <v>-0.34</v>
       </c>
       <c r="AZ4" t="n">
-        <v>-0.27</v>
+        <v>-0.28</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
@@ -2086,7 +2086,7 @@
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-106.26</t>
+          <t>-106.61</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
@@ -2096,43 +2096,43 @@
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>75574.61814345993</t>
+          <t>75475.9297752809</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
-          <t>21298.0</t>
+          <t>4845.0</t>
         </is>
       </c>
       <c r="BF4" t="n">
-        <v>9270</v>
+        <v>9321</v>
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>6579.4</t>
+          <t>6532.2</t>
         </is>
       </c>
       <c r="BH4" t="n">
-        <v>11878.36</v>
+        <v>11521.76</v>
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>2690</t>
+          <t>2788</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr">
         <is>
-          <t>-814.4929814714977</t>
+          <t>-654.0307246368856</t>
         </is>
       </c>
       <c r="BK4" t="inlineStr">
         <is>
-          <t>610.419588440709</t>
+          <t>228.5116879534808</t>
         </is>
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>21298.0</t>
+          <t>4845.0</t>
         </is>
       </c>
       <c r="BM4" t="inlineStr">
@@ -2152,7 +2152,7 @@
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>-8.21</t>
+          <t>-8.31</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
@@ -2177,7 +2177,7 @@
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
@@ -2197,12 +2197,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2212,7 +2212,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>6.11</t>
+          <t>6.12</t>
         </is>
       </c>
       <c r="CC4" t="inlineStr">
@@ -2222,7 +2222,7 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>10.23</t>
+          <t>10.2</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
@@ -2237,12 +2237,12 @@
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>47.2</t>
+          <t>47.76</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
         <is>
-          <t>4262</t>
+          <t>4253</t>
         </is>
       </c>
       <c r="CI4" t="inlineStr">
@@ -2262,22 +2262,22 @@
       </c>
       <c r="CL4" t="inlineStr">
         <is>
-          <t>44.55</t>
+          <t>44.75</t>
         </is>
       </c>
       <c r="CM4" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>44.75</t>
         </is>
       </c>
       <c r="CN4" t="inlineStr">
         <is>
-          <t>44.3</t>
+          <t>44.5</t>
         </is>
       </c>
       <c r="CO4" t="inlineStr">
         <is>
-          <t>44.75</t>
+          <t>44.7</t>
         </is>
       </c>
       <c r="CP4" t="inlineStr">
@@ -2309,12 +2309,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>-1.8</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>478.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2324,7 +2324,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>45.55</t>
+          <t>44.75</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2334,7 +2334,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-0.55</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -2344,7 +2344,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>9.71</t>
+          <t>40.89</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2409,7 +2409,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-8.44</t>
+          <t>-10.05</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2454,22 +2454,22 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>4.05</t>
+          <t>18.79</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-1.09</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
@@ -2480,17 +2480,17 @@
       <c r="AK5" t="inlineStr"/>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>143</t>
+          <t>78</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>52.63</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
@@ -2499,47 +2499,47 @@
         </is>
       </c>
       <c r="AP5" t="n">
-        <v>0.26</v>
+        <v>-1.04</v>
       </c>
       <c r="AQ5" t="n">
-        <v>-0.78</v>
+        <v>-0.93</v>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-1.04</t>
+          <t>-1.16</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>-2.32</t>
+          <t>-2.39</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>45.42999999999999</t>
+          <t>45.21999999999999</t>
         </is>
       </c>
       <c r="AU5" t="n">
-        <v>45.78</v>
+        <v>45.64</v>
       </c>
       <c r="AV5" t="n">
-        <v>46.27</v>
+        <v>46.18</v>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>47.37</t>
+          <t>47.31</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-14.07</t>
         </is>
       </c>
       <c r="AY5" t="n">
-        <v>-0.26</v>
+        <v>-0.31</v>
       </c>
       <c r="AZ5" t="n">
-        <v>-0.26</v>
+        <v>-0.27</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
@@ -2548,7 +2548,7 @@
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-106.04</t>
+          <t>-106.26</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
@@ -2558,43 +2558,43 @@
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>75574.61814345993</t>
+          <t>75475.9297752809</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
-          <t>4714.0</t>
+          <t>21298.0</t>
         </is>
       </c>
       <c r="BF5" t="n">
-        <v>5622.2</v>
+        <v>9270</v>
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>5124.4</t>
+          <t>6579.4</t>
         </is>
       </c>
       <c r="BH5" t="n">
-        <v>11707.74</v>
+        <v>11878.36</v>
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>497</t>
+          <t>2690</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr">
         <is>
-          <t>-1073.567994182808</t>
+          <t>-814.4929814714977</t>
         </is>
       </c>
       <c r="BK5" t="inlineStr">
         <is>
-          <t>-628.6198247361344</t>
+          <t>610.419588440709</t>
         </is>
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>4714.0</t>
+          <t>21298.0</t>
         </is>
       </c>
       <c r="BM5" t="inlineStr">
@@ -2614,7 +2614,7 @@
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>-6.56</t>
+          <t>-8.21</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
@@ -2639,7 +2639,7 @@
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
@@ -2659,22 +2659,22 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>6.11</t>
+          <t>6.12</t>
         </is>
       </c>
       <c r="CC5" t="inlineStr">
@@ -2684,7 +2684,7 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>10.23</t>
+          <t>10.2</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
@@ -2699,12 +2699,12 @@
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>47.2</t>
+          <t>47.76</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
         <is>
-          <t>4262</t>
+          <t>4253</t>
         </is>
       </c>
       <c r="CI5" t="inlineStr">
@@ -2724,22 +2724,22 @@
       </c>
       <c r="CL5" t="inlineStr">
         <is>
-          <t>45.65</t>
+          <t>44.55</t>
         </is>
       </c>
       <c r="CM5" t="inlineStr">
         <is>
-          <t>46.3</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="CN5" t="inlineStr">
         <is>
-          <t>45.3</t>
+          <t>44.3</t>
         </is>
       </c>
       <c r="CO5" t="inlineStr">
         <is>
-          <t>45.55</t>
+          <t>44.75</t>
         </is>
       </c>
       <c r="CP5" t="inlineStr">
@@ -2771,12 +2771,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>246.0</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2786,7 +2786,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>45.05</t>
+          <t>45.55</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>-0.77</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>8.33</t>
+          <t>9.71</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2871,7 +2871,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-9.45</t>
+          <t>-8.44</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2916,22 +2916,22 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>9.67</t>
+          <t>4.05</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>-1.09</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
@@ -2942,63 +2942,63 @@
       <c r="AK6" t="inlineStr"/>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>143</t>
+          <t>78</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>52.63</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>9.52</t>
+          <t>17.54</t>
         </is>
       </c>
       <c r="AP6" t="n">
-        <v>-0.95</v>
+        <v>0.26</v>
       </c>
       <c r="AQ6" t="n">
-        <v>-0.87</v>
+        <v>-0.78</v>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.97</t>
+          <t>-1.04</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>-2.29</t>
+          <t>-2.32</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>45.48</t>
+          <t>45.42999999999999</t>
         </is>
       </c>
       <c r="AU6" t="n">
-        <v>45.88</v>
+        <v>45.78</v>
       </c>
       <c r="AV6" t="n">
-        <v>46.32</v>
+        <v>46.27</v>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>47.41</t>
+          <t>47.37</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>-7.02</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AY6" t="n">
-        <v>-0.28</v>
+        <v>-0.26</v>
       </c>
       <c r="AZ6" t="n">
         <v>-0.26</v>
@@ -3020,43 +3020,43 @@
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>75574.61814345993</t>
+          <t>75475.9297752809</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
-          <t>11034.0</t>
+          <t>4714.0</t>
         </is>
       </c>
       <c r="BF6" t="n">
-        <v>5441.2</v>
+        <v>5622.2</v>
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>5022.6</t>
+          <t>5124.4</t>
         </is>
       </c>
       <c r="BH6" t="n">
-        <v>11858.6</v>
+        <v>11707.74</v>
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>418</t>
+          <t>497</t>
         </is>
       </c>
       <c r="BJ6" t="inlineStr">
         <is>
-          <t>-1154.46766135493</t>
+          <t>-1073.567994182808</t>
         </is>
       </c>
       <c r="BK6" t="inlineStr">
         <is>
-          <t>-599.3682783910481</t>
+          <t>-628.6198247361344</t>
         </is>
       </c>
       <c r="BL6" t="inlineStr">
         <is>
-          <t>11034.0</t>
+          <t>4714.0</t>
         </is>
       </c>
       <c r="BM6" t="inlineStr">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>-7.59</t>
+          <t>-6.56</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
@@ -3101,7 +3101,7 @@
       </c>
       <c r="BU6" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="BV6" t="inlineStr">
@@ -3121,22 +3121,22 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>6.11</t>
+          <t>6.12</t>
         </is>
       </c>
       <c r="CC6" t="inlineStr">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>10.23</t>
+          <t>10.2</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
@@ -3161,12 +3161,12 @@
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>47.2</t>
+          <t>47.76</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
         <is>
-          <t>4262</t>
+          <t>4253</t>
         </is>
       </c>
       <c r="CI6" t="inlineStr">
@@ -3186,22 +3186,22 @@
       </c>
       <c r="CL6" t="inlineStr">
         <is>
-          <t>45.25</t>
+          <t>45.65</t>
         </is>
       </c>
       <c r="CM6" t="inlineStr">
         <is>
-          <t>45.45</t>
+          <t>46.3</t>
         </is>
       </c>
       <c r="CN6" t="inlineStr">
         <is>
-          <t>44.5</t>
+          <t>45.3</t>
         </is>
       </c>
       <c r="CO6" t="inlineStr">
         <is>
-          <t>45.05</t>
+          <t>45.55</t>
         </is>
       </c>
       <c r="CP6" t="inlineStr">
@@ -3223,7 +3223,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>【d2】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3233,12 +3233,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-0.55</t>
+          <t>-0.44</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>104.0</t>
+          <t>246.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3248,7 +3248,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>45.25</t>
+          <t>45.05</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3258,7 +3258,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>0.33</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -3268,7 +3268,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-8.48</t>
+          <t>8.33</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3333,7 +3333,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-9.05</t>
+          <t>-9.45</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3383,17 +3383,17 @@
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>4.09</t>
+          <t>9.67</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
@@ -3404,12 +3404,12 @@
       <c r="AK7" t="inlineStr"/>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>143</t>
+          <t>78</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
@@ -3419,51 +3419,51 @@
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>37.52</t>
+          <t>9.52</t>
         </is>
       </c>
       <c r="AP7" t="n">
-        <v>-0.83</v>
+        <v>-0.95</v>
       </c>
       <c r="AQ7" t="n">
-        <v>-0.75</v>
+        <v>-0.87</v>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.9</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>-2.24</t>
+          <t>-2.29</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>45.63</t>
+          <t>45.48</t>
         </is>
       </c>
       <c r="AU7" t="n">
-        <v>45.98</v>
+        <v>45.88</v>
       </c>
       <c r="AV7" t="n">
-        <v>46.39</v>
+        <v>46.32</v>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>47.46</t>
+          <t>47.41</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>3.73</t>
+          <t>-7.02</t>
         </is>
       </c>
       <c r="AY7" t="n">
-        <v>-0.24</v>
+        <v>-0.28</v>
       </c>
       <c r="AZ7" t="n">
-        <v>-0.25</v>
+        <v>-0.26</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
@@ -3472,7 +3472,7 @@
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-105.93</t>
+          <t>-106.04</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
@@ -3482,43 +3482,43 @@
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>75574.61814345993</t>
+          <t>75475.9297752809</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
-          <t>4714.0</t>
+          <t>11034.0</t>
         </is>
       </c>
       <c r="BF7" t="n">
-        <v>3990.2</v>
+        <v>5441.2</v>
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>4360.0</t>
+          <t>5022.6</t>
         </is>
       </c>
       <c r="BH7" t="n">
-        <v>11948.92</v>
+        <v>11858.6</v>
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>-369</t>
+          <t>418</t>
         </is>
       </c>
       <c r="BJ7" t="inlineStr">
         <is>
-          <t>-1255.394821893818</t>
+          <t>-1154.46766135493</t>
         </is>
       </c>
       <c r="BK7" t="inlineStr">
         <is>
-          <t>-1213.317202241243</t>
+          <t>-599.3682783910481</t>
         </is>
       </c>
       <c r="BL7" t="inlineStr">
         <is>
-          <t>4714.0</t>
+          <t>11034.0</t>
         </is>
       </c>
       <c r="BM7" t="inlineStr">
@@ -3538,7 +3538,7 @@
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>-7.18</t>
+          <t>-7.59</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="BU7" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="BV7" t="inlineStr">
@@ -3583,12 +3583,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>6.11</t>
+          <t>6.12</t>
         </is>
       </c>
       <c r="CC7" t="inlineStr">
@@ -3608,7 +3608,7 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>10.23</t>
+          <t>10.2</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
@@ -3623,12 +3623,12 @@
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>47.2</t>
+          <t>47.76</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
         <is>
-          <t>4262</t>
+          <t>4253</t>
         </is>
       </c>
       <c r="CI7" t="inlineStr">
@@ -3648,22 +3648,22 @@
       </c>
       <c r="CL7" t="inlineStr">
         <is>
-          <t>45.5</t>
+          <t>45.25</t>
         </is>
       </c>
       <c r="CM7" t="inlineStr">
         <is>
-          <t>45.5</t>
+          <t>45.45</t>
         </is>
       </c>
       <c r="CN7" t="inlineStr">
         <is>
-          <t>44.9</t>
+          <t>44.5</t>
         </is>
       </c>
       <c r="CO7" t="inlineStr">
         <is>
-          <t>45.25</t>
+          <t>45.05</t>
         </is>
       </c>
       <c r="CP7" t="inlineStr">
@@ -3695,12 +3695,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>-0.55</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>104.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3710,7 +3710,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>45.5</t>
+          <t>45.25</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3720,7 +3720,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -3730,7 +3730,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-20.03</t>
+          <t>-8.48</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3795,7 +3795,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-8.54</t>
+          <t>-9.05</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3840,22 +3840,22 @@
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>3.97</t>
+          <t>4.09</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
@@ -3866,66 +3866,66 @@
       <c r="AK8" t="inlineStr"/>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>143</t>
+          <t>78</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>28.57</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>65.52</t>
+          <t>37.52</t>
         </is>
       </c>
       <c r="AP8" t="n">
-        <v>-0.61</v>
+        <v>-0.83</v>
       </c>
       <c r="AQ8" t="n">
-        <v>-0.58</v>
+        <v>-0.75</v>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.89</t>
+          <t>-0.9</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>-2.14</t>
+          <t>-2.24</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>45.77999999999999</t>
+          <t>45.63</t>
         </is>
       </c>
       <c r="AU8" t="n">
-        <v>46.04</v>
+        <v>45.98</v>
       </c>
       <c r="AV8" t="n">
-        <v>46.46</v>
+        <v>46.39</v>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>47.48</t>
+          <t>47.46</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>14.06</t>
+          <t>3.73</t>
         </is>
       </c>
       <c r="AY8" t="n">
-        <v>-0.22</v>
+        <v>-0.24</v>
       </c>
       <c r="AZ8" t="n">
-        <v>-0.26</v>
+        <v>-0.25</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
@@ -3934,7 +3934,7 @@
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-105.99</t>
+          <t>-105.93</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
@@ -3944,43 +3944,43 @@
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>75574.61814345993</t>
+          <t>75475.9297752809</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
-          <t>4590.0</t>
+          <t>4714.0</t>
         </is>
       </c>
       <c r="BF8" t="n">
-        <v>3743.4</v>
+        <v>3990.2</v>
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>4681.2</t>
+          <t>4360.0</t>
         </is>
       </c>
       <c r="BH8" t="n">
-        <v>12007.9</v>
+        <v>11948.92</v>
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>-937</t>
+          <t>-369</t>
         </is>
       </c>
       <c r="BJ8" t="inlineStr">
         <is>
-          <t>-1263.045298194286</t>
+          <t>-1255.394821893818</t>
         </is>
       </c>
       <c r="BK8" t="inlineStr">
         <is>
-          <t>-1369.911479090048</t>
+          <t>-1213.317202241243</t>
         </is>
       </c>
       <c r="BL8" t="inlineStr">
         <is>
-          <t>4590.0</t>
+          <t>4714.0</t>
         </is>
       </c>
       <c r="BM8" t="inlineStr">
@@ -4000,7 +4000,7 @@
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>-6.67</t>
+          <t>-7.18</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
@@ -4025,7 +4025,7 @@
       </c>
       <c r="BU8" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="BV8" t="inlineStr">
@@ -4045,7 +4045,7 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
@@ -4055,12 +4055,12 @@
       </c>
       <c r="CA8" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>6.11</t>
+          <t>6.12</t>
         </is>
       </c>
       <c r="CC8" t="inlineStr">
@@ -4070,7 +4070,7 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>10.23</t>
+          <t>10.2</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
@@ -4085,12 +4085,12 @@
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>47.2</t>
+          <t>47.76</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
         <is>
-          <t>4262</t>
+          <t>4253</t>
         </is>
       </c>
       <c r="CI8" t="inlineStr">
@@ -4110,22 +4110,22 @@
       </c>
       <c r="CL8" t="inlineStr">
         <is>
-          <t>46.0</t>
+          <t>45.5</t>
         </is>
       </c>
       <c r="CM8" t="inlineStr">
         <is>
-          <t>46.05</t>
+          <t>45.5</t>
         </is>
       </c>
       <c r="CN8" t="inlineStr">
         <is>
-          <t>45.15</t>
+          <t>44.9</t>
         </is>
       </c>
       <c r="CO8" t="inlineStr">
         <is>
-          <t>45.5</t>
+          <t>45.25</t>
         </is>
       </c>
       <c r="CP8" t="inlineStr">
@@ -4157,42 +4157,42 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
+          <t>-0.65</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>101.0</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>45.5</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>-0.66</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>67.0</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>45.8</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>-1.1</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-14.39</t>
+          <t>-20.03</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4257,7 +4257,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-7.94</t>
+          <t>-8.54</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4302,22 +4302,22 @@
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>2.63</t>
+          <t>3.97</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
@@ -4328,63 +4328,63 @@
       <c r="AK9" t="inlineStr"/>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>143</t>
+          <t>78</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>28.57</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>65.52</t>
         </is>
       </c>
       <c r="AP9" t="n">
-        <v>-0.17</v>
+        <v>-0.61</v>
       </c>
       <c r="AQ9" t="n">
-        <v>-0.52</v>
+        <v>-0.58</v>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.87</t>
+          <t>-0.89</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>-2.06</t>
+          <t>-2.14</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>45.88</t>
+          <t>45.77999999999999</t>
         </is>
       </c>
       <c r="AU9" t="n">
-        <v>46.12</v>
+        <v>46.04</v>
       </c>
       <c r="AV9" t="n">
-        <v>46.52</v>
+        <v>46.46</v>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>47.5</t>
+          <t>47.48</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>20.22</t>
+          <t>14.06</t>
         </is>
       </c>
       <c r="AY9" t="n">
-        <v>-0.21</v>
+        <v>-0.22</v>
       </c>
       <c r="AZ9" t="n">
         <v>-0.26</v>
@@ -4396,7 +4396,7 @@
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-106.20</t>
+          <t>-105.99</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
@@ -4406,43 +4406,43 @@
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>75574.61814345993</t>
+          <t>75475.9297752809</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
-          <t>3059.0</t>
+          <t>4590.0</t>
         </is>
       </c>
       <c r="BF9" t="n">
-        <v>3888.8</v>
+        <v>3743.4</v>
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>4542.6</t>
+          <t>4681.2</t>
         </is>
       </c>
       <c r="BH9" t="n">
-        <v>12062.18</v>
+        <v>12007.9</v>
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>-653</t>
+          <t>-937</t>
         </is>
       </c>
       <c r="BJ9" t="inlineStr">
         <is>
-          <t>-1243.615083485966</t>
+          <t>-1263.045298194286</t>
         </is>
       </c>
       <c r="BK9" t="inlineStr">
         <is>
-          <t>-1531.406464620841</t>
+          <t>-1369.911479090048</t>
         </is>
       </c>
       <c r="BL9" t="inlineStr">
         <is>
-          <t>3059.0</t>
+          <t>4590.0</t>
         </is>
       </c>
       <c r="BM9" t="inlineStr">
@@ -4462,7 +4462,7 @@
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>-6.05</t>
+          <t>-6.67</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
@@ -4487,7 +4487,7 @@
       </c>
       <c r="BU9" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="BV9" t="inlineStr">
@@ -4507,7 +4507,7 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
@@ -4517,12 +4517,12 @@
       </c>
       <c r="CA9" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>6.11</t>
+          <t>6.12</t>
         </is>
       </c>
       <c r="CC9" t="inlineStr">
@@ -4532,7 +4532,7 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>10.23</t>
+          <t>10.2</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>47.2</t>
+          <t>47.76</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
         <is>
-          <t>4262</t>
+          <t>4253</t>
         </is>
       </c>
       <c r="CI9" t="inlineStr">
@@ -4572,22 +4572,22 @@
       </c>
       <c r="CL9" t="inlineStr">
         <is>
-          <t>45.8</t>
+          <t>46.0</t>
         </is>
       </c>
       <c r="CM9" t="inlineStr">
         <is>
-          <t>46.0</t>
+          <t>46.05</t>
         </is>
       </c>
       <c r="CN9" t="inlineStr">
         <is>
-          <t>45.7</t>
+          <t>45.15</t>
         </is>
       </c>
       <c r="CO9" t="inlineStr">
         <is>
-          <t>45.8</t>
+          <t>45.5</t>
         </is>
       </c>
       <c r="CP9" t="inlineStr">
@@ -4624,7 +4624,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4644,7 +4644,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-1.1</t>
+          <t>-1.33</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -4654,7 +4654,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-2.42</t>
+          <t>-14.39</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4764,22 +4764,22 @@
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>3.26</t>
+          <t>2.63</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
@@ -4790,12 +4790,12 @@
       <c r="AK10" t="inlineStr"/>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>143</t>
+          <t>78</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
@@ -4805,23 +4805,23 @@
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>89.33</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AP10" t="n">
         <v>-0.17</v>
       </c>
       <c r="AQ10" t="n">
-        <v>-0.46</v>
+        <v>-0.52</v>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-1.07</t>
+          <t>-0.87</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>-1.95</t>
+          <t>-2.06</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
@@ -4830,26 +4830,26 @@
         </is>
       </c>
       <c r="AU10" t="n">
-        <v>46.09</v>
+        <v>46.12</v>
       </c>
       <c r="AV10" t="n">
-        <v>46.59</v>
+        <v>46.52</v>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>47.52</t>
+          <t>47.5</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>18.14</t>
+          <t>20.22</t>
         </is>
       </c>
       <c r="AY10" t="n">
-        <v>-0.23</v>
+        <v>-0.21</v>
       </c>
       <c r="AZ10" t="n">
-        <v>-0.28</v>
+        <v>-0.26</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
@@ -4858,7 +4858,7 @@
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-106.51</t>
+          <t>-106.20</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
@@ -4868,43 +4868,43 @@
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>75574.61814345993</t>
+          <t>75475.9297752809</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
-          <t>3809.0</t>
+          <t>3059.0</t>
         </is>
       </c>
       <c r="BF10" t="n">
-        <v>4626.6</v>
+        <v>3888.8</v>
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>4741.3</t>
+          <t>4542.6</t>
         </is>
       </c>
       <c r="BH10" t="n">
-        <v>12259.36</v>
+        <v>12062.18</v>
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>-114</t>
+          <t>-653</t>
         </is>
       </c>
       <c r="BJ10" t="inlineStr">
         <is>
-          <t>-1191.289377825079</t>
+          <t>-1243.615083485966</t>
         </is>
       </c>
       <c r="BK10" t="inlineStr">
         <is>
-          <t>-1543.3847844998</t>
+          <t>-1531.406464620841</t>
         </is>
       </c>
       <c r="BL10" t="inlineStr">
         <is>
-          <t>3809.0</t>
+          <t>3059.0</t>
         </is>
       </c>
       <c r="BM10" t="inlineStr">
@@ -4949,7 +4949,7 @@
       </c>
       <c r="BU10" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="BV10" t="inlineStr">
@@ -4969,7 +4969,7 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -4984,7 +4984,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>6.11</t>
+          <t>6.12</t>
         </is>
       </c>
       <c r="CC10" t="inlineStr">
@@ -4994,7 +4994,7 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>10.23</t>
+          <t>10.2</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
@@ -5009,12 +5009,12 @@
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>47.2</t>
+          <t>47.76</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
         <is>
-          <t>4262</t>
+          <t>4253</t>
         </is>
       </c>
       <c r="CI10" t="inlineStr">
@@ -5034,17 +5034,17 @@
       </c>
       <c r="CL10" t="inlineStr">
         <is>
-          <t>46.2</t>
+          <t>45.8</t>
         </is>
       </c>
       <c r="CM10" t="inlineStr">
         <is>
-          <t>46.2</t>
+          <t>46.0</t>
         </is>
       </c>
       <c r="CN10" t="inlineStr">
         <is>
-          <t>45.6</t>
+          <t>45.7</t>
         </is>
       </c>
       <c r="CO10" t="inlineStr">
@@ -5081,167 +5081,167 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>83.0</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>45.8</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>-1.33</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>-2.42</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>2025-09-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>2025-09-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>2025-03-06 00:00:00</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>2025-03-10 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>51.1</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>49.75</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>57.7</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>56.5</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>-7.94</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>-9.56</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025/05/23</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>51.4</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>2025/10/14</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>44.35</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>2025/06/30</t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>48.2</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>2025-12-02</t>
+        </is>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>3.26</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
           <t>-0.43</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>82.0</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>45.8</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>-1.1</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>-20.54</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>2025-09-02 00:00:00</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>2025-09-12 00:00:00</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>2025-03-06 00:00:00</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>2025-03-10 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>51.1</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>49.75</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>57.7</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>56.5</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>-7.94</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>-9.56</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>2025/05/23</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>51.4</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>2025/10/14</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>44.35</t>
-        </is>
-      </c>
-      <c r="AD11" t="inlineStr">
-        <is>
-          <t>2025/06/30</t>
-        </is>
-      </c>
-      <c r="AE11" t="inlineStr">
-        <is>
-          <t>48.2</t>
-        </is>
-      </c>
-      <c r="AF11" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="AG11" t="inlineStr">
-        <is>
-          <t>2025-12-01</t>
-        </is>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>3.22</t>
-        </is>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>0.00</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
@@ -5252,12 +5252,12 @@
       <c r="AK11" t="inlineStr"/>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>143</t>
+          <t>78</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
@@ -5267,51 +5267,51 @@
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>83.86</t>
+          <t>89.33</t>
         </is>
       </c>
       <c r="AP11" t="n">
-        <v>0.02</v>
+        <v>-0.17</v>
       </c>
       <c r="AQ11" t="n">
-        <v>-0.58</v>
+        <v>-0.46</v>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>-1.87</t>
+          <t>-1.95</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>45.79</t>
+          <t>45.88</t>
         </is>
       </c>
       <c r="AU11" t="n">
-        <v>46.06</v>
+        <v>46.09</v>
       </c>
       <c r="AV11" t="n">
-        <v>46.64</v>
+        <v>46.59</v>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>47.53</t>
+          <t>47.52</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>15.60</t>
+          <t>18.14</t>
         </is>
       </c>
       <c r="AY11" t="n">
-        <v>-0.25</v>
+        <v>-0.23</v>
       </c>
       <c r="AZ11" t="n">
-        <v>-0.29</v>
+        <v>-0.28</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
@@ -5320,7 +5320,7 @@
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-106.80</t>
+          <t>-106.51</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
@@ -5330,43 +5330,43 @@
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>75574.61814345993</t>
+          <t>75475.9297752809</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
-          <t>3779.0</t>
+          <t>3809.0</t>
         </is>
       </c>
       <c r="BF11" t="n">
-        <v>4604</v>
+        <v>4626.6</v>
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>5794.0</t>
+          <t>4741.3</t>
         </is>
       </c>
       <c r="BH11" t="n">
-        <v>12544.52</v>
+        <v>12259.36</v>
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>-1190</t>
+          <t>-114</t>
         </is>
       </c>
       <c r="BJ11" t="inlineStr">
         <is>
-          <t>-1127.272031156948</t>
+          <t>-1191.289377825079</t>
         </is>
       </c>
       <c r="BK11" t="inlineStr">
         <is>
-          <t>-1585.732927737606</t>
+          <t>-1543.3847844998</t>
         </is>
       </c>
       <c r="BL11" t="inlineStr">
         <is>
-          <t>3779.0</t>
+          <t>3809.0</t>
         </is>
       </c>
       <c r="BM11" t="inlineStr">
@@ -5411,7 +5411,7 @@
       </c>
       <c r="BU11" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="BV11" t="inlineStr">
@@ -5431,7 +5431,7 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5446,7 +5446,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>6.11</t>
+          <t>6.12</t>
         </is>
       </c>
       <c r="CC11" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>10.23</t>
+          <t>10.2</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
@@ -5471,12 +5471,12 @@
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>47.2</t>
+          <t>47.76</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
         <is>
-          <t>4262</t>
+          <t>4253</t>
         </is>
       </c>
       <c r="CI11" t="inlineStr">
@@ -5496,17 +5496,17 @@
       </c>
       <c r="CL11" t="inlineStr">
         <is>
-          <t>46.0</t>
+          <t>46.2</t>
         </is>
       </c>
       <c r="CM11" t="inlineStr">
         <is>
-          <t>46.05</t>
+          <t>46.2</t>
         </is>
       </c>
       <c r="CN11" t="inlineStr">
         <is>
-          <t>45.55</t>
+          <t>45.6</t>
         </is>
       </c>
       <c r="CO11" t="inlineStr">
@@ -5543,42 +5543,42 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
+          <t>-0.43</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>45.8</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>-1.33</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>75.0</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>46.0</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>-1.55</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-26.22</t>
+          <t>-20.54</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5643,7 +5643,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-7.54</t>
+          <t>-7.94</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5688,22 +5688,22 @@
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>2.95</t>
+          <t>3.22</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-0.98</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
@@ -5714,66 +5714,66 @@
       <c r="AK12" t="inlineStr"/>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>143</t>
+          <t>78</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>71.07</t>
+          <t>83.86</t>
         </is>
       </c>
       <c r="AP12" t="n">
-        <v>0.68</v>
+        <v>0.02</v>
       </c>
       <c r="AQ12" t="n">
-        <v>-0.75</v>
+        <v>-0.58</v>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>-1.76</t>
+          <t>-1.87</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>45.69</t>
+          <t>45.79</t>
         </is>
       </c>
       <c r="AU12" t="n">
-        <v>46.04</v>
+        <v>46.06</v>
       </c>
       <c r="AV12" t="n">
-        <v>46.7</v>
+        <v>46.64</v>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>47.54</t>
+          <t>47.53</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>12.46</t>
+          <t>15.60</t>
         </is>
       </c>
       <c r="AY12" t="n">
-        <v>-0.26</v>
+        <v>-0.25</v>
       </c>
       <c r="AZ12" t="n">
-        <v>-0.3</v>
+        <v>-0.29</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
@@ -5782,7 +5782,7 @@
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-107.07</t>
+          <t>-106.80</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
@@ -5792,43 +5792,43 @@
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>75574.61814345993</t>
+          <t>75475.9297752809</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
-          <t>3480.0</t>
+          <t>3779.0</t>
         </is>
       </c>
       <c r="BF12" t="n">
-        <v>4729.8</v>
+        <v>4604</v>
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>6410.4</t>
+          <t>5794.0</t>
         </is>
       </c>
       <c r="BH12" t="n">
-        <v>12782.88</v>
+        <v>12544.52</v>
       </c>
       <c r="BI12" t="inlineStr">
         <is>
-          <t>-1680</t>
+          <t>-1190</t>
         </is>
       </c>
       <c r="BJ12" t="inlineStr">
         <is>
-          <t>-1043.91550450592</t>
+          <t>-1127.272031156948</t>
         </is>
       </c>
       <c r="BK12" t="inlineStr">
         <is>
-          <t>-1586.382670658128</t>
+          <t>-1585.732927737606</t>
         </is>
       </c>
       <c r="BL12" t="inlineStr">
         <is>
-          <t>3480.0</t>
+          <t>3779.0</t>
         </is>
       </c>
       <c r="BM12" t="inlineStr">
@@ -5848,7 +5848,7 @@
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>-5.64</t>
+          <t>-6.05</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
@@ -5873,7 +5873,7 @@
       </c>
       <c r="BU12" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="BV12" t="inlineStr">
@@ -5893,7 +5893,7 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -5903,12 +5903,12 @@
       </c>
       <c r="CA12" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>6.11</t>
+          <t>6.12</t>
         </is>
       </c>
       <c r="CC12" t="inlineStr">
@@ -5918,7 +5918,7 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>10.23</t>
+          <t>10.2</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
@@ -5933,12 +5933,12 @@
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>47.2</t>
+          <t>47.76</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
         <is>
-          <t>4262</t>
+          <t>4253</t>
         </is>
       </c>
       <c r="CI12" t="inlineStr">
@@ -5958,22 +5958,22 @@
       </c>
       <c r="CL12" t="inlineStr">
         <is>
-          <t>46.4</t>
+          <t>46.0</t>
         </is>
       </c>
       <c r="CM12" t="inlineStr">
         <is>
-          <t>46.45</t>
+          <t>46.05</t>
         </is>
       </c>
       <c r="CN12" t="inlineStr">
         <is>
-          <t>46.0</t>
+          <t>45.55</t>
         </is>
       </c>
       <c r="CO12" t="inlineStr">
         <is>
-          <t>46.0</t>
+          <t>45.8</t>
         </is>
       </c>
       <c r="CP12" t="inlineStr">

--- a/Result/checksun_type/PET膜.xlsx
+++ b/Result/checksun_type/PET膜.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CR12"/>
+  <dimension ref="A1:CV12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -566,345 +566,365 @@
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
+          <t>MACD_hist_diff</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
           <t>MA_death_cross_d</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>MA_death_cross_d收盤價</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>MA_death_cross_d2</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>MA_death_cross_d2收盤價</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>MACD_hist_diff</t>
-        </is>
-      </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
+          <t>MACD_death_cross_d</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>MACD_death_cross_d收盤價</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>MACD_death_cross_d2</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>MACD_death_cross_d2收盤價</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
           <t>日期</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>量能</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>價能</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>cond_entry</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>text_desc</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>盤後量</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>成交量</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>%K</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>%D</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>MA5_%</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>均價_%</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
         <is>
           <t>均價long_%</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="AW1" s="1" t="inlineStr">
         <is>
           <t>均價longlong_%</t>
         </is>
       </c>
-      <c r="AT1" s="1" t="inlineStr">
+      <c r="AX1" s="1" t="inlineStr">
         <is>
           <t>MA_short</t>
         </is>
       </c>
-      <c r="AU1" s="1" t="inlineStr">
+      <c r="AY1" s="1" t="inlineStr">
         <is>
           <t>MA_long</t>
         </is>
       </c>
-      <c r="AV1" s="1" t="inlineStr">
+      <c r="AZ1" s="1" t="inlineStr">
         <is>
           <t>MA_longlong</t>
         </is>
       </c>
-      <c r="AW1" s="1" t="inlineStr">
+      <c r="BA1" s="1" t="inlineStr">
         <is>
           <t>MA_longlonglong</t>
         </is>
       </c>
-      <c r="AX1" s="1" t="inlineStr">
+      <c r="BB1" s="1" t="inlineStr">
         <is>
           <t>MACD_%</t>
         </is>
       </c>
-      <c r="AY1" s="1" t="inlineStr">
+      <c r="BC1" s="1" t="inlineStr">
         <is>
           <t>MACD</t>
         </is>
       </c>
-      <c r="AZ1" s="1" t="inlineStr">
+      <c r="BD1" s="1" t="inlineStr">
         <is>
           <t>MACD-SL</t>
         </is>
       </c>
-      <c r="BA1" s="1" t="inlineStr">
+      <c r="BE1" s="1" t="inlineStr">
         <is>
           <t>MACD-SL_max</t>
         </is>
       </c>
-      <c r="BB1" s="1" t="inlineStr">
+      <c r="BF1" s="1" t="inlineStr">
         <is>
           <t>MACDSL_%</t>
         </is>
       </c>
-      <c r="BC1" s="1" t="inlineStr">
+      <c r="BG1" s="1" t="inlineStr">
         <is>
           <t>MACD_last_cross_date</t>
         </is>
       </c>
-      <c r="BD1" s="1" t="inlineStr">
+      <c r="BH1" s="1" t="inlineStr">
         <is>
           <t>成交金額平均</t>
         </is>
       </c>
-      <c r="BE1" s="1" t="inlineStr">
+      <c r="BI1" s="1" t="inlineStr">
         <is>
           <t>成交金額</t>
         </is>
       </c>
-      <c r="BF1" s="1" t="inlineStr">
+      <c r="BJ1" s="1" t="inlineStr">
         <is>
           <t>Volume_MA_short</t>
         </is>
       </c>
-      <c r="BG1" s="1" t="inlineStr">
+      <c r="BK1" s="1" t="inlineStr">
         <is>
           <t>Volume_MA_long</t>
         </is>
       </c>
-      <c r="BH1" s="1" t="inlineStr">
+      <c r="BL1" s="1" t="inlineStr">
         <is>
           <t>Volume_MA_long50</t>
         </is>
       </c>
-      <c r="BI1" s="1" t="inlineStr">
+      <c r="BM1" s="1" t="inlineStr">
         <is>
           <t>Volume_Oscillator</t>
         </is>
       </c>
-      <c r="BJ1" s="1" t="inlineStr">
+      <c r="BN1" s="1" t="inlineStr">
         <is>
           <t>volume_threshold</t>
         </is>
       </c>
-      <c r="BK1" s="1" t="inlineStr">
+      <c r="BO1" s="1" t="inlineStr">
         <is>
           <t>VPC_MACD</t>
         </is>
       </c>
-      <c r="BL1" s="1" t="inlineStr">
+      <c r="BP1" s="1" t="inlineStr">
         <is>
           <t>Volume_Price_Change</t>
         </is>
       </c>
-      <c r="BM1" s="1" t="inlineStr">
+      <c r="BQ1" s="1" t="inlineStr">
         <is>
           <t>highlight_enddate</t>
         </is>
       </c>
-      <c r="BN1" s="1" t="inlineStr">
+      <c r="BR1" s="1" t="inlineStr">
         <is>
           <t>MA_last_cross_date收盤價</t>
         </is>
       </c>
-      <c r="BO1" s="1" t="inlineStr">
+      <c r="BS1" s="1" t="inlineStr">
         <is>
           <t>MA_last_cross_date</t>
         </is>
       </c>
-      <c r="BP1" s="1" t="inlineStr">
+      <c r="BT1" s="1" t="inlineStr">
         <is>
           <t>MA_last_cross_%</t>
         </is>
       </c>
-      <c r="BQ1" s="1" t="inlineStr">
+      <c r="BU1" s="1" t="inlineStr">
         <is>
           <t>stock_name</t>
         </is>
       </c>
-      <c r="BR1" s="1" t="inlineStr">
+      <c r="BV1" s="1" t="inlineStr">
         <is>
           <t>Type0</t>
         </is>
       </c>
-      <c r="BS1" s="1" t="inlineStr">
+      <c r="BW1" s="1" t="inlineStr">
         <is>
           <t>Type1</t>
         </is>
       </c>
-      <c r="BT1" s="1" t="inlineStr">
+      <c r="BX1" s="1" t="inlineStr">
         <is>
           <t>Type2</t>
         </is>
       </c>
-      <c r="BU1" s="1" t="inlineStr">
+      <c r="BY1" s="1" t="inlineStr">
         <is>
           <t>貝他值</t>
         </is>
       </c>
-      <c r="BV1" s="1" t="inlineStr">
+      <c r="BZ1" s="1" t="inlineStr">
         <is>
           <t>營業收入-上月比較增減(%)</t>
         </is>
       </c>
-      <c r="BW1" s="1" t="inlineStr">
+      <c r="CA1" s="1" t="inlineStr">
         <is>
           <t>營業收入-去年同月增減(%)</t>
         </is>
       </c>
-      <c r="BX1" s="1" t="inlineStr">
+      <c r="CB1" s="1" t="inlineStr">
         <is>
           <t>累計營業收入-前期比較增減(%)</t>
         </is>
       </c>
-      <c r="BY1" s="1" t="inlineStr">
+      <c r="CC1" s="1" t="inlineStr">
         <is>
           <t>Full_Summary</t>
         </is>
       </c>
-      <c r="BZ1" s="1" t="inlineStr">
+      <c r="CD1" s="1" t="inlineStr">
         <is>
           <t>textdesc</t>
         </is>
       </c>
-      <c r="CA1" s="1" t="inlineStr">
+      <c r="CE1" s="1" t="inlineStr">
         <is>
           <t>淨值倍率</t>
         </is>
       </c>
-      <c r="CB1" s="1" t="inlineStr">
+      <c r="CF1" s="1" t="inlineStr">
         <is>
           <t>殖利率</t>
         </is>
       </c>
-      <c r="CC1" s="1" t="inlineStr">
+      <c r="CG1" s="1" t="inlineStr">
         <is>
           <t>每股營收(元)</t>
         </is>
       </c>
-      <c r="CD1" s="1" t="inlineStr">
+      <c r="CH1" s="1" t="inlineStr">
         <is>
           <t>本益比</t>
         </is>
       </c>
-      <c r="CE1" s="1" t="inlineStr">
+      <c r="CI1" s="1" t="inlineStr">
         <is>
           <t>營業毛利率</t>
         </is>
       </c>
-      <c r="CF1" s="1" t="inlineStr">
+      <c r="CJ1" s="1" t="inlineStr">
         <is>
           <t>營業利益率</t>
         </is>
       </c>
-      <c r="CG1" s="1" t="inlineStr">
+      <c r="CK1" s="1" t="inlineStr">
         <is>
           <t>同業平均本益比</t>
         </is>
       </c>
-      <c r="CH1" s="1" t="inlineStr">
+      <c r="CL1" s="1" t="inlineStr">
         <is>
           <t>總市值</t>
         </is>
       </c>
-      <c r="CI1" s="1" t="inlineStr">
+      <c r="CM1" s="1" t="inlineStr">
         <is>
           <t>營收比重</t>
         </is>
       </c>
-      <c r="CJ1" s="1" t="inlineStr">
+      <c r="CN1" s="1" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="CK1" s="1" t="inlineStr">
+      <c r="CO1" s="1" t="inlineStr">
         <is>
           <t>Typelevel</t>
         </is>
       </c>
-      <c r="CL1" s="1" t="inlineStr">
+      <c r="CP1" s="1" t="inlineStr">
         <is>
           <t>開盤價</t>
         </is>
       </c>
-      <c r="CM1" s="1" t="inlineStr">
+      <c r="CQ1" s="1" t="inlineStr">
         <is>
           <t>最高價</t>
         </is>
       </c>
-      <c r="CN1" s="1" t="inlineStr">
+      <c r="CR1" s="1" t="inlineStr">
         <is>
           <t>最低價</t>
         </is>
       </c>
-      <c r="CO1" s="1" t="inlineStr">
+      <c r="CS1" s="1" t="inlineStr">
         <is>
           <t>收盤價</t>
         </is>
       </c>
-      <c r="CP1" s="1" t="inlineStr">
+      <c r="CT1" s="1" t="inlineStr">
         <is>
           <t>每股淨值(元)</t>
         </is>
       </c>
-      <c r="CQ1" s="1" t="inlineStr">
+      <c r="CU1" s="1" t="inlineStr">
         <is>
           <t>desc</t>
         </is>
       </c>
-      <c r="CR1" s="1" t="inlineStr">
+      <c r="CV1" s="1" t="inlineStr">
         <is>
           <t>flag_stat</t>
         </is>
@@ -1048,325 +1068,345 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
+          <t>0.02</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
           <t>2025/10/14</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
+      <c r="AD2" t="inlineStr">
         <is>
           <t>44.35</t>
         </is>
       </c>
-      <c r="AD2" t="inlineStr">
+      <c r="AE2" t="inlineStr">
         <is>
           <t>2025/06/30</t>
         </is>
       </c>
-      <c r="AE2" t="inlineStr">
+      <c r="AF2" t="inlineStr">
         <is>
           <t>48.2</t>
         </is>
       </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>0.02</t>
-        </is>
-      </c>
       <c r="AG2" t="inlineStr">
         <is>
+          <t>2025/12/08</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>45.05</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>2025/11/19</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>45.05</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
           <t>2025-12-15</t>
         </is>
       </c>
-      <c r="AH2" t="inlineStr">
+      <c r="AL2" t="inlineStr">
         <is>
           <t>3.07</t>
         </is>
       </c>
-      <c r="AI2" t="inlineStr">
+      <c r="AM2" t="inlineStr">
         <is>
           <t>-0.55</t>
         </is>
       </c>
-      <c r="AJ2" t="inlineStr">
+      <c r="AN2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AK2" t="inlineStr"/>
-      <c r="AL2" t="inlineStr">
+      <c r="AO2" t="inlineStr"/>
+      <c r="AP2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
+      <c r="AQ2" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="AN2" t="inlineStr">
+      <c r="AR2" t="inlineStr">
         <is>
           <t>45.45</t>
         </is>
       </c>
-      <c r="AO2" t="inlineStr">
+      <c r="AS2" t="inlineStr">
         <is>
           <t>33.33</t>
         </is>
       </c>
-      <c r="AP2" t="n">
+      <c r="AT2" t="n">
         <v>0.22</v>
       </c>
-      <c r="AQ2" t="n">
+      <c r="AU2" t="n">
         <v>-0.58</v>
       </c>
-      <c r="AR2" t="inlineStr">
+      <c r="AV2" t="inlineStr">
         <is>
           <t>-1.27</t>
         </is>
       </c>
-      <c r="AS2" t="inlineStr">
+      <c r="AW2" t="inlineStr">
         <is>
           <t>-2.57</t>
         </is>
       </c>
-      <c r="AT2" t="inlineStr">
+      <c r="AX2" t="inlineStr">
         <is>
           <t>45.1</t>
         </is>
       </c>
-      <c r="AU2" t="n">
+      <c r="AY2" t="n">
         <v>45.36</v>
       </c>
-      <c r="AV2" t="n">
+      <c r="AZ2" t="n">
         <v>45.95</v>
       </c>
-      <c r="AW2" t="inlineStr">
+      <c r="BA2" t="inlineStr">
         <is>
           <t>47.16</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="BB2" t="inlineStr">
         <is>
           <t>-4.49</t>
         </is>
       </c>
-      <c r="AY2" t="n">
+      <c r="BC2" t="n">
         <v>-0.31</v>
       </c>
-      <c r="AZ2" t="n">
+      <c r="BD2" t="n">
         <v>-0.29</v>
       </c>
-      <c r="BA2" t="inlineStr">
+      <c r="BE2" t="inlineStr">
         <is>
           <t>4.28</t>
         </is>
       </c>
-      <c r="BB2" t="inlineStr">
+      <c r="BF2" t="inlineStr">
         <is>
           <t>-106.86</t>
         </is>
       </c>
-      <c r="BC2" t="inlineStr">
+      <c r="BG2" t="inlineStr">
         <is>
           <t>2025/11/27</t>
         </is>
       </c>
-      <c r="BD2" t="inlineStr">
+      <c r="BH2" t="inlineStr">
         <is>
           <t>75475.9297752809</t>
         </is>
       </c>
-      <c r="BE2" t="inlineStr">
+      <c r="BI2" t="inlineStr">
         <is>
           <t>3539.0</t>
         </is>
       </c>
-      <c r="BF2" t="n">
+      <c r="BJ2" t="n">
         <v>8163.8</v>
       </c>
-      <c r="BG2" t="inlineStr">
+      <c r="BK2" t="inlineStr">
         <is>
           <t>6802.5</t>
         </is>
       </c>
-      <c r="BH2" t="n">
+      <c r="BL2" t="n">
         <v>11065.56</v>
       </c>
-      <c r="BI2" t="inlineStr">
+      <c r="BM2" t="inlineStr">
         <is>
           <t>1361</t>
         </is>
       </c>
-      <c r="BJ2" t="inlineStr">
+      <c r="BN2" t="inlineStr">
         <is>
           <t>-497.5264159701541</t>
         </is>
       </c>
-      <c r="BK2" t="inlineStr">
+      <c r="BO2" t="inlineStr">
         <is>
           <t>-252.6207944996822</t>
         </is>
       </c>
-      <c r="BL2" t="inlineStr">
+      <c r="BP2" t="inlineStr">
         <is>
           <t>3539.0</t>
         </is>
       </c>
-      <c r="BM2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BN2" t="inlineStr">
+      <c r="BQ2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR2" t="inlineStr">
         <is>
           <t>48.75</t>
         </is>
       </c>
-      <c r="BO2" t="inlineStr">
+      <c r="BS2" t="inlineStr">
         <is>
           <t>2025/08/25</t>
         </is>
       </c>
-      <c r="BP2" t="inlineStr">
+      <c r="BT2" t="inlineStr">
         <is>
           <t>-7.28</t>
         </is>
       </c>
-      <c r="BQ2" t="inlineStr">
+      <c r="BU2" t="inlineStr">
         <is>
           <t>岱稜</t>
         </is>
       </c>
-      <c r="BR2" t="inlineStr">
+      <c r="BV2" t="inlineStr">
         <is>
           <t>岱稜</t>
         </is>
       </c>
-      <c r="BS2" t="inlineStr">
+      <c r="BW2" t="inlineStr">
         <is>
           <t>其他電子業</t>
         </is>
       </c>
-      <c r="BT2" t="inlineStr">
+      <c r="BX2" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BU2" t="inlineStr">
+      <c r="BY2" t="inlineStr">
         <is>
           <t>1.03</t>
         </is>
       </c>
-      <c r="BV2" t="inlineStr">
+      <c r="BZ2" t="inlineStr">
         <is>
           <t>-1.004452687200723</t>
         </is>
       </c>
-      <c r="BW2" t="inlineStr">
+      <c r="CA2" t="inlineStr">
         <is>
           <t>11.92388165594906</t>
         </is>
       </c>
-      <c r="BX2" t="inlineStr">
+      <c r="CB2" t="inlineStr">
         <is>
           <t>2.060463205899802</t>
         </is>
       </c>
-      <c r="BY2" t="inlineStr">
+      <c r="CC2" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BZ2" t="inlineStr">
+      <c r="CD2" t="inlineStr">
         <is>
           <t>價-量縮</t>
         </is>
       </c>
-      <c r="CA2" t="inlineStr">
+      <c r="CE2" t="inlineStr">
         <is>
           <t>1.83</t>
         </is>
       </c>
-      <c r="CB2" t="inlineStr">
+      <c r="CF2" t="inlineStr">
         <is>
           <t>6.12</t>
         </is>
       </c>
-      <c r="CC2" t="inlineStr">
+      <c r="CG2" t="inlineStr">
         <is>
           <t>8.56</t>
         </is>
       </c>
-      <c r="CD2" t="inlineStr">
+      <c r="CH2" t="inlineStr">
         <is>
           <t>10.2</t>
         </is>
       </c>
-      <c r="CE2" t="inlineStr">
+      <c r="CI2" t="inlineStr">
         <is>
           <t>33.67%</t>
         </is>
       </c>
-      <c r="CF2" t="inlineStr">
+      <c r="CJ2" t="inlineStr">
         <is>
           <t>12.48%</t>
         </is>
       </c>
-      <c r="CG2" t="inlineStr">
+      <c r="CK2" t="inlineStr">
         <is>
           <t>47.76</t>
         </is>
       </c>
-      <c r="CH2" t="inlineStr">
+      <c r="CL2" t="inlineStr">
         <is>
           <t>4253</t>
         </is>
       </c>
-      <c r="CI2" t="inlineStr">
+      <c r="CM2" t="inlineStr">
         <is>
           <t>真空蒸鍍薄膜95.00%、光電材料5.00% (2024年)</t>
         </is>
       </c>
-      <c r="CJ2" t="inlineStr">
+      <c r="CN2" t="inlineStr">
         <is>
           <t>岱稜-其他電子業-上櫃</t>
         </is>
       </c>
-      <c r="CK2" t="inlineStr">
+      <c r="CO2" t="inlineStr">
         <is>
           <t>其他電子業平上櫃</t>
         </is>
       </c>
-      <c r="CL2" t="inlineStr">
+      <c r="CP2" t="inlineStr">
         <is>
           <t>45.05</t>
         </is>
       </c>
-      <c r="CM2" t="inlineStr">
+      <c r="CQ2" t="inlineStr">
         <is>
           <t>45.6</t>
         </is>
       </c>
-      <c r="CN2" t="inlineStr">
+      <c r="CR2" t="inlineStr">
         <is>
           <t>45.05</t>
         </is>
       </c>
-      <c r="CO2" t="inlineStr">
+      <c r="CS2" t="inlineStr">
         <is>
           <t>45.2</t>
         </is>
       </c>
-      <c r="CP2" t="inlineStr">
+      <c r="CT2" t="inlineStr">
         <is>
           <t>24.66</t>
         </is>
       </c>
-      <c r="CQ2" t="inlineStr">
+      <c r="CU2" t="inlineStr">
         <is>
           <t>** 觸控面板 - PET膜** 其他 - 其他電子產品及電子服務產業、其他** 醫療器材 - 塑化材料</t>
         </is>
       </c>
-      <c r="CR2" t="inlineStr">
+      <c r="CV2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -1510,325 +1550,345 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
+          <t>0.03</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
           <t>2025/10/14</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
+      <c r="AD3" t="inlineStr">
         <is>
           <t>44.35</t>
         </is>
       </c>
-      <c r="AD3" t="inlineStr">
+      <c r="AE3" t="inlineStr">
         <is>
           <t>2025/06/30</t>
         </is>
       </c>
-      <c r="AE3" t="inlineStr">
+      <c r="AF3" t="inlineStr">
         <is>
           <t>48.2</t>
         </is>
       </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>0.03</t>
-        </is>
-      </c>
       <c r="AG3" t="inlineStr">
         <is>
+          <t>2025/12/08</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>45.05</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>2025/11/19</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>45.05</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
           <t>2025-12-12</t>
         </is>
       </c>
-      <c r="AH3" t="inlineStr">
+      <c r="AL3" t="inlineStr">
         <is>
           <t>5.62</t>
         </is>
       </c>
-      <c r="AI3" t="inlineStr">
+      <c r="AM3" t="inlineStr">
         <is>
           <t>1.23</t>
         </is>
       </c>
-      <c r="AJ3" t="inlineStr">
+      <c r="AN3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AK3" t="inlineStr"/>
-      <c r="AL3" t="inlineStr">
+      <c r="AO3" t="inlineStr"/>
+      <c r="AP3" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
+      <c r="AQ3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="AN3" t="inlineStr">
+      <c r="AR3" t="inlineStr">
         <is>
           <t>54.55</t>
         </is>
       </c>
-      <c r="AO3" t="inlineStr">
+      <c r="AS3" t="inlineStr">
         <is>
           <t>18.18</t>
         </is>
       </c>
-      <c r="AP3" t="n">
+      <c r="AT3" t="n">
         <v>0.51</v>
       </c>
-      <c r="AQ3" t="n">
+      <c r="AU3" t="n">
         <v>-0.8</v>
       </c>
-      <c r="AR3" t="inlineStr">
+      <c r="AV3" t="inlineStr">
         <is>
           <t>-1.32</t>
         </is>
       </c>
-      <c r="AS3" t="inlineStr">
+      <c r="AW3" t="inlineStr">
         <is>
           <t>-2.47</t>
         </is>
       </c>
-      <c r="AT3" t="inlineStr">
+      <c r="AX3" t="inlineStr">
         <is>
           <t>45.07000000000001</t>
         </is>
       </c>
-      <c r="AU3" t="n">
+      <c r="AY3" t="n">
         <v>45.44</v>
       </c>
-      <c r="AV3" t="n">
+      <c r="AZ3" t="n">
         <v>46.04</v>
       </c>
-      <c r="AW3" t="inlineStr">
+      <c r="BA3" t="inlineStr">
         <is>
           <t>47.21</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
+      <c r="BB3" t="inlineStr">
         <is>
           <t>-10.29</t>
         </is>
       </c>
-      <c r="AY3" t="n">
+      <c r="BC3" t="n">
         <v>-0.32</v>
       </c>
-      <c r="AZ3" t="n">
+      <c r="BD3" t="n">
         <v>-0.29</v>
       </c>
-      <c r="BA3" t="inlineStr">
+      <c r="BE3" t="inlineStr">
         <is>
           <t>4.28</t>
         </is>
       </c>
-      <c r="BB3" t="inlineStr">
+      <c r="BF3" t="inlineStr">
         <is>
           <t>-106.78</t>
         </is>
       </c>
-      <c r="BC3" t="inlineStr">
+      <c r="BG3" t="inlineStr">
         <is>
           <t>2025/11/27</t>
         </is>
       </c>
-      <c r="BD3" t="inlineStr">
+      <c r="BH3" t="inlineStr">
         <is>
           <t>75475.9297752809</t>
         </is>
       </c>
-      <c r="BE3" t="inlineStr">
+      <c r="BI3" t="inlineStr">
         <is>
           <t>6423.0</t>
         </is>
       </c>
-      <c r="BF3" t="n">
+      <c r="BJ3" t="n">
         <v>9662.799999999999</v>
       </c>
-      <c r="BG3" t="inlineStr">
+      <c r="BK3" t="inlineStr">
         <is>
           <t>6826.5</t>
         </is>
       </c>
-      <c r="BH3" t="n">
+      <c r="BL3" t="n">
         <v>11523.86</v>
       </c>
-      <c r="BI3" t="inlineStr">
+      <c r="BM3" t="inlineStr">
         <is>
           <t>2836</t>
         </is>
       </c>
-      <c r="BJ3" t="inlineStr">
+      <c r="BN3" t="inlineStr">
         <is>
           <t>-542.0547107829672</t>
         </is>
       </c>
-      <c r="BK3" t="inlineStr">
+      <c r="BO3" t="inlineStr">
         <is>
           <t>73.8133654135845</t>
         </is>
       </c>
-      <c r="BL3" t="inlineStr">
+      <c r="BP3" t="inlineStr">
         <is>
           <t>6423.0</t>
         </is>
       </c>
-      <c r="BM3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BN3" t="inlineStr">
+      <c r="BQ3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR3" t="inlineStr">
         <is>
           <t>48.75</t>
         </is>
       </c>
-      <c r="BO3" t="inlineStr">
+      <c r="BS3" t="inlineStr">
         <is>
           <t>2025/08/25</t>
         </is>
       </c>
-      <c r="BP3" t="inlineStr">
+      <c r="BT3" t="inlineStr">
         <is>
           <t>-7.08</t>
         </is>
       </c>
-      <c r="BQ3" t="inlineStr">
+      <c r="BU3" t="inlineStr">
         <is>
           <t>岱稜</t>
         </is>
       </c>
-      <c r="BR3" t="inlineStr">
+      <c r="BV3" t="inlineStr">
         <is>
           <t>岱稜</t>
         </is>
       </c>
-      <c r="BS3" t="inlineStr">
+      <c r="BW3" t="inlineStr">
         <is>
           <t>其他電子業</t>
         </is>
       </c>
-      <c r="BT3" t="inlineStr">
+      <c r="BX3" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BU3" t="inlineStr">
+      <c r="BY3" t="inlineStr">
         <is>
           <t>1.03</t>
         </is>
       </c>
-      <c r="BV3" t="inlineStr">
+      <c r="BZ3" t="inlineStr">
         <is>
           <t>-1.004452687200723</t>
         </is>
       </c>
-      <c r="BW3" t="inlineStr">
+      <c r="CA3" t="inlineStr">
         <is>
           <t>11.92388165594906</t>
         </is>
       </c>
-      <c r="BX3" t="inlineStr">
+      <c r="CB3" t="inlineStr">
         <is>
           <t>2.060463205899802</t>
         </is>
       </c>
-      <c r="BY3" t="inlineStr">
+      <c r="CC3" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BZ3" t="inlineStr">
+      <c r="CD3" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="CA3" t="inlineStr">
+      <c r="CE3" t="inlineStr">
         <is>
           <t>1.84</t>
         </is>
       </c>
-      <c r="CB3" t="inlineStr">
+      <c r="CF3" t="inlineStr">
         <is>
           <t>6.12</t>
         </is>
       </c>
-      <c r="CC3" t="inlineStr">
+      <c r="CG3" t="inlineStr">
         <is>
           <t>8.56</t>
         </is>
       </c>
-      <c r="CD3" t="inlineStr">
+      <c r="CH3" t="inlineStr">
         <is>
           <t>10.2</t>
         </is>
       </c>
-      <c r="CE3" t="inlineStr">
+      <c r="CI3" t="inlineStr">
         <is>
           <t>33.67%</t>
         </is>
       </c>
-      <c r="CF3" t="inlineStr">
+      <c r="CJ3" t="inlineStr">
         <is>
           <t>12.48%</t>
         </is>
       </c>
-      <c r="CG3" t="inlineStr">
+      <c r="CK3" t="inlineStr">
         <is>
           <t>47.76</t>
         </is>
       </c>
-      <c r="CH3" t="inlineStr">
+      <c r="CL3" t="inlineStr">
         <is>
           <t>4253</t>
         </is>
       </c>
-      <c r="CI3" t="inlineStr">
+      <c r="CM3" t="inlineStr">
         <is>
           <t>真空蒸鍍薄膜95.00%、光電材料5.00% (2024年)</t>
         </is>
       </c>
-      <c r="CJ3" t="inlineStr">
+      <c r="CN3" t="inlineStr">
         <is>
           <t>岱稜-其他電子業-上櫃</t>
         </is>
       </c>
-      <c r="CK3" t="inlineStr">
+      <c r="CO3" t="inlineStr">
         <is>
           <t>其他電子業平上櫃</t>
         </is>
       </c>
-      <c r="CL3" t="inlineStr">
+      <c r="CP3" t="inlineStr">
         <is>
           <t>44.8</t>
         </is>
       </c>
-      <c r="CM3" t="inlineStr">
+      <c r="CQ3" t="inlineStr">
         <is>
           <t>45.3</t>
         </is>
       </c>
-      <c r="CN3" t="inlineStr">
+      <c r="CR3" t="inlineStr">
         <is>
           <t>44.75</t>
         </is>
       </c>
-      <c r="CO3" t="inlineStr">
+      <c r="CS3" t="inlineStr">
         <is>
           <t>45.3</t>
         </is>
       </c>
-      <c r="CP3" t="inlineStr">
+      <c r="CT3" t="inlineStr">
         <is>
           <t>24.66</t>
         </is>
       </c>
-      <c r="CQ3" t="inlineStr">
+      <c r="CU3" t="inlineStr">
         <is>
           <t>** 觸控面板 - PET膜** 其他 - 其他電子產品及電子服務產業、其他** 醫療器材 - 塑化材料</t>
         </is>
       </c>
-      <c r="CR3" t="inlineStr">
+      <c r="CV3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -1972,325 +2032,345 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
+          <t>-0.02</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
           <t>2025/10/14</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
+      <c r="AD4" t="inlineStr">
         <is>
           <t>44.35</t>
         </is>
       </c>
-      <c r="AD4" t="inlineStr">
+      <c r="AE4" t="inlineStr">
         <is>
           <t>2025/06/30</t>
         </is>
       </c>
-      <c r="AE4" t="inlineStr">
+      <c r="AF4" t="inlineStr">
         <is>
           <t>48.2</t>
         </is>
       </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>-0.02</t>
-        </is>
-      </c>
       <c r="AG4" t="inlineStr">
         <is>
+          <t>2025/12/08</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>45.05</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>2025/11/19</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>45.05</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="AH4" t="inlineStr">
+      <c r="AL4" t="inlineStr">
         <is>
           <t>4.28</t>
         </is>
       </c>
-      <c r="AI4" t="inlineStr">
+      <c r="AM4" t="inlineStr">
         <is>
           <t>0.34</t>
         </is>
       </c>
-      <c r="AJ4" t="inlineStr">
+      <c r="AN4" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AK4" t="inlineStr"/>
-      <c r="AL4" t="inlineStr">
+      <c r="AO4" t="inlineStr"/>
+      <c r="AP4" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
+      <c r="AQ4" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="AN4" t="inlineStr">
+      <c r="AR4" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AO4" t="inlineStr">
+      <c r="AS4" t="inlineStr">
         <is>
           <t>17.54</t>
         </is>
       </c>
-      <c r="AP4" t="n">
+      <c r="AT4" t="n">
         <v>-0.8</v>
       </c>
-      <c r="AQ4" t="n">
+      <c r="AU4" t="n">
         <v>-1.02</v>
       </c>
-      <c r="AR4" t="inlineStr">
+      <c r="AV4" t="inlineStr">
         <is>
           <t>-1.27</t>
         </is>
       </c>
-      <c r="AS4" t="inlineStr">
+      <c r="AW4" t="inlineStr">
         <is>
           <t>-2.44</t>
         </is>
       </c>
-      <c r="AT4" t="inlineStr">
+      <c r="AX4" t="inlineStr">
         <is>
           <t>45.06</t>
         </is>
       </c>
-      <c r="AU4" t="n">
+      <c r="AY4" t="n">
         <v>45.52</v>
       </c>
-      <c r="AV4" t="n">
+      <c r="AZ4" t="n">
         <v>46.11</v>
       </c>
-      <c r="AW4" t="inlineStr">
+      <c r="BA4" t="inlineStr">
         <is>
           <t>47.26</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
+      <c r="BB4" t="inlineStr">
         <is>
           <t>-21.20</t>
         </is>
       </c>
-      <c r="AY4" t="n">
+      <c r="BC4" t="n">
         <v>-0.34</v>
       </c>
-      <c r="AZ4" t="n">
+      <c r="BD4" t="n">
         <v>-0.28</v>
       </c>
-      <c r="BA4" t="inlineStr">
+      <c r="BE4" t="inlineStr">
         <is>
           <t>4.28</t>
         </is>
       </c>
-      <c r="BB4" t="inlineStr">
+      <c r="BF4" t="inlineStr">
         <is>
           <t>-106.61</t>
         </is>
       </c>
-      <c r="BC4" t="inlineStr">
+      <c r="BG4" t="inlineStr">
         <is>
           <t>2025/11/27</t>
         </is>
       </c>
-      <c r="BD4" t="inlineStr">
+      <c r="BH4" t="inlineStr">
         <is>
           <t>75475.9297752809</t>
         </is>
       </c>
-      <c r="BE4" t="inlineStr">
+      <c r="BI4" t="inlineStr">
         <is>
           <t>4845.0</t>
         </is>
       </c>
-      <c r="BF4" t="n">
+      <c r="BJ4" t="n">
         <v>9321</v>
       </c>
-      <c r="BG4" t="inlineStr">
+      <c r="BK4" t="inlineStr">
         <is>
           <t>6532.2</t>
         </is>
       </c>
-      <c r="BH4" t="n">
+      <c r="BL4" t="n">
         <v>11521.76</v>
       </c>
-      <c r="BI4" t="inlineStr">
+      <c r="BM4" t="inlineStr">
         <is>
           <t>2788</t>
         </is>
       </c>
-      <c r="BJ4" t="inlineStr">
+      <c r="BN4" t="inlineStr">
         <is>
           <t>-654.0307246368856</t>
         </is>
       </c>
-      <c r="BK4" t="inlineStr">
+      <c r="BO4" t="inlineStr">
         <is>
           <t>228.5116879534808</t>
         </is>
       </c>
-      <c r="BL4" t="inlineStr">
+      <c r="BP4" t="inlineStr">
         <is>
           <t>4845.0</t>
         </is>
       </c>
-      <c r="BM4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BN4" t="inlineStr">
+      <c r="BQ4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR4" t="inlineStr">
         <is>
           <t>48.75</t>
         </is>
       </c>
-      <c r="BO4" t="inlineStr">
+      <c r="BS4" t="inlineStr">
         <is>
           <t>2025/08/25</t>
         </is>
       </c>
-      <c r="BP4" t="inlineStr">
+      <c r="BT4" t="inlineStr">
         <is>
           <t>-8.31</t>
         </is>
       </c>
-      <c r="BQ4" t="inlineStr">
+      <c r="BU4" t="inlineStr">
         <is>
           <t>岱稜</t>
         </is>
       </c>
-      <c r="BR4" t="inlineStr">
+      <c r="BV4" t="inlineStr">
         <is>
           <t>岱稜</t>
         </is>
       </c>
-      <c r="BS4" t="inlineStr">
+      <c r="BW4" t="inlineStr">
         <is>
           <t>其他電子業</t>
         </is>
       </c>
-      <c r="BT4" t="inlineStr">
+      <c r="BX4" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BU4" t="inlineStr">
+      <c r="BY4" t="inlineStr">
         <is>
           <t>1.03</t>
         </is>
       </c>
-      <c r="BV4" t="inlineStr">
+      <c r="BZ4" t="inlineStr">
         <is>
           <t>-1.004452687200723</t>
         </is>
       </c>
-      <c r="BW4" t="inlineStr">
+      <c r="CA4" t="inlineStr">
         <is>
           <t>11.92388165594906</t>
         </is>
       </c>
-      <c r="BX4" t="inlineStr">
+      <c r="CB4" t="inlineStr">
         <is>
           <t>2.060463205899802</t>
         </is>
       </c>
-      <c r="BY4" t="inlineStr">
+      <c r="CC4" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BZ4" t="inlineStr">
+      <c r="CD4" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="CA4" t="inlineStr">
+      <c r="CE4" t="inlineStr">
         <is>
           <t>1.81</t>
         </is>
       </c>
-      <c r="CB4" t="inlineStr">
+      <c r="CF4" t="inlineStr">
         <is>
           <t>6.12</t>
         </is>
       </c>
-      <c r="CC4" t="inlineStr">
+      <c r="CG4" t="inlineStr">
         <is>
           <t>8.56</t>
         </is>
       </c>
-      <c r="CD4" t="inlineStr">
+      <c r="CH4" t="inlineStr">
         <is>
           <t>10.2</t>
         </is>
       </c>
-      <c r="CE4" t="inlineStr">
+      <c r="CI4" t="inlineStr">
         <is>
           <t>33.67%</t>
         </is>
       </c>
-      <c r="CF4" t="inlineStr">
+      <c r="CJ4" t="inlineStr">
         <is>
           <t>12.48%</t>
         </is>
       </c>
-      <c r="CG4" t="inlineStr">
+      <c r="CK4" t="inlineStr">
         <is>
           <t>47.76</t>
         </is>
       </c>
-      <c r="CH4" t="inlineStr">
+      <c r="CL4" t="inlineStr">
         <is>
           <t>4253</t>
         </is>
       </c>
-      <c r="CI4" t="inlineStr">
+      <c r="CM4" t="inlineStr">
         <is>
           <t>真空蒸鍍薄膜95.00%、光電材料5.00% (2024年)</t>
         </is>
       </c>
-      <c r="CJ4" t="inlineStr">
+      <c r="CN4" t="inlineStr">
         <is>
           <t>岱稜-其他電子業-上櫃</t>
         </is>
       </c>
-      <c r="CK4" t="inlineStr">
+      <c r="CO4" t="inlineStr">
         <is>
           <t>其他電子業平上櫃</t>
         </is>
       </c>
-      <c r="CL4" t="inlineStr">
+      <c r="CP4" t="inlineStr">
         <is>
           <t>44.75</t>
         </is>
       </c>
-      <c r="CM4" t="inlineStr">
+      <c r="CQ4" t="inlineStr">
         <is>
           <t>44.75</t>
         </is>
       </c>
-      <c r="CN4" t="inlineStr">
+      <c r="CR4" t="inlineStr">
         <is>
           <t>44.5</t>
         </is>
       </c>
-      <c r="CO4" t="inlineStr">
+      <c r="CS4" t="inlineStr">
         <is>
           <t>44.7</t>
         </is>
       </c>
-      <c r="CP4" t="inlineStr">
+      <c r="CT4" t="inlineStr">
         <is>
           <t>24.66</t>
         </is>
       </c>
-      <c r="CQ4" t="inlineStr">
+      <c r="CU4" t="inlineStr">
         <is>
           <t>** 觸控面板 - PET膜** 其他 - 其他電子產品及電子服務產業、其他** 醫療器材 - 塑化材料</t>
         </is>
       </c>
-      <c r="CR4" t="inlineStr">
+      <c r="CV4" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -2434,325 +2514,345 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
+          <t>-0.04</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
           <t>2025/10/14</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
+      <c r="AD5" t="inlineStr">
         <is>
           <t>44.35</t>
         </is>
       </c>
-      <c r="AD5" t="inlineStr">
+      <c r="AE5" t="inlineStr">
         <is>
           <t>2025/06/30</t>
         </is>
       </c>
-      <c r="AE5" t="inlineStr">
+      <c r="AF5" t="inlineStr">
         <is>
           <t>48.2</t>
         </is>
       </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>-0.04</t>
-        </is>
-      </c>
       <c r="AG5" t="inlineStr">
         <is>
+          <t>2025/12/08</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>45.05</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>2025/11/19</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>45.05</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
           <t>2025-12-10</t>
         </is>
       </c>
-      <c r="AH5" t="inlineStr">
+      <c r="AL5" t="inlineStr">
         <is>
           <t>18.79</t>
         </is>
       </c>
-      <c r="AI5" t="inlineStr">
+      <c r="AM5" t="inlineStr">
         <is>
           <t>0.46</t>
         </is>
       </c>
-      <c r="AJ5" t="inlineStr">
+      <c r="AN5" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AK5" t="inlineStr"/>
-      <c r="AL5" t="inlineStr">
+      <c r="AO5" t="inlineStr"/>
+      <c r="AP5" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
+      <c r="AQ5" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="AN5" t="inlineStr">
+      <c r="AR5" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AO5" t="inlineStr">
+      <c r="AS5" t="inlineStr">
         <is>
           <t>17.54</t>
         </is>
       </c>
-      <c r="AP5" t="n">
+      <c r="AT5" t="n">
         <v>-1.04</v>
       </c>
-      <c r="AQ5" t="n">
+      <c r="AU5" t="n">
         <v>-0.93</v>
       </c>
-      <c r="AR5" t="inlineStr">
+      <c r="AV5" t="inlineStr">
         <is>
           <t>-1.16</t>
         </is>
       </c>
-      <c r="AS5" t="inlineStr">
+      <c r="AW5" t="inlineStr">
         <is>
           <t>-2.39</t>
         </is>
       </c>
-      <c r="AT5" t="inlineStr">
+      <c r="AX5" t="inlineStr">
         <is>
           <t>45.21999999999999</t>
         </is>
       </c>
-      <c r="AU5" t="n">
+      <c r="AY5" t="n">
         <v>45.64</v>
       </c>
-      <c r="AV5" t="n">
+      <c r="AZ5" t="n">
         <v>46.18</v>
       </c>
-      <c r="AW5" t="inlineStr">
+      <c r="BA5" t="inlineStr">
         <is>
           <t>47.31</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
+      <c r="BB5" t="inlineStr">
         <is>
           <t>-14.07</t>
         </is>
       </c>
-      <c r="AY5" t="n">
+      <c r="BC5" t="n">
         <v>-0.31</v>
       </c>
-      <c r="AZ5" t="n">
+      <c r="BD5" t="n">
         <v>-0.27</v>
       </c>
-      <c r="BA5" t="inlineStr">
+      <c r="BE5" t="inlineStr">
         <is>
           <t>4.28</t>
         </is>
       </c>
-      <c r="BB5" t="inlineStr">
+      <c r="BF5" t="inlineStr">
         <is>
           <t>-106.26</t>
         </is>
       </c>
-      <c r="BC5" t="inlineStr">
+      <c r="BG5" t="inlineStr">
         <is>
           <t>2025/11/27</t>
         </is>
       </c>
-      <c r="BD5" t="inlineStr">
+      <c r="BH5" t="inlineStr">
         <is>
           <t>75475.9297752809</t>
         </is>
       </c>
-      <c r="BE5" t="inlineStr">
+      <c r="BI5" t="inlineStr">
         <is>
           <t>21298.0</t>
         </is>
       </c>
-      <c r="BF5" t="n">
+      <c r="BJ5" t="n">
         <v>9270</v>
       </c>
-      <c r="BG5" t="inlineStr">
+      <c r="BK5" t="inlineStr">
         <is>
           <t>6579.4</t>
         </is>
       </c>
-      <c r="BH5" t="n">
+      <c r="BL5" t="n">
         <v>11878.36</v>
       </c>
-      <c r="BI5" t="inlineStr">
+      <c r="BM5" t="inlineStr">
         <is>
           <t>2690</t>
         </is>
       </c>
-      <c r="BJ5" t="inlineStr">
+      <c r="BN5" t="inlineStr">
         <is>
           <t>-814.4929814714977</t>
         </is>
       </c>
-      <c r="BK5" t="inlineStr">
+      <c r="BO5" t="inlineStr">
         <is>
           <t>610.419588440709</t>
         </is>
       </c>
-      <c r="BL5" t="inlineStr">
+      <c r="BP5" t="inlineStr">
         <is>
           <t>21298.0</t>
         </is>
       </c>
-      <c r="BM5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BN5" t="inlineStr">
+      <c r="BQ5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR5" t="inlineStr">
         <is>
           <t>48.75</t>
         </is>
       </c>
-      <c r="BO5" t="inlineStr">
+      <c r="BS5" t="inlineStr">
         <is>
           <t>2025/08/25</t>
         </is>
       </c>
-      <c r="BP5" t="inlineStr">
+      <c r="BT5" t="inlineStr">
         <is>
           <t>-8.21</t>
         </is>
       </c>
-      <c r="BQ5" t="inlineStr">
+      <c r="BU5" t="inlineStr">
         <is>
           <t>岱稜</t>
         </is>
       </c>
-      <c r="BR5" t="inlineStr">
+      <c r="BV5" t="inlineStr">
         <is>
           <t>岱稜</t>
         </is>
       </c>
-      <c r="BS5" t="inlineStr">
+      <c r="BW5" t="inlineStr">
         <is>
           <t>其他電子業</t>
         </is>
       </c>
-      <c r="BT5" t="inlineStr">
+      <c r="BX5" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BU5" t="inlineStr">
+      <c r="BY5" t="inlineStr">
         <is>
           <t>1.03</t>
         </is>
       </c>
-      <c r="BV5" t="inlineStr">
+      <c r="BZ5" t="inlineStr">
         <is>
           <t>-1.004452687200723</t>
         </is>
       </c>
-      <c r="BW5" t="inlineStr">
+      <c r="CA5" t="inlineStr">
         <is>
           <t>11.92388165594906</t>
         </is>
       </c>
-      <c r="BX5" t="inlineStr">
+      <c r="CB5" t="inlineStr">
         <is>
           <t>2.060463205899802</t>
         </is>
       </c>
-      <c r="BY5" t="inlineStr">
+      <c r="CC5" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BZ5" t="inlineStr">
+      <c r="CD5" t="inlineStr">
         <is>
           <t>價-量增</t>
         </is>
       </c>
-      <c r="CA5" t="inlineStr">
+      <c r="CE5" t="inlineStr">
         <is>
           <t>1.81</t>
         </is>
       </c>
-      <c r="CB5" t="inlineStr">
+      <c r="CF5" t="inlineStr">
         <is>
           <t>6.12</t>
         </is>
       </c>
-      <c r="CC5" t="inlineStr">
+      <c r="CG5" t="inlineStr">
         <is>
           <t>8.56</t>
         </is>
       </c>
-      <c r="CD5" t="inlineStr">
+      <c r="CH5" t="inlineStr">
         <is>
           <t>10.2</t>
         </is>
       </c>
-      <c r="CE5" t="inlineStr">
+      <c r="CI5" t="inlineStr">
         <is>
           <t>33.67%</t>
         </is>
       </c>
-      <c r="CF5" t="inlineStr">
+      <c r="CJ5" t="inlineStr">
         <is>
           <t>12.48%</t>
         </is>
       </c>
-      <c r="CG5" t="inlineStr">
+      <c r="CK5" t="inlineStr">
         <is>
           <t>47.76</t>
         </is>
       </c>
-      <c r="CH5" t="inlineStr">
+      <c r="CL5" t="inlineStr">
         <is>
           <t>4253</t>
         </is>
       </c>
-      <c r="CI5" t="inlineStr">
+      <c r="CM5" t="inlineStr">
         <is>
           <t>真空蒸鍍薄膜95.00%、光電材料5.00% (2024年)</t>
         </is>
       </c>
-      <c r="CJ5" t="inlineStr">
+      <c r="CN5" t="inlineStr">
         <is>
           <t>岱稜-其他電子業-上櫃</t>
         </is>
       </c>
-      <c r="CK5" t="inlineStr">
+      <c r="CO5" t="inlineStr">
         <is>
           <t>其他電子業平上櫃</t>
         </is>
       </c>
-      <c r="CL5" t="inlineStr">
+      <c r="CP5" t="inlineStr">
         <is>
           <t>44.55</t>
         </is>
       </c>
-      <c r="CM5" t="inlineStr">
+      <c r="CQ5" t="inlineStr">
         <is>
           <t>45.0</t>
         </is>
       </c>
-      <c r="CN5" t="inlineStr">
+      <c r="CR5" t="inlineStr">
         <is>
           <t>44.3</t>
         </is>
       </c>
-      <c r="CO5" t="inlineStr">
+      <c r="CS5" t="inlineStr">
         <is>
           <t>44.75</t>
         </is>
       </c>
-      <c r="CP5" t="inlineStr">
+      <c r="CT5" t="inlineStr">
         <is>
           <t>24.66</t>
         </is>
       </c>
-      <c r="CQ5" t="inlineStr">
+      <c r="CU5" t="inlineStr">
         <is>
           <t>** 觸控面板 - PET膜** 其他 - 其他電子產品及電子服務產業、其他** 醫療器材 - 塑化材料</t>
         </is>
       </c>
-      <c r="CR5" t="inlineStr">
+      <c r="CV5" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -2896,325 +2996,345 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
+          <t>0.02</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
           <t>2025/10/14</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
+      <c r="AD6" t="inlineStr">
         <is>
           <t>44.35</t>
         </is>
       </c>
-      <c r="AD6" t="inlineStr">
+      <c r="AE6" t="inlineStr">
         <is>
           <t>2025/06/30</t>
         </is>
       </c>
-      <c r="AE6" t="inlineStr">
+      <c r="AF6" t="inlineStr">
         <is>
           <t>48.2</t>
         </is>
       </c>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t>0.02</t>
-        </is>
-      </c>
       <c r="AG6" t="inlineStr">
         <is>
+          <t>2025/12/08</t>
+        </is>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>45.05</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>2025/11/19</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>45.05</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
           <t>2025-12-09</t>
         </is>
       </c>
-      <c r="AH6" t="inlineStr">
+      <c r="AL6" t="inlineStr">
         <is>
           <t>4.05</t>
         </is>
       </c>
-      <c r="AI6" t="inlineStr">
+      <c r="AM6" t="inlineStr">
         <is>
           <t>-1.09</t>
         </is>
       </c>
-      <c r="AJ6" t="inlineStr">
+      <c r="AN6" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AK6" t="inlineStr"/>
-      <c r="AL6" t="inlineStr">
+      <c r="AO6" t="inlineStr"/>
+      <c r="AP6" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
+      <c r="AQ6" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="AN6" t="inlineStr">
+      <c r="AR6" t="inlineStr">
         <is>
           <t>52.63</t>
         </is>
       </c>
-      <c r="AO6" t="inlineStr">
+      <c r="AS6" t="inlineStr">
         <is>
           <t>17.54</t>
         </is>
       </c>
-      <c r="AP6" t="n">
+      <c r="AT6" t="n">
         <v>0.26</v>
       </c>
-      <c r="AQ6" t="n">
+      <c r="AU6" t="n">
         <v>-0.78</v>
       </c>
-      <c r="AR6" t="inlineStr">
+      <c r="AV6" t="inlineStr">
         <is>
           <t>-1.04</t>
         </is>
       </c>
-      <c r="AS6" t="inlineStr">
+      <c r="AW6" t="inlineStr">
         <is>
           <t>-2.32</t>
         </is>
       </c>
-      <c r="AT6" t="inlineStr">
+      <c r="AX6" t="inlineStr">
         <is>
           <t>45.42999999999999</t>
         </is>
       </c>
-      <c r="AU6" t="n">
+      <c r="AY6" t="n">
         <v>45.78</v>
       </c>
-      <c r="AV6" t="n">
+      <c r="AZ6" t="n">
         <v>46.27</v>
       </c>
-      <c r="AW6" t="inlineStr">
+      <c r="BA6" t="inlineStr">
         <is>
           <t>47.37</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
+      <c r="BB6" t="inlineStr">
         <is>
           <t>-0.08</t>
         </is>
       </c>
-      <c r="AY6" t="n">
+      <c r="BC6" t="n">
         <v>-0.26</v>
       </c>
-      <c r="AZ6" t="n">
+      <c r="BD6" t="n">
         <v>-0.26</v>
       </c>
-      <c r="BA6" t="inlineStr">
+      <c r="BE6" t="inlineStr">
         <is>
           <t>4.28</t>
         </is>
       </c>
-      <c r="BB6" t="inlineStr">
+      <c r="BF6" t="inlineStr">
         <is>
           <t>-106.04</t>
         </is>
       </c>
-      <c r="BC6" t="inlineStr">
+      <c r="BG6" t="inlineStr">
         <is>
           <t>2025/11/27</t>
         </is>
       </c>
-      <c r="BD6" t="inlineStr">
+      <c r="BH6" t="inlineStr">
         <is>
           <t>75475.9297752809</t>
         </is>
       </c>
-      <c r="BE6" t="inlineStr">
+      <c r="BI6" t="inlineStr">
         <is>
           <t>4714.0</t>
         </is>
       </c>
-      <c r="BF6" t="n">
+      <c r="BJ6" t="n">
         <v>5622.2</v>
       </c>
-      <c r="BG6" t="inlineStr">
+      <c r="BK6" t="inlineStr">
         <is>
           <t>5124.4</t>
         </is>
       </c>
-      <c r="BH6" t="n">
+      <c r="BL6" t="n">
         <v>11707.74</v>
       </c>
-      <c r="BI6" t="inlineStr">
+      <c r="BM6" t="inlineStr">
         <is>
           <t>497</t>
         </is>
       </c>
-      <c r="BJ6" t="inlineStr">
+      <c r="BN6" t="inlineStr">
         <is>
           <t>-1073.567994182808</t>
         </is>
       </c>
-      <c r="BK6" t="inlineStr">
+      <c r="BO6" t="inlineStr">
         <is>
           <t>-628.6198247361344</t>
         </is>
       </c>
-      <c r="BL6" t="inlineStr">
+      <c r="BP6" t="inlineStr">
         <is>
           <t>4714.0</t>
         </is>
       </c>
-      <c r="BM6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BN6" t="inlineStr">
+      <c r="BQ6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR6" t="inlineStr">
         <is>
           <t>48.75</t>
         </is>
       </c>
-      <c r="BO6" t="inlineStr">
+      <c r="BS6" t="inlineStr">
         <is>
           <t>2025/08/25</t>
         </is>
       </c>
-      <c r="BP6" t="inlineStr">
+      <c r="BT6" t="inlineStr">
         <is>
           <t>-6.56</t>
         </is>
       </c>
-      <c r="BQ6" t="inlineStr">
+      <c r="BU6" t="inlineStr">
         <is>
           <t>岱稜</t>
         </is>
       </c>
-      <c r="BR6" t="inlineStr">
+      <c r="BV6" t="inlineStr">
         <is>
           <t>岱稜</t>
         </is>
       </c>
-      <c r="BS6" t="inlineStr">
+      <c r="BW6" t="inlineStr">
         <is>
           <t>其他電子業</t>
         </is>
       </c>
-      <c r="BT6" t="inlineStr">
+      <c r="BX6" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BU6" t="inlineStr">
+      <c r="BY6" t="inlineStr">
         <is>
           <t>1.03</t>
         </is>
       </c>
-      <c r="BV6" t="inlineStr">
+      <c r="BZ6" t="inlineStr">
         <is>
           <t>-1.004452687200723</t>
         </is>
       </c>
-      <c r="BW6" t="inlineStr">
+      <c r="CA6" t="inlineStr">
         <is>
           <t>11.92388165594906</t>
         </is>
       </c>
-      <c r="BX6" t="inlineStr">
+      <c r="CB6" t="inlineStr">
         <is>
           <t>2.060463205899802</t>
         </is>
       </c>
-      <c r="BY6" t="inlineStr">
+      <c r="CC6" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BZ6" t="inlineStr">
+      <c r="CD6" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="CA6" t="inlineStr">
+      <c r="CE6" t="inlineStr">
         <is>
           <t>1.85</t>
         </is>
       </c>
-      <c r="CB6" t="inlineStr">
+      <c r="CF6" t="inlineStr">
         <is>
           <t>6.12</t>
         </is>
       </c>
-      <c r="CC6" t="inlineStr">
+      <c r="CG6" t="inlineStr">
         <is>
           <t>8.56</t>
         </is>
       </c>
-      <c r="CD6" t="inlineStr">
+      <c r="CH6" t="inlineStr">
         <is>
           <t>10.2</t>
         </is>
       </c>
-      <c r="CE6" t="inlineStr">
+      <c r="CI6" t="inlineStr">
         <is>
           <t>33.67%</t>
         </is>
       </c>
-      <c r="CF6" t="inlineStr">
+      <c r="CJ6" t="inlineStr">
         <is>
           <t>12.48%</t>
         </is>
       </c>
-      <c r="CG6" t="inlineStr">
+      <c r="CK6" t="inlineStr">
         <is>
           <t>47.76</t>
         </is>
       </c>
-      <c r="CH6" t="inlineStr">
+      <c r="CL6" t="inlineStr">
         <is>
           <t>4253</t>
         </is>
       </c>
-      <c r="CI6" t="inlineStr">
+      <c r="CM6" t="inlineStr">
         <is>
           <t>真空蒸鍍薄膜95.00%、光電材料5.00% (2024年)</t>
         </is>
       </c>
-      <c r="CJ6" t="inlineStr">
+      <c r="CN6" t="inlineStr">
         <is>
           <t>岱稜-其他電子業-上櫃</t>
         </is>
       </c>
-      <c r="CK6" t="inlineStr">
+      <c r="CO6" t="inlineStr">
         <is>
           <t>其他電子業平上櫃</t>
         </is>
       </c>
-      <c r="CL6" t="inlineStr">
+      <c r="CP6" t="inlineStr">
         <is>
           <t>45.65</t>
         </is>
       </c>
-      <c r="CM6" t="inlineStr">
+      <c r="CQ6" t="inlineStr">
         <is>
           <t>46.3</t>
         </is>
       </c>
-      <c r="CN6" t="inlineStr">
+      <c r="CR6" t="inlineStr">
         <is>
           <t>45.3</t>
         </is>
       </c>
-      <c r="CO6" t="inlineStr">
+      <c r="CS6" t="inlineStr">
         <is>
           <t>45.55</t>
         </is>
       </c>
-      <c r="CP6" t="inlineStr">
+      <c r="CT6" t="inlineStr">
         <is>
           <t>24.66</t>
         </is>
       </c>
-      <c r="CQ6" t="inlineStr">
+      <c r="CU6" t="inlineStr">
         <is>
           <t>** 觸控面板 - PET膜** 其他 - 其他電子產品及電子服務產業、其他** 醫療器材 - 塑化材料</t>
         </is>
       </c>
-      <c r="CR6" t="inlineStr">
+      <c r="CV6" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -3358,325 +3478,345 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
+          <t>-0.03</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
           <t>2025/10/14</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
+      <c r="AD7" t="inlineStr">
         <is>
           <t>44.35</t>
         </is>
       </c>
-      <c r="AD7" t="inlineStr">
+      <c r="AE7" t="inlineStr">
         <is>
           <t>2025/06/30</t>
         </is>
       </c>
-      <c r="AE7" t="inlineStr">
+      <c r="AF7" t="inlineStr">
         <is>
           <t>48.2</t>
         </is>
       </c>
-      <c r="AF7" t="inlineStr">
-        <is>
-          <t>-0.03</t>
-        </is>
-      </c>
       <c r="AG7" t="inlineStr">
         <is>
+          <t>2025/12/08</t>
+        </is>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>45.05</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>2025/11/19</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>45.05</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
           <t>2025-12-08</t>
         </is>
       </c>
-      <c r="AH7" t="inlineStr">
+      <c r="AL7" t="inlineStr">
         <is>
           <t>9.67</t>
         </is>
       </c>
-      <c r="AI7" t="inlineStr">
+      <c r="AM7" t="inlineStr">
         <is>
           <t>0.35</t>
         </is>
       </c>
-      <c r="AJ7" t="inlineStr">
+      <c r="AN7" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AK7" t="inlineStr"/>
-      <c r="AL7" t="inlineStr">
+      <c r="AO7" t="inlineStr"/>
+      <c r="AP7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
+      <c r="AQ7" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="AN7" t="inlineStr">
+      <c r="AR7" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AO7" t="inlineStr">
+      <c r="AS7" t="inlineStr">
         <is>
           <t>9.52</t>
         </is>
       </c>
-      <c r="AP7" t="n">
+      <c r="AT7" t="n">
         <v>-0.95</v>
       </c>
-      <c r="AQ7" t="n">
+      <c r="AU7" t="n">
         <v>-0.87</v>
       </c>
-      <c r="AR7" t="inlineStr">
+      <c r="AV7" t="inlineStr">
         <is>
           <t>-0.97</t>
         </is>
       </c>
-      <c r="AS7" t="inlineStr">
+      <c r="AW7" t="inlineStr">
         <is>
           <t>-2.29</t>
         </is>
       </c>
-      <c r="AT7" t="inlineStr">
+      <c r="AX7" t="inlineStr">
         <is>
           <t>45.48</t>
         </is>
       </c>
-      <c r="AU7" t="n">
+      <c r="AY7" t="n">
         <v>45.88</v>
       </c>
-      <c r="AV7" t="n">
+      <c r="AZ7" t="n">
         <v>46.32</v>
       </c>
-      <c r="AW7" t="inlineStr">
+      <c r="BA7" t="inlineStr">
         <is>
           <t>47.41</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
+      <c r="BB7" t="inlineStr">
         <is>
           <t>-7.02</t>
         </is>
       </c>
-      <c r="AY7" t="n">
+      <c r="BC7" t="n">
         <v>-0.28</v>
       </c>
-      <c r="AZ7" t="n">
+      <c r="BD7" t="n">
         <v>-0.26</v>
       </c>
-      <c r="BA7" t="inlineStr">
+      <c r="BE7" t="inlineStr">
         <is>
           <t>4.28</t>
         </is>
       </c>
-      <c r="BB7" t="inlineStr">
+      <c r="BF7" t="inlineStr">
         <is>
           <t>-106.04</t>
         </is>
       </c>
-      <c r="BC7" t="inlineStr">
+      <c r="BG7" t="inlineStr">
         <is>
           <t>2025/11/27</t>
         </is>
       </c>
-      <c r="BD7" t="inlineStr">
+      <c r="BH7" t="inlineStr">
         <is>
           <t>75475.9297752809</t>
         </is>
       </c>
-      <c r="BE7" t="inlineStr">
+      <c r="BI7" t="inlineStr">
         <is>
           <t>11034.0</t>
         </is>
       </c>
-      <c r="BF7" t="n">
+      <c r="BJ7" t="n">
         <v>5441.2</v>
       </c>
-      <c r="BG7" t="inlineStr">
+      <c r="BK7" t="inlineStr">
         <is>
           <t>5022.6</t>
         </is>
       </c>
-      <c r="BH7" t="n">
+      <c r="BL7" t="n">
         <v>11858.6</v>
       </c>
-      <c r="BI7" t="inlineStr">
+      <c r="BM7" t="inlineStr">
         <is>
           <t>418</t>
         </is>
       </c>
-      <c r="BJ7" t="inlineStr">
+      <c r="BN7" t="inlineStr">
         <is>
           <t>-1154.46766135493</t>
         </is>
       </c>
-      <c r="BK7" t="inlineStr">
+      <c r="BO7" t="inlineStr">
         <is>
           <t>-599.3682783910481</t>
         </is>
       </c>
-      <c r="BL7" t="inlineStr">
+      <c r="BP7" t="inlineStr">
         <is>
           <t>11034.0</t>
         </is>
       </c>
-      <c r="BM7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BN7" t="inlineStr">
+      <c r="BQ7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR7" t="inlineStr">
         <is>
           <t>48.75</t>
         </is>
       </c>
-      <c r="BO7" t="inlineStr">
+      <c r="BS7" t="inlineStr">
         <is>
           <t>2025/08/25</t>
         </is>
       </c>
-      <c r="BP7" t="inlineStr">
+      <c r="BT7" t="inlineStr">
         <is>
           <t>-7.59</t>
         </is>
       </c>
-      <c r="BQ7" t="inlineStr">
+      <c r="BU7" t="inlineStr">
         <is>
           <t>岱稜</t>
         </is>
       </c>
-      <c r="BR7" t="inlineStr">
+      <c r="BV7" t="inlineStr">
         <is>
           <t>岱稜</t>
         </is>
       </c>
-      <c r="BS7" t="inlineStr">
+      <c r="BW7" t="inlineStr">
         <is>
           <t>其他電子業</t>
         </is>
       </c>
-      <c r="BT7" t="inlineStr">
+      <c r="BX7" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BU7" t="inlineStr">
+      <c r="BY7" t="inlineStr">
         <is>
           <t>1.03</t>
         </is>
       </c>
-      <c r="BV7" t="inlineStr">
+      <c r="BZ7" t="inlineStr">
         <is>
           <t>-1.004452687200723</t>
         </is>
       </c>
-      <c r="BW7" t="inlineStr">
+      <c r="CA7" t="inlineStr">
         <is>
           <t>11.92388165594906</t>
         </is>
       </c>
-      <c r="BX7" t="inlineStr">
+      <c r="CB7" t="inlineStr">
         <is>
           <t>2.060463205899802</t>
         </is>
       </c>
-      <c r="BY7" t="inlineStr">
+      <c r="CC7" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
-      <c r="BZ7" t="inlineStr">
+      <c r="CD7" t="inlineStr">
         <is>
           <t>價-量增</t>
         </is>
       </c>
-      <c r="CA7" t="inlineStr">
+      <c r="CE7" t="inlineStr">
         <is>
           <t>1.83</t>
         </is>
       </c>
-      <c r="CB7" t="inlineStr">
+      <c r="CF7" t="inlineStr">
         <is>
           <t>6.12</t>
         </is>
       </c>
-      <c r="CC7" t="inlineStr">
+      <c r="CG7" t="inlineStr">
         <is>
           <t>8.56</t>
         </is>
       </c>
-      <c r="CD7" t="inlineStr">
+      <c r="CH7" t="inlineStr">
         <is>
           <t>10.2</t>
         </is>
       </c>
-      <c r="CE7" t="inlineStr">
+      <c r="CI7" t="inlineStr">
         <is>
           <t>33.67%</t>
         </is>
       </c>
-      <c r="CF7" t="inlineStr">
+      <c r="CJ7" t="inlineStr">
         <is>
           <t>12.48%</t>
         </is>
       </c>
-      <c r="CG7" t="inlineStr">
+      <c r="CK7" t="inlineStr">
         <is>
           <t>47.76</t>
         </is>
       </c>
-      <c r="CH7" t="inlineStr">
+      <c r="CL7" t="inlineStr">
         <is>
           <t>4253</t>
         </is>
       </c>
-      <c r="CI7" t="inlineStr">
+      <c r="CM7" t="inlineStr">
         <is>
           <t>真空蒸鍍薄膜95.00%、光電材料5.00% (2024年)</t>
         </is>
       </c>
-      <c r="CJ7" t="inlineStr">
+      <c r="CN7" t="inlineStr">
         <is>
           <t>岱稜-其他電子業-上櫃</t>
         </is>
       </c>
-      <c r="CK7" t="inlineStr">
+      <c r="CO7" t="inlineStr">
         <is>
           <t>其他電子業平上櫃</t>
         </is>
       </c>
-      <c r="CL7" t="inlineStr">
+      <c r="CP7" t="inlineStr">
         <is>
           <t>45.25</t>
         </is>
       </c>
-      <c r="CM7" t="inlineStr">
+      <c r="CQ7" t="inlineStr">
         <is>
           <t>45.45</t>
         </is>
       </c>
-      <c r="CN7" t="inlineStr">
+      <c r="CR7" t="inlineStr">
         <is>
           <t>44.5</t>
         </is>
       </c>
-      <c r="CO7" t="inlineStr">
+      <c r="CS7" t="inlineStr">
         <is>
           <t>45.05</t>
         </is>
       </c>
-      <c r="CP7" t="inlineStr">
+      <c r="CT7" t="inlineStr">
         <is>
           <t>24.66</t>
         </is>
       </c>
-      <c r="CQ7" t="inlineStr">
+      <c r="CU7" t="inlineStr">
         <is>
           <t>** 觸控面板 - PET膜** 其他 - 其他電子產品及電子服務產業、其他** 醫療器材 - 塑化材料</t>
         </is>
       </c>
-      <c r="CR7" t="inlineStr">
+      <c r="CV7" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -3820,325 +3960,345 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
+          <t>-0.03</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
           <t>2025/10/14</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
+      <c r="AD8" t="inlineStr">
         <is>
           <t>44.35</t>
         </is>
       </c>
-      <c r="AD8" t="inlineStr">
+      <c r="AE8" t="inlineStr">
         <is>
           <t>2025/06/30</t>
         </is>
       </c>
-      <c r="AE8" t="inlineStr">
+      <c r="AF8" t="inlineStr">
         <is>
           <t>48.2</t>
         </is>
       </c>
-      <c r="AF8" t="inlineStr">
-        <is>
-          <t>-0.03</t>
-        </is>
-      </c>
       <c r="AG8" t="inlineStr">
         <is>
+          <t>2025/12/08</t>
+        </is>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>45.05</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>2025/11/19</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>45.05</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
           <t>2025-12-05</t>
         </is>
       </c>
-      <c r="AH8" t="inlineStr">
+      <c r="AL8" t="inlineStr">
         <is>
           <t>4.09</t>
         </is>
       </c>
-      <c r="AI8" t="inlineStr">
+      <c r="AM8" t="inlineStr">
         <is>
           <t>0.23</t>
         </is>
       </c>
-      <c r="AJ8" t="inlineStr">
+      <c r="AN8" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AK8" t="inlineStr"/>
-      <c r="AL8" t="inlineStr">
+      <c r="AO8" t="inlineStr"/>
+      <c r="AP8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
+      <c r="AQ8" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="AN8" t="inlineStr">
+      <c r="AR8" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AO8" t="inlineStr">
+      <c r="AS8" t="inlineStr">
         <is>
           <t>37.52</t>
         </is>
       </c>
-      <c r="AP8" t="n">
+      <c r="AT8" t="n">
         <v>-0.83</v>
       </c>
-      <c r="AQ8" t="n">
+      <c r="AU8" t="n">
         <v>-0.75</v>
       </c>
-      <c r="AR8" t="inlineStr">
+      <c r="AV8" t="inlineStr">
         <is>
           <t>-0.9</t>
         </is>
       </c>
-      <c r="AS8" t="inlineStr">
+      <c r="AW8" t="inlineStr">
         <is>
           <t>-2.24</t>
         </is>
       </c>
-      <c r="AT8" t="inlineStr">
+      <c r="AX8" t="inlineStr">
         <is>
           <t>45.63</t>
         </is>
       </c>
-      <c r="AU8" t="n">
+      <c r="AY8" t="n">
         <v>45.98</v>
       </c>
-      <c r="AV8" t="n">
+      <c r="AZ8" t="n">
         <v>46.39</v>
       </c>
-      <c r="AW8" t="inlineStr">
+      <c r="BA8" t="inlineStr">
         <is>
           <t>47.46</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
+      <c r="BB8" t="inlineStr">
         <is>
           <t>3.73</t>
         </is>
       </c>
-      <c r="AY8" t="n">
+      <c r="BC8" t="n">
         <v>-0.24</v>
       </c>
-      <c r="AZ8" t="n">
+      <c r="BD8" t="n">
         <v>-0.25</v>
       </c>
-      <c r="BA8" t="inlineStr">
+      <c r="BE8" t="inlineStr">
         <is>
           <t>4.28</t>
         </is>
       </c>
-      <c r="BB8" t="inlineStr">
+      <c r="BF8" t="inlineStr">
         <is>
           <t>-105.93</t>
         </is>
       </c>
-      <c r="BC8" t="inlineStr">
+      <c r="BG8" t="inlineStr">
         <is>
           <t>2025/11/27</t>
         </is>
       </c>
-      <c r="BD8" t="inlineStr">
+      <c r="BH8" t="inlineStr">
         <is>
           <t>75475.9297752809</t>
         </is>
       </c>
-      <c r="BE8" t="inlineStr">
+      <c r="BI8" t="inlineStr">
         <is>
           <t>4714.0</t>
         </is>
       </c>
-      <c r="BF8" t="n">
+      <c r="BJ8" t="n">
         <v>3990.2</v>
       </c>
-      <c r="BG8" t="inlineStr">
+      <c r="BK8" t="inlineStr">
         <is>
           <t>4360.0</t>
         </is>
       </c>
-      <c r="BH8" t="n">
+      <c r="BL8" t="n">
         <v>11948.92</v>
       </c>
-      <c r="BI8" t="inlineStr">
+      <c r="BM8" t="inlineStr">
         <is>
           <t>-369</t>
         </is>
       </c>
-      <c r="BJ8" t="inlineStr">
+      <c r="BN8" t="inlineStr">
         <is>
           <t>-1255.394821893818</t>
         </is>
       </c>
-      <c r="BK8" t="inlineStr">
+      <c r="BO8" t="inlineStr">
         <is>
           <t>-1213.317202241243</t>
         </is>
       </c>
-      <c r="BL8" t="inlineStr">
+      <c r="BP8" t="inlineStr">
         <is>
           <t>4714.0</t>
         </is>
       </c>
-      <c r="BM8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BN8" t="inlineStr">
+      <c r="BQ8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR8" t="inlineStr">
         <is>
           <t>48.75</t>
         </is>
       </c>
-      <c r="BO8" t="inlineStr">
+      <c r="BS8" t="inlineStr">
         <is>
           <t>2025/08/25</t>
         </is>
       </c>
-      <c r="BP8" t="inlineStr">
+      <c r="BT8" t="inlineStr">
         <is>
           <t>-7.18</t>
         </is>
       </c>
-      <c r="BQ8" t="inlineStr">
+      <c r="BU8" t="inlineStr">
         <is>
           <t>岱稜</t>
         </is>
       </c>
-      <c r="BR8" t="inlineStr">
+      <c r="BV8" t="inlineStr">
         <is>
           <t>岱稜</t>
         </is>
       </c>
-      <c r="BS8" t="inlineStr">
+      <c r="BW8" t="inlineStr">
         <is>
           <t>其他電子業</t>
         </is>
       </c>
-      <c r="BT8" t="inlineStr">
+      <c r="BX8" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BU8" t="inlineStr">
+      <c r="BY8" t="inlineStr">
         <is>
           <t>1.03</t>
         </is>
       </c>
-      <c r="BV8" t="inlineStr">
+      <c r="BZ8" t="inlineStr">
         <is>
           <t>-1.004452687200723</t>
         </is>
       </c>
-      <c r="BW8" t="inlineStr">
+      <c r="CA8" t="inlineStr">
         <is>
           <t>11.92388165594906</t>
         </is>
       </c>
-      <c r="BX8" t="inlineStr">
+      <c r="CB8" t="inlineStr">
         <is>
           <t>2.060463205899802</t>
         </is>
       </c>
-      <c r="BY8" t="inlineStr">
+      <c r="CC8" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BZ8" t="inlineStr">
+      <c r="CD8" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="CA8" t="inlineStr">
+      <c r="CE8" t="inlineStr">
         <is>
           <t>1.83</t>
         </is>
       </c>
-      <c r="CB8" t="inlineStr">
+      <c r="CF8" t="inlineStr">
         <is>
           <t>6.12</t>
         </is>
       </c>
-      <c r="CC8" t="inlineStr">
+      <c r="CG8" t="inlineStr">
         <is>
           <t>8.56</t>
         </is>
       </c>
-      <c r="CD8" t="inlineStr">
+      <c r="CH8" t="inlineStr">
         <is>
           <t>10.2</t>
         </is>
       </c>
-      <c r="CE8" t="inlineStr">
+      <c r="CI8" t="inlineStr">
         <is>
           <t>33.67%</t>
         </is>
       </c>
-      <c r="CF8" t="inlineStr">
+      <c r="CJ8" t="inlineStr">
         <is>
           <t>12.48%</t>
         </is>
       </c>
-      <c r="CG8" t="inlineStr">
+      <c r="CK8" t="inlineStr">
         <is>
           <t>47.76</t>
         </is>
       </c>
-      <c r="CH8" t="inlineStr">
+      <c r="CL8" t="inlineStr">
         <is>
           <t>4253</t>
         </is>
       </c>
-      <c r="CI8" t="inlineStr">
+      <c r="CM8" t="inlineStr">
         <is>
           <t>真空蒸鍍薄膜95.00%、光電材料5.00% (2024年)</t>
         </is>
       </c>
-      <c r="CJ8" t="inlineStr">
+      <c r="CN8" t="inlineStr">
         <is>
           <t>岱稜-其他電子業-上櫃</t>
         </is>
       </c>
-      <c r="CK8" t="inlineStr">
+      <c r="CO8" t="inlineStr">
         <is>
           <t>其他電子業平上櫃</t>
         </is>
       </c>
-      <c r="CL8" t="inlineStr">
+      <c r="CP8" t="inlineStr">
         <is>
           <t>45.5</t>
         </is>
       </c>
-      <c r="CM8" t="inlineStr">
+      <c r="CQ8" t="inlineStr">
         <is>
           <t>45.5</t>
         </is>
       </c>
-      <c r="CN8" t="inlineStr">
+      <c r="CR8" t="inlineStr">
         <is>
           <t>44.9</t>
         </is>
       </c>
-      <c r="CO8" t="inlineStr">
+      <c r="CS8" t="inlineStr">
         <is>
           <t>45.25</t>
         </is>
       </c>
-      <c r="CP8" t="inlineStr">
+      <c r="CT8" t="inlineStr">
         <is>
           <t>24.66</t>
         </is>
       </c>
-      <c r="CQ8" t="inlineStr">
+      <c r="CU8" t="inlineStr">
         <is>
           <t>** 觸控面板 - PET膜** 其他 - 其他電子產品及電子服務產業、其他** 醫療器材 - 塑化材料</t>
         </is>
       </c>
-      <c r="CR8" t="inlineStr">
+      <c r="CV8" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -4282,325 +4442,345 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
+          <t>-0.02</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
           <t>2025/10/14</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
+      <c r="AD9" t="inlineStr">
         <is>
           <t>44.35</t>
         </is>
       </c>
-      <c r="AD9" t="inlineStr">
+      <c r="AE9" t="inlineStr">
         <is>
           <t>2025/06/30</t>
         </is>
       </c>
-      <c r="AE9" t="inlineStr">
+      <c r="AF9" t="inlineStr">
         <is>
           <t>48.2</t>
         </is>
       </c>
-      <c r="AF9" t="inlineStr">
-        <is>
-          <t>-0.02</t>
-        </is>
-      </c>
       <c r="AG9" t="inlineStr">
         <is>
+          <t>2025/12/08</t>
+        </is>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>45.05</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>2025/11/19</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>45.05</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
           <t>2025-12-04</t>
         </is>
       </c>
-      <c r="AH9" t="inlineStr">
+      <c r="AL9" t="inlineStr">
         <is>
           <t>3.97</t>
         </is>
       </c>
-      <c r="AI9" t="inlineStr">
+      <c r="AM9" t="inlineStr">
         <is>
           <t>-0.43</t>
         </is>
       </c>
-      <c r="AJ9" t="inlineStr">
+      <c r="AN9" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AK9" t="inlineStr"/>
-      <c r="AL9" t="inlineStr">
+      <c r="AO9" t="inlineStr"/>
+      <c r="AP9" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
+      <c r="AQ9" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="AN9" t="inlineStr">
+      <c r="AR9" t="inlineStr">
         <is>
           <t>28.57</t>
         </is>
       </c>
-      <c r="AO9" t="inlineStr">
+      <c r="AS9" t="inlineStr">
         <is>
           <t>65.52</t>
         </is>
       </c>
-      <c r="AP9" t="n">
+      <c r="AT9" t="n">
         <v>-0.61</v>
       </c>
-      <c r="AQ9" t="n">
+      <c r="AU9" t="n">
         <v>-0.58</v>
       </c>
-      <c r="AR9" t="inlineStr">
+      <c r="AV9" t="inlineStr">
         <is>
           <t>-0.89</t>
         </is>
       </c>
-      <c r="AS9" t="inlineStr">
+      <c r="AW9" t="inlineStr">
         <is>
           <t>-2.14</t>
         </is>
       </c>
-      <c r="AT9" t="inlineStr">
+      <c r="AX9" t="inlineStr">
         <is>
           <t>45.77999999999999</t>
         </is>
       </c>
-      <c r="AU9" t="n">
+      <c r="AY9" t="n">
         <v>46.04</v>
       </c>
-      <c r="AV9" t="n">
+      <c r="AZ9" t="n">
         <v>46.46</v>
       </c>
-      <c r="AW9" t="inlineStr">
+      <c r="BA9" t="inlineStr">
         <is>
           <t>47.48</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
+      <c r="BB9" t="inlineStr">
         <is>
           <t>14.06</t>
         </is>
       </c>
-      <c r="AY9" t="n">
+      <c r="BC9" t="n">
         <v>-0.22</v>
       </c>
-      <c r="AZ9" t="n">
+      <c r="BD9" t="n">
         <v>-0.26</v>
       </c>
-      <c r="BA9" t="inlineStr">
+      <c r="BE9" t="inlineStr">
         <is>
           <t>4.28</t>
         </is>
       </c>
-      <c r="BB9" t="inlineStr">
+      <c r="BF9" t="inlineStr">
         <is>
           <t>-105.99</t>
         </is>
       </c>
-      <c r="BC9" t="inlineStr">
+      <c r="BG9" t="inlineStr">
         <is>
           <t>2025/11/27</t>
         </is>
       </c>
-      <c r="BD9" t="inlineStr">
+      <c r="BH9" t="inlineStr">
         <is>
           <t>75475.9297752809</t>
         </is>
       </c>
-      <c r="BE9" t="inlineStr">
+      <c r="BI9" t="inlineStr">
         <is>
           <t>4590.0</t>
         </is>
       </c>
-      <c r="BF9" t="n">
+      <c r="BJ9" t="n">
         <v>3743.4</v>
       </c>
-      <c r="BG9" t="inlineStr">
+      <c r="BK9" t="inlineStr">
         <is>
           <t>4681.2</t>
         </is>
       </c>
-      <c r="BH9" t="n">
+      <c r="BL9" t="n">
         <v>12007.9</v>
       </c>
-      <c r="BI9" t="inlineStr">
+      <c r="BM9" t="inlineStr">
         <is>
           <t>-937</t>
         </is>
       </c>
-      <c r="BJ9" t="inlineStr">
+      <c r="BN9" t="inlineStr">
         <is>
           <t>-1263.045298194286</t>
         </is>
       </c>
-      <c r="BK9" t="inlineStr">
+      <c r="BO9" t="inlineStr">
         <is>
           <t>-1369.911479090048</t>
         </is>
       </c>
-      <c r="BL9" t="inlineStr">
+      <c r="BP9" t="inlineStr">
         <is>
           <t>4590.0</t>
         </is>
       </c>
-      <c r="BM9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BN9" t="inlineStr">
+      <c r="BQ9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR9" t="inlineStr">
         <is>
           <t>48.75</t>
         </is>
       </c>
-      <c r="BO9" t="inlineStr">
+      <c r="BS9" t="inlineStr">
         <is>
           <t>2025/08/25</t>
         </is>
       </c>
-      <c r="BP9" t="inlineStr">
+      <c r="BT9" t="inlineStr">
         <is>
           <t>-6.67</t>
         </is>
       </c>
-      <c r="BQ9" t="inlineStr">
+      <c r="BU9" t="inlineStr">
         <is>
           <t>岱稜</t>
         </is>
       </c>
-      <c r="BR9" t="inlineStr">
+      <c r="BV9" t="inlineStr">
         <is>
           <t>岱稜</t>
         </is>
       </c>
-      <c r="BS9" t="inlineStr">
+      <c r="BW9" t="inlineStr">
         <is>
           <t>其他電子業</t>
         </is>
       </c>
-      <c r="BT9" t="inlineStr">
+      <c r="BX9" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BU9" t="inlineStr">
+      <c r="BY9" t="inlineStr">
         <is>
           <t>1.03</t>
         </is>
       </c>
-      <c r="BV9" t="inlineStr">
+      <c r="BZ9" t="inlineStr">
         <is>
           <t>-1.004452687200723</t>
         </is>
       </c>
-      <c r="BW9" t="inlineStr">
+      <c r="CA9" t="inlineStr">
         <is>
           <t>11.92388165594906</t>
         </is>
       </c>
-      <c r="BX9" t="inlineStr">
+      <c r="CB9" t="inlineStr">
         <is>
           <t>2.060463205899802</t>
         </is>
       </c>
-      <c r="BY9" t="inlineStr">
+      <c r="CC9" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BZ9" t="inlineStr">
+      <c r="CD9" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="CA9" t="inlineStr">
+      <c r="CE9" t="inlineStr">
         <is>
           <t>1.85</t>
         </is>
       </c>
-      <c r="CB9" t="inlineStr">
+      <c r="CF9" t="inlineStr">
         <is>
           <t>6.12</t>
         </is>
       </c>
-      <c r="CC9" t="inlineStr">
+      <c r="CG9" t="inlineStr">
         <is>
           <t>8.56</t>
         </is>
       </c>
-      <c r="CD9" t="inlineStr">
+      <c r="CH9" t="inlineStr">
         <is>
           <t>10.2</t>
         </is>
       </c>
-      <c r="CE9" t="inlineStr">
+      <c r="CI9" t="inlineStr">
         <is>
           <t>33.67%</t>
         </is>
       </c>
-      <c r="CF9" t="inlineStr">
+      <c r="CJ9" t="inlineStr">
         <is>
           <t>12.48%</t>
         </is>
       </c>
-      <c r="CG9" t="inlineStr">
+      <c r="CK9" t="inlineStr">
         <is>
           <t>47.76</t>
         </is>
       </c>
-      <c r="CH9" t="inlineStr">
+      <c r="CL9" t="inlineStr">
         <is>
           <t>4253</t>
         </is>
       </c>
-      <c r="CI9" t="inlineStr">
+      <c r="CM9" t="inlineStr">
         <is>
           <t>真空蒸鍍薄膜95.00%、光電材料5.00% (2024年)</t>
         </is>
       </c>
-      <c r="CJ9" t="inlineStr">
+      <c r="CN9" t="inlineStr">
         <is>
           <t>岱稜-其他電子業-上櫃</t>
         </is>
       </c>
-      <c r="CK9" t="inlineStr">
+      <c r="CO9" t="inlineStr">
         <is>
           <t>其他電子業平上櫃</t>
         </is>
       </c>
-      <c r="CL9" t="inlineStr">
+      <c r="CP9" t="inlineStr">
         <is>
           <t>46.0</t>
         </is>
       </c>
-      <c r="CM9" t="inlineStr">
+      <c r="CQ9" t="inlineStr">
         <is>
           <t>46.05</t>
         </is>
       </c>
-      <c r="CN9" t="inlineStr">
+      <c r="CR9" t="inlineStr">
         <is>
           <t>45.15</t>
         </is>
       </c>
-      <c r="CO9" t="inlineStr">
+      <c r="CS9" t="inlineStr">
         <is>
           <t>45.5</t>
         </is>
       </c>
-      <c r="CP9" t="inlineStr">
+      <c r="CT9" t="inlineStr">
         <is>
           <t>24.66</t>
         </is>
       </c>
-      <c r="CQ9" t="inlineStr">
+      <c r="CU9" t="inlineStr">
         <is>
           <t>** 觸控面板 - PET膜** 其他 - 其他電子產品及電子服務產業、其他** 醫療器材 - 塑化材料</t>
         </is>
       </c>
-      <c r="CR9" t="inlineStr">
+      <c r="CV9" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -4744,325 +4924,345 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
           <t>2025/10/14</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
+      <c r="AD10" t="inlineStr">
         <is>
           <t>44.35</t>
         </is>
       </c>
-      <c r="AD10" t="inlineStr">
+      <c r="AE10" t="inlineStr">
         <is>
           <t>2025/06/30</t>
         </is>
       </c>
-      <c r="AE10" t="inlineStr">
+      <c r="AF10" t="inlineStr">
         <is>
           <t>48.2</t>
         </is>
       </c>
-      <c r="AF10" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="AG10" t="inlineStr">
         <is>
+          <t>2025/12/08</t>
+        </is>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>45.05</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>2025/11/19</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>45.05</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
           <t>2025-12-03</t>
         </is>
       </c>
-      <c r="AH10" t="inlineStr">
+      <c r="AL10" t="inlineStr">
         <is>
           <t>2.63</t>
         </is>
       </c>
-      <c r="AI10" t="inlineStr">
+      <c r="AM10" t="inlineStr">
         <is>
           <t>-0.22</t>
         </is>
       </c>
-      <c r="AJ10" t="inlineStr">
+      <c r="AN10" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AK10" t="inlineStr"/>
-      <c r="AL10" t="inlineStr">
+      <c r="AO10" t="inlineStr"/>
+      <c r="AP10" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
+      <c r="AQ10" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="AN10" t="inlineStr">
+      <c r="AR10" t="inlineStr">
         <is>
           <t>84.0</t>
         </is>
       </c>
-      <c r="AO10" t="inlineStr">
+      <c r="AS10" t="inlineStr">
         <is>
           <t>84.0</t>
         </is>
       </c>
-      <c r="AP10" t="n">
+      <c r="AT10" t="n">
         <v>-0.17</v>
       </c>
-      <c r="AQ10" t="n">
+      <c r="AU10" t="n">
         <v>-0.52</v>
       </c>
-      <c r="AR10" t="inlineStr">
+      <c r="AV10" t="inlineStr">
         <is>
           <t>-0.87</t>
         </is>
       </c>
-      <c r="AS10" t="inlineStr">
+      <c r="AW10" t="inlineStr">
         <is>
           <t>-2.06</t>
         </is>
       </c>
-      <c r="AT10" t="inlineStr">
+      <c r="AX10" t="inlineStr">
         <is>
           <t>45.88</t>
         </is>
       </c>
-      <c r="AU10" t="n">
+      <c r="AY10" t="n">
         <v>46.12</v>
       </c>
-      <c r="AV10" t="n">
+      <c r="AZ10" t="n">
         <v>46.52</v>
       </c>
-      <c r="AW10" t="inlineStr">
+      <c r="BA10" t="inlineStr">
         <is>
           <t>47.5</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
+      <c r="BB10" t="inlineStr">
         <is>
           <t>20.22</t>
         </is>
       </c>
-      <c r="AY10" t="n">
+      <c r="BC10" t="n">
         <v>-0.21</v>
       </c>
-      <c r="AZ10" t="n">
+      <c r="BD10" t="n">
         <v>-0.26</v>
       </c>
-      <c r="BA10" t="inlineStr">
+      <c r="BE10" t="inlineStr">
         <is>
           <t>4.28</t>
         </is>
       </c>
-      <c r="BB10" t="inlineStr">
+      <c r="BF10" t="inlineStr">
         <is>
           <t>-106.20</t>
         </is>
       </c>
-      <c r="BC10" t="inlineStr">
+      <c r="BG10" t="inlineStr">
         <is>
           <t>2025/11/27</t>
         </is>
       </c>
-      <c r="BD10" t="inlineStr">
+      <c r="BH10" t="inlineStr">
         <is>
           <t>75475.9297752809</t>
         </is>
       </c>
-      <c r="BE10" t="inlineStr">
+      <c r="BI10" t="inlineStr">
         <is>
           <t>3059.0</t>
         </is>
       </c>
-      <c r="BF10" t="n">
+      <c r="BJ10" t="n">
         <v>3888.8</v>
       </c>
-      <c r="BG10" t="inlineStr">
+      <c r="BK10" t="inlineStr">
         <is>
           <t>4542.6</t>
         </is>
       </c>
-      <c r="BH10" t="n">
+      <c r="BL10" t="n">
         <v>12062.18</v>
       </c>
-      <c r="BI10" t="inlineStr">
+      <c r="BM10" t="inlineStr">
         <is>
           <t>-653</t>
         </is>
       </c>
-      <c r="BJ10" t="inlineStr">
+      <c r="BN10" t="inlineStr">
         <is>
           <t>-1243.615083485966</t>
         </is>
       </c>
-      <c r="BK10" t="inlineStr">
+      <c r="BO10" t="inlineStr">
         <is>
           <t>-1531.406464620841</t>
         </is>
       </c>
-      <c r="BL10" t="inlineStr">
+      <c r="BP10" t="inlineStr">
         <is>
           <t>3059.0</t>
         </is>
       </c>
-      <c r="BM10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BN10" t="inlineStr">
+      <c r="BQ10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR10" t="inlineStr">
         <is>
           <t>48.75</t>
         </is>
       </c>
-      <c r="BO10" t="inlineStr">
+      <c r="BS10" t="inlineStr">
         <is>
           <t>2025/08/25</t>
         </is>
       </c>
-      <c r="BP10" t="inlineStr">
+      <c r="BT10" t="inlineStr">
         <is>
           <t>-6.05</t>
         </is>
       </c>
-      <c r="BQ10" t="inlineStr">
+      <c r="BU10" t="inlineStr">
         <is>
           <t>岱稜</t>
         </is>
       </c>
-      <c r="BR10" t="inlineStr">
+      <c r="BV10" t="inlineStr">
         <is>
           <t>岱稜</t>
         </is>
       </c>
-      <c r="BS10" t="inlineStr">
+      <c r="BW10" t="inlineStr">
         <is>
           <t>其他電子業</t>
         </is>
       </c>
-      <c r="BT10" t="inlineStr">
+      <c r="BX10" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BU10" t="inlineStr">
+      <c r="BY10" t="inlineStr">
         <is>
           <t>1.03</t>
         </is>
       </c>
-      <c r="BV10" t="inlineStr">
+      <c r="BZ10" t="inlineStr">
         <is>
           <t>-1.004452687200723</t>
         </is>
       </c>
-      <c r="BW10" t="inlineStr">
+      <c r="CA10" t="inlineStr">
         <is>
           <t>11.92388165594906</t>
         </is>
       </c>
-      <c r="BX10" t="inlineStr">
+      <c r="CB10" t="inlineStr">
         <is>
           <t>2.060463205899802</t>
         </is>
       </c>
-      <c r="BY10" t="inlineStr">
+      <c r="CC10" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BZ10" t="inlineStr">
+      <c r="CD10" t="inlineStr">
         <is>
           <t>價-量增</t>
         </is>
       </c>
-      <c r="CA10" t="inlineStr">
+      <c r="CE10" t="inlineStr">
         <is>
           <t>1.86</t>
         </is>
       </c>
-      <c r="CB10" t="inlineStr">
+      <c r="CF10" t="inlineStr">
         <is>
           <t>6.12</t>
         </is>
       </c>
-      <c r="CC10" t="inlineStr">
+      <c r="CG10" t="inlineStr">
         <is>
           <t>8.56</t>
         </is>
       </c>
-      <c r="CD10" t="inlineStr">
+      <c r="CH10" t="inlineStr">
         <is>
           <t>10.2</t>
         </is>
       </c>
-      <c r="CE10" t="inlineStr">
+      <c r="CI10" t="inlineStr">
         <is>
           <t>33.67%</t>
         </is>
       </c>
-      <c r="CF10" t="inlineStr">
+      <c r="CJ10" t="inlineStr">
         <is>
           <t>12.48%</t>
         </is>
       </c>
-      <c r="CG10" t="inlineStr">
+      <c r="CK10" t="inlineStr">
         <is>
           <t>47.76</t>
         </is>
       </c>
-      <c r="CH10" t="inlineStr">
+      <c r="CL10" t="inlineStr">
         <is>
           <t>4253</t>
         </is>
       </c>
-      <c r="CI10" t="inlineStr">
+      <c r="CM10" t="inlineStr">
         <is>
           <t>真空蒸鍍薄膜95.00%、光電材料5.00% (2024年)</t>
         </is>
       </c>
-      <c r="CJ10" t="inlineStr">
+      <c r="CN10" t="inlineStr">
         <is>
           <t>岱稜-其他電子業-上櫃</t>
         </is>
       </c>
-      <c r="CK10" t="inlineStr">
+      <c r="CO10" t="inlineStr">
         <is>
           <t>其他電子業平上櫃</t>
         </is>
       </c>
-      <c r="CL10" t="inlineStr">
+      <c r="CP10" t="inlineStr">
         <is>
           <t>45.8</t>
         </is>
       </c>
-      <c r="CM10" t="inlineStr">
+      <c r="CQ10" t="inlineStr">
         <is>
           <t>46.0</t>
         </is>
       </c>
-      <c r="CN10" t="inlineStr">
+      <c r="CR10" t="inlineStr">
         <is>
           <t>45.7</t>
         </is>
       </c>
-      <c r="CO10" t="inlineStr">
+      <c r="CS10" t="inlineStr">
         <is>
           <t>45.8</t>
         </is>
       </c>
-      <c r="CP10" t="inlineStr">
+      <c r="CT10" t="inlineStr">
         <is>
           <t>24.66</t>
         </is>
       </c>
-      <c r="CQ10" t="inlineStr">
+      <c r="CU10" t="inlineStr">
         <is>
           <t>** 觸控面板 - PET膜** 其他 - 其他電子產品及電子服務產業、其他** 醫療器材 - 塑化材料</t>
         </is>
       </c>
-      <c r="CR10" t="inlineStr">
+      <c r="CV10" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -5206,325 +5406,345 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
           <t>2025/10/14</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
+      <c r="AD11" t="inlineStr">
         <is>
           <t>44.35</t>
         </is>
       </c>
-      <c r="AD11" t="inlineStr">
+      <c r="AE11" t="inlineStr">
         <is>
           <t>2025/06/30</t>
         </is>
       </c>
-      <c r="AE11" t="inlineStr">
+      <c r="AF11" t="inlineStr">
         <is>
           <t>48.2</t>
         </is>
       </c>
-      <c r="AF11" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
       <c r="AG11" t="inlineStr">
         <is>
+          <t>2025/12/08</t>
+        </is>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>45.05</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>2025/11/19</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>45.05</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
           <t>2025-12-02</t>
         </is>
       </c>
-      <c r="AH11" t="inlineStr">
+      <c r="AL11" t="inlineStr">
         <is>
           <t>3.26</t>
         </is>
       </c>
-      <c r="AI11" t="inlineStr">
+      <c r="AM11" t="inlineStr">
         <is>
           <t>-0.43</t>
         </is>
       </c>
-      <c r="AJ11" t="inlineStr">
+      <c r="AN11" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AK11" t="inlineStr"/>
-      <c r="AL11" t="inlineStr">
+      <c r="AO11" t="inlineStr"/>
+      <c r="AP11" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
+      <c r="AQ11" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="AN11" t="inlineStr">
+      <c r="AR11" t="inlineStr">
         <is>
           <t>84.0</t>
         </is>
       </c>
-      <c r="AO11" t="inlineStr">
+      <c r="AS11" t="inlineStr">
         <is>
           <t>89.33</t>
         </is>
       </c>
-      <c r="AP11" t="n">
+      <c r="AT11" t="n">
         <v>-0.17</v>
       </c>
-      <c r="AQ11" t="n">
+      <c r="AU11" t="n">
         <v>-0.46</v>
       </c>
-      <c r="AR11" t="inlineStr">
+      <c r="AV11" t="inlineStr">
         <is>
           <t>-1.07</t>
         </is>
       </c>
-      <c r="AS11" t="inlineStr">
+      <c r="AW11" t="inlineStr">
         <is>
           <t>-1.95</t>
         </is>
       </c>
-      <c r="AT11" t="inlineStr">
+      <c r="AX11" t="inlineStr">
         <is>
           <t>45.88</t>
         </is>
       </c>
-      <c r="AU11" t="n">
+      <c r="AY11" t="n">
         <v>46.09</v>
       </c>
-      <c r="AV11" t="n">
+      <c r="AZ11" t="n">
         <v>46.59</v>
       </c>
-      <c r="AW11" t="inlineStr">
+      <c r="BA11" t="inlineStr">
         <is>
           <t>47.52</t>
         </is>
       </c>
-      <c r="AX11" t="inlineStr">
+      <c r="BB11" t="inlineStr">
         <is>
           <t>18.14</t>
         </is>
       </c>
-      <c r="AY11" t="n">
+      <c r="BC11" t="n">
         <v>-0.23</v>
       </c>
-      <c r="AZ11" t="n">
+      <c r="BD11" t="n">
         <v>-0.28</v>
       </c>
-      <c r="BA11" t="inlineStr">
+      <c r="BE11" t="inlineStr">
         <is>
           <t>4.28</t>
         </is>
       </c>
-      <c r="BB11" t="inlineStr">
+      <c r="BF11" t="inlineStr">
         <is>
           <t>-106.51</t>
         </is>
       </c>
-      <c r="BC11" t="inlineStr">
+      <c r="BG11" t="inlineStr">
         <is>
           <t>2025/11/27</t>
         </is>
       </c>
-      <c r="BD11" t="inlineStr">
+      <c r="BH11" t="inlineStr">
         <is>
           <t>75475.9297752809</t>
         </is>
       </c>
-      <c r="BE11" t="inlineStr">
+      <c r="BI11" t="inlineStr">
         <is>
           <t>3809.0</t>
         </is>
       </c>
-      <c r="BF11" t="n">
+      <c r="BJ11" t="n">
         <v>4626.6</v>
       </c>
-      <c r="BG11" t="inlineStr">
+      <c r="BK11" t="inlineStr">
         <is>
           <t>4741.3</t>
         </is>
       </c>
-      <c r="BH11" t="n">
+      <c r="BL11" t="n">
         <v>12259.36</v>
       </c>
-      <c r="BI11" t="inlineStr">
+      <c r="BM11" t="inlineStr">
         <is>
           <t>-114</t>
         </is>
       </c>
-      <c r="BJ11" t="inlineStr">
+      <c r="BN11" t="inlineStr">
         <is>
           <t>-1191.289377825079</t>
         </is>
       </c>
-      <c r="BK11" t="inlineStr">
+      <c r="BO11" t="inlineStr">
         <is>
           <t>-1543.3847844998</t>
         </is>
       </c>
-      <c r="BL11" t="inlineStr">
+      <c r="BP11" t="inlineStr">
         <is>
           <t>3809.0</t>
         </is>
       </c>
-      <c r="BM11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BN11" t="inlineStr">
+      <c r="BQ11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR11" t="inlineStr">
         <is>
           <t>48.75</t>
         </is>
       </c>
-      <c r="BO11" t="inlineStr">
+      <c r="BS11" t="inlineStr">
         <is>
           <t>2025/08/25</t>
         </is>
       </c>
-      <c r="BP11" t="inlineStr">
+      <c r="BT11" t="inlineStr">
         <is>
           <t>-6.05</t>
         </is>
       </c>
-      <c r="BQ11" t="inlineStr">
+      <c r="BU11" t="inlineStr">
         <is>
           <t>岱稜</t>
         </is>
       </c>
-      <c r="BR11" t="inlineStr">
+      <c r="BV11" t="inlineStr">
         <is>
           <t>岱稜</t>
         </is>
       </c>
-      <c r="BS11" t="inlineStr">
+      <c r="BW11" t="inlineStr">
         <is>
           <t>其他電子業</t>
         </is>
       </c>
-      <c r="BT11" t="inlineStr">
+      <c r="BX11" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BU11" t="inlineStr">
+      <c r="BY11" t="inlineStr">
         <is>
           <t>1.03</t>
         </is>
       </c>
-      <c r="BV11" t="inlineStr">
+      <c r="BZ11" t="inlineStr">
         <is>
           <t>-1.004452687200723</t>
         </is>
       </c>
-      <c r="BW11" t="inlineStr">
+      <c r="CA11" t="inlineStr">
         <is>
           <t>11.92388165594906</t>
         </is>
       </c>
-      <c r="BX11" t="inlineStr">
+      <c r="CB11" t="inlineStr">
         <is>
           <t>2.060463205899802</t>
         </is>
       </c>
-      <c r="BY11" t="inlineStr">
+      <c r="CC11" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BZ11" t="inlineStr">
+      <c r="CD11" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="CA11" t="inlineStr">
+      <c r="CE11" t="inlineStr">
         <is>
           <t>1.86</t>
         </is>
       </c>
-      <c r="CB11" t="inlineStr">
+      <c r="CF11" t="inlineStr">
         <is>
           <t>6.12</t>
         </is>
       </c>
-      <c r="CC11" t="inlineStr">
+      <c r="CG11" t="inlineStr">
         <is>
           <t>8.56</t>
         </is>
       </c>
-      <c r="CD11" t="inlineStr">
+      <c r="CH11" t="inlineStr">
         <is>
           <t>10.2</t>
         </is>
       </c>
-      <c r="CE11" t="inlineStr">
+      <c r="CI11" t="inlineStr">
         <is>
           <t>33.67%</t>
         </is>
       </c>
-      <c r="CF11" t="inlineStr">
+      <c r="CJ11" t="inlineStr">
         <is>
           <t>12.48%</t>
         </is>
       </c>
-      <c r="CG11" t="inlineStr">
+      <c r="CK11" t="inlineStr">
         <is>
           <t>47.76</t>
         </is>
       </c>
-      <c r="CH11" t="inlineStr">
+      <c r="CL11" t="inlineStr">
         <is>
           <t>4253</t>
         </is>
       </c>
-      <c r="CI11" t="inlineStr">
+      <c r="CM11" t="inlineStr">
         <is>
           <t>真空蒸鍍薄膜95.00%、光電材料5.00% (2024年)</t>
         </is>
       </c>
-      <c r="CJ11" t="inlineStr">
+      <c r="CN11" t="inlineStr">
         <is>
           <t>岱稜-其他電子業-上櫃</t>
         </is>
       </c>
-      <c r="CK11" t="inlineStr">
+      <c r="CO11" t="inlineStr">
         <is>
           <t>其他電子業平上櫃</t>
         </is>
       </c>
-      <c r="CL11" t="inlineStr">
+      <c r="CP11" t="inlineStr">
         <is>
           <t>46.2</t>
         </is>
       </c>
-      <c r="CM11" t="inlineStr">
+      <c r="CQ11" t="inlineStr">
         <is>
           <t>46.2</t>
         </is>
       </c>
-      <c r="CN11" t="inlineStr">
+      <c r="CR11" t="inlineStr">
         <is>
           <t>45.6</t>
         </is>
       </c>
-      <c r="CO11" t="inlineStr">
+      <c r="CS11" t="inlineStr">
         <is>
           <t>45.8</t>
         </is>
       </c>
-      <c r="CP11" t="inlineStr">
+      <c r="CT11" t="inlineStr">
         <is>
           <t>24.66</t>
         </is>
       </c>
-      <c r="CQ11" t="inlineStr">
+      <c r="CU11" t="inlineStr">
         <is>
           <t>** 觸控面板 - PET膜** 其他 - 其他電子產品及電子服務產業、其他** 醫療器材 - 塑化材料</t>
         </is>
       </c>
-      <c r="CR11" t="inlineStr">
+      <c r="CV11" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -5668,325 +5888,345 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
           <t>2025/10/14</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
+      <c r="AD12" t="inlineStr">
         <is>
           <t>44.35</t>
         </is>
       </c>
-      <c r="AD12" t="inlineStr">
+      <c r="AE12" t="inlineStr">
         <is>
           <t>2025/06/30</t>
         </is>
       </c>
-      <c r="AE12" t="inlineStr">
+      <c r="AF12" t="inlineStr">
         <is>
           <t>48.2</t>
         </is>
       </c>
-      <c r="AF12" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
       <c r="AG12" t="inlineStr">
         <is>
+          <t>2025/12/08</t>
+        </is>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>45.05</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>2025/11/19</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>45.05</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
           <t>2025-12-01</t>
         </is>
       </c>
-      <c r="AH12" t="inlineStr">
+      <c r="AL12" t="inlineStr">
         <is>
           <t>3.22</t>
         </is>
       </c>
-      <c r="AI12" t="inlineStr">
+      <c r="AM12" t="inlineStr">
         <is>
           <t>0.00</t>
         </is>
       </c>
-      <c r="AJ12" t="inlineStr">
+      <c r="AN12" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AK12" t="inlineStr"/>
-      <c r="AL12" t="inlineStr">
+      <c r="AO12" t="inlineStr"/>
+      <c r="AP12" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AM12" t="inlineStr">
+      <c r="AQ12" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="AN12" t="inlineStr">
+      <c r="AR12" t="inlineStr">
         <is>
           <t>84.0</t>
         </is>
       </c>
-      <c r="AO12" t="inlineStr">
+      <c r="AS12" t="inlineStr">
         <is>
           <t>83.86</t>
         </is>
       </c>
-      <c r="AP12" t="n">
+      <c r="AT12" t="n">
         <v>0.02</v>
       </c>
-      <c r="AQ12" t="n">
+      <c r="AU12" t="n">
         <v>-0.58</v>
       </c>
-      <c r="AR12" t="inlineStr">
+      <c r="AV12" t="inlineStr">
         <is>
           <t>-1.25</t>
         </is>
       </c>
-      <c r="AS12" t="inlineStr">
+      <c r="AW12" t="inlineStr">
         <is>
           <t>-1.87</t>
         </is>
       </c>
-      <c r="AT12" t="inlineStr">
+      <c r="AX12" t="inlineStr">
         <is>
           <t>45.79</t>
         </is>
       </c>
-      <c r="AU12" t="n">
+      <c r="AY12" t="n">
         <v>46.06</v>
       </c>
-      <c r="AV12" t="n">
+      <c r="AZ12" t="n">
         <v>46.64</v>
       </c>
-      <c r="AW12" t="inlineStr">
+      <c r="BA12" t="inlineStr">
         <is>
           <t>47.53</t>
         </is>
       </c>
-      <c r="AX12" t="inlineStr">
+      <c r="BB12" t="inlineStr">
         <is>
           <t>15.60</t>
         </is>
       </c>
-      <c r="AY12" t="n">
+      <c r="BC12" t="n">
         <v>-0.25</v>
       </c>
-      <c r="AZ12" t="n">
+      <c r="BD12" t="n">
         <v>-0.29</v>
       </c>
-      <c r="BA12" t="inlineStr">
+      <c r="BE12" t="inlineStr">
         <is>
           <t>4.28</t>
         </is>
       </c>
-      <c r="BB12" t="inlineStr">
+      <c r="BF12" t="inlineStr">
         <is>
           <t>-106.80</t>
         </is>
       </c>
-      <c r="BC12" t="inlineStr">
+      <c r="BG12" t="inlineStr">
         <is>
           <t>2025/11/27</t>
         </is>
       </c>
-      <c r="BD12" t="inlineStr">
+      <c r="BH12" t="inlineStr">
         <is>
           <t>75475.9297752809</t>
         </is>
       </c>
-      <c r="BE12" t="inlineStr">
+      <c r="BI12" t="inlineStr">
         <is>
           <t>3779.0</t>
         </is>
       </c>
-      <c r="BF12" t="n">
+      <c r="BJ12" t="n">
         <v>4604</v>
       </c>
-      <c r="BG12" t="inlineStr">
+      <c r="BK12" t="inlineStr">
         <is>
           <t>5794.0</t>
         </is>
       </c>
-      <c r="BH12" t="n">
+      <c r="BL12" t="n">
         <v>12544.52</v>
       </c>
-      <c r="BI12" t="inlineStr">
+      <c r="BM12" t="inlineStr">
         <is>
           <t>-1190</t>
         </is>
       </c>
-      <c r="BJ12" t="inlineStr">
+      <c r="BN12" t="inlineStr">
         <is>
           <t>-1127.272031156948</t>
         </is>
       </c>
-      <c r="BK12" t="inlineStr">
+      <c r="BO12" t="inlineStr">
         <is>
           <t>-1585.732927737606</t>
         </is>
       </c>
-      <c r="BL12" t="inlineStr">
+      <c r="BP12" t="inlineStr">
         <is>
           <t>3779.0</t>
         </is>
       </c>
-      <c r="BM12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BN12" t="inlineStr">
+      <c r="BQ12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR12" t="inlineStr">
         <is>
           <t>48.75</t>
         </is>
       </c>
-      <c r="BO12" t="inlineStr">
+      <c r="BS12" t="inlineStr">
         <is>
           <t>2025/08/25</t>
         </is>
       </c>
-      <c r="BP12" t="inlineStr">
+      <c r="BT12" t="inlineStr">
         <is>
           <t>-6.05</t>
         </is>
       </c>
-      <c r="BQ12" t="inlineStr">
+      <c r="BU12" t="inlineStr">
         <is>
           <t>岱稜</t>
         </is>
       </c>
-      <c r="BR12" t="inlineStr">
+      <c r="BV12" t="inlineStr">
         <is>
           <t>岱稜</t>
         </is>
       </c>
-      <c r="BS12" t="inlineStr">
+      <c r="BW12" t="inlineStr">
         <is>
           <t>其他電子業</t>
         </is>
       </c>
-      <c r="BT12" t="inlineStr">
+      <c r="BX12" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BU12" t="inlineStr">
+      <c r="BY12" t="inlineStr">
         <is>
           <t>1.03</t>
         </is>
       </c>
-      <c r="BV12" t="inlineStr">
+      <c r="BZ12" t="inlineStr">
         <is>
           <t>-1.004452687200723</t>
         </is>
       </c>
-      <c r="BW12" t="inlineStr">
+      <c r="CA12" t="inlineStr">
         <is>
           <t>11.92388165594906</t>
         </is>
       </c>
-      <c r="BX12" t="inlineStr">
+      <c r="CB12" t="inlineStr">
         <is>
           <t>2.060463205899802</t>
         </is>
       </c>
-      <c r="BY12" t="inlineStr">
+      <c r="CC12" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BZ12" t="inlineStr">
+      <c r="CD12" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="CA12" t="inlineStr">
+      <c r="CE12" t="inlineStr">
         <is>
           <t>1.86</t>
         </is>
       </c>
-      <c r="CB12" t="inlineStr">
+      <c r="CF12" t="inlineStr">
         <is>
           <t>6.12</t>
         </is>
       </c>
-      <c r="CC12" t="inlineStr">
+      <c r="CG12" t="inlineStr">
         <is>
           <t>8.56</t>
         </is>
       </c>
-      <c r="CD12" t="inlineStr">
+      <c r="CH12" t="inlineStr">
         <is>
           <t>10.2</t>
         </is>
       </c>
-      <c r="CE12" t="inlineStr">
+      <c r="CI12" t="inlineStr">
         <is>
           <t>33.67%</t>
         </is>
       </c>
-      <c r="CF12" t="inlineStr">
+      <c r="CJ12" t="inlineStr">
         <is>
           <t>12.48%</t>
         </is>
       </c>
-      <c r="CG12" t="inlineStr">
+      <c r="CK12" t="inlineStr">
         <is>
           <t>47.76</t>
         </is>
       </c>
-      <c r="CH12" t="inlineStr">
+      <c r="CL12" t="inlineStr">
         <is>
           <t>4253</t>
         </is>
       </c>
-      <c r="CI12" t="inlineStr">
+      <c r="CM12" t="inlineStr">
         <is>
           <t>真空蒸鍍薄膜95.00%、光電材料5.00% (2024年)</t>
         </is>
       </c>
-      <c r="CJ12" t="inlineStr">
+      <c r="CN12" t="inlineStr">
         <is>
           <t>岱稜-其他電子業-上櫃</t>
         </is>
       </c>
-      <c r="CK12" t="inlineStr">
+      <c r="CO12" t="inlineStr">
         <is>
           <t>其他電子業平上櫃</t>
         </is>
       </c>
-      <c r="CL12" t="inlineStr">
+      <c r="CP12" t="inlineStr">
         <is>
           <t>46.0</t>
         </is>
       </c>
-      <c r="CM12" t="inlineStr">
+      <c r="CQ12" t="inlineStr">
         <is>
           <t>46.05</t>
         </is>
       </c>
-      <c r="CN12" t="inlineStr">
+      <c r="CR12" t="inlineStr">
         <is>
           <t>45.55</t>
         </is>
       </c>
-      <c r="CO12" t="inlineStr">
+      <c r="CS12" t="inlineStr">
         <is>
           <t>45.8</t>
         </is>
       </c>
-      <c r="CP12" t="inlineStr">
+      <c r="CT12" t="inlineStr">
         <is>
           <t>24.66</t>
         </is>
       </c>
-      <c r="CQ12" t="inlineStr">
+      <c r="CU12" t="inlineStr">
         <is>
           <t>** 觸控面板 - PET膜** 其他 - 其他電子產品及電子服務產業、其他** 醫療器材 - 塑化材料</t>
         </is>
       </c>
-      <c r="CR12" t="inlineStr">
+      <c r="CV12" t="inlineStr">
         <is>
           <t>False</t>
         </is>

--- a/Result/checksun_type/PET膜.xlsx
+++ b/Result/checksun_type/PET膜.xlsx
@@ -943,12 +943,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.44</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -958,7 +958,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>45.2</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>20.01</t>
+          <t>17.57</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -1043,7 +1043,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-9.15</t>
+          <t>-9.55</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -1068,7 +1068,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -1113,17 +1113,17 @@
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>3.07</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>-0.55</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
@@ -1134,66 +1134,66 @@
       <c r="AO2" t="inlineStr"/>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>89</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>45.45</t>
+          <t>35.29</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>45.1</t>
         </is>
       </c>
       <c r="AT2" t="n">
-        <v>0.22</v>
+        <v>0.02</v>
       </c>
       <c r="AU2" t="n">
-        <v>-0.58</v>
+        <v>-0.85</v>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>-1.27</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>-2.57</t>
+          <t>-2.67</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>45.1</t>
+          <t>44.98999999999999</t>
         </is>
       </c>
       <c r="AY2" t="n">
-        <v>45.36</v>
+        <v>45.38</v>
       </c>
       <c r="AZ2" t="n">
-        <v>45.95</v>
+        <v>45.86</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>47.16</t>
+          <t>47.12</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-4.49</t>
+          <t>-4.09</t>
         </is>
       </c>
       <c r="BC2" t="n">
         <v>-0.31</v>
       </c>
       <c r="BD2" t="n">
-        <v>-0.29</v>
+        <v>-0.3</v>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1202,7 +1202,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>-106.86</t>
+          <t>-106.93</t>
         </is>
       </c>
       <c r="BG2" t="inlineStr">
@@ -1212,43 +1212,43 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>75475.9297752809</t>
+          <t>75378.46704067322</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>3539.0</t>
+          <t>3990.0</t>
         </is>
       </c>
       <c r="BJ2" t="n">
-        <v>8163.8</v>
+        <v>8019</v>
       </c>
       <c r="BK2" t="inlineStr">
         <is>
-          <t>6802.5</t>
+          <t>6820.6</t>
         </is>
       </c>
       <c r="BL2" t="n">
-        <v>11065.56</v>
+        <v>10934.42</v>
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>1361</t>
+          <t>1198</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>-497.5264159701541</t>
+          <t>-488.82761144805</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
         <is>
-          <t>-252.6207944996822</t>
+          <t>-440.9841865764774</t>
         </is>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>3539.0</t>
+          <t>3990.0</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
@@ -1268,7 +1268,7 @@
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>-7.28</t>
+          <t>-7.69</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1313,22 +1313,22 @@
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>6.12</t>
+          <t>6.15</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1338,7 +1338,7 @@
       </c>
       <c r="CH2" t="inlineStr">
         <is>
-          <t>10.2</t>
+          <t>10.16</t>
         </is>
       </c>
       <c r="CI2" t="inlineStr">
@@ -1353,12 +1353,12 @@
       </c>
       <c r="CK2" t="inlineStr">
         <is>
-          <t>47.76</t>
+          <t>46.96</t>
         </is>
       </c>
       <c r="CL2" t="inlineStr">
         <is>
-          <t>4253</t>
+          <t>4234</t>
         </is>
       </c>
       <c r="CM2" t="inlineStr">
@@ -1378,22 +1378,22 @@
       </c>
       <c r="CP2" t="inlineStr">
         <is>
-          <t>45.05</t>
+          <t>45.5</t>
         </is>
       </c>
       <c r="CQ2" t="inlineStr">
         <is>
-          <t>45.6</t>
+          <t>45.5</t>
         </is>
       </c>
       <c r="CR2" t="inlineStr">
         <is>
-          <t>45.05</t>
+          <t>44.6</t>
         </is>
       </c>
       <c r="CS2" t="inlineStr">
         <is>
-          <t>45.2</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="CT2" t="inlineStr">
@@ -1425,12 +1425,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>143.0</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1440,7 +1440,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>45.3</t>
+          <t>45.2</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1450,7 +1450,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.44</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -1460,7 +1460,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>41.55</t>
+          <t>20.01</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1525,7 +1525,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-8.94</t>
+          <t>-9.15</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1550,7 +1550,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -1595,17 +1595,17 @@
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>5.62</t>
+          <t>3.07</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>-0.55</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
@@ -1616,63 +1616,63 @@
       <c r="AO3" t="inlineStr"/>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>89</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>54.55</t>
+          <t>45.45</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>18.18</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AT3" t="n">
-        <v>0.51</v>
+        <v>0.22</v>
       </c>
       <c r="AU3" t="n">
-        <v>-0.8</v>
+        <v>-0.58</v>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>-1.32</t>
+          <t>-1.27</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>-2.47</t>
+          <t>-2.57</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>45.07000000000001</t>
+          <t>45.1</t>
         </is>
       </c>
       <c r="AY3" t="n">
-        <v>45.44</v>
+        <v>45.36</v>
       </c>
       <c r="AZ3" t="n">
-        <v>46.04</v>
+        <v>45.95</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>47.21</t>
+          <t>47.16</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-10.29</t>
+          <t>-4.49</t>
         </is>
       </c>
       <c r="BC3" t="n">
-        <v>-0.32</v>
+        <v>-0.31</v>
       </c>
       <c r="BD3" t="n">
         <v>-0.29</v>
@@ -1684,7 +1684,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>-106.78</t>
+          <t>-106.86</t>
         </is>
       </c>
       <c r="BG3" t="inlineStr">
@@ -1694,43 +1694,43 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>75475.9297752809</t>
+          <t>75378.46704067322</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>6423.0</t>
+          <t>3539.0</t>
         </is>
       </c>
       <c r="BJ3" t="n">
-        <v>9662.799999999999</v>
+        <v>8163.8</v>
       </c>
       <c r="BK3" t="inlineStr">
         <is>
-          <t>6826.5</t>
+          <t>6802.5</t>
         </is>
       </c>
       <c r="BL3" t="n">
-        <v>11523.86</v>
+        <v>11065.56</v>
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>2836</t>
+          <t>1361</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>-542.0547107829672</t>
+          <t>-497.5264159701541</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
         <is>
-          <t>73.8133654135845</t>
+          <t>-252.6207944996822</t>
         </is>
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>6423.0</t>
+          <t>3539.0</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
@@ -1750,7 +1750,7 @@
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>-7.08</t>
+          <t>-7.28</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1795,22 +1795,22 @@
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>6.12</t>
+          <t>6.15</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="CH3" t="inlineStr">
         <is>
-          <t>10.2</t>
+          <t>10.16</t>
         </is>
       </c>
       <c r="CI3" t="inlineStr">
@@ -1835,12 +1835,12 @@
       </c>
       <c r="CK3" t="inlineStr">
         <is>
-          <t>47.76</t>
+          <t>46.96</t>
         </is>
       </c>
       <c r="CL3" t="inlineStr">
         <is>
-          <t>4253</t>
+          <t>4234</t>
         </is>
       </c>
       <c r="CM3" t="inlineStr">
@@ -1860,22 +1860,22 @@
       </c>
       <c r="CP3" t="inlineStr">
         <is>
-          <t>44.8</t>
+          <t>45.05</t>
         </is>
       </c>
       <c r="CQ3" t="inlineStr">
         <is>
-          <t>45.3</t>
+          <t>45.6</t>
         </is>
       </c>
       <c r="CR3" t="inlineStr">
         <is>
-          <t>44.75</t>
+          <t>45.05</t>
         </is>
       </c>
       <c r="CS3" t="inlineStr">
         <is>
-          <t>45.3</t>
+          <t>45.2</t>
         </is>
       </c>
       <c r="CT3" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>109.0</t>
+          <t>143.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1922,7 +1922,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>44.7</t>
+          <t>45.3</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1942,7 +1942,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>42.69</t>
+          <t>41.55</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -2007,7 +2007,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-10.15</t>
+          <t>-8.94</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -2032,7 +2032,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -2077,17 +2077,17 @@
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>4.28</t>
+          <t>5.62</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
@@ -2098,66 +2098,66 @@
       <c r="AO4" t="inlineStr"/>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>89</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>54.55</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>17.54</t>
+          <t>18.18</t>
         </is>
       </c>
       <c r="AT4" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="AU4" t="n">
         <v>-0.8</v>
       </c>
-      <c r="AU4" t="n">
-        <v>-1.02</v>
-      </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>-1.27</t>
+          <t>-1.32</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>-2.44</t>
+          <t>-2.47</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>45.06</t>
+          <t>45.07000000000001</t>
         </is>
       </c>
       <c r="AY4" t="n">
-        <v>45.52</v>
+        <v>45.44</v>
       </c>
       <c r="AZ4" t="n">
-        <v>46.11</v>
+        <v>46.04</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>47.26</t>
+          <t>47.21</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-21.20</t>
+          <t>-10.29</t>
         </is>
       </c>
       <c r="BC4" t="n">
-        <v>-0.34</v>
+        <v>-0.32</v>
       </c>
       <c r="BD4" t="n">
-        <v>-0.28</v>
+        <v>-0.29</v>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2166,7 +2166,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>-106.61</t>
+          <t>-106.78</t>
         </is>
       </c>
       <c r="BG4" t="inlineStr">
@@ -2176,43 +2176,43 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>75475.9297752809</t>
+          <t>75378.46704067322</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>4845.0</t>
+          <t>6423.0</t>
         </is>
       </c>
       <c r="BJ4" t="n">
-        <v>9321</v>
+        <v>9662.799999999999</v>
       </c>
       <c r="BK4" t="inlineStr">
         <is>
-          <t>6532.2</t>
+          <t>6826.5</t>
         </is>
       </c>
       <c r="BL4" t="n">
-        <v>11521.76</v>
+        <v>11523.86</v>
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>2788</t>
+          <t>2836</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>-654.0307246368856</t>
+          <t>-542.0547107829672</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>228.5116879534808</t>
+          <t>73.8133654135845</t>
         </is>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>4845.0</t>
+          <t>6423.0</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
@@ -2232,7 +2232,7 @@
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>-8.31</t>
+          <t>-7.08</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2277,7 +2277,7 @@
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>1.84</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>6.12</t>
+          <t>6.15</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2302,7 +2302,7 @@
       </c>
       <c r="CH4" t="inlineStr">
         <is>
-          <t>10.2</t>
+          <t>10.16</t>
         </is>
       </c>
       <c r="CI4" t="inlineStr">
@@ -2317,12 +2317,12 @@
       </c>
       <c r="CK4" t="inlineStr">
         <is>
-          <t>47.76</t>
+          <t>46.96</t>
         </is>
       </c>
       <c r="CL4" t="inlineStr">
         <is>
-          <t>4253</t>
+          <t>4234</t>
         </is>
       </c>
       <c r="CM4" t="inlineStr">
@@ -2342,22 +2342,22 @@
       </c>
       <c r="CP4" t="inlineStr">
         <is>
+          <t>44.8</t>
+        </is>
+      </c>
+      <c r="CQ4" t="inlineStr">
+        <is>
+          <t>45.3</t>
+        </is>
+      </c>
+      <c r="CR4" t="inlineStr">
+        <is>
           <t>44.75</t>
         </is>
       </c>
-      <c r="CQ4" t="inlineStr">
-        <is>
-          <t>44.75</t>
-        </is>
-      </c>
-      <c r="CR4" t="inlineStr">
-        <is>
-          <t>44.5</t>
-        </is>
-      </c>
       <c r="CS4" t="inlineStr">
         <is>
-          <t>44.7</t>
+          <t>45.3</t>
         </is>
       </c>
       <c r="CT4" t="inlineStr">
@@ -2389,12 +2389,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-1.8</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>478.0</t>
+          <t>109.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>44.75</t>
+          <t>44.7</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2414,7 +2414,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -2424,7 +2424,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>40.89</t>
+          <t>42.69</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2489,7 +2489,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-10.05</t>
+          <t>-10.15</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2514,7 +2514,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -2559,17 +2559,17 @@
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>18.79</t>
+          <t>4.28</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
@@ -2580,12 +2580,12 @@
       <c r="AO5" t="inlineStr"/>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>89</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
@@ -2599,47 +2599,47 @@
         </is>
       </c>
       <c r="AT5" t="n">
-        <v>-1.04</v>
+        <v>-0.8</v>
       </c>
       <c r="AU5" t="n">
-        <v>-0.93</v>
+        <v>-1.02</v>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>-1.16</t>
+          <t>-1.27</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>-2.39</t>
+          <t>-2.44</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>45.21999999999999</t>
+          <t>45.06</t>
         </is>
       </c>
       <c r="AY5" t="n">
-        <v>45.64</v>
+        <v>45.52</v>
       </c>
       <c r="AZ5" t="n">
-        <v>46.18</v>
+        <v>46.11</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>47.31</t>
+          <t>47.26</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-14.07</t>
+          <t>-21.20</t>
         </is>
       </c>
       <c r="BC5" t="n">
-        <v>-0.31</v>
+        <v>-0.34</v>
       </c>
       <c r="BD5" t="n">
-        <v>-0.27</v>
+        <v>-0.28</v>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>-106.26</t>
+          <t>-106.61</t>
         </is>
       </c>
       <c r="BG5" t="inlineStr">
@@ -2658,43 +2658,43 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>75475.9297752809</t>
+          <t>75378.46704067322</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>21298.0</t>
+          <t>4845.0</t>
         </is>
       </c>
       <c r="BJ5" t="n">
-        <v>9270</v>
+        <v>9321</v>
       </c>
       <c r="BK5" t="inlineStr">
         <is>
-          <t>6579.4</t>
+          <t>6532.2</t>
         </is>
       </c>
       <c r="BL5" t="n">
-        <v>11878.36</v>
+        <v>11521.76</v>
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>2690</t>
+          <t>2788</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>-814.4929814714977</t>
+          <t>-654.0307246368856</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>610.419588440709</t>
+          <t>228.5116879534808</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>21298.0</t>
+          <t>4845.0</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
@@ -2714,7 +2714,7 @@
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>-8.21</t>
+          <t>-8.31</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2759,12 +2759,12 @@
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
@@ -2774,7 +2774,7 @@
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>6.12</t>
+          <t>6.15</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2784,7 +2784,7 @@
       </c>
       <c r="CH5" t="inlineStr">
         <is>
-          <t>10.2</t>
+          <t>10.16</t>
         </is>
       </c>
       <c r="CI5" t="inlineStr">
@@ -2799,12 +2799,12 @@
       </c>
       <c r="CK5" t="inlineStr">
         <is>
-          <t>47.76</t>
+          <t>46.96</t>
         </is>
       </c>
       <c r="CL5" t="inlineStr">
         <is>
-          <t>4253</t>
+          <t>4234</t>
         </is>
       </c>
       <c r="CM5" t="inlineStr">
@@ -2824,22 +2824,22 @@
       </c>
       <c r="CP5" t="inlineStr">
         <is>
-          <t>44.55</t>
+          <t>44.75</t>
         </is>
       </c>
       <c r="CQ5" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>44.75</t>
         </is>
       </c>
       <c r="CR5" t="inlineStr">
         <is>
-          <t>44.3</t>
+          <t>44.5</t>
         </is>
       </c>
       <c r="CS5" t="inlineStr">
         <is>
-          <t>44.75</t>
+          <t>44.7</t>
         </is>
       </c>
       <c r="CT5" t="inlineStr">
@@ -2871,12 +2871,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>-1.8</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>478.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2886,7 +2886,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>45.55</t>
+          <t>44.75</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2896,7 +2896,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-0.77</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -2906,7 +2906,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>9.71</t>
+          <t>40.89</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-8.44</t>
+          <t>-10.05</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2996,7 +2996,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -3041,17 +3041,17 @@
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>4.05</t>
+          <t>18.79</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>-1.09</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
@@ -3062,17 +3062,17 @@
       <c r="AO6" t="inlineStr"/>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>89</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>52.63</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -3081,47 +3081,47 @@
         </is>
       </c>
       <c r="AT6" t="n">
-        <v>0.26</v>
+        <v>-1.04</v>
       </c>
       <c r="AU6" t="n">
-        <v>-0.78</v>
+        <v>-0.93</v>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>-1.04</t>
+          <t>-1.16</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>-2.32</t>
+          <t>-2.39</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>45.42999999999999</t>
+          <t>45.21999999999999</t>
         </is>
       </c>
       <c r="AY6" t="n">
-        <v>45.78</v>
+        <v>45.64</v>
       </c>
       <c r="AZ6" t="n">
-        <v>46.27</v>
+        <v>46.18</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>47.37</t>
+          <t>47.31</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-14.07</t>
         </is>
       </c>
       <c r="BC6" t="n">
-        <v>-0.26</v>
+        <v>-0.31</v>
       </c>
       <c r="BD6" t="n">
-        <v>-0.26</v>
+        <v>-0.27</v>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -3130,7 +3130,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>-106.04</t>
+          <t>-106.26</t>
         </is>
       </c>
       <c r="BG6" t="inlineStr">
@@ -3140,43 +3140,43 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>75475.9297752809</t>
+          <t>75378.46704067322</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>4714.0</t>
+          <t>21298.0</t>
         </is>
       </c>
       <c r="BJ6" t="n">
-        <v>5622.2</v>
+        <v>9270</v>
       </c>
       <c r="BK6" t="inlineStr">
         <is>
-          <t>5124.4</t>
+          <t>6579.4</t>
         </is>
       </c>
       <c r="BL6" t="n">
-        <v>11707.74</v>
+        <v>11878.36</v>
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>497</t>
+          <t>2690</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
         <is>
-          <t>-1073.567994182808</t>
+          <t>-814.4929814714977</t>
         </is>
       </c>
       <c r="BO6" t="inlineStr">
         <is>
-          <t>-628.6198247361344</t>
+          <t>610.419588440709</t>
         </is>
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>4714.0</t>
+          <t>21298.0</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
@@ -3196,7 +3196,7 @@
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>-6.56</t>
+          <t>-8.21</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -3241,22 +3241,22 @@
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>6.12</t>
+          <t>6.15</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -3266,7 +3266,7 @@
       </c>
       <c r="CH6" t="inlineStr">
         <is>
-          <t>10.2</t>
+          <t>10.16</t>
         </is>
       </c>
       <c r="CI6" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="CK6" t="inlineStr">
         <is>
-          <t>47.76</t>
+          <t>46.96</t>
         </is>
       </c>
       <c r="CL6" t="inlineStr">
         <is>
-          <t>4253</t>
+          <t>4234</t>
         </is>
       </c>
       <c r="CM6" t="inlineStr">
@@ -3306,22 +3306,22 @@
       </c>
       <c r="CP6" t="inlineStr">
         <is>
-          <t>45.65</t>
+          <t>44.55</t>
         </is>
       </c>
       <c r="CQ6" t="inlineStr">
         <is>
-          <t>46.3</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="CR6" t="inlineStr">
         <is>
-          <t>45.3</t>
+          <t>44.3</t>
         </is>
       </c>
       <c r="CS6" t="inlineStr">
         <is>
-          <t>45.55</t>
+          <t>44.75</t>
         </is>
       </c>
       <c r="CT6" t="inlineStr">
@@ -3353,12 +3353,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>246.0</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3368,172 +3368,172 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
+          <t>45.55</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>-1.22</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>9.71</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>2025-09-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>2025-09-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>2025-03-06 00:00:00</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>2025-03-10 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>51.1</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>49.75</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>57.7</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>56.5</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>-8.44</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>-9.56</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025/05/23</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>51.4</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>0.02</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>2025/10/14</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>44.35</t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>2025/06/30</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>48.2</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>2025/12/08</t>
+        </is>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
           <t>45.05</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>0.33</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>8.33</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>2025-09-02 00:00:00</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>2025-09-12 00:00:00</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>2025-03-06 00:00:00</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>2025-03-10 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>51.1</t>
-        </is>
-      </c>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>49.75</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>57.7</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>56.5</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>-9.45</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>-9.56</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>2025/05/23</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>51.4</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>-0.03</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>2025/10/14</t>
-        </is>
-      </c>
-      <c r="AD7" t="inlineStr">
-        <is>
-          <t>44.35</t>
-        </is>
-      </c>
-      <c r="AE7" t="inlineStr">
-        <is>
-          <t>2025/06/30</t>
-        </is>
-      </c>
-      <c r="AF7" t="inlineStr">
-        <is>
-          <t>48.2</t>
-        </is>
-      </c>
-      <c r="AG7" t="inlineStr">
-        <is>
-          <t>2025/12/08</t>
-        </is>
-      </c>
-      <c r="AH7" t="inlineStr">
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>2025/11/19</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
         <is>
           <t>45.05</t>
         </is>
       </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>2025/11/19</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>45.05</t>
-        </is>
-      </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>9.67</t>
+          <t>4.05</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>-1.09</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
@@ -3544,63 +3544,63 @@
       <c r="AO7" t="inlineStr"/>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>89</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>52.63</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>9.52</t>
+          <t>17.54</t>
         </is>
       </c>
       <c r="AT7" t="n">
-        <v>-0.95</v>
+        <v>0.26</v>
       </c>
       <c r="AU7" t="n">
-        <v>-0.87</v>
+        <v>-0.78</v>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>-0.97</t>
+          <t>-1.04</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>-2.29</t>
+          <t>-2.32</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>45.48</t>
+          <t>45.42999999999999</t>
         </is>
       </c>
       <c r="AY7" t="n">
-        <v>45.88</v>
+        <v>45.78</v>
       </c>
       <c r="AZ7" t="n">
-        <v>46.32</v>
+        <v>46.27</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>47.41</t>
+          <t>47.37</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-7.02</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="BC7" t="n">
-        <v>-0.28</v>
+        <v>-0.26</v>
       </c>
       <c r="BD7" t="n">
         <v>-0.26</v>
@@ -3622,43 +3622,43 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>75475.9297752809</t>
+          <t>75378.46704067322</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>11034.0</t>
+          <t>4714.0</t>
         </is>
       </c>
       <c r="BJ7" t="n">
-        <v>5441.2</v>
+        <v>5622.2</v>
       </c>
       <c r="BK7" t="inlineStr">
         <is>
-          <t>5022.6</t>
+          <t>5124.4</t>
         </is>
       </c>
       <c r="BL7" t="n">
-        <v>11858.6</v>
+        <v>11707.74</v>
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>418</t>
+          <t>497</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
         <is>
-          <t>-1154.46766135493</t>
+          <t>-1073.567994182808</t>
         </is>
       </c>
       <c r="BO7" t="inlineStr">
         <is>
-          <t>-599.3682783910481</t>
+          <t>-628.6198247361344</t>
         </is>
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>11034.0</t>
+          <t>4714.0</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
@@ -3678,7 +3678,7 @@
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>-7.59</t>
+          <t>-6.56</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3723,22 +3723,22 @@
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>6.12</t>
+          <t>6.15</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3748,7 +3748,7 @@
       </c>
       <c r="CH7" t="inlineStr">
         <is>
-          <t>10.2</t>
+          <t>10.16</t>
         </is>
       </c>
       <c r="CI7" t="inlineStr">
@@ -3763,12 +3763,12 @@
       </c>
       <c r="CK7" t="inlineStr">
         <is>
-          <t>47.76</t>
+          <t>46.96</t>
         </is>
       </c>
       <c r="CL7" t="inlineStr">
         <is>
-          <t>4253</t>
+          <t>4234</t>
         </is>
       </c>
       <c r="CM7" t="inlineStr">
@@ -3788,22 +3788,22 @@
       </c>
       <c r="CP7" t="inlineStr">
         <is>
-          <t>45.25</t>
+          <t>45.65</t>
         </is>
       </c>
       <c r="CQ7" t="inlineStr">
         <is>
-          <t>45.45</t>
+          <t>46.3</t>
         </is>
       </c>
       <c r="CR7" t="inlineStr">
         <is>
-          <t>44.5</t>
+          <t>45.3</t>
         </is>
       </c>
       <c r="CS7" t="inlineStr">
         <is>
-          <t>45.05</t>
+          <t>45.55</t>
         </is>
       </c>
       <c r="CT7" t="inlineStr">
@@ -3825,7 +3825,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>【d2】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3835,12 +3835,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-0.55</t>
+          <t>-0.44</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>104.0</t>
+          <t>246.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3850,7 +3850,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>45.25</t>
+          <t>45.05</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3870,7 +3870,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-8.48</t>
+          <t>8.33</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3935,7 +3935,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-9.05</t>
+          <t>-9.45</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -4005,17 +4005,17 @@
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>4.09</t>
+          <t>9.67</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
@@ -4026,12 +4026,12 @@
       <c r="AO8" t="inlineStr"/>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>89</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
@@ -4041,51 +4041,51 @@
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>37.52</t>
+          <t>9.52</t>
         </is>
       </c>
       <c r="AT8" t="n">
-        <v>-0.83</v>
+        <v>-0.95</v>
       </c>
       <c r="AU8" t="n">
-        <v>-0.75</v>
+        <v>-0.87</v>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>-0.9</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>-2.24</t>
+          <t>-2.29</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>45.63</t>
+          <t>45.48</t>
         </is>
       </c>
       <c r="AY8" t="n">
-        <v>45.98</v>
+        <v>45.88</v>
       </c>
       <c r="AZ8" t="n">
-        <v>46.39</v>
+        <v>46.32</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>47.46</t>
+          <t>47.41</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>3.73</t>
+          <t>-7.02</t>
         </is>
       </c>
       <c r="BC8" t="n">
-        <v>-0.24</v>
+        <v>-0.28</v>
       </c>
       <c r="BD8" t="n">
-        <v>-0.25</v>
+        <v>-0.26</v>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -4094,7 +4094,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>-105.93</t>
+          <t>-106.04</t>
         </is>
       </c>
       <c r="BG8" t="inlineStr">
@@ -4104,43 +4104,43 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>75475.9297752809</t>
+          <t>75378.46704067322</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>4714.0</t>
+          <t>11034.0</t>
         </is>
       </c>
       <c r="BJ8" t="n">
-        <v>3990.2</v>
+        <v>5441.2</v>
       </c>
       <c r="BK8" t="inlineStr">
         <is>
-          <t>4360.0</t>
+          <t>5022.6</t>
         </is>
       </c>
       <c r="BL8" t="n">
-        <v>11948.92</v>
+        <v>11858.6</v>
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>-369</t>
+          <t>418</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
         <is>
-          <t>-1255.394821893818</t>
+          <t>-1154.46766135493</t>
         </is>
       </c>
       <c r="BO8" t="inlineStr">
         <is>
-          <t>-1213.317202241243</t>
+          <t>-599.3682783910481</t>
         </is>
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>4714.0</t>
+          <t>11034.0</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
@@ -4160,7 +4160,7 @@
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>-7.18</t>
+          <t>-7.59</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -4205,12 +4205,12 @@
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
@@ -4220,7 +4220,7 @@
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>6.12</t>
+          <t>6.15</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -4230,7 +4230,7 @@
       </c>
       <c r="CH8" t="inlineStr">
         <is>
-          <t>10.2</t>
+          <t>10.16</t>
         </is>
       </c>
       <c r="CI8" t="inlineStr">
@@ -4245,12 +4245,12 @@
       </c>
       <c r="CK8" t="inlineStr">
         <is>
-          <t>47.76</t>
+          <t>46.96</t>
         </is>
       </c>
       <c r="CL8" t="inlineStr">
         <is>
-          <t>4253</t>
+          <t>4234</t>
         </is>
       </c>
       <c r="CM8" t="inlineStr">
@@ -4270,22 +4270,22 @@
       </c>
       <c r="CP8" t="inlineStr">
         <is>
-          <t>45.5</t>
+          <t>45.25</t>
         </is>
       </c>
       <c r="CQ8" t="inlineStr">
         <is>
-          <t>45.5</t>
+          <t>45.45</t>
         </is>
       </c>
       <c r="CR8" t="inlineStr">
         <is>
-          <t>44.9</t>
+          <t>44.5</t>
         </is>
       </c>
       <c r="CS8" t="inlineStr">
         <is>
-          <t>45.25</t>
+          <t>45.05</t>
         </is>
       </c>
       <c r="CT8" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>-0.55</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>104.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -4332,7 +4332,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>45.5</t>
+          <t>45.25</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -4342,7 +4342,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-0.56</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -4352,7 +4352,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-20.03</t>
+          <t>-8.48</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4417,7 +4417,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-8.54</t>
+          <t>-9.05</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4442,7 +4442,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -4487,17 +4487,17 @@
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>3.97</t>
+          <t>4.09</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
@@ -4508,66 +4508,66 @@
       <c r="AO9" t="inlineStr"/>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>89</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>28.57</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>65.52</t>
+          <t>37.52</t>
         </is>
       </c>
       <c r="AT9" t="n">
-        <v>-0.61</v>
+        <v>-0.83</v>
       </c>
       <c r="AU9" t="n">
-        <v>-0.58</v>
+        <v>-0.75</v>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>-0.89</t>
+          <t>-0.9</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>-2.14</t>
+          <t>-2.24</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>45.77999999999999</t>
+          <t>45.63</t>
         </is>
       </c>
       <c r="AY9" t="n">
-        <v>46.04</v>
+        <v>45.98</v>
       </c>
       <c r="AZ9" t="n">
-        <v>46.46</v>
+        <v>46.39</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>47.48</t>
+          <t>47.46</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>14.06</t>
+          <t>3.73</t>
         </is>
       </c>
       <c r="BC9" t="n">
-        <v>-0.22</v>
+        <v>-0.24</v>
       </c>
       <c r="BD9" t="n">
-        <v>-0.26</v>
+        <v>-0.25</v>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4576,7 +4576,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>-105.99</t>
+          <t>-105.93</t>
         </is>
       </c>
       <c r="BG9" t="inlineStr">
@@ -4586,43 +4586,43 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>75475.9297752809</t>
+          <t>75378.46704067322</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>4590.0</t>
+          <t>4714.0</t>
         </is>
       </c>
       <c r="BJ9" t="n">
-        <v>3743.4</v>
+        <v>3990.2</v>
       </c>
       <c r="BK9" t="inlineStr">
         <is>
-          <t>4681.2</t>
+          <t>4360.0</t>
         </is>
       </c>
       <c r="BL9" t="n">
-        <v>12007.9</v>
+        <v>11948.92</v>
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>-937</t>
+          <t>-369</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
         <is>
-          <t>-1263.045298194286</t>
+          <t>-1255.394821893818</t>
         </is>
       </c>
       <c r="BO9" t="inlineStr">
         <is>
-          <t>-1369.911479090048</t>
+          <t>-1213.317202241243</t>
         </is>
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>4590.0</t>
+          <t>4714.0</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
@@ -4642,7 +4642,7 @@
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>-6.67</t>
+          <t>-7.18</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4687,7 +4687,7 @@
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>6.12</t>
+          <t>6.15</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4712,7 +4712,7 @@
       </c>
       <c r="CH9" t="inlineStr">
         <is>
-          <t>10.2</t>
+          <t>10.16</t>
         </is>
       </c>
       <c r="CI9" t="inlineStr">
@@ -4727,12 +4727,12 @@
       </c>
       <c r="CK9" t="inlineStr">
         <is>
-          <t>47.76</t>
+          <t>46.96</t>
         </is>
       </c>
       <c r="CL9" t="inlineStr">
         <is>
-          <t>4253</t>
+          <t>4234</t>
         </is>
       </c>
       <c r="CM9" t="inlineStr">
@@ -4752,22 +4752,22 @@
       </c>
       <c r="CP9" t="inlineStr">
         <is>
-          <t>46.0</t>
+          <t>45.5</t>
         </is>
       </c>
       <c r="CQ9" t="inlineStr">
         <is>
-          <t>46.05</t>
+          <t>45.5</t>
         </is>
       </c>
       <c r="CR9" t="inlineStr">
         <is>
-          <t>45.15</t>
+          <t>44.9</t>
         </is>
       </c>
       <c r="CS9" t="inlineStr">
         <is>
-          <t>45.5</t>
+          <t>45.25</t>
         </is>
       </c>
       <c r="CT9" t="inlineStr">
@@ -4799,42 +4799,42 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
+          <t>-0.65</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>101.0</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>45.5</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>-1.11</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>67.0</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>45.8</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>-1.33</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-14.39</t>
+          <t>-20.03</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4899,7 +4899,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-7.94</t>
+          <t>-8.54</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4924,7 +4924,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -4969,17 +4969,17 @@
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>2.63</t>
+          <t>3.97</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
@@ -4990,63 +4990,63 @@
       <c r="AO10" t="inlineStr"/>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>89</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>28.57</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>65.52</t>
         </is>
       </c>
       <c r="AT10" t="n">
-        <v>-0.17</v>
+        <v>-0.61</v>
       </c>
       <c r="AU10" t="n">
-        <v>-0.52</v>
+        <v>-0.58</v>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>-0.87</t>
+          <t>-0.89</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>-2.06</t>
+          <t>-2.14</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>45.88</t>
+          <t>45.77999999999999</t>
         </is>
       </c>
       <c r="AY10" t="n">
-        <v>46.12</v>
+        <v>46.04</v>
       </c>
       <c r="AZ10" t="n">
-        <v>46.52</v>
+        <v>46.46</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>47.5</t>
+          <t>47.48</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>20.22</t>
+          <t>14.06</t>
         </is>
       </c>
       <c r="BC10" t="n">
-        <v>-0.21</v>
+        <v>-0.22</v>
       </c>
       <c r="BD10" t="n">
         <v>-0.26</v>
@@ -5058,7 +5058,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>-106.20</t>
+          <t>-105.99</t>
         </is>
       </c>
       <c r="BG10" t="inlineStr">
@@ -5068,43 +5068,43 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>75475.9297752809</t>
+          <t>75378.46704067322</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>3059.0</t>
+          <t>4590.0</t>
         </is>
       </c>
       <c r="BJ10" t="n">
-        <v>3888.8</v>
+        <v>3743.4</v>
       </c>
       <c r="BK10" t="inlineStr">
         <is>
-          <t>4542.6</t>
+          <t>4681.2</t>
         </is>
       </c>
       <c r="BL10" t="n">
-        <v>12062.18</v>
+        <v>12007.9</v>
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>-653</t>
+          <t>-937</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
         <is>
-          <t>-1243.615083485966</t>
+          <t>-1263.045298194286</t>
         </is>
       </c>
       <c r="BO10" t="inlineStr">
         <is>
-          <t>-1531.406464620841</t>
+          <t>-1369.911479090048</t>
         </is>
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>3059.0</t>
+          <t>4590.0</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
@@ -5124,7 +5124,7 @@
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>-6.05</t>
+          <t>-6.67</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -5169,7 +5169,7 @@
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
@@ -5179,12 +5179,12 @@
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>6.12</t>
+          <t>6.15</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -5194,7 +5194,7 @@
       </c>
       <c r="CH10" t="inlineStr">
         <is>
-          <t>10.2</t>
+          <t>10.16</t>
         </is>
       </c>
       <c r="CI10" t="inlineStr">
@@ -5209,12 +5209,12 @@
       </c>
       <c r="CK10" t="inlineStr">
         <is>
-          <t>47.76</t>
+          <t>46.96</t>
         </is>
       </c>
       <c r="CL10" t="inlineStr">
         <is>
-          <t>4253</t>
+          <t>4234</t>
         </is>
       </c>
       <c r="CM10" t="inlineStr">
@@ -5234,22 +5234,22 @@
       </c>
       <c r="CP10" t="inlineStr">
         <is>
-          <t>45.8</t>
+          <t>46.0</t>
         </is>
       </c>
       <c r="CQ10" t="inlineStr">
         <is>
-          <t>46.0</t>
+          <t>46.05</t>
         </is>
       </c>
       <c r="CR10" t="inlineStr">
         <is>
-          <t>45.7</t>
+          <t>45.15</t>
         </is>
       </c>
       <c r="CS10" t="inlineStr">
         <is>
-          <t>45.8</t>
+          <t>45.5</t>
         </is>
       </c>
       <c r="CT10" t="inlineStr">
@@ -5286,7 +5286,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -5306,7 +5306,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-1.33</t>
+          <t>-1.78</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -5316,7 +5316,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-2.42</t>
+          <t>-14.39</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -5406,7 +5406,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -5451,17 +5451,17 @@
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>3.26</t>
+          <t>2.63</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
@@ -5472,12 +5472,12 @@
       <c r="AO11" t="inlineStr"/>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>89</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
@@ -5487,23 +5487,23 @@
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>89.33</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AT11" t="n">
         <v>-0.17</v>
       </c>
       <c r="AU11" t="n">
-        <v>-0.46</v>
+        <v>-0.52</v>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>-1.07</t>
+          <t>-0.87</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>-1.95</t>
+          <t>-2.06</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
@@ -5512,26 +5512,26 @@
         </is>
       </c>
       <c r="AY11" t="n">
-        <v>46.09</v>
+        <v>46.12</v>
       </c>
       <c r="AZ11" t="n">
-        <v>46.59</v>
+        <v>46.52</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>47.52</t>
+          <t>47.5</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>18.14</t>
+          <t>20.22</t>
         </is>
       </c>
       <c r="BC11" t="n">
-        <v>-0.23</v>
+        <v>-0.21</v>
       </c>
       <c r="BD11" t="n">
-        <v>-0.28</v>
+        <v>-0.26</v>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5540,7 +5540,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>-106.51</t>
+          <t>-106.20</t>
         </is>
       </c>
       <c r="BG11" t="inlineStr">
@@ -5550,43 +5550,43 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>75475.9297752809</t>
+          <t>75378.46704067322</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>3809.0</t>
+          <t>3059.0</t>
         </is>
       </c>
       <c r="BJ11" t="n">
-        <v>4626.6</v>
+        <v>3888.8</v>
       </c>
       <c r="BK11" t="inlineStr">
         <is>
-          <t>4741.3</t>
+          <t>4542.6</t>
         </is>
       </c>
       <c r="BL11" t="n">
-        <v>12259.36</v>
+        <v>12062.18</v>
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>-114</t>
+          <t>-653</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
         <is>
-          <t>-1191.289377825079</t>
+          <t>-1243.615083485966</t>
         </is>
       </c>
       <c r="BO11" t="inlineStr">
         <is>
-          <t>-1543.3847844998</t>
+          <t>-1531.406464620841</t>
         </is>
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>3809.0</t>
+          <t>3059.0</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
@@ -5651,7 +5651,7 @@
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
@@ -5666,7 +5666,7 @@
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>6.12</t>
+          <t>6.15</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
@@ -5676,7 +5676,7 @@
       </c>
       <c r="CH11" t="inlineStr">
         <is>
-          <t>10.2</t>
+          <t>10.16</t>
         </is>
       </c>
       <c r="CI11" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="CK11" t="inlineStr">
         <is>
-          <t>47.76</t>
+          <t>46.96</t>
         </is>
       </c>
       <c r="CL11" t="inlineStr">
         <is>
-          <t>4253</t>
+          <t>4234</t>
         </is>
       </c>
       <c r="CM11" t="inlineStr">
@@ -5716,17 +5716,17 @@
       </c>
       <c r="CP11" t="inlineStr">
         <is>
-          <t>46.2</t>
+          <t>45.8</t>
         </is>
       </c>
       <c r="CQ11" t="inlineStr">
         <is>
-          <t>46.2</t>
+          <t>46.0</t>
         </is>
       </c>
       <c r="CR11" t="inlineStr">
         <is>
-          <t>45.6</t>
+          <t>45.7</t>
         </is>
       </c>
       <c r="CS11" t="inlineStr">
@@ -5763,187 +5763,187 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>83.0</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>45.8</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>-1.78</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>-2.42</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>2025-09-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>2025-09-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>2025-03-06 00:00:00</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>2025-03-10 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>51.1</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>49.75</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>57.7</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>56.5</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>-7.94</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>-9.56</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025/05/23</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>51.4</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>2025/10/14</t>
+        </is>
+      </c>
+      <c r="AD12" t="inlineStr">
+        <is>
+          <t>44.35</t>
+        </is>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>2025/06/30</t>
+        </is>
+      </c>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t>48.2</t>
+        </is>
+      </c>
+      <c r="AG12" t="inlineStr">
+        <is>
+          <t>2025/12/08</t>
+        </is>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>45.05</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>2025/11/19</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>45.05</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>2025-12-02</t>
+        </is>
+      </c>
+      <c r="AL12" t="inlineStr">
+        <is>
+          <t>3.26</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
           <t>-0.43</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>82.0</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>45.8</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>-1.33</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>-20.54</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>2025-09-02 00:00:00</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>2025-09-12 00:00:00</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>2025-03-06 00:00:00</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>2025-03-10 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>51.1</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>49.75</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>57.7</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>56.5</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>-7.94</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>-9.56</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>2025/05/23</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>51.4</t>
-        </is>
-      </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>2025/10/14</t>
-        </is>
-      </c>
-      <c r="AD12" t="inlineStr">
-        <is>
-          <t>44.35</t>
-        </is>
-      </c>
-      <c r="AE12" t="inlineStr">
-        <is>
-          <t>2025/06/30</t>
-        </is>
-      </c>
-      <c r="AF12" t="inlineStr">
-        <is>
-          <t>48.2</t>
-        </is>
-      </c>
-      <c r="AG12" t="inlineStr">
-        <is>
-          <t>2025/12/08</t>
-        </is>
-      </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>45.05</t>
-        </is>
-      </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>2025/11/19</t>
-        </is>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>45.05</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>2025-12-01</t>
-        </is>
-      </c>
-      <c r="AL12" t="inlineStr">
-        <is>
-          <t>3.22</t>
-        </is>
-      </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>0.00</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
@@ -5954,12 +5954,12 @@
       <c r="AO12" t="inlineStr"/>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>89</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
@@ -5969,51 +5969,51 @@
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>83.86</t>
+          <t>89.33</t>
         </is>
       </c>
       <c r="AT12" t="n">
-        <v>0.02</v>
+        <v>-0.17</v>
       </c>
       <c r="AU12" t="n">
-        <v>-0.58</v>
+        <v>-0.46</v>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>-1.87</t>
+          <t>-1.95</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>45.79</t>
+          <t>45.88</t>
         </is>
       </c>
       <c r="AY12" t="n">
-        <v>46.06</v>
+        <v>46.09</v>
       </c>
       <c r="AZ12" t="n">
-        <v>46.64</v>
+        <v>46.59</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>47.53</t>
+          <t>47.52</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>15.60</t>
+          <t>18.14</t>
         </is>
       </c>
       <c r="BC12" t="n">
-        <v>-0.25</v>
+        <v>-0.23</v>
       </c>
       <c r="BD12" t="n">
-        <v>-0.29</v>
+        <v>-0.28</v>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -6022,7 +6022,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>-106.80</t>
+          <t>-106.51</t>
         </is>
       </c>
       <c r="BG12" t="inlineStr">
@@ -6032,43 +6032,43 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>75475.9297752809</t>
+          <t>75378.46704067322</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
         <is>
-          <t>3779.0</t>
+          <t>3809.0</t>
         </is>
       </c>
       <c r="BJ12" t="n">
-        <v>4604</v>
+        <v>4626.6</v>
       </c>
       <c r="BK12" t="inlineStr">
         <is>
-          <t>5794.0</t>
+          <t>4741.3</t>
         </is>
       </c>
       <c r="BL12" t="n">
-        <v>12544.52</v>
+        <v>12259.36</v>
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>-1190</t>
+          <t>-114</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
         <is>
-          <t>-1127.272031156948</t>
+          <t>-1191.289377825079</t>
         </is>
       </c>
       <c r="BO12" t="inlineStr">
         <is>
-          <t>-1585.732927737606</t>
+          <t>-1543.3847844998</t>
         </is>
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>3779.0</t>
+          <t>3809.0</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
@@ -6133,7 +6133,7 @@
       </c>
       <c r="CC12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD12" t="inlineStr">
@@ -6148,7 +6148,7 @@
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>6.12</t>
+          <t>6.15</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
@@ -6158,7 +6158,7 @@
       </c>
       <c r="CH12" t="inlineStr">
         <is>
-          <t>10.2</t>
+          <t>10.16</t>
         </is>
       </c>
       <c r="CI12" t="inlineStr">
@@ -6173,12 +6173,12 @@
       </c>
       <c r="CK12" t="inlineStr">
         <is>
-          <t>47.76</t>
+          <t>46.96</t>
         </is>
       </c>
       <c r="CL12" t="inlineStr">
         <is>
-          <t>4253</t>
+          <t>4234</t>
         </is>
       </c>
       <c r="CM12" t="inlineStr">
@@ -6198,17 +6198,17 @@
       </c>
       <c r="CP12" t="inlineStr">
         <is>
-          <t>46.0</t>
+          <t>46.2</t>
         </is>
       </c>
       <c r="CQ12" t="inlineStr">
         <is>
-          <t>46.05</t>
+          <t>46.2</t>
         </is>
       </c>
       <c r="CR12" t="inlineStr">
         <is>
-          <t>45.55</t>
+          <t>45.6</t>
         </is>
       </c>
       <c r="CS12" t="inlineStr">

--- a/Result/checksun_type/PET膜.xlsx
+++ b/Result/checksun_type/PET膜.xlsx
@@ -943,12 +943,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -958,7 +958,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>44.8</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>17.57</t>
+          <t>-35.30</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -1043,7 +1043,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-9.55</t>
+          <t>-9.95</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -1068,7 +1068,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -1113,17 +1113,17 @@
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>2.95</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
@@ -1139,58 +1139,58 @@
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>75</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>35.29</t>
+          <t>11.76</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>45.1</t>
+          <t>30.84</t>
         </is>
       </c>
       <c r="AT2" t="n">
-        <v>0.02</v>
+        <v>-0.44</v>
       </c>
       <c r="AU2" t="n">
-        <v>-0.85</v>
+        <v>-0.8</v>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>-1.07</t>
+          <t>-0.96</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>-2.67</t>
+          <t>-2.69</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>44.98999999999999</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="AY2" t="n">
-        <v>45.38</v>
+        <v>45.36</v>
       </c>
       <c r="AZ2" t="n">
-        <v>45.86</v>
+        <v>45.8</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>47.12</t>
+          <t>47.07</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-4.09</t>
+          <t>-6.93</t>
         </is>
       </c>
       <c r="BC2" t="n">
-        <v>-0.31</v>
+        <v>-0.32</v>
       </c>
       <c r="BD2" t="n">
         <v>-0.3</v>
@@ -1202,7 +1202,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>-106.93</t>
+          <t>-107.05</t>
         </is>
       </c>
       <c r="BG2" t="inlineStr">
@@ -1212,43 +1212,43 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>75378.46704067322</t>
+          <t>75279.96638655462</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>3990.0</t>
+          <t>3366.0</t>
         </is>
       </c>
       <c r="BJ2" t="n">
-        <v>8019</v>
+        <v>4432.6</v>
       </c>
       <c r="BK2" t="inlineStr">
         <is>
-          <t>6820.6</t>
+          <t>6851.3</t>
         </is>
       </c>
       <c r="BL2" t="n">
-        <v>10934.42</v>
+        <v>10642.9</v>
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>1198</t>
+          <t>-2418</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>-488.82761144805</t>
+          <t>-507.2562798969379</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
         <is>
-          <t>-440.9841865764774</t>
+          <t>-608.6139563658217</t>
         </is>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>3990.0</t>
+          <t>3366.0</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
@@ -1268,7 +1268,7 @@
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>-7.69</t>
+          <t>-8.10</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>6.15</t>
+          <t>6.17</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1338,7 +1338,7 @@
       </c>
       <c r="CH2" t="inlineStr">
         <is>
-          <t>10.16</t>
+          <t>10.11</t>
         </is>
       </c>
       <c r="CI2" t="inlineStr">
@@ -1353,12 +1353,12 @@
       </c>
       <c r="CK2" t="inlineStr">
         <is>
-          <t>46.96</t>
+          <t>46.35</t>
         </is>
       </c>
       <c r="CL2" t="inlineStr">
         <is>
-          <t>4234</t>
+          <t>4215</t>
         </is>
       </c>
       <c r="CM2" t="inlineStr">
@@ -1378,22 +1378,22 @@
       </c>
       <c r="CP2" t="inlineStr">
         <is>
-          <t>45.5</t>
+          <t>44.8</t>
         </is>
       </c>
       <c r="CQ2" t="inlineStr">
         <is>
-          <t>45.5</t>
+          <t>45.1</t>
         </is>
       </c>
       <c r="CR2" t="inlineStr">
         <is>
-          <t>44.6</t>
+          <t>44.55</t>
         </is>
       </c>
       <c r="CS2" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>44.8</t>
         </is>
       </c>
       <c r="CT2" t="inlineStr">
@@ -1425,12 +1425,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.44</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1440,7 +1440,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>45.2</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1450,7 +1450,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -1460,7 +1460,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>20.01</t>
+          <t>17.57</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1525,7 +1525,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-9.15</t>
+          <t>-9.55</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1550,7 +1550,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -1595,17 +1595,17 @@
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>3.07</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>-0.55</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
@@ -1621,61 +1621,61 @@
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>75</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>45.45</t>
+          <t>35.29</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>45.1</t>
         </is>
       </c>
       <c r="AT3" t="n">
-        <v>0.22</v>
+        <v>0.02</v>
       </c>
       <c r="AU3" t="n">
-        <v>-0.58</v>
+        <v>-0.85</v>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>-1.27</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>-2.57</t>
+          <t>-2.67</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>45.1</t>
+          <t>44.98999999999999</t>
         </is>
       </c>
       <c r="AY3" t="n">
-        <v>45.36</v>
+        <v>45.38</v>
       </c>
       <c r="AZ3" t="n">
-        <v>45.95</v>
+        <v>45.86</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>47.16</t>
+          <t>47.12</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-4.49</t>
+          <t>-4.09</t>
         </is>
       </c>
       <c r="BC3" t="n">
         <v>-0.31</v>
       </c>
       <c r="BD3" t="n">
-        <v>-0.29</v>
+        <v>-0.3</v>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1684,7 +1684,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>-106.86</t>
+          <t>-106.93</t>
         </is>
       </c>
       <c r="BG3" t="inlineStr">
@@ -1694,43 +1694,43 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>75378.46704067322</t>
+          <t>75279.96638655462</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>3539.0</t>
+          <t>3990.0</t>
         </is>
       </c>
       <c r="BJ3" t="n">
-        <v>8163.8</v>
+        <v>8019</v>
       </c>
       <c r="BK3" t="inlineStr">
         <is>
-          <t>6802.5</t>
+          <t>6820.6</t>
         </is>
       </c>
       <c r="BL3" t="n">
-        <v>11065.56</v>
+        <v>10934.42</v>
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>1361</t>
+          <t>1198</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>-497.5264159701541</t>
+          <t>-488.82761144805</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
         <is>
-          <t>-252.6207944996822</t>
+          <t>-440.9841865764774</t>
         </is>
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>3539.0</t>
+          <t>3990.0</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
@@ -1750,7 +1750,7 @@
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>-7.28</t>
+          <t>-7.69</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1795,22 +1795,22 @@
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>6.15</t>
+          <t>6.17</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="CH3" t="inlineStr">
         <is>
-          <t>10.16</t>
+          <t>10.11</t>
         </is>
       </c>
       <c r="CI3" t="inlineStr">
@@ -1835,12 +1835,12 @@
       </c>
       <c r="CK3" t="inlineStr">
         <is>
-          <t>46.96</t>
+          <t>46.35</t>
         </is>
       </c>
       <c r="CL3" t="inlineStr">
         <is>
-          <t>4234</t>
+          <t>4215</t>
         </is>
       </c>
       <c r="CM3" t="inlineStr">
@@ -1860,22 +1860,22 @@
       </c>
       <c r="CP3" t="inlineStr">
         <is>
-          <t>45.05</t>
+          <t>45.5</t>
         </is>
       </c>
       <c r="CQ3" t="inlineStr">
         <is>
-          <t>45.6</t>
+          <t>45.5</t>
         </is>
       </c>
       <c r="CR3" t="inlineStr">
         <is>
-          <t>45.05</t>
+          <t>44.6</t>
         </is>
       </c>
       <c r="CS3" t="inlineStr">
         <is>
-          <t>45.2</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="CT3" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>143.0</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1922,7 +1922,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>45.3</t>
+          <t>45.2</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>-0.89</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1942,7 +1942,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>41.55</t>
+          <t>20.01</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -2007,7 +2007,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-8.94</t>
+          <t>-9.15</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -2032,7 +2032,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -2077,17 +2077,17 @@
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>5.62</t>
+          <t>3.07</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>-0.55</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
@@ -2103,58 +2103,58 @@
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>75</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>54.55</t>
+          <t>45.45</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>18.18</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AT4" t="n">
-        <v>0.51</v>
+        <v>0.22</v>
       </c>
       <c r="AU4" t="n">
-        <v>-0.8</v>
+        <v>-0.58</v>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>-1.32</t>
+          <t>-1.27</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>-2.47</t>
+          <t>-2.57</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>45.07000000000001</t>
+          <t>45.1</t>
         </is>
       </c>
       <c r="AY4" t="n">
-        <v>45.44</v>
+        <v>45.36</v>
       </c>
       <c r="AZ4" t="n">
-        <v>46.04</v>
+        <v>45.95</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>47.21</t>
+          <t>47.16</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-10.29</t>
+          <t>-4.49</t>
         </is>
       </c>
       <c r="BC4" t="n">
-        <v>-0.32</v>
+        <v>-0.31</v>
       </c>
       <c r="BD4" t="n">
         <v>-0.29</v>
@@ -2166,7 +2166,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>-106.78</t>
+          <t>-106.86</t>
         </is>
       </c>
       <c r="BG4" t="inlineStr">
@@ -2176,43 +2176,43 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>75378.46704067322</t>
+          <t>75279.96638655462</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>6423.0</t>
+          <t>3539.0</t>
         </is>
       </c>
       <c r="BJ4" t="n">
-        <v>9662.799999999999</v>
+        <v>8163.8</v>
       </c>
       <c r="BK4" t="inlineStr">
         <is>
-          <t>6826.5</t>
+          <t>6802.5</t>
         </is>
       </c>
       <c r="BL4" t="n">
-        <v>11523.86</v>
+        <v>11065.56</v>
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>2836</t>
+          <t>1361</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>-542.0547107829672</t>
+          <t>-497.5264159701541</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>73.8133654135845</t>
+          <t>-252.6207944996822</t>
         </is>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>6423.0</t>
+          <t>3539.0</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
@@ -2232,7 +2232,7 @@
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>-7.08</t>
+          <t>-7.28</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2277,22 +2277,22 @@
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>6.15</t>
+          <t>6.17</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2302,7 +2302,7 @@
       </c>
       <c r="CH4" t="inlineStr">
         <is>
-          <t>10.16</t>
+          <t>10.11</t>
         </is>
       </c>
       <c r="CI4" t="inlineStr">
@@ -2317,12 +2317,12 @@
       </c>
       <c r="CK4" t="inlineStr">
         <is>
-          <t>46.96</t>
+          <t>46.35</t>
         </is>
       </c>
       <c r="CL4" t="inlineStr">
         <is>
-          <t>4234</t>
+          <t>4215</t>
         </is>
       </c>
       <c r="CM4" t="inlineStr">
@@ -2342,22 +2342,22 @@
       </c>
       <c r="CP4" t="inlineStr">
         <is>
-          <t>44.8</t>
+          <t>45.05</t>
         </is>
       </c>
       <c r="CQ4" t="inlineStr">
         <is>
-          <t>45.3</t>
+          <t>45.6</t>
         </is>
       </c>
       <c r="CR4" t="inlineStr">
         <is>
-          <t>44.75</t>
+          <t>45.05</t>
         </is>
       </c>
       <c r="CS4" t="inlineStr">
         <is>
-          <t>45.3</t>
+          <t>45.2</t>
         </is>
       </c>
       <c r="CT4" t="inlineStr">
@@ -2389,12 +2389,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>109.0</t>
+          <t>143.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>44.7</t>
+          <t>45.3</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2414,7 +2414,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>-1.12</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -2424,7 +2424,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>42.69</t>
+          <t>41.55</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2489,7 +2489,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-10.15</t>
+          <t>-8.94</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2514,7 +2514,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -2559,17 +2559,17 @@
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>4.28</t>
+          <t>5.62</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
@@ -2585,61 +2585,61 @@
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>75</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>54.55</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>17.54</t>
+          <t>18.18</t>
         </is>
       </c>
       <c r="AT5" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="AU5" t="n">
         <v>-0.8</v>
       </c>
-      <c r="AU5" t="n">
-        <v>-1.02</v>
-      </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>-1.27</t>
+          <t>-1.32</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>-2.44</t>
+          <t>-2.47</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>45.06</t>
+          <t>45.07000000000001</t>
         </is>
       </c>
       <c r="AY5" t="n">
-        <v>45.52</v>
+        <v>45.44</v>
       </c>
       <c r="AZ5" t="n">
-        <v>46.11</v>
+        <v>46.04</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>47.26</t>
+          <t>47.21</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-21.20</t>
+          <t>-10.29</t>
         </is>
       </c>
       <c r="BC5" t="n">
-        <v>-0.34</v>
+        <v>-0.32</v>
       </c>
       <c r="BD5" t="n">
-        <v>-0.28</v>
+        <v>-0.29</v>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>-106.61</t>
+          <t>-106.78</t>
         </is>
       </c>
       <c r="BG5" t="inlineStr">
@@ -2658,43 +2658,43 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>75378.46704067322</t>
+          <t>75279.96638655462</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>4845.0</t>
+          <t>6423.0</t>
         </is>
       </c>
       <c r="BJ5" t="n">
-        <v>9321</v>
+        <v>9662.799999999999</v>
       </c>
       <c r="BK5" t="inlineStr">
         <is>
-          <t>6532.2</t>
+          <t>6826.5</t>
         </is>
       </c>
       <c r="BL5" t="n">
-        <v>11521.76</v>
+        <v>11523.86</v>
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>2788</t>
+          <t>2836</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>-654.0307246368856</t>
+          <t>-542.0547107829672</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>228.5116879534808</t>
+          <t>73.8133654135845</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>4845.0</t>
+          <t>6423.0</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
@@ -2714,7 +2714,7 @@
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>-8.31</t>
+          <t>-7.08</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2759,7 +2759,7 @@
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
@@ -2769,12 +2769,12 @@
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>1.84</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>6.15</t>
+          <t>6.17</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2784,7 +2784,7 @@
       </c>
       <c r="CH5" t="inlineStr">
         <is>
-          <t>10.16</t>
+          <t>10.11</t>
         </is>
       </c>
       <c r="CI5" t="inlineStr">
@@ -2799,12 +2799,12 @@
       </c>
       <c r="CK5" t="inlineStr">
         <is>
-          <t>46.96</t>
+          <t>46.35</t>
         </is>
       </c>
       <c r="CL5" t="inlineStr">
         <is>
-          <t>4234</t>
+          <t>4215</t>
         </is>
       </c>
       <c r="CM5" t="inlineStr">
@@ -2824,22 +2824,22 @@
       </c>
       <c r="CP5" t="inlineStr">
         <is>
+          <t>44.8</t>
+        </is>
+      </c>
+      <c r="CQ5" t="inlineStr">
+        <is>
+          <t>45.3</t>
+        </is>
+      </c>
+      <c r="CR5" t="inlineStr">
+        <is>
           <t>44.75</t>
         </is>
       </c>
-      <c r="CQ5" t="inlineStr">
-        <is>
-          <t>44.75</t>
-        </is>
-      </c>
-      <c r="CR5" t="inlineStr">
-        <is>
-          <t>44.5</t>
-        </is>
-      </c>
       <c r="CS5" t="inlineStr">
         <is>
-          <t>44.7</t>
+          <t>45.3</t>
         </is>
       </c>
       <c r="CT5" t="inlineStr">
@@ -2871,12 +2871,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-1.8</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>478.0</t>
+          <t>109.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2886,7 +2886,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>44.75</t>
+          <t>44.7</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2896,7 +2896,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -2906,7 +2906,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>40.89</t>
+          <t>42.69</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-10.05</t>
+          <t>-10.15</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2996,7 +2996,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -3041,17 +3041,17 @@
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>18.79</t>
+          <t>4.28</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
@@ -3067,7 +3067,7 @@
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>75</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
@@ -3081,47 +3081,47 @@
         </is>
       </c>
       <c r="AT6" t="n">
-        <v>-1.04</v>
+        <v>-0.8</v>
       </c>
       <c r="AU6" t="n">
-        <v>-0.93</v>
+        <v>-1.02</v>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>-1.16</t>
+          <t>-1.27</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>-2.39</t>
+          <t>-2.44</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>45.21999999999999</t>
+          <t>45.06</t>
         </is>
       </c>
       <c r="AY6" t="n">
-        <v>45.64</v>
+        <v>45.52</v>
       </c>
       <c r="AZ6" t="n">
-        <v>46.18</v>
+        <v>46.11</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>47.31</t>
+          <t>47.26</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-14.07</t>
+          <t>-21.20</t>
         </is>
       </c>
       <c r="BC6" t="n">
-        <v>-0.31</v>
+        <v>-0.34</v>
       </c>
       <c r="BD6" t="n">
-        <v>-0.27</v>
+        <v>-0.28</v>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -3130,7 +3130,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>-106.26</t>
+          <t>-106.61</t>
         </is>
       </c>
       <c r="BG6" t="inlineStr">
@@ -3140,43 +3140,43 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>75378.46704067322</t>
+          <t>75279.96638655462</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>21298.0</t>
+          <t>4845.0</t>
         </is>
       </c>
       <c r="BJ6" t="n">
-        <v>9270</v>
+        <v>9321</v>
       </c>
       <c r="BK6" t="inlineStr">
         <is>
-          <t>6579.4</t>
+          <t>6532.2</t>
         </is>
       </c>
       <c r="BL6" t="n">
-        <v>11878.36</v>
+        <v>11521.76</v>
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>2690</t>
+          <t>2788</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
         <is>
-          <t>-814.4929814714977</t>
+          <t>-654.0307246368856</t>
         </is>
       </c>
       <c r="BO6" t="inlineStr">
         <is>
-          <t>610.419588440709</t>
+          <t>228.5116879534808</t>
         </is>
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>21298.0</t>
+          <t>4845.0</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
@@ -3196,7 +3196,7 @@
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>-8.21</t>
+          <t>-8.31</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -3241,12 +3241,12 @@
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
@@ -3256,7 +3256,7 @@
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>6.15</t>
+          <t>6.17</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -3266,7 +3266,7 @@
       </c>
       <c r="CH6" t="inlineStr">
         <is>
-          <t>10.16</t>
+          <t>10.11</t>
         </is>
       </c>
       <c r="CI6" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="CK6" t="inlineStr">
         <is>
-          <t>46.96</t>
+          <t>46.35</t>
         </is>
       </c>
       <c r="CL6" t="inlineStr">
         <is>
-          <t>4234</t>
+          <t>4215</t>
         </is>
       </c>
       <c r="CM6" t="inlineStr">
@@ -3306,22 +3306,22 @@
       </c>
       <c r="CP6" t="inlineStr">
         <is>
-          <t>44.55</t>
+          <t>44.75</t>
         </is>
       </c>
       <c r="CQ6" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>44.75</t>
         </is>
       </c>
       <c r="CR6" t="inlineStr">
         <is>
-          <t>44.3</t>
+          <t>44.5</t>
         </is>
       </c>
       <c r="CS6" t="inlineStr">
         <is>
-          <t>44.75</t>
+          <t>44.7</t>
         </is>
       </c>
       <c r="CT6" t="inlineStr">
@@ -3353,12 +3353,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>-1.8</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>478.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3368,7 +3368,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>45.55</t>
+          <t>44.75</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3378,7 +3378,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-1.22</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -3388,7 +3388,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>9.71</t>
+          <t>40.89</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3453,7 +3453,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-8.44</t>
+          <t>-10.05</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -3523,17 +3523,17 @@
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>4.05</t>
+          <t>18.79</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>-1.09</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>75</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>52.63</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3563,47 +3563,47 @@
         </is>
       </c>
       <c r="AT7" t="n">
-        <v>0.26</v>
+        <v>-1.04</v>
       </c>
       <c r="AU7" t="n">
-        <v>-0.78</v>
+        <v>-0.93</v>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>-1.04</t>
+          <t>-1.16</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>-2.32</t>
+          <t>-2.39</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>45.42999999999999</t>
+          <t>45.21999999999999</t>
         </is>
       </c>
       <c r="AY7" t="n">
-        <v>45.78</v>
+        <v>45.64</v>
       </c>
       <c r="AZ7" t="n">
-        <v>46.27</v>
+        <v>46.18</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>47.37</t>
+          <t>47.31</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-14.07</t>
         </is>
       </c>
       <c r="BC7" t="n">
-        <v>-0.26</v>
+        <v>-0.31</v>
       </c>
       <c r="BD7" t="n">
-        <v>-0.26</v>
+        <v>-0.27</v>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>-106.04</t>
+          <t>-106.26</t>
         </is>
       </c>
       <c r="BG7" t="inlineStr">
@@ -3622,43 +3622,43 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>75378.46704067322</t>
+          <t>75279.96638655462</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>4714.0</t>
+          <t>21298.0</t>
         </is>
       </c>
       <c r="BJ7" t="n">
-        <v>5622.2</v>
+        <v>9270</v>
       </c>
       <c r="BK7" t="inlineStr">
         <is>
-          <t>5124.4</t>
+          <t>6579.4</t>
         </is>
       </c>
       <c r="BL7" t="n">
-        <v>11707.74</v>
+        <v>11878.36</v>
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>497</t>
+          <t>2690</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
         <is>
-          <t>-1073.567994182808</t>
+          <t>-814.4929814714977</t>
         </is>
       </c>
       <c r="BO7" t="inlineStr">
         <is>
-          <t>-628.6198247361344</t>
+          <t>610.419588440709</t>
         </is>
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>4714.0</t>
+          <t>21298.0</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
@@ -3678,7 +3678,7 @@
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>-6.56</t>
+          <t>-8.21</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3723,22 +3723,22 @@
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>6.15</t>
+          <t>6.17</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3748,7 +3748,7 @@
       </c>
       <c r="CH7" t="inlineStr">
         <is>
-          <t>10.16</t>
+          <t>10.11</t>
         </is>
       </c>
       <c r="CI7" t="inlineStr">
@@ -3763,12 +3763,12 @@
       </c>
       <c r="CK7" t="inlineStr">
         <is>
-          <t>46.96</t>
+          <t>46.35</t>
         </is>
       </c>
       <c r="CL7" t="inlineStr">
         <is>
-          <t>4234</t>
+          <t>4215</t>
         </is>
       </c>
       <c r="CM7" t="inlineStr">
@@ -3788,22 +3788,22 @@
       </c>
       <c r="CP7" t="inlineStr">
         <is>
-          <t>45.65</t>
+          <t>44.55</t>
         </is>
       </c>
       <c r="CQ7" t="inlineStr">
         <is>
-          <t>46.3</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="CR7" t="inlineStr">
         <is>
-          <t>45.3</t>
+          <t>44.3</t>
         </is>
       </c>
       <c r="CS7" t="inlineStr">
         <is>
-          <t>45.55</t>
+          <t>44.75</t>
         </is>
       </c>
       <c r="CT7" t="inlineStr">
@@ -3835,12 +3835,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>246.0</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3850,172 +3850,172 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
+          <t>45.55</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>-1.67</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>9.71</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>2025-09-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>2025-09-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>2025-03-06 00:00:00</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>2025-03-10 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>51.1</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>49.75</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>57.7</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>56.5</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>-8.44</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>-9.56</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025/05/23</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>51.4</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>0.02</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>2025/10/14</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>44.35</t>
+        </is>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>2025/06/30</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>48.2</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>2025/12/08</t>
+        </is>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
           <t>45.05</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>-0.11</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>8.33</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>2025-09-02 00:00:00</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>2025-09-12 00:00:00</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>2025-03-06 00:00:00</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>2025-03-10 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>51.1</t>
-        </is>
-      </c>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t>49.75</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>57.7</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>56.5</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>-9.45</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>-9.56</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>2025/05/23</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>51.4</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>-0.03</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>2025/10/14</t>
-        </is>
-      </c>
-      <c r="AD8" t="inlineStr">
-        <is>
-          <t>44.35</t>
-        </is>
-      </c>
-      <c r="AE8" t="inlineStr">
-        <is>
-          <t>2025/06/30</t>
-        </is>
-      </c>
-      <c r="AF8" t="inlineStr">
-        <is>
-          <t>48.2</t>
-        </is>
-      </c>
-      <c r="AG8" t="inlineStr">
-        <is>
-          <t>2025/12/08</t>
-        </is>
-      </c>
-      <c r="AH8" t="inlineStr">
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>2025/11/19</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
         <is>
           <t>45.05</t>
         </is>
       </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>2025/11/19</t>
-        </is>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>45.05</t>
-        </is>
-      </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>9.67</t>
+          <t>4.05</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>-1.09</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
@@ -4031,58 +4031,58 @@
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>75</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>52.63</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>9.52</t>
+          <t>17.54</t>
         </is>
       </c>
       <c r="AT8" t="n">
-        <v>-0.95</v>
+        <v>0.26</v>
       </c>
       <c r="AU8" t="n">
-        <v>-0.87</v>
+        <v>-0.78</v>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>-0.97</t>
+          <t>-1.04</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>-2.29</t>
+          <t>-2.32</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>45.48</t>
+          <t>45.42999999999999</t>
         </is>
       </c>
       <c r="AY8" t="n">
-        <v>45.88</v>
+        <v>45.78</v>
       </c>
       <c r="AZ8" t="n">
-        <v>46.32</v>
+        <v>46.27</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>47.41</t>
+          <t>47.37</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-7.02</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="BC8" t="n">
-        <v>-0.28</v>
+        <v>-0.26</v>
       </c>
       <c r="BD8" t="n">
         <v>-0.26</v>
@@ -4104,43 +4104,43 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>75378.46704067322</t>
+          <t>75279.96638655462</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>11034.0</t>
+          <t>4714.0</t>
         </is>
       </c>
       <c r="BJ8" t="n">
-        <v>5441.2</v>
+        <v>5622.2</v>
       </c>
       <c r="BK8" t="inlineStr">
         <is>
-          <t>5022.6</t>
+          <t>5124.4</t>
         </is>
       </c>
       <c r="BL8" t="n">
-        <v>11858.6</v>
+        <v>11707.74</v>
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>418</t>
+          <t>497</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
         <is>
-          <t>-1154.46766135493</t>
+          <t>-1073.567994182808</t>
         </is>
       </c>
       <c r="BO8" t="inlineStr">
         <is>
-          <t>-599.3682783910481</t>
+          <t>-628.6198247361344</t>
         </is>
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>11034.0</t>
+          <t>4714.0</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
@@ -4160,7 +4160,7 @@
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>-7.59</t>
+          <t>-6.56</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -4205,22 +4205,22 @@
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>6.15</t>
+          <t>6.17</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -4230,7 +4230,7 @@
       </c>
       <c r="CH8" t="inlineStr">
         <is>
-          <t>10.16</t>
+          <t>10.11</t>
         </is>
       </c>
       <c r="CI8" t="inlineStr">
@@ -4245,12 +4245,12 @@
       </c>
       <c r="CK8" t="inlineStr">
         <is>
-          <t>46.96</t>
+          <t>46.35</t>
         </is>
       </c>
       <c r="CL8" t="inlineStr">
         <is>
-          <t>4234</t>
+          <t>4215</t>
         </is>
       </c>
       <c r="CM8" t="inlineStr">
@@ -4270,22 +4270,22 @@
       </c>
       <c r="CP8" t="inlineStr">
         <is>
-          <t>45.25</t>
+          <t>45.65</t>
         </is>
       </c>
       <c r="CQ8" t="inlineStr">
         <is>
-          <t>45.45</t>
+          <t>46.3</t>
         </is>
       </c>
       <c r="CR8" t="inlineStr">
         <is>
-          <t>44.5</t>
+          <t>45.3</t>
         </is>
       </c>
       <c r="CS8" t="inlineStr">
         <is>
-          <t>45.05</t>
+          <t>45.55</t>
         </is>
       </c>
       <c r="CT8" t="inlineStr">
@@ -4307,7 +4307,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>【d2】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-0.55</t>
+          <t>-0.44</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>104.0</t>
+          <t>246.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -4332,7 +4332,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>45.25</t>
+          <t>45.05</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -4352,7 +4352,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-8.48</t>
+          <t>8.33</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4417,7 +4417,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-9.05</t>
+          <t>-9.45</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4487,17 +4487,17 @@
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>4.09</t>
+          <t>9.67</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
@@ -4513,7 +4513,7 @@
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>75</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
@@ -4523,51 +4523,51 @@
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>37.52</t>
+          <t>9.52</t>
         </is>
       </c>
       <c r="AT9" t="n">
-        <v>-0.83</v>
+        <v>-0.95</v>
       </c>
       <c r="AU9" t="n">
-        <v>-0.75</v>
+        <v>-0.87</v>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>-0.9</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>-2.24</t>
+          <t>-2.29</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>45.63</t>
+          <t>45.48</t>
         </is>
       </c>
       <c r="AY9" t="n">
-        <v>45.98</v>
+        <v>45.88</v>
       </c>
       <c r="AZ9" t="n">
-        <v>46.39</v>
+        <v>46.32</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>47.46</t>
+          <t>47.41</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>3.73</t>
+          <t>-7.02</t>
         </is>
       </c>
       <c r="BC9" t="n">
-        <v>-0.24</v>
+        <v>-0.28</v>
       </c>
       <c r="BD9" t="n">
-        <v>-0.25</v>
+        <v>-0.26</v>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4576,7 +4576,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>-105.93</t>
+          <t>-106.04</t>
         </is>
       </c>
       <c r="BG9" t="inlineStr">
@@ -4586,43 +4586,43 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>75378.46704067322</t>
+          <t>75279.96638655462</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>4714.0</t>
+          <t>11034.0</t>
         </is>
       </c>
       <c r="BJ9" t="n">
-        <v>3990.2</v>
+        <v>5441.2</v>
       </c>
       <c r="BK9" t="inlineStr">
         <is>
-          <t>4360.0</t>
+          <t>5022.6</t>
         </is>
       </c>
       <c r="BL9" t="n">
-        <v>11948.92</v>
+        <v>11858.6</v>
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>-369</t>
+          <t>418</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
         <is>
-          <t>-1255.394821893818</t>
+          <t>-1154.46766135493</t>
         </is>
       </c>
       <c r="BO9" t="inlineStr">
         <is>
-          <t>-1213.317202241243</t>
+          <t>-599.3682783910481</t>
         </is>
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>4714.0</t>
+          <t>11034.0</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
@@ -4642,7 +4642,7 @@
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>-7.18</t>
+          <t>-7.59</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4687,12 +4687,12 @@
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
@@ -4702,7 +4702,7 @@
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>6.15</t>
+          <t>6.17</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4712,7 +4712,7 @@
       </c>
       <c r="CH9" t="inlineStr">
         <is>
-          <t>10.16</t>
+          <t>10.11</t>
         </is>
       </c>
       <c r="CI9" t="inlineStr">
@@ -4727,12 +4727,12 @@
       </c>
       <c r="CK9" t="inlineStr">
         <is>
-          <t>46.96</t>
+          <t>46.35</t>
         </is>
       </c>
       <c r="CL9" t="inlineStr">
         <is>
-          <t>4234</t>
+          <t>4215</t>
         </is>
       </c>
       <c r="CM9" t="inlineStr">
@@ -4752,22 +4752,22 @@
       </c>
       <c r="CP9" t="inlineStr">
         <is>
-          <t>45.5</t>
+          <t>45.25</t>
         </is>
       </c>
       <c r="CQ9" t="inlineStr">
         <is>
-          <t>45.5</t>
+          <t>45.45</t>
         </is>
       </c>
       <c r="CR9" t="inlineStr">
         <is>
-          <t>44.9</t>
+          <t>44.5</t>
         </is>
       </c>
       <c r="CS9" t="inlineStr">
         <is>
-          <t>45.25</t>
+          <t>45.05</t>
         </is>
       </c>
       <c r="CT9" t="inlineStr">
@@ -4799,12 +4799,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>-0.55</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>104.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4814,7 +4814,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>45.5</t>
+          <t>45.25</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4824,7 +4824,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-1.11</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -4834,7 +4834,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-20.03</t>
+          <t>-8.48</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4899,7 +4899,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-8.54</t>
+          <t>-9.05</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4924,7 +4924,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -4969,17 +4969,17 @@
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>3.97</t>
+          <t>4.09</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
@@ -4995,61 +4995,61 @@
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>75</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>28.57</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>65.52</t>
+          <t>37.52</t>
         </is>
       </c>
       <c r="AT10" t="n">
-        <v>-0.61</v>
+        <v>-0.83</v>
       </c>
       <c r="AU10" t="n">
-        <v>-0.58</v>
+        <v>-0.75</v>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>-0.89</t>
+          <t>-0.9</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>-2.14</t>
+          <t>-2.24</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>45.77999999999999</t>
+          <t>45.63</t>
         </is>
       </c>
       <c r="AY10" t="n">
-        <v>46.04</v>
+        <v>45.98</v>
       </c>
       <c r="AZ10" t="n">
-        <v>46.46</v>
+        <v>46.39</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>47.48</t>
+          <t>47.46</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>14.06</t>
+          <t>3.73</t>
         </is>
       </c>
       <c r="BC10" t="n">
-        <v>-0.22</v>
+        <v>-0.24</v>
       </c>
       <c r="BD10" t="n">
-        <v>-0.26</v>
+        <v>-0.25</v>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -5058,7 +5058,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>-105.99</t>
+          <t>-105.93</t>
         </is>
       </c>
       <c r="BG10" t="inlineStr">
@@ -5068,43 +5068,43 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>75378.46704067322</t>
+          <t>75279.96638655462</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>4590.0</t>
+          <t>4714.0</t>
         </is>
       </c>
       <c r="BJ10" t="n">
-        <v>3743.4</v>
+        <v>3990.2</v>
       </c>
       <c r="BK10" t="inlineStr">
         <is>
-          <t>4681.2</t>
+          <t>4360.0</t>
         </is>
       </c>
       <c r="BL10" t="n">
-        <v>12007.9</v>
+        <v>11948.92</v>
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>-937</t>
+          <t>-369</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
         <is>
-          <t>-1263.045298194286</t>
+          <t>-1255.394821893818</t>
         </is>
       </c>
       <c r="BO10" t="inlineStr">
         <is>
-          <t>-1369.911479090048</t>
+          <t>-1213.317202241243</t>
         </is>
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>4590.0</t>
+          <t>4714.0</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
@@ -5124,7 +5124,7 @@
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>-6.67</t>
+          <t>-7.18</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -5169,7 +5169,7 @@
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
@@ -5179,12 +5179,12 @@
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>6.15</t>
+          <t>6.17</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -5194,7 +5194,7 @@
       </c>
       <c r="CH10" t="inlineStr">
         <is>
-          <t>10.16</t>
+          <t>10.11</t>
         </is>
       </c>
       <c r="CI10" t="inlineStr">
@@ -5209,12 +5209,12 @@
       </c>
       <c r="CK10" t="inlineStr">
         <is>
-          <t>46.96</t>
+          <t>46.35</t>
         </is>
       </c>
       <c r="CL10" t="inlineStr">
         <is>
-          <t>4234</t>
+          <t>4215</t>
         </is>
       </c>
       <c r="CM10" t="inlineStr">
@@ -5234,22 +5234,22 @@
       </c>
       <c r="CP10" t="inlineStr">
         <is>
-          <t>46.0</t>
+          <t>45.5</t>
         </is>
       </c>
       <c r="CQ10" t="inlineStr">
         <is>
-          <t>46.05</t>
+          <t>45.5</t>
         </is>
       </c>
       <c r="CR10" t="inlineStr">
         <is>
-          <t>45.15</t>
+          <t>44.9</t>
         </is>
       </c>
       <c r="CS10" t="inlineStr">
         <is>
-          <t>45.5</t>
+          <t>45.25</t>
         </is>
       </c>
       <c r="CT10" t="inlineStr">
@@ -5281,42 +5281,42 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
+          <t>-0.65</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>101.0</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>45.5</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>-1.56</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>67.0</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>45.8</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>-1.78</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-14.39</t>
+          <t>-20.03</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -5381,7 +5381,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-7.94</t>
+          <t>-8.54</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -5406,7 +5406,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -5451,17 +5451,17 @@
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>2.63</t>
+          <t>3.97</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
@@ -5477,58 +5477,58 @@
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>75</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>28.57</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>65.52</t>
         </is>
       </c>
       <c r="AT11" t="n">
-        <v>-0.17</v>
+        <v>-0.61</v>
       </c>
       <c r="AU11" t="n">
-        <v>-0.52</v>
+        <v>-0.58</v>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>-0.87</t>
+          <t>-0.89</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>-2.06</t>
+          <t>-2.14</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>45.88</t>
+          <t>45.77999999999999</t>
         </is>
       </c>
       <c r="AY11" t="n">
-        <v>46.12</v>
+        <v>46.04</v>
       </c>
       <c r="AZ11" t="n">
-        <v>46.52</v>
+        <v>46.46</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>47.5</t>
+          <t>47.48</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>20.22</t>
+          <t>14.06</t>
         </is>
       </c>
       <c r="BC11" t="n">
-        <v>-0.21</v>
+        <v>-0.22</v>
       </c>
       <c r="BD11" t="n">
         <v>-0.26</v>
@@ -5540,7 +5540,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>-106.20</t>
+          <t>-105.99</t>
         </is>
       </c>
       <c r="BG11" t="inlineStr">
@@ -5550,43 +5550,43 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>75378.46704067322</t>
+          <t>75279.96638655462</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>3059.0</t>
+          <t>4590.0</t>
         </is>
       </c>
       <c r="BJ11" t="n">
-        <v>3888.8</v>
+        <v>3743.4</v>
       </c>
       <c r="BK11" t="inlineStr">
         <is>
-          <t>4542.6</t>
+          <t>4681.2</t>
         </is>
       </c>
       <c r="BL11" t="n">
-        <v>12062.18</v>
+        <v>12007.9</v>
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>-653</t>
+          <t>-937</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
         <is>
-          <t>-1243.615083485966</t>
+          <t>-1263.045298194286</t>
         </is>
       </c>
       <c r="BO11" t="inlineStr">
         <is>
-          <t>-1531.406464620841</t>
+          <t>-1369.911479090048</t>
         </is>
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>3059.0</t>
+          <t>4590.0</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
@@ -5606,7 +5606,7 @@
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>-6.05</t>
+          <t>-6.67</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5651,7 +5651,7 @@
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
@@ -5661,12 +5661,12 @@
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>6.15</t>
+          <t>6.17</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
@@ -5676,7 +5676,7 @@
       </c>
       <c r="CH11" t="inlineStr">
         <is>
-          <t>10.16</t>
+          <t>10.11</t>
         </is>
       </c>
       <c r="CI11" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="CK11" t="inlineStr">
         <is>
-          <t>46.96</t>
+          <t>46.35</t>
         </is>
       </c>
       <c r="CL11" t="inlineStr">
         <is>
-          <t>4234</t>
+          <t>4215</t>
         </is>
       </c>
       <c r="CM11" t="inlineStr">
@@ -5716,22 +5716,22 @@
       </c>
       <c r="CP11" t="inlineStr">
         <is>
-          <t>45.8</t>
+          <t>46.0</t>
         </is>
       </c>
       <c r="CQ11" t="inlineStr">
         <is>
-          <t>46.0</t>
+          <t>46.05</t>
         </is>
       </c>
       <c r="CR11" t="inlineStr">
         <is>
-          <t>45.7</t>
+          <t>45.15</t>
         </is>
       </c>
       <c r="CS11" t="inlineStr">
         <is>
-          <t>45.8</t>
+          <t>45.5</t>
         </is>
       </c>
       <c r="CT11" t="inlineStr">
@@ -5768,7 +5768,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5788,7 +5788,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-1.78</t>
+          <t>-2.23</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -5798,7 +5798,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-2.42</t>
+          <t>-14.39</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5888,7 +5888,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -5933,17 +5933,17 @@
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>3.26</t>
+          <t>2.63</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
@@ -5959,7 +5959,7 @@
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>75</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
@@ -5969,23 +5969,23 @@
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>89.33</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AT12" t="n">
         <v>-0.17</v>
       </c>
       <c r="AU12" t="n">
-        <v>-0.46</v>
+        <v>-0.52</v>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>-1.07</t>
+          <t>-0.87</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>-1.95</t>
+          <t>-2.06</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
@@ -5994,26 +5994,26 @@
         </is>
       </c>
       <c r="AY12" t="n">
-        <v>46.09</v>
+        <v>46.12</v>
       </c>
       <c r="AZ12" t="n">
-        <v>46.59</v>
+        <v>46.52</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>47.52</t>
+          <t>47.5</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>18.14</t>
+          <t>20.22</t>
         </is>
       </c>
       <c r="BC12" t="n">
-        <v>-0.23</v>
+        <v>-0.21</v>
       </c>
       <c r="BD12" t="n">
-        <v>-0.28</v>
+        <v>-0.26</v>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -6022,7 +6022,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>-106.51</t>
+          <t>-106.20</t>
         </is>
       </c>
       <c r="BG12" t="inlineStr">
@@ -6032,43 +6032,43 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>75378.46704067322</t>
+          <t>75279.96638655462</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
         <is>
-          <t>3809.0</t>
+          <t>3059.0</t>
         </is>
       </c>
       <c r="BJ12" t="n">
-        <v>4626.6</v>
+        <v>3888.8</v>
       </c>
       <c r="BK12" t="inlineStr">
         <is>
-          <t>4741.3</t>
+          <t>4542.6</t>
         </is>
       </c>
       <c r="BL12" t="n">
-        <v>12259.36</v>
+        <v>12062.18</v>
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>-114</t>
+          <t>-653</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
         <is>
-          <t>-1191.289377825079</t>
+          <t>-1243.615083485966</t>
         </is>
       </c>
       <c r="BO12" t="inlineStr">
         <is>
-          <t>-1543.3847844998</t>
+          <t>-1531.406464620841</t>
         </is>
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>3809.0</t>
+          <t>3059.0</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
@@ -6133,7 +6133,7 @@
       </c>
       <c r="CC12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD12" t="inlineStr">
@@ -6148,7 +6148,7 @@
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>6.15</t>
+          <t>6.17</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
@@ -6158,7 +6158,7 @@
       </c>
       <c r="CH12" t="inlineStr">
         <is>
-          <t>10.16</t>
+          <t>10.11</t>
         </is>
       </c>
       <c r="CI12" t="inlineStr">
@@ -6173,12 +6173,12 @@
       </c>
       <c r="CK12" t="inlineStr">
         <is>
-          <t>46.96</t>
+          <t>46.35</t>
         </is>
       </c>
       <c r="CL12" t="inlineStr">
         <is>
-          <t>4234</t>
+          <t>4215</t>
         </is>
       </c>
       <c r="CM12" t="inlineStr">
@@ -6198,17 +6198,17 @@
       </c>
       <c r="CP12" t="inlineStr">
         <is>
-          <t>46.2</t>
+          <t>45.8</t>
         </is>
       </c>
       <c r="CQ12" t="inlineStr">
         <is>
-          <t>46.2</t>
+          <t>46.0</t>
         </is>
       </c>
       <c r="CR12" t="inlineStr">
         <is>
-          <t>45.6</t>
+          <t>45.7</t>
         </is>
       </c>
       <c r="CS12" t="inlineStr">

--- a/Result/checksun_type/PET膜.xlsx
+++ b/Result/checksun_type/PET膜.xlsx
@@ -943,12 +943,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>55.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -958,7 +958,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>44.8</t>
+          <t>44.75</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-35.30</t>
+          <t>-40.37</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -1043,7 +1043,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-9.95</t>
+          <t>-10.05</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -1068,7 +1068,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>-0.0</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -1113,17 +1113,17 @@
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>2.95</t>
+          <t>2.16</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
@@ -1134,66 +1134,66 @@
       <c r="AO2" t="inlineStr"/>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>55</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>11.76</t>
+          <t>5.88</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>30.84</t>
+          <t>17.65</t>
         </is>
       </c>
       <c r="AT2" t="n">
-        <v>-0.44</v>
+        <v>-0.58</v>
       </c>
       <c r="AU2" t="n">
-        <v>-0.8</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>-2.69</t>
+          <t>-2.72</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>45.01000000000001</t>
         </is>
       </c>
       <c r="AY2" t="n">
-        <v>45.36</v>
+        <v>45.32</v>
       </c>
       <c r="AZ2" t="n">
-        <v>45.8</v>
+        <v>45.74</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>47.07</t>
+          <t>47.02</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-6.93</t>
+          <t>-8.36</t>
         </is>
       </c>
       <c r="BC2" t="n">
-        <v>-0.32</v>
+        <v>-0.33</v>
       </c>
       <c r="BD2" t="n">
-        <v>-0.3</v>
+        <v>-0.31</v>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1202,7 +1202,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>-107.05</t>
+          <t>-107.20</t>
         </is>
       </c>
       <c r="BG2" t="inlineStr">
@@ -1212,43 +1212,43 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>75279.96638655462</t>
+          <t>75179.87832167832</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>3366.0</t>
+          <t>2478.0</t>
         </is>
       </c>
       <c r="BJ2" t="n">
-        <v>4432.6</v>
+        <v>3959.2</v>
       </c>
       <c r="BK2" t="inlineStr">
         <is>
-          <t>6851.3</t>
+          <t>6640.1</t>
         </is>
       </c>
       <c r="BL2" t="n">
-        <v>10642.9</v>
+        <v>10394.42</v>
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>-2418</t>
+          <t>-2680</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>-507.2562798969379</t>
+          <t>-548.8075362680578</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
         <is>
-          <t>-608.6139563658217</t>
+          <t>-777.3394463092172</t>
         </is>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>3366.0</t>
+          <t>2478.0</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
@@ -1268,7 +1268,7 @@
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>-8.10</t>
+          <t>-8.21</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>6.17</t>
+          <t>6.18</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1338,7 +1338,7 @@
       </c>
       <c r="CH2" t="inlineStr">
         <is>
-          <t>10.11</t>
+          <t>10.1</t>
         </is>
       </c>
       <c r="CI2" t="inlineStr">
@@ -1353,12 +1353,12 @@
       </c>
       <c r="CK2" t="inlineStr">
         <is>
-          <t>46.35</t>
+          <t>45.55</t>
         </is>
       </c>
       <c r="CL2" t="inlineStr">
         <is>
-          <t>4215</t>
+          <t>4211</t>
         </is>
       </c>
       <c r="CM2" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="CP2" t="inlineStr">
         <is>
-          <t>44.8</t>
+          <t>44.7</t>
         </is>
       </c>
       <c r="CQ2" t="inlineStr">
@@ -1388,12 +1388,12 @@
       </c>
       <c r="CR2" t="inlineStr">
         <is>
-          <t>44.55</t>
+          <t>44.7</t>
         </is>
       </c>
       <c r="CS2" t="inlineStr">
         <is>
-          <t>44.8</t>
+          <t>44.75</t>
         </is>
       </c>
       <c r="CT2" t="inlineStr">
@@ -1425,12 +1425,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1440,7 +1440,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>44.8</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1450,7 +1450,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -1460,7 +1460,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>17.57</t>
+          <t>-35.30</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1525,7 +1525,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-9.55</t>
+          <t>-9.95</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1550,7 +1550,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -1595,17 +1595,17 @@
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>2.95</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
@@ -1616,63 +1616,63 @@
       <c r="AO3" t="inlineStr"/>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>55</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>35.29</t>
+          <t>11.76</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>45.1</t>
+          <t>30.84</t>
         </is>
       </c>
       <c r="AT3" t="n">
-        <v>0.02</v>
+        <v>-0.44</v>
       </c>
       <c r="AU3" t="n">
-        <v>-0.85</v>
+        <v>-0.8</v>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>-1.07</t>
+          <t>-0.96</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>-2.67</t>
+          <t>-2.69</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>44.98999999999999</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="AY3" t="n">
-        <v>45.38</v>
+        <v>45.36</v>
       </c>
       <c r="AZ3" t="n">
-        <v>45.86</v>
+        <v>45.8</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>47.12</t>
+          <t>47.07</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-4.09</t>
+          <t>-6.93</t>
         </is>
       </c>
       <c r="BC3" t="n">
-        <v>-0.31</v>
+        <v>-0.32</v>
       </c>
       <c r="BD3" t="n">
         <v>-0.3</v>
@@ -1684,7 +1684,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>-106.93</t>
+          <t>-107.05</t>
         </is>
       </c>
       <c r="BG3" t="inlineStr">
@@ -1694,43 +1694,43 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>75279.96638655462</t>
+          <t>75179.87832167832</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>3990.0</t>
+          <t>3366.0</t>
         </is>
       </c>
       <c r="BJ3" t="n">
-        <v>8019</v>
+        <v>4432.6</v>
       </c>
       <c r="BK3" t="inlineStr">
         <is>
-          <t>6820.6</t>
+          <t>6851.3</t>
         </is>
       </c>
       <c r="BL3" t="n">
-        <v>10934.42</v>
+        <v>10642.9</v>
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>1198</t>
+          <t>-2418</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>-488.82761144805</t>
+          <t>-507.2562798969379</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
         <is>
-          <t>-440.9841865764774</t>
+          <t>-608.6139563658217</t>
         </is>
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>3990.0</t>
+          <t>3366.0</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
@@ -1750,7 +1750,7 @@
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>-7.69</t>
+          <t>-8.10</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1795,7 +1795,7 @@
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
@@ -1810,7 +1810,7 @@
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>6.17</t>
+          <t>6.18</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="CH3" t="inlineStr">
         <is>
-          <t>10.11</t>
+          <t>10.1</t>
         </is>
       </c>
       <c r="CI3" t="inlineStr">
@@ -1835,12 +1835,12 @@
       </c>
       <c r="CK3" t="inlineStr">
         <is>
-          <t>46.35</t>
+          <t>45.55</t>
         </is>
       </c>
       <c r="CL3" t="inlineStr">
         <is>
-          <t>4215</t>
+          <t>4211</t>
         </is>
       </c>
       <c r="CM3" t="inlineStr">
@@ -1860,22 +1860,22 @@
       </c>
       <c r="CP3" t="inlineStr">
         <is>
-          <t>45.5</t>
+          <t>44.8</t>
         </is>
       </c>
       <c r="CQ3" t="inlineStr">
         <is>
-          <t>45.5</t>
+          <t>45.1</t>
         </is>
       </c>
       <c r="CR3" t="inlineStr">
         <is>
-          <t>44.6</t>
+          <t>44.55</t>
         </is>
       </c>
       <c r="CS3" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>44.8</t>
         </is>
       </c>
       <c r="CT3" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.44</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1922,7 +1922,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>45.2</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-0.89</t>
+          <t>-0.56</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1942,7 +1942,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>20.01</t>
+          <t>17.57</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -2007,7 +2007,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-9.15</t>
+          <t>-9.55</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -2032,7 +2032,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -2077,17 +2077,17 @@
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>3.07</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>-0.55</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
@@ -2098,66 +2098,66 @@
       <c r="AO4" t="inlineStr"/>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>55</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>45.45</t>
+          <t>35.29</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>45.1</t>
         </is>
       </c>
       <c r="AT4" t="n">
-        <v>0.22</v>
+        <v>0.02</v>
       </c>
       <c r="AU4" t="n">
-        <v>-0.58</v>
+        <v>-0.85</v>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>-1.27</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>-2.57</t>
+          <t>-2.67</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>45.1</t>
+          <t>44.98999999999999</t>
         </is>
       </c>
       <c r="AY4" t="n">
-        <v>45.36</v>
+        <v>45.38</v>
       </c>
       <c r="AZ4" t="n">
-        <v>45.95</v>
+        <v>45.86</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>47.16</t>
+          <t>47.12</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-4.49</t>
+          <t>-4.09</t>
         </is>
       </c>
       <c r="BC4" t="n">
         <v>-0.31</v>
       </c>
       <c r="BD4" t="n">
-        <v>-0.29</v>
+        <v>-0.3</v>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2166,7 +2166,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>-106.86</t>
+          <t>-106.93</t>
         </is>
       </c>
       <c r="BG4" t="inlineStr">
@@ -2176,43 +2176,43 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>75279.96638655462</t>
+          <t>75179.87832167832</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>3539.0</t>
+          <t>3990.0</t>
         </is>
       </c>
       <c r="BJ4" t="n">
-        <v>8163.8</v>
+        <v>8019</v>
       </c>
       <c r="BK4" t="inlineStr">
         <is>
-          <t>6802.5</t>
+          <t>6820.6</t>
         </is>
       </c>
       <c r="BL4" t="n">
-        <v>11065.56</v>
+        <v>10934.42</v>
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>1361</t>
+          <t>1198</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>-497.5264159701541</t>
+          <t>-488.82761144805</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>-252.6207944996822</t>
+          <t>-440.9841865764774</t>
         </is>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>3539.0</t>
+          <t>3990.0</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
@@ -2232,7 +2232,7 @@
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>-7.28</t>
+          <t>-7.69</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2277,22 +2277,22 @@
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>6.17</t>
+          <t>6.18</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2302,7 +2302,7 @@
       </c>
       <c r="CH4" t="inlineStr">
         <is>
-          <t>10.11</t>
+          <t>10.1</t>
         </is>
       </c>
       <c r="CI4" t="inlineStr">
@@ -2317,12 +2317,12 @@
       </c>
       <c r="CK4" t="inlineStr">
         <is>
-          <t>46.35</t>
+          <t>45.55</t>
         </is>
       </c>
       <c r="CL4" t="inlineStr">
         <is>
-          <t>4215</t>
+          <t>4211</t>
         </is>
       </c>
       <c r="CM4" t="inlineStr">
@@ -2342,22 +2342,22 @@
       </c>
       <c r="CP4" t="inlineStr">
         <is>
-          <t>45.05</t>
+          <t>45.5</t>
         </is>
       </c>
       <c r="CQ4" t="inlineStr">
         <is>
-          <t>45.6</t>
+          <t>45.5</t>
         </is>
       </c>
       <c r="CR4" t="inlineStr">
         <is>
-          <t>45.05</t>
+          <t>44.6</t>
         </is>
       </c>
       <c r="CS4" t="inlineStr">
         <is>
-          <t>45.2</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="CT4" t="inlineStr">
@@ -2389,12 +2389,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>143.0</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>45.3</t>
+          <t>45.2</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2414,7 +2414,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-1.12</t>
+          <t>-1.01</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -2424,7 +2424,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>41.55</t>
+          <t>20.01</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2489,7 +2489,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-8.94</t>
+          <t>-9.15</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2514,7 +2514,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -2559,17 +2559,17 @@
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>5.62</t>
+          <t>3.07</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>-0.55</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
@@ -2580,63 +2580,63 @@
       <c r="AO5" t="inlineStr"/>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>55</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>54.55</t>
+          <t>45.45</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>18.18</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AT5" t="n">
-        <v>0.51</v>
+        <v>0.22</v>
       </c>
       <c r="AU5" t="n">
-        <v>-0.8</v>
+        <v>-0.58</v>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>-1.32</t>
+          <t>-1.27</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>-2.47</t>
+          <t>-2.57</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>45.07000000000001</t>
+          <t>45.1</t>
         </is>
       </c>
       <c r="AY5" t="n">
-        <v>45.44</v>
+        <v>45.36</v>
       </c>
       <c r="AZ5" t="n">
-        <v>46.04</v>
+        <v>45.95</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>47.21</t>
+          <t>47.16</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-10.29</t>
+          <t>-4.49</t>
         </is>
       </c>
       <c r="BC5" t="n">
-        <v>-0.32</v>
+        <v>-0.31</v>
       </c>
       <c r="BD5" t="n">
         <v>-0.29</v>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>-106.78</t>
+          <t>-106.86</t>
         </is>
       </c>
       <c r="BG5" t="inlineStr">
@@ -2658,43 +2658,43 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>75279.96638655462</t>
+          <t>75179.87832167832</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>6423.0</t>
+          <t>3539.0</t>
         </is>
       </c>
       <c r="BJ5" t="n">
-        <v>9662.799999999999</v>
+        <v>8163.8</v>
       </c>
       <c r="BK5" t="inlineStr">
         <is>
-          <t>6826.5</t>
+          <t>6802.5</t>
         </is>
       </c>
       <c r="BL5" t="n">
-        <v>11523.86</v>
+        <v>11065.56</v>
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>2836</t>
+          <t>1361</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>-542.0547107829672</t>
+          <t>-497.5264159701541</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>73.8133654135845</t>
+          <t>-252.6207944996822</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>6423.0</t>
+          <t>3539.0</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
@@ -2714,7 +2714,7 @@
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>-7.08</t>
+          <t>-7.28</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2759,22 +2759,22 @@
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>6.17</t>
+          <t>6.18</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2784,7 +2784,7 @@
       </c>
       <c r="CH5" t="inlineStr">
         <is>
-          <t>10.11</t>
+          <t>10.1</t>
         </is>
       </c>
       <c r="CI5" t="inlineStr">
@@ -2799,12 +2799,12 @@
       </c>
       <c r="CK5" t="inlineStr">
         <is>
-          <t>46.35</t>
+          <t>45.55</t>
         </is>
       </c>
       <c r="CL5" t="inlineStr">
         <is>
-          <t>4215</t>
+          <t>4211</t>
         </is>
       </c>
       <c r="CM5" t="inlineStr">
@@ -2824,22 +2824,22 @@
       </c>
       <c r="CP5" t="inlineStr">
         <is>
-          <t>44.8</t>
+          <t>45.05</t>
         </is>
       </c>
       <c r="CQ5" t="inlineStr">
         <is>
-          <t>45.3</t>
+          <t>45.6</t>
         </is>
       </c>
       <c r="CR5" t="inlineStr">
         <is>
-          <t>44.75</t>
+          <t>45.05</t>
         </is>
       </c>
       <c r="CS5" t="inlineStr">
         <is>
-          <t>45.3</t>
+          <t>45.2</t>
         </is>
       </c>
       <c r="CT5" t="inlineStr">
@@ -2871,12 +2871,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>109.0</t>
+          <t>143.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2886,7 +2886,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>44.7</t>
+          <t>45.3</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2896,7 +2896,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>-1.23</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -2906,7 +2906,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>42.69</t>
+          <t>41.55</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-10.15</t>
+          <t>-8.94</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2996,7 +2996,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -3041,17 +3041,17 @@
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>4.28</t>
+          <t>5.62</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
@@ -3062,66 +3062,66 @@
       <c r="AO6" t="inlineStr"/>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>55</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>54.55</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>17.54</t>
+          <t>18.18</t>
         </is>
       </c>
       <c r="AT6" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="AU6" t="n">
         <v>-0.8</v>
       </c>
-      <c r="AU6" t="n">
-        <v>-1.02</v>
-      </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>-1.27</t>
+          <t>-1.32</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>-2.44</t>
+          <t>-2.47</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>45.06</t>
+          <t>45.07000000000001</t>
         </is>
       </c>
       <c r="AY6" t="n">
-        <v>45.52</v>
+        <v>45.44</v>
       </c>
       <c r="AZ6" t="n">
-        <v>46.11</v>
+        <v>46.04</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>47.26</t>
+          <t>47.21</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-21.20</t>
+          <t>-10.29</t>
         </is>
       </c>
       <c r="BC6" t="n">
-        <v>-0.34</v>
+        <v>-0.32</v>
       </c>
       <c r="BD6" t="n">
-        <v>-0.28</v>
+        <v>-0.29</v>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -3130,7 +3130,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>-106.61</t>
+          <t>-106.78</t>
         </is>
       </c>
       <c r="BG6" t="inlineStr">
@@ -3140,43 +3140,43 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>75279.96638655462</t>
+          <t>75179.87832167832</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>4845.0</t>
+          <t>6423.0</t>
         </is>
       </c>
       <c r="BJ6" t="n">
-        <v>9321</v>
+        <v>9662.799999999999</v>
       </c>
       <c r="BK6" t="inlineStr">
         <is>
-          <t>6532.2</t>
+          <t>6826.5</t>
         </is>
       </c>
       <c r="BL6" t="n">
-        <v>11521.76</v>
+        <v>11523.86</v>
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>2788</t>
+          <t>2836</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
         <is>
-          <t>-654.0307246368856</t>
+          <t>-542.0547107829672</t>
         </is>
       </c>
       <c r="BO6" t="inlineStr">
         <is>
-          <t>228.5116879534808</t>
+          <t>73.8133654135845</t>
         </is>
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>4845.0</t>
+          <t>6423.0</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
@@ -3196,7 +3196,7 @@
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>-8.31</t>
+          <t>-7.08</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>1.84</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>6.17</t>
+          <t>6.18</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -3266,7 +3266,7 @@
       </c>
       <c r="CH6" t="inlineStr">
         <is>
-          <t>10.11</t>
+          <t>10.1</t>
         </is>
       </c>
       <c r="CI6" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="CK6" t="inlineStr">
         <is>
-          <t>46.35</t>
+          <t>45.55</t>
         </is>
       </c>
       <c r="CL6" t="inlineStr">
         <is>
-          <t>4215</t>
+          <t>4211</t>
         </is>
       </c>
       <c r="CM6" t="inlineStr">
@@ -3306,22 +3306,22 @@
       </c>
       <c r="CP6" t="inlineStr">
         <is>
+          <t>44.8</t>
+        </is>
+      </c>
+      <c r="CQ6" t="inlineStr">
+        <is>
+          <t>45.3</t>
+        </is>
+      </c>
+      <c r="CR6" t="inlineStr">
+        <is>
           <t>44.75</t>
         </is>
       </c>
-      <c r="CQ6" t="inlineStr">
-        <is>
-          <t>44.75</t>
-        </is>
-      </c>
-      <c r="CR6" t="inlineStr">
-        <is>
-          <t>44.5</t>
-        </is>
-      </c>
       <c r="CS6" t="inlineStr">
         <is>
-          <t>44.7</t>
+          <t>45.3</t>
         </is>
       </c>
       <c r="CT6" t="inlineStr">
@@ -3353,12 +3353,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-1.8</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>478.0</t>
+          <t>109.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3368,7 +3368,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>44.75</t>
+          <t>44.7</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3388,7 +3388,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>40.89</t>
+          <t>42.69</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3453,7 +3453,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-10.05</t>
+          <t>-10.15</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -3523,17 +3523,17 @@
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>18.79</t>
+          <t>4.28</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
@@ -3544,12 +3544,12 @@
       <c r="AO7" t="inlineStr"/>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>55</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
@@ -3563,47 +3563,47 @@
         </is>
       </c>
       <c r="AT7" t="n">
-        <v>-1.04</v>
+        <v>-0.8</v>
       </c>
       <c r="AU7" t="n">
-        <v>-0.93</v>
+        <v>-1.02</v>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>-1.16</t>
+          <t>-1.27</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>-2.39</t>
+          <t>-2.44</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>45.21999999999999</t>
+          <t>45.06</t>
         </is>
       </c>
       <c r="AY7" t="n">
-        <v>45.64</v>
+        <v>45.52</v>
       </c>
       <c r="AZ7" t="n">
-        <v>46.18</v>
+        <v>46.11</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>47.31</t>
+          <t>47.26</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-14.07</t>
+          <t>-21.20</t>
         </is>
       </c>
       <c r="BC7" t="n">
-        <v>-0.31</v>
+        <v>-0.34</v>
       </c>
       <c r="BD7" t="n">
-        <v>-0.27</v>
+        <v>-0.28</v>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>-106.26</t>
+          <t>-106.61</t>
         </is>
       </c>
       <c r="BG7" t="inlineStr">
@@ -3622,43 +3622,43 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>75279.96638655462</t>
+          <t>75179.87832167832</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>21298.0</t>
+          <t>4845.0</t>
         </is>
       </c>
       <c r="BJ7" t="n">
-        <v>9270</v>
+        <v>9321</v>
       </c>
       <c r="BK7" t="inlineStr">
         <is>
-          <t>6579.4</t>
+          <t>6532.2</t>
         </is>
       </c>
       <c r="BL7" t="n">
-        <v>11878.36</v>
+        <v>11521.76</v>
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>2690</t>
+          <t>2788</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
         <is>
-          <t>-814.4929814714977</t>
+          <t>-654.0307246368856</t>
         </is>
       </c>
       <c r="BO7" t="inlineStr">
         <is>
-          <t>610.419588440709</t>
+          <t>228.5116879534808</t>
         </is>
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>21298.0</t>
+          <t>4845.0</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
@@ -3678,7 +3678,7 @@
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>-8.21</t>
+          <t>-8.31</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3723,12 +3723,12 @@
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
@@ -3738,7 +3738,7 @@
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>6.17</t>
+          <t>6.18</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3748,7 +3748,7 @@
       </c>
       <c r="CH7" t="inlineStr">
         <is>
-          <t>10.11</t>
+          <t>10.1</t>
         </is>
       </c>
       <c r="CI7" t="inlineStr">
@@ -3763,12 +3763,12 @@
       </c>
       <c r="CK7" t="inlineStr">
         <is>
-          <t>46.35</t>
+          <t>45.55</t>
         </is>
       </c>
       <c r="CL7" t="inlineStr">
         <is>
-          <t>4215</t>
+          <t>4211</t>
         </is>
       </c>
       <c r="CM7" t="inlineStr">
@@ -3788,22 +3788,22 @@
       </c>
       <c r="CP7" t="inlineStr">
         <is>
-          <t>44.55</t>
+          <t>44.75</t>
         </is>
       </c>
       <c r="CQ7" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>44.75</t>
         </is>
       </c>
       <c r="CR7" t="inlineStr">
         <is>
-          <t>44.3</t>
+          <t>44.5</t>
         </is>
       </c>
       <c r="CS7" t="inlineStr">
         <is>
-          <t>44.75</t>
+          <t>44.7</t>
         </is>
       </c>
       <c r="CT7" t="inlineStr">
@@ -3835,12 +3835,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>-1.8</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>478.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3850,7 +3850,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>45.55</t>
+          <t>44.75</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-1.67</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -3870,7 +3870,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>9.71</t>
+          <t>40.89</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3935,7 +3935,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-8.44</t>
+          <t>-10.05</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3960,7 +3960,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -4005,17 +4005,17 @@
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>4.05</t>
+          <t>18.79</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>-1.09</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
@@ -4026,17 +4026,17 @@
       <c r="AO8" t="inlineStr"/>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>55</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>52.63</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -4045,47 +4045,47 @@
         </is>
       </c>
       <c r="AT8" t="n">
-        <v>0.26</v>
+        <v>-1.04</v>
       </c>
       <c r="AU8" t="n">
-        <v>-0.78</v>
+        <v>-0.93</v>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>-1.04</t>
+          <t>-1.16</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>-2.32</t>
+          <t>-2.39</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>45.42999999999999</t>
+          <t>45.21999999999999</t>
         </is>
       </c>
       <c r="AY8" t="n">
-        <v>45.78</v>
+        <v>45.64</v>
       </c>
       <c r="AZ8" t="n">
-        <v>46.27</v>
+        <v>46.18</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>47.37</t>
+          <t>47.31</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-14.07</t>
         </is>
       </c>
       <c r="BC8" t="n">
-        <v>-0.26</v>
+        <v>-0.31</v>
       </c>
       <c r="BD8" t="n">
-        <v>-0.26</v>
+        <v>-0.27</v>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -4094,7 +4094,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>-106.04</t>
+          <t>-106.26</t>
         </is>
       </c>
       <c r="BG8" t="inlineStr">
@@ -4104,43 +4104,43 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>75279.96638655462</t>
+          <t>75179.87832167832</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>4714.0</t>
+          <t>21298.0</t>
         </is>
       </c>
       <c r="BJ8" t="n">
-        <v>5622.2</v>
+        <v>9270</v>
       </c>
       <c r="BK8" t="inlineStr">
         <is>
-          <t>5124.4</t>
+          <t>6579.4</t>
         </is>
       </c>
       <c r="BL8" t="n">
-        <v>11707.74</v>
+        <v>11878.36</v>
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>497</t>
+          <t>2690</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
         <is>
-          <t>-1073.567994182808</t>
+          <t>-814.4929814714977</t>
         </is>
       </c>
       <c r="BO8" t="inlineStr">
         <is>
-          <t>-628.6198247361344</t>
+          <t>610.419588440709</t>
         </is>
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>4714.0</t>
+          <t>21298.0</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
@@ -4160,7 +4160,7 @@
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>-6.56</t>
+          <t>-8.21</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -4205,22 +4205,22 @@
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>6.17</t>
+          <t>6.18</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -4230,7 +4230,7 @@
       </c>
       <c r="CH8" t="inlineStr">
         <is>
-          <t>10.11</t>
+          <t>10.1</t>
         </is>
       </c>
       <c r="CI8" t="inlineStr">
@@ -4245,12 +4245,12 @@
       </c>
       <c r="CK8" t="inlineStr">
         <is>
-          <t>46.35</t>
+          <t>45.55</t>
         </is>
       </c>
       <c r="CL8" t="inlineStr">
         <is>
-          <t>4215</t>
+          <t>4211</t>
         </is>
       </c>
       <c r="CM8" t="inlineStr">
@@ -4270,22 +4270,22 @@
       </c>
       <c r="CP8" t="inlineStr">
         <is>
-          <t>45.65</t>
+          <t>44.55</t>
         </is>
       </c>
       <c r="CQ8" t="inlineStr">
         <is>
-          <t>46.3</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="CR8" t="inlineStr">
         <is>
-          <t>45.3</t>
+          <t>44.3</t>
         </is>
       </c>
       <c r="CS8" t="inlineStr">
         <is>
-          <t>45.55</t>
+          <t>44.75</t>
         </is>
       </c>
       <c r="CT8" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>246.0</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -4332,172 +4332,172 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
+          <t>45.55</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>-1.79</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>9.71</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>2025-09-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>2025-09-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>2025-03-06 00:00:00</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>2025-03-10 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>51.1</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>49.75</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>57.7</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>56.5</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>-8.44</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>-9.56</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025/05/23</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>51.4</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>0.02</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>2025/10/14</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>44.35</t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>2025/06/30</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>48.2</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>2025/12/08</t>
+        </is>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
           <t>45.05</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>-0.56</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>8.33</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>2025-09-02 00:00:00</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>2025-09-12 00:00:00</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>2025-03-06 00:00:00</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>2025-03-10 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>51.1</t>
-        </is>
-      </c>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>49.75</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>57.7</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>56.5</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>-9.45</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>-9.56</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>2025/05/23</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>51.4</t>
-        </is>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>-0.03</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>2025/10/14</t>
-        </is>
-      </c>
-      <c r="AD9" t="inlineStr">
-        <is>
-          <t>44.35</t>
-        </is>
-      </c>
-      <c r="AE9" t="inlineStr">
-        <is>
-          <t>2025/06/30</t>
-        </is>
-      </c>
-      <c r="AF9" t="inlineStr">
-        <is>
-          <t>48.2</t>
-        </is>
-      </c>
-      <c r="AG9" t="inlineStr">
-        <is>
-          <t>2025/12/08</t>
-        </is>
-      </c>
-      <c r="AH9" t="inlineStr">
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>2025/11/19</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
         <is>
           <t>45.05</t>
         </is>
       </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>2025/11/19</t>
-        </is>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>45.05</t>
-        </is>
-      </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>9.67</t>
+          <t>4.05</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>-1.09</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
@@ -4508,63 +4508,63 @@
       <c r="AO9" t="inlineStr"/>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>55</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>52.63</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>9.52</t>
+          <t>17.54</t>
         </is>
       </c>
       <c r="AT9" t="n">
-        <v>-0.95</v>
+        <v>0.26</v>
       </c>
       <c r="AU9" t="n">
-        <v>-0.87</v>
+        <v>-0.78</v>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>-0.97</t>
+          <t>-1.04</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>-2.29</t>
+          <t>-2.32</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>45.48</t>
+          <t>45.42999999999999</t>
         </is>
       </c>
       <c r="AY9" t="n">
-        <v>45.88</v>
+        <v>45.78</v>
       </c>
       <c r="AZ9" t="n">
-        <v>46.32</v>
+        <v>46.27</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>47.41</t>
+          <t>47.37</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-7.02</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="BC9" t="n">
-        <v>-0.28</v>
+        <v>-0.26</v>
       </c>
       <c r="BD9" t="n">
         <v>-0.26</v>
@@ -4586,43 +4586,43 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>75279.96638655462</t>
+          <t>75179.87832167832</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>11034.0</t>
+          <t>4714.0</t>
         </is>
       </c>
       <c r="BJ9" t="n">
-        <v>5441.2</v>
+        <v>5622.2</v>
       </c>
       <c r="BK9" t="inlineStr">
         <is>
-          <t>5022.6</t>
+          <t>5124.4</t>
         </is>
       </c>
       <c r="BL9" t="n">
-        <v>11858.6</v>
+        <v>11707.74</v>
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>418</t>
+          <t>497</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
         <is>
-          <t>-1154.46766135493</t>
+          <t>-1073.567994182808</t>
         </is>
       </c>
       <c r="BO9" t="inlineStr">
         <is>
-          <t>-599.3682783910481</t>
+          <t>-628.6198247361344</t>
         </is>
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>11034.0</t>
+          <t>4714.0</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
@@ -4642,7 +4642,7 @@
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>-7.59</t>
+          <t>-6.56</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4687,22 +4687,22 @@
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>6.17</t>
+          <t>6.18</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4712,7 +4712,7 @@
       </c>
       <c r="CH9" t="inlineStr">
         <is>
-          <t>10.11</t>
+          <t>10.1</t>
         </is>
       </c>
       <c r="CI9" t="inlineStr">
@@ -4727,12 +4727,12 @@
       </c>
       <c r="CK9" t="inlineStr">
         <is>
-          <t>46.35</t>
+          <t>45.55</t>
         </is>
       </c>
       <c r="CL9" t="inlineStr">
         <is>
-          <t>4215</t>
+          <t>4211</t>
         </is>
       </c>
       <c r="CM9" t="inlineStr">
@@ -4752,22 +4752,22 @@
       </c>
       <c r="CP9" t="inlineStr">
         <is>
-          <t>45.25</t>
+          <t>45.65</t>
         </is>
       </c>
       <c r="CQ9" t="inlineStr">
         <is>
-          <t>45.45</t>
+          <t>46.3</t>
         </is>
       </c>
       <c r="CR9" t="inlineStr">
         <is>
-          <t>44.5</t>
+          <t>45.3</t>
         </is>
       </c>
       <c r="CS9" t="inlineStr">
         <is>
-          <t>45.05</t>
+          <t>45.55</t>
         </is>
       </c>
       <c r="CT9" t="inlineStr">
@@ -4789,7 +4789,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>【d2】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4799,12 +4799,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-0.55</t>
+          <t>-0.44</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>104.0</t>
+          <t>246.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4814,7 +4814,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>45.25</t>
+          <t>45.05</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4824,7 +4824,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -4834,7 +4834,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-8.48</t>
+          <t>8.33</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4899,7 +4899,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-9.05</t>
+          <t>-9.45</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4969,17 +4969,17 @@
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>4.09</t>
+          <t>9.67</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
@@ -4990,12 +4990,12 @@
       <c r="AO10" t="inlineStr"/>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>55</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
@@ -5005,51 +5005,51 @@
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>37.52</t>
+          <t>9.52</t>
         </is>
       </c>
       <c r="AT10" t="n">
-        <v>-0.83</v>
+        <v>-0.95</v>
       </c>
       <c r="AU10" t="n">
-        <v>-0.75</v>
+        <v>-0.87</v>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>-0.9</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>-2.24</t>
+          <t>-2.29</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>45.63</t>
+          <t>45.48</t>
         </is>
       </c>
       <c r="AY10" t="n">
-        <v>45.98</v>
+        <v>45.88</v>
       </c>
       <c r="AZ10" t="n">
-        <v>46.39</v>
+        <v>46.32</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>47.46</t>
+          <t>47.41</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>3.73</t>
+          <t>-7.02</t>
         </is>
       </c>
       <c r="BC10" t="n">
-        <v>-0.24</v>
+        <v>-0.28</v>
       </c>
       <c r="BD10" t="n">
-        <v>-0.25</v>
+        <v>-0.26</v>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -5058,7 +5058,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>-105.93</t>
+          <t>-106.04</t>
         </is>
       </c>
       <c r="BG10" t="inlineStr">
@@ -5068,43 +5068,43 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>75279.96638655462</t>
+          <t>75179.87832167832</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>4714.0</t>
+          <t>11034.0</t>
         </is>
       </c>
       <c r="BJ10" t="n">
-        <v>3990.2</v>
+        <v>5441.2</v>
       </c>
       <c r="BK10" t="inlineStr">
         <is>
-          <t>4360.0</t>
+          <t>5022.6</t>
         </is>
       </c>
       <c r="BL10" t="n">
-        <v>11948.92</v>
+        <v>11858.6</v>
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>-369</t>
+          <t>418</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
         <is>
-          <t>-1255.394821893818</t>
+          <t>-1154.46766135493</t>
         </is>
       </c>
       <c r="BO10" t="inlineStr">
         <is>
-          <t>-1213.317202241243</t>
+          <t>-599.3682783910481</t>
         </is>
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>4714.0</t>
+          <t>11034.0</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
@@ -5124,7 +5124,7 @@
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>-7.18</t>
+          <t>-7.59</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -5169,7 +5169,7 @@
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
@@ -5184,7 +5184,7 @@
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>6.17</t>
+          <t>6.18</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -5194,7 +5194,7 @@
       </c>
       <c r="CH10" t="inlineStr">
         <is>
-          <t>10.11</t>
+          <t>10.1</t>
         </is>
       </c>
       <c r="CI10" t="inlineStr">
@@ -5209,12 +5209,12 @@
       </c>
       <c r="CK10" t="inlineStr">
         <is>
-          <t>46.35</t>
+          <t>45.55</t>
         </is>
       </c>
       <c r="CL10" t="inlineStr">
         <is>
-          <t>4215</t>
+          <t>4211</t>
         </is>
       </c>
       <c r="CM10" t="inlineStr">
@@ -5234,22 +5234,22 @@
       </c>
       <c r="CP10" t="inlineStr">
         <is>
-          <t>45.5</t>
+          <t>45.25</t>
         </is>
       </c>
       <c r="CQ10" t="inlineStr">
         <is>
-          <t>45.5</t>
+          <t>45.45</t>
         </is>
       </c>
       <c r="CR10" t="inlineStr">
         <is>
-          <t>44.9</t>
+          <t>44.5</t>
         </is>
       </c>
       <c r="CS10" t="inlineStr">
         <is>
-          <t>45.25</t>
+          <t>45.05</t>
         </is>
       </c>
       <c r="CT10" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>-0.55</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>104.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -5296,7 +5296,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>45.5</t>
+          <t>45.25</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -5306,7 +5306,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-1.56</t>
+          <t>-1.12</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -5316,7 +5316,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-20.03</t>
+          <t>-8.48</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -5381,7 +5381,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-8.54</t>
+          <t>-9.05</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -5406,7 +5406,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -5451,17 +5451,17 @@
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>3.97</t>
+          <t>4.09</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
@@ -5472,66 +5472,66 @@
       <c r="AO11" t="inlineStr"/>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>55</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>28.57</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>65.52</t>
+          <t>37.52</t>
         </is>
       </c>
       <c r="AT11" t="n">
-        <v>-0.61</v>
+        <v>-0.83</v>
       </c>
       <c r="AU11" t="n">
-        <v>-0.58</v>
+        <v>-0.75</v>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>-0.89</t>
+          <t>-0.9</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>-2.14</t>
+          <t>-2.24</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>45.77999999999999</t>
+          <t>45.63</t>
         </is>
       </c>
       <c r="AY11" t="n">
-        <v>46.04</v>
+        <v>45.98</v>
       </c>
       <c r="AZ11" t="n">
-        <v>46.46</v>
+        <v>46.39</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>47.48</t>
+          <t>47.46</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>14.06</t>
+          <t>3.73</t>
         </is>
       </c>
       <c r="BC11" t="n">
-        <v>-0.22</v>
+        <v>-0.24</v>
       </c>
       <c r="BD11" t="n">
-        <v>-0.26</v>
+        <v>-0.25</v>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5540,7 +5540,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>-105.99</t>
+          <t>-105.93</t>
         </is>
       </c>
       <c r="BG11" t="inlineStr">
@@ -5550,43 +5550,43 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>75279.96638655462</t>
+          <t>75179.87832167832</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>4590.0</t>
+          <t>4714.0</t>
         </is>
       </c>
       <c r="BJ11" t="n">
-        <v>3743.4</v>
+        <v>3990.2</v>
       </c>
       <c r="BK11" t="inlineStr">
         <is>
-          <t>4681.2</t>
+          <t>4360.0</t>
         </is>
       </c>
       <c r="BL11" t="n">
-        <v>12007.9</v>
+        <v>11948.92</v>
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>-937</t>
+          <t>-369</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
         <is>
-          <t>-1263.045298194286</t>
+          <t>-1255.394821893818</t>
         </is>
       </c>
       <c r="BO11" t="inlineStr">
         <is>
-          <t>-1369.911479090048</t>
+          <t>-1213.317202241243</t>
         </is>
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>4590.0</t>
+          <t>4714.0</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
@@ -5606,7 +5606,7 @@
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>-6.67</t>
+          <t>-7.18</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5651,7 +5651,7 @@
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
@@ -5661,12 +5661,12 @@
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>6.17</t>
+          <t>6.18</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
@@ -5676,7 +5676,7 @@
       </c>
       <c r="CH11" t="inlineStr">
         <is>
-          <t>10.11</t>
+          <t>10.1</t>
         </is>
       </c>
       <c r="CI11" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="CK11" t="inlineStr">
         <is>
-          <t>46.35</t>
+          <t>45.55</t>
         </is>
       </c>
       <c r="CL11" t="inlineStr">
         <is>
-          <t>4215</t>
+          <t>4211</t>
         </is>
       </c>
       <c r="CM11" t="inlineStr">
@@ -5716,22 +5716,22 @@
       </c>
       <c r="CP11" t="inlineStr">
         <is>
-          <t>46.0</t>
+          <t>45.5</t>
         </is>
       </c>
       <c r="CQ11" t="inlineStr">
         <is>
-          <t>46.05</t>
+          <t>45.5</t>
         </is>
       </c>
       <c r="CR11" t="inlineStr">
         <is>
-          <t>45.15</t>
+          <t>44.9</t>
         </is>
       </c>
       <c r="CS11" t="inlineStr">
         <is>
-          <t>45.5</t>
+          <t>45.25</t>
         </is>
       </c>
       <c r="CT11" t="inlineStr">
@@ -5763,42 +5763,42 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
+          <t>-0.65</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>101.0</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>45.5</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>-1.68</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>67.0</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>45.8</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>-2.23</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-14.39</t>
+          <t>-20.03</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5863,7 +5863,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-7.94</t>
+          <t>-8.54</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5888,7 +5888,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -5933,17 +5933,17 @@
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>2.63</t>
+          <t>3.97</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
@@ -5954,63 +5954,63 @@
       <c r="AO12" t="inlineStr"/>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>55</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>28.57</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>65.52</t>
         </is>
       </c>
       <c r="AT12" t="n">
-        <v>-0.17</v>
+        <v>-0.61</v>
       </c>
       <c r="AU12" t="n">
-        <v>-0.52</v>
+        <v>-0.58</v>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>-0.87</t>
+          <t>-0.89</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>-2.06</t>
+          <t>-2.14</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>45.88</t>
+          <t>45.77999999999999</t>
         </is>
       </c>
       <c r="AY12" t="n">
-        <v>46.12</v>
+        <v>46.04</v>
       </c>
       <c r="AZ12" t="n">
-        <v>46.52</v>
+        <v>46.46</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>47.5</t>
+          <t>47.48</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>20.22</t>
+          <t>14.06</t>
         </is>
       </c>
       <c r="BC12" t="n">
-        <v>-0.21</v>
+        <v>-0.22</v>
       </c>
       <c r="BD12" t="n">
         <v>-0.26</v>
@@ -6022,7 +6022,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>-106.20</t>
+          <t>-105.99</t>
         </is>
       </c>
       <c r="BG12" t="inlineStr">
@@ -6032,43 +6032,43 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>75279.96638655462</t>
+          <t>75179.87832167832</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
         <is>
-          <t>3059.0</t>
+          <t>4590.0</t>
         </is>
       </c>
       <c r="BJ12" t="n">
-        <v>3888.8</v>
+        <v>3743.4</v>
       </c>
       <c r="BK12" t="inlineStr">
         <is>
-          <t>4542.6</t>
+          <t>4681.2</t>
         </is>
       </c>
       <c r="BL12" t="n">
-        <v>12062.18</v>
+        <v>12007.9</v>
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>-653</t>
+          <t>-937</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
         <is>
-          <t>-1243.615083485966</t>
+          <t>-1263.045298194286</t>
         </is>
       </c>
       <c r="BO12" t="inlineStr">
         <is>
-          <t>-1531.406464620841</t>
+          <t>-1369.911479090048</t>
         </is>
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>3059.0</t>
+          <t>4590.0</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
@@ -6088,7 +6088,7 @@
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>-6.05</t>
+          <t>-6.67</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -6133,7 +6133,7 @@
       </c>
       <c r="CC12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD12" t="inlineStr">
@@ -6143,12 +6143,12 @@
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>6.17</t>
+          <t>6.18</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
@@ -6158,7 +6158,7 @@
       </c>
       <c r="CH12" t="inlineStr">
         <is>
-          <t>10.11</t>
+          <t>10.1</t>
         </is>
       </c>
       <c r="CI12" t="inlineStr">
@@ -6173,12 +6173,12 @@
       </c>
       <c r="CK12" t="inlineStr">
         <is>
-          <t>46.35</t>
+          <t>45.55</t>
         </is>
       </c>
       <c r="CL12" t="inlineStr">
         <is>
-          <t>4215</t>
+          <t>4211</t>
         </is>
       </c>
       <c r="CM12" t="inlineStr">
@@ -6198,22 +6198,22 @@
       </c>
       <c r="CP12" t="inlineStr">
         <is>
-          <t>45.8</t>
+          <t>46.0</t>
         </is>
       </c>
       <c r="CQ12" t="inlineStr">
         <is>
-          <t>46.0</t>
+          <t>46.05</t>
         </is>
       </c>
       <c r="CR12" t="inlineStr">
         <is>
-          <t>45.7</t>
+          <t>45.15</t>
         </is>
       </c>
       <c r="CS12" t="inlineStr">
         <is>
-          <t>45.8</t>
+          <t>45.5</t>
         </is>
       </c>
       <c r="CT12" t="inlineStr">

--- a/Result/checksun_type/PET膜.xlsx
+++ b/Result/checksun_type/PET膜.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CV12"/>
+  <dimension ref="A1:CW12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -611,320 +611,325 @@
       </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
+          <t>voc_cross_d</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
           <t>日期</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>量能</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>價能</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>cond_entry</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>text_desc</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>盤後量</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>成交量</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>%K</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>%D</t>
         </is>
       </c>
-      <c r="AT1" s="1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>MA5_%</t>
         </is>
       </c>
-      <c r="AU1" s="1" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
         <is>
           <t>均價_%</t>
         </is>
       </c>
-      <c r="AV1" s="1" t="inlineStr">
+      <c r="AW1" s="1" t="inlineStr">
         <is>
           <t>均價long_%</t>
         </is>
       </c>
-      <c r="AW1" s="1" t="inlineStr">
+      <c r="AX1" s="1" t="inlineStr">
         <is>
           <t>均價longlong_%</t>
         </is>
       </c>
-      <c r="AX1" s="1" t="inlineStr">
+      <c r="AY1" s="1" t="inlineStr">
         <is>
           <t>MA_short</t>
         </is>
       </c>
-      <c r="AY1" s="1" t="inlineStr">
+      <c r="AZ1" s="1" t="inlineStr">
         <is>
           <t>MA_long</t>
         </is>
       </c>
-      <c r="AZ1" s="1" t="inlineStr">
+      <c r="BA1" s="1" t="inlineStr">
         <is>
           <t>MA_longlong</t>
         </is>
       </c>
-      <c r="BA1" s="1" t="inlineStr">
+      <c r="BB1" s="1" t="inlineStr">
         <is>
           <t>MA_longlonglong</t>
         </is>
       </c>
-      <c r="BB1" s="1" t="inlineStr">
+      <c r="BC1" s="1" t="inlineStr">
         <is>
           <t>MACD_%</t>
         </is>
       </c>
-      <c r="BC1" s="1" t="inlineStr">
+      <c r="BD1" s="1" t="inlineStr">
         <is>
           <t>MACD</t>
         </is>
       </c>
-      <c r="BD1" s="1" t="inlineStr">
+      <c r="BE1" s="1" t="inlineStr">
         <is>
           <t>MACD-SL</t>
         </is>
       </c>
-      <c r="BE1" s="1" t="inlineStr">
+      <c r="BF1" s="1" t="inlineStr">
         <is>
           <t>MACD-SL_max</t>
         </is>
       </c>
-      <c r="BF1" s="1" t="inlineStr">
+      <c r="BG1" s="1" t="inlineStr">
         <is>
           <t>MACDSL_%</t>
         </is>
       </c>
-      <c r="BG1" s="1" t="inlineStr">
+      <c r="BH1" s="1" t="inlineStr">
         <is>
           <t>MACD_last_cross_date</t>
         </is>
       </c>
-      <c r="BH1" s="1" t="inlineStr">
+      <